--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B2" t="n">
-        <v>299.2746539241452</v>
+        <v>301.4039344978193</v>
       </c>
       <c r="C2" t="n">
-        <v>301.7767742987404</v>
+        <v>304.1317481949604</v>
       </c>
       <c r="D2" t="n">
-        <v>297.9990690164523</v>
+        <v>301.4039344978193</v>
       </c>
       <c r="E2" t="n">
-        <v>301.1488037109375</v>
+        <v>303.1014404296875</v>
       </c>
       <c r="F2" t="n">
-        <v>6846700</v>
+        <v>7122000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B3" t="n">
-        <v>301.403964844485</v>
+        <v>304.1807788708881</v>
       </c>
       <c r="C3" t="n">
-        <v>304.1317788162744</v>
+        <v>305.0638783689902</v>
       </c>
       <c r="D3" t="n">
-        <v>301.403964844485</v>
+        <v>301.3646583866889</v>
       </c>
       <c r="E3" t="n">
-        <v>303.1014709472656</v>
+        <v>303.385986328125</v>
       </c>
       <c r="F3" t="n">
-        <v>7122000</v>
+        <v>10525600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B4" t="n">
-        <v>304.1807788708881</v>
+        <v>304.563492987762</v>
       </c>
       <c r="C4" t="n">
-        <v>305.0638783689902</v>
+        <v>307.0361777394413</v>
       </c>
       <c r="D4" t="n">
-        <v>301.3646583866889</v>
+        <v>302.973877849489</v>
       </c>
       <c r="E4" t="n">
-        <v>303.385986328125</v>
+        <v>305.89794921875</v>
       </c>
       <c r="F4" t="n">
-        <v>10525600</v>
+        <v>8657800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B5" t="n">
-        <v>304.563492987762</v>
+        <v>305.9372178866198</v>
       </c>
       <c r="C5" t="n">
-        <v>307.0361777394413</v>
+        <v>307.556238792954</v>
       </c>
       <c r="D5" t="n">
-        <v>302.973877849489</v>
+        <v>303.7981171700278</v>
       </c>
       <c r="E5" t="n">
-        <v>305.89794921875</v>
+        <v>307.3501892089844</v>
       </c>
       <c r="F5" t="n">
-        <v>8657800</v>
+        <v>8050700</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B6" t="n">
-        <v>305.9372178866198</v>
+        <v>307.7132209495945</v>
       </c>
       <c r="C6" t="n">
-        <v>307.556238792954</v>
+        <v>309.8719053836384</v>
       </c>
       <c r="D6" t="n">
-        <v>303.7981171700278</v>
+        <v>303.3173070986313</v>
       </c>
       <c r="E6" t="n">
-        <v>307.3501892089844</v>
+        <v>308.8710632324219</v>
       </c>
       <c r="F6" t="n">
-        <v>8050700</v>
+        <v>23568600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B7" t="n">
-        <v>307.7132209495945</v>
+        <v>303.9845245259009</v>
       </c>
       <c r="C7" t="n">
-        <v>309.8719053836384</v>
+        <v>307.8113389670314</v>
       </c>
       <c r="D7" t="n">
-        <v>303.3173070986313</v>
+        <v>303.7490393091097</v>
       </c>
       <c r="E7" t="n">
-        <v>308.8710632324219</v>
+        <v>306.5749816894531</v>
       </c>
       <c r="F7" t="n">
-        <v>23568600</v>
+        <v>7520200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B8" t="n">
-        <v>303.9845245259009</v>
+        <v>305.9666409066948</v>
       </c>
       <c r="C8" t="n">
-        <v>307.8113389670314</v>
+        <v>310.3723467544506</v>
       </c>
       <c r="D8" t="n">
-        <v>303.7490393091097</v>
+        <v>304.7498973520222</v>
       </c>
       <c r="E8" t="n">
-        <v>306.5749816894531</v>
+        <v>306.8693542480469</v>
       </c>
       <c r="F8" t="n">
-        <v>7520200</v>
+        <v>8584400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B9" t="n">
-        <v>305.9666409066948</v>
+        <v>308.154769837798</v>
       </c>
       <c r="C9" t="n">
-        <v>310.3723467544506</v>
+        <v>310.6372765145315</v>
       </c>
       <c r="D9" t="n">
-        <v>304.7498973520222</v>
+        <v>305.8194713781714</v>
       </c>
       <c r="E9" t="n">
-        <v>306.8693542480469</v>
+        <v>307.53662109375</v>
       </c>
       <c r="F9" t="n">
-        <v>8584400</v>
+        <v>7310500</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B10" t="n">
-        <v>308.154769837798</v>
+        <v>308.2234768510796</v>
       </c>
       <c r="C10" t="n">
-        <v>310.6372765145315</v>
+        <v>309.7247551863121</v>
       </c>
       <c r="D10" t="n">
-        <v>305.8194713781714</v>
+        <v>305.947019653492</v>
       </c>
       <c r="E10" t="n">
-        <v>307.53662109375</v>
+        <v>307.5660705566406</v>
       </c>
       <c r="F10" t="n">
-        <v>7310500</v>
+        <v>7083200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B11" t="n">
-        <v>308.2234462682717</v>
+        <v>308.988785738579</v>
       </c>
       <c r="C11" t="n">
-        <v>309.7247244545431</v>
+        <v>311.8441636854759</v>
       </c>
       <c r="D11" t="n">
-        <v>305.9469892965607</v>
+        <v>307.8113297451866</v>
       </c>
       <c r="E11" t="n">
-        <v>307.5660400390625</v>
+        <v>310.1270141601562</v>
       </c>
       <c r="F11" t="n">
-        <v>7083200</v>
+        <v>7258100</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B12" t="n">
-        <v>308.988785738579</v>
+        <v>311.1082857354447</v>
       </c>
       <c r="C12" t="n">
-        <v>311.8441636854759</v>
+        <v>312.0404647281687</v>
       </c>
       <c r="D12" t="n">
-        <v>307.8113297451866</v>
+        <v>307.7721150397051</v>
       </c>
       <c r="E12" t="n">
-        <v>310.1270141601562</v>
+        <v>309.7640075683594</v>
       </c>
       <c r="F12" t="n">
-        <v>7258100</v>
+        <v>6462400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B13" t="n">
-        <v>311.1082550854298</v>
+        <v>310.3134645283819</v>
       </c>
       <c r="C13" t="n">
-        <v>312.0404339863167</v>
+        <v>311.4516930034957</v>
       </c>
       <c r="D13" t="n">
-        <v>307.7720847183659</v>
+        <v>304.288708108424</v>
       </c>
       <c r="E13" t="n">
-        <v>309.7639770507812</v>
+        <v>309.5088500976562</v>
       </c>
       <c r="F13" t="n">
-        <v>6462400</v>
+        <v>11823300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B14" t="n">
-        <v>310.3134645283819</v>
+        <v>308.0763169713923</v>
       </c>
       <c r="C14" t="n">
-        <v>311.4516930034957</v>
+        <v>308.6846738574029</v>
       </c>
       <c r="D14" t="n">
-        <v>304.288708108424</v>
+        <v>301.6394603311547</v>
       </c>
       <c r="E14" t="n">
-        <v>309.5088500976562</v>
+        <v>304.8775024414062</v>
       </c>
       <c r="F14" t="n">
-        <v>11823300</v>
+        <v>9235200</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B15" t="n">
-        <v>308.0762861336198</v>
+        <v>304.1808160870063</v>
       </c>
       <c r="C15" t="n">
-        <v>308.6846429587351</v>
+        <v>304.7303016172636</v>
       </c>
       <c r="D15" t="n">
-        <v>301.6394301376976</v>
+        <v>300.393288685967</v>
       </c>
       <c r="E15" t="n">
-        <v>304.8774719238281</v>
+        <v>301.7767944335938</v>
       </c>
       <c r="F15" t="n">
-        <v>9235200</v>
+        <v>7600000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B16" t="n">
-        <v>304.1808160870063</v>
+        <v>302.7188095956571</v>
       </c>
       <c r="C16" t="n">
-        <v>304.7303016172636</v>
+        <v>305.809673335546</v>
       </c>
       <c r="D16" t="n">
-        <v>300.393288685967</v>
+        <v>302.4244230832239</v>
       </c>
       <c r="E16" t="n">
-        <v>301.7767944335938</v>
+        <v>304.2102661132812</v>
       </c>
       <c r="F16" t="n">
-        <v>7600000</v>
+        <v>6029900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,25 +859,25 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B17" t="n">
-        <v>302.718779227698</v>
+        <v>305.8371035459471</v>
       </c>
       <c r="C17" t="n">
-        <v>305.8096426575195</v>
+        <v>307.3851288987199</v>
       </c>
       <c r="D17" t="n">
-        <v>302.4243927447969</v>
+        <v>300.8578215934895</v>
       </c>
       <c r="E17" t="n">
-        <v>304.2102355957031</v>
+        <v>304.8511047363281</v>
       </c>
       <c r="F17" t="n">
-        <v>6029900</v>
+        <v>7214500</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -885,25 +885,25 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B18" t="n">
-        <v>305.8371035459471</v>
+        <v>305.0187502270194</v>
       </c>
       <c r="C18" t="n">
-        <v>307.3851288987199</v>
+        <v>305.6695130787729</v>
       </c>
       <c r="D18" t="n">
-        <v>300.8578215934895</v>
+        <v>300.4338615931582</v>
       </c>
       <c r="E18" t="n">
-        <v>304.8511047363281</v>
+        <v>303.3819885253906</v>
       </c>
       <c r="F18" t="n">
-        <v>7214500</v>
+        <v>8454200</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B19" t="n">
-        <v>305.0187502270194</v>
+        <v>303.894722712774</v>
       </c>
       <c r="C19" t="n">
-        <v>305.6695130787729</v>
+        <v>304.4567493262524</v>
       </c>
       <c r="D19" t="n">
-        <v>300.4338615931582</v>
+        <v>299.2999640741864</v>
       </c>
       <c r="E19" t="n">
-        <v>303.3819885253906</v>
+        <v>299.7732543945312</v>
       </c>
       <c r="F19" t="n">
-        <v>8454200</v>
+        <v>6489900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B20" t="n">
-        <v>303.8946917756213</v>
+        <v>300.7789375021521</v>
       </c>
       <c r="C20" t="n">
-        <v>304.4567183318842</v>
+        <v>303.7270945284432</v>
       </c>
       <c r="D20" t="n">
-        <v>299.2999336047902</v>
+        <v>299.1422058887319</v>
       </c>
       <c r="E20" t="n">
-        <v>299.7732238769531</v>
+        <v>301.2522277832031</v>
       </c>
       <c r="F20" t="n">
-        <v>6489900</v>
+        <v>7060300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B21" t="n">
-        <v>300.7789679717848</v>
+        <v>301.3804193716138</v>
       </c>
       <c r="C21" t="n">
-        <v>303.7271252967313</v>
+        <v>306.1230715472904</v>
       </c>
       <c r="D21" t="n">
-        <v>299.1422361925597</v>
+        <v>296.5983188157025</v>
       </c>
       <c r="E21" t="n">
-        <v>301.2522583007812</v>
+        <v>296.6772155761719</v>
       </c>
       <c r="F21" t="n">
-        <v>7060300</v>
+        <v>8597400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B22" t="n">
-        <v>301.3804193716138</v>
+        <v>301.321238204041</v>
       </c>
       <c r="C22" t="n">
-        <v>306.1230715472904</v>
+        <v>305.1271791148808</v>
       </c>
       <c r="D22" t="n">
-        <v>296.5983188157025</v>
+        <v>301.173344402637</v>
       </c>
       <c r="E22" t="n">
-        <v>296.6772155761719</v>
+        <v>303.6580505371094</v>
       </c>
       <c r="F22" t="n">
-        <v>8597400</v>
+        <v>10788700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B23" t="n">
-        <v>301.321238204041</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C23" t="n">
-        <v>305.1271791148808</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D23" t="n">
-        <v>301.173344402637</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E23" t="n">
-        <v>303.6580505371094</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F23" t="n">
-        <v>10788700</v>
+        <v>16178800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B24" t="n">
-        <v>301.5578902761218</v>
+        <v>302.1001843350741</v>
       </c>
       <c r="C24" t="n">
-        <v>302.7016525742085</v>
+        <v>307.7499381556482</v>
       </c>
       <c r="D24" t="n">
-        <v>290.0907186231138</v>
+        <v>301.1634734465224</v>
       </c>
       <c r="E24" t="n">
-        <v>297.8505249023438</v>
+        <v>301.4099731445312</v>
       </c>
       <c r="F24" t="n">
-        <v>16178800</v>
+        <v>11354800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B25" t="n">
-        <v>302.1001843350741</v>
+        <v>301.0747572360179</v>
       </c>
       <c r="C25" t="n">
-        <v>307.7499381556482</v>
+        <v>304.3581201926382</v>
       </c>
       <c r="D25" t="n">
-        <v>301.1634734465224</v>
+        <v>292.9106878973514</v>
       </c>
       <c r="E25" t="n">
-        <v>301.4099731445312</v>
+        <v>294.360107421875</v>
       </c>
       <c r="F25" t="n">
-        <v>11354800</v>
+        <v>10549400</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B26" t="n">
-        <v>301.0747572360179</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C26" t="n">
-        <v>304.3581201926382</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D26" t="n">
-        <v>292.9106878973514</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E26" t="n">
-        <v>294.360107421875</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F26" t="n">
-        <v>10549400</v>
+        <v>10153500</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B27" t="n">
-        <v>294.9714335987563</v>
+        <v>294.3206459359216</v>
       </c>
       <c r="C27" t="n">
-        <v>295.3559575215809</v>
+        <v>299.4379821870563</v>
       </c>
       <c r="D27" t="n">
-        <v>290.0808874955599</v>
+        <v>293.9854099500461</v>
       </c>
       <c r="E27" t="n">
-        <v>293.3938293457031</v>
+        <v>298.1265869140625</v>
       </c>
       <c r="F27" t="n">
-        <v>10153500</v>
+        <v>6894900</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B28" t="n">
-        <v>294.3206760639065</v>
+        <v>297.436411288458</v>
       </c>
       <c r="C28" t="n">
-        <v>299.4380128388747</v>
+        <v>299.7929328501146</v>
       </c>
       <c r="D28" t="n">
-        <v>293.9854400437148</v>
+        <v>292.8416531202475</v>
       </c>
       <c r="E28" t="n">
-        <v>298.1266174316406</v>
+        <v>292.9303894042969</v>
       </c>
       <c r="F28" t="n">
-        <v>6894900</v>
+        <v>7372700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B29" t="n">
-        <v>297.436411288458</v>
+        <v>293.6008552074487</v>
       </c>
       <c r="C29" t="n">
-        <v>299.7929328501146</v>
+        <v>293.8868032880077</v>
       </c>
       <c r="D29" t="n">
-        <v>292.8416531202475</v>
+        <v>286.4721030595595</v>
       </c>
       <c r="E29" t="n">
-        <v>292.9303894042969</v>
+        <v>289.9920959472656</v>
       </c>
       <c r="F29" t="n">
-        <v>7372700</v>
+        <v>8054100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B30" t="n">
-        <v>293.6008552074487</v>
+        <v>290.2583437522712</v>
       </c>
       <c r="C30" t="n">
-        <v>293.8868032880077</v>
+        <v>292.2204718178062</v>
       </c>
       <c r="D30" t="n">
-        <v>286.4721030595595</v>
+        <v>288.4145307332595</v>
       </c>
       <c r="E30" t="n">
-        <v>289.9920959472656</v>
+        <v>290.4161071777344</v>
       </c>
       <c r="F30" t="n">
-        <v>8054100</v>
+        <v>5438800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B31" t="n">
-        <v>290.2583437522712</v>
+        <v>291.9345194575729</v>
       </c>
       <c r="C31" t="n">
-        <v>292.2204718178062</v>
+        <v>298.3632510673837</v>
       </c>
       <c r="D31" t="n">
-        <v>288.4145307332595</v>
+        <v>291.3133654724136</v>
       </c>
       <c r="E31" t="n">
-        <v>290.4161071777344</v>
+        <v>296.2334899902344</v>
       </c>
       <c r="F31" t="n">
-        <v>5438800</v>
+        <v>7228300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B32" t="n">
-        <v>291.9345194575729</v>
+        <v>297.92941246883</v>
       </c>
       <c r="C32" t="n">
-        <v>298.3632510673837</v>
+        <v>300.2662249001909</v>
       </c>
       <c r="D32" t="n">
-        <v>291.3133654724136</v>
+        <v>296.7955198233114</v>
       </c>
       <c r="E32" t="n">
-        <v>296.2334899902344</v>
+        <v>299.8915405273438</v>
       </c>
       <c r="F32" t="n">
-        <v>7228300</v>
+        <v>5642200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B33" t="n">
-        <v>297.9294427867379</v>
+        <v>300.5915953010157</v>
       </c>
       <c r="C33" t="n">
-        <v>300.2662554558976</v>
+        <v>303.6580673748709</v>
       </c>
       <c r="D33" t="n">
-        <v>296.7955500258321</v>
+        <v>298.915415308335</v>
       </c>
       <c r="E33" t="n">
-        <v>299.8915710449219</v>
+        <v>301.0845947265625</v>
       </c>
       <c r="F33" t="n">
-        <v>5642200</v>
+        <v>6336000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B34" t="n">
-        <v>300.5915953010157</v>
+        <v>299.2605157595805</v>
       </c>
       <c r="C34" t="n">
-        <v>303.6580673748709</v>
+        <v>303.9341406042103</v>
       </c>
       <c r="D34" t="n">
-        <v>298.915415308335</v>
+        <v>298.7675163425421</v>
       </c>
       <c r="E34" t="n">
-        <v>301.0845947265625</v>
+        <v>301.2325134277344</v>
       </c>
       <c r="F34" t="n">
-        <v>6336000</v>
+        <v>7520300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B35" t="n">
-        <v>299.2605157595805</v>
+        <v>301.5085931686638</v>
       </c>
       <c r="C35" t="n">
-        <v>303.9341406042103</v>
+        <v>308.2330823767899</v>
       </c>
       <c r="D35" t="n">
-        <v>298.7675163425421</v>
+        <v>300.828251563059</v>
       </c>
       <c r="E35" t="n">
-        <v>301.2325134277344</v>
+        <v>305.1074829101562</v>
       </c>
       <c r="F35" t="n">
-        <v>7520300</v>
+        <v>7514600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B36" t="n">
-        <v>301.5085931686638</v>
+        <v>304.2200828300273</v>
       </c>
       <c r="C36" t="n">
-        <v>308.2330823767899</v>
+        <v>308.4894444595929</v>
       </c>
       <c r="D36" t="n">
-        <v>300.828251563059</v>
+        <v>302.9481359332913</v>
       </c>
       <c r="E36" t="n">
-        <v>305.1074829101562</v>
+        <v>306.7639465332031</v>
       </c>
       <c r="F36" t="n">
-        <v>7514600</v>
+        <v>7721300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B37" t="n">
-        <v>304.2200828300273</v>
+        <v>306.6456604912348</v>
       </c>
       <c r="C37" t="n">
-        <v>308.4894444595929</v>
+        <v>307.9471862719047</v>
       </c>
       <c r="D37" t="n">
-        <v>302.9481359332913</v>
+        <v>301.9227172950412</v>
       </c>
       <c r="E37" t="n">
-        <v>306.7639465332031</v>
+        <v>305.0187683105469</v>
       </c>
       <c r="F37" t="n">
-        <v>7721300</v>
+        <v>7770000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B38" t="n">
-        <v>306.6456298108837</v>
+        <v>302.415720333495</v>
       </c>
       <c r="C38" t="n">
-        <v>307.947155461334</v>
+        <v>307.8485840116909</v>
       </c>
       <c r="D38" t="n">
-        <v>301.9226870872275</v>
+        <v>300.8282765156093</v>
       </c>
       <c r="E38" t="n">
-        <v>305.0187377929688</v>
+        <v>304.920166015625</v>
       </c>
       <c r="F38" t="n">
-        <v>7770000</v>
+        <v>7085200</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B39" t="n">
-        <v>302.415720333495</v>
+        <v>305.2751066360906</v>
       </c>
       <c r="C39" t="n">
-        <v>307.8485840116909</v>
+        <v>308.7162632770978</v>
       </c>
       <c r="D39" t="n">
-        <v>300.8282765156093</v>
+        <v>301.3508502506656</v>
       </c>
       <c r="E39" t="n">
-        <v>304.920166015625</v>
+        <v>307.3161315917969</v>
       </c>
       <c r="F39" t="n">
-        <v>7085200</v>
+        <v>6865200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B40" t="n">
-        <v>305.2751066360906</v>
+        <v>306.6357687557767</v>
       </c>
       <c r="C40" t="n">
-        <v>308.7162632770978</v>
+        <v>310.4318702971036</v>
       </c>
       <c r="D40" t="n">
-        <v>301.3508502506656</v>
+        <v>305.9160088624015</v>
       </c>
       <c r="E40" t="n">
-        <v>307.3161315917969</v>
+        <v>309.0317687988281</v>
       </c>
       <c r="F40" t="n">
-        <v>6865200</v>
+        <v>7206100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B41" t="n">
-        <v>306.6357687557767</v>
+        <v>307.5232049313688</v>
       </c>
       <c r="C41" t="n">
-        <v>310.4318702971036</v>
+        <v>310.0276204199649</v>
       </c>
       <c r="D41" t="n">
-        <v>305.9160088624015</v>
+        <v>303.3327096940284</v>
       </c>
       <c r="E41" t="n">
-        <v>309.0317687988281</v>
+        <v>309.8106994628906</v>
       </c>
       <c r="F41" t="n">
-        <v>7206100</v>
+        <v>7302300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B42" t="n">
-        <v>307.5231746391179</v>
+        <v>310.5896337890794</v>
       </c>
       <c r="C42" t="n">
-        <v>310.0275898810191</v>
+        <v>315.0857860805166</v>
       </c>
       <c r="D42" t="n">
-        <v>303.3326798145578</v>
+        <v>309.8106862822301</v>
       </c>
       <c r="E42" t="n">
-        <v>309.8106689453125</v>
+        <v>312.4531860351562</v>
       </c>
       <c r="F42" t="n">
-        <v>7302300</v>
+        <v>5794100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B43" t="n">
-        <v>310.5896034535161</v>
+        <v>313.0546102409576</v>
       </c>
       <c r="C43" t="n">
-        <v>315.0857553058102</v>
+        <v>314.5828963020791</v>
       </c>
       <c r="D43" t="n">
-        <v>309.8106560227473</v>
+        <v>310.8656917625901</v>
       </c>
       <c r="E43" t="n">
-        <v>312.4531555175781</v>
+        <v>311.200927734375</v>
       </c>
       <c r="F43" t="n">
-        <v>5794100</v>
+        <v>5030200</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B44" t="n">
-        <v>313.054640940315</v>
+        <v>311.8320000281587</v>
       </c>
       <c r="C44" t="n">
-        <v>314.5829271513063</v>
+        <v>317.7381233989844</v>
       </c>
       <c r="D44" t="n">
-        <v>310.8657222472937</v>
+        <v>311.782682032414</v>
       </c>
       <c r="E44" t="n">
-        <v>311.2009582519531</v>
+        <v>315.9238891601562</v>
       </c>
       <c r="F44" t="n">
-        <v>5030200</v>
+        <v>10578300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B45" t="n">
-        <v>311.8320000281587</v>
+        <v>314.7604626322791</v>
       </c>
       <c r="C45" t="n">
-        <v>317.7381233989844</v>
+        <v>316.1408551748796</v>
       </c>
       <c r="D45" t="n">
-        <v>311.782682032414</v>
+        <v>304.7722882324798</v>
       </c>
       <c r="E45" t="n">
-        <v>315.9238891601562</v>
+        <v>305.14697265625</v>
       </c>
       <c r="F45" t="n">
-        <v>10578300</v>
+        <v>8973300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B46" t="n">
-        <v>314.7604311532612</v>
+        <v>303.2044890700107</v>
       </c>
       <c r="C46" t="n">
-        <v>316.1408235578094</v>
+        <v>303.3326737235763</v>
       </c>
       <c r="D46" t="n">
-        <v>304.7722577523736</v>
+        <v>297.012418045434</v>
       </c>
       <c r="E46" t="n">
-        <v>305.1469421386719</v>
+        <v>299.3590698242188</v>
       </c>
       <c r="F46" t="n">
-        <v>8973300</v>
+        <v>10327000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B47" t="n">
-        <v>303.2045199796025</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C47" t="n">
-        <v>303.3327046462357</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D47" t="n">
-        <v>297.0124483237873</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E47" t="n">
-        <v>299.3591003417969</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F47" t="n">
-        <v>10327000</v>
+        <v>8344000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B48" t="n">
-        <v>299.7436397411884</v>
+        <v>295.3066623130797</v>
       </c>
       <c r="C48" t="n">
-        <v>301.3113742461044</v>
+        <v>298.708370459316</v>
       </c>
       <c r="D48" t="n">
-        <v>293.5022804823602</v>
+        <v>292.8613742767781</v>
       </c>
       <c r="E48" t="n">
-        <v>296.1644592285156</v>
+        <v>295.2179260253906</v>
       </c>
       <c r="F48" t="n">
-        <v>8344000</v>
+        <v>8077300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B49" t="n">
-        <v>295.3066623130797</v>
+        <v>295.5432597963394</v>
       </c>
       <c r="C49" t="n">
-        <v>298.708370459316</v>
+        <v>300.1873356382808</v>
       </c>
       <c r="D49" t="n">
-        <v>292.8613742767781</v>
+        <v>295.0798391737984</v>
       </c>
       <c r="E49" t="n">
-        <v>295.2179260253906</v>
+        <v>299.0238342285156</v>
       </c>
       <c r="F49" t="n">
-        <v>8077300</v>
+        <v>5546600</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B50" t="n">
-        <v>295.5432899586994</v>
+        <v>302.0508736933244</v>
       </c>
       <c r="C50" t="n">
-        <v>300.1873662746028</v>
+        <v>305.5807663052954</v>
       </c>
       <c r="D50" t="n">
-        <v>295.0798692888629</v>
+        <v>293.9854105998292</v>
       </c>
       <c r="E50" t="n">
-        <v>299.0238647460938</v>
+        <v>294.2023315429688</v>
       </c>
       <c r="F50" t="n">
-        <v>5546600</v>
+        <v>7501600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B51" t="n">
-        <v>302.0509050250311</v>
+        <v>297.0715864028587</v>
       </c>
       <c r="C51" t="n">
-        <v>305.5807980031574</v>
+        <v>297.456110287291</v>
       </c>
       <c r="D51" t="n">
-        <v>293.9854410949062</v>
+        <v>288.7103057597054</v>
       </c>
       <c r="E51" t="n">
-        <v>294.2023620605469</v>
+        <v>293.8473510742188</v>
       </c>
       <c r="F51" t="n">
-        <v>7501600</v>
+        <v>11766800</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B52" t="n">
-        <v>297.0715864028587</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C52" t="n">
-        <v>297.456110287291</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D52" t="n">
-        <v>288.7103057597054</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E52" t="n">
-        <v>293.8473510742188</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F52" t="n">
-        <v>11766800</v>
+        <v>10940200</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B53" t="n">
-        <v>294.0642973394352</v>
+        <v>295.848951187077</v>
       </c>
       <c r="C53" t="n">
-        <v>295.6221924256846</v>
+        <v>300.236658228506</v>
       </c>
       <c r="D53" t="n">
-        <v>290.386540762355</v>
+        <v>291.4218258555586</v>
       </c>
       <c r="E53" t="n">
-        <v>293.8276672363281</v>
+        <v>298.7576599121094</v>
       </c>
       <c r="F53" t="n">
-        <v>10940200</v>
+        <v>8877200</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B54" t="n">
-        <v>295.848951187077</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C54" t="n">
-        <v>300.236658228506</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D54" t="n">
-        <v>291.4218258555586</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E54" t="n">
-        <v>298.7576599121094</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F54" t="n">
-        <v>8877200</v>
+        <v>7910900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B55" t="n">
-        <v>300.7296512123902</v>
+        <v>304.7722465716023</v>
       </c>
       <c r="C55" t="n">
-        <v>304.2102259719906</v>
+        <v>309.3275563846455</v>
       </c>
       <c r="D55" t="n">
-        <v>298.9548653069277</v>
+        <v>303.9242719247256</v>
       </c>
       <c r="E55" t="n">
-        <v>303.3327026367188</v>
+        <v>308.6965026855469</v>
       </c>
       <c r="F55" t="n">
-        <v>7910900</v>
+        <v>4322400</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B56" t="n">
-        <v>304.7722465716023</v>
+        <v>308.5683309692949</v>
       </c>
       <c r="C56" t="n">
-        <v>309.3275563846455</v>
+        <v>309.6430660312097</v>
       </c>
       <c r="D56" t="n">
-        <v>303.9242719247256</v>
+        <v>304.2200727283419</v>
       </c>
       <c r="E56" t="n">
-        <v>308.6965026855469</v>
+        <v>304.5947570800781</v>
       </c>
       <c r="F56" t="n">
-        <v>4322400</v>
+        <v>7727300</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B57" t="n">
-        <v>308.5683618849884</v>
+        <v>304.4172805196406</v>
       </c>
       <c r="C57" t="n">
-        <v>309.6430970545817</v>
+        <v>306.1329390093465</v>
       </c>
       <c r="D57" t="n">
-        <v>304.2201032083801</v>
+        <v>302.7903884074122</v>
       </c>
       <c r="E57" t="n">
-        <v>304.5947875976562</v>
+        <v>303.5693359375</v>
       </c>
       <c r="F57" t="n">
-        <v>7727300</v>
+        <v>7249000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B58" t="n">
-        <v>304.4172499168193</v>
+        <v>302.8988595387675</v>
       </c>
       <c r="C58" t="n">
-        <v>306.1329082340515</v>
+        <v>307.9865871384521</v>
       </c>
       <c r="D58" t="n">
-        <v>302.7903579681411</v>
+        <v>302.5044359255107</v>
       </c>
       <c r="E58" t="n">
-        <v>303.5693054199219</v>
+        <v>307.7598266601562</v>
       </c>
       <c r="F58" t="n">
-        <v>7249000</v>
+        <v>8535300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B59" t="n">
-        <v>302.8988595387675</v>
+        <v>308.8740221323167</v>
       </c>
       <c r="C59" t="n">
-        <v>307.9865871384521</v>
+        <v>314.0307770729326</v>
       </c>
       <c r="D59" t="n">
-        <v>302.5044359255107</v>
+        <v>308.617652791837</v>
       </c>
       <c r="E59" t="n">
-        <v>307.7598266601562</v>
+        <v>311.6742553710938</v>
       </c>
       <c r="F59" t="n">
-        <v>8535300</v>
+        <v>9627800</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B60" t="n">
-        <v>308.8739918889233</v>
+        <v>311.2206946896725</v>
       </c>
       <c r="C60" t="n">
-        <v>314.0307463246157</v>
+        <v>314.0209278419201</v>
       </c>
       <c r="D60" t="n">
-        <v>308.6176225735461</v>
+        <v>310.2741141188276</v>
       </c>
       <c r="E60" t="n">
-        <v>311.6742248535156</v>
+        <v>310.6290893554688</v>
       </c>
       <c r="F60" t="n">
-        <v>9627800</v>
+        <v>6518900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B61" t="n">
-        <v>311.2206641139725</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C61" t="n">
-        <v>314.0208969911127</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D61" t="n">
-        <v>310.2740836361238</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E61" t="n">
-        <v>310.6290588378906</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F61" t="n">
-        <v>6518900</v>
+        <v>7417200</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B62" t="n">
-        <v>310.6487980837529</v>
+        <v>310.5403783790639</v>
       </c>
       <c r="C62" t="n">
-        <v>312.0390600856641</v>
+        <v>314.336450228146</v>
       </c>
       <c r="D62" t="n">
-        <v>308.9627484602848</v>
+        <v>295.8193913272319</v>
       </c>
       <c r="E62" t="n">
-        <v>310.7966918945312</v>
+        <v>296.3025512695312</v>
       </c>
       <c r="F62" t="n">
-        <v>7417200</v>
+        <v>18049200</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B63" t="n">
-        <v>310.5403783790639</v>
+        <v>296.292632599085</v>
       </c>
       <c r="C63" t="n">
-        <v>314.336450228146</v>
+        <v>306.8329619363725</v>
       </c>
       <c r="D63" t="n">
-        <v>295.8193913272319</v>
+        <v>294.2811866679717</v>
       </c>
       <c r="E63" t="n">
-        <v>296.3025512695312</v>
+        <v>305.76806640625</v>
       </c>
       <c r="F63" t="n">
-        <v>18049200</v>
+        <v>18874100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B64" t="n">
-        <v>296.2926621709551</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C64" t="n">
-        <v>306.8329925602339</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D64" t="n">
-        <v>294.2812160390869</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E64" t="n">
-        <v>305.7680969238281</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F64" t="n">
-        <v>18874100</v>
+        <v>9721900</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B65" t="n">
-        <v>304.9102649889192</v>
+        <v>315.2041261224818</v>
       </c>
       <c r="C65" t="n">
-        <v>313.5476242674454</v>
+        <v>315.7858618718594</v>
       </c>
       <c r="D65" t="n">
-        <v>304.9102649889192</v>
+        <v>312.1672627021157</v>
       </c>
       <c r="E65" t="n">
-        <v>312.9363098144531</v>
+        <v>314.0603637695312</v>
       </c>
       <c r="F65" t="n">
-        <v>9721900</v>
+        <v>8982900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B66" t="n">
-        <v>315.2041261224818</v>
+        <v>315.115395356304</v>
       </c>
       <c r="C66" t="n">
-        <v>315.7858618718594</v>
+        <v>318.3593402708456</v>
       </c>
       <c r="D66" t="n">
-        <v>312.1672627021157</v>
+        <v>313.9322146909975</v>
       </c>
       <c r="E66" t="n">
-        <v>314.0603637695312</v>
+        <v>315.5393676757812</v>
       </c>
       <c r="F66" t="n">
-        <v>8982900</v>
+        <v>10864100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B67" t="n">
-        <v>315.1153648797306</v>
+        <v>314.6224027314819</v>
       </c>
       <c r="C67" t="n">
-        <v>318.3593094805321</v>
+        <v>315.0463750601788</v>
       </c>
       <c r="D67" t="n">
-        <v>313.9321843288561</v>
+        <v>309.9980652283745</v>
       </c>
       <c r="E67" t="n">
-        <v>315.5393371582031</v>
+        <v>311.1319580078125</v>
       </c>
       <c r="F67" t="n">
-        <v>10864100</v>
+        <v>8331300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B68" t="n">
-        <v>314.6223718715413</v>
+        <v>313.971593609235</v>
       </c>
       <c r="C68" t="n">
-        <v>315.0463441586525</v>
+        <v>314.8984348971578</v>
       </c>
       <c r="D68" t="n">
-        <v>309.9980348220149</v>
+        <v>310.254388930852</v>
       </c>
       <c r="E68" t="n">
-        <v>311.1319274902344</v>
+        <v>310.5699157714844</v>
       </c>
       <c r="F68" t="n">
-        <v>8331300</v>
+        <v>8718700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B69" t="n">
-        <v>313.971593609235</v>
+        <v>311.575672673722</v>
       </c>
       <c r="C69" t="n">
-        <v>314.8984348971578</v>
+        <v>313.2518829489097</v>
       </c>
       <c r="D69" t="n">
-        <v>310.254388930852</v>
+        <v>307.8485977928193</v>
       </c>
       <c r="E69" t="n">
-        <v>310.5699157714844</v>
+        <v>308.61767578125</v>
       </c>
       <c r="F69" t="n">
-        <v>8718700</v>
+        <v>11444900</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B70" t="n">
-        <v>311.5756418636432</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C70" t="n">
-        <v>313.2518519730792</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D70" t="n">
-        <v>307.8485673512913</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E70" t="n">
-        <v>308.6176452636719</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F70" t="n">
-        <v>11444900</v>
+        <v>24494400</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B71" t="n">
-        <v>309.3965776494671</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="C71" t="n">
-        <v>314.099781180705</v>
+        <v>318.7043994886834</v>
       </c>
       <c r="D71" t="n">
-        <v>308.8049723403709</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="E71" t="n">
-        <v>312.7686767578125</v>
+        <v>318.5663452148438</v>
       </c>
       <c r="F71" t="n">
-        <v>24494400</v>
+        <v>8354600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B72" t="n">
-        <v>313.0644852104395</v>
+        <v>319.0790830432475</v>
       </c>
       <c r="C72" t="n">
-        <v>318.7043994886834</v>
+        <v>323.1907116116738</v>
       </c>
       <c r="D72" t="n">
-        <v>313.0644852104395</v>
+        <v>318.5663744582675</v>
       </c>
       <c r="E72" t="n">
-        <v>318.5663452148438</v>
+        <v>321.3666076660156</v>
       </c>
       <c r="F72" t="n">
-        <v>8354600</v>
+        <v>6668300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B73" t="n">
-        <v>319.0790830432475</v>
+        <v>321.6722493328215</v>
       </c>
       <c r="C73" t="n">
-        <v>323.1907116116738</v>
+        <v>325.3697449529369</v>
       </c>
       <c r="D73" t="n">
-        <v>318.5663744582675</v>
+        <v>320.9426198260136</v>
       </c>
       <c r="E73" t="n">
-        <v>321.3666076660156</v>
+        <v>324.5612487792969</v>
       </c>
       <c r="F73" t="n">
-        <v>6668300</v>
+        <v>4289300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B74" t="n">
-        <v>321.6722795787551</v>
+        <v>324.502058709128</v>
       </c>
       <c r="C74" t="n">
-        <v>325.3697755465356</v>
+        <v>326.2275566521161</v>
       </c>
       <c r="D74" t="n">
-        <v>320.9426500033422</v>
+        <v>321.9680645986219</v>
       </c>
       <c r="E74" t="n">
-        <v>324.561279296875</v>
+        <v>323.3188781738281</v>
       </c>
       <c r="F74" t="n">
-        <v>4289300</v>
+        <v>4158300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B75" t="n">
-        <v>324.502058709128</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C75" t="n">
-        <v>326.2275566521161</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D75" t="n">
-        <v>321.9680645986219</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E75" t="n">
-        <v>323.3188781738281</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F75" t="n">
-        <v>4158300</v>
+        <v>8635300</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B76" t="n">
-        <v>322.4216288798564</v>
+        <v>320.2623075229155</v>
       </c>
       <c r="C76" t="n">
-        <v>323.1808371734579</v>
+        <v>320.3904921972535</v>
       </c>
       <c r="D76" t="n">
-        <v>319.0002116144308</v>
+        <v>317.9747828016658</v>
       </c>
       <c r="E76" t="n">
-        <v>319.2171325683594</v>
+        <v>318.8917846679688</v>
       </c>
       <c r="F76" t="n">
-        <v>8635300</v>
+        <v>7904300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B77" t="n">
-        <v>320.2623075229155</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C77" t="n">
-        <v>320.3904921972535</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D77" t="n">
-        <v>317.9747828016658</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E77" t="n">
-        <v>318.8917846679688</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F77" t="n">
-        <v>7904300</v>
+        <v>5048500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B78" t="n">
-        <v>319.7988699190817</v>
+        <v>317.9846252281575</v>
       </c>
       <c r="C78" t="n">
-        <v>320.3313177342217</v>
+        <v>321.1694123071354</v>
       </c>
       <c r="D78" t="n">
-        <v>317.5310845539587</v>
+        <v>316.2492576445291</v>
       </c>
       <c r="E78" t="n">
-        <v>317.7085571289062</v>
+        <v>320.9229125976562</v>
       </c>
       <c r="F78" t="n">
-        <v>5048500</v>
+        <v>8054000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B79" t="n">
-        <v>317.9846252281575</v>
+        <v>320.9426586744551</v>
       </c>
       <c r="C79" t="n">
-        <v>321.1694123071354</v>
+        <v>332.5281463531796</v>
       </c>
       <c r="D79" t="n">
-        <v>316.2492576445291</v>
+        <v>320.637001406751</v>
       </c>
       <c r="E79" t="n">
-        <v>320.9229125976562</v>
+        <v>329.3630981445312</v>
       </c>
       <c r="F79" t="n">
-        <v>8054000</v>
+        <v>10752600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,25 +2497,25 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B80" t="n">
-        <v>320.942628937084</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C80" t="n">
-        <v>332.5281155423397</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D80" t="n">
-        <v>320.636971697701</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E80" t="n">
-        <v>329.3630676269531</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F80" t="n">
-        <v>10752600</v>
+        <v>7660800</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2523,25 +2523,25 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B81" t="n">
-        <v>329.4422902981328</v>
+        <v>327.9764350864437</v>
       </c>
       <c r="C81" t="n">
-        <v>332.6612412306879</v>
+        <v>328.9767653957764</v>
       </c>
       <c r="D81" t="n">
-        <v>327.491109600743</v>
+        <v>321.4989071734381</v>
       </c>
       <c r="E81" t="n">
-        <v>331.4132690429688</v>
+        <v>323.8660583496094</v>
       </c>
       <c r="F81" t="n">
-        <v>7660800</v>
+        <v>9815200</v>
       </c>
       <c r="G81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B82" t="n">
-        <v>327.9764350864437</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C82" t="n">
-        <v>328.9767653957764</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D82" t="n">
-        <v>321.4989071734381</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E82" t="n">
-        <v>323.8660583496094</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F82" t="n">
-        <v>9815200</v>
+        <v>11737100</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B83" t="n">
-        <v>323.2718313763784</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C83" t="n">
-        <v>328.2339475379842</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D83" t="n">
-        <v>322.5388804495614</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E83" t="n">
-        <v>326.6393432617188</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F83" t="n">
-        <v>11737100</v>
+        <v>6738100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B84" t="n">
-        <v>326.1936353875406</v>
+        <v>318.8049332018166</v>
       </c>
       <c r="C84" t="n">
-        <v>328.7291759216584</v>
+        <v>322.9053661093398</v>
       </c>
       <c r="D84" t="n">
-        <v>325.0348299492433</v>
+        <v>318.1611490039577</v>
       </c>
       <c r="E84" t="n">
-        <v>326.0450744628906</v>
+        <v>321.3899841308594</v>
       </c>
       <c r="F84" t="n">
-        <v>6738100</v>
+        <v>12805100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B85" t="n">
-        <v>318.8049332018166</v>
+        <v>321.2017865718998</v>
       </c>
       <c r="C85" t="n">
-        <v>322.9053661093398</v>
+        <v>323.7373271836527</v>
       </c>
       <c r="D85" t="n">
-        <v>318.1611490039577</v>
+        <v>307.6029755260753</v>
       </c>
       <c r="E85" t="n">
-        <v>321.3899841308594</v>
+        <v>307.9298095703125</v>
       </c>
       <c r="F85" t="n">
-        <v>12805100</v>
+        <v>19371200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B86" t="n">
-        <v>321.2017865718998</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C86" t="n">
-        <v>323.7373271836527</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D86" t="n">
-        <v>307.6029755260753</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E86" t="n">
-        <v>307.9298095703125</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F86" t="n">
-        <v>19371200</v>
+        <v>25951500</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B87" t="n">
-        <v>305.2556057077196</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C87" t="n">
-        <v>308.7815926253858</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D87" t="n">
-        <v>303.1954601804828</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E87" t="n">
-        <v>304.9287414550781</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F87" t="n">
-        <v>25951500</v>
+        <v>14751400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B88" t="n">
-        <v>305.5230197927318</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C88" t="n">
-        <v>309.95031666446</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D88" t="n">
-        <v>304.8098971346673</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E88" t="n">
-        <v>306.3054809570312</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F88" t="n">
-        <v>14751400</v>
+        <v>14652500</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B89" t="n">
-        <v>307.385060616362</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C89" t="n">
-        <v>314.1795087286461</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D89" t="n">
-        <v>307.0383983149945</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E89" t="n">
-        <v>309.4848022460938</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F89" t="n">
-        <v>14652500</v>
+        <v>12900600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B90" t="n">
-        <v>303.2845981841295</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C90" t="n">
-        <v>308.1774060521912</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D90" t="n">
-        <v>298.9761500928895</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E90" t="n">
-        <v>299.8477478027344</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F90" t="n">
-        <v>12900600</v>
+        <v>10270100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B91" t="n">
-        <v>300.5311849469782</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C91" t="n">
-        <v>302.4823658305288</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D91" t="n">
-        <v>298.2729680555718</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E91" t="n">
-        <v>299.1544799804688</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F91" t="n">
-        <v>10270100</v>
+        <v>10535800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B92" t="n">
-        <v>301.9474777854751</v>
+        <v>299.1148422218051</v>
       </c>
       <c r="C92" t="n">
-        <v>305.2555953909441</v>
+        <v>299.4813025896872</v>
       </c>
       <c r="D92" t="n">
-        <v>300.0062112868251</v>
+        <v>293.6773006232809</v>
       </c>
       <c r="E92" t="n">
-        <v>300.729248046875</v>
+        <v>294.875732421875</v>
       </c>
       <c r="F92" t="n">
-        <v>10535800</v>
+        <v>11107900</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B93" t="n">
-        <v>299.1148422218051</v>
+        <v>294.9648788077786</v>
       </c>
       <c r="C93" t="n">
-        <v>299.4813025896872</v>
+        <v>298.8969527426069</v>
       </c>
       <c r="D93" t="n">
-        <v>293.6773006232809</v>
+        <v>294.6083325653198</v>
       </c>
       <c r="E93" t="n">
-        <v>294.875732421875</v>
+        <v>298.1640319824219</v>
       </c>
       <c r="F93" t="n">
-        <v>11107900</v>
+        <v>11752700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B94" t="n">
-        <v>294.9648788077786</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C94" t="n">
-        <v>298.8969527426069</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D94" t="n">
-        <v>294.6083325653198</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E94" t="n">
-        <v>298.1640319824219</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F94" t="n">
-        <v>11752700</v>
+        <v>11527400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B95" t="n">
-        <v>298.4512235287846</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C95" t="n">
-        <v>299.0851237823749</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D95" t="n">
-        <v>295.3016109870806</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E95" t="n">
-        <v>297.4409790039062</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F95" t="n">
-        <v>11527400</v>
+        <v>9556700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B96" t="n">
-        <v>297.4013222225187</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C96" t="n">
-        <v>299.0355829225425</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D96" t="n">
-        <v>295.2025300603667</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E96" t="n">
-        <v>297.8965454101562</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F96" t="n">
-        <v>9556700</v>
+        <v>11580000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B97" t="n">
-        <v>299.5110006693188</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C97" t="n">
-        <v>303.898671192008</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D97" t="n">
-        <v>299.3327275624257</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E97" t="n">
-        <v>303.4926147460938</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F97" t="n">
-        <v>11580000</v>
+        <v>11953200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B98" t="n">
-        <v>302.333781642444</v>
+        <v>301.5513012828864</v>
       </c>
       <c r="C98" t="n">
-        <v>304.9881708986046</v>
+        <v>306.3450582127215</v>
       </c>
       <c r="D98" t="n">
-        <v>299.6694782493637</v>
+        <v>298.4908255461663</v>
       </c>
       <c r="E98" t="n">
-        <v>302.9676818847656</v>
+        <v>305.1961669921875</v>
       </c>
       <c r="F98" t="n">
-        <v>11953200</v>
+        <v>9839400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B99" t="n">
-        <v>301.5513012828864</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C99" t="n">
-        <v>306.3450582127215</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D99" t="n">
-        <v>298.4908255461663</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E99" t="n">
-        <v>305.1961669921875</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F99" t="n">
-        <v>9839400</v>
+        <v>12688000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B100" t="n">
-        <v>306.7709905338949</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="C100" t="n">
-        <v>313.2286905211348</v>
+        <v>316.2594719758441</v>
       </c>
       <c r="D100" t="n">
-        <v>306.1470044328188</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="E100" t="n">
-        <v>311.8420715332031</v>
+        <v>314.2389526367188</v>
       </c>
       <c r="F100" t="n">
-        <v>12688000</v>
+        <v>9848800</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B101" t="n">
-        <v>311.4062901330092</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C101" t="n">
-        <v>316.2594719758441</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D101" t="n">
-        <v>311.4062901330092</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E101" t="n">
-        <v>314.2389526367188</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F101" t="n">
-        <v>9848800</v>
+        <v>9388000</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B102" t="n">
-        <v>311.9906259989966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C102" t="n">
-        <v>312.9909865673853</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D102" t="n">
-        <v>302.6210112179966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E102" t="n">
-        <v>307.1968688964844</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F102" t="n">
-        <v>9388000</v>
+        <v>17797400</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B103" t="n">
-        <v>311.7034102684662</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C103" t="n">
-        <v>321.1522783634816</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D103" t="n">
-        <v>311.7034102684662</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E103" t="n">
-        <v>319.3199462890625</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F103" t="n">
-        <v>17797400</v>
+        <v>11477500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B104" t="n">
-        <v>318.2700781279603</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C104" t="n">
-        <v>323.2817350541263</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D104" t="n">
-        <v>317.0518180384032</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E104" t="n">
-        <v>319.0228271484375</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F104" t="n">
-        <v>11477500</v>
+        <v>9902200</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B105" t="n">
-        <v>319.4684837021083</v>
+        <v>320.1518827061323</v>
       </c>
       <c r="C105" t="n">
-        <v>323.014298845819</v>
+        <v>322.1724018130651</v>
       </c>
       <c r="D105" t="n">
-        <v>312.1094739861534</v>
+        <v>305.7805260837019</v>
       </c>
       <c r="E105" t="n">
-        <v>315.2392883300781</v>
+        <v>307.8505554199219</v>
       </c>
       <c r="F105" t="n">
-        <v>9902200</v>
+        <v>8703500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B106" t="n">
-        <v>320.1518827061323</v>
+        <v>309.2966374972976</v>
       </c>
       <c r="C106" t="n">
-        <v>322.1724018130651</v>
+        <v>310.6238322045743</v>
       </c>
       <c r="D106" t="n">
-        <v>305.7805260837019</v>
+        <v>297.1537535117247</v>
       </c>
       <c r="E106" t="n">
-        <v>307.8505554199219</v>
+        <v>299.7487487792969</v>
       </c>
       <c r="F106" t="n">
-        <v>8703500</v>
+        <v>13443400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B107" t="n">
-        <v>309.2966374972976</v>
+        <v>295.6680782309701</v>
       </c>
       <c r="C107" t="n">
-        <v>310.6238322045743</v>
+        <v>301.3829738793206</v>
       </c>
       <c r="D107" t="n">
-        <v>297.1537535117247</v>
+        <v>293.6871852314235</v>
       </c>
       <c r="E107" t="n">
-        <v>299.7487487792969</v>
+        <v>299.6595764160156</v>
       </c>
       <c r="F107" t="n">
-        <v>13443400</v>
+        <v>9114500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B108" t="n">
-        <v>295.6680782309701</v>
+        <v>299.8675850307636</v>
       </c>
       <c r="C108" t="n">
-        <v>301.3829738793206</v>
+        <v>305.2952123797385</v>
       </c>
       <c r="D108" t="n">
-        <v>293.6871852314235</v>
+        <v>299.6100592744303</v>
       </c>
       <c r="E108" t="n">
-        <v>299.6595764160156</v>
+        <v>304.1958312988281</v>
       </c>
       <c r="F108" t="n">
-        <v>9114500</v>
+        <v>8896800</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B109" t="n">
-        <v>299.8675850307636</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C109" t="n">
-        <v>305.2952123797385</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D109" t="n">
-        <v>299.6100592744303</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E109" t="n">
-        <v>304.1958312988281</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F109" t="n">
-        <v>8896800</v>
+        <v>7209600</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B110" t="n">
-        <v>305.5130974954087</v>
+        <v>304.2354272061944</v>
       </c>
       <c r="C110" t="n">
-        <v>309.2966101142475</v>
+        <v>306.2262038721237</v>
       </c>
       <c r="D110" t="n">
-        <v>304.2849535938903</v>
+        <v>302.2049939958365</v>
       </c>
       <c r="E110" t="n">
-        <v>305.8300476074219</v>
+        <v>305.1069946289062</v>
       </c>
       <c r="F110" t="n">
-        <v>7209600</v>
+        <v>6737700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B111" t="n">
-        <v>304.2354272061944</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C111" t="n">
-        <v>306.2262038721237</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D111" t="n">
-        <v>302.2049939958365</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E111" t="n">
-        <v>305.1069946289062</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F111" t="n">
-        <v>6737700</v>
+        <v>7792700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B112" t="n">
-        <v>305.4536802835111</v>
+        <v>305.8498457788994</v>
       </c>
       <c r="C112" t="n">
-        <v>308.0288471084009</v>
+        <v>308.0288400173425</v>
       </c>
       <c r="D112" t="n">
-        <v>302.7596647203387</v>
+        <v>292.2807478108573</v>
       </c>
       <c r="E112" t="n">
-        <v>307.8208618164062</v>
+        <v>294.8262023925781</v>
       </c>
       <c r="F112" t="n">
-        <v>7792700</v>
+        <v>12955400</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B113" t="n">
-        <v>305.8498457788994</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C113" t="n">
-        <v>308.0288400173425</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D113" t="n">
-        <v>292.2807478108573</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E113" t="n">
-        <v>294.8262023925781</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F113" t="n">
-        <v>12955400</v>
+        <v>13554100</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B114" t="n">
-        <v>293.9843218466586</v>
+        <v>295.7869507950724</v>
       </c>
       <c r="C114" t="n">
-        <v>296.886322684036</v>
+        <v>300.7589812348872</v>
       </c>
       <c r="D114" t="n">
-        <v>288.5962907533433</v>
+        <v>294.1725181992404</v>
       </c>
       <c r="E114" t="n">
-        <v>294.459716796875</v>
+        <v>300.4024047851562</v>
       </c>
       <c r="F114" t="n">
-        <v>13554100</v>
+        <v>8095500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B115" t="n">
-        <v>295.7869507950724</v>
+        <v>301.670173133609</v>
       </c>
       <c r="C115" t="n">
-        <v>300.7589812348872</v>
+        <v>306.0578739762234</v>
       </c>
       <c r="D115" t="n">
-        <v>294.1725181992404</v>
+        <v>300.7391812579012</v>
       </c>
       <c r="E115" t="n">
-        <v>300.4024047851562</v>
+        <v>303.2053833007812</v>
       </c>
       <c r="F115" t="n">
-        <v>8095500</v>
+        <v>7007800</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B116" t="n">
-        <v>301.670173133609</v>
+        <v>297.1339389424841</v>
       </c>
       <c r="C116" t="n">
-        <v>306.0578739762234</v>
+        <v>300.0557680991628</v>
       </c>
       <c r="D116" t="n">
-        <v>300.7391812579012</v>
+        <v>291.636973162459</v>
       </c>
       <c r="E116" t="n">
-        <v>303.2053833007812</v>
+        <v>297.4310607910156</v>
       </c>
       <c r="F116" t="n">
-        <v>7007800</v>
+        <v>18620800</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B117" t="n">
-        <v>297.1339389424841</v>
+        <v>291.9935267958635</v>
       </c>
       <c r="C117" t="n">
-        <v>300.0557680991628</v>
+        <v>297.1141484397957</v>
       </c>
       <c r="D117" t="n">
-        <v>291.636973162459</v>
+        <v>290.4088063693875</v>
       </c>
       <c r="E117" t="n">
-        <v>297.4310607910156</v>
+        <v>294.7172546386719</v>
       </c>
       <c r="F117" t="n">
-        <v>18620800</v>
+        <v>8508900</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B118" t="n">
-        <v>291.9935267958635</v>
+        <v>289.4975898716125</v>
       </c>
       <c r="C118" t="n">
-        <v>297.1141484397957</v>
+        <v>299.5011046657454</v>
       </c>
       <c r="D118" t="n">
-        <v>290.4088063693875</v>
+        <v>286.7342359222354</v>
       </c>
       <c r="E118" t="n">
-        <v>294.7172546386719</v>
+        <v>297.3914489746094</v>
       </c>
       <c r="F118" t="n">
-        <v>8508900</v>
+        <v>10278200</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B119" t="n">
-        <v>289.4975898716125</v>
+        <v>297.1240288614248</v>
       </c>
       <c r="C119" t="n">
-        <v>299.5011046657454</v>
+        <v>298.1243894751821</v>
       </c>
       <c r="D119" t="n">
-        <v>286.7342359222354</v>
+        <v>292.993883980321</v>
       </c>
       <c r="E119" t="n">
-        <v>297.3914489746094</v>
+        <v>296.52978515625</v>
       </c>
       <c r="F119" t="n">
-        <v>10278200</v>
+        <v>8055700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B120" t="n">
-        <v>297.1240288614248</v>
+        <v>295.1332451958745</v>
       </c>
       <c r="C120" t="n">
-        <v>298.1243894751821</v>
+        <v>298.3620800816865</v>
       </c>
       <c r="D120" t="n">
-        <v>292.993883980321</v>
+        <v>289.6362492414601</v>
       </c>
       <c r="E120" t="n">
-        <v>296.52978515625</v>
+        <v>290.7455444335938</v>
       </c>
       <c r="F120" t="n">
-        <v>8055700</v>
+        <v>12732500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B121" t="n">
-        <v>295.1332451958745</v>
+        <v>283.6044306839189</v>
       </c>
       <c r="C121" t="n">
-        <v>298.3620800816865</v>
+        <v>287.2195541533999</v>
       </c>
       <c r="D121" t="n">
-        <v>289.6362492414601</v>
+        <v>280.9995517042956</v>
       </c>
       <c r="E121" t="n">
-        <v>290.7455444335938</v>
+        <v>286.7144470214844</v>
       </c>
       <c r="F121" t="n">
-        <v>12732500</v>
+        <v>13496500</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B122" t="n">
-        <v>283.6044306839189</v>
+        <v>282.7724816341387</v>
       </c>
       <c r="C122" t="n">
-        <v>287.2195541533999</v>
+        <v>288.3189881947603</v>
       </c>
       <c r="D122" t="n">
-        <v>280.9995517042956</v>
+        <v>277.7707387954702</v>
       </c>
       <c r="E122" t="n">
-        <v>286.7144470214844</v>
+        <v>287.1502685546875</v>
       </c>
       <c r="F122" t="n">
-        <v>13496500</v>
+        <v>12241100</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B123" t="n">
-        <v>282.7724816341387</v>
+        <v>286.5262662545288</v>
       </c>
       <c r="C123" t="n">
-        <v>288.3189881947603</v>
+        <v>289.9532025593205</v>
       </c>
       <c r="D123" t="n">
-        <v>277.7707387954702</v>
+        <v>284.4364084963449</v>
       </c>
       <c r="E123" t="n">
-        <v>287.1502685546875</v>
+        <v>285.9716186523438</v>
       </c>
       <c r="F123" t="n">
-        <v>12241100</v>
+        <v>8344900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B124" t="n">
-        <v>286.5262662545288</v>
+        <v>286.0508166178312</v>
       </c>
       <c r="C124" t="n">
-        <v>289.9532025593205</v>
+        <v>287.7048753720447</v>
       </c>
       <c r="D124" t="n">
-        <v>284.4364084963449</v>
+        <v>282.1385413260368</v>
       </c>
       <c r="E124" t="n">
-        <v>285.9716186523438</v>
+        <v>284.7731323242188</v>
       </c>
       <c r="F124" t="n">
-        <v>8344900</v>
+        <v>10205000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B125" t="n">
-        <v>286.0508166178312</v>
+        <v>280.1279538528093</v>
       </c>
       <c r="C125" t="n">
-        <v>287.7048753720447</v>
+        <v>281.167940752382</v>
       </c>
       <c r="D125" t="n">
-        <v>282.1385413260368</v>
+        <v>276.4336079693154</v>
       </c>
       <c r="E125" t="n">
-        <v>284.7731323242188</v>
+        <v>280.1874084472656</v>
       </c>
       <c r="F125" t="n">
-        <v>10205000</v>
+        <v>13760500</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B126" t="n">
-        <v>280.1279538528093</v>
+        <v>281.9504072447318</v>
       </c>
       <c r="C126" t="n">
-        <v>281.167940752382</v>
+        <v>284.4463214441296</v>
       </c>
       <c r="D126" t="n">
-        <v>276.4336079693154</v>
+        <v>280.2468381234208</v>
       </c>
       <c r="E126" t="n">
-        <v>280.1874084472656</v>
+        <v>280.7321472167969</v>
       </c>
       <c r="F126" t="n">
-        <v>13760500</v>
+        <v>9091200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B127" t="n">
-        <v>281.9504072447318</v>
+        <v>283.6044205599556</v>
       </c>
       <c r="C127" t="n">
-        <v>284.4463214441296</v>
+        <v>286.506421278288</v>
       </c>
       <c r="D127" t="n">
-        <v>280.2468381234208</v>
+        <v>281.8909373944359</v>
       </c>
       <c r="E127" t="n">
-        <v>280.7321472167969</v>
+        <v>283.4261474609375</v>
       </c>
       <c r="F127" t="n">
-        <v>9091200</v>
+        <v>8149000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B128" t="n">
-        <v>283.6044205599556</v>
+        <v>286.2390279690733</v>
       </c>
       <c r="C128" t="n">
-        <v>286.506421278288</v>
+        <v>288.9726698808299</v>
       </c>
       <c r="D128" t="n">
-        <v>281.8909373944359</v>
+        <v>283.2181783456238</v>
       </c>
       <c r="E128" t="n">
-        <v>283.4261474609375</v>
+        <v>284.1492004394531</v>
       </c>
       <c r="F128" t="n">
-        <v>8149000</v>
+        <v>8961200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B129" t="n">
-        <v>286.2390279690733</v>
+        <v>284.0897484324327</v>
       </c>
       <c r="C129" t="n">
-        <v>288.9726698808299</v>
+        <v>286.6451172582804</v>
       </c>
       <c r="D129" t="n">
-        <v>283.2181783456238</v>
+        <v>282.3960934275981</v>
       </c>
       <c r="E129" t="n">
-        <v>284.1492004394531</v>
+        <v>284.9910583496094</v>
       </c>
       <c r="F129" t="n">
-        <v>8961200</v>
+        <v>10057000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B130" t="n">
-        <v>284.0897484324327</v>
+        <v>284.1392586396808</v>
       </c>
       <c r="C130" t="n">
-        <v>286.6451172582804</v>
+        <v>286.7441374214082</v>
       </c>
       <c r="D130" t="n">
-        <v>282.3960934275981</v>
+        <v>281.9008401776293</v>
       </c>
       <c r="E130" t="n">
-        <v>284.9910583496094</v>
+        <v>285.2188415527344</v>
       </c>
       <c r="F130" t="n">
-        <v>10057000</v>
+        <v>9846700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B131" t="n">
-        <v>284.1392586396808</v>
+        <v>285.327825032355</v>
       </c>
       <c r="C131" t="n">
-        <v>286.7441374214082</v>
+        <v>287.9327042603992</v>
       </c>
       <c r="D131" t="n">
-        <v>281.9008401776293</v>
+        <v>282.5446726819272</v>
       </c>
       <c r="E131" t="n">
-        <v>285.2188415527344</v>
+        <v>283.8223571777344</v>
       </c>
       <c r="F131" t="n">
-        <v>9846700</v>
+        <v>22436500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B132" t="n">
-        <v>285.327825032355</v>
+        <v>291.4982779446762</v>
       </c>
       <c r="C132" t="n">
-        <v>287.9327042603992</v>
+        <v>292.9245231806114</v>
       </c>
       <c r="D132" t="n">
-        <v>282.5446726819272</v>
+        <v>285.2188513876401</v>
       </c>
       <c r="E132" t="n">
-        <v>283.8223571777344</v>
+        <v>287.1403198242188</v>
       </c>
       <c r="F132" t="n">
-        <v>22436500</v>
+        <v>11470800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B133" t="n">
-        <v>291.4982779446762</v>
+        <v>283.4360748065673</v>
       </c>
       <c r="C133" t="n">
-        <v>292.9245231806114</v>
+        <v>292.6571288676103</v>
       </c>
       <c r="D133" t="n">
-        <v>285.2188513876401</v>
+        <v>282.6436995084055</v>
       </c>
       <c r="E133" t="n">
-        <v>287.1403198242188</v>
+        <v>289.6065368652344</v>
       </c>
       <c r="F133" t="n">
-        <v>11470800</v>
+        <v>11092300</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B134" t="n">
-        <v>283.4360748065673</v>
+        <v>291.3398308899875</v>
       </c>
       <c r="C134" t="n">
-        <v>292.6571288676103</v>
+        <v>294.7965097163498</v>
       </c>
       <c r="D134" t="n">
-        <v>282.6436995084055</v>
+        <v>289.6461758443202</v>
       </c>
       <c r="E134" t="n">
-        <v>289.6065368652344</v>
+        <v>292.5977172851562</v>
       </c>
       <c r="F134" t="n">
-        <v>11092300</v>
+        <v>12188200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B135" t="n">
-        <v>291.3398308899875</v>
+        <v>289.7848205526045</v>
       </c>
       <c r="C135" t="n">
-        <v>294.7965097163498</v>
+        <v>292.1718002190451</v>
       </c>
       <c r="D135" t="n">
-        <v>289.6461758443202</v>
+        <v>287.9525187281419</v>
       </c>
       <c r="E135" t="n">
-        <v>292.5977172851562</v>
+        <v>288.8736267089844</v>
       </c>
       <c r="F135" t="n">
-        <v>12188200</v>
+        <v>8669200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B136" t="n">
-        <v>289.7848205526045</v>
+        <v>286.3777093696089</v>
       </c>
       <c r="C136" t="n">
-        <v>292.1718002190451</v>
+        <v>287.3384134369941</v>
       </c>
       <c r="D136" t="n">
-        <v>287.9525187281419</v>
+        <v>279.0582953832721</v>
       </c>
       <c r="E136" t="n">
-        <v>288.8736267089844</v>
+        <v>280.1378784179688</v>
       </c>
       <c r="F136" t="n">
-        <v>8669200</v>
+        <v>9873300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B137" t="n">
-        <v>286.3777093696089</v>
+        <v>282.0197247859078</v>
       </c>
       <c r="C137" t="n">
-        <v>287.3384134369941</v>
+        <v>284.505755156032</v>
       </c>
       <c r="D137" t="n">
-        <v>279.0582953832721</v>
+        <v>279.6327451103039</v>
       </c>
       <c r="E137" t="n">
-        <v>280.1378784179688</v>
+        <v>281.0589904785156</v>
       </c>
       <c r="F137" t="n">
-        <v>9873300</v>
+        <v>11734400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B138" t="n">
-        <v>282.0197247859078</v>
+        <v>285.7140887250632</v>
       </c>
       <c r="C138" t="n">
-        <v>284.505755156032</v>
+        <v>292.2510413422024</v>
       </c>
       <c r="D138" t="n">
-        <v>279.6327451103039</v>
+        <v>282.2277281014015</v>
       </c>
       <c r="E138" t="n">
-        <v>281.0589904785156</v>
+        <v>291.3497314453125</v>
       </c>
       <c r="F138" t="n">
-        <v>11734400</v>
+        <v>12956900</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B139" t="n">
-        <v>285.7140887250632</v>
+        <v>292.567989087923</v>
       </c>
       <c r="C139" t="n">
-        <v>292.2510413422024</v>
+        <v>295.8661624411999</v>
       </c>
       <c r="D139" t="n">
-        <v>282.2277281014015</v>
+        <v>290.1116710297465</v>
       </c>
       <c r="E139" t="n">
-        <v>291.3497314453125</v>
+        <v>292.5580749511719</v>
       </c>
       <c r="F139" t="n">
-        <v>12956900</v>
+        <v>11267200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B140" t="n">
-        <v>292.567989087923</v>
+        <v>289.1212191631598</v>
       </c>
       <c r="C140" t="n">
-        <v>295.8661624411999</v>
+        <v>292.7957669317203</v>
       </c>
       <c r="D140" t="n">
-        <v>290.1116710297465</v>
+        <v>285.9616926535428</v>
       </c>
       <c r="E140" t="n">
-        <v>292.5580749511719</v>
+        <v>291.7855224609375</v>
       </c>
       <c r="F140" t="n">
-        <v>11267200</v>
+        <v>6669300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,25 +4083,25 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B141" t="n">
-        <v>289.1212191631598</v>
+        <v>292.7412191857173</v>
       </c>
       <c r="C141" t="n">
-        <v>292.7957669317203</v>
+        <v>295.4987855589938</v>
       </c>
       <c r="D141" t="n">
-        <v>285.9616926535428</v>
+        <v>291.8850906324002</v>
       </c>
       <c r="E141" t="n">
-        <v>291.7855224609375</v>
+        <v>294.125</v>
       </c>
       <c r="F141" t="n">
-        <v>6669300</v>
+        <v>7142600</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4109,25 +4109,25 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B142" t="n">
-        <v>292.7412191857173</v>
+        <v>291.8253790066561</v>
       </c>
       <c r="C142" t="n">
-        <v>295.4987855589938</v>
+        <v>296.8427544058445</v>
       </c>
       <c r="D142" t="n">
-        <v>291.8850906324002</v>
+        <v>291.3873498301165</v>
       </c>
       <c r="E142" t="n">
-        <v>294.125</v>
+        <v>296.0662536621094</v>
       </c>
       <c r="F142" t="n">
-        <v>7142600</v>
+        <v>7849100</v>
       </c>
       <c r="G142" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B143" t="n">
-        <v>291.8253790066561</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="C143" t="n">
-        <v>296.8427544058445</v>
+        <v>309.8640903908154</v>
       </c>
       <c r="D143" t="n">
-        <v>291.3873498301165</v>
+        <v>303.9606617936424</v>
       </c>
       <c r="E143" t="n">
-        <v>296.0662536621094</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="F143" t="n">
-        <v>7849100</v>
+        <v>10590200</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B144" t="n">
-        <v>306.5888366699219</v>
+        <v>305.5734164156603</v>
       </c>
       <c r="C144" t="n">
-        <v>309.8640903908154</v>
+        <v>309.8640846884941</v>
       </c>
       <c r="D144" t="n">
-        <v>303.9606617936424</v>
+        <v>304.73715687535</v>
       </c>
       <c r="E144" t="n">
-        <v>306.5888366699219</v>
+        <v>308.938232421875</v>
       </c>
       <c r="F144" t="n">
-        <v>10590200</v>
+        <v>6586600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B145" t="n">
-        <v>305.5734164156603</v>
+        <v>308.6097380099313</v>
       </c>
       <c r="C145" t="n">
-        <v>309.8640846884941</v>
+        <v>308.9581744354404</v>
       </c>
       <c r="D145" t="n">
-        <v>304.73715687535</v>
+        <v>305.344449093958</v>
       </c>
       <c r="E145" t="n">
-        <v>308.938232421875</v>
+        <v>308.4803161621094</v>
       </c>
       <c r="F145" t="n">
-        <v>6586600</v>
+        <v>6069700</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B146" t="n">
-        <v>308.6097380099313</v>
+        <v>306.0910825316173</v>
       </c>
       <c r="C146" t="n">
-        <v>308.9581744354404</v>
+        <v>312.3329523629397</v>
       </c>
       <c r="D146" t="n">
-        <v>305.344449093958</v>
+        <v>304.0900871089203</v>
       </c>
       <c r="E146" t="n">
-        <v>308.4803161621094</v>
+        <v>312.2732238769531</v>
       </c>
       <c r="F146" t="n">
-        <v>6069700</v>
+        <v>8318200</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B147" t="n">
-        <v>306.0910825316173</v>
+        <v>308.4305432499699</v>
       </c>
       <c r="C147" t="n">
-        <v>312.3329523629397</v>
+        <v>312.9103618924516</v>
       </c>
       <c r="D147" t="n">
-        <v>304.0900871089203</v>
+        <v>307.4847916064935</v>
       </c>
       <c r="E147" t="n">
-        <v>312.2732238769531</v>
+        <v>309.7247009277344</v>
       </c>
       <c r="F147" t="n">
-        <v>8318200</v>
+        <v>11455500</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B148" t="n">
-        <v>308.4305432499699</v>
+        <v>312.5420354159922</v>
       </c>
       <c r="C148" t="n">
-        <v>312.9103618924516</v>
+        <v>312.8307129741003</v>
       </c>
       <c r="D148" t="n">
-        <v>307.4847916064935</v>
+        <v>302.8954898881459</v>
       </c>
       <c r="E148" t="n">
-        <v>309.7247009277344</v>
+        <v>304.5579833984375</v>
       </c>
       <c r="F148" t="n">
-        <v>11455500</v>
+        <v>9885800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B149" t="n">
-        <v>312.5420354159922</v>
+        <v>303.9805907681049</v>
       </c>
       <c r="C149" t="n">
-        <v>312.8307129741003</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="D149" t="n">
-        <v>302.8954898881459</v>
+        <v>303.8312695552229</v>
       </c>
       <c r="E149" t="n">
-        <v>304.5579833984375</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="F149" t="n">
-        <v>9885800</v>
+        <v>8208600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B150" t="n">
-        <v>303.9805907681049</v>
+        <v>311.068653468178</v>
       </c>
       <c r="C150" t="n">
-        <v>308.5599670410156</v>
+        <v>313.4877482505245</v>
       </c>
       <c r="D150" t="n">
-        <v>303.8312695552229</v>
+        <v>308.6993222963794</v>
       </c>
       <c r="E150" t="n">
-        <v>308.5599670410156</v>
+        <v>308.8984375</v>
       </c>
       <c r="F150" t="n">
-        <v>8208600</v>
+        <v>11082400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B151" t="n">
-        <v>311.068653468178</v>
+        <v>309.4559416581444</v>
       </c>
       <c r="C151" t="n">
-        <v>313.4877482505245</v>
+        <v>315.7077766193834</v>
       </c>
       <c r="D151" t="n">
-        <v>308.6993222963794</v>
+        <v>308.9780833700189</v>
       </c>
       <c r="E151" t="n">
-        <v>308.8984375</v>
+        <v>315.5683898925781</v>
       </c>
       <c r="F151" t="n">
-        <v>11082400</v>
+        <v>10772000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B152" t="n">
-        <v>309.4559416581444</v>
+        <v>316.0661368489313</v>
       </c>
       <c r="C152" t="n">
-        <v>315.7077766193834</v>
+        <v>318.8038038717339</v>
       </c>
       <c r="D152" t="n">
-        <v>308.9780833700189</v>
+        <v>311.3474041387296</v>
       </c>
       <c r="E152" t="n">
-        <v>315.5683898925781</v>
+        <v>311.5962829589844</v>
       </c>
       <c r="F152" t="n">
-        <v>10772000</v>
+        <v>7084300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B153" t="n">
-        <v>316.0661368489313</v>
+        <v>313.4379903862348</v>
       </c>
       <c r="C153" t="n">
-        <v>318.8038038717339</v>
+        <v>313.7366328164263</v>
       </c>
       <c r="D153" t="n">
-        <v>311.3474041387296</v>
+        <v>310.5410372905177</v>
       </c>
       <c r="E153" t="n">
-        <v>311.5962829589844</v>
+        <v>311.6161804199219</v>
       </c>
       <c r="F153" t="n">
-        <v>7084300</v>
+        <v>5545900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B154" t="n">
-        <v>313.4379903862348</v>
+        <v>312.1139549773267</v>
       </c>
       <c r="C154" t="n">
-        <v>313.7366328164263</v>
+        <v>313.5773637260273</v>
       </c>
       <c r="D154" t="n">
-        <v>310.5410372905177</v>
+        <v>307.5047445243564</v>
       </c>
       <c r="E154" t="n">
-        <v>311.6161804199219</v>
+        <v>310.2921752929688</v>
       </c>
       <c r="F154" t="n">
-        <v>5545900</v>
+        <v>6969700</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B155" t="n">
-        <v>312.1139549773267</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="C155" t="n">
-        <v>313.5773637260273</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="D155" t="n">
-        <v>307.5047445243564</v>
+        <v>306.5092257615542</v>
       </c>
       <c r="E155" t="n">
-        <v>310.2921752929688</v>
+        <v>306.8974609375</v>
       </c>
       <c r="F155" t="n">
-        <v>6969700</v>
+        <v>5215300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B156" t="n">
-        <v>309.7545850384977</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="C156" t="n">
-        <v>309.7545850384977</v>
+        <v>311.1781431330245</v>
       </c>
       <c r="D156" t="n">
-        <v>306.5092257615542</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="E156" t="n">
-        <v>306.8974609375</v>
+        <v>310.232421875</v>
       </c>
       <c r="F156" t="n">
-        <v>5215300</v>
+        <v>7925300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B157" t="n">
-        <v>305.5037244427344</v>
+        <v>313.7864355589005</v>
       </c>
       <c r="C157" t="n">
-        <v>311.1781431330245</v>
+        <v>314.035314384572</v>
       </c>
       <c r="D157" t="n">
-        <v>305.5037244427344</v>
+        <v>309.7745101043047</v>
       </c>
       <c r="E157" t="n">
-        <v>310.232421875</v>
+        <v>310.0532531738281</v>
       </c>
       <c r="F157" t="n">
-        <v>7925300</v>
+        <v>7398600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B158" t="n">
-        <v>313.7864355589005</v>
+        <v>309.1771855961317</v>
       </c>
       <c r="C158" t="n">
-        <v>314.035314384572</v>
+        <v>310.6505287563671</v>
       </c>
       <c r="D158" t="n">
-        <v>309.7745101043047</v>
+        <v>305.9118967162461</v>
       </c>
       <c r="E158" t="n">
-        <v>310.0532531738281</v>
+        <v>307.8630981445312</v>
       </c>
       <c r="F158" t="n">
-        <v>7398600</v>
+        <v>8031800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B159" t="n">
-        <v>309.1771855961317</v>
+        <v>305.6928786901284</v>
       </c>
       <c r="C159" t="n">
-        <v>310.6505287563671</v>
+        <v>312.6913497643884</v>
       </c>
       <c r="D159" t="n">
-        <v>305.9118967162461</v>
+        <v>305.1951210592971</v>
       </c>
       <c r="E159" t="n">
-        <v>307.8630981445312</v>
+        <v>311.8252563476562</v>
       </c>
       <c r="F159" t="n">
-        <v>8031800</v>
+        <v>8865400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B160" t="n">
-        <v>305.6928786901284</v>
+        <v>312.5420381202088</v>
       </c>
       <c r="C160" t="n">
-        <v>312.6913497643884</v>
+        <v>314.6624601726697</v>
       </c>
       <c r="D160" t="n">
-        <v>305.1951210592971</v>
+        <v>310.431520181067</v>
       </c>
       <c r="E160" t="n">
-        <v>311.8252563476562</v>
+        <v>311.0686645507812</v>
       </c>
       <c r="F160" t="n">
-        <v>8865400</v>
+        <v>6135400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B161" t="n">
-        <v>312.5420381202088</v>
+        <v>309.2269452093906</v>
       </c>
       <c r="C161" t="n">
-        <v>314.6624601726697</v>
+        <v>309.2568094519629</v>
       </c>
       <c r="D161" t="n">
-        <v>310.431520181067</v>
+        <v>305.1353920734132</v>
       </c>
       <c r="E161" t="n">
-        <v>311.0686645507812</v>
+        <v>306.270263671875</v>
       </c>
       <c r="F161" t="n">
-        <v>6135400</v>
+        <v>7338200</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B162" t="n">
-        <v>309.2269452093906</v>
+        <v>306.3299974055641</v>
       </c>
       <c r="C162" t="n">
-        <v>309.2568094519629</v>
+        <v>309.5753869306937</v>
       </c>
       <c r="D162" t="n">
-        <v>305.1353920734132</v>
+        <v>305.42407485773</v>
       </c>
       <c r="E162" t="n">
-        <v>306.270263671875</v>
+        <v>308.0124206542969</v>
       </c>
       <c r="F162" t="n">
-        <v>7338200</v>
+        <v>6316800</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B163" t="n">
-        <v>306.3299974055641</v>
+        <v>310.0532528884956</v>
       </c>
       <c r="C163" t="n">
-        <v>309.5753869306937</v>
+        <v>314.8416790595512</v>
       </c>
       <c r="D163" t="n">
-        <v>305.42407485773</v>
+        <v>309.9536952821754</v>
       </c>
       <c r="E163" t="n">
-        <v>308.0124206542969</v>
+        <v>313.4877624511719</v>
       </c>
       <c r="F163" t="n">
-        <v>6316800</v>
+        <v>8629500</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B164" t="n">
-        <v>310.0532528884956</v>
+        <v>313.2388767644321</v>
       </c>
       <c r="C164" t="n">
-        <v>314.8416790595512</v>
+        <v>314.8814709002291</v>
       </c>
       <c r="D164" t="n">
-        <v>309.9536952821754</v>
+        <v>304.7670623908274</v>
       </c>
       <c r="E164" t="n">
-        <v>313.4877624511719</v>
+        <v>304.8964538574219</v>
       </c>
       <c r="F164" t="n">
-        <v>8629500</v>
+        <v>8359600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B165" t="n">
-        <v>313.2388767644321</v>
+        <v>306.8675912418493</v>
       </c>
       <c r="C165" t="n">
-        <v>314.8814709002291</v>
+        <v>307.6042628420606</v>
       </c>
       <c r="D165" t="n">
-        <v>304.7670623908274</v>
+        <v>299.1523476664256</v>
       </c>
       <c r="E165" t="n">
-        <v>304.8964538574219</v>
+        <v>300.7451782226562</v>
       </c>
       <c r="F165" t="n">
-        <v>8359600</v>
+        <v>9464300</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B166" t="n">
-        <v>306.8675912418493</v>
+        <v>300.7451596100784</v>
       </c>
       <c r="C166" t="n">
-        <v>307.6042628420606</v>
+        <v>301.8302675742967</v>
       </c>
       <c r="D166" t="n">
-        <v>299.1523476664256</v>
+        <v>297.5395993270601</v>
       </c>
       <c r="E166" t="n">
-        <v>300.7451782226562</v>
+        <v>298.6545715332031</v>
       </c>
       <c r="F166" t="n">
-        <v>9464300</v>
+        <v>9512000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B167" t="n">
-        <v>300.7451596100784</v>
+        <v>298.6744753830843</v>
       </c>
       <c r="C167" t="n">
-        <v>301.8302675742967</v>
+        <v>304.6873960201211</v>
       </c>
       <c r="D167" t="n">
-        <v>297.5395993270601</v>
+        <v>294.2245209852311</v>
       </c>
       <c r="E167" t="n">
-        <v>298.6545715332031</v>
+        <v>303.5126953125</v>
       </c>
       <c r="F167" t="n">
-        <v>9512000</v>
+        <v>9498200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B168" t="n">
-        <v>298.6744753830843</v>
+        <v>300.9144028967509</v>
       </c>
       <c r="C168" t="n">
-        <v>304.6873960201211</v>
+        <v>301.6411400127173</v>
       </c>
       <c r="D168" t="n">
-        <v>294.2245209852311</v>
+        <v>298.7242874353194</v>
       </c>
       <c r="E168" t="n">
-        <v>303.5126953125</v>
+        <v>298.9034729003906</v>
       </c>
       <c r="F168" t="n">
-        <v>9498200</v>
+        <v>7709500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B169" t="n">
-        <v>300.9144028967509</v>
+        <v>300.8945046380796</v>
       </c>
       <c r="C169" t="n">
-        <v>301.6411400127173</v>
+        <v>302.387777613951</v>
       </c>
       <c r="D169" t="n">
-        <v>298.7242874353194</v>
+        <v>297.4699295162906</v>
       </c>
       <c r="E169" t="n">
-        <v>298.9034729003906</v>
+        <v>298.5650024414062</v>
       </c>
       <c r="F169" t="n">
-        <v>7709500</v>
+        <v>7364300</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B170" t="n">
-        <v>300.8945046380796</v>
+        <v>298.8636262885424</v>
       </c>
       <c r="C170" t="n">
-        <v>302.387777613951</v>
+        <v>299.4410421498196</v>
       </c>
       <c r="D170" t="n">
-        <v>297.4699295162906</v>
+        <v>295.1205095874812</v>
       </c>
       <c r="E170" t="n">
-        <v>298.5650024414062</v>
+        <v>296.4743957519531</v>
       </c>
       <c r="F170" t="n">
-        <v>7364300</v>
+        <v>8699300</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B171" t="n">
-        <v>298.8636262885424</v>
+        <v>296.6635495230975</v>
       </c>
       <c r="C171" t="n">
-        <v>299.4410421498196</v>
+        <v>299.908939014877</v>
       </c>
       <c r="D171" t="n">
-        <v>295.1205095874812</v>
+        <v>295.8870488301784</v>
       </c>
       <c r="E171" t="n">
-        <v>296.4743957519531</v>
+        <v>299.3813171386719</v>
       </c>
       <c r="F171" t="n">
-        <v>8699300</v>
+        <v>7546300</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B172" t="n">
-        <v>296.6635495230975</v>
+        <v>299.7396822358739</v>
       </c>
       <c r="C172" t="n">
-        <v>299.908939014877</v>
+        <v>300.436555061437</v>
       </c>
       <c r="D172" t="n">
-        <v>295.8870488301784</v>
+        <v>293.935841710235</v>
       </c>
       <c r="E172" t="n">
-        <v>299.3813171386719</v>
+        <v>294.3738708496094</v>
       </c>
       <c r="F172" t="n">
-        <v>7546300</v>
+        <v>8066900</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B173" t="n">
-        <v>299.7396822358739</v>
+        <v>295.3694126574367</v>
       </c>
       <c r="C173" t="n">
-        <v>300.436555061437</v>
+        <v>301.57145376365</v>
       </c>
       <c r="D173" t="n">
-        <v>293.935841710235</v>
+        <v>292.3530024013792</v>
       </c>
       <c r="E173" t="n">
-        <v>294.3738708496094</v>
+        <v>300.625732421875</v>
       </c>
       <c r="F173" t="n">
-        <v>8066900</v>
+        <v>9327000</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B174" t="n">
-        <v>295.3694126574367</v>
+        <v>299.8790926087445</v>
       </c>
       <c r="C174" t="n">
-        <v>301.57145376365</v>
+        <v>302.6167597554335</v>
       </c>
       <c r="D174" t="n">
-        <v>292.3530024013792</v>
+        <v>298.8636475324957</v>
       </c>
       <c r="E174" t="n">
-        <v>300.625732421875</v>
+        <v>301.6411437988281</v>
       </c>
       <c r="F174" t="n">
-        <v>9327000</v>
+        <v>7874400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B175" t="n">
-        <v>299.8790926087445</v>
+        <v>303.3135932887391</v>
       </c>
       <c r="C175" t="n">
-        <v>302.6167597554335</v>
+        <v>306.0711901040885</v>
       </c>
       <c r="D175" t="n">
-        <v>298.8636475324957</v>
+        <v>302.4773640852478</v>
       </c>
       <c r="E175" t="n">
-        <v>301.6411437988281</v>
+        <v>305.0059814453125</v>
       </c>
       <c r="F175" t="n">
-        <v>7874400</v>
+        <v>5973900</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B176" t="n">
-        <v>303.3135932887391</v>
+        <v>307.1065011172144</v>
       </c>
       <c r="C176" t="n">
-        <v>306.0711901040885</v>
+        <v>308.5400455607295</v>
       </c>
       <c r="D176" t="n">
-        <v>302.4773640852478</v>
+        <v>304.0701916446211</v>
       </c>
       <c r="E176" t="n">
-        <v>305.0059814453125</v>
+        <v>305.3643493652344</v>
       </c>
       <c r="F176" t="n">
-        <v>5973900</v>
+        <v>7725400</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B177" t="n">
-        <v>307.1065011172144</v>
+        <v>303.6321536663258</v>
       </c>
       <c r="C177" t="n">
-        <v>308.5400455607295</v>
+        <v>304.5281113223131</v>
       </c>
       <c r="D177" t="n">
-        <v>304.0701916446211</v>
+        <v>294.4236375305438</v>
       </c>
       <c r="E177" t="n">
-        <v>305.3643493652344</v>
+        <v>297.9378051757812</v>
       </c>
       <c r="F177" t="n">
-        <v>7725400</v>
+        <v>11779200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B178" t="n">
-        <v>303.6321536663258</v>
+        <v>296.2354906683788</v>
       </c>
       <c r="C178" t="n">
-        <v>304.5281113223131</v>
+        <v>299.7197941661088</v>
       </c>
       <c r="D178" t="n">
-        <v>294.4236375305438</v>
+        <v>294.4236455581874</v>
       </c>
       <c r="E178" t="n">
-        <v>297.9378051757812</v>
+        <v>295.3992614746094</v>
       </c>
       <c r="F178" t="n">
-        <v>11779200</v>
+        <v>9757700</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B179" t="n">
-        <v>296.2354906683788</v>
+        <v>295.070728717322</v>
       </c>
       <c r="C179" t="n">
-        <v>299.7197941661088</v>
+        <v>298.5351328968941</v>
       </c>
       <c r="D179" t="n">
-        <v>294.4236455581874</v>
+        <v>293.8761285862639</v>
       </c>
       <c r="E179" t="n">
-        <v>295.3992614746094</v>
+        <v>297.9676818847656</v>
       </c>
       <c r="F179" t="n">
-        <v>9757700</v>
+        <v>13969000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B180" t="n">
-        <v>295.070728717322</v>
+        <v>296.3549462063085</v>
       </c>
       <c r="C180" t="n">
-        <v>298.5351328968941</v>
+        <v>298.2065900448191</v>
       </c>
       <c r="D180" t="n">
-        <v>293.8761285862639</v>
+        <v>293.9457858606032</v>
       </c>
       <c r="E180" t="n">
-        <v>297.9676818847656</v>
+        <v>295.2499084472656</v>
       </c>
       <c r="F180" t="n">
-        <v>13969000</v>
+        <v>7930000</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B181" t="n">
-        <v>296.3549462063085</v>
+        <v>295.170270518017</v>
       </c>
       <c r="C181" t="n">
-        <v>298.2065900448191</v>
+        <v>300.7152977310929</v>
       </c>
       <c r="D181" t="n">
-        <v>293.9457858606032</v>
+        <v>293.9457758280521</v>
       </c>
       <c r="E181" t="n">
-        <v>295.2499084472656</v>
+        <v>299.6102600097656</v>
       </c>
       <c r="F181" t="n">
-        <v>7930000</v>
+        <v>8296200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B182" t="n">
-        <v>295.170270518017</v>
+        <v>298.5749714904202</v>
       </c>
       <c r="C182" t="n">
-        <v>300.7152977310929</v>
+        <v>300.6058008918799</v>
       </c>
       <c r="D182" t="n">
-        <v>293.9457758280521</v>
+        <v>295.2300241797341</v>
       </c>
       <c r="E182" t="n">
-        <v>299.6102600097656</v>
+        <v>299.5007934570312</v>
       </c>
       <c r="F182" t="n">
-        <v>8296200</v>
+        <v>7003900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B183" t="n">
-        <v>298.5749714904202</v>
+        <v>304.3688300919619</v>
       </c>
       <c r="C183" t="n">
-        <v>300.6058008918799</v>
+        <v>311.5066879726736</v>
       </c>
       <c r="D183" t="n">
-        <v>295.2300241797341</v>
+        <v>303.0746723882986</v>
       </c>
       <c r="E183" t="n">
-        <v>299.5007934570312</v>
+        <v>309.4957580566406</v>
       </c>
       <c r="F183" t="n">
-        <v>7003900</v>
+        <v>10345200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B184" t="n">
-        <v>304.3688300919619</v>
+        <v>312.8805189963161</v>
       </c>
       <c r="C184" t="n">
-        <v>311.5066879726736</v>
+        <v>313.5873263681962</v>
       </c>
       <c r="D184" t="n">
-        <v>303.0746723882986</v>
+        <v>308.211549706599</v>
       </c>
       <c r="E184" t="n">
-        <v>309.4957580566406</v>
+        <v>310.9691162109375</v>
       </c>
       <c r="F184" t="n">
-        <v>10345200</v>
+        <v>9118800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B185" t="n">
-        <v>312.8805189963161</v>
+        <v>311.8451695343703</v>
       </c>
       <c r="C185" t="n">
-        <v>313.5873263681962</v>
+        <v>314.881479064701</v>
       </c>
       <c r="D185" t="n">
-        <v>308.211549706599</v>
+        <v>309.3862455138746</v>
       </c>
       <c r="E185" t="n">
-        <v>310.9691162109375</v>
+        <v>309.7147521972656</v>
       </c>
       <c r="F185" t="n">
-        <v>9118800</v>
+        <v>6827000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B186" t="n">
-        <v>311.8451695343703</v>
+        <v>312.1040028799189</v>
       </c>
       <c r="C186" t="n">
-        <v>314.881479064701</v>
+        <v>315.0009559692908</v>
       </c>
       <c r="D186" t="n">
-        <v>309.3862455138746</v>
+        <v>307.6241841525692</v>
       </c>
       <c r="E186" t="n">
-        <v>309.7147521972656</v>
+        <v>311.2976379394531</v>
       </c>
       <c r="F186" t="n">
-        <v>6827000</v>
+        <v>11594600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B187" t="n">
-        <v>312.1040028799189</v>
+        <v>311.1582462393224</v>
       </c>
       <c r="C187" t="n">
-        <v>315.0009559692908</v>
+        <v>313.3384270822022</v>
       </c>
       <c r="D187" t="n">
-        <v>307.6241841525692</v>
+        <v>307.6440785979976</v>
       </c>
       <c r="E187" t="n">
-        <v>311.2976379394531</v>
+        <v>307.7536010742188</v>
       </c>
       <c r="F187" t="n">
-        <v>11594600</v>
+        <v>7446200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B188" t="n">
-        <v>311.1582462393224</v>
+        <v>308.1717081621576</v>
       </c>
       <c r="C188" t="n">
-        <v>313.3384270822022</v>
+        <v>313.3085706612414</v>
       </c>
       <c r="D188" t="n">
-        <v>307.6440785979976</v>
+        <v>307.4947650619962</v>
       </c>
       <c r="E188" t="n">
-        <v>307.7536010742188</v>
+        <v>312.0840759277344</v>
       </c>
       <c r="F188" t="n">
-        <v>7446200</v>
+        <v>9116600</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B189" t="n">
-        <v>308.1717081621576</v>
+        <v>314.5529794375797</v>
       </c>
       <c r="C189" t="n">
-        <v>313.3085706612414</v>
+        <v>319.8590627688811</v>
       </c>
       <c r="D189" t="n">
-        <v>307.4947650619962</v>
+        <v>314.1348496322589</v>
       </c>
       <c r="E189" t="n">
-        <v>312.0840759277344</v>
+        <v>319.2816772460938</v>
       </c>
       <c r="F189" t="n">
-        <v>9116600</v>
+        <v>7426200</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B190" t="n">
-        <v>314.5529794375797</v>
+        <v>322.4673390673774</v>
       </c>
       <c r="C190" t="n">
-        <v>319.8590627688811</v>
+        <v>324.4583697274161</v>
       </c>
       <c r="D190" t="n">
-        <v>314.1348496322589</v>
+        <v>317.4101041776777</v>
       </c>
       <c r="E190" t="n">
-        <v>319.2816772460938</v>
+        <v>317.9675903320312</v>
       </c>
       <c r="F190" t="n">
-        <v>7426200</v>
+        <v>7988900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B191" t="n">
-        <v>322.4673390673774</v>
+        <v>322.8455866314347</v>
       </c>
       <c r="C191" t="n">
-        <v>324.4583697274161</v>
+        <v>330.2621874699331</v>
       </c>
       <c r="D191" t="n">
-        <v>317.4101041776777</v>
+        <v>322.5668435738929</v>
       </c>
       <c r="E191" t="n">
-        <v>317.9675903320312</v>
+        <v>329.6549377441406</v>
       </c>
       <c r="F191" t="n">
-        <v>7988900</v>
+        <v>11094900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B192" t="n">
-        <v>322.8455866314347</v>
+        <v>330.6902497468859</v>
       </c>
       <c r="C192" t="n">
-        <v>330.2621874699331</v>
+        <v>336.2551763704633</v>
       </c>
       <c r="D192" t="n">
-        <v>322.5668435738929</v>
+        <v>330.0133066656099</v>
       </c>
       <c r="E192" t="n">
-        <v>329.6549377441406</v>
+        <v>331.9645080566406</v>
       </c>
       <c r="F192" t="n">
-        <v>11094900</v>
+        <v>12246400</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B193" t="n">
-        <v>330.6902497468859</v>
+        <v>335.4388795655989</v>
       </c>
       <c r="C193" t="n">
-        <v>336.2551763704633</v>
+        <v>336.5737511659094</v>
       </c>
       <c r="D193" t="n">
-        <v>330.0133066656099</v>
+        <v>322.7062308624821</v>
       </c>
       <c r="E193" t="n">
-        <v>331.9645080566406</v>
+        <v>323.761474609375</v>
       </c>
       <c r="F193" t="n">
-        <v>12246400</v>
+        <v>20111000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B194" t="n">
-        <v>335.4388795655989</v>
+        <v>328.221392261561</v>
       </c>
       <c r="C194" t="n">
-        <v>336.5737511659094</v>
+        <v>331.2776010100568</v>
       </c>
       <c r="D194" t="n">
-        <v>322.7062308624821</v>
+        <v>325.2846101022313</v>
       </c>
       <c r="E194" t="n">
-        <v>323.761474609375</v>
+        <v>329.993408203125</v>
       </c>
       <c r="F194" t="n">
-        <v>20111000</v>
+        <v>10182500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B195" t="n">
-        <v>328.221392261561</v>
+        <v>327.9924099173137</v>
       </c>
       <c r="C195" t="n">
-        <v>331.2776010100568</v>
+        <v>333.8659438033595</v>
       </c>
       <c r="D195" t="n">
-        <v>325.2846101022313</v>
+        <v>325.7425357353925</v>
       </c>
       <c r="E195" t="n">
-        <v>329.993408203125</v>
+        <v>332.6414794921875</v>
       </c>
       <c r="F195" t="n">
-        <v>10182500</v>
+        <v>7582200</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B196" t="n">
-        <v>327.9924099173137</v>
+        <v>331.5762891678024</v>
       </c>
       <c r="C196" t="n">
-        <v>333.8659438033595</v>
+        <v>333.0297330031709</v>
       </c>
       <c r="D196" t="n">
-        <v>325.7425357353925</v>
+        <v>328.291070440402</v>
       </c>
       <c r="E196" t="n">
-        <v>332.6414794921875</v>
+        <v>331.95458984375</v>
       </c>
       <c r="F196" t="n">
-        <v>7582200</v>
+        <v>7907400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B197" t="n">
-        <v>331.5762891678024</v>
+        <v>333.4577793441399</v>
       </c>
       <c r="C197" t="n">
-        <v>333.0297330031709</v>
+        <v>341.909724468194</v>
       </c>
       <c r="D197" t="n">
-        <v>328.291070440402</v>
+        <v>333.2586945227413</v>
       </c>
       <c r="E197" t="n">
-        <v>331.95458984375</v>
+        <v>333.6170654296875</v>
       </c>
       <c r="F197" t="n">
-        <v>7907400</v>
+        <v>10043100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B198" t="n">
-        <v>333.4577793441399</v>
+        <v>334.4931229022353</v>
       </c>
       <c r="C198" t="n">
-        <v>341.909724468194</v>
+        <v>334.8913229247855</v>
       </c>
       <c r="D198" t="n">
-        <v>333.2586945227413</v>
+        <v>326.0312433050061</v>
       </c>
       <c r="E198" t="n">
-        <v>333.6170654296875</v>
+        <v>327.5742797851562</v>
       </c>
       <c r="F198" t="n">
-        <v>10043100</v>
+        <v>17640900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B199" t="n">
-        <v>334.4931229022353</v>
+        <v>326.8077430430495</v>
       </c>
       <c r="C199" t="n">
-        <v>334.8913229247855</v>
+        <v>330.8993264933345</v>
       </c>
       <c r="D199" t="n">
-        <v>326.0312433050061</v>
+        <v>325.7325999471821</v>
       </c>
       <c r="E199" t="n">
-        <v>327.5742797851562</v>
+        <v>327.9127807617188</v>
       </c>
       <c r="F199" t="n">
-        <v>17640900</v>
+        <v>7981800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B200" t="n">
-        <v>326.8077430430495</v>
+        <v>327.4150312810326</v>
       </c>
       <c r="C200" t="n">
-        <v>330.8993264933345</v>
+        <v>328.9580677951163</v>
       </c>
       <c r="D200" t="n">
-        <v>325.7325999471821</v>
+        <v>325.2149206632551</v>
       </c>
       <c r="E200" t="n">
-        <v>327.9127807617188</v>
+        <v>325.8619995117188</v>
       </c>
       <c r="F200" t="n">
-        <v>7981800</v>
+        <v>8080100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B201" t="n">
-        <v>327.4150312810326</v>
+        <v>326.8973584256916</v>
       </c>
       <c r="C201" t="n">
-        <v>328.9580677951163</v>
+        <v>334.1347741939035</v>
       </c>
       <c r="D201" t="n">
-        <v>325.2149206632551</v>
+        <v>323.5524415571975</v>
       </c>
       <c r="E201" t="n">
-        <v>325.8619995117188</v>
+        <v>332.5718078613281</v>
       </c>
       <c r="F201" t="n">
-        <v>8080100</v>
+        <v>15210200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B202" t="n">
-        <v>326.8973584256916</v>
+        <v>336.5040683580973</v>
       </c>
       <c r="C202" t="n">
-        <v>334.1347741939035</v>
+        <v>338.4751995750331</v>
       </c>
       <c r="D202" t="n">
-        <v>323.5524415571975</v>
+        <v>330.2820977776739</v>
       </c>
       <c r="E202" t="n">
-        <v>332.5718078613281</v>
+        <v>332.9700012207031</v>
       </c>
       <c r="F202" t="n">
-        <v>15210200</v>
+        <v>8413900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,25 +5695,25 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B203" t="n">
-        <v>336.5040683580973</v>
+        <v>335</v>
       </c>
       <c r="C203" t="n">
-        <v>338.4751995750331</v>
+        <v>339.7200012207031</v>
       </c>
       <c r="D203" t="n">
-        <v>330.2820977776739</v>
+        <v>334.1099853515625</v>
       </c>
       <c r="E203" t="n">
-        <v>332.9700012207031</v>
+        <v>337.7200012207031</v>
       </c>
       <c r="F203" t="n">
-        <v>8413900</v>
+        <v>8673500</v>
       </c>
       <c r="G203" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -5721,25 +5721,25 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B204" t="n">
-        <v>335</v>
+        <v>340.9800109863281</v>
       </c>
       <c r="C204" t="n">
-        <v>339.7200012207031</v>
+        <v>341.3999938964844</v>
       </c>
       <c r="D204" t="n">
-        <v>334.1099853515625</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E204" t="n">
-        <v>337.7200012207031</v>
+        <v>339.2200012207031</v>
       </c>
       <c r="F204" t="n">
-        <v>8673500</v>
+        <v>7115800</v>
       </c>
       <c r="G204" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B205" t="n">
-        <v>340.9800109863281</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="C205" t="n">
-        <v>341.3999938964844</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="D205" t="n">
-        <v>337.0899963378906</v>
+        <v>330.1300048828125</v>
       </c>
       <c r="E205" t="n">
-        <v>339.2200012207031</v>
+        <v>330.6199951171875</v>
       </c>
       <c r="F205" t="n">
-        <v>7115800</v>
+        <v>18505200</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B206" t="n">
-        <v>336.5299987792969</v>
+        <v>331.4599914550781</v>
       </c>
       <c r="C206" t="n">
-        <v>336.5299987792969</v>
+        <v>337</v>
       </c>
       <c r="D206" t="n">
-        <v>330.1300048828125</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="E206" t="n">
-        <v>330.6199951171875</v>
+        <v>335.4700012207031</v>
       </c>
       <c r="F206" t="n">
-        <v>18505200</v>
+        <v>15570600</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B207" t="n">
-        <v>331.4599914550781</v>
+        <v>337.4700012207031</v>
       </c>
       <c r="C207" t="n">
-        <v>337</v>
+        <v>338.5899963378906</v>
       </c>
       <c r="D207" t="n">
-        <v>330.8099975585938</v>
+        <v>335.7699890136719</v>
       </c>
       <c r="E207" t="n">
-        <v>335.4700012207031</v>
+        <v>336.4700012207031</v>
       </c>
       <c r="F207" t="n">
-        <v>15570600</v>
+        <v>6299000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B208" t="n">
-        <v>337.4700012207031</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="C208" t="n">
-        <v>338.5899963378906</v>
+        <v>338.3500061035156</v>
       </c>
       <c r="D208" t="n">
-        <v>335.7699890136719</v>
+        <v>332.5</v>
       </c>
       <c r="E208" t="n">
-        <v>336.4700012207031</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="F208" t="n">
-        <v>6299000</v>
+        <v>7120300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B209" t="n">
-        <v>338.3399963378906</v>
+        <v>327</v>
       </c>
       <c r="C209" t="n">
-        <v>338.3500061035156</v>
+        <v>344.7300109863281</v>
       </c>
       <c r="D209" t="n">
-        <v>332.5</v>
+        <v>325.75</v>
       </c>
       <c r="E209" t="n">
-        <v>334.5299987792969</v>
+        <v>342.8900146484375</v>
       </c>
       <c r="F209" t="n">
-        <v>7120300</v>
+        <v>14537900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>327</v>
+        <v>345.8500061035156</v>
       </c>
       <c r="C210" t="n">
-        <v>344.7300109863281</v>
+        <v>351.239990234375</v>
       </c>
       <c r="D210" t="n">
-        <v>325.75</v>
+        <v>344.0499877929688</v>
       </c>
       <c r="E210" t="n">
-        <v>342.8900146484375</v>
+        <v>346.9100036621094</v>
       </c>
       <c r="F210" t="n">
-        <v>14537900</v>
+        <v>10750000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B211" t="n">
-        <v>345.8500061035156</v>
+        <v>349.2799987792969</v>
       </c>
       <c r="C211" t="n">
-        <v>351.239990234375</v>
+        <v>349.3399963378906</v>
       </c>
       <c r="D211" t="n">
-        <v>344.0499877929688</v>
+        <v>341.1099853515625</v>
       </c>
       <c r="E211" t="n">
-        <v>346.9100036621094</v>
+        <v>343.1499938964844</v>
       </c>
       <c r="F211" t="n">
-        <v>10750000</v>
+        <v>12432400</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B212" t="n">
-        <v>349.2799987792969</v>
+        <v>339.0299987792969</v>
       </c>
       <c r="C212" t="n">
-        <v>349.3399963378906</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="D212" t="n">
-        <v>341.1099853515625</v>
+        <v>335.0499877929688</v>
       </c>
       <c r="E212" t="n">
-        <v>343.1499938964844</v>
+        <v>341.1000061035156</v>
       </c>
       <c r="F212" t="n">
-        <v>12432400</v>
+        <v>9250900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B213" t="n">
-        <v>339.0299987792969</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="C213" t="n">
-        <v>346.1300048828125</v>
+        <v>344.260009765625</v>
       </c>
       <c r="D213" t="n">
-        <v>335.0499877929688</v>
+        <v>337.3699951171875</v>
       </c>
       <c r="E213" t="n">
-        <v>341.1000061035156</v>
+        <v>338.8699951171875</v>
       </c>
       <c r="F213" t="n">
-        <v>9250900</v>
+        <v>7723300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B214" t="n">
-        <v>341.7999877929688</v>
+        <v>340.1199951171875</v>
       </c>
       <c r="C214" t="n">
-        <v>344.260009765625</v>
+        <v>345.739990234375</v>
       </c>
       <c r="D214" t="n">
-        <v>337.3699951171875</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E214" t="n">
-        <v>338.8699951171875</v>
+        <v>345.2300109863281</v>
       </c>
       <c r="F214" t="n">
-        <v>7723300</v>
+        <v>6015300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B215" t="n">
-        <v>340.1199951171875</v>
+        <v>345.0700073242188</v>
       </c>
       <c r="C215" t="n">
-        <v>345.739990234375</v>
+        <v>349.0700073242188</v>
       </c>
       <c r="D215" t="n">
-        <v>337.2999877929688</v>
+        <v>344.25</v>
       </c>
       <c r="E215" t="n">
-        <v>345.2300109863281</v>
+        <v>348.2099914550781</v>
       </c>
       <c r="F215" t="n">
-        <v>6015300</v>
+        <v>8040200</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B216" t="n">
-        <v>345.0700073242188</v>
+        <v>346.5799865722656</v>
       </c>
       <c r="C216" t="n">
-        <v>349.0700073242188</v>
+        <v>349.9200134277344</v>
       </c>
       <c r="D216" t="n">
-        <v>344.25</v>
+        <v>345.4200134277344</v>
       </c>
       <c r="E216" t="n">
-        <v>348.2099914550781</v>
+        <v>349.8999938964844</v>
       </c>
       <c r="F216" t="n">
-        <v>8040200</v>
+        <v>10913000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B217" t="n">
-        <v>346.5799865722656</v>
+        <v>350.6400146484375</v>
       </c>
       <c r="C217" t="n">
-        <v>349.9200134277344</v>
+        <v>353.3699951171875</v>
       </c>
       <c r="D217" t="n">
-        <v>345.4200134277344</v>
+        <v>347.5</v>
       </c>
       <c r="E217" t="n">
-        <v>349.8999938964844</v>
+        <v>353.2099914550781</v>
       </c>
       <c r="F217" t="n">
-        <v>10913000</v>
+        <v>7520800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B218" t="n">
-        <v>350.6400146484375</v>
+        <v>357.8900146484375</v>
       </c>
       <c r="C218" t="n">
-        <v>353.3699951171875</v>
+        <v>359.0499877929688</v>
       </c>
       <c r="D218" t="n">
-        <v>347.5</v>
+        <v>352.5799865722656</v>
       </c>
       <c r="E218" t="n">
-        <v>353.2099914550781</v>
+        <v>356.2000122070312</v>
       </c>
       <c r="F218" t="n">
-        <v>7520800</v>
+        <v>7884900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B219" t="n">
-        <v>357.8900146484375</v>
+        <v>357.2999877929688</v>
       </c>
       <c r="C219" t="n">
-        <v>359.0499877929688</v>
+        <v>359.2999877929688</v>
       </c>
       <c r="D219" t="n">
-        <v>352.5799865722656</v>
+        <v>354.1499938964844</v>
       </c>
       <c r="E219" t="n">
-        <v>356.2000122070312</v>
+        <v>357.3099975585938</v>
       </c>
       <c r="F219" t="n">
-        <v>7884900</v>
+        <v>6533800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B220" t="n">
-        <v>357.2999877929688</v>
+        <v>356.5</v>
       </c>
       <c r="C220" t="n">
-        <v>359.2999877929688</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D220" t="n">
-        <v>354.1499938964844</v>
+        <v>343.7799987792969</v>
       </c>
       <c r="E220" t="n">
-        <v>357.3099975585938</v>
+        <v>344.7099914550781</v>
       </c>
       <c r="F220" t="n">
-        <v>6533800</v>
+        <v>8265300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B221" t="n">
-        <v>356.5</v>
+        <v>347.5400085449219</v>
       </c>
       <c r="C221" t="n">
-        <v>357.3699951171875</v>
+        <v>352.2799987792969</v>
       </c>
       <c r="D221" t="n">
-        <v>343.7799987792969</v>
+        <v>345.3699951171875</v>
       </c>
       <c r="E221" t="n">
-        <v>344.7099914550781</v>
+        <v>350.8500061035156</v>
       </c>
       <c r="F221" t="n">
-        <v>8265300</v>
+        <v>7606500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B222" t="n">
-        <v>347.5400085449219</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C222" t="n">
-        <v>352.2799987792969</v>
+        <v>354.4700012207031</v>
       </c>
       <c r="D222" t="n">
-        <v>345.3699951171875</v>
+        <v>349.7000122070312</v>
       </c>
       <c r="E222" t="n">
-        <v>350.8500061035156</v>
+        <v>351.7900085449219</v>
       </c>
       <c r="F222" t="n">
-        <v>7606500</v>
+        <v>6603400</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B223" t="n">
-        <v>353.2999877929688</v>
+        <v>353.75</v>
       </c>
       <c r="C223" t="n">
-        <v>354.4700012207031</v>
+        <v>355.6199951171875</v>
       </c>
       <c r="D223" t="n">
-        <v>349.7000122070312</v>
+        <v>350.8399963378906</v>
       </c>
       <c r="E223" t="n">
-        <v>351.7900085449219</v>
+        <v>352.6400146484375</v>
       </c>
       <c r="F223" t="n">
-        <v>6603400</v>
+        <v>6436600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B224" t="n">
-        <v>353.75</v>
+        <v>355</v>
       </c>
       <c r="C224" t="n">
-        <v>355.6199951171875</v>
+        <v>363</v>
       </c>
       <c r="D224" t="n">
-        <v>350.8399963378906</v>
+        <v>353.8699951171875</v>
       </c>
       <c r="E224" t="n">
-        <v>352.6400146484375</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F224" t="n">
-        <v>6436600</v>
+        <v>8477200</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B225" t="n">
-        <v>355</v>
+        <v>358.9700012207031</v>
       </c>
       <c r="C225" t="n">
-        <v>363</v>
+        <v>362.1700134277344</v>
       </c>
       <c r="D225" t="n">
-        <v>353.8699951171875</v>
+        <v>358.2000122070312</v>
       </c>
       <c r="E225" t="n">
-        <v>357.5199890136719</v>
+        <v>359.239990234375</v>
       </c>
       <c r="F225" t="n">
-        <v>8477200</v>
+        <v>5269500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B226" t="n">
-        <v>358.9700012207031</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="C226" t="n">
-        <v>362.1700134277344</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="D226" t="n">
-        <v>358.2000122070312</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="E226" t="n">
-        <v>359.239990234375</v>
+        <v>356.2999877929688</v>
       </c>
       <c r="F226" t="n">
-        <v>5269500</v>
+        <v>5820100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B227" t="n">
-        <v>362.8099975585938</v>
+        <v>355.760009765625</v>
       </c>
       <c r="C227" t="n">
-        <v>362.8099975585938</v>
+        <v>358.8500061035156</v>
       </c>
       <c r="D227" t="n">
-        <v>354.9500122070312</v>
+        <v>353.3299865722656</v>
       </c>
       <c r="E227" t="n">
-        <v>356.2999877929688</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F227" t="n">
-        <v>5820100</v>
+        <v>4566200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B228" t="n">
-        <v>355.760009765625</v>
+        <v>357.9599914550781</v>
       </c>
       <c r="C228" t="n">
-        <v>358.8500061035156</v>
+        <v>359.989990234375</v>
       </c>
       <c r="D228" t="n">
-        <v>353.3299865722656</v>
+        <v>356.5</v>
       </c>
       <c r="E228" t="n">
-        <v>357.5199890136719</v>
+        <v>359.7900085449219</v>
       </c>
       <c r="F228" t="n">
-        <v>4566200</v>
+        <v>5327500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B229" t="n">
-        <v>357.9599914550781</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="C229" t="n">
-        <v>359.989990234375</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="D229" t="n">
-        <v>356.5</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="E229" t="n">
-        <v>359.7900085449219</v>
+        <v>362.0400085449219</v>
       </c>
       <c r="F229" t="n">
-        <v>5327500</v>
+        <v>4576500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B230" t="n">
-        <v>360.0499877929688</v>
+        <v>362.9700012207031</v>
       </c>
       <c r="C230" t="n">
-        <v>363.1199951171875</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="D230" t="n">
-        <v>358.6000061035156</v>
+        <v>361.2999877929688</v>
       </c>
       <c r="E230" t="n">
-        <v>362.0400085449219</v>
+        <v>365.1799926757812</v>
       </c>
       <c r="F230" t="n">
-        <v>4576500</v>
+        <v>4366800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B231" t="n">
-        <v>362.9700012207031</v>
+        <v>366.5</v>
       </c>
       <c r="C231" t="n">
-        <v>366.0899963378906</v>
+        <v>366.5</v>
       </c>
       <c r="D231" t="n">
-        <v>361.2999877929688</v>
+        <v>361.5199890136719</v>
       </c>
       <c r="E231" t="n">
-        <v>365.1799926757812</v>
+        <v>363.1099853515625</v>
       </c>
       <c r="F231" t="n">
-        <v>4366800</v>
+        <v>5102700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B232" t="n">
-        <v>366.5</v>
+        <v>363</v>
       </c>
       <c r="C232" t="n">
-        <v>366.5</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="D232" t="n">
-        <v>361.5199890136719</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="E232" t="n">
-        <v>363.1099853515625</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="F232" t="n">
-        <v>5102700</v>
+        <v>5058600</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B233" t="n">
-        <v>363</v>
+        <v>361.9400024414062</v>
       </c>
       <c r="C233" t="n">
-        <v>365.8999938964844</v>
+        <v>365.75</v>
       </c>
       <c r="D233" t="n">
-        <v>361.4500122070312</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="E233" t="n">
-        <v>362.8399963378906</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="F233" t="n">
-        <v>5058600</v>
+        <v>5282600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B234" t="n">
-        <v>361.9400024414062</v>
+        <v>362.3399963378906</v>
       </c>
       <c r="C234" t="n">
-        <v>365.75</v>
+        <v>363.5700073242188</v>
       </c>
       <c r="D234" t="n">
-        <v>360.9599914550781</v>
+        <v>359.2699890136719</v>
       </c>
       <c r="E234" t="n">
-        <v>360.9599914550781</v>
+        <v>363.25</v>
       </c>
       <c r="F234" t="n">
-        <v>5282600</v>
+        <v>5525100</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B235" t="n">
-        <v>362.3399963378906</v>
+        <v>363.010009765625</v>
       </c>
       <c r="C235" t="n">
-        <v>363.5700073242188</v>
+        <v>363.0499877929688</v>
       </c>
       <c r="D235" t="n">
-        <v>359.2699890136719</v>
+        <v>355.6499938964844</v>
       </c>
       <c r="E235" t="n">
-        <v>363.25</v>
+        <v>357.260009765625</v>
       </c>
       <c r="F235" t="n">
-        <v>5525100</v>
+        <v>6696200</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B236" t="n">
-        <v>363.010009765625</v>
+        <v>357.6000061035156</v>
       </c>
       <c r="C236" t="n">
-        <v>363.0499877929688</v>
+        <v>357.9500122070312</v>
       </c>
       <c r="D236" t="n">
-        <v>355.6499938964844</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E236" t="n">
-        <v>357.260009765625</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="F236" t="n">
-        <v>6696200</v>
+        <v>6799700</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B237" t="n">
-        <v>357.6000061035156</v>
+        <v>354.0700073242188</v>
       </c>
       <c r="C237" t="n">
-        <v>357.9500122070312</v>
+        <v>356.8599853515625</v>
       </c>
       <c r="D237" t="n">
-        <v>351.5499877929688</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="E237" t="n">
-        <v>351.5499877929688</v>
+        <v>351.5799865722656</v>
       </c>
       <c r="F237" t="n">
-        <v>6799700</v>
+        <v>8112100</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B238" t="n">
-        <v>354.0700073242188</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C238" t="n">
-        <v>356.8599853515625</v>
+        <v>358.2799987792969</v>
       </c>
       <c r="D238" t="n">
-        <v>350.3699951171875</v>
+        <v>352.8200073242188</v>
       </c>
       <c r="E238" t="n">
-        <v>351.5799865722656</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="F238" t="n">
-        <v>8112100</v>
+        <v>4394400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B239" t="n">
-        <v>353.2999877929688</v>
+        <v>357</v>
       </c>
       <c r="C239" t="n">
-        <v>358.2799987792969</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D239" t="n">
-        <v>352.8200073242188</v>
+        <v>353.0700073242188</v>
       </c>
       <c r="E239" t="n">
-        <v>356.3900146484375</v>
+        <v>356.6900024414062</v>
       </c>
       <c r="F239" t="n">
-        <v>4394400</v>
+        <v>4298000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B240" t="n">
-        <v>357</v>
+        <v>356.5</v>
       </c>
       <c r="C240" t="n">
-        <v>357.3699951171875</v>
+        <v>358.3500061035156</v>
       </c>
       <c r="D240" t="n">
-        <v>353.0700073242188</v>
+        <v>354.6000061035156</v>
       </c>
       <c r="E240" t="n">
-        <v>356.6900024414062</v>
+        <v>356.5</v>
       </c>
       <c r="F240" t="n">
-        <v>4298000</v>
+        <v>5796500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B241" t="n">
-        <v>356.5</v>
+        <v>354.6799926757812</v>
       </c>
       <c r="C241" t="n">
-        <v>358.3500061035156</v>
+        <v>357.5700073242188</v>
       </c>
       <c r="D241" t="n">
-        <v>354.6000061035156</v>
+        <v>352.2300109863281</v>
       </c>
       <c r="E241" t="n">
-        <v>356.5</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="F241" t="n">
-        <v>5796500</v>
+        <v>5209900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B242" t="n">
-        <v>354.6799926757812</v>
+        <v>355.6700134277344</v>
       </c>
       <c r="C242" t="n">
-        <v>357.5700073242188</v>
+        <v>358.7300109863281</v>
       </c>
       <c r="D242" t="n">
-        <v>352.2300109863281</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="E242" t="n">
-        <v>354.2200012207031</v>
+        <v>357.6199951171875</v>
       </c>
       <c r="F242" t="n">
-        <v>5209900</v>
+        <v>3914500</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B243" t="n">
-        <v>355.6700134277344</v>
+        <v>355.8999938964844</v>
       </c>
       <c r="C243" t="n">
-        <v>358.7300109863281</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="D243" t="n">
-        <v>354.2200012207031</v>
+        <v>354.7699890136719</v>
       </c>
       <c r="E243" t="n">
-        <v>357.6199951171875</v>
+        <v>356.0199890136719</v>
       </c>
       <c r="F243" t="n">
-        <v>3914500</v>
+        <v>7962900</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B244" t="n">
-        <v>355.8999938964844</v>
+        <v>355.7300109863281</v>
       </c>
       <c r="C244" t="n">
-        <v>357.7699890136719</v>
+        <v>359.9299926757812</v>
       </c>
       <c r="D244" t="n">
-        <v>354.7699890136719</v>
+        <v>354.1199951171875</v>
       </c>
       <c r="E244" t="n">
-        <v>356.0199890136719</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="F244" t="n">
-        <v>7962900</v>
+        <v>5079000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B245" t="n">
-        <v>355.7300109863281</v>
+        <v>357.5499877929688</v>
       </c>
       <c r="C245" t="n">
-        <v>359.9299926757812</v>
+        <v>361.4700012207031</v>
       </c>
       <c r="D245" t="n">
-        <v>354.1199951171875</v>
+        <v>353.7900085449219</v>
       </c>
       <c r="E245" t="n">
-        <v>354.9500122070312</v>
+        <v>356.2200012207031</v>
       </c>
       <c r="F245" t="n">
-        <v>5079000</v>
+        <v>5341400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B246" t="n">
-        <v>357.5499877929688</v>
+        <v>358.6799926757812</v>
       </c>
       <c r="C246" t="n">
-        <v>361.4700012207031</v>
+        <v>362.8500061035156</v>
       </c>
       <c r="D246" t="n">
-        <v>353.7900085449219</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="E246" t="n">
-        <v>356.2200012207031</v>
+        <v>362.0599975585938</v>
       </c>
       <c r="F246" t="n">
-        <v>5341400</v>
+        <v>5414200</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B247" t="n">
-        <v>358.6799926757812</v>
+        <v>361</v>
       </c>
       <c r="C247" t="n">
-        <v>362.8500061035156</v>
+        <v>362.8599853515625</v>
       </c>
       <c r="D247" t="n">
-        <v>356.3900146484375</v>
+        <v>355.2000122070312</v>
       </c>
       <c r="E247" t="n">
-        <v>362.0599975585938</v>
+        <v>358.6400146484375</v>
       </c>
       <c r="F247" t="n">
-        <v>5414200</v>
+        <v>4873500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B248" t="n">
-        <v>361</v>
+        <v>357.1000061035156</v>
       </c>
       <c r="C248" t="n">
-        <v>362.8599853515625</v>
+        <v>358.5499877929688</v>
       </c>
       <c r="D248" t="n">
-        <v>355.2000122070312</v>
+        <v>353.2300109863281</v>
       </c>
       <c r="E248" t="n">
-        <v>358.6400146484375</v>
+        <v>353.510009765625</v>
       </c>
       <c r="F248" t="n">
-        <v>4873500</v>
+        <v>5631400</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B249" t="n">
-        <v>357.1000061035156</v>
+        <v>352</v>
       </c>
       <c r="C249" t="n">
-        <v>358.5499877929688</v>
+        <v>356.3299865722656</v>
       </c>
       <c r="D249" t="n">
-        <v>353.2300109863281</v>
+        <v>348.6900024414062</v>
       </c>
       <c r="E249" t="n">
-        <v>353.510009765625</v>
+        <v>354.7099914550781</v>
       </c>
       <c r="F249" t="n">
-        <v>5631400</v>
+        <v>6318200</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B250" t="n">
-        <v>352</v>
+        <v>353.510009765625</v>
       </c>
       <c r="C250" t="n">
-        <v>356.3299865722656</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="D250" t="n">
-        <v>348.6900024414062</v>
+        <v>351.1199951171875</v>
       </c>
       <c r="E250" t="n">
-        <v>354.7099914550781</v>
+        <v>353.5599975585938</v>
       </c>
       <c r="F250" t="n">
-        <v>6318200</v>
+        <v>4184200</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B251" t="n">
-        <v>353.510009765625</v>
+        <v>358.3200073242188</v>
       </c>
       <c r="C251" t="n">
-        <v>354.2200012207031</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="D251" t="n">
-        <v>351.1199951171875</v>
+        <v>354.7900085449219</v>
       </c>
       <c r="E251" t="n">
-        <v>353.5599975585938</v>
+        <v>356.2300109863281</v>
       </c>
       <c r="F251" t="n">
-        <v>4184200</v>
+        <v>5354600</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B252" t="n">
-        <v>358.3200073242188</v>
+        <v>354.2300109863281</v>
       </c>
       <c r="C252" t="n">
-        <v>360.0499877929688</v>
+        <v>355.2799987792969</v>
       </c>
       <c r="D252" t="n">
-        <v>354.7900085449219</v>
+        <v>347.5499877929688</v>
       </c>
       <c r="E252" t="n">
-        <v>356.2300109863281</v>
+        <v>350.1300048828125</v>
       </c>
       <c r="F252" t="n">
-        <v>5354600</v>
+        <v>9609900</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10017,34 +10017,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>350.13</v>
+      </c>
+      <c r="D2" t="n">
         <v>356.23</v>
       </c>
-      <c r="D2" t="n">
-        <v>353.56</v>
-      </c>
       <c r="E2" t="n">
-        <v>358.32</v>
+        <v>354.23</v>
       </c>
       <c r="F2" t="n">
-        <v>360.04</v>
+        <v>355.25</v>
       </c>
       <c r="G2" t="n">
-        <v>354.8</v>
+        <v>347.545</v>
       </c>
       <c r="H2" t="n">
-        <v>5340945</v>
+        <v>8228221</v>
       </c>
       <c r="I2" t="n">
-        <v>7952185</v>
+        <v>7978498</v>
       </c>
       <c r="J2" t="n">
-        <v>946925731840</v>
+        <v>930710749184</v>
       </c>
       <c r="K2" t="n">
-        <v>15.269182</v>
+        <v>15.007715</v>
       </c>
       <c r="L2" t="n">
-        <v>14.256049</v>
+        <v>14.011931</v>
       </c>
       <c r="M2" t="n">
         <v>23.33</v>
@@ -10087,7 +10087,7 @@
         <v>133.007</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.67828</v>
+        <v>2.632418</v>
       </c>
       <c r="Z2" t="n">
         <v>0.469</v>
@@ -10099,7 +10099,7 @@
         <v>186328006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>784853696512</v>
+        <v>768638713856</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-12 21:47:07</t>
+          <t>2026-09-15 14:14:13</t>
         </is>
       </c>
     </row>

--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B2" t="n">
-        <v>301.4039344978193</v>
+        <v>304.563492987762</v>
       </c>
       <c r="C2" t="n">
-        <v>304.1317481949604</v>
+        <v>307.0361777394413</v>
       </c>
       <c r="D2" t="n">
-        <v>301.4039344978193</v>
+        <v>302.973877849489</v>
       </c>
       <c r="E2" t="n">
-        <v>303.1014404296875</v>
+        <v>305.89794921875</v>
       </c>
       <c r="F2" t="n">
-        <v>7122000</v>
+        <v>8657800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B3" t="n">
-        <v>304.1807788708881</v>
+        <v>305.9372178866198</v>
       </c>
       <c r="C3" t="n">
-        <v>305.0638783689902</v>
+        <v>307.556238792954</v>
       </c>
       <c r="D3" t="n">
-        <v>301.3646583866889</v>
+        <v>303.7981171700278</v>
       </c>
       <c r="E3" t="n">
-        <v>303.385986328125</v>
+        <v>307.3501892089844</v>
       </c>
       <c r="F3" t="n">
-        <v>10525600</v>
+        <v>8050700</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B4" t="n">
-        <v>304.563492987762</v>
+        <v>307.7132209495945</v>
       </c>
       <c r="C4" t="n">
-        <v>307.0361777394413</v>
+        <v>309.8719053836384</v>
       </c>
       <c r="D4" t="n">
-        <v>302.973877849489</v>
+        <v>303.3173070986313</v>
       </c>
       <c r="E4" t="n">
-        <v>305.89794921875</v>
+        <v>308.8710632324219</v>
       </c>
       <c r="F4" t="n">
-        <v>8657800</v>
+        <v>23568600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B5" t="n">
-        <v>305.9372178866198</v>
+        <v>303.9845245259009</v>
       </c>
       <c r="C5" t="n">
-        <v>307.556238792954</v>
+        <v>307.8113389670314</v>
       </c>
       <c r="D5" t="n">
-        <v>303.7981171700278</v>
+        <v>303.7490393091097</v>
       </c>
       <c r="E5" t="n">
-        <v>307.3501892089844</v>
+        <v>306.5749816894531</v>
       </c>
       <c r="F5" t="n">
-        <v>8050700</v>
+        <v>7520200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B6" t="n">
-        <v>307.7132209495945</v>
+        <v>305.9666409066948</v>
       </c>
       <c r="C6" t="n">
-        <v>309.8719053836384</v>
+        <v>310.3723467544506</v>
       </c>
       <c r="D6" t="n">
-        <v>303.3173070986313</v>
+        <v>304.7498973520222</v>
       </c>
       <c r="E6" t="n">
-        <v>308.8710632324219</v>
+        <v>306.8693542480469</v>
       </c>
       <c r="F6" t="n">
-        <v>23568600</v>
+        <v>8584400</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B7" t="n">
-        <v>303.9845245259009</v>
+        <v>308.154769837798</v>
       </c>
       <c r="C7" t="n">
-        <v>307.8113389670314</v>
+        <v>310.6372765145315</v>
       </c>
       <c r="D7" t="n">
-        <v>303.7490393091097</v>
+        <v>305.8194713781714</v>
       </c>
       <c r="E7" t="n">
-        <v>306.5749816894531</v>
+        <v>307.53662109375</v>
       </c>
       <c r="F7" t="n">
-        <v>7520200</v>
+        <v>7310500</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B8" t="n">
-        <v>305.9666409066948</v>
+        <v>308.2234768510796</v>
       </c>
       <c r="C8" t="n">
-        <v>310.3723467544506</v>
+        <v>309.7247551863121</v>
       </c>
       <c r="D8" t="n">
-        <v>304.7498973520222</v>
+        <v>305.947019653492</v>
       </c>
       <c r="E8" t="n">
-        <v>306.8693542480469</v>
+        <v>307.5660705566406</v>
       </c>
       <c r="F8" t="n">
-        <v>8584400</v>
+        <v>7083200</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B9" t="n">
-        <v>308.154769837798</v>
+        <v>308.988785738579</v>
       </c>
       <c r="C9" t="n">
-        <v>310.6372765145315</v>
+        <v>311.8441636854759</v>
       </c>
       <c r="D9" t="n">
-        <v>305.8194713781714</v>
+        <v>307.8113297451866</v>
       </c>
       <c r="E9" t="n">
-        <v>307.53662109375</v>
+        <v>310.1270141601562</v>
       </c>
       <c r="F9" t="n">
-        <v>7310500</v>
+        <v>7258100</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B10" t="n">
-        <v>308.2234768510796</v>
+        <v>311.1082857354447</v>
       </c>
       <c r="C10" t="n">
-        <v>309.7247551863121</v>
+        <v>312.0404647281687</v>
       </c>
       <c r="D10" t="n">
-        <v>305.947019653492</v>
+        <v>307.7721150397051</v>
       </c>
       <c r="E10" t="n">
-        <v>307.5660705566406</v>
+        <v>309.7640075683594</v>
       </c>
       <c r="F10" t="n">
-        <v>7083200</v>
+        <v>6462400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B11" t="n">
-        <v>308.988785738579</v>
+        <v>310.3134645283819</v>
       </c>
       <c r="C11" t="n">
-        <v>311.8441636854759</v>
+        <v>311.4516930034957</v>
       </c>
       <c r="D11" t="n">
-        <v>307.8113297451866</v>
+        <v>304.288708108424</v>
       </c>
       <c r="E11" t="n">
-        <v>310.1270141601562</v>
+        <v>309.5088500976562</v>
       </c>
       <c r="F11" t="n">
-        <v>7258100</v>
+        <v>11823300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B12" t="n">
-        <v>311.1082857354447</v>
+        <v>308.0762861336198</v>
       </c>
       <c r="C12" t="n">
-        <v>312.0404647281687</v>
+        <v>308.6846429587351</v>
       </c>
       <c r="D12" t="n">
-        <v>307.7721150397051</v>
+        <v>301.6394301376976</v>
       </c>
       <c r="E12" t="n">
-        <v>309.7640075683594</v>
+        <v>304.8774719238281</v>
       </c>
       <c r="F12" t="n">
-        <v>6462400</v>
+        <v>9235200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B13" t="n">
-        <v>310.3134645283819</v>
+        <v>304.1808160870063</v>
       </c>
       <c r="C13" t="n">
-        <v>311.4516930034957</v>
+        <v>304.7303016172636</v>
       </c>
       <c r="D13" t="n">
-        <v>304.288708108424</v>
+        <v>300.393288685967</v>
       </c>
       <c r="E13" t="n">
-        <v>309.5088500976562</v>
+        <v>301.7767944335938</v>
       </c>
       <c r="F13" t="n">
-        <v>11823300</v>
+        <v>7600000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B14" t="n">
-        <v>308.0763169713923</v>
+        <v>302.718779227698</v>
       </c>
       <c r="C14" t="n">
-        <v>308.6846738574029</v>
+        <v>305.8096426575195</v>
       </c>
       <c r="D14" t="n">
-        <v>301.6394603311547</v>
+        <v>302.4243927447969</v>
       </c>
       <c r="E14" t="n">
-        <v>304.8775024414062</v>
+        <v>304.2102355957031</v>
       </c>
       <c r="F14" t="n">
-        <v>9235200</v>
+        <v>6029900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,25 +807,25 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B15" t="n">
-        <v>304.1808160870063</v>
+        <v>305.8371341622301</v>
       </c>
       <c r="C15" t="n">
-        <v>304.7303016172636</v>
+        <v>307.3851596699703</v>
       </c>
       <c r="D15" t="n">
-        <v>300.393288685967</v>
+        <v>300.857851711314</v>
       </c>
       <c r="E15" t="n">
-        <v>301.7767944335938</v>
+        <v>304.8511352539062</v>
       </c>
       <c r="F15" t="n">
-        <v>7600000</v>
+        <v>7214500</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B16" t="n">
-        <v>302.7188095956571</v>
+        <v>305.0187502270194</v>
       </c>
       <c r="C16" t="n">
-        <v>305.809673335546</v>
+        <v>305.6695130787729</v>
       </c>
       <c r="D16" t="n">
-        <v>302.4244230832239</v>
+        <v>300.4338615931582</v>
       </c>
       <c r="E16" t="n">
-        <v>304.2102661132812</v>
+        <v>303.3819885253906</v>
       </c>
       <c r="F16" t="n">
-        <v>6029900</v>
+        <v>8454200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,25 +859,25 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B17" t="n">
-        <v>305.8371035459471</v>
+        <v>303.8946917756213</v>
       </c>
       <c r="C17" t="n">
-        <v>307.3851288987199</v>
+        <v>304.4567183318842</v>
       </c>
       <c r="D17" t="n">
-        <v>300.8578215934895</v>
+        <v>299.2999336047902</v>
       </c>
       <c r="E17" t="n">
-        <v>304.8511047363281</v>
+        <v>299.7732238769531</v>
       </c>
       <c r="F17" t="n">
-        <v>7214500</v>
+        <v>6489900</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B18" t="n">
-        <v>305.0187502270194</v>
+        <v>300.7789375021521</v>
       </c>
       <c r="C18" t="n">
-        <v>305.6695130787729</v>
+        <v>303.7270945284432</v>
       </c>
       <c r="D18" t="n">
-        <v>300.4338615931582</v>
+        <v>299.1422058887319</v>
       </c>
       <c r="E18" t="n">
-        <v>303.3819885253906</v>
+        <v>301.2522277832031</v>
       </c>
       <c r="F18" t="n">
-        <v>8454200</v>
+        <v>7060300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B19" t="n">
-        <v>303.894722712774</v>
+        <v>301.3804193716138</v>
       </c>
       <c r="C19" t="n">
-        <v>304.4567493262524</v>
+        <v>306.1230715472904</v>
       </c>
       <c r="D19" t="n">
-        <v>299.2999640741864</v>
+        <v>296.5983188157025</v>
       </c>
       <c r="E19" t="n">
-        <v>299.7732543945312</v>
+        <v>296.6772155761719</v>
       </c>
       <c r="F19" t="n">
-        <v>6489900</v>
+        <v>8597400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B20" t="n">
-        <v>300.7789375021521</v>
+        <v>301.3212684867699</v>
       </c>
       <c r="C20" t="n">
-        <v>303.7270945284432</v>
+        <v>305.1272097801061</v>
       </c>
       <c r="D20" t="n">
-        <v>299.1422058887319</v>
+        <v>301.1733746705027</v>
       </c>
       <c r="E20" t="n">
-        <v>301.2522277832031</v>
+        <v>303.6580810546875</v>
       </c>
       <c r="F20" t="n">
-        <v>7060300</v>
+        <v>10788700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B21" t="n">
-        <v>301.3804193716138</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C21" t="n">
-        <v>306.1230715472904</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D21" t="n">
-        <v>296.5983188157025</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E21" t="n">
-        <v>296.6772155761719</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F21" t="n">
-        <v>8597400</v>
+        <v>16178800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B22" t="n">
-        <v>301.321238204041</v>
+        <v>302.1002149225357</v>
       </c>
       <c r="C22" t="n">
-        <v>305.1271791148808</v>
+        <v>307.7499693151439</v>
       </c>
       <c r="D22" t="n">
-        <v>301.173344402637</v>
+        <v>301.1635039391426</v>
       </c>
       <c r="E22" t="n">
-        <v>303.6580505371094</v>
+        <v>301.4100036621094</v>
       </c>
       <c r="F22" t="n">
-        <v>10788700</v>
+        <v>11354800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B23" t="n">
-        <v>301.5578902761218</v>
+        <v>301.0747260223031</v>
       </c>
       <c r="C23" t="n">
-        <v>302.7016525742085</v>
+        <v>304.358088638523</v>
       </c>
       <c r="D23" t="n">
-        <v>290.0907186231138</v>
+        <v>292.9106575300408</v>
       </c>
       <c r="E23" t="n">
-        <v>297.8505249023438</v>
+        <v>294.3600769042969</v>
       </c>
       <c r="F23" t="n">
-        <v>16178800</v>
+        <v>10549400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B24" t="n">
-        <v>302.1001843350741</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C24" t="n">
-        <v>307.7499381556482</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D24" t="n">
-        <v>301.1634734465224</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E24" t="n">
-        <v>301.4099731445312</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F24" t="n">
-        <v>11354800</v>
+        <v>10153500</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B25" t="n">
-        <v>301.0747572360179</v>
+        <v>294.3206459359216</v>
       </c>
       <c r="C25" t="n">
-        <v>304.3581201926382</v>
+        <v>299.4379821870563</v>
       </c>
       <c r="D25" t="n">
-        <v>292.9106878973514</v>
+        <v>293.9854099500461</v>
       </c>
       <c r="E25" t="n">
-        <v>294.360107421875</v>
+        <v>298.1265869140625</v>
       </c>
       <c r="F25" t="n">
-        <v>10549400</v>
+        <v>6894900</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B26" t="n">
-        <v>294.9714335987563</v>
+        <v>297.436411288458</v>
       </c>
       <c r="C26" t="n">
-        <v>295.3559575215809</v>
+        <v>299.7929328501146</v>
       </c>
       <c r="D26" t="n">
-        <v>290.0808874955599</v>
+        <v>292.8416531202475</v>
       </c>
       <c r="E26" t="n">
-        <v>293.3938293457031</v>
+        <v>292.9303894042969</v>
       </c>
       <c r="F26" t="n">
-        <v>10153500</v>
+        <v>7372700</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B27" t="n">
-        <v>294.3206459359216</v>
+        <v>293.6008552074487</v>
       </c>
       <c r="C27" t="n">
-        <v>299.4379821870563</v>
+        <v>293.8868032880077</v>
       </c>
       <c r="D27" t="n">
-        <v>293.9854099500461</v>
+        <v>286.4721030595595</v>
       </c>
       <c r="E27" t="n">
-        <v>298.1265869140625</v>
+        <v>289.9920959472656</v>
       </c>
       <c r="F27" t="n">
-        <v>6894900</v>
+        <v>8054100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B28" t="n">
-        <v>297.436411288458</v>
+        <v>290.2583742532713</v>
       </c>
       <c r="C28" t="n">
-        <v>299.7929328501146</v>
+        <v>292.220502524991</v>
       </c>
       <c r="D28" t="n">
-        <v>292.8416531202475</v>
+        <v>288.4145610405075</v>
       </c>
       <c r="E28" t="n">
-        <v>292.9303894042969</v>
+        <v>290.4161376953125</v>
       </c>
       <c r="F28" t="n">
-        <v>7372700</v>
+        <v>5438800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B29" t="n">
-        <v>293.6008552074487</v>
+        <v>291.9345495322769</v>
       </c>
       <c r="C29" t="n">
-        <v>293.8868032880077</v>
+        <v>298.3632818043669</v>
       </c>
       <c r="D29" t="n">
-        <v>286.4721030595595</v>
+        <v>291.3133954831271</v>
       </c>
       <c r="E29" t="n">
-        <v>289.9920959472656</v>
+        <v>296.2335205078125</v>
       </c>
       <c r="F29" t="n">
-        <v>8054100</v>
+        <v>7228300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B30" t="n">
-        <v>290.2583437522712</v>
+        <v>297.92941246883</v>
       </c>
       <c r="C30" t="n">
-        <v>292.2204718178062</v>
+        <v>300.2662249001909</v>
       </c>
       <c r="D30" t="n">
-        <v>288.4145307332595</v>
+        <v>296.7955198233114</v>
       </c>
       <c r="E30" t="n">
-        <v>290.4161071777344</v>
+        <v>299.8915405273438</v>
       </c>
       <c r="F30" t="n">
-        <v>5438800</v>
+        <v>5642200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B31" t="n">
-        <v>291.9345194575729</v>
+        <v>300.5915953010157</v>
       </c>
       <c r="C31" t="n">
-        <v>298.3632510673837</v>
+        <v>303.6580673748709</v>
       </c>
       <c r="D31" t="n">
-        <v>291.3133654724136</v>
+        <v>298.915415308335</v>
       </c>
       <c r="E31" t="n">
-        <v>296.2334899902344</v>
+        <v>301.0845947265625</v>
       </c>
       <c r="F31" t="n">
-        <v>7228300</v>
+        <v>6336000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B32" t="n">
-        <v>297.92941246883</v>
+        <v>299.2605157595805</v>
       </c>
       <c r="C32" t="n">
-        <v>300.2662249001909</v>
+        <v>303.9341406042103</v>
       </c>
       <c r="D32" t="n">
-        <v>296.7955198233114</v>
+        <v>298.7675163425421</v>
       </c>
       <c r="E32" t="n">
-        <v>299.8915405273438</v>
+        <v>301.2325134277344</v>
       </c>
       <c r="F32" t="n">
-        <v>5642200</v>
+        <v>7520300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B33" t="n">
-        <v>300.5915953010157</v>
+        <v>301.5086233262724</v>
       </c>
       <c r="C33" t="n">
-        <v>303.6580673748709</v>
+        <v>308.233113206998</v>
       </c>
       <c r="D33" t="n">
-        <v>298.915415308335</v>
+        <v>300.8282816526182</v>
       </c>
       <c r="E33" t="n">
-        <v>301.0845947265625</v>
+        <v>305.1075134277344</v>
       </c>
       <c r="F33" t="n">
-        <v>6336000</v>
+        <v>7514600</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B34" t="n">
-        <v>299.2605157595805</v>
+        <v>304.2200828300273</v>
       </c>
       <c r="C34" t="n">
-        <v>303.9341406042103</v>
+        <v>308.4894444595929</v>
       </c>
       <c r="D34" t="n">
-        <v>298.7675163425421</v>
+        <v>302.9481359332913</v>
       </c>
       <c r="E34" t="n">
-        <v>301.2325134277344</v>
+        <v>306.7639465332031</v>
       </c>
       <c r="F34" t="n">
-        <v>7520300</v>
+        <v>7721300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B35" t="n">
-        <v>301.5085931686638</v>
+        <v>306.6456604912348</v>
       </c>
       <c r="C35" t="n">
-        <v>308.2330823767899</v>
+        <v>307.9471862719047</v>
       </c>
       <c r="D35" t="n">
-        <v>300.828251563059</v>
+        <v>301.9227172950412</v>
       </c>
       <c r="E35" t="n">
-        <v>305.1074829101562</v>
+        <v>305.0187683105469</v>
       </c>
       <c r="F35" t="n">
-        <v>7514600</v>
+        <v>7770000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B36" t="n">
-        <v>304.2200828300273</v>
+        <v>302.415720333495</v>
       </c>
       <c r="C36" t="n">
-        <v>308.4894444595929</v>
+        <v>307.8485840116909</v>
       </c>
       <c r="D36" t="n">
-        <v>302.9481359332913</v>
+        <v>300.8282765156093</v>
       </c>
       <c r="E36" t="n">
-        <v>306.7639465332031</v>
+        <v>304.920166015625</v>
       </c>
       <c r="F36" t="n">
-        <v>7721300</v>
+        <v>7085200</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B37" t="n">
-        <v>306.6456604912348</v>
+        <v>305.2751066360906</v>
       </c>
       <c r="C37" t="n">
-        <v>307.9471862719047</v>
+        <v>308.7162632770978</v>
       </c>
       <c r="D37" t="n">
-        <v>301.9227172950412</v>
+        <v>301.3508502506656</v>
       </c>
       <c r="E37" t="n">
-        <v>305.0187683105469</v>
+        <v>307.3161315917969</v>
       </c>
       <c r="F37" t="n">
-        <v>7770000</v>
+        <v>6865200</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B38" t="n">
-        <v>302.415720333495</v>
+        <v>306.6357990367445</v>
       </c>
       <c r="C38" t="n">
-        <v>307.8485840116909</v>
+        <v>310.4319009529449</v>
       </c>
       <c r="D38" t="n">
-        <v>300.8282765156093</v>
+        <v>305.9160390722913</v>
       </c>
       <c r="E38" t="n">
-        <v>304.920166015625</v>
+        <v>309.0317993164062</v>
       </c>
       <c r="F38" t="n">
-        <v>7085200</v>
+        <v>7206100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B39" t="n">
-        <v>305.2751066360906</v>
+        <v>307.5232049313688</v>
       </c>
       <c r="C39" t="n">
-        <v>308.7162632770978</v>
+        <v>310.0276204199649</v>
       </c>
       <c r="D39" t="n">
-        <v>301.3508502506656</v>
+        <v>303.3327096940284</v>
       </c>
       <c r="E39" t="n">
-        <v>307.3161315917969</v>
+        <v>309.8106994628906</v>
       </c>
       <c r="F39" t="n">
-        <v>6865200</v>
+        <v>7302300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B40" t="n">
-        <v>306.6357687557767</v>
+        <v>310.5896337890794</v>
       </c>
       <c r="C40" t="n">
-        <v>310.4318702971036</v>
+        <v>315.0857860805166</v>
       </c>
       <c r="D40" t="n">
-        <v>305.9160088624015</v>
+        <v>309.8106862822301</v>
       </c>
       <c r="E40" t="n">
-        <v>309.0317687988281</v>
+        <v>312.4531860351562</v>
       </c>
       <c r="F40" t="n">
-        <v>7206100</v>
+        <v>5794100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B41" t="n">
-        <v>307.5232049313688</v>
+        <v>313.0546102409576</v>
       </c>
       <c r="C41" t="n">
-        <v>310.0276204199649</v>
+        <v>314.5828963020791</v>
       </c>
       <c r="D41" t="n">
-        <v>303.3327096940284</v>
+        <v>310.8656917625901</v>
       </c>
       <c r="E41" t="n">
-        <v>309.8106994628906</v>
+        <v>311.200927734375</v>
       </c>
       <c r="F41" t="n">
-        <v>7302300</v>
+        <v>5030200</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B42" t="n">
-        <v>310.5896337890794</v>
+        <v>311.8320000281587</v>
       </c>
       <c r="C42" t="n">
-        <v>315.0857860805166</v>
+        <v>317.7381233989844</v>
       </c>
       <c r="D42" t="n">
-        <v>309.8106862822301</v>
+        <v>311.782682032414</v>
       </c>
       <c r="E42" t="n">
-        <v>312.4531860351562</v>
+        <v>315.9238891601562</v>
       </c>
       <c r="F42" t="n">
-        <v>5794100</v>
+        <v>10578300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B43" t="n">
-        <v>313.0546102409576</v>
+        <v>314.7604311532612</v>
       </c>
       <c r="C43" t="n">
-        <v>314.5828963020791</v>
+        <v>316.1408235578094</v>
       </c>
       <c r="D43" t="n">
-        <v>310.8656917625901</v>
+        <v>304.7722577523736</v>
       </c>
       <c r="E43" t="n">
-        <v>311.200927734375</v>
+        <v>305.1469421386719</v>
       </c>
       <c r="F43" t="n">
-        <v>5030200</v>
+        <v>8973300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B44" t="n">
-        <v>311.8320000281587</v>
+        <v>303.2044890700107</v>
       </c>
       <c r="C44" t="n">
-        <v>317.7381233989844</v>
+        <v>303.3326737235763</v>
       </c>
       <c r="D44" t="n">
-        <v>311.782682032414</v>
+        <v>297.012418045434</v>
       </c>
       <c r="E44" t="n">
-        <v>315.9238891601562</v>
+        <v>299.3590698242188</v>
       </c>
       <c r="F44" t="n">
-        <v>10578300</v>
+        <v>10327000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B45" t="n">
-        <v>314.7604626322791</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C45" t="n">
-        <v>316.1408551748796</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D45" t="n">
-        <v>304.7722882324798</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E45" t="n">
-        <v>305.14697265625</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F45" t="n">
-        <v>8973300</v>
+        <v>8344000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B46" t="n">
-        <v>303.2044890700107</v>
+        <v>295.3066623130797</v>
       </c>
       <c r="C46" t="n">
-        <v>303.3326737235763</v>
+        <v>298.708370459316</v>
       </c>
       <c r="D46" t="n">
-        <v>297.012418045434</v>
+        <v>292.8613742767781</v>
       </c>
       <c r="E46" t="n">
-        <v>299.3590698242188</v>
+        <v>295.2179260253906</v>
       </c>
       <c r="F46" t="n">
-        <v>10327000</v>
+        <v>8077300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B47" t="n">
-        <v>299.7436397411884</v>
+        <v>295.5432899586994</v>
       </c>
       <c r="C47" t="n">
-        <v>301.3113742461044</v>
+        <v>300.1873662746028</v>
       </c>
       <c r="D47" t="n">
-        <v>293.5022804823602</v>
+        <v>295.0798692888629</v>
       </c>
       <c r="E47" t="n">
-        <v>296.1644592285156</v>
+        <v>299.0238647460938</v>
       </c>
       <c r="F47" t="n">
-        <v>8344000</v>
+        <v>5546600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B48" t="n">
-        <v>295.3066623130797</v>
+        <v>302.0509050250311</v>
       </c>
       <c r="C48" t="n">
-        <v>298.708370459316</v>
+        <v>305.5807980031574</v>
       </c>
       <c r="D48" t="n">
-        <v>292.8613742767781</v>
+        <v>293.9854410949062</v>
       </c>
       <c r="E48" t="n">
-        <v>295.2179260253906</v>
+        <v>294.2023620605469</v>
       </c>
       <c r="F48" t="n">
-        <v>8077300</v>
+        <v>7501600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B49" t="n">
-        <v>295.5432597963394</v>
+        <v>297.0716172552904</v>
       </c>
       <c r="C49" t="n">
-        <v>300.1873356382808</v>
+        <v>297.4561411796575</v>
       </c>
       <c r="D49" t="n">
-        <v>295.0798391737984</v>
+        <v>288.7103357437745</v>
       </c>
       <c r="E49" t="n">
-        <v>299.0238342285156</v>
+        <v>293.8473815917969</v>
       </c>
       <c r="F49" t="n">
-        <v>5546600</v>
+        <v>11766800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B50" t="n">
-        <v>302.0508736933244</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C50" t="n">
-        <v>305.5807663052954</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D50" t="n">
-        <v>293.9854105998292</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E50" t="n">
-        <v>294.2023315429688</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F50" t="n">
-        <v>7501600</v>
+        <v>10940200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B51" t="n">
-        <v>297.0715864028587</v>
+        <v>295.8489209666184</v>
       </c>
       <c r="C51" t="n">
-        <v>297.456110287291</v>
+        <v>300.2366275598507</v>
       </c>
       <c r="D51" t="n">
-        <v>288.7103057597054</v>
+        <v>291.4217960873232</v>
       </c>
       <c r="E51" t="n">
-        <v>293.8473510742188</v>
+        <v>298.7576293945312</v>
       </c>
       <c r="F51" t="n">
-        <v>11766800</v>
+        <v>8877200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B52" t="n">
-        <v>294.0642973394352</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C52" t="n">
-        <v>295.6221924256846</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D52" t="n">
-        <v>290.386540762355</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E52" t="n">
-        <v>293.8276672363281</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F52" t="n">
-        <v>10940200</v>
+        <v>7910900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B53" t="n">
-        <v>295.848951187077</v>
+        <v>304.7722465716023</v>
       </c>
       <c r="C53" t="n">
-        <v>300.236658228506</v>
+        <v>309.3275563846455</v>
       </c>
       <c r="D53" t="n">
-        <v>291.4218258555586</v>
+        <v>303.9242719247256</v>
       </c>
       <c r="E53" t="n">
-        <v>298.7576599121094</v>
+        <v>308.6965026855469</v>
       </c>
       <c r="F53" t="n">
-        <v>8877200</v>
+        <v>4322400</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B54" t="n">
-        <v>300.7296512123902</v>
+        <v>308.5683618849884</v>
       </c>
       <c r="C54" t="n">
-        <v>304.2102259719906</v>
+        <v>309.6430970545817</v>
       </c>
       <c r="D54" t="n">
-        <v>298.9548653069277</v>
+        <v>304.2201032083801</v>
       </c>
       <c r="E54" t="n">
-        <v>303.3327026367188</v>
+        <v>304.5947875976562</v>
       </c>
       <c r="F54" t="n">
-        <v>7910900</v>
+        <v>7727300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B55" t="n">
-        <v>304.7722465716023</v>
+        <v>304.4172805196406</v>
       </c>
       <c r="C55" t="n">
-        <v>309.3275563846455</v>
+        <v>306.1329390093465</v>
       </c>
       <c r="D55" t="n">
-        <v>303.9242719247256</v>
+        <v>302.7903884074122</v>
       </c>
       <c r="E55" t="n">
-        <v>308.6965026855469</v>
+        <v>303.5693359375</v>
       </c>
       <c r="F55" t="n">
-        <v>4322400</v>
+        <v>7249000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B56" t="n">
-        <v>308.5683309692949</v>
+        <v>302.8988595387675</v>
       </c>
       <c r="C56" t="n">
-        <v>309.6430660312097</v>
+        <v>307.9865871384521</v>
       </c>
       <c r="D56" t="n">
-        <v>304.2200727283419</v>
+        <v>302.5044359255107</v>
       </c>
       <c r="E56" t="n">
-        <v>304.5947570800781</v>
+        <v>307.7598266601562</v>
       </c>
       <c r="F56" t="n">
-        <v>7727300</v>
+        <v>8535300</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B57" t="n">
-        <v>304.4172805196406</v>
+        <v>308.8740523757101</v>
       </c>
       <c r="C57" t="n">
-        <v>306.1329390093465</v>
+        <v>314.0308078212495</v>
       </c>
       <c r="D57" t="n">
-        <v>302.7903884074122</v>
+        <v>308.617683010128</v>
       </c>
       <c r="E57" t="n">
-        <v>303.5693359375</v>
+        <v>311.6742858886719</v>
       </c>
       <c r="F57" t="n">
-        <v>7249000</v>
+        <v>9627800</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B58" t="n">
-        <v>302.8988595387675</v>
+        <v>311.2207252653726</v>
       </c>
       <c r="C58" t="n">
-        <v>307.9865871384521</v>
+        <v>314.0209586927274</v>
       </c>
       <c r="D58" t="n">
-        <v>302.5044359255107</v>
+        <v>310.2741446015314</v>
       </c>
       <c r="E58" t="n">
-        <v>307.7598266601562</v>
+        <v>310.6291198730469</v>
       </c>
       <c r="F58" t="n">
-        <v>8535300</v>
+        <v>6518900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B59" t="n">
-        <v>308.8740221323167</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C59" t="n">
-        <v>314.0307770729326</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D59" t="n">
-        <v>308.617652791837</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E59" t="n">
-        <v>311.6742553710938</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F59" t="n">
-        <v>9627800</v>
+        <v>7417200</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B60" t="n">
-        <v>311.2206946896725</v>
+        <v>310.5403783790639</v>
       </c>
       <c r="C60" t="n">
-        <v>314.0209278419201</v>
+        <v>314.336450228146</v>
       </c>
       <c r="D60" t="n">
-        <v>310.2741141188276</v>
+        <v>295.8193913272319</v>
       </c>
       <c r="E60" t="n">
-        <v>310.6290893554688</v>
+        <v>296.3025512695312</v>
       </c>
       <c r="F60" t="n">
-        <v>6518900</v>
+        <v>18049200</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B61" t="n">
-        <v>310.6487980837529</v>
+        <v>296.292632599085</v>
       </c>
       <c r="C61" t="n">
-        <v>312.0390600856641</v>
+        <v>306.8329619363725</v>
       </c>
       <c r="D61" t="n">
-        <v>308.9627484602848</v>
+        <v>294.2811866679717</v>
       </c>
       <c r="E61" t="n">
-        <v>310.7966918945312</v>
+        <v>305.76806640625</v>
       </c>
       <c r="F61" t="n">
-        <v>7417200</v>
+        <v>18874100</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B62" t="n">
-        <v>310.5403783790639</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C62" t="n">
-        <v>314.336450228146</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D62" t="n">
-        <v>295.8193913272319</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E62" t="n">
-        <v>296.3025512695312</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F62" t="n">
-        <v>18049200</v>
+        <v>9721900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B63" t="n">
-        <v>296.292632599085</v>
+        <v>315.2041261224818</v>
       </c>
       <c r="C63" t="n">
-        <v>306.8329619363725</v>
+        <v>315.7858618718594</v>
       </c>
       <c r="D63" t="n">
-        <v>294.2811866679717</v>
+        <v>312.1672627021157</v>
       </c>
       <c r="E63" t="n">
-        <v>305.76806640625</v>
+        <v>314.0603637695312</v>
       </c>
       <c r="F63" t="n">
-        <v>18874100</v>
+        <v>8982900</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B64" t="n">
-        <v>304.9102649889192</v>
+        <v>315.1153648797306</v>
       </c>
       <c r="C64" t="n">
-        <v>313.5476242674454</v>
+        <v>318.3593094805321</v>
       </c>
       <c r="D64" t="n">
-        <v>304.9102649889192</v>
+        <v>313.9321843288561</v>
       </c>
       <c r="E64" t="n">
-        <v>312.9363098144531</v>
+        <v>315.5393371582031</v>
       </c>
       <c r="F64" t="n">
-        <v>9721900</v>
+        <v>10864100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B65" t="n">
-        <v>315.2041261224818</v>
+        <v>314.6224027314819</v>
       </c>
       <c r="C65" t="n">
-        <v>315.7858618718594</v>
+        <v>315.0463750601788</v>
       </c>
       <c r="D65" t="n">
-        <v>312.1672627021157</v>
+        <v>309.9980652283745</v>
       </c>
       <c r="E65" t="n">
-        <v>314.0603637695312</v>
+        <v>311.1319580078125</v>
       </c>
       <c r="F65" t="n">
-        <v>8982900</v>
+        <v>8331300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B66" t="n">
-        <v>315.115395356304</v>
+        <v>313.9716244610726</v>
       </c>
       <c r="C66" t="n">
-        <v>318.3593402708456</v>
+        <v>314.8984658400699</v>
       </c>
       <c r="D66" t="n">
-        <v>313.9322146909975</v>
+        <v>310.2544194174254</v>
       </c>
       <c r="E66" t="n">
-        <v>315.5393676757812</v>
+        <v>310.5699462890625</v>
       </c>
       <c r="F66" t="n">
-        <v>10864100</v>
+        <v>8718700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B67" t="n">
-        <v>314.6224027314819</v>
+        <v>311.5756418636432</v>
       </c>
       <c r="C67" t="n">
-        <v>315.0463750601788</v>
+        <v>313.2518519730792</v>
       </c>
       <c r="D67" t="n">
-        <v>309.9980652283745</v>
+        <v>307.8485673512913</v>
       </c>
       <c r="E67" t="n">
-        <v>311.1319580078125</v>
+        <v>308.6176452636719</v>
       </c>
       <c r="F67" t="n">
-        <v>8331300</v>
+        <v>11444900</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B68" t="n">
-        <v>313.971593609235</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C68" t="n">
-        <v>314.8984348971578</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D68" t="n">
-        <v>310.254388930852</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E68" t="n">
-        <v>310.5699157714844</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F68" t="n">
-        <v>8718700</v>
+        <v>24494400</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B69" t="n">
-        <v>311.575672673722</v>
+        <v>313.064515200958</v>
       </c>
       <c r="C69" t="n">
-        <v>313.2518829489097</v>
+        <v>318.7044300194866</v>
       </c>
       <c r="D69" t="n">
-        <v>307.8485977928193</v>
+        <v>313.064515200958</v>
       </c>
       <c r="E69" t="n">
-        <v>308.61767578125</v>
+        <v>318.5663757324219</v>
       </c>
       <c r="F69" t="n">
-        <v>11444900</v>
+        <v>8354600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B70" t="n">
-        <v>309.3965776494671</v>
+        <v>319.0790830432475</v>
       </c>
       <c r="C70" t="n">
-        <v>314.099781180705</v>
+        <v>323.1907116116738</v>
       </c>
       <c r="D70" t="n">
-        <v>308.8049723403709</v>
+        <v>318.5663744582675</v>
       </c>
       <c r="E70" t="n">
-        <v>312.7686767578125</v>
+        <v>321.3666076660156</v>
       </c>
       <c r="F70" t="n">
-        <v>24494400</v>
+        <v>6668300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B71" t="n">
-        <v>313.0644852104395</v>
+        <v>321.6722493328215</v>
       </c>
       <c r="C71" t="n">
-        <v>318.7043994886834</v>
+        <v>325.3697449529369</v>
       </c>
       <c r="D71" t="n">
-        <v>313.0644852104395</v>
+        <v>320.9426198260136</v>
       </c>
       <c r="E71" t="n">
-        <v>318.5663452148438</v>
+        <v>324.5612487792969</v>
       </c>
       <c r="F71" t="n">
-        <v>8354600</v>
+        <v>4289300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B72" t="n">
-        <v>319.0790830432475</v>
+        <v>324.5020893383847</v>
       </c>
       <c r="C72" t="n">
-        <v>323.1907116116738</v>
+        <v>326.22758744424</v>
       </c>
       <c r="D72" t="n">
-        <v>318.5663744582675</v>
+        <v>321.9680949886989</v>
       </c>
       <c r="E72" t="n">
-        <v>321.3666076660156</v>
+        <v>323.3189086914062</v>
       </c>
       <c r="F72" t="n">
-        <v>6668300</v>
+        <v>4158300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B73" t="n">
-        <v>321.6722493328215</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C73" t="n">
-        <v>325.3697449529369</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D73" t="n">
-        <v>320.9426198260136</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E73" t="n">
-        <v>324.5612487792969</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F73" t="n">
-        <v>4289300</v>
+        <v>8635300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B74" t="n">
-        <v>324.502058709128</v>
+        <v>320.2623075229155</v>
       </c>
       <c r="C74" t="n">
-        <v>326.2275566521161</v>
+        <v>320.3904921972535</v>
       </c>
       <c r="D74" t="n">
-        <v>321.9680645986219</v>
+        <v>317.9747828016658</v>
       </c>
       <c r="E74" t="n">
-        <v>323.3188781738281</v>
+        <v>318.8917846679688</v>
       </c>
       <c r="F74" t="n">
-        <v>4158300</v>
+        <v>7904300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B75" t="n">
-        <v>322.4216288798564</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C75" t="n">
-        <v>323.1808371734579</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D75" t="n">
-        <v>319.0002116144308</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E75" t="n">
-        <v>319.2171325683594</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F75" t="n">
-        <v>8635300</v>
+        <v>5048500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B76" t="n">
-        <v>320.2623075229155</v>
+        <v>317.9846252281575</v>
       </c>
       <c r="C76" t="n">
-        <v>320.3904921972535</v>
+        <v>321.1694123071354</v>
       </c>
       <c r="D76" t="n">
-        <v>317.9747828016658</v>
+        <v>316.2492576445291</v>
       </c>
       <c r="E76" t="n">
-        <v>318.8917846679688</v>
+        <v>320.9229125976562</v>
       </c>
       <c r="F76" t="n">
-        <v>7904300</v>
+        <v>8054000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B77" t="n">
-        <v>319.7988699190817</v>
+        <v>320.942628937084</v>
       </c>
       <c r="C77" t="n">
-        <v>320.3313177342217</v>
+        <v>332.5281155423397</v>
       </c>
       <c r="D77" t="n">
-        <v>317.5310845539587</v>
+        <v>320.636971697701</v>
       </c>
       <c r="E77" t="n">
-        <v>317.7085571289062</v>
+        <v>329.3630676269531</v>
       </c>
       <c r="F77" t="n">
-        <v>5048500</v>
+        <v>10752600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,25 +2445,25 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B78" t="n">
-        <v>317.9846252281575</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C78" t="n">
-        <v>321.1694123071354</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D78" t="n">
-        <v>316.2492576445291</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E78" t="n">
-        <v>320.9229125976562</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F78" t="n">
-        <v>8054000</v>
+        <v>7660800</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B79" t="n">
-        <v>320.9426586744551</v>
+        <v>327.9764659913386</v>
       </c>
       <c r="C79" t="n">
-        <v>332.5281463531796</v>
+        <v>328.9767963949314</v>
       </c>
       <c r="D79" t="n">
-        <v>320.637001406751</v>
+        <v>321.4989374679619</v>
       </c>
       <c r="E79" t="n">
-        <v>329.3630981445312</v>
+        <v>323.8660888671875</v>
       </c>
       <c r="F79" t="n">
-        <v>10752600</v>
+        <v>9815200</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,25 +2497,25 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B80" t="n">
-        <v>329.4422902981328</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C80" t="n">
-        <v>332.6612412306879</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D80" t="n">
-        <v>327.491109600743</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E80" t="n">
-        <v>331.4132690429688</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F80" t="n">
-        <v>7660800</v>
+        <v>11737100</v>
       </c>
       <c r="G80" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B81" t="n">
-        <v>327.9764350864437</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C81" t="n">
-        <v>328.9767653957764</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D81" t="n">
-        <v>321.4989071734381</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E81" t="n">
-        <v>323.8660583496094</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F81" t="n">
-        <v>9815200</v>
+        <v>6738100</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B82" t="n">
-        <v>323.2718313763784</v>
+        <v>318.8049029297019</v>
       </c>
       <c r="C82" t="n">
-        <v>328.2339475379842</v>
+        <v>322.9053354478686</v>
       </c>
       <c r="D82" t="n">
-        <v>322.5388804495614</v>
+        <v>318.1611187929736</v>
       </c>
       <c r="E82" t="n">
-        <v>326.6393432617188</v>
+        <v>321.3899536132812</v>
       </c>
       <c r="F82" t="n">
-        <v>11737100</v>
+        <v>12805100</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B83" t="n">
-        <v>326.1936353875406</v>
+        <v>321.2017547389941</v>
       </c>
       <c r="C83" t="n">
-        <v>328.7291759216584</v>
+        <v>323.7372950994605</v>
       </c>
       <c r="D83" t="n">
-        <v>325.0348299492433</v>
+        <v>307.6029450408882</v>
       </c>
       <c r="E83" t="n">
-        <v>326.0450744628906</v>
+        <v>307.9297790527344</v>
       </c>
       <c r="F83" t="n">
-        <v>6738100</v>
+        <v>19371200</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B84" t="n">
-        <v>318.8049332018166</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C84" t="n">
-        <v>322.9053661093398</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D84" t="n">
-        <v>318.1611490039577</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E84" t="n">
-        <v>321.3899841308594</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F84" t="n">
-        <v>12805100</v>
+        <v>25951500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B85" t="n">
-        <v>321.2017865718998</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C85" t="n">
-        <v>323.7373271836527</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D85" t="n">
-        <v>307.6029755260753</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E85" t="n">
-        <v>307.9298095703125</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F85" t="n">
-        <v>19371200</v>
+        <v>14751400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B86" t="n">
-        <v>305.2556057077196</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C86" t="n">
-        <v>308.7815926253858</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D86" t="n">
-        <v>303.1954601804828</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E86" t="n">
-        <v>304.9287414550781</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F86" t="n">
-        <v>25951500</v>
+        <v>14652500</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B87" t="n">
-        <v>305.5230197927318</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C87" t="n">
-        <v>309.95031666446</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D87" t="n">
-        <v>304.8098971346673</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E87" t="n">
-        <v>306.3054809570312</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F87" t="n">
-        <v>14751400</v>
+        <v>12900600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B88" t="n">
-        <v>307.385060616362</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C88" t="n">
-        <v>314.1795087286461</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D88" t="n">
-        <v>307.0383983149945</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E88" t="n">
-        <v>309.4848022460938</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F88" t="n">
-        <v>14652500</v>
+        <v>10270100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B89" t="n">
-        <v>303.2845981841295</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C89" t="n">
-        <v>308.1774060521912</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D89" t="n">
-        <v>298.9761500928895</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E89" t="n">
-        <v>299.8477478027344</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F89" t="n">
-        <v>12900600</v>
+        <v>10535800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B90" t="n">
-        <v>300.5311849469782</v>
+        <v>299.1148112655088</v>
       </c>
       <c r="C90" t="n">
-        <v>302.4823658305288</v>
+        <v>299.4812715954647</v>
       </c>
       <c r="D90" t="n">
-        <v>298.2729680555718</v>
+        <v>293.6772702297321</v>
       </c>
       <c r="E90" t="n">
-        <v>299.1544799804688</v>
+        <v>294.8757019042969</v>
       </c>
       <c r="F90" t="n">
-        <v>10270100</v>
+        <v>11107900</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B91" t="n">
-        <v>301.9474777854751</v>
+        <v>294.9648486176391</v>
       </c>
       <c r="C91" t="n">
-        <v>305.2555953909441</v>
+        <v>298.8969221500132</v>
       </c>
       <c r="D91" t="n">
-        <v>300.0062112868251</v>
+        <v>294.6083024116733</v>
       </c>
       <c r="E91" t="n">
-        <v>300.729248046875</v>
+        <v>298.1640014648438</v>
       </c>
       <c r="F91" t="n">
-        <v>10535800</v>
+        <v>11752700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B92" t="n">
-        <v>299.1148422218051</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C92" t="n">
-        <v>299.4813025896872</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D92" t="n">
-        <v>293.6773006232809</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E92" t="n">
-        <v>294.875732421875</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F92" t="n">
-        <v>11107900</v>
+        <v>11527400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B93" t="n">
-        <v>294.9648788077786</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C93" t="n">
-        <v>298.8969527426069</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D93" t="n">
-        <v>294.6083325653198</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E93" t="n">
-        <v>298.1640319824219</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F93" t="n">
-        <v>11752700</v>
+        <v>9556700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B94" t="n">
-        <v>298.4512235287846</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C94" t="n">
-        <v>299.0851237823749</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D94" t="n">
-        <v>295.3016109870806</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E94" t="n">
-        <v>297.4409790039062</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F94" t="n">
-        <v>11527400</v>
+        <v>11580000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B95" t="n">
-        <v>297.4013222225187</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C95" t="n">
-        <v>299.0355829225425</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D95" t="n">
-        <v>295.2025300603667</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E95" t="n">
-        <v>297.8965454101562</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F95" t="n">
-        <v>9556700</v>
+        <v>11953200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B96" t="n">
-        <v>299.5110006693188</v>
+        <v>301.5513314360023</v>
       </c>
       <c r="C96" t="n">
-        <v>303.898671192008</v>
+        <v>306.3450888451811</v>
       </c>
       <c r="D96" t="n">
-        <v>299.3327275624257</v>
+        <v>298.4908553932551</v>
       </c>
       <c r="E96" t="n">
-        <v>303.4926147460938</v>
+        <v>305.1961975097656</v>
       </c>
       <c r="F96" t="n">
-        <v>11580000</v>
+        <v>9839400</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B97" t="n">
-        <v>302.333781642444</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C97" t="n">
-        <v>304.9881708986046</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D97" t="n">
-        <v>299.6694782493637</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E97" t="n">
-        <v>302.9676818847656</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F97" t="n">
-        <v>11953200</v>
+        <v>12688000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B98" t="n">
-        <v>301.5513012828864</v>
+        <v>311.4062598905275</v>
       </c>
       <c r="C98" t="n">
-        <v>306.3450582127215</v>
+        <v>316.2594412620415</v>
       </c>
       <c r="D98" t="n">
-        <v>298.4908255461663</v>
+        <v>311.4062598905275</v>
       </c>
       <c r="E98" t="n">
-        <v>305.1961669921875</v>
+        <v>314.2389221191406</v>
       </c>
       <c r="F98" t="n">
-        <v>9839400</v>
+        <v>9848800</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B99" t="n">
-        <v>306.7709905338949</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C99" t="n">
-        <v>313.2286905211348</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D99" t="n">
-        <v>306.1470044328188</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E99" t="n">
-        <v>311.8420715332031</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F99" t="n">
-        <v>12688000</v>
+        <v>9388000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B100" t="n">
-        <v>311.4062901330092</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C100" t="n">
-        <v>316.2594719758441</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D100" t="n">
-        <v>311.4062901330092</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E100" t="n">
-        <v>314.2389526367188</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F100" t="n">
-        <v>9848800</v>
+        <v>17797400</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B101" t="n">
-        <v>311.9906259989966</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C101" t="n">
-        <v>312.9909865673853</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D101" t="n">
-        <v>302.6210112179966</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E101" t="n">
-        <v>307.1968688964844</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F101" t="n">
-        <v>9388000</v>
+        <v>11477500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B102" t="n">
-        <v>311.7034102684662</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C102" t="n">
-        <v>321.1522783634816</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D102" t="n">
-        <v>311.7034102684662</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E102" t="n">
-        <v>319.3199462890625</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F102" t="n">
-        <v>17797400</v>
+        <v>9902200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B103" t="n">
-        <v>318.2700781279603</v>
+        <v>320.1519144431551</v>
       </c>
       <c r="C103" t="n">
-        <v>323.2817350541263</v>
+        <v>322.1724337503843</v>
       </c>
       <c r="D103" t="n">
-        <v>317.0518180384032</v>
+        <v>305.7805563960757</v>
       </c>
       <c r="E103" t="n">
-        <v>319.0228271484375</v>
+        <v>307.8505859375</v>
       </c>
       <c r="F103" t="n">
-        <v>11477500</v>
+        <v>8703500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B104" t="n">
-        <v>319.4684837021083</v>
+        <v>309.2966060076438</v>
       </c>
       <c r="C104" t="n">
-        <v>323.014298845819</v>
+        <v>310.6238005797982</v>
       </c>
       <c r="D104" t="n">
-        <v>312.1094739861534</v>
+        <v>297.1537232583444</v>
       </c>
       <c r="E104" t="n">
-        <v>315.2392883300781</v>
+        <v>299.7487182617188</v>
       </c>
       <c r="F104" t="n">
-        <v>9902200</v>
+        <v>13443400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B105" t="n">
-        <v>320.1518827061323</v>
+        <v>295.6680481198895</v>
       </c>
       <c r="C105" t="n">
-        <v>322.1724018130651</v>
+        <v>301.3829431862302</v>
       </c>
       <c r="D105" t="n">
-        <v>305.7805260837019</v>
+        <v>293.6871553220786</v>
       </c>
       <c r="E105" t="n">
-        <v>307.8505554199219</v>
+        <v>299.6595458984375</v>
       </c>
       <c r="F105" t="n">
-        <v>8703500</v>
+        <v>9114500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B106" t="n">
-        <v>309.2966374972976</v>
+        <v>299.8675549474044</v>
       </c>
       <c r="C106" t="n">
-        <v>310.6238322045743</v>
+        <v>305.2951817518681</v>
       </c>
       <c r="D106" t="n">
-        <v>297.1537535117247</v>
+        <v>299.6100292169066</v>
       </c>
       <c r="E106" t="n">
-        <v>299.7487487792969</v>
+        <v>304.19580078125</v>
       </c>
       <c r="F106" t="n">
-        <v>13443400</v>
+        <v>8896800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B107" t="n">
-        <v>295.6680782309701</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C107" t="n">
-        <v>301.3829738793206</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D107" t="n">
-        <v>293.6871852314235</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E107" t="n">
-        <v>299.6595764160156</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F107" t="n">
-        <v>9114500</v>
+        <v>7209600</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B108" t="n">
-        <v>299.8675850307636</v>
+        <v>304.2354576365961</v>
       </c>
       <c r="C108" t="n">
-        <v>305.2952123797385</v>
+        <v>306.226234501648</v>
       </c>
       <c r="D108" t="n">
-        <v>299.6100592744303</v>
+        <v>302.2050242231491</v>
       </c>
       <c r="E108" t="n">
-        <v>304.1958312988281</v>
+        <v>305.1070251464844</v>
       </c>
       <c r="F108" t="n">
-        <v>8896800</v>
+        <v>6737700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B109" t="n">
-        <v>305.5130974954087</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C109" t="n">
-        <v>309.2966101142475</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D109" t="n">
-        <v>304.2849535938903</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E109" t="n">
-        <v>305.8300476074219</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F109" t="n">
-        <v>7209600</v>
+        <v>7792700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B110" t="n">
-        <v>304.2354272061944</v>
+        <v>305.8498774375392</v>
       </c>
       <c r="C110" t="n">
-        <v>306.2262038721237</v>
+        <v>308.028871901531</v>
       </c>
       <c r="D110" t="n">
-        <v>302.2049939958365</v>
+        <v>292.2807780649544</v>
       </c>
       <c r="E110" t="n">
-        <v>305.1069946289062</v>
+        <v>294.8262329101562</v>
       </c>
       <c r="F110" t="n">
-        <v>6737700</v>
+        <v>12955400</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B111" t="n">
-        <v>305.4536802835111</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C111" t="n">
-        <v>308.0288471084009</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D111" t="n">
-        <v>302.7596647203387</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E111" t="n">
-        <v>307.8208618164062</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F111" t="n">
-        <v>7792700</v>
+        <v>13554100</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B112" t="n">
-        <v>305.8498457788994</v>
+        <v>295.7869207463737</v>
       </c>
       <c r="C112" t="n">
-        <v>308.0288400173425</v>
+        <v>300.7589506810849</v>
       </c>
       <c r="D112" t="n">
-        <v>292.2807478108573</v>
+        <v>294.1724883145502</v>
       </c>
       <c r="E112" t="n">
-        <v>294.8262023925781</v>
+        <v>300.4023742675781</v>
       </c>
       <c r="F112" t="n">
-        <v>12955400</v>
+        <v>8095500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B113" t="n">
-        <v>293.9843218466586</v>
+        <v>301.670173133609</v>
       </c>
       <c r="C113" t="n">
-        <v>296.886322684036</v>
+        <v>306.0578739762234</v>
       </c>
       <c r="D113" t="n">
-        <v>288.5962907533433</v>
+        <v>300.7391812579012</v>
       </c>
       <c r="E113" t="n">
-        <v>294.459716796875</v>
+        <v>303.2053833007812</v>
       </c>
       <c r="F113" t="n">
-        <v>13554100</v>
+        <v>7007800</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B114" t="n">
-        <v>295.7869507950724</v>
+        <v>297.1339389424841</v>
       </c>
       <c r="C114" t="n">
-        <v>300.7589812348872</v>
+        <v>300.0557680991628</v>
       </c>
       <c r="D114" t="n">
-        <v>294.1725181992404</v>
+        <v>291.636973162459</v>
       </c>
       <c r="E114" t="n">
-        <v>300.4024047851562</v>
+        <v>297.4310607910156</v>
       </c>
       <c r="F114" t="n">
-        <v>8095500</v>
+        <v>18620800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B115" t="n">
-        <v>301.670173133609</v>
+        <v>291.9935267958635</v>
       </c>
       <c r="C115" t="n">
-        <v>306.0578739762234</v>
+        <v>297.1141484397957</v>
       </c>
       <c r="D115" t="n">
-        <v>300.7391812579012</v>
+        <v>290.4088063693875</v>
       </c>
       <c r="E115" t="n">
-        <v>303.2053833007812</v>
+        <v>294.7172546386719</v>
       </c>
       <c r="F115" t="n">
-        <v>7007800</v>
+        <v>8508900</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B116" t="n">
-        <v>297.1339389424841</v>
+        <v>289.4975898716125</v>
       </c>
       <c r="C116" t="n">
-        <v>300.0557680991628</v>
+        <v>299.5011046657454</v>
       </c>
       <c r="D116" t="n">
-        <v>291.636973162459</v>
+        <v>286.7342359222354</v>
       </c>
       <c r="E116" t="n">
-        <v>297.4310607910156</v>
+        <v>297.3914489746094</v>
       </c>
       <c r="F116" t="n">
-        <v>18620800</v>
+        <v>10278200</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B117" t="n">
-        <v>291.9935267958635</v>
+        <v>297.1240288614248</v>
       </c>
       <c r="C117" t="n">
-        <v>297.1141484397957</v>
+        <v>298.1243894751821</v>
       </c>
       <c r="D117" t="n">
-        <v>290.4088063693875</v>
+        <v>292.993883980321</v>
       </c>
       <c r="E117" t="n">
-        <v>294.7172546386719</v>
+        <v>296.52978515625</v>
       </c>
       <c r="F117" t="n">
-        <v>8508900</v>
+        <v>8055700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B118" t="n">
-        <v>289.4975898716125</v>
+        <v>295.1332451958745</v>
       </c>
       <c r="C118" t="n">
-        <v>299.5011046657454</v>
+        <v>298.3620800816865</v>
       </c>
       <c r="D118" t="n">
-        <v>286.7342359222354</v>
+        <v>289.6362492414601</v>
       </c>
       <c r="E118" t="n">
-        <v>297.3914489746094</v>
+        <v>290.7455444335938</v>
       </c>
       <c r="F118" t="n">
-        <v>10278200</v>
+        <v>12732500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B119" t="n">
-        <v>297.1240288614248</v>
+        <v>283.6044306839189</v>
       </c>
       <c r="C119" t="n">
-        <v>298.1243894751821</v>
+        <v>287.2195541533999</v>
       </c>
       <c r="D119" t="n">
-        <v>292.993883980321</v>
+        <v>280.9995517042956</v>
       </c>
       <c r="E119" t="n">
-        <v>296.52978515625</v>
+        <v>286.7144470214844</v>
       </c>
       <c r="F119" t="n">
-        <v>8055700</v>
+        <v>13496500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B120" t="n">
-        <v>295.1332451958745</v>
+        <v>282.7724816341387</v>
       </c>
       <c r="C120" t="n">
-        <v>298.3620800816865</v>
+        <v>288.3189881947603</v>
       </c>
       <c r="D120" t="n">
-        <v>289.6362492414601</v>
+        <v>277.7707387954702</v>
       </c>
       <c r="E120" t="n">
-        <v>290.7455444335938</v>
+        <v>287.1502685546875</v>
       </c>
       <c r="F120" t="n">
-        <v>12732500</v>
+        <v>12241100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B121" t="n">
-        <v>283.6044306839189</v>
+        <v>286.5262662545288</v>
       </c>
       <c r="C121" t="n">
-        <v>287.2195541533999</v>
+        <v>289.9532025593205</v>
       </c>
       <c r="D121" t="n">
-        <v>280.9995517042956</v>
+        <v>284.4364084963449</v>
       </c>
       <c r="E121" t="n">
-        <v>286.7144470214844</v>
+        <v>285.9716186523438</v>
       </c>
       <c r="F121" t="n">
-        <v>13496500</v>
+        <v>8344900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B122" t="n">
-        <v>282.7724816341387</v>
+        <v>286.0508472723319</v>
       </c>
       <c r="C122" t="n">
-        <v>288.3189881947603</v>
+        <v>287.7049062038017</v>
       </c>
       <c r="D122" t="n">
-        <v>277.7707387954702</v>
+        <v>282.1385715612803</v>
       </c>
       <c r="E122" t="n">
-        <v>287.1502685546875</v>
+        <v>284.7731628417969</v>
       </c>
       <c r="F122" t="n">
-        <v>12241100</v>
+        <v>10205000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B123" t="n">
-        <v>286.5262662545288</v>
+        <v>280.1279843639117</v>
       </c>
       <c r="C123" t="n">
-        <v>289.9532025593205</v>
+        <v>281.1679713767581</v>
       </c>
       <c r="D123" t="n">
-        <v>284.4364084963449</v>
+        <v>276.4336380780354</v>
       </c>
       <c r="E123" t="n">
-        <v>285.9716186523438</v>
+        <v>280.1874389648438</v>
       </c>
       <c r="F123" t="n">
-        <v>8344900</v>
+        <v>13760500</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B124" t="n">
-        <v>286.0508166178312</v>
+        <v>281.9504072447318</v>
       </c>
       <c r="C124" t="n">
-        <v>287.7048753720447</v>
+        <v>284.4463214441296</v>
       </c>
       <c r="D124" t="n">
-        <v>282.1385413260368</v>
+        <v>280.2468381234208</v>
       </c>
       <c r="E124" t="n">
-        <v>284.7731323242188</v>
+        <v>280.7321472167969</v>
       </c>
       <c r="F124" t="n">
-        <v>10205000</v>
+        <v>9091200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B125" t="n">
-        <v>280.1279538528093</v>
+        <v>283.6044205599556</v>
       </c>
       <c r="C125" t="n">
-        <v>281.167940752382</v>
+        <v>286.506421278288</v>
       </c>
       <c r="D125" t="n">
-        <v>276.4336079693154</v>
+        <v>281.8909373944359</v>
       </c>
       <c r="E125" t="n">
-        <v>280.1874084472656</v>
+        <v>283.4261474609375</v>
       </c>
       <c r="F125" t="n">
-        <v>13760500</v>
+        <v>8149000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B126" t="n">
-        <v>281.9504072447318</v>
+        <v>286.2390279690733</v>
       </c>
       <c r="C126" t="n">
-        <v>284.4463214441296</v>
+        <v>288.9726698808299</v>
       </c>
       <c r="D126" t="n">
-        <v>280.2468381234208</v>
+        <v>283.2181783456238</v>
       </c>
       <c r="E126" t="n">
-        <v>280.7321472167969</v>
+        <v>284.1492004394531</v>
       </c>
       <c r="F126" t="n">
-        <v>9091200</v>
+        <v>8961200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B127" t="n">
-        <v>283.6044205599556</v>
+        <v>284.0897180113691</v>
       </c>
       <c r="C127" t="n">
-        <v>286.506421278288</v>
+        <v>286.6450865635814</v>
       </c>
       <c r="D127" t="n">
-        <v>281.8909373944359</v>
+        <v>282.3960631878955</v>
       </c>
       <c r="E127" t="n">
-        <v>283.4261474609375</v>
+        <v>284.9910278320312</v>
       </c>
       <c r="F127" t="n">
-        <v>8149000</v>
+        <v>10057000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B128" t="n">
-        <v>286.2390279690733</v>
+        <v>284.1392890417467</v>
       </c>
       <c r="C128" t="n">
-        <v>288.9726698808299</v>
+        <v>286.7441681021885</v>
       </c>
       <c r="D128" t="n">
-        <v>283.2181783456238</v>
+        <v>281.900870340191</v>
       </c>
       <c r="E128" t="n">
-        <v>284.1492004394531</v>
+        <v>285.2188720703125</v>
       </c>
       <c r="F128" t="n">
-        <v>8961200</v>
+        <v>9846700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B129" t="n">
-        <v>284.0897484324327</v>
+        <v>285.3277943529036</v>
       </c>
       <c r="C129" t="n">
-        <v>286.6451172582804</v>
+        <v>287.9326733008621</v>
       </c>
       <c r="D129" t="n">
-        <v>282.3960934275981</v>
+        <v>282.5446423017302</v>
       </c>
       <c r="E129" t="n">
-        <v>284.9910583496094</v>
+        <v>283.8223266601562</v>
       </c>
       <c r="F129" t="n">
-        <v>10057000</v>
+        <v>22436500</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B130" t="n">
-        <v>284.1392586396808</v>
+        <v>291.4982779446762</v>
       </c>
       <c r="C130" t="n">
-        <v>286.7441374214082</v>
+        <v>292.9245231806114</v>
       </c>
       <c r="D130" t="n">
-        <v>281.9008401776293</v>
+        <v>285.2188513876401</v>
       </c>
       <c r="E130" t="n">
-        <v>285.2188415527344</v>
+        <v>287.1403198242188</v>
       </c>
       <c r="F130" t="n">
-        <v>9846700</v>
+        <v>11470800</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B131" t="n">
-        <v>285.327825032355</v>
+        <v>283.4360748065673</v>
       </c>
       <c r="C131" t="n">
-        <v>287.9327042603992</v>
+        <v>292.6571288676103</v>
       </c>
       <c r="D131" t="n">
-        <v>282.5446726819272</v>
+        <v>282.6436995084055</v>
       </c>
       <c r="E131" t="n">
-        <v>283.8223571777344</v>
+        <v>289.6065368652344</v>
       </c>
       <c r="F131" t="n">
-        <v>22436500</v>
+        <v>11092300</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B132" t="n">
-        <v>291.4982779446762</v>
+        <v>291.3398308899875</v>
       </c>
       <c r="C132" t="n">
-        <v>292.9245231806114</v>
+        <v>294.7965097163498</v>
       </c>
       <c r="D132" t="n">
-        <v>285.2188513876401</v>
+        <v>289.6461758443202</v>
       </c>
       <c r="E132" t="n">
-        <v>287.1403198242188</v>
+        <v>292.5977172851562</v>
       </c>
       <c r="F132" t="n">
-        <v>11470800</v>
+        <v>12188200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B133" t="n">
-        <v>283.4360748065673</v>
+        <v>289.7847899387647</v>
       </c>
       <c r="C133" t="n">
-        <v>292.6571288676103</v>
+        <v>292.1717693530369</v>
       </c>
       <c r="D133" t="n">
-        <v>282.6436995084055</v>
+        <v>287.9524883078727</v>
       </c>
       <c r="E133" t="n">
-        <v>289.6065368652344</v>
+        <v>288.8735961914062</v>
       </c>
       <c r="F133" t="n">
-        <v>11092300</v>
+        <v>8669200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B134" t="n">
-        <v>291.3398308899875</v>
+        <v>286.3777093696089</v>
       </c>
       <c r="C134" t="n">
-        <v>294.7965097163498</v>
+        <v>287.3384134369941</v>
       </c>
       <c r="D134" t="n">
-        <v>289.6461758443202</v>
+        <v>279.0582953832721</v>
       </c>
       <c r="E134" t="n">
-        <v>292.5977172851562</v>
+        <v>280.1378784179688</v>
       </c>
       <c r="F134" t="n">
-        <v>12188200</v>
+        <v>9873300</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B135" t="n">
-        <v>289.7848205526045</v>
+        <v>282.0197247859078</v>
       </c>
       <c r="C135" t="n">
-        <v>292.1718002190451</v>
+        <v>284.505755156032</v>
       </c>
       <c r="D135" t="n">
-        <v>287.9525187281419</v>
+        <v>279.6327451103039</v>
       </c>
       <c r="E135" t="n">
-        <v>288.8736267089844</v>
+        <v>281.0589904785156</v>
       </c>
       <c r="F135" t="n">
-        <v>8669200</v>
+        <v>11734400</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B136" t="n">
-        <v>286.3777093696089</v>
+        <v>285.7140887250632</v>
       </c>
       <c r="C136" t="n">
-        <v>287.3384134369941</v>
+        <v>292.2510413422024</v>
       </c>
       <c r="D136" t="n">
-        <v>279.0582953832721</v>
+        <v>282.2277281014015</v>
       </c>
       <c r="E136" t="n">
-        <v>280.1378784179688</v>
+        <v>291.3497314453125</v>
       </c>
       <c r="F136" t="n">
-        <v>9873300</v>
+        <v>12956900</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B137" t="n">
-        <v>282.0197247859078</v>
+        <v>292.567989087923</v>
       </c>
       <c r="C137" t="n">
-        <v>284.505755156032</v>
+        <v>295.8661624411999</v>
       </c>
       <c r="D137" t="n">
-        <v>279.6327451103039</v>
+        <v>290.1116710297465</v>
       </c>
       <c r="E137" t="n">
-        <v>281.0589904785156</v>
+        <v>292.5580749511719</v>
       </c>
       <c r="F137" t="n">
-        <v>11734400</v>
+        <v>11267200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B138" t="n">
-        <v>285.7140887250632</v>
+        <v>289.1212191631598</v>
       </c>
       <c r="C138" t="n">
-        <v>292.2510413422024</v>
+        <v>292.7957669317203</v>
       </c>
       <c r="D138" t="n">
-        <v>282.2277281014015</v>
+        <v>285.9616926535428</v>
       </c>
       <c r="E138" t="n">
-        <v>291.3497314453125</v>
+        <v>291.7855224609375</v>
       </c>
       <c r="F138" t="n">
-        <v>12956900</v>
+        <v>6669300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,25 +4031,25 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B139" t="n">
-        <v>292.567989087923</v>
+        <v>292.7412191857173</v>
       </c>
       <c r="C139" t="n">
-        <v>295.8661624411999</v>
+        <v>295.4987855589938</v>
       </c>
       <c r="D139" t="n">
-        <v>290.1116710297465</v>
+        <v>291.8850906324002</v>
       </c>
       <c r="E139" t="n">
-        <v>292.5580749511719</v>
+        <v>294.125</v>
       </c>
       <c r="F139" t="n">
-        <v>11267200</v>
+        <v>7142600</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B140" t="n">
-        <v>289.1212191631598</v>
+        <v>291.8253790066561</v>
       </c>
       <c r="C140" t="n">
-        <v>292.7957669317203</v>
+        <v>296.8427544058445</v>
       </c>
       <c r="D140" t="n">
-        <v>285.9616926535428</v>
+        <v>291.3873498301165</v>
       </c>
       <c r="E140" t="n">
-        <v>291.7855224609375</v>
+        <v>296.0662536621094</v>
       </c>
       <c r="F140" t="n">
-        <v>6669300</v>
+        <v>7849100</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,25 +4083,25 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B141" t="n">
-        <v>292.7412191857173</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="C141" t="n">
-        <v>295.4987855589938</v>
+        <v>309.8640903908154</v>
       </c>
       <c r="D141" t="n">
-        <v>291.8850906324002</v>
+        <v>303.9606617936424</v>
       </c>
       <c r="E141" t="n">
-        <v>294.125</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="F141" t="n">
-        <v>7142600</v>
+        <v>10590200</v>
       </c>
       <c r="G141" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B142" t="n">
-        <v>291.8253790066561</v>
+        <v>305.5734164156603</v>
       </c>
       <c r="C142" t="n">
-        <v>296.8427544058445</v>
+        <v>309.8640846884941</v>
       </c>
       <c r="D142" t="n">
-        <v>291.3873498301165</v>
+        <v>304.73715687535</v>
       </c>
       <c r="E142" t="n">
-        <v>296.0662536621094</v>
+        <v>308.938232421875</v>
       </c>
       <c r="F142" t="n">
-        <v>7849100</v>
+        <v>6586600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B143" t="n">
-        <v>306.5888366699219</v>
+        <v>308.6097380099313</v>
       </c>
       <c r="C143" t="n">
-        <v>309.8640903908154</v>
+        <v>308.9581744354404</v>
       </c>
       <c r="D143" t="n">
-        <v>303.9606617936424</v>
+        <v>305.344449093958</v>
       </c>
       <c r="E143" t="n">
-        <v>306.5888366699219</v>
+        <v>308.4803161621094</v>
       </c>
       <c r="F143" t="n">
-        <v>10590200</v>
+        <v>6069700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B144" t="n">
-        <v>305.5734164156603</v>
+        <v>306.0910825316173</v>
       </c>
       <c r="C144" t="n">
-        <v>309.8640846884941</v>
+        <v>312.3329523629397</v>
       </c>
       <c r="D144" t="n">
-        <v>304.73715687535</v>
+        <v>304.0900871089203</v>
       </c>
       <c r="E144" t="n">
-        <v>308.938232421875</v>
+        <v>312.2732238769531</v>
       </c>
       <c r="F144" t="n">
-        <v>6586600</v>
+        <v>8318200</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B145" t="n">
-        <v>308.6097380099313</v>
+        <v>308.4305432499699</v>
       </c>
       <c r="C145" t="n">
-        <v>308.9581744354404</v>
+        <v>312.9103618924516</v>
       </c>
       <c r="D145" t="n">
-        <v>305.344449093958</v>
+        <v>307.4847916064935</v>
       </c>
       <c r="E145" t="n">
-        <v>308.4803161621094</v>
+        <v>309.7247009277344</v>
       </c>
       <c r="F145" t="n">
-        <v>6069700</v>
+        <v>11455500</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B146" t="n">
-        <v>306.0910825316173</v>
+        <v>312.5420354159922</v>
       </c>
       <c r="C146" t="n">
-        <v>312.3329523629397</v>
+        <v>312.8307129741003</v>
       </c>
       <c r="D146" t="n">
-        <v>304.0900871089203</v>
+        <v>302.8954898881459</v>
       </c>
       <c r="E146" t="n">
-        <v>312.2732238769531</v>
+        <v>304.5579833984375</v>
       </c>
       <c r="F146" t="n">
-        <v>8318200</v>
+        <v>9885800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B147" t="n">
-        <v>308.4305432499699</v>
+        <v>303.9805907681049</v>
       </c>
       <c r="C147" t="n">
-        <v>312.9103618924516</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="D147" t="n">
-        <v>307.4847916064935</v>
+        <v>303.8312695552229</v>
       </c>
       <c r="E147" t="n">
-        <v>309.7247009277344</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="F147" t="n">
-        <v>11455500</v>
+        <v>8208600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B148" t="n">
-        <v>312.5420354159922</v>
+        <v>311.068653468178</v>
       </c>
       <c r="C148" t="n">
-        <v>312.8307129741003</v>
+        <v>313.4877482505245</v>
       </c>
       <c r="D148" t="n">
-        <v>302.8954898881459</v>
+        <v>308.6993222963794</v>
       </c>
       <c r="E148" t="n">
-        <v>304.5579833984375</v>
+        <v>308.8984375</v>
       </c>
       <c r="F148" t="n">
-        <v>9885800</v>
+        <v>11082400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B149" t="n">
-        <v>303.9805907681049</v>
+        <v>309.4559416581444</v>
       </c>
       <c r="C149" t="n">
-        <v>308.5599670410156</v>
+        <v>315.7077766193834</v>
       </c>
       <c r="D149" t="n">
-        <v>303.8312695552229</v>
+        <v>308.9780833700189</v>
       </c>
       <c r="E149" t="n">
-        <v>308.5599670410156</v>
+        <v>315.5683898925781</v>
       </c>
       <c r="F149" t="n">
-        <v>8208600</v>
+        <v>10772000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B150" t="n">
-        <v>311.068653468178</v>
+        <v>316.0661368489313</v>
       </c>
       <c r="C150" t="n">
-        <v>313.4877482505245</v>
+        <v>318.8038038717339</v>
       </c>
       <c r="D150" t="n">
-        <v>308.6993222963794</v>
+        <v>311.3474041387296</v>
       </c>
       <c r="E150" t="n">
-        <v>308.8984375</v>
+        <v>311.5962829589844</v>
       </c>
       <c r="F150" t="n">
-        <v>11082400</v>
+        <v>7084300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B151" t="n">
-        <v>309.4559416581444</v>
+        <v>313.4379903862348</v>
       </c>
       <c r="C151" t="n">
-        <v>315.7077766193834</v>
+        <v>313.7366328164263</v>
       </c>
       <c r="D151" t="n">
-        <v>308.9780833700189</v>
+        <v>310.5410372905177</v>
       </c>
       <c r="E151" t="n">
-        <v>315.5683898925781</v>
+        <v>311.6161804199219</v>
       </c>
       <c r="F151" t="n">
-        <v>10772000</v>
+        <v>5545900</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B152" t="n">
-        <v>316.0661368489313</v>
+        <v>312.1139549773267</v>
       </c>
       <c r="C152" t="n">
-        <v>318.8038038717339</v>
+        <v>313.5773637260273</v>
       </c>
       <c r="D152" t="n">
-        <v>311.3474041387296</v>
+        <v>307.5047445243564</v>
       </c>
       <c r="E152" t="n">
-        <v>311.5962829589844</v>
+        <v>310.2921752929688</v>
       </c>
       <c r="F152" t="n">
-        <v>7084300</v>
+        <v>6969700</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B153" t="n">
-        <v>313.4379903862348</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="C153" t="n">
-        <v>313.7366328164263</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="D153" t="n">
-        <v>310.5410372905177</v>
+        <v>306.5092257615542</v>
       </c>
       <c r="E153" t="n">
-        <v>311.6161804199219</v>
+        <v>306.8974609375</v>
       </c>
       <c r="F153" t="n">
-        <v>5545900</v>
+        <v>5215300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B154" t="n">
-        <v>312.1139549773267</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="C154" t="n">
-        <v>313.5773637260273</v>
+        <v>311.1781431330245</v>
       </c>
       <c r="D154" t="n">
-        <v>307.5047445243564</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="E154" t="n">
-        <v>310.2921752929688</v>
+        <v>310.232421875</v>
       </c>
       <c r="F154" t="n">
-        <v>6969700</v>
+        <v>7925300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B155" t="n">
-        <v>309.7545850384977</v>
+        <v>313.7864355589005</v>
       </c>
       <c r="C155" t="n">
-        <v>309.7545850384977</v>
+        <v>314.035314384572</v>
       </c>
       <c r="D155" t="n">
-        <v>306.5092257615542</v>
+        <v>309.7745101043047</v>
       </c>
       <c r="E155" t="n">
-        <v>306.8974609375</v>
+        <v>310.0532531738281</v>
       </c>
       <c r="F155" t="n">
-        <v>5215300</v>
+        <v>7398600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B156" t="n">
-        <v>305.5037244427344</v>
+        <v>309.1771855961317</v>
       </c>
       <c r="C156" t="n">
-        <v>311.1781431330245</v>
+        <v>310.6505287563671</v>
       </c>
       <c r="D156" t="n">
-        <v>305.5037244427344</v>
+        <v>305.9118967162461</v>
       </c>
       <c r="E156" t="n">
-        <v>310.232421875</v>
+        <v>307.8630981445312</v>
       </c>
       <c r="F156" t="n">
-        <v>7925300</v>
+        <v>8031800</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B157" t="n">
-        <v>313.7864355589005</v>
+        <v>305.6928786901284</v>
       </c>
       <c r="C157" t="n">
-        <v>314.035314384572</v>
+        <v>312.6913497643884</v>
       </c>
       <c r="D157" t="n">
-        <v>309.7745101043047</v>
+        <v>305.1951210592971</v>
       </c>
       <c r="E157" t="n">
-        <v>310.0532531738281</v>
+        <v>311.8252563476562</v>
       </c>
       <c r="F157" t="n">
-        <v>7398600</v>
+        <v>8865400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B158" t="n">
-        <v>309.1771855961317</v>
+        <v>312.5420381202088</v>
       </c>
       <c r="C158" t="n">
-        <v>310.6505287563671</v>
+        <v>314.6624601726697</v>
       </c>
       <c r="D158" t="n">
-        <v>305.9118967162461</v>
+        <v>310.431520181067</v>
       </c>
       <c r="E158" t="n">
-        <v>307.8630981445312</v>
+        <v>311.0686645507812</v>
       </c>
       <c r="F158" t="n">
-        <v>8031800</v>
+        <v>6135400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B159" t="n">
-        <v>305.6928786901284</v>
+        <v>309.2269452093906</v>
       </c>
       <c r="C159" t="n">
-        <v>312.6913497643884</v>
+        <v>309.2568094519629</v>
       </c>
       <c r="D159" t="n">
-        <v>305.1951210592971</v>
+        <v>305.1353920734132</v>
       </c>
       <c r="E159" t="n">
-        <v>311.8252563476562</v>
+        <v>306.270263671875</v>
       </c>
       <c r="F159" t="n">
-        <v>8865400</v>
+        <v>7338200</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B160" t="n">
-        <v>312.5420381202088</v>
+        <v>306.3299974055641</v>
       </c>
       <c r="C160" t="n">
-        <v>314.6624601726697</v>
+        <v>309.5753869306937</v>
       </c>
       <c r="D160" t="n">
-        <v>310.431520181067</v>
+        <v>305.42407485773</v>
       </c>
       <c r="E160" t="n">
-        <v>311.0686645507812</v>
+        <v>308.0124206542969</v>
       </c>
       <c r="F160" t="n">
-        <v>6135400</v>
+        <v>6316800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B161" t="n">
-        <v>309.2269452093906</v>
+        <v>310.0532528884956</v>
       </c>
       <c r="C161" t="n">
-        <v>309.2568094519629</v>
+        <v>314.8416790595512</v>
       </c>
       <c r="D161" t="n">
-        <v>305.1353920734132</v>
+        <v>309.9536952821754</v>
       </c>
       <c r="E161" t="n">
-        <v>306.270263671875</v>
+        <v>313.4877624511719</v>
       </c>
       <c r="F161" t="n">
-        <v>7338200</v>
+        <v>8629500</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B162" t="n">
-        <v>306.3299974055641</v>
+        <v>313.2388767644321</v>
       </c>
       <c r="C162" t="n">
-        <v>309.5753869306937</v>
+        <v>314.8814709002291</v>
       </c>
       <c r="D162" t="n">
-        <v>305.42407485773</v>
+        <v>304.7670623908274</v>
       </c>
       <c r="E162" t="n">
-        <v>308.0124206542969</v>
+        <v>304.8964538574219</v>
       </c>
       <c r="F162" t="n">
-        <v>6316800</v>
+        <v>8359600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B163" t="n">
-        <v>310.0532528884956</v>
+        <v>306.8675912418493</v>
       </c>
       <c r="C163" t="n">
-        <v>314.8416790595512</v>
+        <v>307.6042628420606</v>
       </c>
       <c r="D163" t="n">
-        <v>309.9536952821754</v>
+        <v>299.1523476664256</v>
       </c>
       <c r="E163" t="n">
-        <v>313.4877624511719</v>
+        <v>300.7451782226562</v>
       </c>
       <c r="F163" t="n">
-        <v>8629500</v>
+        <v>9464300</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B164" t="n">
-        <v>313.2388767644321</v>
+        <v>300.7451596100784</v>
       </c>
       <c r="C164" t="n">
-        <v>314.8814709002291</v>
+        <v>301.8302675742967</v>
       </c>
       <c r="D164" t="n">
-        <v>304.7670623908274</v>
+        <v>297.5395993270601</v>
       </c>
       <c r="E164" t="n">
-        <v>304.8964538574219</v>
+        <v>298.6545715332031</v>
       </c>
       <c r="F164" t="n">
-        <v>8359600</v>
+        <v>9512000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B165" t="n">
-        <v>306.8675912418493</v>
+        <v>298.6744753830843</v>
       </c>
       <c r="C165" t="n">
-        <v>307.6042628420606</v>
+        <v>304.6873960201211</v>
       </c>
       <c r="D165" t="n">
-        <v>299.1523476664256</v>
+        <v>294.2245209852311</v>
       </c>
       <c r="E165" t="n">
-        <v>300.7451782226562</v>
+        <v>303.5126953125</v>
       </c>
       <c r="F165" t="n">
-        <v>9464300</v>
+        <v>9498200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B166" t="n">
-        <v>300.7451596100784</v>
+        <v>300.9144028967509</v>
       </c>
       <c r="C166" t="n">
-        <v>301.8302675742967</v>
+        <v>301.6411400127173</v>
       </c>
       <c r="D166" t="n">
-        <v>297.5395993270601</v>
+        <v>298.7242874353194</v>
       </c>
       <c r="E166" t="n">
-        <v>298.6545715332031</v>
+        <v>298.9034729003906</v>
       </c>
       <c r="F166" t="n">
-        <v>9512000</v>
+        <v>7709500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B167" t="n">
-        <v>298.6744753830843</v>
+        <v>300.8945046380796</v>
       </c>
       <c r="C167" t="n">
-        <v>304.6873960201211</v>
+        <v>302.387777613951</v>
       </c>
       <c r="D167" t="n">
-        <v>294.2245209852311</v>
+        <v>297.4699295162906</v>
       </c>
       <c r="E167" t="n">
-        <v>303.5126953125</v>
+        <v>298.5650024414062</v>
       </c>
       <c r="F167" t="n">
-        <v>9498200</v>
+        <v>7364300</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B168" t="n">
-        <v>300.9144028967509</v>
+        <v>298.8636262885424</v>
       </c>
       <c r="C168" t="n">
-        <v>301.6411400127173</v>
+        <v>299.4410421498196</v>
       </c>
       <c r="D168" t="n">
-        <v>298.7242874353194</v>
+        <v>295.1205095874812</v>
       </c>
       <c r="E168" t="n">
-        <v>298.9034729003906</v>
+        <v>296.4743957519531</v>
       </c>
       <c r="F168" t="n">
-        <v>7709500</v>
+        <v>8699300</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B169" t="n">
-        <v>300.8945046380796</v>
+        <v>296.6635495230975</v>
       </c>
       <c r="C169" t="n">
-        <v>302.387777613951</v>
+        <v>299.908939014877</v>
       </c>
       <c r="D169" t="n">
-        <v>297.4699295162906</v>
+        <v>295.8870488301784</v>
       </c>
       <c r="E169" t="n">
-        <v>298.5650024414062</v>
+        <v>299.3813171386719</v>
       </c>
       <c r="F169" t="n">
-        <v>7364300</v>
+        <v>7546300</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B170" t="n">
-        <v>298.8636262885424</v>
+        <v>299.7396822358739</v>
       </c>
       <c r="C170" t="n">
-        <v>299.4410421498196</v>
+        <v>300.436555061437</v>
       </c>
       <c r="D170" t="n">
-        <v>295.1205095874812</v>
+        <v>293.935841710235</v>
       </c>
       <c r="E170" t="n">
-        <v>296.4743957519531</v>
+        <v>294.3738708496094</v>
       </c>
       <c r="F170" t="n">
-        <v>8699300</v>
+        <v>8066900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B171" t="n">
-        <v>296.6635495230975</v>
+        <v>295.3694126574367</v>
       </c>
       <c r="C171" t="n">
-        <v>299.908939014877</v>
+        <v>301.57145376365</v>
       </c>
       <c r="D171" t="n">
-        <v>295.8870488301784</v>
+        <v>292.3530024013792</v>
       </c>
       <c r="E171" t="n">
-        <v>299.3813171386719</v>
+        <v>300.625732421875</v>
       </c>
       <c r="F171" t="n">
-        <v>7546300</v>
+        <v>9327000</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B172" t="n">
-        <v>299.7396822358739</v>
+        <v>299.8790926087445</v>
       </c>
       <c r="C172" t="n">
-        <v>300.436555061437</v>
+        <v>302.6167597554335</v>
       </c>
       <c r="D172" t="n">
-        <v>293.935841710235</v>
+        <v>298.8636475324957</v>
       </c>
       <c r="E172" t="n">
-        <v>294.3738708496094</v>
+        <v>301.6411437988281</v>
       </c>
       <c r="F172" t="n">
-        <v>8066900</v>
+        <v>7874400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B173" t="n">
-        <v>295.3694126574367</v>
+        <v>303.3135932887391</v>
       </c>
       <c r="C173" t="n">
-        <v>301.57145376365</v>
+        <v>306.0711901040885</v>
       </c>
       <c r="D173" t="n">
-        <v>292.3530024013792</v>
+        <v>302.4773640852478</v>
       </c>
       <c r="E173" t="n">
-        <v>300.625732421875</v>
+        <v>305.0059814453125</v>
       </c>
       <c r="F173" t="n">
-        <v>9327000</v>
+        <v>5973900</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B174" t="n">
-        <v>299.8790926087445</v>
+        <v>307.1065011172144</v>
       </c>
       <c r="C174" t="n">
-        <v>302.6167597554335</v>
+        <v>308.5400455607295</v>
       </c>
       <c r="D174" t="n">
-        <v>298.8636475324957</v>
+        <v>304.0701916446211</v>
       </c>
       <c r="E174" t="n">
-        <v>301.6411437988281</v>
+        <v>305.3643493652344</v>
       </c>
       <c r="F174" t="n">
-        <v>7874400</v>
+        <v>7725400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B175" t="n">
-        <v>303.3135932887391</v>
+        <v>303.6321536663258</v>
       </c>
       <c r="C175" t="n">
-        <v>306.0711901040885</v>
+        <v>304.5281113223131</v>
       </c>
       <c r="D175" t="n">
-        <v>302.4773640852478</v>
+        <v>294.4236375305438</v>
       </c>
       <c r="E175" t="n">
-        <v>305.0059814453125</v>
+        <v>297.9378051757812</v>
       </c>
       <c r="F175" t="n">
-        <v>5973900</v>
+        <v>11779200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B176" t="n">
-        <v>307.1065011172144</v>
+        <v>296.2354906683788</v>
       </c>
       <c r="C176" t="n">
-        <v>308.5400455607295</v>
+        <v>299.7197941661088</v>
       </c>
       <c r="D176" t="n">
-        <v>304.0701916446211</v>
+        <v>294.4236455581874</v>
       </c>
       <c r="E176" t="n">
-        <v>305.3643493652344</v>
+        <v>295.3992614746094</v>
       </c>
       <c r="F176" t="n">
-        <v>7725400</v>
+        <v>9757700</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B177" t="n">
-        <v>303.6321536663258</v>
+        <v>295.070728717322</v>
       </c>
       <c r="C177" t="n">
-        <v>304.5281113223131</v>
+        <v>298.5351328968941</v>
       </c>
       <c r="D177" t="n">
-        <v>294.4236375305438</v>
+        <v>293.8761285862639</v>
       </c>
       <c r="E177" t="n">
-        <v>297.9378051757812</v>
+        <v>297.9676818847656</v>
       </c>
       <c r="F177" t="n">
-        <v>11779200</v>
+        <v>13969000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B178" t="n">
-        <v>296.2354906683788</v>
+        <v>296.3549462063085</v>
       </c>
       <c r="C178" t="n">
-        <v>299.7197941661088</v>
+        <v>298.2065900448191</v>
       </c>
       <c r="D178" t="n">
-        <v>294.4236455581874</v>
+        <v>293.9457858606032</v>
       </c>
       <c r="E178" t="n">
-        <v>295.3992614746094</v>
+        <v>295.2499084472656</v>
       </c>
       <c r="F178" t="n">
-        <v>9757700</v>
+        <v>7930000</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B179" t="n">
-        <v>295.070728717322</v>
+        <v>295.170270518017</v>
       </c>
       <c r="C179" t="n">
-        <v>298.5351328968941</v>
+        <v>300.7152977310929</v>
       </c>
       <c r="D179" t="n">
-        <v>293.8761285862639</v>
+        <v>293.9457758280521</v>
       </c>
       <c r="E179" t="n">
-        <v>297.9676818847656</v>
+        <v>299.6102600097656</v>
       </c>
       <c r="F179" t="n">
-        <v>13969000</v>
+        <v>8296200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B180" t="n">
-        <v>296.3549462063085</v>
+        <v>298.5749714904202</v>
       </c>
       <c r="C180" t="n">
-        <v>298.2065900448191</v>
+        <v>300.6058008918799</v>
       </c>
       <c r="D180" t="n">
-        <v>293.9457858606032</v>
+        <v>295.2300241797341</v>
       </c>
       <c r="E180" t="n">
-        <v>295.2499084472656</v>
+        <v>299.5007934570312</v>
       </c>
       <c r="F180" t="n">
-        <v>7930000</v>
+        <v>7003900</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B181" t="n">
-        <v>295.170270518017</v>
+        <v>304.3688300919619</v>
       </c>
       <c r="C181" t="n">
-        <v>300.7152977310929</v>
+        <v>311.5066879726736</v>
       </c>
       <c r="D181" t="n">
-        <v>293.9457758280521</v>
+        <v>303.0746723882986</v>
       </c>
       <c r="E181" t="n">
-        <v>299.6102600097656</v>
+        <v>309.4957580566406</v>
       </c>
       <c r="F181" t="n">
-        <v>8296200</v>
+        <v>10345200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B182" t="n">
-        <v>298.5749714904202</v>
+        <v>312.8805189963161</v>
       </c>
       <c r="C182" t="n">
-        <v>300.6058008918799</v>
+        <v>313.5873263681962</v>
       </c>
       <c r="D182" t="n">
-        <v>295.2300241797341</v>
+        <v>308.211549706599</v>
       </c>
       <c r="E182" t="n">
-        <v>299.5007934570312</v>
+        <v>310.9691162109375</v>
       </c>
       <c r="F182" t="n">
-        <v>7003900</v>
+        <v>9118800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B183" t="n">
-        <v>304.3688300919619</v>
+        <v>311.8451695343703</v>
       </c>
       <c r="C183" t="n">
-        <v>311.5066879726736</v>
+        <v>314.881479064701</v>
       </c>
       <c r="D183" t="n">
-        <v>303.0746723882986</v>
+        <v>309.3862455138746</v>
       </c>
       <c r="E183" t="n">
-        <v>309.4957580566406</v>
+        <v>309.7147521972656</v>
       </c>
       <c r="F183" t="n">
-        <v>10345200</v>
+        <v>6827000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B184" t="n">
-        <v>312.8805189963161</v>
+        <v>312.1040028799189</v>
       </c>
       <c r="C184" t="n">
-        <v>313.5873263681962</v>
+        <v>315.0009559692908</v>
       </c>
       <c r="D184" t="n">
-        <v>308.211549706599</v>
+        <v>307.6241841525692</v>
       </c>
       <c r="E184" t="n">
-        <v>310.9691162109375</v>
+        <v>311.2976379394531</v>
       </c>
       <c r="F184" t="n">
-        <v>9118800</v>
+        <v>11594600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B185" t="n">
-        <v>311.8451695343703</v>
+        <v>311.1582462393224</v>
       </c>
       <c r="C185" t="n">
-        <v>314.881479064701</v>
+        <v>313.3384270822022</v>
       </c>
       <c r="D185" t="n">
-        <v>309.3862455138746</v>
+        <v>307.6440785979976</v>
       </c>
       <c r="E185" t="n">
-        <v>309.7147521972656</v>
+        <v>307.7536010742188</v>
       </c>
       <c r="F185" t="n">
-        <v>6827000</v>
+        <v>7446200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B186" t="n">
-        <v>312.1040028799189</v>
+        <v>308.1717081621576</v>
       </c>
       <c r="C186" t="n">
-        <v>315.0009559692908</v>
+        <v>313.3085706612414</v>
       </c>
       <c r="D186" t="n">
-        <v>307.6241841525692</v>
+        <v>307.4947650619962</v>
       </c>
       <c r="E186" t="n">
-        <v>311.2976379394531</v>
+        <v>312.0840759277344</v>
       </c>
       <c r="F186" t="n">
-        <v>11594600</v>
+        <v>9116600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B187" t="n">
-        <v>311.1582462393224</v>
+        <v>314.5529794375797</v>
       </c>
       <c r="C187" t="n">
-        <v>313.3384270822022</v>
+        <v>319.8590627688811</v>
       </c>
       <c r="D187" t="n">
-        <v>307.6440785979976</v>
+        <v>314.1348496322589</v>
       </c>
       <c r="E187" t="n">
-        <v>307.7536010742188</v>
+        <v>319.2816772460938</v>
       </c>
       <c r="F187" t="n">
-        <v>7446200</v>
+        <v>7426200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B188" t="n">
-        <v>308.1717081621576</v>
+        <v>322.4673390673774</v>
       </c>
       <c r="C188" t="n">
-        <v>313.3085706612414</v>
+        <v>324.4583697274161</v>
       </c>
       <c r="D188" t="n">
-        <v>307.4947650619962</v>
+        <v>317.4101041776777</v>
       </c>
       <c r="E188" t="n">
-        <v>312.0840759277344</v>
+        <v>317.9675903320312</v>
       </c>
       <c r="F188" t="n">
-        <v>9116600</v>
+        <v>7988900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B189" t="n">
-        <v>314.5529794375797</v>
+        <v>322.8455866314347</v>
       </c>
       <c r="C189" t="n">
-        <v>319.8590627688811</v>
+        <v>330.2621874699331</v>
       </c>
       <c r="D189" t="n">
-        <v>314.1348496322589</v>
+        <v>322.5668435738929</v>
       </c>
       <c r="E189" t="n">
-        <v>319.2816772460938</v>
+        <v>329.6549377441406</v>
       </c>
       <c r="F189" t="n">
-        <v>7426200</v>
+        <v>11094900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B190" t="n">
-        <v>322.4673390673774</v>
+        <v>330.6902497468859</v>
       </c>
       <c r="C190" t="n">
-        <v>324.4583697274161</v>
+        <v>336.2551763704633</v>
       </c>
       <c r="D190" t="n">
-        <v>317.4101041776777</v>
+        <v>330.0133066656099</v>
       </c>
       <c r="E190" t="n">
-        <v>317.9675903320312</v>
+        <v>331.9645080566406</v>
       </c>
       <c r="F190" t="n">
-        <v>7988900</v>
+        <v>12246400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B191" t="n">
-        <v>322.8455866314347</v>
+        <v>335.4388795655989</v>
       </c>
       <c r="C191" t="n">
-        <v>330.2621874699331</v>
+        <v>336.5737511659094</v>
       </c>
       <c r="D191" t="n">
-        <v>322.5668435738929</v>
+        <v>322.7062308624821</v>
       </c>
       <c r="E191" t="n">
-        <v>329.6549377441406</v>
+        <v>323.761474609375</v>
       </c>
       <c r="F191" t="n">
-        <v>11094900</v>
+        <v>20111000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B192" t="n">
-        <v>330.6902497468859</v>
+        <v>328.221392261561</v>
       </c>
       <c r="C192" t="n">
-        <v>336.2551763704633</v>
+        <v>331.2776010100568</v>
       </c>
       <c r="D192" t="n">
-        <v>330.0133066656099</v>
+        <v>325.2846101022313</v>
       </c>
       <c r="E192" t="n">
-        <v>331.9645080566406</v>
+        <v>329.993408203125</v>
       </c>
       <c r="F192" t="n">
-        <v>12246400</v>
+        <v>10182500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B193" t="n">
-        <v>335.4388795655989</v>
+        <v>327.9924099173137</v>
       </c>
       <c r="C193" t="n">
-        <v>336.5737511659094</v>
+        <v>333.8659438033595</v>
       </c>
       <c r="D193" t="n">
-        <v>322.7062308624821</v>
+        <v>325.7425357353925</v>
       </c>
       <c r="E193" t="n">
-        <v>323.761474609375</v>
+        <v>332.6414794921875</v>
       </c>
       <c r="F193" t="n">
-        <v>20111000</v>
+        <v>7582200</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B194" t="n">
-        <v>328.221392261561</v>
+        <v>331.5762891678024</v>
       </c>
       <c r="C194" t="n">
-        <v>331.2776010100568</v>
+        <v>333.0297330031709</v>
       </c>
       <c r="D194" t="n">
-        <v>325.2846101022313</v>
+        <v>328.291070440402</v>
       </c>
       <c r="E194" t="n">
-        <v>329.993408203125</v>
+        <v>331.95458984375</v>
       </c>
       <c r="F194" t="n">
-        <v>10182500</v>
+        <v>7907400</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B195" t="n">
-        <v>327.9924099173137</v>
+        <v>333.4577793441399</v>
       </c>
       <c r="C195" t="n">
-        <v>333.8659438033595</v>
+        <v>341.909724468194</v>
       </c>
       <c r="D195" t="n">
-        <v>325.7425357353925</v>
+        <v>333.2586945227413</v>
       </c>
       <c r="E195" t="n">
-        <v>332.6414794921875</v>
+        <v>333.6170654296875</v>
       </c>
       <c r="F195" t="n">
-        <v>7582200</v>
+        <v>10043100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B196" t="n">
-        <v>331.5762891678024</v>
+        <v>334.4931229022353</v>
       </c>
       <c r="C196" t="n">
-        <v>333.0297330031709</v>
+        <v>334.8913229247855</v>
       </c>
       <c r="D196" t="n">
-        <v>328.291070440402</v>
+        <v>326.0312433050061</v>
       </c>
       <c r="E196" t="n">
-        <v>331.95458984375</v>
+        <v>327.5742797851562</v>
       </c>
       <c r="F196" t="n">
-        <v>7907400</v>
+        <v>17640900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B197" t="n">
-        <v>333.4577793441399</v>
+        <v>326.8077430430495</v>
       </c>
       <c r="C197" t="n">
-        <v>341.909724468194</v>
+        <v>330.8993264933345</v>
       </c>
       <c r="D197" t="n">
-        <v>333.2586945227413</v>
+        <v>325.7325999471821</v>
       </c>
       <c r="E197" t="n">
-        <v>333.6170654296875</v>
+        <v>327.9127807617188</v>
       </c>
       <c r="F197" t="n">
-        <v>10043100</v>
+        <v>7981800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B198" t="n">
-        <v>334.4931229022353</v>
+        <v>327.4150312810326</v>
       </c>
       <c r="C198" t="n">
-        <v>334.8913229247855</v>
+        <v>328.9580677951163</v>
       </c>
       <c r="D198" t="n">
-        <v>326.0312433050061</v>
+        <v>325.2149206632551</v>
       </c>
       <c r="E198" t="n">
-        <v>327.5742797851562</v>
+        <v>325.8619995117188</v>
       </c>
       <c r="F198" t="n">
-        <v>17640900</v>
+        <v>8080100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B199" t="n">
-        <v>326.8077430430495</v>
+        <v>326.8973584256916</v>
       </c>
       <c r="C199" t="n">
-        <v>330.8993264933345</v>
+        <v>334.1347741939035</v>
       </c>
       <c r="D199" t="n">
-        <v>325.7325999471821</v>
+        <v>323.5524415571975</v>
       </c>
       <c r="E199" t="n">
-        <v>327.9127807617188</v>
+        <v>332.5718078613281</v>
       </c>
       <c r="F199" t="n">
-        <v>7981800</v>
+        <v>15210200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B200" t="n">
-        <v>327.4150312810326</v>
+        <v>336.5040683580973</v>
       </c>
       <c r="C200" t="n">
-        <v>328.9580677951163</v>
+        <v>338.4751995750331</v>
       </c>
       <c r="D200" t="n">
-        <v>325.2149206632551</v>
+        <v>330.2820977776739</v>
       </c>
       <c r="E200" t="n">
-        <v>325.8619995117188</v>
+        <v>332.9700012207031</v>
       </c>
       <c r="F200" t="n">
-        <v>8080100</v>
+        <v>8413900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,25 +5643,25 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B201" t="n">
-        <v>326.8973584256916</v>
+        <v>335</v>
       </c>
       <c r="C201" t="n">
-        <v>334.1347741939035</v>
+        <v>339.7200012207031</v>
       </c>
       <c r="D201" t="n">
-        <v>323.5524415571975</v>
+        <v>334.1099853515625</v>
       </c>
       <c r="E201" t="n">
-        <v>332.5718078613281</v>
+        <v>337.7200012207031</v>
       </c>
       <c r="F201" t="n">
-        <v>15210200</v>
+        <v>8673500</v>
       </c>
       <c r="G201" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B202" t="n">
-        <v>336.5040683580973</v>
+        <v>340.9800109863281</v>
       </c>
       <c r="C202" t="n">
-        <v>338.4751995750331</v>
+        <v>341.3999938964844</v>
       </c>
       <c r="D202" t="n">
-        <v>330.2820977776739</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E202" t="n">
-        <v>332.9700012207031</v>
+        <v>339.2200012207031</v>
       </c>
       <c r="F202" t="n">
-        <v>8413900</v>
+        <v>7115800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,25 +5695,25 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B203" t="n">
-        <v>335</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="C203" t="n">
-        <v>339.7200012207031</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="D203" t="n">
-        <v>334.1099853515625</v>
+        <v>330.1300048828125</v>
       </c>
       <c r="E203" t="n">
-        <v>337.7200012207031</v>
+        <v>330.6199951171875</v>
       </c>
       <c r="F203" t="n">
-        <v>8673500</v>
+        <v>18505200</v>
       </c>
       <c r="G203" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B204" t="n">
-        <v>340.9800109863281</v>
+        <v>331.4599914550781</v>
       </c>
       <c r="C204" t="n">
-        <v>341.3999938964844</v>
+        <v>337</v>
       </c>
       <c r="D204" t="n">
-        <v>337.0899963378906</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="E204" t="n">
-        <v>339.2200012207031</v>
+        <v>335.4700012207031</v>
       </c>
       <c r="F204" t="n">
-        <v>7115800</v>
+        <v>15570600</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B205" t="n">
-        <v>336.5299987792969</v>
+        <v>337.4700012207031</v>
       </c>
       <c r="C205" t="n">
-        <v>336.5299987792969</v>
+        <v>338.5899963378906</v>
       </c>
       <c r="D205" t="n">
-        <v>330.1300048828125</v>
+        <v>335.7699890136719</v>
       </c>
       <c r="E205" t="n">
-        <v>330.6199951171875</v>
+        <v>336.4700012207031</v>
       </c>
       <c r="F205" t="n">
-        <v>18505200</v>
+        <v>6299000</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B206" t="n">
-        <v>331.4599914550781</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="C206" t="n">
-        <v>337</v>
+        <v>338.3500061035156</v>
       </c>
       <c r="D206" t="n">
-        <v>330.8099975585938</v>
+        <v>332.5</v>
       </c>
       <c r="E206" t="n">
-        <v>335.4700012207031</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="F206" t="n">
-        <v>15570600</v>
+        <v>7120300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B207" t="n">
-        <v>337.4700012207031</v>
+        <v>327</v>
       </c>
       <c r="C207" t="n">
-        <v>338.5899963378906</v>
+        <v>344.7300109863281</v>
       </c>
       <c r="D207" t="n">
-        <v>335.7699890136719</v>
+        <v>325.75</v>
       </c>
       <c r="E207" t="n">
-        <v>336.4700012207031</v>
+        <v>342.8900146484375</v>
       </c>
       <c r="F207" t="n">
-        <v>6299000</v>
+        <v>14537900</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>338.3399963378906</v>
+        <v>345.8500061035156</v>
       </c>
       <c r="C208" t="n">
-        <v>338.3500061035156</v>
+        <v>351.239990234375</v>
       </c>
       <c r="D208" t="n">
-        <v>332.5</v>
+        <v>344.0499877929688</v>
       </c>
       <c r="E208" t="n">
-        <v>334.5299987792969</v>
+        <v>346.9100036621094</v>
       </c>
       <c r="F208" t="n">
-        <v>7120300</v>
+        <v>10750000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B209" t="n">
-        <v>327</v>
+        <v>349.2799987792969</v>
       </c>
       <c r="C209" t="n">
-        <v>344.7300109863281</v>
+        <v>349.3399963378906</v>
       </c>
       <c r="D209" t="n">
-        <v>325.75</v>
+        <v>341.1099853515625</v>
       </c>
       <c r="E209" t="n">
-        <v>342.8900146484375</v>
+        <v>343.1499938964844</v>
       </c>
       <c r="F209" t="n">
-        <v>14537900</v>
+        <v>12432400</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B210" t="n">
-        <v>345.8500061035156</v>
+        <v>339.0299987792969</v>
       </c>
       <c r="C210" t="n">
-        <v>351.239990234375</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="D210" t="n">
-        <v>344.0499877929688</v>
+        <v>335.0499877929688</v>
       </c>
       <c r="E210" t="n">
-        <v>346.9100036621094</v>
+        <v>341.1000061035156</v>
       </c>
       <c r="F210" t="n">
-        <v>10750000</v>
+        <v>9250900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B211" t="n">
-        <v>349.2799987792969</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="C211" t="n">
-        <v>349.3399963378906</v>
+        <v>344.260009765625</v>
       </c>
       <c r="D211" t="n">
-        <v>341.1099853515625</v>
+        <v>337.3699951171875</v>
       </c>
       <c r="E211" t="n">
-        <v>343.1499938964844</v>
+        <v>338.8699951171875</v>
       </c>
       <c r="F211" t="n">
-        <v>12432400</v>
+        <v>7723300</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B212" t="n">
-        <v>339.0299987792969</v>
+        <v>340.1199951171875</v>
       </c>
       <c r="C212" t="n">
-        <v>346.1300048828125</v>
+        <v>345.739990234375</v>
       </c>
       <c r="D212" t="n">
-        <v>335.0499877929688</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E212" t="n">
-        <v>341.1000061035156</v>
+        <v>345.2300109863281</v>
       </c>
       <c r="F212" t="n">
-        <v>9250900</v>
+        <v>6015300</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B213" t="n">
-        <v>341.7999877929688</v>
+        <v>345.0700073242188</v>
       </c>
       <c r="C213" t="n">
-        <v>344.260009765625</v>
+        <v>349.0700073242188</v>
       </c>
       <c r="D213" t="n">
-        <v>337.3699951171875</v>
+        <v>344.25</v>
       </c>
       <c r="E213" t="n">
-        <v>338.8699951171875</v>
+        <v>348.2099914550781</v>
       </c>
       <c r="F213" t="n">
-        <v>7723300</v>
+        <v>8040200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B214" t="n">
-        <v>340.1199951171875</v>
+        <v>346.5799865722656</v>
       </c>
       <c r="C214" t="n">
-        <v>345.739990234375</v>
+        <v>349.9200134277344</v>
       </c>
       <c r="D214" t="n">
-        <v>337.2999877929688</v>
+        <v>345.4200134277344</v>
       </c>
       <c r="E214" t="n">
-        <v>345.2300109863281</v>
+        <v>349.8999938964844</v>
       </c>
       <c r="F214" t="n">
-        <v>6015300</v>
+        <v>10913000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B215" t="n">
-        <v>345.0700073242188</v>
+        <v>350.6400146484375</v>
       </c>
       <c r="C215" t="n">
-        <v>349.0700073242188</v>
+        <v>353.3699951171875</v>
       </c>
       <c r="D215" t="n">
-        <v>344.25</v>
+        <v>347.5</v>
       </c>
       <c r="E215" t="n">
-        <v>348.2099914550781</v>
+        <v>353.2099914550781</v>
       </c>
       <c r="F215" t="n">
-        <v>8040200</v>
+        <v>7520800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B216" t="n">
-        <v>346.5799865722656</v>
+        <v>357.8900146484375</v>
       </c>
       <c r="C216" t="n">
-        <v>349.9200134277344</v>
+        <v>359.0499877929688</v>
       </c>
       <c r="D216" t="n">
-        <v>345.4200134277344</v>
+        <v>352.5799865722656</v>
       </c>
       <c r="E216" t="n">
-        <v>349.8999938964844</v>
+        <v>356.2000122070312</v>
       </c>
       <c r="F216" t="n">
-        <v>10913000</v>
+        <v>7884900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B217" t="n">
-        <v>350.6400146484375</v>
+        <v>357.2999877929688</v>
       </c>
       <c r="C217" t="n">
-        <v>353.3699951171875</v>
+        <v>359.2999877929688</v>
       </c>
       <c r="D217" t="n">
-        <v>347.5</v>
+        <v>354.1499938964844</v>
       </c>
       <c r="E217" t="n">
-        <v>353.2099914550781</v>
+        <v>357.3099975585938</v>
       </c>
       <c r="F217" t="n">
-        <v>7520800</v>
+        <v>6533800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B218" t="n">
-        <v>357.8900146484375</v>
+        <v>356.5</v>
       </c>
       <c r="C218" t="n">
-        <v>359.0499877929688</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D218" t="n">
-        <v>352.5799865722656</v>
+        <v>343.7799987792969</v>
       </c>
       <c r="E218" t="n">
-        <v>356.2000122070312</v>
+        <v>344.7099914550781</v>
       </c>
       <c r="F218" t="n">
-        <v>7884900</v>
+        <v>8265300</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B219" t="n">
-        <v>357.2999877929688</v>
+        <v>347.5400085449219</v>
       </c>
       <c r="C219" t="n">
-        <v>359.2999877929688</v>
+        <v>352.2799987792969</v>
       </c>
       <c r="D219" t="n">
-        <v>354.1499938964844</v>
+        <v>345.3699951171875</v>
       </c>
       <c r="E219" t="n">
-        <v>357.3099975585938</v>
+        <v>350.8500061035156</v>
       </c>
       <c r="F219" t="n">
-        <v>6533800</v>
+        <v>7606500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B220" t="n">
-        <v>356.5</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C220" t="n">
-        <v>357.3699951171875</v>
+        <v>354.4700012207031</v>
       </c>
       <c r="D220" t="n">
-        <v>343.7799987792969</v>
+        <v>349.7000122070312</v>
       </c>
       <c r="E220" t="n">
-        <v>344.7099914550781</v>
+        <v>351.7900085449219</v>
       </c>
       <c r="F220" t="n">
-        <v>8265300</v>
+        <v>6603400</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B221" t="n">
-        <v>347.5400085449219</v>
+        <v>353.75</v>
       </c>
       <c r="C221" t="n">
-        <v>352.2799987792969</v>
+        <v>355.6199951171875</v>
       </c>
       <c r="D221" t="n">
-        <v>345.3699951171875</v>
+        <v>350.8399963378906</v>
       </c>
       <c r="E221" t="n">
-        <v>350.8500061035156</v>
+        <v>352.6400146484375</v>
       </c>
       <c r="F221" t="n">
-        <v>7606500</v>
+        <v>6436600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B222" t="n">
-        <v>353.2999877929688</v>
+        <v>355</v>
       </c>
       <c r="C222" t="n">
-        <v>354.4700012207031</v>
+        <v>363</v>
       </c>
       <c r="D222" t="n">
-        <v>349.7000122070312</v>
+        <v>353.8699951171875</v>
       </c>
       <c r="E222" t="n">
-        <v>351.7900085449219</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F222" t="n">
-        <v>6603400</v>
+        <v>8477200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B223" t="n">
-        <v>353.75</v>
+        <v>358.9700012207031</v>
       </c>
       <c r="C223" t="n">
-        <v>355.6199951171875</v>
+        <v>362.1700134277344</v>
       </c>
       <c r="D223" t="n">
-        <v>350.8399963378906</v>
+        <v>358.2000122070312</v>
       </c>
       <c r="E223" t="n">
-        <v>352.6400146484375</v>
+        <v>359.239990234375</v>
       </c>
       <c r="F223" t="n">
-        <v>6436600</v>
+        <v>5269500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B224" t="n">
-        <v>355</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="C224" t="n">
-        <v>363</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="D224" t="n">
-        <v>353.8699951171875</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="E224" t="n">
-        <v>357.5199890136719</v>
+        <v>356.2999877929688</v>
       </c>
       <c r="F224" t="n">
-        <v>8477200</v>
+        <v>5820100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B225" t="n">
-        <v>358.9700012207031</v>
+        <v>355.760009765625</v>
       </c>
       <c r="C225" t="n">
-        <v>362.1700134277344</v>
+        <v>358.8500061035156</v>
       </c>
       <c r="D225" t="n">
-        <v>358.2000122070312</v>
+        <v>353.3299865722656</v>
       </c>
       <c r="E225" t="n">
-        <v>359.239990234375</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F225" t="n">
-        <v>5269500</v>
+        <v>4566200</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B226" t="n">
-        <v>362.8099975585938</v>
+        <v>357.9599914550781</v>
       </c>
       <c r="C226" t="n">
-        <v>362.8099975585938</v>
+        <v>359.989990234375</v>
       </c>
       <c r="D226" t="n">
-        <v>354.9500122070312</v>
+        <v>356.5</v>
       </c>
       <c r="E226" t="n">
-        <v>356.2999877929688</v>
+        <v>359.7900085449219</v>
       </c>
       <c r="F226" t="n">
-        <v>5820100</v>
+        <v>5327500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B227" t="n">
-        <v>355.760009765625</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="C227" t="n">
-        <v>358.8500061035156</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="D227" t="n">
-        <v>353.3299865722656</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="E227" t="n">
-        <v>357.5199890136719</v>
+        <v>362.0400085449219</v>
       </c>
       <c r="F227" t="n">
-        <v>4566200</v>
+        <v>4576500</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B228" t="n">
-        <v>357.9599914550781</v>
+        <v>362.9700012207031</v>
       </c>
       <c r="C228" t="n">
-        <v>359.989990234375</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="D228" t="n">
-        <v>356.5</v>
+        <v>361.2999877929688</v>
       </c>
       <c r="E228" t="n">
-        <v>359.7900085449219</v>
+        <v>365.1799926757812</v>
       </c>
       <c r="F228" t="n">
-        <v>5327500</v>
+        <v>4366800</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B229" t="n">
-        <v>360.0499877929688</v>
+        <v>366.5</v>
       </c>
       <c r="C229" t="n">
-        <v>363.1199951171875</v>
+        <v>366.5</v>
       </c>
       <c r="D229" t="n">
-        <v>358.6000061035156</v>
+        <v>361.5199890136719</v>
       </c>
       <c r="E229" t="n">
-        <v>362.0400085449219</v>
+        <v>363.1099853515625</v>
       </c>
       <c r="F229" t="n">
-        <v>4576500</v>
+        <v>5102700</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B230" t="n">
-        <v>362.9700012207031</v>
+        <v>363</v>
       </c>
       <c r="C230" t="n">
-        <v>366.0899963378906</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="D230" t="n">
-        <v>361.2999877929688</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="E230" t="n">
-        <v>365.1799926757812</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="F230" t="n">
-        <v>4366800</v>
+        <v>5058600</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B231" t="n">
-        <v>366.5</v>
+        <v>361.9400024414062</v>
       </c>
       <c r="C231" t="n">
-        <v>366.5</v>
+        <v>365.75</v>
       </c>
       <c r="D231" t="n">
-        <v>361.5199890136719</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="E231" t="n">
-        <v>363.1099853515625</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="F231" t="n">
-        <v>5102700</v>
+        <v>5282600</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B232" t="n">
-        <v>363</v>
+        <v>362.3399963378906</v>
       </c>
       <c r="C232" t="n">
-        <v>365.8999938964844</v>
+        <v>363.5700073242188</v>
       </c>
       <c r="D232" t="n">
-        <v>361.4500122070312</v>
+        <v>359.2699890136719</v>
       </c>
       <c r="E232" t="n">
-        <v>362.8399963378906</v>
+        <v>363.25</v>
       </c>
       <c r="F232" t="n">
-        <v>5058600</v>
+        <v>5525100</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B233" t="n">
-        <v>361.9400024414062</v>
+        <v>363.010009765625</v>
       </c>
       <c r="C233" t="n">
-        <v>365.75</v>
+        <v>363.0499877929688</v>
       </c>
       <c r="D233" t="n">
-        <v>360.9599914550781</v>
+        <v>355.6499938964844</v>
       </c>
       <c r="E233" t="n">
-        <v>360.9599914550781</v>
+        <v>357.260009765625</v>
       </c>
       <c r="F233" t="n">
-        <v>5282600</v>
+        <v>6696200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B234" t="n">
-        <v>362.3399963378906</v>
+        <v>357.6000061035156</v>
       </c>
       <c r="C234" t="n">
-        <v>363.5700073242188</v>
+        <v>357.9500122070312</v>
       </c>
       <c r="D234" t="n">
-        <v>359.2699890136719</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E234" t="n">
-        <v>363.25</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="F234" t="n">
-        <v>5525100</v>
+        <v>6799700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B235" t="n">
-        <v>363.010009765625</v>
+        <v>354.0700073242188</v>
       </c>
       <c r="C235" t="n">
-        <v>363.0499877929688</v>
+        <v>356.8599853515625</v>
       </c>
       <c r="D235" t="n">
-        <v>355.6499938964844</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="E235" t="n">
-        <v>357.260009765625</v>
+        <v>351.5799865722656</v>
       </c>
       <c r="F235" t="n">
-        <v>6696200</v>
+        <v>8112100</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B236" t="n">
-        <v>357.6000061035156</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C236" t="n">
-        <v>357.9500122070312</v>
+        <v>358.2799987792969</v>
       </c>
       <c r="D236" t="n">
-        <v>351.5499877929688</v>
+        <v>352.8200073242188</v>
       </c>
       <c r="E236" t="n">
-        <v>351.5499877929688</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="F236" t="n">
-        <v>6799700</v>
+        <v>4394400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B237" t="n">
-        <v>354.0700073242188</v>
+        <v>357</v>
       </c>
       <c r="C237" t="n">
-        <v>356.8599853515625</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D237" t="n">
-        <v>350.3699951171875</v>
+        <v>353.0700073242188</v>
       </c>
       <c r="E237" t="n">
-        <v>351.5799865722656</v>
+        <v>356.6900024414062</v>
       </c>
       <c r="F237" t="n">
-        <v>8112100</v>
+        <v>4298000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B238" t="n">
-        <v>353.2999877929688</v>
+        <v>356.5</v>
       </c>
       <c r="C238" t="n">
-        <v>358.2799987792969</v>
+        <v>358.3500061035156</v>
       </c>
       <c r="D238" t="n">
-        <v>352.8200073242188</v>
+        <v>354.6000061035156</v>
       </c>
       <c r="E238" t="n">
-        <v>356.3900146484375</v>
+        <v>356.5</v>
       </c>
       <c r="F238" t="n">
-        <v>4394400</v>
+        <v>5796500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B239" t="n">
-        <v>357</v>
+        <v>354.6799926757812</v>
       </c>
       <c r="C239" t="n">
-        <v>357.3699951171875</v>
+        <v>357.5700073242188</v>
       </c>
       <c r="D239" t="n">
-        <v>353.0700073242188</v>
+        <v>352.2300109863281</v>
       </c>
       <c r="E239" t="n">
-        <v>356.6900024414062</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="F239" t="n">
-        <v>4298000</v>
+        <v>5209900</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B240" t="n">
-        <v>356.5</v>
+        <v>355.6700134277344</v>
       </c>
       <c r="C240" t="n">
-        <v>358.3500061035156</v>
+        <v>358.7300109863281</v>
       </c>
       <c r="D240" t="n">
-        <v>354.6000061035156</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="E240" t="n">
-        <v>356.5</v>
+        <v>357.6199951171875</v>
       </c>
       <c r="F240" t="n">
-        <v>5796500</v>
+        <v>3914500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B241" t="n">
-        <v>354.6799926757812</v>
+        <v>355.8999938964844</v>
       </c>
       <c r="C241" t="n">
-        <v>357.5700073242188</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="D241" t="n">
-        <v>352.2300109863281</v>
+        <v>354.7699890136719</v>
       </c>
       <c r="E241" t="n">
-        <v>354.2200012207031</v>
+        <v>356.0199890136719</v>
       </c>
       <c r="F241" t="n">
-        <v>5209900</v>
+        <v>7962900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B242" t="n">
-        <v>355.6700134277344</v>
+        <v>355.7300109863281</v>
       </c>
       <c r="C242" t="n">
-        <v>358.7300109863281</v>
+        <v>359.9299926757812</v>
       </c>
       <c r="D242" t="n">
-        <v>354.2200012207031</v>
+        <v>354.1199951171875</v>
       </c>
       <c r="E242" t="n">
-        <v>357.6199951171875</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="F242" t="n">
-        <v>3914500</v>
+        <v>5079000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B243" t="n">
-        <v>355.8999938964844</v>
+        <v>357.5499877929688</v>
       </c>
       <c r="C243" t="n">
-        <v>357.7699890136719</v>
+        <v>361.4700012207031</v>
       </c>
       <c r="D243" t="n">
-        <v>354.7699890136719</v>
+        <v>353.7900085449219</v>
       </c>
       <c r="E243" t="n">
-        <v>356.0199890136719</v>
+        <v>356.2200012207031</v>
       </c>
       <c r="F243" t="n">
-        <v>7962900</v>
+        <v>5341400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B244" t="n">
-        <v>355.7300109863281</v>
+        <v>358.6799926757812</v>
       </c>
       <c r="C244" t="n">
-        <v>359.9299926757812</v>
+        <v>362.8500061035156</v>
       </c>
       <c r="D244" t="n">
-        <v>354.1199951171875</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="E244" t="n">
-        <v>354.9500122070312</v>
+        <v>362.0599975585938</v>
       </c>
       <c r="F244" t="n">
-        <v>5079000</v>
+        <v>5414200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B245" t="n">
-        <v>357.5499877929688</v>
+        <v>361</v>
       </c>
       <c r="C245" t="n">
-        <v>361.4700012207031</v>
+        <v>362.8599853515625</v>
       </c>
       <c r="D245" t="n">
-        <v>353.7900085449219</v>
+        <v>355.2000122070312</v>
       </c>
       <c r="E245" t="n">
-        <v>356.2200012207031</v>
+        <v>358.6400146484375</v>
       </c>
       <c r="F245" t="n">
-        <v>5341400</v>
+        <v>4873500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B246" t="n">
-        <v>358.6799926757812</v>
+        <v>357.1000061035156</v>
       </c>
       <c r="C246" t="n">
-        <v>362.8500061035156</v>
+        <v>358.5499877929688</v>
       </c>
       <c r="D246" t="n">
-        <v>356.3900146484375</v>
+        <v>353.2300109863281</v>
       </c>
       <c r="E246" t="n">
-        <v>362.0599975585938</v>
+        <v>353.510009765625</v>
       </c>
       <c r="F246" t="n">
-        <v>5414200</v>
+        <v>5631400</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B247" t="n">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C247" t="n">
-        <v>362.8599853515625</v>
+        <v>356.3299865722656</v>
       </c>
       <c r="D247" t="n">
-        <v>355.2000122070312</v>
+        <v>348.6900024414062</v>
       </c>
       <c r="E247" t="n">
-        <v>358.6400146484375</v>
+        <v>354.7099914550781</v>
       </c>
       <c r="F247" t="n">
-        <v>4873500</v>
+        <v>6318200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B248" t="n">
-        <v>357.1000061035156</v>
+        <v>353.510009765625</v>
       </c>
       <c r="C248" t="n">
-        <v>358.5499877929688</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="D248" t="n">
-        <v>353.2300109863281</v>
+        <v>351.1199951171875</v>
       </c>
       <c r="E248" t="n">
-        <v>353.510009765625</v>
+        <v>353.5599975585938</v>
       </c>
       <c r="F248" t="n">
-        <v>5631400</v>
+        <v>4184200</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B249" t="n">
-        <v>352</v>
+        <v>358.3200073242188</v>
       </c>
       <c r="C249" t="n">
-        <v>356.3299865722656</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="D249" t="n">
-        <v>348.6900024414062</v>
+        <v>354.7900085449219</v>
       </c>
       <c r="E249" t="n">
-        <v>354.7099914550781</v>
+        <v>356.2300109863281</v>
       </c>
       <c r="F249" t="n">
-        <v>6318200</v>
+        <v>5354600</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B250" t="n">
-        <v>353.510009765625</v>
+        <v>354.2300109863281</v>
       </c>
       <c r="C250" t="n">
-        <v>354.2200012207031</v>
+        <v>355.2799987792969</v>
       </c>
       <c r="D250" t="n">
-        <v>351.1199951171875</v>
+        <v>347.5499877929688</v>
       </c>
       <c r="E250" t="n">
-        <v>353.5599975585938</v>
+        <v>350.1300048828125</v>
       </c>
       <c r="F250" t="n">
-        <v>4184200</v>
+        <v>9609900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B251" t="n">
-        <v>358.3200073242188</v>
+        <v>351</v>
       </c>
       <c r="C251" t="n">
-        <v>360.0499877929688</v>
+        <v>354.7000122070312</v>
       </c>
       <c r="D251" t="n">
-        <v>354.7900085449219</v>
+        <v>343.0700073242188</v>
       </c>
       <c r="E251" t="n">
-        <v>356.2300109863281</v>
+        <v>352.489990234375</v>
       </c>
       <c r="F251" t="n">
-        <v>5354600</v>
+        <v>14026500</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,14 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B252" t="n">
-        <v>354.2300109863281</v>
-      </c>
-      <c r="C252" t="n">
-        <v>355.2799987792969</v>
-      </c>
-      <c r="D252" t="n">
-        <v>347.5499877929688</v>
-      </c>
-      <c r="E252" t="n">
-        <v>350.1300048828125</v>
-      </c>
+        <v>46281</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>9609900</v>
+        <v>8303359</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10017,37 +10009,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>350.13</v>
+        <v>348.92</v>
       </c>
       <c r="D2" t="n">
-        <v>356.23</v>
+        <v>352.49</v>
       </c>
       <c r="E2" t="n">
-        <v>354.23</v>
+        <v>353.38</v>
       </c>
       <c r="F2" t="n">
-        <v>355.25</v>
+        <v>355.6</v>
       </c>
       <c r="G2" t="n">
-        <v>347.545</v>
+        <v>344.685</v>
       </c>
       <c r="H2" t="n">
-        <v>8228221</v>
+        <v>8303359</v>
       </c>
       <c r="I2" t="n">
-        <v>7978498</v>
+        <v>8025614</v>
       </c>
       <c r="J2" t="n">
-        <v>930710749184</v>
+        <v>927494373376</v>
       </c>
       <c r="K2" t="n">
-        <v>15.007715</v>
+        <v>15.104762</v>
       </c>
       <c r="L2" t="n">
-        <v>14.011931</v>
+        <v>13.963509</v>
       </c>
       <c r="M2" t="n">
-        <v>23.33</v>
+        <v>23.1</v>
       </c>
       <c r="N2" t="n">
         <v>366.5</v>
@@ -10059,7 +10051,7 @@
         <v>0.975</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
         <v>0.34921002</v>
@@ -10087,7 +10079,7 @@
         <v>133.007</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.632418</v>
+        <v>2.6233206</v>
       </c>
       <c r="Z2" t="n">
         <v>0.469</v>
@@ -10099,7 +10091,7 @@
         <v>186328006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>768638713856</v>
+        <v>765422338048</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -10128,7 +10120,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:14:13</t>
+          <t>2026-09-17 08:10:00</t>
         </is>
       </c>
     </row>

--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B2" t="n">
-        <v>304.563492987762</v>
+        <v>305.9371875093393</v>
       </c>
       <c r="C2" t="n">
-        <v>307.0361777394413</v>
+        <v>307.5562082549167</v>
       </c>
       <c r="D2" t="n">
-        <v>302.973877849489</v>
+        <v>303.7980870051439</v>
       </c>
       <c r="E2" t="n">
-        <v>305.89794921875</v>
+        <v>307.3501586914062</v>
       </c>
       <c r="F2" t="n">
-        <v>8657800</v>
+        <v>8050700</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B3" t="n">
-        <v>305.9372178866198</v>
+        <v>307.7131905464154</v>
       </c>
       <c r="C3" t="n">
-        <v>307.556238792954</v>
+        <v>309.8718747671735</v>
       </c>
       <c r="D3" t="n">
-        <v>303.7981171700278</v>
+        <v>303.3172771297843</v>
       </c>
       <c r="E3" t="n">
-        <v>307.3501892089844</v>
+        <v>308.8710327148438</v>
       </c>
       <c r="F3" t="n">
-        <v>8050700</v>
+        <v>23568600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B4" t="n">
-        <v>307.7132209495945</v>
+        <v>303.9845245259009</v>
       </c>
       <c r="C4" t="n">
-        <v>309.8719053836384</v>
+        <v>307.8113389670314</v>
       </c>
       <c r="D4" t="n">
-        <v>303.3173070986313</v>
+        <v>303.7490393091097</v>
       </c>
       <c r="E4" t="n">
-        <v>308.8710632324219</v>
+        <v>306.5749816894531</v>
       </c>
       <c r="F4" t="n">
-        <v>23568600</v>
+        <v>7520200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B5" t="n">
-        <v>303.9845245259009</v>
+        <v>305.9666104788898</v>
       </c>
       <c r="C5" t="n">
-        <v>307.8113389670314</v>
+        <v>310.3723158885065</v>
       </c>
       <c r="D5" t="n">
-        <v>303.7490393091097</v>
+        <v>304.7498670452201</v>
       </c>
       <c r="E5" t="n">
-        <v>306.5749816894531</v>
+        <v>306.8693237304688</v>
       </c>
       <c r="F5" t="n">
-        <v>7520200</v>
+        <v>8584400</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B6" t="n">
-        <v>305.9666409066948</v>
+        <v>308.1547392588795</v>
       </c>
       <c r="C6" t="n">
-        <v>310.3723467544506</v>
+        <v>310.6372456892681</v>
       </c>
       <c r="D6" t="n">
-        <v>304.7498973520222</v>
+        <v>305.8194410309901</v>
       </c>
       <c r="E6" t="n">
-        <v>306.8693542480469</v>
+        <v>307.5365905761719</v>
       </c>
       <c r="F6" t="n">
-        <v>8584400</v>
+        <v>7310500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B7" t="n">
-        <v>308.154769837798</v>
+        <v>308.2234462682717</v>
       </c>
       <c r="C7" t="n">
-        <v>310.6372765145315</v>
+        <v>309.7247244545431</v>
       </c>
       <c r="D7" t="n">
-        <v>305.8194713781714</v>
+        <v>305.9469892965607</v>
       </c>
       <c r="E7" t="n">
-        <v>307.53662109375</v>
+        <v>307.5660400390625</v>
       </c>
       <c r="F7" t="n">
-        <v>7310500</v>
+        <v>7083200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B8" t="n">
-        <v>308.2234768510796</v>
+        <v>308.9888161441515</v>
       </c>
       <c r="C8" t="n">
-        <v>309.7247551863121</v>
+        <v>311.8441943720275</v>
       </c>
       <c r="D8" t="n">
-        <v>305.947019653492</v>
+        <v>307.8113600348933</v>
       </c>
       <c r="E8" t="n">
-        <v>307.5660705566406</v>
+        <v>310.1270446777344</v>
       </c>
       <c r="F8" t="n">
-        <v>7083200</v>
+        <v>7258100</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B9" t="n">
-        <v>308.988785738579</v>
+        <v>311.1082550854298</v>
       </c>
       <c r="C9" t="n">
-        <v>311.8441636854759</v>
+        <v>312.0404339863167</v>
       </c>
       <c r="D9" t="n">
-        <v>307.8113297451866</v>
+        <v>307.7720847183659</v>
       </c>
       <c r="E9" t="n">
-        <v>310.1270141601562</v>
+        <v>309.7639770507812</v>
       </c>
       <c r="F9" t="n">
-        <v>7258100</v>
+        <v>6462400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B10" t="n">
-        <v>311.1082857354447</v>
+        <v>310.3134645283819</v>
       </c>
       <c r="C10" t="n">
-        <v>312.0404647281687</v>
+        <v>311.4516930034957</v>
       </c>
       <c r="D10" t="n">
-        <v>307.7721150397051</v>
+        <v>304.288708108424</v>
       </c>
       <c r="E10" t="n">
-        <v>309.7640075683594</v>
+        <v>309.5088500976562</v>
       </c>
       <c r="F10" t="n">
-        <v>6462400</v>
+        <v>11823300</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B11" t="n">
-        <v>310.3134645283819</v>
+        <v>308.0762861336198</v>
       </c>
       <c r="C11" t="n">
-        <v>311.4516930034957</v>
+        <v>308.6846429587351</v>
       </c>
       <c r="D11" t="n">
-        <v>304.288708108424</v>
+        <v>301.6394301376976</v>
       </c>
       <c r="E11" t="n">
-        <v>309.5088500976562</v>
+        <v>304.8774719238281</v>
       </c>
       <c r="F11" t="n">
-        <v>11823300</v>
+        <v>9235200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B12" t="n">
-        <v>308.0762861336198</v>
+        <v>304.1807853263183</v>
       </c>
       <c r="C12" t="n">
-        <v>308.6846429587351</v>
+        <v>304.7302708010082</v>
       </c>
       <c r="D12" t="n">
-        <v>301.6394301376976</v>
+        <v>300.3932583082978</v>
       </c>
       <c r="E12" t="n">
-        <v>304.8774719238281</v>
+        <v>301.7767639160156</v>
       </c>
       <c r="F12" t="n">
-        <v>9235200</v>
+        <v>7600000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B13" t="n">
-        <v>304.1808160870063</v>
+        <v>302.718779227698</v>
       </c>
       <c r="C13" t="n">
-        <v>304.7303016172636</v>
+        <v>305.8096426575195</v>
       </c>
       <c r="D13" t="n">
-        <v>300.393288685967</v>
+        <v>302.4243927447969</v>
       </c>
       <c r="E13" t="n">
-        <v>301.7767944335938</v>
+        <v>304.2102355957031</v>
       </c>
       <c r="F13" t="n">
-        <v>7600000</v>
+        <v>6029900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,25 +781,25 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B14" t="n">
-        <v>302.718779227698</v>
+        <v>305.8371035459471</v>
       </c>
       <c r="C14" t="n">
-        <v>305.8096426575195</v>
+        <v>307.3851288987199</v>
       </c>
       <c r="D14" t="n">
-        <v>302.4243927447969</v>
+        <v>300.8578215934895</v>
       </c>
       <c r="E14" t="n">
-        <v>304.2102355957031</v>
+        <v>304.8511047363281</v>
       </c>
       <c r="F14" t="n">
-        <v>6029900</v>
+        <v>7214500</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -807,25 +807,25 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B15" t="n">
-        <v>305.8371341622301</v>
+        <v>305.0187502270194</v>
       </c>
       <c r="C15" t="n">
-        <v>307.3851596699703</v>
+        <v>305.6695130787729</v>
       </c>
       <c r="D15" t="n">
-        <v>300.857851711314</v>
+        <v>300.4338615931582</v>
       </c>
       <c r="E15" t="n">
-        <v>304.8511352539062</v>
+        <v>303.3819885253906</v>
       </c>
       <c r="F15" t="n">
-        <v>7214500</v>
+        <v>8454200</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B16" t="n">
-        <v>305.0187502270194</v>
+        <v>303.8946917756213</v>
       </c>
       <c r="C16" t="n">
-        <v>305.6695130787729</v>
+        <v>304.4567183318842</v>
       </c>
       <c r="D16" t="n">
-        <v>300.4338615931582</v>
+        <v>299.2999336047902</v>
       </c>
       <c r="E16" t="n">
-        <v>303.3819885253906</v>
+        <v>299.7732238769531</v>
       </c>
       <c r="F16" t="n">
-        <v>8454200</v>
+        <v>6489900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B17" t="n">
-        <v>303.8946917756213</v>
+        <v>300.7789375021521</v>
       </c>
       <c r="C17" t="n">
-        <v>304.4567183318842</v>
+        <v>303.7270945284432</v>
       </c>
       <c r="D17" t="n">
-        <v>299.2999336047902</v>
+        <v>299.1422058887319</v>
       </c>
       <c r="E17" t="n">
-        <v>299.7732238769531</v>
+        <v>301.2522277832031</v>
       </c>
       <c r="F17" t="n">
-        <v>6489900</v>
+        <v>7060300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B18" t="n">
-        <v>300.7789375021521</v>
+        <v>301.380450372985</v>
       </c>
       <c r="C18" t="n">
-        <v>303.7270945284432</v>
+        <v>306.1231030365125</v>
       </c>
       <c r="D18" t="n">
-        <v>299.1422058887319</v>
+        <v>296.5983493251649</v>
       </c>
       <c r="E18" t="n">
-        <v>301.2522277832031</v>
+        <v>296.67724609375</v>
       </c>
       <c r="F18" t="n">
-        <v>7060300</v>
+        <v>8597400</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B19" t="n">
-        <v>301.3804193716138</v>
+        <v>301.3212684867699</v>
       </c>
       <c r="C19" t="n">
-        <v>306.1230715472904</v>
+        <v>305.1272097801061</v>
       </c>
       <c r="D19" t="n">
-        <v>296.5983188157025</v>
+        <v>301.1733746705027</v>
       </c>
       <c r="E19" t="n">
-        <v>296.6772155761719</v>
+        <v>303.6580810546875</v>
       </c>
       <c r="F19" t="n">
-        <v>8597400</v>
+        <v>10788700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B20" t="n">
-        <v>301.3212684867699</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C20" t="n">
-        <v>305.1272097801061</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D20" t="n">
-        <v>301.1733746705027</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E20" t="n">
-        <v>303.6580810546875</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F20" t="n">
-        <v>10788700</v>
+        <v>16178800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B21" t="n">
-        <v>301.5578902761218</v>
+        <v>302.1001843350741</v>
       </c>
       <c r="C21" t="n">
-        <v>302.7016525742085</v>
+        <v>307.7499381556482</v>
       </c>
       <c r="D21" t="n">
-        <v>290.0907186231138</v>
+        <v>301.1634734465224</v>
       </c>
       <c r="E21" t="n">
-        <v>297.8505249023438</v>
+        <v>301.4099731445312</v>
       </c>
       <c r="F21" t="n">
-        <v>16178800</v>
+        <v>11354800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B22" t="n">
-        <v>302.1002149225357</v>
+        <v>301.0747572360179</v>
       </c>
       <c r="C22" t="n">
-        <v>307.7499693151439</v>
+        <v>304.3581201926382</v>
       </c>
       <c r="D22" t="n">
-        <v>301.1635039391426</v>
+        <v>292.9106878973514</v>
       </c>
       <c r="E22" t="n">
-        <v>301.4100036621094</v>
+        <v>294.360107421875</v>
       </c>
       <c r="F22" t="n">
-        <v>11354800</v>
+        <v>10549400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B23" t="n">
-        <v>301.0747260223031</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C23" t="n">
-        <v>304.358088638523</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D23" t="n">
-        <v>292.9106575300408</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E23" t="n">
-        <v>294.3600769042969</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F23" t="n">
-        <v>10549400</v>
+        <v>10153500</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B24" t="n">
-        <v>294.9714335987563</v>
+        <v>294.3206459359216</v>
       </c>
       <c r="C24" t="n">
-        <v>295.3559575215809</v>
+        <v>299.4379821870563</v>
       </c>
       <c r="D24" t="n">
-        <v>290.0808874955599</v>
+        <v>293.9854099500461</v>
       </c>
       <c r="E24" t="n">
-        <v>293.3938293457031</v>
+        <v>298.1265869140625</v>
       </c>
       <c r="F24" t="n">
-        <v>10153500</v>
+        <v>6894900</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B25" t="n">
-        <v>294.3206459359216</v>
+        <v>297.436411288458</v>
       </c>
       <c r="C25" t="n">
-        <v>299.4379821870563</v>
+        <v>299.7929328501146</v>
       </c>
       <c r="D25" t="n">
-        <v>293.9854099500461</v>
+        <v>292.8416531202475</v>
       </c>
       <c r="E25" t="n">
-        <v>298.1265869140625</v>
+        <v>292.9303894042969</v>
       </c>
       <c r="F25" t="n">
-        <v>6894900</v>
+        <v>7372700</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B26" t="n">
-        <v>297.436411288458</v>
+        <v>293.6008861047978</v>
       </c>
       <c r="C26" t="n">
-        <v>299.7929328501146</v>
+        <v>293.8868342154489</v>
       </c>
       <c r="D26" t="n">
-        <v>292.8416531202475</v>
+        <v>286.4721332067081</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9303894042969</v>
+        <v>289.9921264648438</v>
       </c>
       <c r="F26" t="n">
-        <v>7372700</v>
+        <v>8054100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B27" t="n">
-        <v>293.6008552074487</v>
+        <v>290.2583437522712</v>
       </c>
       <c r="C27" t="n">
-        <v>293.8868032880077</v>
+        <v>292.2204718178062</v>
       </c>
       <c r="D27" t="n">
-        <v>286.4721030595595</v>
+        <v>288.4145307332595</v>
       </c>
       <c r="E27" t="n">
-        <v>289.9920959472656</v>
+        <v>290.4161071777344</v>
       </c>
       <c r="F27" t="n">
-        <v>8054100</v>
+        <v>5438800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B28" t="n">
-        <v>290.2583742532713</v>
+        <v>291.9345194575729</v>
       </c>
       <c r="C28" t="n">
-        <v>292.220502524991</v>
+        <v>298.3632510673837</v>
       </c>
       <c r="D28" t="n">
-        <v>288.4145610405075</v>
+        <v>291.3133654724136</v>
       </c>
       <c r="E28" t="n">
-        <v>290.4161376953125</v>
+        <v>296.2334899902344</v>
       </c>
       <c r="F28" t="n">
-        <v>5438800</v>
+        <v>7228300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B29" t="n">
-        <v>291.9345495322769</v>
+        <v>297.9294427867379</v>
       </c>
       <c r="C29" t="n">
-        <v>298.3632818043669</v>
+        <v>300.2662554558976</v>
       </c>
       <c r="D29" t="n">
-        <v>291.3133954831271</v>
+        <v>296.7955500258321</v>
       </c>
       <c r="E29" t="n">
-        <v>296.2335205078125</v>
+        <v>299.8915710449219</v>
       </c>
       <c r="F29" t="n">
-        <v>7228300</v>
+        <v>5642200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B30" t="n">
-        <v>297.92941246883</v>
+        <v>300.5915953010157</v>
       </c>
       <c r="C30" t="n">
-        <v>300.2662249001909</v>
+        <v>303.6580673748709</v>
       </c>
       <c r="D30" t="n">
-        <v>296.7955198233114</v>
+        <v>298.915415308335</v>
       </c>
       <c r="E30" t="n">
-        <v>299.8915405273438</v>
+        <v>301.0845947265625</v>
       </c>
       <c r="F30" t="n">
-        <v>5642200</v>
+        <v>6336000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B31" t="n">
-        <v>300.5915953010157</v>
+        <v>299.2605157595805</v>
       </c>
       <c r="C31" t="n">
-        <v>303.6580673748709</v>
+        <v>303.9341406042103</v>
       </c>
       <c r="D31" t="n">
-        <v>298.915415308335</v>
+        <v>298.7675163425421</v>
       </c>
       <c r="E31" t="n">
-        <v>301.0845947265625</v>
+        <v>301.2325134277344</v>
       </c>
       <c r="F31" t="n">
-        <v>6336000</v>
+        <v>7520300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B32" t="n">
-        <v>299.2605157595805</v>
+        <v>301.5085931686638</v>
       </c>
       <c r="C32" t="n">
-        <v>303.9341406042103</v>
+        <v>308.2330823767899</v>
       </c>
       <c r="D32" t="n">
-        <v>298.7675163425421</v>
+        <v>300.828251563059</v>
       </c>
       <c r="E32" t="n">
-        <v>301.2325134277344</v>
+        <v>305.1074829101562</v>
       </c>
       <c r="F32" t="n">
-        <v>7520300</v>
+        <v>7514600</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B33" t="n">
-        <v>301.5086233262724</v>
+        <v>304.2200828300273</v>
       </c>
       <c r="C33" t="n">
-        <v>308.233113206998</v>
+        <v>308.4894444595929</v>
       </c>
       <c r="D33" t="n">
-        <v>300.8282816526182</v>
+        <v>302.9481359332913</v>
       </c>
       <c r="E33" t="n">
-        <v>305.1075134277344</v>
+        <v>306.7639465332031</v>
       </c>
       <c r="F33" t="n">
-        <v>7514600</v>
+        <v>7721300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B34" t="n">
-        <v>304.2200828300273</v>
+        <v>306.6456298108837</v>
       </c>
       <c r="C34" t="n">
-        <v>308.4894444595929</v>
+        <v>307.947155461334</v>
       </c>
       <c r="D34" t="n">
-        <v>302.9481359332913</v>
+        <v>301.9226870872275</v>
       </c>
       <c r="E34" t="n">
-        <v>306.7639465332031</v>
+        <v>305.0187377929688</v>
       </c>
       <c r="F34" t="n">
-        <v>7721300</v>
+        <v>7770000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B35" t="n">
-        <v>306.6456604912348</v>
+        <v>302.4156900665715</v>
       </c>
       <c r="C35" t="n">
-        <v>307.9471862719047</v>
+        <v>307.8485532010255</v>
       </c>
       <c r="D35" t="n">
-        <v>301.9227172950412</v>
+        <v>300.8282464075632</v>
       </c>
       <c r="E35" t="n">
-        <v>305.0187683105469</v>
+        <v>304.9201354980469</v>
       </c>
       <c r="F35" t="n">
-        <v>7770000</v>
+        <v>7085200</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B36" t="n">
-        <v>302.415720333495</v>
+        <v>305.2750763211935</v>
       </c>
       <c r="C36" t="n">
-        <v>307.8485840116909</v>
+        <v>308.7162326204817</v>
       </c>
       <c r="D36" t="n">
-        <v>300.8282765156093</v>
+        <v>301.350820325461</v>
       </c>
       <c r="E36" t="n">
-        <v>304.920166015625</v>
+        <v>307.3161010742188</v>
       </c>
       <c r="F36" t="n">
-        <v>7085200</v>
+        <v>6865200</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B37" t="n">
-        <v>305.2751066360906</v>
+        <v>306.6357687557767</v>
       </c>
       <c r="C37" t="n">
-        <v>308.7162632770978</v>
+        <v>310.4318702971036</v>
       </c>
       <c r="D37" t="n">
-        <v>301.3508502506656</v>
+        <v>305.9160088624015</v>
       </c>
       <c r="E37" t="n">
-        <v>307.3161315917969</v>
+        <v>309.0317687988281</v>
       </c>
       <c r="F37" t="n">
-        <v>6865200</v>
+        <v>7206100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B38" t="n">
-        <v>306.6357990367445</v>
+        <v>307.5231746391179</v>
       </c>
       <c r="C38" t="n">
-        <v>310.4319009529449</v>
+        <v>310.0275898810191</v>
       </c>
       <c r="D38" t="n">
-        <v>305.9160390722913</v>
+        <v>303.3326798145578</v>
       </c>
       <c r="E38" t="n">
-        <v>309.0317993164062</v>
+        <v>309.8106689453125</v>
       </c>
       <c r="F38" t="n">
-        <v>7206100</v>
+        <v>7302300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B39" t="n">
-        <v>307.5232049313688</v>
+        <v>310.5896337890794</v>
       </c>
       <c r="C39" t="n">
-        <v>310.0276204199649</v>
+        <v>315.0857860805166</v>
       </c>
       <c r="D39" t="n">
-        <v>303.3327096940284</v>
+        <v>309.8106862822301</v>
       </c>
       <c r="E39" t="n">
-        <v>309.8106994628906</v>
+        <v>312.4531860351562</v>
       </c>
       <c r="F39" t="n">
-        <v>7302300</v>
+        <v>5794100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B40" t="n">
-        <v>310.5896337890794</v>
+        <v>313.054640940315</v>
       </c>
       <c r="C40" t="n">
-        <v>315.0857860805166</v>
+        <v>314.5829271513063</v>
       </c>
       <c r="D40" t="n">
-        <v>309.8106862822301</v>
+        <v>310.8657222472937</v>
       </c>
       <c r="E40" t="n">
-        <v>312.4531860351562</v>
+        <v>311.2009582519531</v>
       </c>
       <c r="F40" t="n">
-        <v>5794100</v>
+        <v>5030200</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B41" t="n">
-        <v>313.0546102409576</v>
+        <v>311.8320000281587</v>
       </c>
       <c r="C41" t="n">
-        <v>314.5828963020791</v>
+        <v>317.7381233989844</v>
       </c>
       <c r="D41" t="n">
-        <v>310.8656917625901</v>
+        <v>311.782682032414</v>
       </c>
       <c r="E41" t="n">
-        <v>311.200927734375</v>
+        <v>315.9238891601562</v>
       </c>
       <c r="F41" t="n">
-        <v>5030200</v>
+        <v>10578300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B42" t="n">
-        <v>311.8320000281587</v>
+        <v>314.7604311532612</v>
       </c>
       <c r="C42" t="n">
-        <v>317.7381233989844</v>
+        <v>316.1408235578094</v>
       </c>
       <c r="D42" t="n">
-        <v>311.782682032414</v>
+        <v>304.7722577523736</v>
       </c>
       <c r="E42" t="n">
-        <v>315.9238891601562</v>
+        <v>305.1469421386719</v>
       </c>
       <c r="F42" t="n">
-        <v>10578300</v>
+        <v>8973300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B43" t="n">
-        <v>314.7604311532612</v>
+        <v>303.2045199796025</v>
       </c>
       <c r="C43" t="n">
-        <v>316.1408235578094</v>
+        <v>303.3327046462357</v>
       </c>
       <c r="D43" t="n">
-        <v>304.7722577523736</v>
+        <v>297.0124483237873</v>
       </c>
       <c r="E43" t="n">
-        <v>305.1469421386719</v>
+        <v>299.3591003417969</v>
       </c>
       <c r="F43" t="n">
-        <v>8973300</v>
+        <v>10327000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B44" t="n">
-        <v>303.2044890700107</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C44" t="n">
-        <v>303.3326737235763</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D44" t="n">
-        <v>297.012418045434</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E44" t="n">
-        <v>299.3590698242188</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F44" t="n">
-        <v>10327000</v>
+        <v>8344000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B45" t="n">
-        <v>299.7436397411884</v>
+        <v>295.3066317863286</v>
       </c>
       <c r="C45" t="n">
-        <v>301.3113742461044</v>
+        <v>298.70833958092</v>
       </c>
       <c r="D45" t="n">
-        <v>293.5022804823602</v>
+        <v>292.8613440028039</v>
       </c>
       <c r="E45" t="n">
-        <v>296.1644592285156</v>
+        <v>295.2178955078125</v>
       </c>
       <c r="F45" t="n">
-        <v>8344000</v>
+        <v>8077300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B46" t="n">
-        <v>295.3066623130797</v>
+        <v>295.5432899586994</v>
       </c>
       <c r="C46" t="n">
-        <v>298.708370459316</v>
+        <v>300.1873662746028</v>
       </c>
       <c r="D46" t="n">
-        <v>292.8613742767781</v>
+        <v>295.0798692888629</v>
       </c>
       <c r="E46" t="n">
-        <v>295.2179260253906</v>
+        <v>299.0238647460938</v>
       </c>
       <c r="F46" t="n">
-        <v>8077300</v>
+        <v>5546600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B47" t="n">
-        <v>295.5432899586994</v>
+        <v>302.0508736933244</v>
       </c>
       <c r="C47" t="n">
-        <v>300.1873662746028</v>
+        <v>305.5807663052954</v>
       </c>
       <c r="D47" t="n">
-        <v>295.0798692888629</v>
+        <v>293.9854105998292</v>
       </c>
       <c r="E47" t="n">
-        <v>299.0238647460938</v>
+        <v>294.2023315429688</v>
       </c>
       <c r="F47" t="n">
-        <v>5546600</v>
+        <v>7501600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B48" t="n">
-        <v>302.0509050250311</v>
+        <v>297.0715864028587</v>
       </c>
       <c r="C48" t="n">
-        <v>305.5807980031574</v>
+        <v>297.456110287291</v>
       </c>
       <c r="D48" t="n">
-        <v>293.9854410949062</v>
+        <v>288.7103057597054</v>
       </c>
       <c r="E48" t="n">
-        <v>294.2023620605469</v>
+        <v>293.8473510742188</v>
       </c>
       <c r="F48" t="n">
-        <v>7501600</v>
+        <v>11766800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B49" t="n">
-        <v>297.0716172552904</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C49" t="n">
-        <v>297.4561411796575</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D49" t="n">
-        <v>288.7103357437745</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E49" t="n">
-        <v>293.8473815917969</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F49" t="n">
-        <v>11766800</v>
+        <v>10940200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B50" t="n">
-        <v>294.0642973394352</v>
+        <v>295.848951187077</v>
       </c>
       <c r="C50" t="n">
-        <v>295.6221924256846</v>
+        <v>300.236658228506</v>
       </c>
       <c r="D50" t="n">
-        <v>290.386540762355</v>
+        <v>291.4218258555586</v>
       </c>
       <c r="E50" t="n">
-        <v>293.8276672363281</v>
+        <v>298.7576599121094</v>
       </c>
       <c r="F50" t="n">
-        <v>10940200</v>
+        <v>8877200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B51" t="n">
-        <v>295.8489209666184</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C51" t="n">
-        <v>300.2366275598507</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D51" t="n">
-        <v>291.4217960873232</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E51" t="n">
-        <v>298.7576293945312</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F51" t="n">
-        <v>8877200</v>
+        <v>7910900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B52" t="n">
-        <v>300.7296512123902</v>
+        <v>304.7722465716023</v>
       </c>
       <c r="C52" t="n">
-        <v>304.2102259719906</v>
+        <v>309.3275563846455</v>
       </c>
       <c r="D52" t="n">
-        <v>298.9548653069277</v>
+        <v>303.9242719247256</v>
       </c>
       <c r="E52" t="n">
-        <v>303.3327026367188</v>
+        <v>308.6965026855469</v>
       </c>
       <c r="F52" t="n">
-        <v>7910900</v>
+        <v>4322400</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B53" t="n">
-        <v>304.7722465716023</v>
+        <v>308.5683618849884</v>
       </c>
       <c r="C53" t="n">
-        <v>309.3275563846455</v>
+        <v>309.6430970545817</v>
       </c>
       <c r="D53" t="n">
-        <v>303.9242719247256</v>
+        <v>304.2201032083801</v>
       </c>
       <c r="E53" t="n">
-        <v>308.6965026855469</v>
+        <v>304.5947875976562</v>
       </c>
       <c r="F53" t="n">
-        <v>4322400</v>
+        <v>7727300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B54" t="n">
-        <v>308.5683618849884</v>
+        <v>304.4172805196406</v>
       </c>
       <c r="C54" t="n">
-        <v>309.6430970545817</v>
+        <v>306.1329390093465</v>
       </c>
       <c r="D54" t="n">
-        <v>304.2201032083801</v>
+        <v>302.7903884074122</v>
       </c>
       <c r="E54" t="n">
-        <v>304.5947875976562</v>
+        <v>303.5693359375</v>
       </c>
       <c r="F54" t="n">
-        <v>7727300</v>
+        <v>7249000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B55" t="n">
-        <v>304.4172805196406</v>
+        <v>302.8988895743303</v>
       </c>
       <c r="C55" t="n">
-        <v>306.1329390093465</v>
+        <v>307.9866176785159</v>
       </c>
       <c r="D55" t="n">
-        <v>302.7903884074122</v>
+        <v>302.5044659219624</v>
       </c>
       <c r="E55" t="n">
-        <v>303.5693359375</v>
+        <v>307.7598571777344</v>
       </c>
       <c r="F55" t="n">
-        <v>7249000</v>
+        <v>8535300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B56" t="n">
-        <v>302.8988595387675</v>
+        <v>308.8739918889233</v>
       </c>
       <c r="C56" t="n">
-        <v>307.9865871384521</v>
+        <v>314.0307463246157</v>
       </c>
       <c r="D56" t="n">
-        <v>302.5044359255107</v>
+        <v>308.6176225735461</v>
       </c>
       <c r="E56" t="n">
-        <v>307.7598266601562</v>
+        <v>311.6742248535156</v>
       </c>
       <c r="F56" t="n">
-        <v>8535300</v>
+        <v>9627800</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B57" t="n">
-        <v>308.8740523757101</v>
+        <v>311.2206641139725</v>
       </c>
       <c r="C57" t="n">
-        <v>314.0308078212495</v>
+        <v>314.0208969911127</v>
       </c>
       <c r="D57" t="n">
-        <v>308.617683010128</v>
+        <v>310.2740836361238</v>
       </c>
       <c r="E57" t="n">
-        <v>311.6742858886719</v>
+        <v>310.6290588378906</v>
       </c>
       <c r="F57" t="n">
-        <v>9627800</v>
+        <v>6518900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B58" t="n">
-        <v>311.2207252653726</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C58" t="n">
-        <v>314.0209586927274</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D58" t="n">
-        <v>310.2741446015314</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E58" t="n">
-        <v>310.6291198730469</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F58" t="n">
-        <v>6518900</v>
+        <v>7417200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B59" t="n">
-        <v>310.6487980837529</v>
+        <v>310.5403783790639</v>
       </c>
       <c r="C59" t="n">
-        <v>312.0390600856641</v>
+        <v>314.336450228146</v>
       </c>
       <c r="D59" t="n">
-        <v>308.9627484602848</v>
+        <v>295.8193913272319</v>
       </c>
       <c r="E59" t="n">
-        <v>310.7966918945312</v>
+        <v>296.3025512695312</v>
       </c>
       <c r="F59" t="n">
-        <v>7417200</v>
+        <v>18049200</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B60" t="n">
-        <v>310.5403783790639</v>
+        <v>296.2926621709551</v>
       </c>
       <c r="C60" t="n">
-        <v>314.336450228146</v>
+        <v>306.8329925602339</v>
       </c>
       <c r="D60" t="n">
-        <v>295.8193913272319</v>
+        <v>294.2812160390869</v>
       </c>
       <c r="E60" t="n">
-        <v>296.3025512695312</v>
+        <v>305.7680969238281</v>
       </c>
       <c r="F60" t="n">
-        <v>18049200</v>
+        <v>18874100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B61" t="n">
-        <v>296.292632599085</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C61" t="n">
-        <v>306.8329619363725</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D61" t="n">
-        <v>294.2811866679717</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E61" t="n">
-        <v>305.76806640625</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F61" t="n">
-        <v>18874100</v>
+        <v>9721900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B62" t="n">
-        <v>304.9102649889192</v>
+        <v>315.2040954937631</v>
       </c>
       <c r="C62" t="n">
-        <v>313.5476242674454</v>
+        <v>315.7858311866128</v>
       </c>
       <c r="D62" t="n">
-        <v>304.9102649889192</v>
+        <v>312.1672323684923</v>
       </c>
       <c r="E62" t="n">
-        <v>312.9363098144531</v>
+        <v>314.0603332519531</v>
       </c>
       <c r="F62" t="n">
-        <v>9721900</v>
+        <v>8982900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B63" t="n">
-        <v>315.2041261224818</v>
+        <v>315.1153648797306</v>
       </c>
       <c r="C63" t="n">
-        <v>315.7858618718594</v>
+        <v>318.3593094805321</v>
       </c>
       <c r="D63" t="n">
-        <v>312.1672627021157</v>
+        <v>313.9321843288561</v>
       </c>
       <c r="E63" t="n">
-        <v>314.0603637695312</v>
+        <v>315.5393371582031</v>
       </c>
       <c r="F63" t="n">
-        <v>8982900</v>
+        <v>10864100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B64" t="n">
-        <v>315.1153648797306</v>
+        <v>314.6223718715413</v>
       </c>
       <c r="C64" t="n">
-        <v>318.3593094805321</v>
+        <v>315.0463441586525</v>
       </c>
       <c r="D64" t="n">
-        <v>313.9321843288561</v>
+        <v>309.9980348220149</v>
       </c>
       <c r="E64" t="n">
-        <v>315.5393371582031</v>
+        <v>311.1319274902344</v>
       </c>
       <c r="F64" t="n">
-        <v>10864100</v>
+        <v>8331300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B65" t="n">
-        <v>314.6224027314819</v>
+        <v>313.971593609235</v>
       </c>
       <c r="C65" t="n">
-        <v>315.0463750601788</v>
+        <v>314.8984348971578</v>
       </c>
       <c r="D65" t="n">
-        <v>309.9980652283745</v>
+        <v>310.254388930852</v>
       </c>
       <c r="E65" t="n">
-        <v>311.1319580078125</v>
+        <v>310.5699157714844</v>
       </c>
       <c r="F65" t="n">
-        <v>8331300</v>
+        <v>8718700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B66" t="n">
-        <v>313.9716244610726</v>
+        <v>311.5756418636432</v>
       </c>
       <c r="C66" t="n">
-        <v>314.8984658400699</v>
+        <v>313.2518519730792</v>
       </c>
       <c r="D66" t="n">
-        <v>310.2544194174254</v>
+        <v>307.8485673512913</v>
       </c>
       <c r="E66" t="n">
-        <v>310.5699462890625</v>
+        <v>308.6176452636719</v>
       </c>
       <c r="F66" t="n">
-        <v>8718700</v>
+        <v>11444900</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B67" t="n">
-        <v>311.5756418636432</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C67" t="n">
-        <v>313.2518519730792</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D67" t="n">
-        <v>307.8485673512913</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E67" t="n">
-        <v>308.6176452636719</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F67" t="n">
-        <v>11444900</v>
+        <v>24494400</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B68" t="n">
-        <v>309.3965776494671</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="C68" t="n">
-        <v>314.099781180705</v>
+        <v>318.7043994886834</v>
       </c>
       <c r="D68" t="n">
-        <v>308.8049723403709</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="E68" t="n">
-        <v>312.7686767578125</v>
+        <v>318.5663452148438</v>
       </c>
       <c r="F68" t="n">
-        <v>24494400</v>
+        <v>8354600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B69" t="n">
-        <v>313.064515200958</v>
+        <v>319.079052742897</v>
       </c>
       <c r="C69" t="n">
-        <v>318.7044300194866</v>
+        <v>323.1906809208754</v>
       </c>
       <c r="D69" t="n">
-        <v>313.064515200958</v>
+        <v>318.5663442066048</v>
       </c>
       <c r="E69" t="n">
-        <v>318.5663757324219</v>
+        <v>321.3665771484375</v>
       </c>
       <c r="F69" t="n">
-        <v>8354600</v>
+        <v>6668300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B70" t="n">
-        <v>319.0790830432475</v>
+        <v>321.6722493328215</v>
       </c>
       <c r="C70" t="n">
-        <v>323.1907116116738</v>
+        <v>325.3697449529369</v>
       </c>
       <c r="D70" t="n">
-        <v>318.5663744582675</v>
+        <v>320.9426198260136</v>
       </c>
       <c r="E70" t="n">
-        <v>321.3666076660156</v>
+        <v>324.5612487792969</v>
       </c>
       <c r="F70" t="n">
-        <v>6668300</v>
+        <v>4289300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B71" t="n">
-        <v>321.6722493328215</v>
+        <v>324.5020893383847</v>
       </c>
       <c r="C71" t="n">
-        <v>325.3697449529369</v>
+        <v>326.22758744424</v>
       </c>
       <c r="D71" t="n">
-        <v>320.9426198260136</v>
+        <v>321.9680949886989</v>
       </c>
       <c r="E71" t="n">
-        <v>324.5612487792969</v>
+        <v>323.3189086914062</v>
       </c>
       <c r="F71" t="n">
-        <v>4289300</v>
+        <v>4158300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B72" t="n">
-        <v>324.5020893383847</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C72" t="n">
-        <v>326.22758744424</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D72" t="n">
-        <v>321.9680949886989</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E72" t="n">
-        <v>323.3189086914062</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F72" t="n">
-        <v>4158300</v>
+        <v>8635300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B73" t="n">
-        <v>322.4216288798564</v>
+        <v>320.2622768741799</v>
       </c>
       <c r="C73" t="n">
-        <v>323.1808371734579</v>
+        <v>320.3904615362508</v>
       </c>
       <c r="D73" t="n">
-        <v>319.0002116144308</v>
+        <v>317.9747523718436</v>
       </c>
       <c r="E73" t="n">
-        <v>319.2171325683594</v>
+        <v>318.8917541503906</v>
       </c>
       <c r="F73" t="n">
-        <v>8635300</v>
+        <v>7904300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B74" t="n">
-        <v>320.2623075229155</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C74" t="n">
-        <v>320.3904921972535</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D74" t="n">
-        <v>317.9747828016658</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E74" t="n">
-        <v>318.8917846679688</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F74" t="n">
-        <v>7904300</v>
+        <v>5048500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B75" t="n">
-        <v>319.7988699190817</v>
+        <v>317.9846252281575</v>
       </c>
       <c r="C75" t="n">
-        <v>320.3313177342217</v>
+        <v>321.1694123071354</v>
       </c>
       <c r="D75" t="n">
-        <v>317.5310845539587</v>
+        <v>316.2492576445291</v>
       </c>
       <c r="E75" t="n">
-        <v>317.7085571289062</v>
+        <v>320.9229125976562</v>
       </c>
       <c r="F75" t="n">
-        <v>5048500</v>
+        <v>8054000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B76" t="n">
-        <v>317.9846252281575</v>
+        <v>320.942599199713</v>
       </c>
       <c r="C76" t="n">
-        <v>321.1694123071354</v>
+        <v>332.5280847314999</v>
       </c>
       <c r="D76" t="n">
-        <v>316.2492576445291</v>
+        <v>320.6369419886511</v>
       </c>
       <c r="E76" t="n">
-        <v>320.9229125976562</v>
+        <v>329.363037109375</v>
       </c>
       <c r="F76" t="n">
-        <v>8054000</v>
+        <v>10752600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,25 +2419,25 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B77" t="n">
-        <v>320.942628937084</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C77" t="n">
-        <v>332.5281155423397</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D77" t="n">
-        <v>320.636971697701</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E77" t="n">
-        <v>329.3630676269531</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F77" t="n">
-        <v>10752600</v>
+        <v>7660800</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2445,25 +2445,25 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B78" t="n">
-        <v>329.4422902981328</v>
+        <v>327.9764350864437</v>
       </c>
       <c r="C78" t="n">
-        <v>332.6612412306879</v>
+        <v>328.9767653957764</v>
       </c>
       <c r="D78" t="n">
-        <v>327.491109600743</v>
+        <v>321.4989071734381</v>
       </c>
       <c r="E78" t="n">
-        <v>331.4132690429688</v>
+        <v>323.8660583496094</v>
       </c>
       <c r="F78" t="n">
-        <v>7660800</v>
+        <v>9815200</v>
       </c>
       <c r="G78" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B79" t="n">
-        <v>327.9764659913386</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C79" t="n">
-        <v>328.9767963949314</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D79" t="n">
-        <v>321.4989374679619</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E79" t="n">
-        <v>323.8660888671875</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F79" t="n">
-        <v>9815200</v>
+        <v>11737100</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B80" t="n">
-        <v>323.2718313763784</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C80" t="n">
-        <v>328.2339475379842</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D80" t="n">
-        <v>322.5388804495614</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E80" t="n">
-        <v>326.6393432617188</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F80" t="n">
-        <v>11737100</v>
+        <v>6738100</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B81" t="n">
-        <v>326.1936353875406</v>
+        <v>318.8049332018166</v>
       </c>
       <c r="C81" t="n">
-        <v>328.7291759216584</v>
+        <v>322.9053661093398</v>
       </c>
       <c r="D81" t="n">
-        <v>325.0348299492433</v>
+        <v>318.1611490039577</v>
       </c>
       <c r="E81" t="n">
-        <v>326.0450744628906</v>
+        <v>321.3899841308594</v>
       </c>
       <c r="F81" t="n">
-        <v>6738100</v>
+        <v>12805100</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B82" t="n">
-        <v>318.8049029297019</v>
+        <v>321.2017865718998</v>
       </c>
       <c r="C82" t="n">
-        <v>322.9053354478686</v>
+        <v>323.7373271836527</v>
       </c>
       <c r="D82" t="n">
-        <v>318.1611187929736</v>
+        <v>307.6029755260753</v>
       </c>
       <c r="E82" t="n">
-        <v>321.3899536132812</v>
+        <v>307.9298095703125</v>
       </c>
       <c r="F82" t="n">
-        <v>12805100</v>
+        <v>19371200</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B83" t="n">
-        <v>321.2017547389941</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C83" t="n">
-        <v>323.7372950994605</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D83" t="n">
-        <v>307.6029450408882</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E83" t="n">
-        <v>307.9297790527344</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F83" t="n">
-        <v>19371200</v>
+        <v>25951500</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B84" t="n">
-        <v>305.2556057077196</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C84" t="n">
-        <v>308.7815926253858</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D84" t="n">
-        <v>303.1954601804828</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E84" t="n">
-        <v>304.9287414550781</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F84" t="n">
-        <v>25951500</v>
+        <v>14751400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B85" t="n">
-        <v>305.5230197927318</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C85" t="n">
-        <v>309.95031666446</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D85" t="n">
-        <v>304.8098971346673</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E85" t="n">
-        <v>306.3054809570312</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F85" t="n">
-        <v>14751400</v>
+        <v>14652500</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B86" t="n">
-        <v>307.385060616362</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C86" t="n">
-        <v>314.1795087286461</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D86" t="n">
-        <v>307.0383983149945</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E86" t="n">
-        <v>309.4848022460938</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F86" t="n">
-        <v>14652500</v>
+        <v>12900600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B87" t="n">
-        <v>303.2845981841295</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C87" t="n">
-        <v>308.1774060521912</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D87" t="n">
-        <v>298.9761500928895</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E87" t="n">
-        <v>299.8477478027344</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F87" t="n">
-        <v>12900600</v>
+        <v>10270100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B88" t="n">
-        <v>300.5311849469782</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C88" t="n">
-        <v>302.4823658305288</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D88" t="n">
-        <v>298.2729680555718</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E88" t="n">
-        <v>299.1544799804688</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F88" t="n">
-        <v>10270100</v>
+        <v>10535800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B89" t="n">
-        <v>301.9474777854751</v>
+        <v>299.1148422218051</v>
       </c>
       <c r="C89" t="n">
-        <v>305.2555953909441</v>
+        <v>299.4813025896872</v>
       </c>
       <c r="D89" t="n">
-        <v>300.0062112868251</v>
+        <v>293.6773006232809</v>
       </c>
       <c r="E89" t="n">
-        <v>300.729248046875</v>
+        <v>294.875732421875</v>
       </c>
       <c r="F89" t="n">
-        <v>10535800</v>
+        <v>11107900</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B90" t="n">
-        <v>299.1148112655088</v>
+        <v>294.9648788077786</v>
       </c>
       <c r="C90" t="n">
-        <v>299.4812715954647</v>
+        <v>298.8969527426069</v>
       </c>
       <c r="D90" t="n">
-        <v>293.6772702297321</v>
+        <v>294.6083325653198</v>
       </c>
       <c r="E90" t="n">
-        <v>294.8757019042969</v>
+        <v>298.1640319824219</v>
       </c>
       <c r="F90" t="n">
-        <v>11107900</v>
+        <v>11752700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B91" t="n">
-        <v>294.9648486176391</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C91" t="n">
-        <v>298.8969221500132</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D91" t="n">
-        <v>294.6083024116733</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E91" t="n">
-        <v>298.1640014648438</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F91" t="n">
-        <v>11752700</v>
+        <v>11527400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B92" t="n">
-        <v>298.4512235287846</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C92" t="n">
-        <v>299.0851237823749</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D92" t="n">
-        <v>295.3016109870806</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E92" t="n">
-        <v>297.4409790039062</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F92" t="n">
-        <v>11527400</v>
+        <v>9556700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B93" t="n">
-        <v>297.4013222225187</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C93" t="n">
-        <v>299.0355829225425</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D93" t="n">
-        <v>295.2025300603667</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E93" t="n">
-        <v>297.8965454101562</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F93" t="n">
-        <v>9556700</v>
+        <v>11580000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B94" t="n">
-        <v>299.5110006693188</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C94" t="n">
-        <v>303.898671192008</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D94" t="n">
-        <v>299.3327275624257</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E94" t="n">
-        <v>303.4926147460938</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F94" t="n">
-        <v>11580000</v>
+        <v>11953200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B95" t="n">
-        <v>302.333781642444</v>
+        <v>301.5513012828864</v>
       </c>
       <c r="C95" t="n">
-        <v>304.9881708986046</v>
+        <v>306.3450582127215</v>
       </c>
       <c r="D95" t="n">
-        <v>299.6694782493637</v>
+        <v>298.4908255461663</v>
       </c>
       <c r="E95" t="n">
-        <v>302.9676818847656</v>
+        <v>305.1961669921875</v>
       </c>
       <c r="F95" t="n">
-        <v>11953200</v>
+        <v>9839400</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B96" t="n">
-        <v>301.5513314360023</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C96" t="n">
-        <v>306.3450888451811</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D96" t="n">
-        <v>298.4908553932551</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E96" t="n">
-        <v>305.1961975097656</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F96" t="n">
-        <v>9839400</v>
+        <v>12688000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B97" t="n">
-        <v>306.7709905338949</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="C97" t="n">
-        <v>313.2286905211348</v>
+        <v>316.2594719758441</v>
       </c>
       <c r="D97" t="n">
-        <v>306.1470044328188</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="E97" t="n">
-        <v>311.8420715332031</v>
+        <v>314.2389526367188</v>
       </c>
       <c r="F97" t="n">
-        <v>12688000</v>
+        <v>9848800</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B98" t="n">
-        <v>311.4062598905275</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C98" t="n">
-        <v>316.2594412620415</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D98" t="n">
-        <v>311.4062598905275</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E98" t="n">
-        <v>314.2389221191406</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F98" t="n">
-        <v>9848800</v>
+        <v>9388000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B99" t="n">
-        <v>311.9906259989966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C99" t="n">
-        <v>312.9909865673853</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D99" t="n">
-        <v>302.6210112179966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E99" t="n">
-        <v>307.1968688964844</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F99" t="n">
-        <v>9388000</v>
+        <v>17797400</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B100" t="n">
-        <v>311.7034102684662</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C100" t="n">
-        <v>321.1522783634816</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D100" t="n">
-        <v>311.7034102684662</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E100" t="n">
-        <v>319.3199462890625</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F100" t="n">
-        <v>17797400</v>
+        <v>11477500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B101" t="n">
-        <v>318.2700781279603</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C101" t="n">
-        <v>323.2817350541263</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D101" t="n">
-        <v>317.0518180384032</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E101" t="n">
-        <v>319.0228271484375</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F101" t="n">
-        <v>11477500</v>
+        <v>9902200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B102" t="n">
-        <v>319.4684837021083</v>
+        <v>320.1518827061323</v>
       </c>
       <c r="C102" t="n">
-        <v>323.014298845819</v>
+        <v>322.1724018130651</v>
       </c>
       <c r="D102" t="n">
-        <v>312.1094739861534</v>
+        <v>305.7805260837019</v>
       </c>
       <c r="E102" t="n">
-        <v>315.2392883300781</v>
+        <v>307.8505554199219</v>
       </c>
       <c r="F102" t="n">
-        <v>9902200</v>
+        <v>8703500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B103" t="n">
-        <v>320.1519144431551</v>
+        <v>309.2966374972976</v>
       </c>
       <c r="C103" t="n">
-        <v>322.1724337503843</v>
+        <v>310.6238322045743</v>
       </c>
       <c r="D103" t="n">
-        <v>305.7805563960757</v>
+        <v>297.1537535117247</v>
       </c>
       <c r="E103" t="n">
-        <v>307.8505859375</v>
+        <v>299.7487487792969</v>
       </c>
       <c r="F103" t="n">
-        <v>8703500</v>
+        <v>13443400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B104" t="n">
-        <v>309.2966060076438</v>
+        <v>295.6680782309701</v>
       </c>
       <c r="C104" t="n">
-        <v>310.6238005797982</v>
+        <v>301.3829738793206</v>
       </c>
       <c r="D104" t="n">
-        <v>297.1537232583444</v>
+        <v>293.6871852314235</v>
       </c>
       <c r="E104" t="n">
-        <v>299.7487182617188</v>
+        <v>299.6595764160156</v>
       </c>
       <c r="F104" t="n">
-        <v>13443400</v>
+        <v>9114500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B105" t="n">
-        <v>295.6680481198895</v>
+        <v>299.8675850307636</v>
       </c>
       <c r="C105" t="n">
-        <v>301.3829431862302</v>
+        <v>305.2952123797385</v>
       </c>
       <c r="D105" t="n">
-        <v>293.6871553220786</v>
+        <v>299.6100592744303</v>
       </c>
       <c r="E105" t="n">
-        <v>299.6595458984375</v>
+        <v>304.1958312988281</v>
       </c>
       <c r="F105" t="n">
-        <v>9114500</v>
+        <v>8896800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B106" t="n">
-        <v>299.8675549474044</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C106" t="n">
-        <v>305.2951817518681</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D106" t="n">
-        <v>299.6100292169066</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E106" t="n">
-        <v>304.19580078125</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F106" t="n">
-        <v>8896800</v>
+        <v>7209600</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B107" t="n">
-        <v>305.5130974954087</v>
+        <v>304.2354272061944</v>
       </c>
       <c r="C107" t="n">
-        <v>309.2966101142475</v>
+        <v>306.2262038721237</v>
       </c>
       <c r="D107" t="n">
-        <v>304.2849535938903</v>
+        <v>302.2049939958365</v>
       </c>
       <c r="E107" t="n">
-        <v>305.8300476074219</v>
+        <v>305.1069946289062</v>
       </c>
       <c r="F107" t="n">
-        <v>7209600</v>
+        <v>6737700</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B108" t="n">
-        <v>304.2354576365961</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C108" t="n">
-        <v>306.226234501648</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D108" t="n">
-        <v>302.2050242231491</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E108" t="n">
-        <v>305.1070251464844</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F108" t="n">
-        <v>6737700</v>
+        <v>7792700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B109" t="n">
-        <v>305.4536802835111</v>
+        <v>305.8498457788994</v>
       </c>
       <c r="C109" t="n">
-        <v>308.0288471084009</v>
+        <v>308.0288400173425</v>
       </c>
       <c r="D109" t="n">
-        <v>302.7596647203387</v>
+        <v>292.2807478108573</v>
       </c>
       <c r="E109" t="n">
-        <v>307.8208618164062</v>
+        <v>294.8262023925781</v>
       </c>
       <c r="F109" t="n">
-        <v>7792700</v>
+        <v>12955400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B110" t="n">
-        <v>305.8498774375392</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C110" t="n">
-        <v>308.028871901531</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D110" t="n">
-        <v>292.2807780649544</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E110" t="n">
-        <v>294.8262329101562</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F110" t="n">
-        <v>12955400</v>
+        <v>13554100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B111" t="n">
-        <v>293.9843218466586</v>
+        <v>295.7869507950724</v>
       </c>
       <c r="C111" t="n">
-        <v>296.886322684036</v>
+        <v>300.7589812348872</v>
       </c>
       <c r="D111" t="n">
-        <v>288.5962907533433</v>
+        <v>294.1725181992404</v>
       </c>
       <c r="E111" t="n">
-        <v>294.459716796875</v>
+        <v>300.4024047851562</v>
       </c>
       <c r="F111" t="n">
-        <v>13554100</v>
+        <v>8095500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B112" t="n">
-        <v>295.7869207463737</v>
+        <v>301.670173133609</v>
       </c>
       <c r="C112" t="n">
-        <v>300.7589506810849</v>
+        <v>306.0578739762234</v>
       </c>
       <c r="D112" t="n">
-        <v>294.1724883145502</v>
+        <v>300.7391812579012</v>
       </c>
       <c r="E112" t="n">
-        <v>300.4023742675781</v>
+        <v>303.2053833007812</v>
       </c>
       <c r="F112" t="n">
-        <v>8095500</v>
+        <v>7007800</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B113" t="n">
-        <v>301.670173133609</v>
+        <v>297.1339389424841</v>
       </c>
       <c r="C113" t="n">
-        <v>306.0578739762234</v>
+        <v>300.0557680991628</v>
       </c>
       <c r="D113" t="n">
-        <v>300.7391812579012</v>
+        <v>291.636973162459</v>
       </c>
       <c r="E113" t="n">
-        <v>303.2053833007812</v>
+        <v>297.4310607910156</v>
       </c>
       <c r="F113" t="n">
-        <v>7007800</v>
+        <v>18620800</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B114" t="n">
-        <v>297.1339389424841</v>
+        <v>291.9935267958635</v>
       </c>
       <c r="C114" t="n">
-        <v>300.0557680991628</v>
+        <v>297.1141484397957</v>
       </c>
       <c r="D114" t="n">
-        <v>291.636973162459</v>
+        <v>290.4088063693875</v>
       </c>
       <c r="E114" t="n">
-        <v>297.4310607910156</v>
+        <v>294.7172546386719</v>
       </c>
       <c r="F114" t="n">
-        <v>18620800</v>
+        <v>8508900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B115" t="n">
-        <v>291.9935267958635</v>
+        <v>289.4975898716125</v>
       </c>
       <c r="C115" t="n">
-        <v>297.1141484397957</v>
+        <v>299.5011046657454</v>
       </c>
       <c r="D115" t="n">
-        <v>290.4088063693875</v>
+        <v>286.7342359222354</v>
       </c>
       <c r="E115" t="n">
-        <v>294.7172546386719</v>
+        <v>297.3914489746094</v>
       </c>
       <c r="F115" t="n">
-        <v>8508900</v>
+        <v>10278200</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B116" t="n">
-        <v>289.4975898716125</v>
+        <v>297.1240288614248</v>
       </c>
       <c r="C116" t="n">
-        <v>299.5011046657454</v>
+        <v>298.1243894751821</v>
       </c>
       <c r="D116" t="n">
-        <v>286.7342359222354</v>
+        <v>292.993883980321</v>
       </c>
       <c r="E116" t="n">
-        <v>297.3914489746094</v>
+        <v>296.52978515625</v>
       </c>
       <c r="F116" t="n">
-        <v>10278200</v>
+        <v>8055700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B117" t="n">
-        <v>297.1240288614248</v>
+        <v>295.1332451958745</v>
       </c>
       <c r="C117" t="n">
-        <v>298.1243894751821</v>
+        <v>298.3620800816865</v>
       </c>
       <c r="D117" t="n">
-        <v>292.993883980321</v>
+        <v>289.6362492414601</v>
       </c>
       <c r="E117" t="n">
-        <v>296.52978515625</v>
+        <v>290.7455444335938</v>
       </c>
       <c r="F117" t="n">
-        <v>8055700</v>
+        <v>12732500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B118" t="n">
-        <v>295.1332451958745</v>
+        <v>283.6044306839189</v>
       </c>
       <c r="C118" t="n">
-        <v>298.3620800816865</v>
+        <v>287.2195541533999</v>
       </c>
       <c r="D118" t="n">
-        <v>289.6362492414601</v>
+        <v>280.9995517042956</v>
       </c>
       <c r="E118" t="n">
-        <v>290.7455444335938</v>
+        <v>286.7144470214844</v>
       </c>
       <c r="F118" t="n">
-        <v>12732500</v>
+        <v>13496500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B119" t="n">
-        <v>283.6044306839189</v>
+        <v>282.7724816341387</v>
       </c>
       <c r="C119" t="n">
-        <v>287.2195541533999</v>
+        <v>288.3189881947603</v>
       </c>
       <c r="D119" t="n">
-        <v>280.9995517042956</v>
+        <v>277.7707387954702</v>
       </c>
       <c r="E119" t="n">
-        <v>286.7144470214844</v>
+        <v>287.1502685546875</v>
       </c>
       <c r="F119" t="n">
-        <v>13496500</v>
+        <v>12241100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B120" t="n">
-        <v>282.7724816341387</v>
+        <v>286.5262662545288</v>
       </c>
       <c r="C120" t="n">
-        <v>288.3189881947603</v>
+        <v>289.9532025593205</v>
       </c>
       <c r="D120" t="n">
-        <v>277.7707387954702</v>
+        <v>284.4364084963449</v>
       </c>
       <c r="E120" t="n">
-        <v>287.1502685546875</v>
+        <v>285.9716186523438</v>
       </c>
       <c r="F120" t="n">
-        <v>12241100</v>
+        <v>8344900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B121" t="n">
-        <v>286.5262662545288</v>
+        <v>286.0508166178312</v>
       </c>
       <c r="C121" t="n">
-        <v>289.9532025593205</v>
+        <v>287.7048753720447</v>
       </c>
       <c r="D121" t="n">
-        <v>284.4364084963449</v>
+        <v>282.1385413260368</v>
       </c>
       <c r="E121" t="n">
-        <v>285.9716186523438</v>
+        <v>284.7731323242188</v>
       </c>
       <c r="F121" t="n">
-        <v>8344900</v>
+        <v>10205000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B122" t="n">
-        <v>286.0508472723319</v>
+        <v>280.1279538528093</v>
       </c>
       <c r="C122" t="n">
-        <v>287.7049062038017</v>
+        <v>281.167940752382</v>
       </c>
       <c r="D122" t="n">
-        <v>282.1385715612803</v>
+        <v>276.4336079693154</v>
       </c>
       <c r="E122" t="n">
-        <v>284.7731628417969</v>
+        <v>280.1874084472656</v>
       </c>
       <c r="F122" t="n">
-        <v>10205000</v>
+        <v>13760500</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B123" t="n">
-        <v>280.1279843639117</v>
+        <v>281.9504072447318</v>
       </c>
       <c r="C123" t="n">
-        <v>281.1679713767581</v>
+        <v>284.4463214441296</v>
       </c>
       <c r="D123" t="n">
-        <v>276.4336380780354</v>
+        <v>280.2468381234208</v>
       </c>
       <c r="E123" t="n">
-        <v>280.1874389648438</v>
+        <v>280.7321472167969</v>
       </c>
       <c r="F123" t="n">
-        <v>13760500</v>
+        <v>9091200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B124" t="n">
-        <v>281.9504072447318</v>
+        <v>283.6044205599556</v>
       </c>
       <c r="C124" t="n">
-        <v>284.4463214441296</v>
+        <v>286.506421278288</v>
       </c>
       <c r="D124" t="n">
-        <v>280.2468381234208</v>
+        <v>281.8909373944359</v>
       </c>
       <c r="E124" t="n">
-        <v>280.7321472167969</v>
+        <v>283.4261474609375</v>
       </c>
       <c r="F124" t="n">
-        <v>9091200</v>
+        <v>8149000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B125" t="n">
-        <v>283.6044205599556</v>
+        <v>286.2390279690733</v>
       </c>
       <c r="C125" t="n">
-        <v>286.506421278288</v>
+        <v>288.9726698808299</v>
       </c>
       <c r="D125" t="n">
-        <v>281.8909373944359</v>
+        <v>283.2181783456238</v>
       </c>
       <c r="E125" t="n">
-        <v>283.4261474609375</v>
+        <v>284.1492004394531</v>
       </c>
       <c r="F125" t="n">
-        <v>8149000</v>
+        <v>8961200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B126" t="n">
-        <v>286.2390279690733</v>
+        <v>284.0897484324327</v>
       </c>
       <c r="C126" t="n">
-        <v>288.9726698808299</v>
+        <v>286.6451172582804</v>
       </c>
       <c r="D126" t="n">
-        <v>283.2181783456238</v>
+        <v>282.3960934275981</v>
       </c>
       <c r="E126" t="n">
-        <v>284.1492004394531</v>
+        <v>284.9910583496094</v>
       </c>
       <c r="F126" t="n">
-        <v>8961200</v>
+        <v>10057000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B127" t="n">
-        <v>284.0897180113691</v>
+        <v>284.1392586396808</v>
       </c>
       <c r="C127" t="n">
-        <v>286.6450865635814</v>
+        <v>286.7441374214082</v>
       </c>
       <c r="D127" t="n">
-        <v>282.3960631878955</v>
+        <v>281.9008401776293</v>
       </c>
       <c r="E127" t="n">
-        <v>284.9910278320312</v>
+        <v>285.2188415527344</v>
       </c>
       <c r="F127" t="n">
-        <v>10057000</v>
+        <v>9846700</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B128" t="n">
-        <v>284.1392890417467</v>
+        <v>285.327825032355</v>
       </c>
       <c r="C128" t="n">
-        <v>286.7441681021885</v>
+        <v>287.9327042603992</v>
       </c>
       <c r="D128" t="n">
-        <v>281.900870340191</v>
+        <v>282.5446726819272</v>
       </c>
       <c r="E128" t="n">
-        <v>285.2188720703125</v>
+        <v>283.8223571777344</v>
       </c>
       <c r="F128" t="n">
-        <v>9846700</v>
+        <v>22436500</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B129" t="n">
-        <v>285.3277943529036</v>
+        <v>291.4982779446762</v>
       </c>
       <c r="C129" t="n">
-        <v>287.9326733008621</v>
+        <v>292.9245231806114</v>
       </c>
       <c r="D129" t="n">
-        <v>282.5446423017302</v>
+        <v>285.2188513876401</v>
       </c>
       <c r="E129" t="n">
-        <v>283.8223266601562</v>
+        <v>287.1403198242188</v>
       </c>
       <c r="F129" t="n">
-        <v>22436500</v>
+        <v>11470800</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B130" t="n">
-        <v>291.4982779446762</v>
+        <v>283.4360748065673</v>
       </c>
       <c r="C130" t="n">
-        <v>292.9245231806114</v>
+        <v>292.6571288676103</v>
       </c>
       <c r="D130" t="n">
-        <v>285.2188513876401</v>
+        <v>282.6436995084055</v>
       </c>
       <c r="E130" t="n">
-        <v>287.1403198242188</v>
+        <v>289.6065368652344</v>
       </c>
       <c r="F130" t="n">
-        <v>11470800</v>
+        <v>11092300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B131" t="n">
-        <v>283.4360748065673</v>
+        <v>291.3398308899875</v>
       </c>
       <c r="C131" t="n">
-        <v>292.6571288676103</v>
+        <v>294.7965097163498</v>
       </c>
       <c r="D131" t="n">
-        <v>282.6436995084055</v>
+        <v>289.6461758443202</v>
       </c>
       <c r="E131" t="n">
-        <v>289.6065368652344</v>
+        <v>292.5977172851562</v>
       </c>
       <c r="F131" t="n">
-        <v>11092300</v>
+        <v>12188200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B132" t="n">
-        <v>291.3398308899875</v>
+        <v>289.7848205526045</v>
       </c>
       <c r="C132" t="n">
-        <v>294.7965097163498</v>
+        <v>292.1718002190451</v>
       </c>
       <c r="D132" t="n">
-        <v>289.6461758443202</v>
+        <v>287.9525187281419</v>
       </c>
       <c r="E132" t="n">
-        <v>292.5977172851562</v>
+        <v>288.8736267089844</v>
       </c>
       <c r="F132" t="n">
-        <v>12188200</v>
+        <v>8669200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B133" t="n">
-        <v>289.7847899387647</v>
+        <v>286.3777093696089</v>
       </c>
       <c r="C133" t="n">
-        <v>292.1717693530369</v>
+        <v>287.3384134369941</v>
       </c>
       <c r="D133" t="n">
-        <v>287.9524883078727</v>
+        <v>279.0582953832721</v>
       </c>
       <c r="E133" t="n">
-        <v>288.8735961914062</v>
+        <v>280.1378784179688</v>
       </c>
       <c r="F133" t="n">
-        <v>8669200</v>
+        <v>9873300</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B134" t="n">
-        <v>286.3777093696089</v>
+        <v>282.0197247859078</v>
       </c>
       <c r="C134" t="n">
-        <v>287.3384134369941</v>
+        <v>284.505755156032</v>
       </c>
       <c r="D134" t="n">
-        <v>279.0582953832721</v>
+        <v>279.6327451103039</v>
       </c>
       <c r="E134" t="n">
-        <v>280.1378784179688</v>
+        <v>281.0589904785156</v>
       </c>
       <c r="F134" t="n">
-        <v>9873300</v>
+        <v>11734400</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B135" t="n">
-        <v>282.0197247859078</v>
+        <v>285.7140887250632</v>
       </c>
       <c r="C135" t="n">
-        <v>284.505755156032</v>
+        <v>292.2510413422024</v>
       </c>
       <c r="D135" t="n">
-        <v>279.6327451103039</v>
+        <v>282.2277281014015</v>
       </c>
       <c r="E135" t="n">
-        <v>281.0589904785156</v>
+        <v>291.3497314453125</v>
       </c>
       <c r="F135" t="n">
-        <v>11734400</v>
+        <v>12956900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B136" t="n">
-        <v>285.7140887250632</v>
+        <v>292.567989087923</v>
       </c>
       <c r="C136" t="n">
-        <v>292.2510413422024</v>
+        <v>295.8661624411999</v>
       </c>
       <c r="D136" t="n">
-        <v>282.2277281014015</v>
+        <v>290.1116710297465</v>
       </c>
       <c r="E136" t="n">
-        <v>291.3497314453125</v>
+        <v>292.5580749511719</v>
       </c>
       <c r="F136" t="n">
-        <v>12956900</v>
+        <v>11267200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B137" t="n">
-        <v>292.567989087923</v>
+        <v>289.1212191631598</v>
       </c>
       <c r="C137" t="n">
-        <v>295.8661624411999</v>
+        <v>292.7957669317203</v>
       </c>
       <c r="D137" t="n">
-        <v>290.1116710297465</v>
+        <v>285.9616926535428</v>
       </c>
       <c r="E137" t="n">
-        <v>292.5580749511719</v>
+        <v>291.7855224609375</v>
       </c>
       <c r="F137" t="n">
-        <v>11267200</v>
+        <v>6669300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,25 +4005,25 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B138" t="n">
-        <v>289.1212191631598</v>
+        <v>292.7412191857173</v>
       </c>
       <c r="C138" t="n">
-        <v>292.7957669317203</v>
+        <v>295.4987855589938</v>
       </c>
       <c r="D138" t="n">
-        <v>285.9616926535428</v>
+        <v>291.8850906324002</v>
       </c>
       <c r="E138" t="n">
-        <v>291.7855224609375</v>
+        <v>294.125</v>
       </c>
       <c r="F138" t="n">
-        <v>6669300</v>
+        <v>7142600</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4031,25 +4031,25 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B139" t="n">
-        <v>292.7412191857173</v>
+        <v>291.8253790066561</v>
       </c>
       <c r="C139" t="n">
-        <v>295.4987855589938</v>
+        <v>296.8427544058445</v>
       </c>
       <c r="D139" t="n">
-        <v>291.8850906324002</v>
+        <v>291.3873498301165</v>
       </c>
       <c r="E139" t="n">
-        <v>294.125</v>
+        <v>296.0662536621094</v>
       </c>
       <c r="F139" t="n">
-        <v>7142600</v>
+        <v>7849100</v>
       </c>
       <c r="G139" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B140" t="n">
-        <v>291.8253790066561</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="C140" t="n">
-        <v>296.8427544058445</v>
+        <v>309.8640903908154</v>
       </c>
       <c r="D140" t="n">
-        <v>291.3873498301165</v>
+        <v>303.9606617936424</v>
       </c>
       <c r="E140" t="n">
-        <v>296.0662536621094</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="F140" t="n">
-        <v>7849100</v>
+        <v>10590200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B141" t="n">
-        <v>306.5888366699219</v>
+        <v>305.5734164156603</v>
       </c>
       <c r="C141" t="n">
-        <v>309.8640903908154</v>
+        <v>309.8640846884941</v>
       </c>
       <c r="D141" t="n">
-        <v>303.9606617936424</v>
+        <v>304.73715687535</v>
       </c>
       <c r="E141" t="n">
-        <v>306.5888366699219</v>
+        <v>308.938232421875</v>
       </c>
       <c r="F141" t="n">
-        <v>10590200</v>
+        <v>6586600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B142" t="n">
-        <v>305.5734164156603</v>
+        <v>308.6097380099313</v>
       </c>
       <c r="C142" t="n">
-        <v>309.8640846884941</v>
+        <v>308.9581744354404</v>
       </c>
       <c r="D142" t="n">
-        <v>304.73715687535</v>
+        <v>305.344449093958</v>
       </c>
       <c r="E142" t="n">
-        <v>308.938232421875</v>
+        <v>308.4803161621094</v>
       </c>
       <c r="F142" t="n">
-        <v>6586600</v>
+        <v>6069700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B143" t="n">
-        <v>308.6097380099313</v>
+        <v>306.0910825316173</v>
       </c>
       <c r="C143" t="n">
-        <v>308.9581744354404</v>
+        <v>312.3329523629397</v>
       </c>
       <c r="D143" t="n">
-        <v>305.344449093958</v>
+        <v>304.0900871089203</v>
       </c>
       <c r="E143" t="n">
-        <v>308.4803161621094</v>
+        <v>312.2732238769531</v>
       </c>
       <c r="F143" t="n">
-        <v>6069700</v>
+        <v>8318200</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B144" t="n">
-        <v>306.0910825316173</v>
+        <v>308.4305432499699</v>
       </c>
       <c r="C144" t="n">
-        <v>312.3329523629397</v>
+        <v>312.9103618924516</v>
       </c>
       <c r="D144" t="n">
-        <v>304.0900871089203</v>
+        <v>307.4847916064935</v>
       </c>
       <c r="E144" t="n">
-        <v>312.2732238769531</v>
+        <v>309.7247009277344</v>
       </c>
       <c r="F144" t="n">
-        <v>8318200</v>
+        <v>11455500</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B145" t="n">
-        <v>308.4305432499699</v>
+        <v>312.5420354159922</v>
       </c>
       <c r="C145" t="n">
-        <v>312.9103618924516</v>
+        <v>312.8307129741003</v>
       </c>
       <c r="D145" t="n">
-        <v>307.4847916064935</v>
+        <v>302.8954898881459</v>
       </c>
       <c r="E145" t="n">
-        <v>309.7247009277344</v>
+        <v>304.5579833984375</v>
       </c>
       <c r="F145" t="n">
-        <v>11455500</v>
+        <v>9885800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B146" t="n">
-        <v>312.5420354159922</v>
+        <v>303.9805907681049</v>
       </c>
       <c r="C146" t="n">
-        <v>312.8307129741003</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="D146" t="n">
-        <v>302.8954898881459</v>
+        <v>303.8312695552229</v>
       </c>
       <c r="E146" t="n">
-        <v>304.5579833984375</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="F146" t="n">
-        <v>9885800</v>
+        <v>8208600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B147" t="n">
-        <v>303.9805907681049</v>
+        <v>311.068653468178</v>
       </c>
       <c r="C147" t="n">
-        <v>308.5599670410156</v>
+        <v>313.4877482505245</v>
       </c>
       <c r="D147" t="n">
-        <v>303.8312695552229</v>
+        <v>308.6993222963794</v>
       </c>
       <c r="E147" t="n">
-        <v>308.5599670410156</v>
+        <v>308.8984375</v>
       </c>
       <c r="F147" t="n">
-        <v>8208600</v>
+        <v>11082400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B148" t="n">
-        <v>311.068653468178</v>
+        <v>309.4559416581444</v>
       </c>
       <c r="C148" t="n">
-        <v>313.4877482505245</v>
+        <v>315.7077766193834</v>
       </c>
       <c r="D148" t="n">
-        <v>308.6993222963794</v>
+        <v>308.9780833700189</v>
       </c>
       <c r="E148" t="n">
-        <v>308.8984375</v>
+        <v>315.5683898925781</v>
       </c>
       <c r="F148" t="n">
-        <v>11082400</v>
+        <v>10772000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B149" t="n">
-        <v>309.4559416581444</v>
+        <v>316.0661368489313</v>
       </c>
       <c r="C149" t="n">
-        <v>315.7077766193834</v>
+        <v>318.8038038717339</v>
       </c>
       <c r="D149" t="n">
-        <v>308.9780833700189</v>
+        <v>311.3474041387296</v>
       </c>
       <c r="E149" t="n">
-        <v>315.5683898925781</v>
+        <v>311.5962829589844</v>
       </c>
       <c r="F149" t="n">
-        <v>10772000</v>
+        <v>7084300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B150" t="n">
-        <v>316.0661368489313</v>
+        <v>313.4379903862348</v>
       </c>
       <c r="C150" t="n">
-        <v>318.8038038717339</v>
+        <v>313.7366328164263</v>
       </c>
       <c r="D150" t="n">
-        <v>311.3474041387296</v>
+        <v>310.5410372905177</v>
       </c>
       <c r="E150" t="n">
-        <v>311.5962829589844</v>
+        <v>311.6161804199219</v>
       </c>
       <c r="F150" t="n">
-        <v>7084300</v>
+        <v>5545900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B151" t="n">
-        <v>313.4379903862348</v>
+        <v>312.1139549773267</v>
       </c>
       <c r="C151" t="n">
-        <v>313.7366328164263</v>
+        <v>313.5773637260273</v>
       </c>
       <c r="D151" t="n">
-        <v>310.5410372905177</v>
+        <v>307.5047445243564</v>
       </c>
       <c r="E151" t="n">
-        <v>311.6161804199219</v>
+        <v>310.2921752929688</v>
       </c>
       <c r="F151" t="n">
-        <v>5545900</v>
+        <v>6969700</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B152" t="n">
-        <v>312.1139549773267</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="C152" t="n">
-        <v>313.5773637260273</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="D152" t="n">
-        <v>307.5047445243564</v>
+        <v>306.5092257615542</v>
       </c>
       <c r="E152" t="n">
-        <v>310.2921752929688</v>
+        <v>306.8974609375</v>
       </c>
       <c r="F152" t="n">
-        <v>6969700</v>
+        <v>5215300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B153" t="n">
-        <v>309.7545850384977</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="C153" t="n">
-        <v>309.7545850384977</v>
+        <v>311.1781431330245</v>
       </c>
       <c r="D153" t="n">
-        <v>306.5092257615542</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="E153" t="n">
-        <v>306.8974609375</v>
+        <v>310.232421875</v>
       </c>
       <c r="F153" t="n">
-        <v>5215300</v>
+        <v>7925300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B154" t="n">
-        <v>305.5037244427344</v>
+        <v>313.7864355589005</v>
       </c>
       <c r="C154" t="n">
-        <v>311.1781431330245</v>
+        <v>314.035314384572</v>
       </c>
       <c r="D154" t="n">
-        <v>305.5037244427344</v>
+        <v>309.7745101043047</v>
       </c>
       <c r="E154" t="n">
-        <v>310.232421875</v>
+        <v>310.0532531738281</v>
       </c>
       <c r="F154" t="n">
-        <v>7925300</v>
+        <v>7398600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B155" t="n">
-        <v>313.7864355589005</v>
+        <v>309.1771855961317</v>
       </c>
       <c r="C155" t="n">
-        <v>314.035314384572</v>
+        <v>310.6505287563671</v>
       </c>
       <c r="D155" t="n">
-        <v>309.7745101043047</v>
+        <v>305.9118967162461</v>
       </c>
       <c r="E155" t="n">
-        <v>310.0532531738281</v>
+        <v>307.8630981445312</v>
       </c>
       <c r="F155" t="n">
-        <v>7398600</v>
+        <v>8031800</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B156" t="n">
-        <v>309.1771855961317</v>
+        <v>305.6928786901284</v>
       </c>
       <c r="C156" t="n">
-        <v>310.6505287563671</v>
+        <v>312.6913497643884</v>
       </c>
       <c r="D156" t="n">
-        <v>305.9118967162461</v>
+        <v>305.1951210592971</v>
       </c>
       <c r="E156" t="n">
-        <v>307.8630981445312</v>
+        <v>311.8252563476562</v>
       </c>
       <c r="F156" t="n">
-        <v>8031800</v>
+        <v>8865400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B157" t="n">
-        <v>305.6928786901284</v>
+        <v>312.5420381202088</v>
       </c>
       <c r="C157" t="n">
-        <v>312.6913497643884</v>
+        <v>314.6624601726697</v>
       </c>
       <c r="D157" t="n">
-        <v>305.1951210592971</v>
+        <v>310.431520181067</v>
       </c>
       <c r="E157" t="n">
-        <v>311.8252563476562</v>
+        <v>311.0686645507812</v>
       </c>
       <c r="F157" t="n">
-        <v>8865400</v>
+        <v>6135400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B158" t="n">
-        <v>312.5420381202088</v>
+        <v>309.2269452093906</v>
       </c>
       <c r="C158" t="n">
-        <v>314.6624601726697</v>
+        <v>309.2568094519629</v>
       </c>
       <c r="D158" t="n">
-        <v>310.431520181067</v>
+        <v>305.1353920734132</v>
       </c>
       <c r="E158" t="n">
-        <v>311.0686645507812</v>
+        <v>306.270263671875</v>
       </c>
       <c r="F158" t="n">
-        <v>6135400</v>
+        <v>7338200</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B159" t="n">
-        <v>309.2269452093906</v>
+        <v>306.3299974055641</v>
       </c>
       <c r="C159" t="n">
-        <v>309.2568094519629</v>
+        <v>309.5753869306937</v>
       </c>
       <c r="D159" t="n">
-        <v>305.1353920734132</v>
+        <v>305.42407485773</v>
       </c>
       <c r="E159" t="n">
-        <v>306.270263671875</v>
+        <v>308.0124206542969</v>
       </c>
       <c r="F159" t="n">
-        <v>7338200</v>
+        <v>6316800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B160" t="n">
-        <v>306.3299974055641</v>
+        <v>310.0532528884956</v>
       </c>
       <c r="C160" t="n">
-        <v>309.5753869306937</v>
+        <v>314.8416790595512</v>
       </c>
       <c r="D160" t="n">
-        <v>305.42407485773</v>
+        <v>309.9536952821754</v>
       </c>
       <c r="E160" t="n">
-        <v>308.0124206542969</v>
+        <v>313.4877624511719</v>
       </c>
       <c r="F160" t="n">
-        <v>6316800</v>
+        <v>8629500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B161" t="n">
-        <v>310.0532528884956</v>
+        <v>313.2388767644321</v>
       </c>
       <c r="C161" t="n">
-        <v>314.8416790595512</v>
+        <v>314.8814709002291</v>
       </c>
       <c r="D161" t="n">
-        <v>309.9536952821754</v>
+        <v>304.7670623908274</v>
       </c>
       <c r="E161" t="n">
-        <v>313.4877624511719</v>
+        <v>304.8964538574219</v>
       </c>
       <c r="F161" t="n">
-        <v>8629500</v>
+        <v>8359600</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B162" t="n">
-        <v>313.2388767644321</v>
+        <v>306.8675912418493</v>
       </c>
       <c r="C162" t="n">
-        <v>314.8814709002291</v>
+        <v>307.6042628420606</v>
       </c>
       <c r="D162" t="n">
-        <v>304.7670623908274</v>
+        <v>299.1523476664256</v>
       </c>
       <c r="E162" t="n">
-        <v>304.8964538574219</v>
+        <v>300.7451782226562</v>
       </c>
       <c r="F162" t="n">
-        <v>8359600</v>
+        <v>9464300</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B163" t="n">
-        <v>306.8675912418493</v>
+        <v>300.7451596100784</v>
       </c>
       <c r="C163" t="n">
-        <v>307.6042628420606</v>
+        <v>301.8302675742967</v>
       </c>
       <c r="D163" t="n">
-        <v>299.1523476664256</v>
+        <v>297.5395993270601</v>
       </c>
       <c r="E163" t="n">
-        <v>300.7451782226562</v>
+        <v>298.6545715332031</v>
       </c>
       <c r="F163" t="n">
-        <v>9464300</v>
+        <v>9512000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B164" t="n">
-        <v>300.7451596100784</v>
+        <v>298.6744753830843</v>
       </c>
       <c r="C164" t="n">
-        <v>301.8302675742967</v>
+        <v>304.6873960201211</v>
       </c>
       <c r="D164" t="n">
-        <v>297.5395993270601</v>
+        <v>294.2245209852311</v>
       </c>
       <c r="E164" t="n">
-        <v>298.6545715332031</v>
+        <v>303.5126953125</v>
       </c>
       <c r="F164" t="n">
-        <v>9512000</v>
+        <v>9498200</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B165" t="n">
-        <v>298.6744753830843</v>
+        <v>300.9144028967509</v>
       </c>
       <c r="C165" t="n">
-        <v>304.6873960201211</v>
+        <v>301.6411400127173</v>
       </c>
       <c r="D165" t="n">
-        <v>294.2245209852311</v>
+        <v>298.7242874353194</v>
       </c>
       <c r="E165" t="n">
-        <v>303.5126953125</v>
+        <v>298.9034729003906</v>
       </c>
       <c r="F165" t="n">
-        <v>9498200</v>
+        <v>7709500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B166" t="n">
-        <v>300.9144028967509</v>
+        <v>300.8945046380796</v>
       </c>
       <c r="C166" t="n">
-        <v>301.6411400127173</v>
+        <v>302.387777613951</v>
       </c>
       <c r="D166" t="n">
-        <v>298.7242874353194</v>
+        <v>297.4699295162906</v>
       </c>
       <c r="E166" t="n">
-        <v>298.9034729003906</v>
+        <v>298.5650024414062</v>
       </c>
       <c r="F166" t="n">
-        <v>7709500</v>
+        <v>7364300</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B167" t="n">
-        <v>300.8945046380796</v>
+        <v>298.8636262885424</v>
       </c>
       <c r="C167" t="n">
-        <v>302.387777613951</v>
+        <v>299.4410421498196</v>
       </c>
       <c r="D167" t="n">
-        <v>297.4699295162906</v>
+        <v>295.1205095874812</v>
       </c>
       <c r="E167" t="n">
-        <v>298.5650024414062</v>
+        <v>296.4743957519531</v>
       </c>
       <c r="F167" t="n">
-        <v>7364300</v>
+        <v>8699300</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B168" t="n">
-        <v>298.8636262885424</v>
+        <v>296.6635495230975</v>
       </c>
       <c r="C168" t="n">
-        <v>299.4410421498196</v>
+        <v>299.908939014877</v>
       </c>
       <c r="D168" t="n">
-        <v>295.1205095874812</v>
+        <v>295.8870488301784</v>
       </c>
       <c r="E168" t="n">
-        <v>296.4743957519531</v>
+        <v>299.3813171386719</v>
       </c>
       <c r="F168" t="n">
-        <v>8699300</v>
+        <v>7546300</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B169" t="n">
-        <v>296.6635495230975</v>
+        <v>299.7396822358739</v>
       </c>
       <c r="C169" t="n">
-        <v>299.908939014877</v>
+        <v>300.436555061437</v>
       </c>
       <c r="D169" t="n">
-        <v>295.8870488301784</v>
+        <v>293.935841710235</v>
       </c>
       <c r="E169" t="n">
-        <v>299.3813171386719</v>
+        <v>294.3738708496094</v>
       </c>
       <c r="F169" t="n">
-        <v>7546300</v>
+        <v>8066900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B170" t="n">
-        <v>299.7396822358739</v>
+        <v>295.3694126574367</v>
       </c>
       <c r="C170" t="n">
-        <v>300.436555061437</v>
+        <v>301.57145376365</v>
       </c>
       <c r="D170" t="n">
-        <v>293.935841710235</v>
+        <v>292.3530024013792</v>
       </c>
       <c r="E170" t="n">
-        <v>294.3738708496094</v>
+        <v>300.625732421875</v>
       </c>
       <c r="F170" t="n">
-        <v>8066900</v>
+        <v>9327000</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B171" t="n">
-        <v>295.3694126574367</v>
+        <v>299.8790926087445</v>
       </c>
       <c r="C171" t="n">
-        <v>301.57145376365</v>
+        <v>302.6167597554335</v>
       </c>
       <c r="D171" t="n">
-        <v>292.3530024013792</v>
+        <v>298.8636475324957</v>
       </c>
       <c r="E171" t="n">
-        <v>300.625732421875</v>
+        <v>301.6411437988281</v>
       </c>
       <c r="F171" t="n">
-        <v>9327000</v>
+        <v>7874400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B172" t="n">
-        <v>299.8790926087445</v>
+        <v>303.3135932887391</v>
       </c>
       <c r="C172" t="n">
-        <v>302.6167597554335</v>
+        <v>306.0711901040885</v>
       </c>
       <c r="D172" t="n">
-        <v>298.8636475324957</v>
+        <v>302.4773640852478</v>
       </c>
       <c r="E172" t="n">
-        <v>301.6411437988281</v>
+        <v>305.0059814453125</v>
       </c>
       <c r="F172" t="n">
-        <v>7874400</v>
+        <v>5973900</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B173" t="n">
-        <v>303.3135932887391</v>
+        <v>307.1065011172144</v>
       </c>
       <c r="C173" t="n">
-        <v>306.0711901040885</v>
+        <v>308.5400455607295</v>
       </c>
       <c r="D173" t="n">
-        <v>302.4773640852478</v>
+        <v>304.0701916446211</v>
       </c>
       <c r="E173" t="n">
-        <v>305.0059814453125</v>
+        <v>305.3643493652344</v>
       </c>
       <c r="F173" t="n">
-        <v>5973900</v>
+        <v>7725400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B174" t="n">
-        <v>307.1065011172144</v>
+        <v>303.6321536663258</v>
       </c>
       <c r="C174" t="n">
-        <v>308.5400455607295</v>
+        <v>304.5281113223131</v>
       </c>
       <c r="D174" t="n">
-        <v>304.0701916446211</v>
+        <v>294.4236375305438</v>
       </c>
       <c r="E174" t="n">
-        <v>305.3643493652344</v>
+        <v>297.9378051757812</v>
       </c>
       <c r="F174" t="n">
-        <v>7725400</v>
+        <v>11779200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B175" t="n">
-        <v>303.6321536663258</v>
+        <v>296.2354906683788</v>
       </c>
       <c r="C175" t="n">
-        <v>304.5281113223131</v>
+        <v>299.7197941661088</v>
       </c>
       <c r="D175" t="n">
-        <v>294.4236375305438</v>
+        <v>294.4236455581874</v>
       </c>
       <c r="E175" t="n">
-        <v>297.9378051757812</v>
+        <v>295.3992614746094</v>
       </c>
       <c r="F175" t="n">
-        <v>11779200</v>
+        <v>9757700</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B176" t="n">
-        <v>296.2354906683788</v>
+        <v>295.070728717322</v>
       </c>
       <c r="C176" t="n">
-        <v>299.7197941661088</v>
+        <v>298.5351328968941</v>
       </c>
       <c r="D176" t="n">
-        <v>294.4236455581874</v>
+        <v>293.8761285862639</v>
       </c>
       <c r="E176" t="n">
-        <v>295.3992614746094</v>
+        <v>297.9676818847656</v>
       </c>
       <c r="F176" t="n">
-        <v>9757700</v>
+        <v>13969000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B177" t="n">
-        <v>295.070728717322</v>
+        <v>296.3549462063085</v>
       </c>
       <c r="C177" t="n">
-        <v>298.5351328968941</v>
+        <v>298.2065900448191</v>
       </c>
       <c r="D177" t="n">
-        <v>293.8761285862639</v>
+        <v>293.9457858606032</v>
       </c>
       <c r="E177" t="n">
-        <v>297.9676818847656</v>
+        <v>295.2499084472656</v>
       </c>
       <c r="F177" t="n">
-        <v>13969000</v>
+        <v>7930000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B178" t="n">
-        <v>296.3549462063085</v>
+        <v>295.170270518017</v>
       </c>
       <c r="C178" t="n">
-        <v>298.2065900448191</v>
+        <v>300.7152977310929</v>
       </c>
       <c r="D178" t="n">
-        <v>293.9457858606032</v>
+        <v>293.9457758280521</v>
       </c>
       <c r="E178" t="n">
-        <v>295.2499084472656</v>
+        <v>299.6102600097656</v>
       </c>
       <c r="F178" t="n">
-        <v>7930000</v>
+        <v>8296200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B179" t="n">
-        <v>295.170270518017</v>
+        <v>298.5749714904202</v>
       </c>
       <c r="C179" t="n">
-        <v>300.7152977310929</v>
+        <v>300.6058008918799</v>
       </c>
       <c r="D179" t="n">
-        <v>293.9457758280521</v>
+        <v>295.2300241797341</v>
       </c>
       <c r="E179" t="n">
-        <v>299.6102600097656</v>
+        <v>299.5007934570312</v>
       </c>
       <c r="F179" t="n">
-        <v>8296200</v>
+        <v>7003900</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B180" t="n">
-        <v>298.5749714904202</v>
+        <v>304.3688300919619</v>
       </c>
       <c r="C180" t="n">
-        <v>300.6058008918799</v>
+        <v>311.5066879726736</v>
       </c>
       <c r="D180" t="n">
-        <v>295.2300241797341</v>
+        <v>303.0746723882986</v>
       </c>
       <c r="E180" t="n">
-        <v>299.5007934570312</v>
+        <v>309.4957580566406</v>
       </c>
       <c r="F180" t="n">
-        <v>7003900</v>
+        <v>10345200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B181" t="n">
-        <v>304.3688300919619</v>
+        <v>312.8805189963161</v>
       </c>
       <c r="C181" t="n">
-        <v>311.5066879726736</v>
+        <v>313.5873263681962</v>
       </c>
       <c r="D181" t="n">
-        <v>303.0746723882986</v>
+        <v>308.211549706599</v>
       </c>
       <c r="E181" t="n">
-        <v>309.4957580566406</v>
+        <v>310.9691162109375</v>
       </c>
       <c r="F181" t="n">
-        <v>10345200</v>
+        <v>9118800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B182" t="n">
-        <v>312.8805189963161</v>
+        <v>311.8451695343703</v>
       </c>
       <c r="C182" t="n">
-        <v>313.5873263681962</v>
+        <v>314.881479064701</v>
       </c>
       <c r="D182" t="n">
-        <v>308.211549706599</v>
+        <v>309.3862455138746</v>
       </c>
       <c r="E182" t="n">
-        <v>310.9691162109375</v>
+        <v>309.7147521972656</v>
       </c>
       <c r="F182" t="n">
-        <v>9118800</v>
+        <v>6827000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B183" t="n">
-        <v>311.8451695343703</v>
+        <v>312.1040028799189</v>
       </c>
       <c r="C183" t="n">
-        <v>314.881479064701</v>
+        <v>315.0009559692908</v>
       </c>
       <c r="D183" t="n">
-        <v>309.3862455138746</v>
+        <v>307.6241841525692</v>
       </c>
       <c r="E183" t="n">
-        <v>309.7147521972656</v>
+        <v>311.2976379394531</v>
       </c>
       <c r="F183" t="n">
-        <v>6827000</v>
+        <v>11594600</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B184" t="n">
-        <v>312.1040028799189</v>
+        <v>311.1582462393224</v>
       </c>
       <c r="C184" t="n">
-        <v>315.0009559692908</v>
+        <v>313.3384270822022</v>
       </c>
       <c r="D184" t="n">
-        <v>307.6241841525692</v>
+        <v>307.6440785979976</v>
       </c>
       <c r="E184" t="n">
-        <v>311.2976379394531</v>
+        <v>307.7536010742188</v>
       </c>
       <c r="F184" t="n">
-        <v>11594600</v>
+        <v>7446200</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B185" t="n">
-        <v>311.1582462393224</v>
+        <v>308.1717081621576</v>
       </c>
       <c r="C185" t="n">
-        <v>313.3384270822022</v>
+        <v>313.3085706612414</v>
       </c>
       <c r="D185" t="n">
-        <v>307.6440785979976</v>
+        <v>307.4947650619962</v>
       </c>
       <c r="E185" t="n">
-        <v>307.7536010742188</v>
+        <v>312.0840759277344</v>
       </c>
       <c r="F185" t="n">
-        <v>7446200</v>
+        <v>9116600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B186" t="n">
-        <v>308.1717081621576</v>
+        <v>314.5529794375797</v>
       </c>
       <c r="C186" t="n">
-        <v>313.3085706612414</v>
+        <v>319.8590627688811</v>
       </c>
       <c r="D186" t="n">
-        <v>307.4947650619962</v>
+        <v>314.1348496322589</v>
       </c>
       <c r="E186" t="n">
-        <v>312.0840759277344</v>
+        <v>319.2816772460938</v>
       </c>
       <c r="F186" t="n">
-        <v>9116600</v>
+        <v>7426200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B187" t="n">
-        <v>314.5529794375797</v>
+        <v>322.4673390673774</v>
       </c>
       <c r="C187" t="n">
-        <v>319.8590627688811</v>
+        <v>324.4583697274161</v>
       </c>
       <c r="D187" t="n">
-        <v>314.1348496322589</v>
+        <v>317.4101041776777</v>
       </c>
       <c r="E187" t="n">
-        <v>319.2816772460938</v>
+        <v>317.9675903320312</v>
       </c>
       <c r="F187" t="n">
-        <v>7426200</v>
+        <v>7988900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B188" t="n">
-        <v>322.4673390673774</v>
+        <v>322.8455866314347</v>
       </c>
       <c r="C188" t="n">
-        <v>324.4583697274161</v>
+        <v>330.2621874699331</v>
       </c>
       <c r="D188" t="n">
-        <v>317.4101041776777</v>
+        <v>322.5668435738929</v>
       </c>
       <c r="E188" t="n">
-        <v>317.9675903320312</v>
+        <v>329.6549377441406</v>
       </c>
       <c r="F188" t="n">
-        <v>7988900</v>
+        <v>11094900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B189" t="n">
-        <v>322.8455866314347</v>
+        <v>330.6902497468859</v>
       </c>
       <c r="C189" t="n">
-        <v>330.2621874699331</v>
+        <v>336.2551763704633</v>
       </c>
       <c r="D189" t="n">
-        <v>322.5668435738929</v>
+        <v>330.0133066656099</v>
       </c>
       <c r="E189" t="n">
-        <v>329.6549377441406</v>
+        <v>331.9645080566406</v>
       </c>
       <c r="F189" t="n">
-        <v>11094900</v>
+        <v>12246400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B190" t="n">
-        <v>330.6902497468859</v>
+        <v>335.4388795655989</v>
       </c>
       <c r="C190" t="n">
-        <v>336.2551763704633</v>
+        <v>336.5737511659094</v>
       </c>
       <c r="D190" t="n">
-        <v>330.0133066656099</v>
+        <v>322.7062308624821</v>
       </c>
       <c r="E190" t="n">
-        <v>331.9645080566406</v>
+        <v>323.761474609375</v>
       </c>
       <c r="F190" t="n">
-        <v>12246400</v>
+        <v>20111000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B191" t="n">
-        <v>335.4388795655989</v>
+        <v>328.221392261561</v>
       </c>
       <c r="C191" t="n">
-        <v>336.5737511659094</v>
+        <v>331.2776010100568</v>
       </c>
       <c r="D191" t="n">
-        <v>322.7062308624821</v>
+        <v>325.2846101022313</v>
       </c>
       <c r="E191" t="n">
-        <v>323.761474609375</v>
+        <v>329.993408203125</v>
       </c>
       <c r="F191" t="n">
-        <v>20111000</v>
+        <v>10182500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B192" t="n">
-        <v>328.221392261561</v>
+        <v>327.9924099173137</v>
       </c>
       <c r="C192" t="n">
-        <v>331.2776010100568</v>
+        <v>333.8659438033595</v>
       </c>
       <c r="D192" t="n">
-        <v>325.2846101022313</v>
+        <v>325.7425357353925</v>
       </c>
       <c r="E192" t="n">
-        <v>329.993408203125</v>
+        <v>332.6414794921875</v>
       </c>
       <c r="F192" t="n">
-        <v>10182500</v>
+        <v>7582200</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B193" t="n">
-        <v>327.9924099173137</v>
+        <v>331.5762891678024</v>
       </c>
       <c r="C193" t="n">
-        <v>333.8659438033595</v>
+        <v>333.0297330031709</v>
       </c>
       <c r="D193" t="n">
-        <v>325.7425357353925</v>
+        <v>328.291070440402</v>
       </c>
       <c r="E193" t="n">
-        <v>332.6414794921875</v>
+        <v>331.95458984375</v>
       </c>
       <c r="F193" t="n">
-        <v>7582200</v>
+        <v>7907400</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B194" t="n">
-        <v>331.5762891678024</v>
+        <v>333.4577793441399</v>
       </c>
       <c r="C194" t="n">
-        <v>333.0297330031709</v>
+        <v>341.909724468194</v>
       </c>
       <c r="D194" t="n">
-        <v>328.291070440402</v>
+        <v>333.2586945227413</v>
       </c>
       <c r="E194" t="n">
-        <v>331.95458984375</v>
+        <v>333.6170654296875</v>
       </c>
       <c r="F194" t="n">
-        <v>7907400</v>
+        <v>10043100</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B195" t="n">
-        <v>333.4577793441399</v>
+        <v>334.4931229022353</v>
       </c>
       <c r="C195" t="n">
-        <v>341.909724468194</v>
+        <v>334.8913229247855</v>
       </c>
       <c r="D195" t="n">
-        <v>333.2586945227413</v>
+        <v>326.0312433050061</v>
       </c>
       <c r="E195" t="n">
-        <v>333.6170654296875</v>
+        <v>327.5742797851562</v>
       </c>
       <c r="F195" t="n">
-        <v>10043100</v>
+        <v>17640900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B196" t="n">
-        <v>334.4931229022353</v>
+        <v>326.8077430430495</v>
       </c>
       <c r="C196" t="n">
-        <v>334.8913229247855</v>
+        <v>330.8993264933345</v>
       </c>
       <c r="D196" t="n">
-        <v>326.0312433050061</v>
+        <v>325.7325999471821</v>
       </c>
       <c r="E196" t="n">
-        <v>327.5742797851562</v>
+        <v>327.9127807617188</v>
       </c>
       <c r="F196" t="n">
-        <v>17640900</v>
+        <v>7981800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B197" t="n">
-        <v>326.8077430430495</v>
+        <v>327.4150312810326</v>
       </c>
       <c r="C197" t="n">
-        <v>330.8993264933345</v>
+        <v>328.9580677951163</v>
       </c>
       <c r="D197" t="n">
-        <v>325.7325999471821</v>
+        <v>325.2149206632551</v>
       </c>
       <c r="E197" t="n">
-        <v>327.9127807617188</v>
+        <v>325.8619995117188</v>
       </c>
       <c r="F197" t="n">
-        <v>7981800</v>
+        <v>8080100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B198" t="n">
-        <v>327.4150312810326</v>
+        <v>326.8973584256916</v>
       </c>
       <c r="C198" t="n">
-        <v>328.9580677951163</v>
+        <v>334.1347741939035</v>
       </c>
       <c r="D198" t="n">
-        <v>325.2149206632551</v>
+        <v>323.5524415571975</v>
       </c>
       <c r="E198" t="n">
-        <v>325.8619995117188</v>
+        <v>332.5718078613281</v>
       </c>
       <c r="F198" t="n">
-        <v>8080100</v>
+        <v>15210200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B199" t="n">
-        <v>326.8973584256916</v>
+        <v>336.5040683580973</v>
       </c>
       <c r="C199" t="n">
-        <v>334.1347741939035</v>
+        <v>338.4751995750331</v>
       </c>
       <c r="D199" t="n">
-        <v>323.5524415571975</v>
+        <v>330.2820977776739</v>
       </c>
       <c r="E199" t="n">
-        <v>332.5718078613281</v>
+        <v>332.9700012207031</v>
       </c>
       <c r="F199" t="n">
-        <v>15210200</v>
+        <v>8413900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,25 +5617,25 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B200" t="n">
-        <v>336.5040683580973</v>
+        <v>335</v>
       </c>
       <c r="C200" t="n">
-        <v>338.4751995750331</v>
+        <v>339.7200012207031</v>
       </c>
       <c r="D200" t="n">
-        <v>330.2820977776739</v>
+        <v>334.1099853515625</v>
       </c>
       <c r="E200" t="n">
-        <v>332.9700012207031</v>
+        <v>337.7200012207031</v>
       </c>
       <c r="F200" t="n">
-        <v>8413900</v>
+        <v>8673500</v>
       </c>
       <c r="G200" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -5643,25 +5643,25 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B201" t="n">
-        <v>335</v>
+        <v>340.9800109863281</v>
       </c>
       <c r="C201" t="n">
-        <v>339.7200012207031</v>
+        <v>341.3999938964844</v>
       </c>
       <c r="D201" t="n">
-        <v>334.1099853515625</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E201" t="n">
-        <v>337.7200012207031</v>
+        <v>339.2200012207031</v>
       </c>
       <c r="F201" t="n">
-        <v>8673500</v>
+        <v>7115800</v>
       </c>
       <c r="G201" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B202" t="n">
-        <v>340.9800109863281</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="C202" t="n">
-        <v>341.3999938964844</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="D202" t="n">
-        <v>337.0899963378906</v>
+        <v>330.1300048828125</v>
       </c>
       <c r="E202" t="n">
-        <v>339.2200012207031</v>
+        <v>330.6199951171875</v>
       </c>
       <c r="F202" t="n">
-        <v>7115800</v>
+        <v>18505200</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B203" t="n">
-        <v>336.5299987792969</v>
+        <v>331.4599914550781</v>
       </c>
       <c r="C203" t="n">
-        <v>336.5299987792969</v>
+        <v>337</v>
       </c>
       <c r="D203" t="n">
-        <v>330.1300048828125</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="E203" t="n">
-        <v>330.6199951171875</v>
+        <v>335.4700012207031</v>
       </c>
       <c r="F203" t="n">
-        <v>18505200</v>
+        <v>15570600</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B204" t="n">
-        <v>331.4599914550781</v>
+        <v>337.4700012207031</v>
       </c>
       <c r="C204" t="n">
-        <v>337</v>
+        <v>338.5899963378906</v>
       </c>
       <c r="D204" t="n">
-        <v>330.8099975585938</v>
+        <v>335.7699890136719</v>
       </c>
       <c r="E204" t="n">
-        <v>335.4700012207031</v>
+        <v>336.4700012207031</v>
       </c>
       <c r="F204" t="n">
-        <v>15570600</v>
+        <v>6299000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B205" t="n">
-        <v>337.4700012207031</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="C205" t="n">
-        <v>338.5899963378906</v>
+        <v>338.3500061035156</v>
       </c>
       <c r="D205" t="n">
-        <v>335.7699890136719</v>
+        <v>332.5</v>
       </c>
       <c r="E205" t="n">
-        <v>336.4700012207031</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="F205" t="n">
-        <v>6299000</v>
+        <v>7120300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B206" t="n">
-        <v>338.3399963378906</v>
+        <v>327</v>
       </c>
       <c r="C206" t="n">
-        <v>338.3500061035156</v>
+        <v>344.7300109863281</v>
       </c>
       <c r="D206" t="n">
-        <v>332.5</v>
+        <v>325.75</v>
       </c>
       <c r="E206" t="n">
-        <v>334.5299987792969</v>
+        <v>342.8900146484375</v>
       </c>
       <c r="F206" t="n">
-        <v>7120300</v>
+        <v>14537900</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B207" t="n">
-        <v>327</v>
+        <v>345.8500061035156</v>
       </c>
       <c r="C207" t="n">
-        <v>344.7300109863281</v>
+        <v>351.239990234375</v>
       </c>
       <c r="D207" t="n">
-        <v>325.75</v>
+        <v>344.0499877929688</v>
       </c>
       <c r="E207" t="n">
-        <v>342.8900146484375</v>
+        <v>346.9100036621094</v>
       </c>
       <c r="F207" t="n">
-        <v>14537900</v>
+        <v>10750000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B208" t="n">
-        <v>345.8500061035156</v>
+        <v>349.2799987792969</v>
       </c>
       <c r="C208" t="n">
-        <v>351.239990234375</v>
+        <v>349.3399963378906</v>
       </c>
       <c r="D208" t="n">
-        <v>344.0499877929688</v>
+        <v>341.1099853515625</v>
       </c>
       <c r="E208" t="n">
-        <v>346.9100036621094</v>
+        <v>343.1499938964844</v>
       </c>
       <c r="F208" t="n">
-        <v>10750000</v>
+        <v>12432400</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B209" t="n">
-        <v>349.2799987792969</v>
+        <v>339.0299987792969</v>
       </c>
       <c r="C209" t="n">
-        <v>349.3399963378906</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="D209" t="n">
-        <v>341.1099853515625</v>
+        <v>335.0499877929688</v>
       </c>
       <c r="E209" t="n">
-        <v>343.1499938964844</v>
+        <v>341.1000061035156</v>
       </c>
       <c r="F209" t="n">
-        <v>12432400</v>
+        <v>9250900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B210" t="n">
-        <v>339.0299987792969</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="C210" t="n">
-        <v>346.1300048828125</v>
+        <v>344.260009765625</v>
       </c>
       <c r="D210" t="n">
-        <v>335.0499877929688</v>
+        <v>337.3699951171875</v>
       </c>
       <c r="E210" t="n">
-        <v>341.1000061035156</v>
+        <v>338.8699951171875</v>
       </c>
       <c r="F210" t="n">
-        <v>9250900</v>
+        <v>7723300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B211" t="n">
-        <v>341.7999877929688</v>
+        <v>340.1199951171875</v>
       </c>
       <c r="C211" t="n">
-        <v>344.260009765625</v>
+        <v>345.739990234375</v>
       </c>
       <c r="D211" t="n">
-        <v>337.3699951171875</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E211" t="n">
-        <v>338.8699951171875</v>
+        <v>345.2300109863281</v>
       </c>
       <c r="F211" t="n">
-        <v>7723300</v>
+        <v>6015300</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B212" t="n">
-        <v>340.1199951171875</v>
+        <v>345.0700073242188</v>
       </c>
       <c r="C212" t="n">
-        <v>345.739990234375</v>
+        <v>349.0700073242188</v>
       </c>
       <c r="D212" t="n">
-        <v>337.2999877929688</v>
+        <v>344.25</v>
       </c>
       <c r="E212" t="n">
-        <v>345.2300109863281</v>
+        <v>348.2099914550781</v>
       </c>
       <c r="F212" t="n">
-        <v>6015300</v>
+        <v>8040200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B213" t="n">
-        <v>345.0700073242188</v>
+        <v>346.5799865722656</v>
       </c>
       <c r="C213" t="n">
-        <v>349.0700073242188</v>
+        <v>349.9200134277344</v>
       </c>
       <c r="D213" t="n">
-        <v>344.25</v>
+        <v>345.4200134277344</v>
       </c>
       <c r="E213" t="n">
-        <v>348.2099914550781</v>
+        <v>349.8999938964844</v>
       </c>
       <c r="F213" t="n">
-        <v>8040200</v>
+        <v>10913000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B214" t="n">
-        <v>346.5799865722656</v>
+        <v>350.6400146484375</v>
       </c>
       <c r="C214" t="n">
-        <v>349.9200134277344</v>
+        <v>353.3699951171875</v>
       </c>
       <c r="D214" t="n">
-        <v>345.4200134277344</v>
+        <v>347.5</v>
       </c>
       <c r="E214" t="n">
-        <v>349.8999938964844</v>
+        <v>353.2099914550781</v>
       </c>
       <c r="F214" t="n">
-        <v>10913000</v>
+        <v>7520800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B215" t="n">
-        <v>350.6400146484375</v>
+        <v>357.8900146484375</v>
       </c>
       <c r="C215" t="n">
-        <v>353.3699951171875</v>
+        <v>359.0499877929688</v>
       </c>
       <c r="D215" t="n">
-        <v>347.5</v>
+        <v>352.5799865722656</v>
       </c>
       <c r="E215" t="n">
-        <v>353.2099914550781</v>
+        <v>356.2000122070312</v>
       </c>
       <c r="F215" t="n">
-        <v>7520800</v>
+        <v>7884900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B216" t="n">
-        <v>357.8900146484375</v>
+        <v>357.2999877929688</v>
       </c>
       <c r="C216" t="n">
-        <v>359.0499877929688</v>
+        <v>359.2999877929688</v>
       </c>
       <c r="D216" t="n">
-        <v>352.5799865722656</v>
+        <v>354.1499938964844</v>
       </c>
       <c r="E216" t="n">
-        <v>356.2000122070312</v>
+        <v>357.3099975585938</v>
       </c>
       <c r="F216" t="n">
-        <v>7884900</v>
+        <v>6533800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B217" t="n">
-        <v>357.2999877929688</v>
+        <v>356.5</v>
       </c>
       <c r="C217" t="n">
-        <v>359.2999877929688</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D217" t="n">
-        <v>354.1499938964844</v>
+        <v>343.7799987792969</v>
       </c>
       <c r="E217" t="n">
-        <v>357.3099975585938</v>
+        <v>344.7099914550781</v>
       </c>
       <c r="F217" t="n">
-        <v>6533800</v>
+        <v>8265300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B218" t="n">
-        <v>356.5</v>
+        <v>347.5400085449219</v>
       </c>
       <c r="C218" t="n">
-        <v>357.3699951171875</v>
+        <v>352.2799987792969</v>
       </c>
       <c r="D218" t="n">
-        <v>343.7799987792969</v>
+        <v>345.3699951171875</v>
       </c>
       <c r="E218" t="n">
-        <v>344.7099914550781</v>
+        <v>350.8500061035156</v>
       </c>
       <c r="F218" t="n">
-        <v>8265300</v>
+        <v>7606500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B219" t="n">
-        <v>347.5400085449219</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C219" t="n">
-        <v>352.2799987792969</v>
+        <v>354.4700012207031</v>
       </c>
       <c r="D219" t="n">
-        <v>345.3699951171875</v>
+        <v>349.7000122070312</v>
       </c>
       <c r="E219" t="n">
-        <v>350.8500061035156</v>
+        <v>351.7900085449219</v>
       </c>
       <c r="F219" t="n">
-        <v>7606500</v>
+        <v>6603400</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B220" t="n">
-        <v>353.2999877929688</v>
+        <v>353.75</v>
       </c>
       <c r="C220" t="n">
-        <v>354.4700012207031</v>
+        <v>355.6199951171875</v>
       </c>
       <c r="D220" t="n">
-        <v>349.7000122070312</v>
+        <v>350.8399963378906</v>
       </c>
       <c r="E220" t="n">
-        <v>351.7900085449219</v>
+        <v>352.6400146484375</v>
       </c>
       <c r="F220" t="n">
-        <v>6603400</v>
+        <v>6436600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B221" t="n">
-        <v>353.75</v>
+        <v>355</v>
       </c>
       <c r="C221" t="n">
-        <v>355.6199951171875</v>
+        <v>363</v>
       </c>
       <c r="D221" t="n">
-        <v>350.8399963378906</v>
+        <v>353.8699951171875</v>
       </c>
       <c r="E221" t="n">
-        <v>352.6400146484375</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F221" t="n">
-        <v>6436600</v>
+        <v>8477200</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B222" t="n">
-        <v>355</v>
+        <v>358.9700012207031</v>
       </c>
       <c r="C222" t="n">
-        <v>363</v>
+        <v>362.1700134277344</v>
       </c>
       <c r="D222" t="n">
-        <v>353.8699951171875</v>
+        <v>358.2000122070312</v>
       </c>
       <c r="E222" t="n">
-        <v>357.5199890136719</v>
+        <v>359.239990234375</v>
       </c>
       <c r="F222" t="n">
-        <v>8477200</v>
+        <v>5269500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B223" t="n">
-        <v>358.9700012207031</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="C223" t="n">
-        <v>362.1700134277344</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="D223" t="n">
-        <v>358.2000122070312</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="E223" t="n">
-        <v>359.239990234375</v>
+        <v>356.2999877929688</v>
       </c>
       <c r="F223" t="n">
-        <v>5269500</v>
+        <v>5820100</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B224" t="n">
-        <v>362.8099975585938</v>
+        <v>355.760009765625</v>
       </c>
       <c r="C224" t="n">
-        <v>362.8099975585938</v>
+        <v>358.8500061035156</v>
       </c>
       <c r="D224" t="n">
-        <v>354.9500122070312</v>
+        <v>353.3299865722656</v>
       </c>
       <c r="E224" t="n">
-        <v>356.2999877929688</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F224" t="n">
-        <v>5820100</v>
+        <v>4566200</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B225" t="n">
-        <v>355.760009765625</v>
+        <v>357.9599914550781</v>
       </c>
       <c r="C225" t="n">
-        <v>358.8500061035156</v>
+        <v>359.989990234375</v>
       </c>
       <c r="D225" t="n">
-        <v>353.3299865722656</v>
+        <v>356.5</v>
       </c>
       <c r="E225" t="n">
-        <v>357.5199890136719</v>
+        <v>359.7900085449219</v>
       </c>
       <c r="F225" t="n">
-        <v>4566200</v>
+        <v>5327500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B226" t="n">
-        <v>357.9599914550781</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="C226" t="n">
-        <v>359.989990234375</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="D226" t="n">
-        <v>356.5</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="E226" t="n">
-        <v>359.7900085449219</v>
+        <v>362.0400085449219</v>
       </c>
       <c r="F226" t="n">
-        <v>5327500</v>
+        <v>4576500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B227" t="n">
-        <v>360.0499877929688</v>
+        <v>362.9700012207031</v>
       </c>
       <c r="C227" t="n">
-        <v>363.1199951171875</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="D227" t="n">
-        <v>358.6000061035156</v>
+        <v>361.2999877929688</v>
       </c>
       <c r="E227" t="n">
-        <v>362.0400085449219</v>
+        <v>365.1799926757812</v>
       </c>
       <c r="F227" t="n">
-        <v>4576500</v>
+        <v>4366800</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B228" t="n">
-        <v>362.9700012207031</v>
+        <v>366.5</v>
       </c>
       <c r="C228" t="n">
-        <v>366.0899963378906</v>
+        <v>366.5</v>
       </c>
       <c r="D228" t="n">
-        <v>361.2999877929688</v>
+        <v>361.5199890136719</v>
       </c>
       <c r="E228" t="n">
-        <v>365.1799926757812</v>
+        <v>363.1099853515625</v>
       </c>
       <c r="F228" t="n">
-        <v>4366800</v>
+        <v>5102700</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B229" t="n">
-        <v>366.5</v>
+        <v>363</v>
       </c>
       <c r="C229" t="n">
-        <v>366.5</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="D229" t="n">
-        <v>361.5199890136719</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="E229" t="n">
-        <v>363.1099853515625</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="F229" t="n">
-        <v>5102700</v>
+        <v>5058600</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B230" t="n">
-        <v>363</v>
+        <v>361.9400024414062</v>
       </c>
       <c r="C230" t="n">
-        <v>365.8999938964844</v>
+        <v>365.75</v>
       </c>
       <c r="D230" t="n">
-        <v>361.4500122070312</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="E230" t="n">
-        <v>362.8399963378906</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="F230" t="n">
-        <v>5058600</v>
+        <v>5282600</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B231" t="n">
-        <v>361.9400024414062</v>
+        <v>362.3399963378906</v>
       </c>
       <c r="C231" t="n">
-        <v>365.75</v>
+        <v>363.5700073242188</v>
       </c>
       <c r="D231" t="n">
-        <v>360.9599914550781</v>
+        <v>359.2699890136719</v>
       </c>
       <c r="E231" t="n">
-        <v>360.9599914550781</v>
+        <v>363.25</v>
       </c>
       <c r="F231" t="n">
-        <v>5282600</v>
+        <v>5525100</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B232" t="n">
-        <v>362.3399963378906</v>
+        <v>363.010009765625</v>
       </c>
       <c r="C232" t="n">
-        <v>363.5700073242188</v>
+        <v>363.0499877929688</v>
       </c>
       <c r="D232" t="n">
-        <v>359.2699890136719</v>
+        <v>355.6499938964844</v>
       </c>
       <c r="E232" t="n">
-        <v>363.25</v>
+        <v>357.260009765625</v>
       </c>
       <c r="F232" t="n">
-        <v>5525100</v>
+        <v>6696200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B233" t="n">
-        <v>363.010009765625</v>
+        <v>357.6000061035156</v>
       </c>
       <c r="C233" t="n">
-        <v>363.0499877929688</v>
+        <v>357.9500122070312</v>
       </c>
       <c r="D233" t="n">
-        <v>355.6499938964844</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E233" t="n">
-        <v>357.260009765625</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="F233" t="n">
-        <v>6696200</v>
+        <v>6799700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B234" t="n">
-        <v>357.6000061035156</v>
+        <v>354.0700073242188</v>
       </c>
       <c r="C234" t="n">
-        <v>357.9500122070312</v>
+        <v>356.8599853515625</v>
       </c>
       <c r="D234" t="n">
-        <v>351.5499877929688</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="E234" t="n">
-        <v>351.5499877929688</v>
+        <v>351.5799865722656</v>
       </c>
       <c r="F234" t="n">
-        <v>6799700</v>
+        <v>8112100</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B235" t="n">
-        <v>354.0700073242188</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C235" t="n">
-        <v>356.8599853515625</v>
+        <v>358.2799987792969</v>
       </c>
       <c r="D235" t="n">
-        <v>350.3699951171875</v>
+        <v>352.8200073242188</v>
       </c>
       <c r="E235" t="n">
-        <v>351.5799865722656</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="F235" t="n">
-        <v>8112100</v>
+        <v>4394400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B236" t="n">
-        <v>353.2999877929688</v>
+        <v>357</v>
       </c>
       <c r="C236" t="n">
-        <v>358.2799987792969</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D236" t="n">
-        <v>352.8200073242188</v>
+        <v>353.0700073242188</v>
       </c>
       <c r="E236" t="n">
-        <v>356.3900146484375</v>
+        <v>356.6900024414062</v>
       </c>
       <c r="F236" t="n">
-        <v>4394400</v>
+        <v>4298000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B237" t="n">
-        <v>357</v>
+        <v>356.5</v>
       </c>
       <c r="C237" t="n">
-        <v>357.3699951171875</v>
+        <v>358.3500061035156</v>
       </c>
       <c r="D237" t="n">
-        <v>353.0700073242188</v>
+        <v>354.6000061035156</v>
       </c>
       <c r="E237" t="n">
-        <v>356.6900024414062</v>
+        <v>356.5</v>
       </c>
       <c r="F237" t="n">
-        <v>4298000</v>
+        <v>5796500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B238" t="n">
-        <v>356.5</v>
+        <v>354.6799926757812</v>
       </c>
       <c r="C238" t="n">
-        <v>358.3500061035156</v>
+        <v>357.5700073242188</v>
       </c>
       <c r="D238" t="n">
-        <v>354.6000061035156</v>
+        <v>352.2300109863281</v>
       </c>
       <c r="E238" t="n">
-        <v>356.5</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="F238" t="n">
-        <v>5796500</v>
+        <v>5209900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B239" t="n">
-        <v>354.6799926757812</v>
+        <v>355.6700134277344</v>
       </c>
       <c r="C239" t="n">
-        <v>357.5700073242188</v>
+        <v>358.7300109863281</v>
       </c>
       <c r="D239" t="n">
-        <v>352.2300109863281</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="E239" t="n">
-        <v>354.2200012207031</v>
+        <v>357.6199951171875</v>
       </c>
       <c r="F239" t="n">
-        <v>5209900</v>
+        <v>3914500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B240" t="n">
-        <v>355.6700134277344</v>
+        <v>355.8999938964844</v>
       </c>
       <c r="C240" t="n">
-        <v>358.7300109863281</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="D240" t="n">
-        <v>354.2200012207031</v>
+        <v>354.7699890136719</v>
       </c>
       <c r="E240" t="n">
-        <v>357.6199951171875</v>
+        <v>356.0199890136719</v>
       </c>
       <c r="F240" t="n">
-        <v>3914500</v>
+        <v>7962900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B241" t="n">
-        <v>355.8999938964844</v>
+        <v>355.7300109863281</v>
       </c>
       <c r="C241" t="n">
-        <v>357.7699890136719</v>
+        <v>359.9299926757812</v>
       </c>
       <c r="D241" t="n">
-        <v>354.7699890136719</v>
+        <v>354.1199951171875</v>
       </c>
       <c r="E241" t="n">
-        <v>356.0199890136719</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="F241" t="n">
-        <v>7962900</v>
+        <v>5079000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B242" t="n">
-        <v>355.7300109863281</v>
+        <v>357.5499877929688</v>
       </c>
       <c r="C242" t="n">
-        <v>359.9299926757812</v>
+        <v>361.4700012207031</v>
       </c>
       <c r="D242" t="n">
-        <v>354.1199951171875</v>
+        <v>353.7900085449219</v>
       </c>
       <c r="E242" t="n">
-        <v>354.9500122070312</v>
+        <v>356.2200012207031</v>
       </c>
       <c r="F242" t="n">
-        <v>5079000</v>
+        <v>5341400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B243" t="n">
-        <v>357.5499877929688</v>
+        <v>358.6799926757812</v>
       </c>
       <c r="C243" t="n">
-        <v>361.4700012207031</v>
+        <v>362.8500061035156</v>
       </c>
       <c r="D243" t="n">
-        <v>353.7900085449219</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="E243" t="n">
-        <v>356.2200012207031</v>
+        <v>362.0599975585938</v>
       </c>
       <c r="F243" t="n">
-        <v>5341400</v>
+        <v>5414200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B244" t="n">
-        <v>358.6799926757812</v>
+        <v>361</v>
       </c>
       <c r="C244" t="n">
-        <v>362.8500061035156</v>
+        <v>362.8599853515625</v>
       </c>
       <c r="D244" t="n">
-        <v>356.3900146484375</v>
+        <v>355.2000122070312</v>
       </c>
       <c r="E244" t="n">
-        <v>362.0599975585938</v>
+        <v>358.6400146484375</v>
       </c>
       <c r="F244" t="n">
-        <v>5414200</v>
+        <v>4873500</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B245" t="n">
-        <v>361</v>
+        <v>357.1000061035156</v>
       </c>
       <c r="C245" t="n">
-        <v>362.8599853515625</v>
+        <v>358.5499877929688</v>
       </c>
       <c r="D245" t="n">
-        <v>355.2000122070312</v>
+        <v>353.2300109863281</v>
       </c>
       <c r="E245" t="n">
-        <v>358.6400146484375</v>
+        <v>353.510009765625</v>
       </c>
       <c r="F245" t="n">
-        <v>4873500</v>
+        <v>5631400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B246" t="n">
-        <v>357.1000061035156</v>
+        <v>352</v>
       </c>
       <c r="C246" t="n">
-        <v>358.5499877929688</v>
+        <v>356.3299865722656</v>
       </c>
       <c r="D246" t="n">
-        <v>353.2300109863281</v>
+        <v>348.6900024414062</v>
       </c>
       <c r="E246" t="n">
-        <v>353.510009765625</v>
+        <v>354.7099914550781</v>
       </c>
       <c r="F246" t="n">
-        <v>5631400</v>
+        <v>6318200</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B247" t="n">
-        <v>352</v>
+        <v>353.510009765625</v>
       </c>
       <c r="C247" t="n">
-        <v>356.3299865722656</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="D247" t="n">
-        <v>348.6900024414062</v>
+        <v>351.1199951171875</v>
       </c>
       <c r="E247" t="n">
-        <v>354.7099914550781</v>
+        <v>353.5599975585938</v>
       </c>
       <c r="F247" t="n">
-        <v>6318200</v>
+        <v>4184200</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B248" t="n">
-        <v>353.510009765625</v>
+        <v>358.3200073242188</v>
       </c>
       <c r="C248" t="n">
-        <v>354.2200012207031</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="D248" t="n">
-        <v>351.1199951171875</v>
+        <v>354.7900085449219</v>
       </c>
       <c r="E248" t="n">
-        <v>353.5599975585938</v>
+        <v>356.2300109863281</v>
       </c>
       <c r="F248" t="n">
-        <v>4184200</v>
+        <v>5354600</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B249" t="n">
-        <v>358.3200073242188</v>
+        <v>354.2300109863281</v>
       </c>
       <c r="C249" t="n">
-        <v>360.0499877929688</v>
+        <v>355.2799987792969</v>
       </c>
       <c r="D249" t="n">
-        <v>354.7900085449219</v>
+        <v>347.5499877929688</v>
       </c>
       <c r="E249" t="n">
-        <v>356.2300109863281</v>
+        <v>350.1300048828125</v>
       </c>
       <c r="F249" t="n">
-        <v>5354600</v>
+        <v>9609900</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B250" t="n">
-        <v>354.2300109863281</v>
+        <v>351</v>
       </c>
       <c r="C250" t="n">
-        <v>355.2799987792969</v>
+        <v>354.7000122070312</v>
       </c>
       <c r="D250" t="n">
-        <v>347.5499877929688</v>
+        <v>343.0700073242188</v>
       </c>
       <c r="E250" t="n">
-        <v>350.1300048828125</v>
+        <v>352.489990234375</v>
       </c>
       <c r="F250" t="n">
-        <v>9609900</v>
+        <v>14026500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B251" t="n">
-        <v>351</v>
+        <v>353.3800048828125</v>
       </c>
       <c r="C251" t="n">
-        <v>354.7000122070312</v>
+        <v>355.6000061035156</v>
       </c>
       <c r="D251" t="n">
-        <v>343.0700073242188</v>
+        <v>344.6900024414062</v>
       </c>
       <c r="E251" t="n">
-        <v>352.489990234375</v>
+        <v>348.9200134277344</v>
       </c>
       <c r="F251" t="n">
-        <v>14026500</v>
+        <v>8303400</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46282</v>
+      </c>
+      <c r="B252" t="n">
+        <v>352.25</v>
+      </c>
+      <c r="C252" t="n">
+        <v>353.489990234375</v>
+      </c>
+      <c r="D252" t="n">
+        <v>345.2699890136719</v>
+      </c>
+      <c r="E252" t="n">
+        <v>349.3099975585938</v>
+      </c>
       <c r="F252" t="n">
-        <v>8303359</v>
+        <v>6480100</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10009,37 +10017,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>349.31</v>
+      </c>
+      <c r="D2" t="n">
         <v>348.92</v>
       </c>
-      <c r="D2" t="n">
-        <v>352.49</v>
-      </c>
       <c r="E2" t="n">
-        <v>353.38</v>
+        <v>352.245</v>
       </c>
       <c r="F2" t="n">
-        <v>355.6</v>
+        <v>353.49</v>
       </c>
       <c r="G2" t="n">
-        <v>344.685</v>
+        <v>345.28</v>
       </c>
       <c r="H2" t="n">
-        <v>8303359</v>
+        <v>6461018</v>
       </c>
       <c r="I2" t="n">
-        <v>8025614</v>
+        <v>7762854</v>
       </c>
       <c r="J2" t="n">
-        <v>927494373376</v>
+        <v>928531021824</v>
       </c>
       <c r="K2" t="n">
-        <v>15.104762</v>
+        <v>14.946939</v>
       </c>
       <c r="L2" t="n">
-        <v>13.963509</v>
+        <v>13.9791155</v>
       </c>
       <c r="M2" t="n">
-        <v>23.1</v>
+        <v>23.37</v>
       </c>
       <c r="N2" t="n">
         <v>366.5</v>
@@ -10051,7 +10059,7 @@
         <v>0.975</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
         <v>0.34921002</v>
@@ -10079,7 +10087,7 @@
         <v>133.007</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.6233206</v>
+        <v>2.6262527</v>
       </c>
       <c r="Z2" t="n">
         <v>0.469</v>
@@ -10091,7 +10099,7 @@
         <v>186328006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>765422338048</v>
+        <v>766459052032</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -10120,7 +10128,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-17 08:10:00</t>
+          <t>2026-09-18 13:15:38</t>
         </is>
       </c>
     </row>

--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B2" t="n">
-        <v>305.9371875093393</v>
+        <v>307.7132209495945</v>
       </c>
       <c r="C2" t="n">
-        <v>307.5562082549167</v>
+        <v>309.8719053836384</v>
       </c>
       <c r="D2" t="n">
-        <v>303.7980870051439</v>
+        <v>303.3173070986313</v>
       </c>
       <c r="E2" t="n">
-        <v>307.3501586914062</v>
+        <v>308.8710632324219</v>
       </c>
       <c r="F2" t="n">
-        <v>8050700</v>
+        <v>23568600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B3" t="n">
-        <v>307.7131905464154</v>
+        <v>303.9845245259009</v>
       </c>
       <c r="C3" t="n">
-        <v>309.8718747671735</v>
+        <v>307.8113389670314</v>
       </c>
       <c r="D3" t="n">
-        <v>303.3172771297843</v>
+        <v>303.7490393091097</v>
       </c>
       <c r="E3" t="n">
-        <v>308.8710327148438</v>
+        <v>306.5749816894531</v>
       </c>
       <c r="F3" t="n">
-        <v>23568600</v>
+        <v>7520200</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B4" t="n">
-        <v>303.9845245259009</v>
+        <v>305.9666409066948</v>
       </c>
       <c r="C4" t="n">
-        <v>307.8113389670314</v>
+        <v>310.3723467544506</v>
       </c>
       <c r="D4" t="n">
-        <v>303.7490393091097</v>
+        <v>304.7498973520222</v>
       </c>
       <c r="E4" t="n">
-        <v>306.5749816894531</v>
+        <v>306.8693542480469</v>
       </c>
       <c r="F4" t="n">
-        <v>7520200</v>
+        <v>8584400</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B5" t="n">
-        <v>305.9666104788898</v>
+        <v>308.1547392588795</v>
       </c>
       <c r="C5" t="n">
-        <v>310.3723158885065</v>
+        <v>310.6372456892681</v>
       </c>
       <c r="D5" t="n">
-        <v>304.7498670452201</v>
+        <v>305.8194410309901</v>
       </c>
       <c r="E5" t="n">
-        <v>306.8693237304688</v>
+        <v>307.5365905761719</v>
       </c>
       <c r="F5" t="n">
-        <v>8584400</v>
+        <v>7310500</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B6" t="n">
-        <v>308.1547392588795</v>
+        <v>308.2234462682717</v>
       </c>
       <c r="C6" t="n">
-        <v>310.6372456892681</v>
+        <v>309.7247244545431</v>
       </c>
       <c r="D6" t="n">
-        <v>305.8194410309901</v>
+        <v>305.9469892965607</v>
       </c>
       <c r="E6" t="n">
-        <v>307.5365905761719</v>
+        <v>307.5660400390625</v>
       </c>
       <c r="F6" t="n">
-        <v>7310500</v>
+        <v>7083200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B7" t="n">
-        <v>308.2234462682717</v>
+        <v>308.9888161441515</v>
       </c>
       <c r="C7" t="n">
-        <v>309.7247244545431</v>
+        <v>311.8441943720275</v>
       </c>
       <c r="D7" t="n">
-        <v>305.9469892965607</v>
+        <v>307.8113600348933</v>
       </c>
       <c r="E7" t="n">
-        <v>307.5660400390625</v>
+        <v>310.1270446777344</v>
       </c>
       <c r="F7" t="n">
-        <v>7083200</v>
+        <v>7258100</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B8" t="n">
-        <v>308.9888161441515</v>
+        <v>311.1082857354447</v>
       </c>
       <c r="C8" t="n">
-        <v>311.8441943720275</v>
+        <v>312.0404647281687</v>
       </c>
       <c r="D8" t="n">
-        <v>307.8113600348933</v>
+        <v>307.7721150397051</v>
       </c>
       <c r="E8" t="n">
-        <v>310.1270446777344</v>
+        <v>309.7640075683594</v>
       </c>
       <c r="F8" t="n">
-        <v>7258100</v>
+        <v>6462400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B9" t="n">
-        <v>311.1082550854298</v>
+        <v>310.3134645283819</v>
       </c>
       <c r="C9" t="n">
-        <v>312.0404339863167</v>
+        <v>311.4516930034957</v>
       </c>
       <c r="D9" t="n">
-        <v>307.7720847183659</v>
+        <v>304.288708108424</v>
       </c>
       <c r="E9" t="n">
-        <v>309.7639770507812</v>
+        <v>309.5088500976562</v>
       </c>
       <c r="F9" t="n">
-        <v>6462400</v>
+        <v>11823300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B10" t="n">
-        <v>310.3134645283819</v>
+        <v>308.0762861336198</v>
       </c>
       <c r="C10" t="n">
-        <v>311.4516930034957</v>
+        <v>308.6846429587351</v>
       </c>
       <c r="D10" t="n">
-        <v>304.288708108424</v>
+        <v>301.6394301376976</v>
       </c>
       <c r="E10" t="n">
-        <v>309.5088500976562</v>
+        <v>304.8774719238281</v>
       </c>
       <c r="F10" t="n">
-        <v>11823300</v>
+        <v>9235200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B11" t="n">
-        <v>308.0762861336198</v>
+        <v>304.1808160870063</v>
       </c>
       <c r="C11" t="n">
-        <v>308.6846429587351</v>
+        <v>304.7303016172636</v>
       </c>
       <c r="D11" t="n">
-        <v>301.6394301376976</v>
+        <v>300.393288685967</v>
       </c>
       <c r="E11" t="n">
-        <v>304.8774719238281</v>
+        <v>301.7767944335938</v>
       </c>
       <c r="F11" t="n">
-        <v>9235200</v>
+        <v>7600000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B12" t="n">
-        <v>304.1807853263183</v>
+        <v>302.718779227698</v>
       </c>
       <c r="C12" t="n">
-        <v>304.7302708010082</v>
+        <v>305.8096426575195</v>
       </c>
       <c r="D12" t="n">
-        <v>300.3932583082978</v>
+        <v>302.4243927447969</v>
       </c>
       <c r="E12" t="n">
-        <v>301.7767639160156</v>
+        <v>304.2102355957031</v>
       </c>
       <c r="F12" t="n">
-        <v>7600000</v>
+        <v>6029900</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,25 +755,25 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B13" t="n">
-        <v>302.718779227698</v>
+        <v>305.8371035459471</v>
       </c>
       <c r="C13" t="n">
-        <v>305.8096426575195</v>
+        <v>307.3851288987199</v>
       </c>
       <c r="D13" t="n">
-        <v>302.4243927447969</v>
+        <v>300.8578215934895</v>
       </c>
       <c r="E13" t="n">
-        <v>304.2102355957031</v>
+        <v>304.8511047363281</v>
       </c>
       <c r="F13" t="n">
-        <v>6029900</v>
+        <v>7214500</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -781,25 +781,25 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B14" t="n">
-        <v>305.8371035459471</v>
+        <v>305.0187502270194</v>
       </c>
       <c r="C14" t="n">
-        <v>307.3851288987199</v>
+        <v>305.6695130787729</v>
       </c>
       <c r="D14" t="n">
-        <v>300.8578215934895</v>
+        <v>300.4338615931582</v>
       </c>
       <c r="E14" t="n">
-        <v>304.8511047363281</v>
+        <v>303.3819885253906</v>
       </c>
       <c r="F14" t="n">
-        <v>7214500</v>
+        <v>8454200</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B15" t="n">
-        <v>305.0187502270194</v>
+        <v>303.8946917756213</v>
       </c>
       <c r="C15" t="n">
-        <v>305.6695130787729</v>
+        <v>304.4567183318842</v>
       </c>
       <c r="D15" t="n">
-        <v>300.4338615931582</v>
+        <v>299.2999336047902</v>
       </c>
       <c r="E15" t="n">
-        <v>303.3819885253906</v>
+        <v>299.7732238769531</v>
       </c>
       <c r="F15" t="n">
-        <v>8454200</v>
+        <v>6489900</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B16" t="n">
-        <v>303.8946917756213</v>
+        <v>300.7789679717848</v>
       </c>
       <c r="C16" t="n">
-        <v>304.4567183318842</v>
+        <v>303.7271252967313</v>
       </c>
       <c r="D16" t="n">
-        <v>299.2999336047902</v>
+        <v>299.1422361925597</v>
       </c>
       <c r="E16" t="n">
-        <v>299.7732238769531</v>
+        <v>301.2522583007812</v>
       </c>
       <c r="F16" t="n">
-        <v>6489900</v>
+        <v>7060300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B17" t="n">
-        <v>300.7789375021521</v>
+        <v>301.3804193716138</v>
       </c>
       <c r="C17" t="n">
-        <v>303.7270945284432</v>
+        <v>306.1230715472904</v>
       </c>
       <c r="D17" t="n">
-        <v>299.1422058887319</v>
+        <v>296.5983188157025</v>
       </c>
       <c r="E17" t="n">
-        <v>301.2522277832031</v>
+        <v>296.6772155761719</v>
       </c>
       <c r="F17" t="n">
-        <v>7060300</v>
+        <v>8597400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B18" t="n">
-        <v>301.380450372985</v>
+        <v>301.321238204041</v>
       </c>
       <c r="C18" t="n">
-        <v>306.1231030365125</v>
+        <v>305.1271791148808</v>
       </c>
       <c r="D18" t="n">
-        <v>296.5983493251649</v>
+        <v>301.173344402637</v>
       </c>
       <c r="E18" t="n">
-        <v>296.67724609375</v>
+        <v>303.6580505371094</v>
       </c>
       <c r="F18" t="n">
-        <v>8597400</v>
+        <v>10788700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B19" t="n">
-        <v>301.3212684867699</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C19" t="n">
-        <v>305.1272097801061</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D19" t="n">
-        <v>301.1733746705027</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E19" t="n">
-        <v>303.6580810546875</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F19" t="n">
-        <v>10788700</v>
+        <v>16178800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B20" t="n">
-        <v>301.5578902761218</v>
+        <v>302.1001843350741</v>
       </c>
       <c r="C20" t="n">
-        <v>302.7016525742085</v>
+        <v>307.7499381556482</v>
       </c>
       <c r="D20" t="n">
-        <v>290.0907186231138</v>
+        <v>301.1634734465224</v>
       </c>
       <c r="E20" t="n">
-        <v>297.8505249023438</v>
+        <v>301.4099731445312</v>
       </c>
       <c r="F20" t="n">
-        <v>16178800</v>
+        <v>11354800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B21" t="n">
-        <v>302.1001843350741</v>
+        <v>301.0747572360179</v>
       </c>
       <c r="C21" t="n">
-        <v>307.7499381556482</v>
+        <v>304.3581201926382</v>
       </c>
       <c r="D21" t="n">
-        <v>301.1634734465224</v>
+        <v>292.9106878973514</v>
       </c>
       <c r="E21" t="n">
-        <v>301.4099731445312</v>
+        <v>294.360107421875</v>
       </c>
       <c r="F21" t="n">
-        <v>11354800</v>
+        <v>10549400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B22" t="n">
-        <v>301.0747572360179</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C22" t="n">
-        <v>304.3581201926382</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D22" t="n">
-        <v>292.9106878973514</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E22" t="n">
-        <v>294.360107421875</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F22" t="n">
-        <v>10549400</v>
+        <v>10153500</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B23" t="n">
-        <v>294.9714335987563</v>
+        <v>294.3206760639065</v>
       </c>
       <c r="C23" t="n">
-        <v>295.3559575215809</v>
+        <v>299.4380128388747</v>
       </c>
       <c r="D23" t="n">
-        <v>290.0808874955599</v>
+        <v>293.9854400437148</v>
       </c>
       <c r="E23" t="n">
-        <v>293.3938293457031</v>
+        <v>298.1266174316406</v>
       </c>
       <c r="F23" t="n">
-        <v>10153500</v>
+        <v>6894900</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B24" t="n">
-        <v>294.3206459359216</v>
+        <v>297.436411288458</v>
       </c>
       <c r="C24" t="n">
-        <v>299.4379821870563</v>
+        <v>299.7929328501146</v>
       </c>
       <c r="D24" t="n">
-        <v>293.9854099500461</v>
+        <v>292.8416531202475</v>
       </c>
       <c r="E24" t="n">
-        <v>298.1265869140625</v>
+        <v>292.9303894042969</v>
       </c>
       <c r="F24" t="n">
-        <v>6894900</v>
+        <v>7372700</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B25" t="n">
-        <v>297.436411288458</v>
+        <v>293.6008552074487</v>
       </c>
       <c r="C25" t="n">
-        <v>299.7929328501146</v>
+        <v>293.8868032880077</v>
       </c>
       <c r="D25" t="n">
-        <v>292.8416531202475</v>
+        <v>286.4721030595595</v>
       </c>
       <c r="E25" t="n">
-        <v>292.9303894042969</v>
+        <v>289.9920959472656</v>
       </c>
       <c r="F25" t="n">
-        <v>7372700</v>
+        <v>8054100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B26" t="n">
-        <v>293.6008861047978</v>
+        <v>290.2583437522712</v>
       </c>
       <c r="C26" t="n">
-        <v>293.8868342154489</v>
+        <v>292.2204718178062</v>
       </c>
       <c r="D26" t="n">
-        <v>286.4721332067081</v>
+        <v>288.4145307332595</v>
       </c>
       <c r="E26" t="n">
-        <v>289.9921264648438</v>
+        <v>290.4161071777344</v>
       </c>
       <c r="F26" t="n">
-        <v>8054100</v>
+        <v>5438800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B27" t="n">
-        <v>290.2583437522712</v>
+        <v>291.9345194575729</v>
       </c>
       <c r="C27" t="n">
-        <v>292.2204718178062</v>
+        <v>298.3632510673837</v>
       </c>
       <c r="D27" t="n">
-        <v>288.4145307332595</v>
+        <v>291.3133654724136</v>
       </c>
       <c r="E27" t="n">
-        <v>290.4161071777344</v>
+        <v>296.2334899902344</v>
       </c>
       <c r="F27" t="n">
-        <v>5438800</v>
+        <v>7228300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B28" t="n">
-        <v>291.9345194575729</v>
+        <v>297.9294427867379</v>
       </c>
       <c r="C28" t="n">
-        <v>298.3632510673837</v>
+        <v>300.2662554558976</v>
       </c>
       <c r="D28" t="n">
-        <v>291.3133654724136</v>
+        <v>296.7955500258321</v>
       </c>
       <c r="E28" t="n">
-        <v>296.2334899902344</v>
+        <v>299.8915710449219</v>
       </c>
       <c r="F28" t="n">
-        <v>7228300</v>
+        <v>5642200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B29" t="n">
-        <v>297.9294427867379</v>
+        <v>300.5915953010157</v>
       </c>
       <c r="C29" t="n">
-        <v>300.2662554558976</v>
+        <v>303.6580673748709</v>
       </c>
       <c r="D29" t="n">
-        <v>296.7955500258321</v>
+        <v>298.915415308335</v>
       </c>
       <c r="E29" t="n">
-        <v>299.8915710449219</v>
+        <v>301.0845947265625</v>
       </c>
       <c r="F29" t="n">
-        <v>5642200</v>
+        <v>6336000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B30" t="n">
-        <v>300.5915953010157</v>
+        <v>299.2605157595805</v>
       </c>
       <c r="C30" t="n">
-        <v>303.6580673748709</v>
+        <v>303.9341406042103</v>
       </c>
       <c r="D30" t="n">
-        <v>298.915415308335</v>
+        <v>298.7675163425421</v>
       </c>
       <c r="E30" t="n">
-        <v>301.0845947265625</v>
+        <v>301.2325134277344</v>
       </c>
       <c r="F30" t="n">
-        <v>6336000</v>
+        <v>7520300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B31" t="n">
-        <v>299.2605157595805</v>
+        <v>301.5085931686638</v>
       </c>
       <c r="C31" t="n">
-        <v>303.9341406042103</v>
+        <v>308.2330823767899</v>
       </c>
       <c r="D31" t="n">
-        <v>298.7675163425421</v>
+        <v>300.828251563059</v>
       </c>
       <c r="E31" t="n">
-        <v>301.2325134277344</v>
+        <v>305.1074829101562</v>
       </c>
       <c r="F31" t="n">
-        <v>7520300</v>
+        <v>7514600</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B32" t="n">
-        <v>301.5085931686638</v>
+        <v>304.2200828300273</v>
       </c>
       <c r="C32" t="n">
-        <v>308.2330823767899</v>
+        <v>308.4894444595929</v>
       </c>
       <c r="D32" t="n">
-        <v>300.828251563059</v>
+        <v>302.9481359332913</v>
       </c>
       <c r="E32" t="n">
-        <v>305.1074829101562</v>
+        <v>306.7639465332031</v>
       </c>
       <c r="F32" t="n">
-        <v>7514600</v>
+        <v>7721300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B33" t="n">
-        <v>304.2200828300273</v>
+        <v>306.6456298108837</v>
       </c>
       <c r="C33" t="n">
-        <v>308.4894444595929</v>
+        <v>307.947155461334</v>
       </c>
       <c r="D33" t="n">
-        <v>302.9481359332913</v>
+        <v>301.9226870872275</v>
       </c>
       <c r="E33" t="n">
-        <v>306.7639465332031</v>
+        <v>305.0187377929688</v>
       </c>
       <c r="F33" t="n">
-        <v>7721300</v>
+        <v>7770000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B34" t="n">
-        <v>306.6456298108837</v>
+        <v>302.415720333495</v>
       </c>
       <c r="C34" t="n">
-        <v>307.947155461334</v>
+        <v>307.8485840116909</v>
       </c>
       <c r="D34" t="n">
-        <v>301.9226870872275</v>
+        <v>300.8282765156093</v>
       </c>
       <c r="E34" t="n">
-        <v>305.0187377929688</v>
+        <v>304.920166015625</v>
       </c>
       <c r="F34" t="n">
-        <v>7770000</v>
+        <v>7085200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B35" t="n">
-        <v>302.4156900665715</v>
+        <v>305.2751066360906</v>
       </c>
       <c r="C35" t="n">
-        <v>307.8485532010255</v>
+        <v>308.7162632770978</v>
       </c>
       <c r="D35" t="n">
-        <v>300.8282464075632</v>
+        <v>301.3508502506656</v>
       </c>
       <c r="E35" t="n">
-        <v>304.9201354980469</v>
+        <v>307.3161315917969</v>
       </c>
       <c r="F35" t="n">
-        <v>7085200</v>
+        <v>6865200</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B36" t="n">
-        <v>305.2750763211935</v>
+        <v>306.6357687557767</v>
       </c>
       <c r="C36" t="n">
-        <v>308.7162326204817</v>
+        <v>310.4318702971036</v>
       </c>
       <c r="D36" t="n">
-        <v>301.350820325461</v>
+        <v>305.9160088624015</v>
       </c>
       <c r="E36" t="n">
-        <v>307.3161010742188</v>
+        <v>309.0317687988281</v>
       </c>
       <c r="F36" t="n">
-        <v>6865200</v>
+        <v>7206100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B37" t="n">
-        <v>306.6357687557767</v>
+        <v>307.5231746391179</v>
       </c>
       <c r="C37" t="n">
-        <v>310.4318702971036</v>
+        <v>310.0275898810191</v>
       </c>
       <c r="D37" t="n">
-        <v>305.9160088624015</v>
+        <v>303.3326798145578</v>
       </c>
       <c r="E37" t="n">
-        <v>309.0317687988281</v>
+        <v>309.8106689453125</v>
       </c>
       <c r="F37" t="n">
-        <v>7206100</v>
+        <v>7302300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B38" t="n">
-        <v>307.5231746391179</v>
+        <v>310.5896034535161</v>
       </c>
       <c r="C38" t="n">
-        <v>310.0275898810191</v>
+        <v>315.0857553058102</v>
       </c>
       <c r="D38" t="n">
-        <v>303.3326798145578</v>
+        <v>309.8106560227473</v>
       </c>
       <c r="E38" t="n">
-        <v>309.8106689453125</v>
+        <v>312.4531555175781</v>
       </c>
       <c r="F38" t="n">
-        <v>7302300</v>
+        <v>5794100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B39" t="n">
-        <v>310.5896337890794</v>
+        <v>313.054640940315</v>
       </c>
       <c r="C39" t="n">
-        <v>315.0857860805166</v>
+        <v>314.5829271513063</v>
       </c>
       <c r="D39" t="n">
-        <v>309.8106862822301</v>
+        <v>310.8657222472937</v>
       </c>
       <c r="E39" t="n">
-        <v>312.4531860351562</v>
+        <v>311.2009582519531</v>
       </c>
       <c r="F39" t="n">
-        <v>5794100</v>
+        <v>5030200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B40" t="n">
-        <v>313.054640940315</v>
+        <v>311.8320000281587</v>
       </c>
       <c r="C40" t="n">
-        <v>314.5829271513063</v>
+        <v>317.7381233989844</v>
       </c>
       <c r="D40" t="n">
-        <v>310.8657222472937</v>
+        <v>311.782682032414</v>
       </c>
       <c r="E40" t="n">
-        <v>311.2009582519531</v>
+        <v>315.9238891601562</v>
       </c>
       <c r="F40" t="n">
-        <v>5030200</v>
+        <v>10578300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B41" t="n">
-        <v>311.8320000281587</v>
+        <v>314.7604311532612</v>
       </c>
       <c r="C41" t="n">
-        <v>317.7381233989844</v>
+        <v>316.1408235578094</v>
       </c>
       <c r="D41" t="n">
-        <v>311.782682032414</v>
+        <v>304.7722577523736</v>
       </c>
       <c r="E41" t="n">
-        <v>315.9238891601562</v>
+        <v>305.1469421386719</v>
       </c>
       <c r="F41" t="n">
-        <v>10578300</v>
+        <v>8973300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B42" t="n">
-        <v>314.7604311532612</v>
+        <v>303.2045199796025</v>
       </c>
       <c r="C42" t="n">
-        <v>316.1408235578094</v>
+        <v>303.3327046462357</v>
       </c>
       <c r="D42" t="n">
-        <v>304.7722577523736</v>
+        <v>297.0124483237873</v>
       </c>
       <c r="E42" t="n">
-        <v>305.1469421386719</v>
+        <v>299.3591003417969</v>
       </c>
       <c r="F42" t="n">
-        <v>8973300</v>
+        <v>10327000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B43" t="n">
-        <v>303.2045199796025</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C43" t="n">
-        <v>303.3327046462357</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D43" t="n">
-        <v>297.0124483237873</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E43" t="n">
-        <v>299.3591003417969</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F43" t="n">
-        <v>10327000</v>
+        <v>8344000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B44" t="n">
-        <v>299.7436397411884</v>
+        <v>295.3066623130797</v>
       </c>
       <c r="C44" t="n">
-        <v>301.3113742461044</v>
+        <v>298.708370459316</v>
       </c>
       <c r="D44" t="n">
-        <v>293.5022804823602</v>
+        <v>292.8613742767781</v>
       </c>
       <c r="E44" t="n">
-        <v>296.1644592285156</v>
+        <v>295.2179260253906</v>
       </c>
       <c r="F44" t="n">
-        <v>8344000</v>
+        <v>8077300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B45" t="n">
-        <v>295.3066317863286</v>
+        <v>295.5432899586994</v>
       </c>
       <c r="C45" t="n">
-        <v>298.70833958092</v>
+        <v>300.1873662746028</v>
       </c>
       <c r="D45" t="n">
-        <v>292.8613440028039</v>
+        <v>295.0798692888629</v>
       </c>
       <c r="E45" t="n">
-        <v>295.2178955078125</v>
+        <v>299.0238647460938</v>
       </c>
       <c r="F45" t="n">
-        <v>8077300</v>
+        <v>5546600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B46" t="n">
-        <v>295.5432899586994</v>
+        <v>302.0509050250311</v>
       </c>
       <c r="C46" t="n">
-        <v>300.1873662746028</v>
+        <v>305.5807980031574</v>
       </c>
       <c r="D46" t="n">
-        <v>295.0798692888629</v>
+        <v>293.9854410949062</v>
       </c>
       <c r="E46" t="n">
-        <v>299.0238647460938</v>
+        <v>294.2023620605469</v>
       </c>
       <c r="F46" t="n">
-        <v>5546600</v>
+        <v>7501600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B47" t="n">
-        <v>302.0508736933244</v>
+        <v>297.0715864028587</v>
       </c>
       <c r="C47" t="n">
-        <v>305.5807663052954</v>
+        <v>297.456110287291</v>
       </c>
       <c r="D47" t="n">
-        <v>293.9854105998292</v>
+        <v>288.7103057597054</v>
       </c>
       <c r="E47" t="n">
-        <v>294.2023315429688</v>
+        <v>293.8473510742188</v>
       </c>
       <c r="F47" t="n">
-        <v>7501600</v>
+        <v>11766800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B48" t="n">
-        <v>297.0715864028587</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C48" t="n">
-        <v>297.456110287291</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D48" t="n">
-        <v>288.7103057597054</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E48" t="n">
-        <v>293.8473510742188</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F48" t="n">
-        <v>11766800</v>
+        <v>10940200</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B49" t="n">
-        <v>294.0642973394352</v>
+        <v>295.848951187077</v>
       </c>
       <c r="C49" t="n">
-        <v>295.6221924256846</v>
+        <v>300.236658228506</v>
       </c>
       <c r="D49" t="n">
-        <v>290.386540762355</v>
+        <v>291.4218258555586</v>
       </c>
       <c r="E49" t="n">
-        <v>293.8276672363281</v>
+        <v>298.7576599121094</v>
       </c>
       <c r="F49" t="n">
-        <v>10940200</v>
+        <v>8877200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B50" t="n">
-        <v>295.848951187077</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C50" t="n">
-        <v>300.236658228506</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D50" t="n">
-        <v>291.4218258555586</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E50" t="n">
-        <v>298.7576599121094</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F50" t="n">
-        <v>8877200</v>
+        <v>7910900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B51" t="n">
-        <v>300.7296512123902</v>
+        <v>304.7722465716023</v>
       </c>
       <c r="C51" t="n">
-        <v>304.2102259719906</v>
+        <v>309.3275563846455</v>
       </c>
       <c r="D51" t="n">
-        <v>298.9548653069277</v>
+        <v>303.9242719247256</v>
       </c>
       <c r="E51" t="n">
-        <v>303.3327026367188</v>
+        <v>308.6965026855469</v>
       </c>
       <c r="F51" t="n">
-        <v>7910900</v>
+        <v>4322400</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B52" t="n">
-        <v>304.7722465716023</v>
+        <v>308.5683618849884</v>
       </c>
       <c r="C52" t="n">
-        <v>309.3275563846455</v>
+        <v>309.6430970545817</v>
       </c>
       <c r="D52" t="n">
-        <v>303.9242719247256</v>
+        <v>304.2201032083801</v>
       </c>
       <c r="E52" t="n">
-        <v>308.6965026855469</v>
+        <v>304.5947875976562</v>
       </c>
       <c r="F52" t="n">
-        <v>4322400</v>
+        <v>7727300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B53" t="n">
-        <v>308.5683618849884</v>
+        <v>304.4172499168193</v>
       </c>
       <c r="C53" t="n">
-        <v>309.6430970545817</v>
+        <v>306.1329082340515</v>
       </c>
       <c r="D53" t="n">
-        <v>304.2201032083801</v>
+        <v>302.7903579681411</v>
       </c>
       <c r="E53" t="n">
-        <v>304.5947875976562</v>
+        <v>303.5693054199219</v>
       </c>
       <c r="F53" t="n">
-        <v>7727300</v>
+        <v>7249000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B54" t="n">
-        <v>304.4172805196406</v>
+        <v>302.8988595387675</v>
       </c>
       <c r="C54" t="n">
-        <v>306.1329390093465</v>
+        <v>307.9865871384521</v>
       </c>
       <c r="D54" t="n">
-        <v>302.7903884074122</v>
+        <v>302.5044359255107</v>
       </c>
       <c r="E54" t="n">
-        <v>303.5693359375</v>
+        <v>307.7598266601562</v>
       </c>
       <c r="F54" t="n">
-        <v>7249000</v>
+        <v>8535300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B55" t="n">
-        <v>302.8988895743303</v>
+        <v>308.8739918889233</v>
       </c>
       <c r="C55" t="n">
-        <v>307.9866176785159</v>
+        <v>314.0307463246157</v>
       </c>
       <c r="D55" t="n">
-        <v>302.5044659219624</v>
+        <v>308.6176225735461</v>
       </c>
       <c r="E55" t="n">
-        <v>307.7598571777344</v>
+        <v>311.6742248535156</v>
       </c>
       <c r="F55" t="n">
-        <v>8535300</v>
+        <v>9627800</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B56" t="n">
-        <v>308.8739918889233</v>
+        <v>311.2206641139725</v>
       </c>
       <c r="C56" t="n">
-        <v>314.0307463246157</v>
+        <v>314.0208969911127</v>
       </c>
       <c r="D56" t="n">
-        <v>308.6176225735461</v>
+        <v>310.2740836361238</v>
       </c>
       <c r="E56" t="n">
-        <v>311.6742248535156</v>
+        <v>310.6290588378906</v>
       </c>
       <c r="F56" t="n">
-        <v>9627800</v>
+        <v>6518900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B57" t="n">
-        <v>311.2206641139725</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C57" t="n">
-        <v>314.0208969911127</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D57" t="n">
-        <v>310.2740836361238</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E57" t="n">
-        <v>310.6290588378906</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F57" t="n">
-        <v>6518900</v>
+        <v>7417200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B58" t="n">
-        <v>310.6487980837529</v>
+        <v>310.5403783790639</v>
       </c>
       <c r="C58" t="n">
-        <v>312.0390600856641</v>
+        <v>314.336450228146</v>
       </c>
       <c r="D58" t="n">
-        <v>308.9627484602848</v>
+        <v>295.8193913272319</v>
       </c>
       <c r="E58" t="n">
-        <v>310.7966918945312</v>
+        <v>296.3025512695312</v>
       </c>
       <c r="F58" t="n">
-        <v>7417200</v>
+        <v>18049200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B59" t="n">
-        <v>310.5403783790639</v>
+        <v>296.2926621709551</v>
       </c>
       <c r="C59" t="n">
-        <v>314.336450228146</v>
+        <v>306.8329925602339</v>
       </c>
       <c r="D59" t="n">
-        <v>295.8193913272319</v>
+        <v>294.2812160390869</v>
       </c>
       <c r="E59" t="n">
-        <v>296.3025512695312</v>
+        <v>305.7680969238281</v>
       </c>
       <c r="F59" t="n">
-        <v>18049200</v>
+        <v>18874100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B60" t="n">
-        <v>296.2926621709551</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C60" t="n">
-        <v>306.8329925602339</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D60" t="n">
-        <v>294.2812160390869</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E60" t="n">
-        <v>305.7680969238281</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F60" t="n">
-        <v>18874100</v>
+        <v>9721900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B61" t="n">
-        <v>304.9102649889192</v>
+        <v>315.2041261224818</v>
       </c>
       <c r="C61" t="n">
-        <v>313.5476242674454</v>
+        <v>315.7858618718594</v>
       </c>
       <c r="D61" t="n">
-        <v>304.9102649889192</v>
+        <v>312.1672627021157</v>
       </c>
       <c r="E61" t="n">
-        <v>312.9363098144531</v>
+        <v>314.0603637695312</v>
       </c>
       <c r="F61" t="n">
-        <v>9721900</v>
+        <v>8982900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B62" t="n">
-        <v>315.2040954937631</v>
+        <v>315.1153648797306</v>
       </c>
       <c r="C62" t="n">
-        <v>315.7858311866128</v>
+        <v>318.3593094805321</v>
       </c>
       <c r="D62" t="n">
-        <v>312.1672323684923</v>
+        <v>313.9321843288561</v>
       </c>
       <c r="E62" t="n">
-        <v>314.0603332519531</v>
+        <v>315.5393371582031</v>
       </c>
       <c r="F62" t="n">
-        <v>8982900</v>
+        <v>10864100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B63" t="n">
-        <v>315.1153648797306</v>
+        <v>314.6223718715413</v>
       </c>
       <c r="C63" t="n">
-        <v>318.3593094805321</v>
+        <v>315.0463441586525</v>
       </c>
       <c r="D63" t="n">
-        <v>313.9321843288561</v>
+        <v>309.9980348220149</v>
       </c>
       <c r="E63" t="n">
-        <v>315.5393371582031</v>
+        <v>311.1319274902344</v>
       </c>
       <c r="F63" t="n">
-        <v>10864100</v>
+        <v>8331300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B64" t="n">
-        <v>314.6223718715413</v>
+        <v>313.971593609235</v>
       </c>
       <c r="C64" t="n">
-        <v>315.0463441586525</v>
+        <v>314.8984348971578</v>
       </c>
       <c r="D64" t="n">
-        <v>309.9980348220149</v>
+        <v>310.254388930852</v>
       </c>
       <c r="E64" t="n">
-        <v>311.1319274902344</v>
+        <v>310.5699157714844</v>
       </c>
       <c r="F64" t="n">
-        <v>8331300</v>
+        <v>8718700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B65" t="n">
-        <v>313.971593609235</v>
+        <v>311.5756418636432</v>
       </c>
       <c r="C65" t="n">
-        <v>314.8984348971578</v>
+        <v>313.2518519730792</v>
       </c>
       <c r="D65" t="n">
-        <v>310.254388930852</v>
+        <v>307.8485673512913</v>
       </c>
       <c r="E65" t="n">
-        <v>310.5699157714844</v>
+        <v>308.6176452636719</v>
       </c>
       <c r="F65" t="n">
-        <v>8718700</v>
+        <v>11444900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B66" t="n">
-        <v>311.5756418636432</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C66" t="n">
-        <v>313.2518519730792</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D66" t="n">
-        <v>307.8485673512913</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E66" t="n">
-        <v>308.6176452636719</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F66" t="n">
-        <v>11444900</v>
+        <v>24494400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B67" t="n">
-        <v>309.3965776494671</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="C67" t="n">
-        <v>314.099781180705</v>
+        <v>318.7043994886834</v>
       </c>
       <c r="D67" t="n">
-        <v>308.8049723403709</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="E67" t="n">
-        <v>312.7686767578125</v>
+        <v>318.5663452148438</v>
       </c>
       <c r="F67" t="n">
-        <v>24494400</v>
+        <v>8354600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B68" t="n">
-        <v>313.0644852104395</v>
+        <v>319.0790830432475</v>
       </c>
       <c r="C68" t="n">
-        <v>318.7043994886834</v>
+        <v>323.1907116116738</v>
       </c>
       <c r="D68" t="n">
-        <v>313.0644852104395</v>
+        <v>318.5663744582675</v>
       </c>
       <c r="E68" t="n">
-        <v>318.5663452148438</v>
+        <v>321.3666076660156</v>
       </c>
       <c r="F68" t="n">
-        <v>8354600</v>
+        <v>6668300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B69" t="n">
-        <v>319.079052742897</v>
+        <v>321.6722795787551</v>
       </c>
       <c r="C69" t="n">
-        <v>323.1906809208754</v>
+        <v>325.3697755465356</v>
       </c>
       <c r="D69" t="n">
-        <v>318.5663442066048</v>
+        <v>320.9426500033422</v>
       </c>
       <c r="E69" t="n">
-        <v>321.3665771484375</v>
+        <v>324.561279296875</v>
       </c>
       <c r="F69" t="n">
-        <v>6668300</v>
+        <v>4289300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B70" t="n">
-        <v>321.6722493328215</v>
+        <v>324.502058709128</v>
       </c>
       <c r="C70" t="n">
-        <v>325.3697449529369</v>
+        <v>326.2275566521161</v>
       </c>
       <c r="D70" t="n">
-        <v>320.9426198260136</v>
+        <v>321.9680645986219</v>
       </c>
       <c r="E70" t="n">
-        <v>324.5612487792969</v>
+        <v>323.3188781738281</v>
       </c>
       <c r="F70" t="n">
-        <v>4289300</v>
+        <v>4158300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B71" t="n">
-        <v>324.5020893383847</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C71" t="n">
-        <v>326.22758744424</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D71" t="n">
-        <v>321.9680949886989</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E71" t="n">
-        <v>323.3189086914062</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F71" t="n">
-        <v>4158300</v>
+        <v>8635300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B72" t="n">
-        <v>322.4216288798564</v>
+        <v>320.2623075229155</v>
       </c>
       <c r="C72" t="n">
-        <v>323.1808371734579</v>
+        <v>320.3904921972535</v>
       </c>
       <c r="D72" t="n">
-        <v>319.0002116144308</v>
+        <v>317.9747828016658</v>
       </c>
       <c r="E72" t="n">
-        <v>319.2171325683594</v>
+        <v>318.8917846679688</v>
       </c>
       <c r="F72" t="n">
-        <v>8635300</v>
+        <v>7904300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B73" t="n">
-        <v>320.2622768741799</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C73" t="n">
-        <v>320.3904615362508</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D73" t="n">
-        <v>317.9747523718436</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E73" t="n">
-        <v>318.8917541503906</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F73" t="n">
-        <v>7904300</v>
+        <v>5048500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B74" t="n">
-        <v>319.7988699190817</v>
+        <v>317.9846252281575</v>
       </c>
       <c r="C74" t="n">
-        <v>320.3313177342217</v>
+        <v>321.1694123071354</v>
       </c>
       <c r="D74" t="n">
-        <v>317.5310845539587</v>
+        <v>316.2492576445291</v>
       </c>
       <c r="E74" t="n">
-        <v>317.7085571289062</v>
+        <v>320.9229125976562</v>
       </c>
       <c r="F74" t="n">
-        <v>5048500</v>
+        <v>8054000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B75" t="n">
-        <v>317.9846252281575</v>
+        <v>320.942628937084</v>
       </c>
       <c r="C75" t="n">
-        <v>321.1694123071354</v>
+        <v>332.5281155423397</v>
       </c>
       <c r="D75" t="n">
-        <v>316.2492576445291</v>
+        <v>320.636971697701</v>
       </c>
       <c r="E75" t="n">
-        <v>320.9229125976562</v>
+        <v>329.3630676269531</v>
       </c>
       <c r="F75" t="n">
-        <v>8054000</v>
+        <v>10752600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,25 +2393,25 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B76" t="n">
-        <v>320.942599199713</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C76" t="n">
-        <v>332.5280847314999</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D76" t="n">
-        <v>320.6369419886511</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E76" t="n">
-        <v>329.363037109375</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F76" t="n">
-        <v>10752600</v>
+        <v>7660800</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2419,25 +2419,25 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B77" t="n">
-        <v>329.4422902981328</v>
+        <v>327.9764350864437</v>
       </c>
       <c r="C77" t="n">
-        <v>332.6612412306879</v>
+        <v>328.9767653957764</v>
       </c>
       <c r="D77" t="n">
-        <v>327.491109600743</v>
+        <v>321.4989071734381</v>
       </c>
       <c r="E77" t="n">
-        <v>331.4132690429688</v>
+        <v>323.8660583496094</v>
       </c>
       <c r="F77" t="n">
-        <v>7660800</v>
+        <v>9815200</v>
       </c>
       <c r="G77" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B78" t="n">
-        <v>327.9764350864437</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C78" t="n">
-        <v>328.9767653957764</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D78" t="n">
-        <v>321.4989071734381</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E78" t="n">
-        <v>323.8660583496094</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F78" t="n">
-        <v>9815200</v>
+        <v>11737100</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B79" t="n">
-        <v>323.2718313763784</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C79" t="n">
-        <v>328.2339475379842</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D79" t="n">
-        <v>322.5388804495614</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E79" t="n">
-        <v>326.6393432617188</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F79" t="n">
-        <v>11737100</v>
+        <v>6738100</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B80" t="n">
-        <v>326.1936353875406</v>
+        <v>318.8049332018166</v>
       </c>
       <c r="C80" t="n">
-        <v>328.7291759216584</v>
+        <v>322.9053661093398</v>
       </c>
       <c r="D80" t="n">
-        <v>325.0348299492433</v>
+        <v>318.1611490039577</v>
       </c>
       <c r="E80" t="n">
-        <v>326.0450744628906</v>
+        <v>321.3899841308594</v>
       </c>
       <c r="F80" t="n">
-        <v>6738100</v>
+        <v>12805100</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B81" t="n">
-        <v>318.8049332018166</v>
+        <v>321.2017865718998</v>
       </c>
       <c r="C81" t="n">
-        <v>322.9053661093398</v>
+        <v>323.7373271836527</v>
       </c>
       <c r="D81" t="n">
-        <v>318.1611490039577</v>
+        <v>307.6029755260753</v>
       </c>
       <c r="E81" t="n">
-        <v>321.3899841308594</v>
+        <v>307.9298095703125</v>
       </c>
       <c r="F81" t="n">
-        <v>12805100</v>
+        <v>19371200</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B82" t="n">
-        <v>321.2017865718998</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C82" t="n">
-        <v>323.7373271836527</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D82" t="n">
-        <v>307.6029755260753</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E82" t="n">
-        <v>307.9298095703125</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F82" t="n">
-        <v>19371200</v>
+        <v>25951500</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B83" t="n">
-        <v>305.2556057077196</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C83" t="n">
-        <v>308.7815926253858</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D83" t="n">
-        <v>303.1954601804828</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E83" t="n">
-        <v>304.9287414550781</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F83" t="n">
-        <v>25951500</v>
+        <v>14751400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B84" t="n">
-        <v>305.5230197927318</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C84" t="n">
-        <v>309.95031666446</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D84" t="n">
-        <v>304.8098971346673</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E84" t="n">
-        <v>306.3054809570312</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F84" t="n">
-        <v>14751400</v>
+        <v>14652500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B85" t="n">
-        <v>307.385060616362</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C85" t="n">
-        <v>314.1795087286461</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D85" t="n">
-        <v>307.0383983149945</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E85" t="n">
-        <v>309.4848022460938</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F85" t="n">
-        <v>14652500</v>
+        <v>12900600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B86" t="n">
-        <v>303.2845981841295</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C86" t="n">
-        <v>308.1774060521912</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D86" t="n">
-        <v>298.9761500928895</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E86" t="n">
-        <v>299.8477478027344</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F86" t="n">
-        <v>12900600</v>
+        <v>10270100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B87" t="n">
-        <v>300.5311849469782</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C87" t="n">
-        <v>302.4823658305288</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D87" t="n">
-        <v>298.2729680555718</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E87" t="n">
-        <v>299.1544799804688</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F87" t="n">
-        <v>10270100</v>
+        <v>10535800</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B88" t="n">
-        <v>301.9474777854751</v>
+        <v>299.1148422218051</v>
       </c>
       <c r="C88" t="n">
-        <v>305.2555953909441</v>
+        <v>299.4813025896872</v>
       </c>
       <c r="D88" t="n">
-        <v>300.0062112868251</v>
+        <v>293.6773006232809</v>
       </c>
       <c r="E88" t="n">
-        <v>300.729248046875</v>
+        <v>294.875732421875</v>
       </c>
       <c r="F88" t="n">
-        <v>10535800</v>
+        <v>11107900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B89" t="n">
-        <v>299.1148422218051</v>
+        <v>294.9648788077786</v>
       </c>
       <c r="C89" t="n">
-        <v>299.4813025896872</v>
+        <v>298.8969527426069</v>
       </c>
       <c r="D89" t="n">
-        <v>293.6773006232809</v>
+        <v>294.6083325653198</v>
       </c>
       <c r="E89" t="n">
-        <v>294.875732421875</v>
+        <v>298.1640319824219</v>
       </c>
       <c r="F89" t="n">
-        <v>11107900</v>
+        <v>11752700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B90" t="n">
-        <v>294.9648788077786</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C90" t="n">
-        <v>298.8969527426069</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D90" t="n">
-        <v>294.6083325653198</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E90" t="n">
-        <v>298.1640319824219</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F90" t="n">
-        <v>11752700</v>
+        <v>11527400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B91" t="n">
-        <v>298.4512235287846</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C91" t="n">
-        <v>299.0851237823749</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D91" t="n">
-        <v>295.3016109870806</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E91" t="n">
-        <v>297.4409790039062</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F91" t="n">
-        <v>11527400</v>
+        <v>9556700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B92" t="n">
-        <v>297.4013222225187</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C92" t="n">
-        <v>299.0355829225425</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D92" t="n">
-        <v>295.2025300603667</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E92" t="n">
-        <v>297.8965454101562</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F92" t="n">
-        <v>9556700</v>
+        <v>11580000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B93" t="n">
-        <v>299.5110006693188</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C93" t="n">
-        <v>303.898671192008</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D93" t="n">
-        <v>299.3327275624257</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E93" t="n">
-        <v>303.4926147460938</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F93" t="n">
-        <v>11580000</v>
+        <v>11953200</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B94" t="n">
-        <v>302.333781642444</v>
+        <v>301.5513012828864</v>
       </c>
       <c r="C94" t="n">
-        <v>304.9881708986046</v>
+        <v>306.3450582127215</v>
       </c>
       <c r="D94" t="n">
-        <v>299.6694782493637</v>
+        <v>298.4908255461663</v>
       </c>
       <c r="E94" t="n">
-        <v>302.9676818847656</v>
+        <v>305.1961669921875</v>
       </c>
       <c r="F94" t="n">
-        <v>11953200</v>
+        <v>9839400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B95" t="n">
-        <v>301.5513012828864</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C95" t="n">
-        <v>306.3450582127215</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D95" t="n">
-        <v>298.4908255461663</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E95" t="n">
-        <v>305.1961669921875</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F95" t="n">
-        <v>9839400</v>
+        <v>12688000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B96" t="n">
-        <v>306.7709905338949</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="C96" t="n">
-        <v>313.2286905211348</v>
+        <v>316.2594719758441</v>
       </c>
       <c r="D96" t="n">
-        <v>306.1470044328188</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="E96" t="n">
-        <v>311.8420715332031</v>
+        <v>314.2389526367188</v>
       </c>
       <c r="F96" t="n">
-        <v>12688000</v>
+        <v>9848800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B97" t="n">
-        <v>311.4062901330092</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C97" t="n">
-        <v>316.2594719758441</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D97" t="n">
-        <v>311.4062901330092</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E97" t="n">
-        <v>314.2389526367188</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F97" t="n">
-        <v>9848800</v>
+        <v>9388000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B98" t="n">
-        <v>311.9906259989966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C98" t="n">
-        <v>312.9909865673853</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D98" t="n">
-        <v>302.6210112179966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E98" t="n">
-        <v>307.1968688964844</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F98" t="n">
-        <v>9388000</v>
+        <v>17797400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B99" t="n">
-        <v>311.7034102684662</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C99" t="n">
-        <v>321.1522783634816</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D99" t="n">
-        <v>311.7034102684662</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E99" t="n">
-        <v>319.3199462890625</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F99" t="n">
-        <v>17797400</v>
+        <v>11477500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B100" t="n">
-        <v>318.2700781279603</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C100" t="n">
-        <v>323.2817350541263</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D100" t="n">
-        <v>317.0518180384032</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E100" t="n">
-        <v>319.0228271484375</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F100" t="n">
-        <v>11477500</v>
+        <v>9902200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B101" t="n">
-        <v>319.4684837021083</v>
+        <v>320.1518827061323</v>
       </c>
       <c r="C101" t="n">
-        <v>323.014298845819</v>
+        <v>322.1724018130651</v>
       </c>
       <c r="D101" t="n">
-        <v>312.1094739861534</v>
+        <v>305.7805260837019</v>
       </c>
       <c r="E101" t="n">
-        <v>315.2392883300781</v>
+        <v>307.8505554199219</v>
       </c>
       <c r="F101" t="n">
-        <v>9902200</v>
+        <v>8703500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B102" t="n">
-        <v>320.1518827061323</v>
+        <v>309.2966374972976</v>
       </c>
       <c r="C102" t="n">
-        <v>322.1724018130651</v>
+        <v>310.6238322045743</v>
       </c>
       <c r="D102" t="n">
-        <v>305.7805260837019</v>
+        <v>297.1537535117247</v>
       </c>
       <c r="E102" t="n">
-        <v>307.8505554199219</v>
+        <v>299.7487487792969</v>
       </c>
       <c r="F102" t="n">
-        <v>8703500</v>
+        <v>13443400</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B103" t="n">
-        <v>309.2966374972976</v>
+        <v>295.6680782309701</v>
       </c>
       <c r="C103" t="n">
-        <v>310.6238322045743</v>
+        <v>301.3829738793206</v>
       </c>
       <c r="D103" t="n">
-        <v>297.1537535117247</v>
+        <v>293.6871852314235</v>
       </c>
       <c r="E103" t="n">
-        <v>299.7487487792969</v>
+        <v>299.6595764160156</v>
       </c>
       <c r="F103" t="n">
-        <v>13443400</v>
+        <v>9114500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B104" t="n">
-        <v>295.6680782309701</v>
+        <v>299.8675850307636</v>
       </c>
       <c r="C104" t="n">
-        <v>301.3829738793206</v>
+        <v>305.2952123797385</v>
       </c>
       <c r="D104" t="n">
-        <v>293.6871852314235</v>
+        <v>299.6100592744303</v>
       </c>
       <c r="E104" t="n">
-        <v>299.6595764160156</v>
+        <v>304.1958312988281</v>
       </c>
       <c r="F104" t="n">
-        <v>9114500</v>
+        <v>8896800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B105" t="n">
-        <v>299.8675850307636</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C105" t="n">
-        <v>305.2952123797385</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D105" t="n">
-        <v>299.6100592744303</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E105" t="n">
-        <v>304.1958312988281</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F105" t="n">
-        <v>8896800</v>
+        <v>7209600</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B106" t="n">
-        <v>305.5130974954087</v>
+        <v>304.2354272061944</v>
       </c>
       <c r="C106" t="n">
-        <v>309.2966101142475</v>
+        <v>306.2262038721237</v>
       </c>
       <c r="D106" t="n">
-        <v>304.2849535938903</v>
+        <v>302.2049939958365</v>
       </c>
       <c r="E106" t="n">
-        <v>305.8300476074219</v>
+        <v>305.1069946289062</v>
       </c>
       <c r="F106" t="n">
-        <v>7209600</v>
+        <v>6737700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B107" t="n">
-        <v>304.2354272061944</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C107" t="n">
-        <v>306.2262038721237</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D107" t="n">
-        <v>302.2049939958365</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E107" t="n">
-        <v>305.1069946289062</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F107" t="n">
-        <v>6737700</v>
+        <v>7792700</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B108" t="n">
-        <v>305.4536802835111</v>
+        <v>305.8498457788994</v>
       </c>
       <c r="C108" t="n">
-        <v>308.0288471084009</v>
+        <v>308.0288400173425</v>
       </c>
       <c r="D108" t="n">
-        <v>302.7596647203387</v>
+        <v>292.2807478108573</v>
       </c>
       <c r="E108" t="n">
-        <v>307.8208618164062</v>
+        <v>294.8262023925781</v>
       </c>
       <c r="F108" t="n">
-        <v>7792700</v>
+        <v>12955400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B109" t="n">
-        <v>305.8498457788994</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C109" t="n">
-        <v>308.0288400173425</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D109" t="n">
-        <v>292.2807478108573</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E109" t="n">
-        <v>294.8262023925781</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F109" t="n">
-        <v>12955400</v>
+        <v>13554100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B110" t="n">
-        <v>293.9843218466586</v>
+        <v>295.7869507950724</v>
       </c>
       <c r="C110" t="n">
-        <v>296.886322684036</v>
+        <v>300.7589812348872</v>
       </c>
       <c r="D110" t="n">
-        <v>288.5962907533433</v>
+        <v>294.1725181992404</v>
       </c>
       <c r="E110" t="n">
-        <v>294.459716796875</v>
+        <v>300.4024047851562</v>
       </c>
       <c r="F110" t="n">
-        <v>13554100</v>
+        <v>8095500</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B111" t="n">
-        <v>295.7869507950724</v>
+        <v>301.670173133609</v>
       </c>
       <c r="C111" t="n">
-        <v>300.7589812348872</v>
+        <v>306.0578739762234</v>
       </c>
       <c r="D111" t="n">
-        <v>294.1725181992404</v>
+        <v>300.7391812579012</v>
       </c>
       <c r="E111" t="n">
-        <v>300.4024047851562</v>
+        <v>303.2053833007812</v>
       </c>
       <c r="F111" t="n">
-        <v>8095500</v>
+        <v>7007800</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B112" t="n">
-        <v>301.670173133609</v>
+        <v>297.1339389424841</v>
       </c>
       <c r="C112" t="n">
-        <v>306.0578739762234</v>
+        <v>300.0557680991628</v>
       </c>
       <c r="D112" t="n">
-        <v>300.7391812579012</v>
+        <v>291.636973162459</v>
       </c>
       <c r="E112" t="n">
-        <v>303.2053833007812</v>
+        <v>297.4310607910156</v>
       </c>
       <c r="F112" t="n">
-        <v>7007800</v>
+        <v>18620800</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B113" t="n">
-        <v>297.1339389424841</v>
+        <v>291.9935267958635</v>
       </c>
       <c r="C113" t="n">
-        <v>300.0557680991628</v>
+        <v>297.1141484397957</v>
       </c>
       <c r="D113" t="n">
-        <v>291.636973162459</v>
+        <v>290.4088063693875</v>
       </c>
       <c r="E113" t="n">
-        <v>297.4310607910156</v>
+        <v>294.7172546386719</v>
       </c>
       <c r="F113" t="n">
-        <v>18620800</v>
+        <v>8508900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B114" t="n">
-        <v>291.9935267958635</v>
+        <v>289.4975898716125</v>
       </c>
       <c r="C114" t="n">
-        <v>297.1141484397957</v>
+        <v>299.5011046657454</v>
       </c>
       <c r="D114" t="n">
-        <v>290.4088063693875</v>
+        <v>286.7342359222354</v>
       </c>
       <c r="E114" t="n">
-        <v>294.7172546386719</v>
+        <v>297.3914489746094</v>
       </c>
       <c r="F114" t="n">
-        <v>8508900</v>
+        <v>10278200</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B115" t="n">
-        <v>289.4975898716125</v>
+        <v>297.1240288614248</v>
       </c>
       <c r="C115" t="n">
-        <v>299.5011046657454</v>
+        <v>298.1243894751821</v>
       </c>
       <c r="D115" t="n">
-        <v>286.7342359222354</v>
+        <v>292.993883980321</v>
       </c>
       <c r="E115" t="n">
-        <v>297.3914489746094</v>
+        <v>296.52978515625</v>
       </c>
       <c r="F115" t="n">
-        <v>10278200</v>
+        <v>8055700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B116" t="n">
-        <v>297.1240288614248</v>
+        <v>295.1332451958745</v>
       </c>
       <c r="C116" t="n">
-        <v>298.1243894751821</v>
+        <v>298.3620800816865</v>
       </c>
       <c r="D116" t="n">
-        <v>292.993883980321</v>
+        <v>289.6362492414601</v>
       </c>
       <c r="E116" t="n">
-        <v>296.52978515625</v>
+        <v>290.7455444335938</v>
       </c>
       <c r="F116" t="n">
-        <v>8055700</v>
+        <v>12732500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B117" t="n">
-        <v>295.1332451958745</v>
+        <v>283.6044306839189</v>
       </c>
       <c r="C117" t="n">
-        <v>298.3620800816865</v>
+        <v>287.2195541533999</v>
       </c>
       <c r="D117" t="n">
-        <v>289.6362492414601</v>
+        <v>280.9995517042956</v>
       </c>
       <c r="E117" t="n">
-        <v>290.7455444335938</v>
+        <v>286.7144470214844</v>
       </c>
       <c r="F117" t="n">
-        <v>12732500</v>
+        <v>13496500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B118" t="n">
-        <v>283.6044306839189</v>
+        <v>282.7724816341387</v>
       </c>
       <c r="C118" t="n">
-        <v>287.2195541533999</v>
+        <v>288.3189881947603</v>
       </c>
       <c r="D118" t="n">
-        <v>280.9995517042956</v>
+        <v>277.7707387954702</v>
       </c>
       <c r="E118" t="n">
-        <v>286.7144470214844</v>
+        <v>287.1502685546875</v>
       </c>
       <c r="F118" t="n">
-        <v>13496500</v>
+        <v>12241100</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B119" t="n">
-        <v>282.7724816341387</v>
+        <v>286.5262662545288</v>
       </c>
       <c r="C119" t="n">
-        <v>288.3189881947603</v>
+        <v>289.9532025593205</v>
       </c>
       <c r="D119" t="n">
-        <v>277.7707387954702</v>
+        <v>284.4364084963449</v>
       </c>
       <c r="E119" t="n">
-        <v>287.1502685546875</v>
+        <v>285.9716186523438</v>
       </c>
       <c r="F119" t="n">
-        <v>12241100</v>
+        <v>8344900</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B120" t="n">
-        <v>286.5262662545288</v>
+        <v>286.0508166178312</v>
       </c>
       <c r="C120" t="n">
-        <v>289.9532025593205</v>
+        <v>287.7048753720447</v>
       </c>
       <c r="D120" t="n">
-        <v>284.4364084963449</v>
+        <v>282.1385413260368</v>
       </c>
       <c r="E120" t="n">
-        <v>285.9716186523438</v>
+        <v>284.7731323242188</v>
       </c>
       <c r="F120" t="n">
-        <v>8344900</v>
+        <v>10205000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B121" t="n">
-        <v>286.0508166178312</v>
+        <v>280.1279538528093</v>
       </c>
       <c r="C121" t="n">
-        <v>287.7048753720447</v>
+        <v>281.167940752382</v>
       </c>
       <c r="D121" t="n">
-        <v>282.1385413260368</v>
+        <v>276.4336079693154</v>
       </c>
       <c r="E121" t="n">
-        <v>284.7731323242188</v>
+        <v>280.1874084472656</v>
       </c>
       <c r="F121" t="n">
-        <v>10205000</v>
+        <v>13760500</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B122" t="n">
-        <v>280.1279538528093</v>
+        <v>281.9504072447318</v>
       </c>
       <c r="C122" t="n">
-        <v>281.167940752382</v>
+        <v>284.4463214441296</v>
       </c>
       <c r="D122" t="n">
-        <v>276.4336079693154</v>
+        <v>280.2468381234208</v>
       </c>
       <c r="E122" t="n">
-        <v>280.1874084472656</v>
+        <v>280.7321472167969</v>
       </c>
       <c r="F122" t="n">
-        <v>13760500</v>
+        <v>9091200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B123" t="n">
-        <v>281.9504072447318</v>
+        <v>283.6044205599556</v>
       </c>
       <c r="C123" t="n">
-        <v>284.4463214441296</v>
+        <v>286.506421278288</v>
       </c>
       <c r="D123" t="n">
-        <v>280.2468381234208</v>
+        <v>281.8909373944359</v>
       </c>
       <c r="E123" t="n">
-        <v>280.7321472167969</v>
+        <v>283.4261474609375</v>
       </c>
       <c r="F123" t="n">
-        <v>9091200</v>
+        <v>8149000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B124" t="n">
-        <v>283.6044205599556</v>
+        <v>286.2390279690733</v>
       </c>
       <c r="C124" t="n">
-        <v>286.506421278288</v>
+        <v>288.9726698808299</v>
       </c>
       <c r="D124" t="n">
-        <v>281.8909373944359</v>
+        <v>283.2181783456238</v>
       </c>
       <c r="E124" t="n">
-        <v>283.4261474609375</v>
+        <v>284.1492004394531</v>
       </c>
       <c r="F124" t="n">
-        <v>8149000</v>
+        <v>8961200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B125" t="n">
-        <v>286.2390279690733</v>
+        <v>284.0897484324327</v>
       </c>
       <c r="C125" t="n">
-        <v>288.9726698808299</v>
+        <v>286.6451172582804</v>
       </c>
       <c r="D125" t="n">
-        <v>283.2181783456238</v>
+        <v>282.3960934275981</v>
       </c>
       <c r="E125" t="n">
-        <v>284.1492004394531</v>
+        <v>284.9910583496094</v>
       </c>
       <c r="F125" t="n">
-        <v>8961200</v>
+        <v>10057000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B126" t="n">
-        <v>284.0897484324327</v>
+        <v>284.1392586396808</v>
       </c>
       <c r="C126" t="n">
-        <v>286.6451172582804</v>
+        <v>286.7441374214082</v>
       </c>
       <c r="D126" t="n">
-        <v>282.3960934275981</v>
+        <v>281.9008401776293</v>
       </c>
       <c r="E126" t="n">
-        <v>284.9910583496094</v>
+        <v>285.2188415527344</v>
       </c>
       <c r="F126" t="n">
-        <v>10057000</v>
+        <v>9846700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B127" t="n">
-        <v>284.1392586396808</v>
+        <v>285.327825032355</v>
       </c>
       <c r="C127" t="n">
-        <v>286.7441374214082</v>
+        <v>287.9327042603992</v>
       </c>
       <c r="D127" t="n">
-        <v>281.9008401776293</v>
+        <v>282.5446726819272</v>
       </c>
       <c r="E127" t="n">
-        <v>285.2188415527344</v>
+        <v>283.8223571777344</v>
       </c>
       <c r="F127" t="n">
-        <v>9846700</v>
+        <v>22436500</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B128" t="n">
-        <v>285.327825032355</v>
+        <v>291.4982779446762</v>
       </c>
       <c r="C128" t="n">
-        <v>287.9327042603992</v>
+        <v>292.9245231806114</v>
       </c>
       <c r="D128" t="n">
-        <v>282.5446726819272</v>
+        <v>285.2188513876401</v>
       </c>
       <c r="E128" t="n">
-        <v>283.8223571777344</v>
+        <v>287.1403198242188</v>
       </c>
       <c r="F128" t="n">
-        <v>22436500</v>
+        <v>11470800</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B129" t="n">
-        <v>291.4982779446762</v>
+        <v>283.4360748065673</v>
       </c>
       <c r="C129" t="n">
-        <v>292.9245231806114</v>
+        <v>292.6571288676103</v>
       </c>
       <c r="D129" t="n">
-        <v>285.2188513876401</v>
+        <v>282.6436995084055</v>
       </c>
       <c r="E129" t="n">
-        <v>287.1403198242188</v>
+        <v>289.6065368652344</v>
       </c>
       <c r="F129" t="n">
-        <v>11470800</v>
+        <v>11092300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B130" t="n">
-        <v>283.4360748065673</v>
+        <v>291.3398308899875</v>
       </c>
       <c r="C130" t="n">
-        <v>292.6571288676103</v>
+        <v>294.7965097163498</v>
       </c>
       <c r="D130" t="n">
-        <v>282.6436995084055</v>
+        <v>289.6461758443202</v>
       </c>
       <c r="E130" t="n">
-        <v>289.6065368652344</v>
+        <v>292.5977172851562</v>
       </c>
       <c r="F130" t="n">
-        <v>11092300</v>
+        <v>12188200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B131" t="n">
-        <v>291.3398308899875</v>
+        <v>289.7848205526045</v>
       </c>
       <c r="C131" t="n">
-        <v>294.7965097163498</v>
+        <v>292.1718002190451</v>
       </c>
       <c r="D131" t="n">
-        <v>289.6461758443202</v>
+        <v>287.9525187281419</v>
       </c>
       <c r="E131" t="n">
-        <v>292.5977172851562</v>
+        <v>288.8736267089844</v>
       </c>
       <c r="F131" t="n">
-        <v>12188200</v>
+        <v>8669200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B132" t="n">
-        <v>289.7848205526045</v>
+        <v>286.3777093696089</v>
       </c>
       <c r="C132" t="n">
-        <v>292.1718002190451</v>
+        <v>287.3384134369941</v>
       </c>
       <c r="D132" t="n">
-        <v>287.9525187281419</v>
+        <v>279.0582953832721</v>
       </c>
       <c r="E132" t="n">
-        <v>288.8736267089844</v>
+        <v>280.1378784179688</v>
       </c>
       <c r="F132" t="n">
-        <v>8669200</v>
+        <v>9873300</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B133" t="n">
-        <v>286.3777093696089</v>
+        <v>282.0197247859078</v>
       </c>
       <c r="C133" t="n">
-        <v>287.3384134369941</v>
+        <v>284.505755156032</v>
       </c>
       <c r="D133" t="n">
-        <v>279.0582953832721</v>
+        <v>279.6327451103039</v>
       </c>
       <c r="E133" t="n">
-        <v>280.1378784179688</v>
+        <v>281.0589904785156</v>
       </c>
       <c r="F133" t="n">
-        <v>9873300</v>
+        <v>11734400</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B134" t="n">
-        <v>282.0197247859078</v>
+        <v>285.7140887250632</v>
       </c>
       <c r="C134" t="n">
-        <v>284.505755156032</v>
+        <v>292.2510413422024</v>
       </c>
       <c r="D134" t="n">
-        <v>279.6327451103039</v>
+        <v>282.2277281014015</v>
       </c>
       <c r="E134" t="n">
-        <v>281.0589904785156</v>
+        <v>291.3497314453125</v>
       </c>
       <c r="F134" t="n">
-        <v>11734400</v>
+        <v>12956900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B135" t="n">
-        <v>285.7140887250632</v>
+        <v>292.567989087923</v>
       </c>
       <c r="C135" t="n">
-        <v>292.2510413422024</v>
+        <v>295.8661624411999</v>
       </c>
       <c r="D135" t="n">
-        <v>282.2277281014015</v>
+        <v>290.1116710297465</v>
       </c>
       <c r="E135" t="n">
-        <v>291.3497314453125</v>
+        <v>292.5580749511719</v>
       </c>
       <c r="F135" t="n">
-        <v>12956900</v>
+        <v>11267200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B136" t="n">
-        <v>292.567989087923</v>
+        <v>289.1212191631598</v>
       </c>
       <c r="C136" t="n">
-        <v>295.8661624411999</v>
+        <v>292.7957669317203</v>
       </c>
       <c r="D136" t="n">
-        <v>290.1116710297465</v>
+        <v>285.9616926535428</v>
       </c>
       <c r="E136" t="n">
-        <v>292.5580749511719</v>
+        <v>291.7855224609375</v>
       </c>
       <c r="F136" t="n">
-        <v>11267200</v>
+        <v>6669300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,25 +3979,25 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B137" t="n">
-        <v>289.1212191631598</v>
+        <v>292.7412191857173</v>
       </c>
       <c r="C137" t="n">
-        <v>292.7957669317203</v>
+        <v>295.4987855589938</v>
       </c>
       <c r="D137" t="n">
-        <v>285.9616926535428</v>
+        <v>291.8850906324002</v>
       </c>
       <c r="E137" t="n">
-        <v>291.7855224609375</v>
+        <v>294.125</v>
       </c>
       <c r="F137" t="n">
-        <v>6669300</v>
+        <v>7142600</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4005,25 +4005,25 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B138" t="n">
-        <v>292.7412191857173</v>
+        <v>291.8253790066561</v>
       </c>
       <c r="C138" t="n">
-        <v>295.4987855589938</v>
+        <v>296.8427544058445</v>
       </c>
       <c r="D138" t="n">
-        <v>291.8850906324002</v>
+        <v>291.3873498301165</v>
       </c>
       <c r="E138" t="n">
-        <v>294.125</v>
+        <v>296.0662536621094</v>
       </c>
       <c r="F138" t="n">
-        <v>7142600</v>
+        <v>7849100</v>
       </c>
       <c r="G138" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B139" t="n">
-        <v>291.8253790066561</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="C139" t="n">
-        <v>296.8427544058445</v>
+        <v>309.8640903908154</v>
       </c>
       <c r="D139" t="n">
-        <v>291.3873498301165</v>
+        <v>303.9606617936424</v>
       </c>
       <c r="E139" t="n">
-        <v>296.0662536621094</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="F139" t="n">
-        <v>7849100</v>
+        <v>10590200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B140" t="n">
-        <v>306.5888366699219</v>
+        <v>305.5734164156603</v>
       </c>
       <c r="C140" t="n">
-        <v>309.8640903908154</v>
+        <v>309.8640846884941</v>
       </c>
       <c r="D140" t="n">
-        <v>303.9606617936424</v>
+        <v>304.73715687535</v>
       </c>
       <c r="E140" t="n">
-        <v>306.5888366699219</v>
+        <v>308.938232421875</v>
       </c>
       <c r="F140" t="n">
-        <v>10590200</v>
+        <v>6586600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B141" t="n">
-        <v>305.5734164156603</v>
+        <v>308.6097380099313</v>
       </c>
       <c r="C141" t="n">
-        <v>309.8640846884941</v>
+        <v>308.9581744354404</v>
       </c>
       <c r="D141" t="n">
-        <v>304.73715687535</v>
+        <v>305.344449093958</v>
       </c>
       <c r="E141" t="n">
-        <v>308.938232421875</v>
+        <v>308.4803161621094</v>
       </c>
       <c r="F141" t="n">
-        <v>6586600</v>
+        <v>6069700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B142" t="n">
-        <v>308.6097380099313</v>
+        <v>306.0910825316173</v>
       </c>
       <c r="C142" t="n">
-        <v>308.9581744354404</v>
+        <v>312.3329523629397</v>
       </c>
       <c r="D142" t="n">
-        <v>305.344449093958</v>
+        <v>304.0900871089203</v>
       </c>
       <c r="E142" t="n">
-        <v>308.4803161621094</v>
+        <v>312.2732238769531</v>
       </c>
       <c r="F142" t="n">
-        <v>6069700</v>
+        <v>8318200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B143" t="n">
-        <v>306.0910825316173</v>
+        <v>308.4305432499699</v>
       </c>
       <c r="C143" t="n">
-        <v>312.3329523629397</v>
+        <v>312.9103618924516</v>
       </c>
       <c r="D143" t="n">
-        <v>304.0900871089203</v>
+        <v>307.4847916064935</v>
       </c>
       <c r="E143" t="n">
-        <v>312.2732238769531</v>
+        <v>309.7247009277344</v>
       </c>
       <c r="F143" t="n">
-        <v>8318200</v>
+        <v>11455500</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B144" t="n">
-        <v>308.4305432499699</v>
+        <v>312.5420354159922</v>
       </c>
       <c r="C144" t="n">
-        <v>312.9103618924516</v>
+        <v>312.8307129741003</v>
       </c>
       <c r="D144" t="n">
-        <v>307.4847916064935</v>
+        <v>302.8954898881459</v>
       </c>
       <c r="E144" t="n">
-        <v>309.7247009277344</v>
+        <v>304.5579833984375</v>
       </c>
       <c r="F144" t="n">
-        <v>11455500</v>
+        <v>9885800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B145" t="n">
-        <v>312.5420354159922</v>
+        <v>303.9805907681049</v>
       </c>
       <c r="C145" t="n">
-        <v>312.8307129741003</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="D145" t="n">
-        <v>302.8954898881459</v>
+        <v>303.8312695552229</v>
       </c>
       <c r="E145" t="n">
-        <v>304.5579833984375</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="F145" t="n">
-        <v>9885800</v>
+        <v>8208600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B146" t="n">
-        <v>303.9805907681049</v>
+        <v>311.068653468178</v>
       </c>
       <c r="C146" t="n">
-        <v>308.5599670410156</v>
+        <v>313.4877482505245</v>
       </c>
       <c r="D146" t="n">
-        <v>303.8312695552229</v>
+        <v>308.6993222963794</v>
       </c>
       <c r="E146" t="n">
-        <v>308.5599670410156</v>
+        <v>308.8984375</v>
       </c>
       <c r="F146" t="n">
-        <v>8208600</v>
+        <v>11082400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B147" t="n">
-        <v>311.068653468178</v>
+        <v>309.4559416581444</v>
       </c>
       <c r="C147" t="n">
-        <v>313.4877482505245</v>
+        <v>315.7077766193834</v>
       </c>
       <c r="D147" t="n">
-        <v>308.6993222963794</v>
+        <v>308.9780833700189</v>
       </c>
       <c r="E147" t="n">
-        <v>308.8984375</v>
+        <v>315.5683898925781</v>
       </c>
       <c r="F147" t="n">
-        <v>11082400</v>
+        <v>10772000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B148" t="n">
-        <v>309.4559416581444</v>
+        <v>316.0661368489313</v>
       </c>
       <c r="C148" t="n">
-        <v>315.7077766193834</v>
+        <v>318.8038038717339</v>
       </c>
       <c r="D148" t="n">
-        <v>308.9780833700189</v>
+        <v>311.3474041387296</v>
       </c>
       <c r="E148" t="n">
-        <v>315.5683898925781</v>
+        <v>311.5962829589844</v>
       </c>
       <c r="F148" t="n">
-        <v>10772000</v>
+        <v>7084300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B149" t="n">
-        <v>316.0661368489313</v>
+        <v>313.4379903862348</v>
       </c>
       <c r="C149" t="n">
-        <v>318.8038038717339</v>
+        <v>313.7366328164263</v>
       </c>
       <c r="D149" t="n">
-        <v>311.3474041387296</v>
+        <v>310.5410372905177</v>
       </c>
       <c r="E149" t="n">
-        <v>311.5962829589844</v>
+        <v>311.6161804199219</v>
       </c>
       <c r="F149" t="n">
-        <v>7084300</v>
+        <v>5545900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B150" t="n">
-        <v>313.4379903862348</v>
+        <v>312.1139549773267</v>
       </c>
       <c r="C150" t="n">
-        <v>313.7366328164263</v>
+        <v>313.5773637260273</v>
       </c>
       <c r="D150" t="n">
-        <v>310.5410372905177</v>
+        <v>307.5047445243564</v>
       </c>
       <c r="E150" t="n">
-        <v>311.6161804199219</v>
+        <v>310.2921752929688</v>
       </c>
       <c r="F150" t="n">
-        <v>5545900</v>
+        <v>6969700</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B151" t="n">
-        <v>312.1139549773267</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="C151" t="n">
-        <v>313.5773637260273</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="D151" t="n">
-        <v>307.5047445243564</v>
+        <v>306.5092257615542</v>
       </c>
       <c r="E151" t="n">
-        <v>310.2921752929688</v>
+        <v>306.8974609375</v>
       </c>
       <c r="F151" t="n">
-        <v>6969700</v>
+        <v>5215300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B152" t="n">
-        <v>309.7545850384977</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="C152" t="n">
-        <v>309.7545850384977</v>
+        <v>311.1781431330245</v>
       </c>
       <c r="D152" t="n">
-        <v>306.5092257615542</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="E152" t="n">
-        <v>306.8974609375</v>
+        <v>310.232421875</v>
       </c>
       <c r="F152" t="n">
-        <v>5215300</v>
+        <v>7925300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B153" t="n">
-        <v>305.5037244427344</v>
+        <v>313.7864355589005</v>
       </c>
       <c r="C153" t="n">
-        <v>311.1781431330245</v>
+        <v>314.035314384572</v>
       </c>
       <c r="D153" t="n">
-        <v>305.5037244427344</v>
+        <v>309.7745101043047</v>
       </c>
       <c r="E153" t="n">
-        <v>310.232421875</v>
+        <v>310.0532531738281</v>
       </c>
       <c r="F153" t="n">
-        <v>7925300</v>
+        <v>7398600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B154" t="n">
-        <v>313.7864355589005</v>
+        <v>309.1771855961317</v>
       </c>
       <c r="C154" t="n">
-        <v>314.035314384572</v>
+        <v>310.6505287563671</v>
       </c>
       <c r="D154" t="n">
-        <v>309.7745101043047</v>
+        <v>305.9118967162461</v>
       </c>
       <c r="E154" t="n">
-        <v>310.0532531738281</v>
+        <v>307.8630981445312</v>
       </c>
       <c r="F154" t="n">
-        <v>7398600</v>
+        <v>8031800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B155" t="n">
-        <v>309.1771855961317</v>
+        <v>305.6928786901284</v>
       </c>
       <c r="C155" t="n">
-        <v>310.6505287563671</v>
+        <v>312.6913497643884</v>
       </c>
       <c r="D155" t="n">
-        <v>305.9118967162461</v>
+        <v>305.1951210592971</v>
       </c>
       <c r="E155" t="n">
-        <v>307.8630981445312</v>
+        <v>311.8252563476562</v>
       </c>
       <c r="F155" t="n">
-        <v>8031800</v>
+        <v>8865400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B156" t="n">
-        <v>305.6928786901284</v>
+        <v>312.5420381202088</v>
       </c>
       <c r="C156" t="n">
-        <v>312.6913497643884</v>
+        <v>314.6624601726697</v>
       </c>
       <c r="D156" t="n">
-        <v>305.1951210592971</v>
+        <v>310.431520181067</v>
       </c>
       <c r="E156" t="n">
-        <v>311.8252563476562</v>
+        <v>311.0686645507812</v>
       </c>
       <c r="F156" t="n">
-        <v>8865400</v>
+        <v>6135400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B157" t="n">
-        <v>312.5420381202088</v>
+        <v>309.2269452093906</v>
       </c>
       <c r="C157" t="n">
-        <v>314.6624601726697</v>
+        <v>309.2568094519629</v>
       </c>
       <c r="D157" t="n">
-        <v>310.431520181067</v>
+        <v>305.1353920734132</v>
       </c>
       <c r="E157" t="n">
-        <v>311.0686645507812</v>
+        <v>306.270263671875</v>
       </c>
       <c r="F157" t="n">
-        <v>6135400</v>
+        <v>7338200</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B158" t="n">
-        <v>309.2269452093906</v>
+        <v>306.3299974055641</v>
       </c>
       <c r="C158" t="n">
-        <v>309.2568094519629</v>
+        <v>309.5753869306937</v>
       </c>
       <c r="D158" t="n">
-        <v>305.1353920734132</v>
+        <v>305.42407485773</v>
       </c>
       <c r="E158" t="n">
-        <v>306.270263671875</v>
+        <v>308.0124206542969</v>
       </c>
       <c r="F158" t="n">
-        <v>7338200</v>
+        <v>6316800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B159" t="n">
-        <v>306.3299974055641</v>
+        <v>310.0532528884956</v>
       </c>
       <c r="C159" t="n">
-        <v>309.5753869306937</v>
+        <v>314.8416790595512</v>
       </c>
       <c r="D159" t="n">
-        <v>305.42407485773</v>
+        <v>309.9536952821754</v>
       </c>
       <c r="E159" t="n">
-        <v>308.0124206542969</v>
+        <v>313.4877624511719</v>
       </c>
       <c r="F159" t="n">
-        <v>6316800</v>
+        <v>8629500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B160" t="n">
-        <v>310.0532528884956</v>
+        <v>313.2388767644321</v>
       </c>
       <c r="C160" t="n">
-        <v>314.8416790595512</v>
+        <v>314.8814709002291</v>
       </c>
       <c r="D160" t="n">
-        <v>309.9536952821754</v>
+        <v>304.7670623908274</v>
       </c>
       <c r="E160" t="n">
-        <v>313.4877624511719</v>
+        <v>304.8964538574219</v>
       </c>
       <c r="F160" t="n">
-        <v>8629500</v>
+        <v>8359600</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B161" t="n">
-        <v>313.2388767644321</v>
+        <v>306.8675912418493</v>
       </c>
       <c r="C161" t="n">
-        <v>314.8814709002291</v>
+        <v>307.6042628420606</v>
       </c>
       <c r="D161" t="n">
-        <v>304.7670623908274</v>
+        <v>299.1523476664256</v>
       </c>
       <c r="E161" t="n">
-        <v>304.8964538574219</v>
+        <v>300.7451782226562</v>
       </c>
       <c r="F161" t="n">
-        <v>8359600</v>
+        <v>9464300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B162" t="n">
-        <v>306.8675912418493</v>
+        <v>300.7451596100784</v>
       </c>
       <c r="C162" t="n">
-        <v>307.6042628420606</v>
+        <v>301.8302675742967</v>
       </c>
       <c r="D162" t="n">
-        <v>299.1523476664256</v>
+        <v>297.5395993270601</v>
       </c>
       <c r="E162" t="n">
-        <v>300.7451782226562</v>
+        <v>298.6545715332031</v>
       </c>
       <c r="F162" t="n">
-        <v>9464300</v>
+        <v>9512000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B163" t="n">
-        <v>300.7451596100784</v>
+        <v>298.6744753830843</v>
       </c>
       <c r="C163" t="n">
-        <v>301.8302675742967</v>
+        <v>304.6873960201211</v>
       </c>
       <c r="D163" t="n">
-        <v>297.5395993270601</v>
+        <v>294.2245209852311</v>
       </c>
       <c r="E163" t="n">
-        <v>298.6545715332031</v>
+        <v>303.5126953125</v>
       </c>
       <c r="F163" t="n">
-        <v>9512000</v>
+        <v>9498200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B164" t="n">
-        <v>298.6744753830843</v>
+        <v>300.9144028967509</v>
       </c>
       <c r="C164" t="n">
-        <v>304.6873960201211</v>
+        <v>301.6411400127173</v>
       </c>
       <c r="D164" t="n">
-        <v>294.2245209852311</v>
+        <v>298.7242874353194</v>
       </c>
       <c r="E164" t="n">
-        <v>303.5126953125</v>
+        <v>298.9034729003906</v>
       </c>
       <c r="F164" t="n">
-        <v>9498200</v>
+        <v>7709500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B165" t="n">
-        <v>300.9144028967509</v>
+        <v>300.8945046380796</v>
       </c>
       <c r="C165" t="n">
-        <v>301.6411400127173</v>
+        <v>302.387777613951</v>
       </c>
       <c r="D165" t="n">
-        <v>298.7242874353194</v>
+        <v>297.4699295162906</v>
       </c>
       <c r="E165" t="n">
-        <v>298.9034729003906</v>
+        <v>298.5650024414062</v>
       </c>
       <c r="F165" t="n">
-        <v>7709500</v>
+        <v>7364300</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B166" t="n">
-        <v>300.8945046380796</v>
+        <v>298.8636262885424</v>
       </c>
       <c r="C166" t="n">
-        <v>302.387777613951</v>
+        <v>299.4410421498196</v>
       </c>
       <c r="D166" t="n">
-        <v>297.4699295162906</v>
+        <v>295.1205095874812</v>
       </c>
       <c r="E166" t="n">
-        <v>298.5650024414062</v>
+        <v>296.4743957519531</v>
       </c>
       <c r="F166" t="n">
-        <v>7364300</v>
+        <v>8699300</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B167" t="n">
-        <v>298.8636262885424</v>
+        <v>296.6635495230975</v>
       </c>
       <c r="C167" t="n">
-        <v>299.4410421498196</v>
+        <v>299.908939014877</v>
       </c>
       <c r="D167" t="n">
-        <v>295.1205095874812</v>
+        <v>295.8870488301784</v>
       </c>
       <c r="E167" t="n">
-        <v>296.4743957519531</v>
+        <v>299.3813171386719</v>
       </c>
       <c r="F167" t="n">
-        <v>8699300</v>
+        <v>7546300</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B168" t="n">
-        <v>296.6635495230975</v>
+        <v>299.7396822358739</v>
       </c>
       <c r="C168" t="n">
-        <v>299.908939014877</v>
+        <v>300.436555061437</v>
       </c>
       <c r="D168" t="n">
-        <v>295.8870488301784</v>
+        <v>293.935841710235</v>
       </c>
       <c r="E168" t="n">
-        <v>299.3813171386719</v>
+        <v>294.3738708496094</v>
       </c>
       <c r="F168" t="n">
-        <v>7546300</v>
+        <v>8066900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B169" t="n">
-        <v>299.7396822358739</v>
+        <v>295.3694126574367</v>
       </c>
       <c r="C169" t="n">
-        <v>300.436555061437</v>
+        <v>301.57145376365</v>
       </c>
       <c r="D169" t="n">
-        <v>293.935841710235</v>
+        <v>292.3530024013792</v>
       </c>
       <c r="E169" t="n">
-        <v>294.3738708496094</v>
+        <v>300.625732421875</v>
       </c>
       <c r="F169" t="n">
-        <v>8066900</v>
+        <v>9327000</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B170" t="n">
-        <v>295.3694126574367</v>
+        <v>299.8790926087445</v>
       </c>
       <c r="C170" t="n">
-        <v>301.57145376365</v>
+        <v>302.6167597554335</v>
       </c>
       <c r="D170" t="n">
-        <v>292.3530024013792</v>
+        <v>298.8636475324957</v>
       </c>
       <c r="E170" t="n">
-        <v>300.625732421875</v>
+        <v>301.6411437988281</v>
       </c>
       <c r="F170" t="n">
-        <v>9327000</v>
+        <v>7874400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B171" t="n">
-        <v>299.8790926087445</v>
+        <v>303.3135932887391</v>
       </c>
       <c r="C171" t="n">
-        <v>302.6167597554335</v>
+        <v>306.0711901040885</v>
       </c>
       <c r="D171" t="n">
-        <v>298.8636475324957</v>
+        <v>302.4773640852478</v>
       </c>
       <c r="E171" t="n">
-        <v>301.6411437988281</v>
+        <v>305.0059814453125</v>
       </c>
       <c r="F171" t="n">
-        <v>7874400</v>
+        <v>5973900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B172" t="n">
-        <v>303.3135932887391</v>
+        <v>307.1065011172144</v>
       </c>
       <c r="C172" t="n">
-        <v>306.0711901040885</v>
+        <v>308.5400455607295</v>
       </c>
       <c r="D172" t="n">
-        <v>302.4773640852478</v>
+        <v>304.0701916446211</v>
       </c>
       <c r="E172" t="n">
-        <v>305.0059814453125</v>
+        <v>305.3643493652344</v>
       </c>
       <c r="F172" t="n">
-        <v>5973900</v>
+        <v>7725400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B173" t="n">
-        <v>307.1065011172144</v>
+        <v>303.6321536663258</v>
       </c>
       <c r="C173" t="n">
-        <v>308.5400455607295</v>
+        <v>304.5281113223131</v>
       </c>
       <c r="D173" t="n">
-        <v>304.0701916446211</v>
+        <v>294.4236375305438</v>
       </c>
       <c r="E173" t="n">
-        <v>305.3643493652344</v>
+        <v>297.9378051757812</v>
       </c>
       <c r="F173" t="n">
-        <v>7725400</v>
+        <v>11779200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B174" t="n">
-        <v>303.6321536663258</v>
+        <v>296.2354906683788</v>
       </c>
       <c r="C174" t="n">
-        <v>304.5281113223131</v>
+        <v>299.7197941661088</v>
       </c>
       <c r="D174" t="n">
-        <v>294.4236375305438</v>
+        <v>294.4236455581874</v>
       </c>
       <c r="E174" t="n">
-        <v>297.9378051757812</v>
+        <v>295.3992614746094</v>
       </c>
       <c r="F174" t="n">
-        <v>11779200</v>
+        <v>9757700</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B175" t="n">
-        <v>296.2354906683788</v>
+        <v>295.070728717322</v>
       </c>
       <c r="C175" t="n">
-        <v>299.7197941661088</v>
+        <v>298.5351328968941</v>
       </c>
       <c r="D175" t="n">
-        <v>294.4236455581874</v>
+        <v>293.8761285862639</v>
       </c>
       <c r="E175" t="n">
-        <v>295.3992614746094</v>
+        <v>297.9676818847656</v>
       </c>
       <c r="F175" t="n">
-        <v>9757700</v>
+        <v>13969000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B176" t="n">
-        <v>295.070728717322</v>
+        <v>296.3549462063085</v>
       </c>
       <c r="C176" t="n">
-        <v>298.5351328968941</v>
+        <v>298.2065900448191</v>
       </c>
       <c r="D176" t="n">
-        <v>293.8761285862639</v>
+        <v>293.9457858606032</v>
       </c>
       <c r="E176" t="n">
-        <v>297.9676818847656</v>
+        <v>295.2499084472656</v>
       </c>
       <c r="F176" t="n">
-        <v>13969000</v>
+        <v>7930000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B177" t="n">
-        <v>296.3549462063085</v>
+        <v>295.170270518017</v>
       </c>
       <c r="C177" t="n">
-        <v>298.2065900448191</v>
+        <v>300.7152977310929</v>
       </c>
       <c r="D177" t="n">
-        <v>293.9457858606032</v>
+        <v>293.9457758280521</v>
       </c>
       <c r="E177" t="n">
-        <v>295.2499084472656</v>
+        <v>299.6102600097656</v>
       </c>
       <c r="F177" t="n">
-        <v>7930000</v>
+        <v>8296200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B178" t="n">
-        <v>295.170270518017</v>
+        <v>298.5749714904202</v>
       </c>
       <c r="C178" t="n">
-        <v>300.7152977310929</v>
+        <v>300.6058008918799</v>
       </c>
       <c r="D178" t="n">
-        <v>293.9457758280521</v>
+        <v>295.2300241797341</v>
       </c>
       <c r="E178" t="n">
-        <v>299.6102600097656</v>
+        <v>299.5007934570312</v>
       </c>
       <c r="F178" t="n">
-        <v>8296200</v>
+        <v>7003900</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B179" t="n">
-        <v>298.5749714904202</v>
+        <v>304.3688300919619</v>
       </c>
       <c r="C179" t="n">
-        <v>300.6058008918799</v>
+        <v>311.5066879726736</v>
       </c>
       <c r="D179" t="n">
-        <v>295.2300241797341</v>
+        <v>303.0746723882986</v>
       </c>
       <c r="E179" t="n">
-        <v>299.5007934570312</v>
+        <v>309.4957580566406</v>
       </c>
       <c r="F179" t="n">
-        <v>7003900</v>
+        <v>10345200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B180" t="n">
-        <v>304.3688300919619</v>
+        <v>312.8805189963161</v>
       </c>
       <c r="C180" t="n">
-        <v>311.5066879726736</v>
+        <v>313.5873263681962</v>
       </c>
       <c r="D180" t="n">
-        <v>303.0746723882986</v>
+        <v>308.211549706599</v>
       </c>
       <c r="E180" t="n">
-        <v>309.4957580566406</v>
+        <v>310.9691162109375</v>
       </c>
       <c r="F180" t="n">
-        <v>10345200</v>
+        <v>9118800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B181" t="n">
-        <v>312.8805189963161</v>
+        <v>311.8451695343703</v>
       </c>
       <c r="C181" t="n">
-        <v>313.5873263681962</v>
+        <v>314.881479064701</v>
       </c>
       <c r="D181" t="n">
-        <v>308.211549706599</v>
+        <v>309.3862455138746</v>
       </c>
       <c r="E181" t="n">
-        <v>310.9691162109375</v>
+        <v>309.7147521972656</v>
       </c>
       <c r="F181" t="n">
-        <v>9118800</v>
+        <v>6827000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B182" t="n">
-        <v>311.8451695343703</v>
+        <v>312.1040028799189</v>
       </c>
       <c r="C182" t="n">
-        <v>314.881479064701</v>
+        <v>315.0009559692908</v>
       </c>
       <c r="D182" t="n">
-        <v>309.3862455138746</v>
+        <v>307.6241841525692</v>
       </c>
       <c r="E182" t="n">
-        <v>309.7147521972656</v>
+        <v>311.2976379394531</v>
       </c>
       <c r="F182" t="n">
-        <v>6827000</v>
+        <v>11594600</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B183" t="n">
-        <v>312.1040028799189</v>
+        <v>311.1582462393224</v>
       </c>
       <c r="C183" t="n">
-        <v>315.0009559692908</v>
+        <v>313.3384270822022</v>
       </c>
       <c r="D183" t="n">
-        <v>307.6241841525692</v>
+        <v>307.6440785979976</v>
       </c>
       <c r="E183" t="n">
-        <v>311.2976379394531</v>
+        <v>307.7536010742188</v>
       </c>
       <c r="F183" t="n">
-        <v>11594600</v>
+        <v>7446200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B184" t="n">
-        <v>311.1582462393224</v>
+        <v>308.1717081621576</v>
       </c>
       <c r="C184" t="n">
-        <v>313.3384270822022</v>
+        <v>313.3085706612414</v>
       </c>
       <c r="D184" t="n">
-        <v>307.6440785979976</v>
+        <v>307.4947650619962</v>
       </c>
       <c r="E184" t="n">
-        <v>307.7536010742188</v>
+        <v>312.0840759277344</v>
       </c>
       <c r="F184" t="n">
-        <v>7446200</v>
+        <v>9116600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B185" t="n">
-        <v>308.1717081621576</v>
+        <v>314.5529794375797</v>
       </c>
       <c r="C185" t="n">
-        <v>313.3085706612414</v>
+        <v>319.8590627688811</v>
       </c>
       <c r="D185" t="n">
-        <v>307.4947650619962</v>
+        <v>314.1348496322589</v>
       </c>
       <c r="E185" t="n">
-        <v>312.0840759277344</v>
+        <v>319.2816772460938</v>
       </c>
       <c r="F185" t="n">
-        <v>9116600</v>
+        <v>7426200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B186" t="n">
-        <v>314.5529794375797</v>
+        <v>322.4673390673774</v>
       </c>
       <c r="C186" t="n">
-        <v>319.8590627688811</v>
+        <v>324.4583697274161</v>
       </c>
       <c r="D186" t="n">
-        <v>314.1348496322589</v>
+        <v>317.4101041776777</v>
       </c>
       <c r="E186" t="n">
-        <v>319.2816772460938</v>
+        <v>317.9675903320312</v>
       </c>
       <c r="F186" t="n">
-        <v>7426200</v>
+        <v>7988900</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B187" t="n">
-        <v>322.4673390673774</v>
+        <v>322.8455866314347</v>
       </c>
       <c r="C187" t="n">
-        <v>324.4583697274161</v>
+        <v>330.2621874699331</v>
       </c>
       <c r="D187" t="n">
-        <v>317.4101041776777</v>
+        <v>322.5668435738929</v>
       </c>
       <c r="E187" t="n">
-        <v>317.9675903320312</v>
+        <v>329.6549377441406</v>
       </c>
       <c r="F187" t="n">
-        <v>7988900</v>
+        <v>11094900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B188" t="n">
-        <v>322.8455866314347</v>
+        <v>330.6902497468859</v>
       </c>
       <c r="C188" t="n">
-        <v>330.2621874699331</v>
+        <v>336.2551763704633</v>
       </c>
       <c r="D188" t="n">
-        <v>322.5668435738929</v>
+        <v>330.0133066656099</v>
       </c>
       <c r="E188" t="n">
-        <v>329.6549377441406</v>
+        <v>331.9645080566406</v>
       </c>
       <c r="F188" t="n">
-        <v>11094900</v>
+        <v>12246400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B189" t="n">
-        <v>330.6902497468859</v>
+        <v>335.4388795655989</v>
       </c>
       <c r="C189" t="n">
-        <v>336.2551763704633</v>
+        <v>336.5737511659094</v>
       </c>
       <c r="D189" t="n">
-        <v>330.0133066656099</v>
+        <v>322.7062308624821</v>
       </c>
       <c r="E189" t="n">
-        <v>331.9645080566406</v>
+        <v>323.761474609375</v>
       </c>
       <c r="F189" t="n">
-        <v>12246400</v>
+        <v>20111000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B190" t="n">
-        <v>335.4388795655989</v>
+        <v>328.221392261561</v>
       </c>
       <c r="C190" t="n">
-        <v>336.5737511659094</v>
+        <v>331.2776010100568</v>
       </c>
       <c r="D190" t="n">
-        <v>322.7062308624821</v>
+        <v>325.2846101022313</v>
       </c>
       <c r="E190" t="n">
-        <v>323.761474609375</v>
+        <v>329.993408203125</v>
       </c>
       <c r="F190" t="n">
-        <v>20111000</v>
+        <v>10182500</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B191" t="n">
-        <v>328.221392261561</v>
+        <v>327.9924099173137</v>
       </c>
       <c r="C191" t="n">
-        <v>331.2776010100568</v>
+        <v>333.8659438033595</v>
       </c>
       <c r="D191" t="n">
-        <v>325.2846101022313</v>
+        <v>325.7425357353925</v>
       </c>
       <c r="E191" t="n">
-        <v>329.993408203125</v>
+        <v>332.6414794921875</v>
       </c>
       <c r="F191" t="n">
-        <v>10182500</v>
+        <v>7582200</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B192" t="n">
-        <v>327.9924099173137</v>
+        <v>331.5762891678024</v>
       </c>
       <c r="C192" t="n">
-        <v>333.8659438033595</v>
+        <v>333.0297330031709</v>
       </c>
       <c r="D192" t="n">
-        <v>325.7425357353925</v>
+        <v>328.291070440402</v>
       </c>
       <c r="E192" t="n">
-        <v>332.6414794921875</v>
+        <v>331.95458984375</v>
       </c>
       <c r="F192" t="n">
-        <v>7582200</v>
+        <v>7907400</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B193" t="n">
-        <v>331.5762891678024</v>
+        <v>333.4577793441399</v>
       </c>
       <c r="C193" t="n">
-        <v>333.0297330031709</v>
+        <v>341.909724468194</v>
       </c>
       <c r="D193" t="n">
-        <v>328.291070440402</v>
+        <v>333.2586945227413</v>
       </c>
       <c r="E193" t="n">
-        <v>331.95458984375</v>
+        <v>333.6170654296875</v>
       </c>
       <c r="F193" t="n">
-        <v>7907400</v>
+        <v>10043100</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B194" t="n">
-        <v>333.4577793441399</v>
+        <v>334.4931229022353</v>
       </c>
       <c r="C194" t="n">
-        <v>341.909724468194</v>
+        <v>334.8913229247855</v>
       </c>
       <c r="D194" t="n">
-        <v>333.2586945227413</v>
+        <v>326.0312433050061</v>
       </c>
       <c r="E194" t="n">
-        <v>333.6170654296875</v>
+        <v>327.5742797851562</v>
       </c>
       <c r="F194" t="n">
-        <v>10043100</v>
+        <v>17640900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B195" t="n">
-        <v>334.4931229022353</v>
+        <v>326.8077430430495</v>
       </c>
       <c r="C195" t="n">
-        <v>334.8913229247855</v>
+        <v>330.8993264933345</v>
       </c>
       <c r="D195" t="n">
-        <v>326.0312433050061</v>
+        <v>325.7325999471821</v>
       </c>
       <c r="E195" t="n">
-        <v>327.5742797851562</v>
+        <v>327.9127807617188</v>
       </c>
       <c r="F195" t="n">
-        <v>17640900</v>
+        <v>7981800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B196" t="n">
-        <v>326.8077430430495</v>
+        <v>327.4150312810326</v>
       </c>
       <c r="C196" t="n">
-        <v>330.8993264933345</v>
+        <v>328.9580677951163</v>
       </c>
       <c r="D196" t="n">
-        <v>325.7325999471821</v>
+        <v>325.2149206632551</v>
       </c>
       <c r="E196" t="n">
-        <v>327.9127807617188</v>
+        <v>325.8619995117188</v>
       </c>
       <c r="F196" t="n">
-        <v>7981800</v>
+        <v>8080100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B197" t="n">
-        <v>327.4150312810326</v>
+        <v>326.8973584256916</v>
       </c>
       <c r="C197" t="n">
-        <v>328.9580677951163</v>
+        <v>334.1347741939035</v>
       </c>
       <c r="D197" t="n">
-        <v>325.2149206632551</v>
+        <v>323.5524415571975</v>
       </c>
       <c r="E197" t="n">
-        <v>325.8619995117188</v>
+        <v>332.5718078613281</v>
       </c>
       <c r="F197" t="n">
-        <v>8080100</v>
+        <v>15210200</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B198" t="n">
-        <v>326.8973584256916</v>
+        <v>336.5040683580973</v>
       </c>
       <c r="C198" t="n">
-        <v>334.1347741939035</v>
+        <v>338.4751995750331</v>
       </c>
       <c r="D198" t="n">
-        <v>323.5524415571975</v>
+        <v>330.2820977776739</v>
       </c>
       <c r="E198" t="n">
-        <v>332.5718078613281</v>
+        <v>332.9700012207031</v>
       </c>
       <c r="F198" t="n">
-        <v>15210200</v>
+        <v>8413900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,25 +5591,25 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B199" t="n">
-        <v>336.5040683580973</v>
+        <v>335</v>
       </c>
       <c r="C199" t="n">
-        <v>338.4751995750331</v>
+        <v>339.7200012207031</v>
       </c>
       <c r="D199" t="n">
-        <v>330.2820977776739</v>
+        <v>334.1099853515625</v>
       </c>
       <c r="E199" t="n">
-        <v>332.9700012207031</v>
+        <v>337.7200012207031</v>
       </c>
       <c r="F199" t="n">
-        <v>8413900</v>
+        <v>8673500</v>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -5617,25 +5617,25 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B200" t="n">
-        <v>335</v>
+        <v>340.9800109863281</v>
       </c>
       <c r="C200" t="n">
-        <v>339.7200012207031</v>
+        <v>341.3999938964844</v>
       </c>
       <c r="D200" t="n">
-        <v>334.1099853515625</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E200" t="n">
-        <v>337.7200012207031</v>
+        <v>339.2200012207031</v>
       </c>
       <c r="F200" t="n">
-        <v>8673500</v>
+        <v>7115800</v>
       </c>
       <c r="G200" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B201" t="n">
-        <v>340.9800109863281</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="C201" t="n">
-        <v>341.3999938964844</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="D201" t="n">
-        <v>337.0899963378906</v>
+        <v>330.1300048828125</v>
       </c>
       <c r="E201" t="n">
-        <v>339.2200012207031</v>
+        <v>330.6199951171875</v>
       </c>
       <c r="F201" t="n">
-        <v>7115800</v>
+        <v>18505200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B202" t="n">
-        <v>336.5299987792969</v>
+        <v>331.4599914550781</v>
       </c>
       <c r="C202" t="n">
-        <v>336.5299987792969</v>
+        <v>337</v>
       </c>
       <c r="D202" t="n">
-        <v>330.1300048828125</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="E202" t="n">
-        <v>330.6199951171875</v>
+        <v>335.4700012207031</v>
       </c>
       <c r="F202" t="n">
-        <v>18505200</v>
+        <v>15570600</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B203" t="n">
-        <v>331.4599914550781</v>
+        <v>337.4700012207031</v>
       </c>
       <c r="C203" t="n">
-        <v>337</v>
+        <v>338.5899963378906</v>
       </c>
       <c r="D203" t="n">
-        <v>330.8099975585938</v>
+        <v>335.7699890136719</v>
       </c>
       <c r="E203" t="n">
-        <v>335.4700012207031</v>
+        <v>336.4700012207031</v>
       </c>
       <c r="F203" t="n">
-        <v>15570600</v>
+        <v>6299000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B204" t="n">
-        <v>337.4700012207031</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="C204" t="n">
-        <v>338.5899963378906</v>
+        <v>338.3500061035156</v>
       </c>
       <c r="D204" t="n">
-        <v>335.7699890136719</v>
+        <v>332.5</v>
       </c>
       <c r="E204" t="n">
-        <v>336.4700012207031</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="F204" t="n">
-        <v>6299000</v>
+        <v>7120300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B205" t="n">
-        <v>338.3399963378906</v>
+        <v>327</v>
       </c>
       <c r="C205" t="n">
-        <v>338.3500061035156</v>
+        <v>344.7300109863281</v>
       </c>
       <c r="D205" t="n">
-        <v>332.5</v>
+        <v>325.75</v>
       </c>
       <c r="E205" t="n">
-        <v>334.5299987792969</v>
+        <v>342.8900146484375</v>
       </c>
       <c r="F205" t="n">
-        <v>7120300</v>
+        <v>14537900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>327</v>
+        <v>345.8500061035156</v>
       </c>
       <c r="C206" t="n">
-        <v>344.7300109863281</v>
+        <v>351.239990234375</v>
       </c>
       <c r="D206" t="n">
-        <v>325.75</v>
+        <v>344.0499877929688</v>
       </c>
       <c r="E206" t="n">
-        <v>342.8900146484375</v>
+        <v>346.9100036621094</v>
       </c>
       <c r="F206" t="n">
-        <v>14537900</v>
+        <v>10750000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B207" t="n">
-        <v>345.8500061035156</v>
+        <v>349.2799987792969</v>
       </c>
       <c r="C207" t="n">
-        <v>351.239990234375</v>
+        <v>349.3399963378906</v>
       </c>
       <c r="D207" t="n">
-        <v>344.0499877929688</v>
+        <v>341.1099853515625</v>
       </c>
       <c r="E207" t="n">
-        <v>346.9100036621094</v>
+        <v>343.1499938964844</v>
       </c>
       <c r="F207" t="n">
-        <v>10750000</v>
+        <v>12432400</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B208" t="n">
-        <v>349.2799987792969</v>
+        <v>339.0299987792969</v>
       </c>
       <c r="C208" t="n">
-        <v>349.3399963378906</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="D208" t="n">
-        <v>341.1099853515625</v>
+        <v>335.0499877929688</v>
       </c>
       <c r="E208" t="n">
-        <v>343.1499938964844</v>
+        <v>341.1000061035156</v>
       </c>
       <c r="F208" t="n">
-        <v>12432400</v>
+        <v>9250900</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B209" t="n">
-        <v>339.0299987792969</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="C209" t="n">
-        <v>346.1300048828125</v>
+        <v>344.260009765625</v>
       </c>
       <c r="D209" t="n">
-        <v>335.0499877929688</v>
+        <v>337.3699951171875</v>
       </c>
       <c r="E209" t="n">
-        <v>341.1000061035156</v>
+        <v>338.8699951171875</v>
       </c>
       <c r="F209" t="n">
-        <v>9250900</v>
+        <v>7723300</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B210" t="n">
-        <v>341.7999877929688</v>
+        <v>340.1199951171875</v>
       </c>
       <c r="C210" t="n">
-        <v>344.260009765625</v>
+        <v>345.739990234375</v>
       </c>
       <c r="D210" t="n">
-        <v>337.3699951171875</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E210" t="n">
-        <v>338.8699951171875</v>
+        <v>345.2300109863281</v>
       </c>
       <c r="F210" t="n">
-        <v>7723300</v>
+        <v>6015300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B211" t="n">
-        <v>340.1199951171875</v>
+        <v>345.0700073242188</v>
       </c>
       <c r="C211" t="n">
-        <v>345.739990234375</v>
+        <v>349.0700073242188</v>
       </c>
       <c r="D211" t="n">
-        <v>337.2999877929688</v>
+        <v>344.25</v>
       </c>
       <c r="E211" t="n">
-        <v>345.2300109863281</v>
+        <v>348.2099914550781</v>
       </c>
       <c r="F211" t="n">
-        <v>6015300</v>
+        <v>8040200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B212" t="n">
-        <v>345.0700073242188</v>
+        <v>346.5799865722656</v>
       </c>
       <c r="C212" t="n">
-        <v>349.0700073242188</v>
+        <v>349.9200134277344</v>
       </c>
       <c r="D212" t="n">
-        <v>344.25</v>
+        <v>345.4200134277344</v>
       </c>
       <c r="E212" t="n">
-        <v>348.2099914550781</v>
+        <v>349.8999938964844</v>
       </c>
       <c r="F212" t="n">
-        <v>8040200</v>
+        <v>10913000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B213" t="n">
-        <v>346.5799865722656</v>
+        <v>350.6400146484375</v>
       </c>
       <c r="C213" t="n">
-        <v>349.9200134277344</v>
+        <v>353.3699951171875</v>
       </c>
       <c r="D213" t="n">
-        <v>345.4200134277344</v>
+        <v>347.5</v>
       </c>
       <c r="E213" t="n">
-        <v>349.8999938964844</v>
+        <v>353.2099914550781</v>
       </c>
       <c r="F213" t="n">
-        <v>10913000</v>
+        <v>7520800</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B214" t="n">
-        <v>350.6400146484375</v>
+        <v>357.8900146484375</v>
       </c>
       <c r="C214" t="n">
-        <v>353.3699951171875</v>
+        <v>359.0499877929688</v>
       </c>
       <c r="D214" t="n">
-        <v>347.5</v>
+        <v>352.5799865722656</v>
       </c>
       <c r="E214" t="n">
-        <v>353.2099914550781</v>
+        <v>356.2000122070312</v>
       </c>
       <c r="F214" t="n">
-        <v>7520800</v>
+        <v>7884900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B215" t="n">
-        <v>357.8900146484375</v>
+        <v>357.2999877929688</v>
       </c>
       <c r="C215" t="n">
-        <v>359.0499877929688</v>
+        <v>359.2999877929688</v>
       </c>
       <c r="D215" t="n">
-        <v>352.5799865722656</v>
+        <v>354.1499938964844</v>
       </c>
       <c r="E215" t="n">
-        <v>356.2000122070312</v>
+        <v>357.3099975585938</v>
       </c>
       <c r="F215" t="n">
-        <v>7884900</v>
+        <v>6533800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B216" t="n">
-        <v>357.2999877929688</v>
+        <v>356.5</v>
       </c>
       <c r="C216" t="n">
-        <v>359.2999877929688</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D216" t="n">
-        <v>354.1499938964844</v>
+        <v>343.7799987792969</v>
       </c>
       <c r="E216" t="n">
-        <v>357.3099975585938</v>
+        <v>344.7099914550781</v>
       </c>
       <c r="F216" t="n">
-        <v>6533800</v>
+        <v>8265300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B217" t="n">
-        <v>356.5</v>
+        <v>347.5400085449219</v>
       </c>
       <c r="C217" t="n">
-        <v>357.3699951171875</v>
+        <v>352.2799987792969</v>
       </c>
       <c r="D217" t="n">
-        <v>343.7799987792969</v>
+        <v>345.3699951171875</v>
       </c>
       <c r="E217" t="n">
-        <v>344.7099914550781</v>
+        <v>350.8500061035156</v>
       </c>
       <c r="F217" t="n">
-        <v>8265300</v>
+        <v>7606500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B218" t="n">
-        <v>347.5400085449219</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C218" t="n">
-        <v>352.2799987792969</v>
+        <v>354.4700012207031</v>
       </c>
       <c r="D218" t="n">
-        <v>345.3699951171875</v>
+        <v>349.7000122070312</v>
       </c>
       <c r="E218" t="n">
-        <v>350.8500061035156</v>
+        <v>351.7900085449219</v>
       </c>
       <c r="F218" t="n">
-        <v>7606500</v>
+        <v>6603400</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B219" t="n">
-        <v>353.2999877929688</v>
+        <v>353.75</v>
       </c>
       <c r="C219" t="n">
-        <v>354.4700012207031</v>
+        <v>355.6199951171875</v>
       </c>
       <c r="D219" t="n">
-        <v>349.7000122070312</v>
+        <v>350.8399963378906</v>
       </c>
       <c r="E219" t="n">
-        <v>351.7900085449219</v>
+        <v>352.6400146484375</v>
       </c>
       <c r="F219" t="n">
-        <v>6603400</v>
+        <v>6436600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B220" t="n">
-        <v>353.75</v>
+        <v>355</v>
       </c>
       <c r="C220" t="n">
-        <v>355.6199951171875</v>
+        <v>363</v>
       </c>
       <c r="D220" t="n">
-        <v>350.8399963378906</v>
+        <v>353.8699951171875</v>
       </c>
       <c r="E220" t="n">
-        <v>352.6400146484375</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F220" t="n">
-        <v>6436600</v>
+        <v>8477200</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B221" t="n">
-        <v>355</v>
+        <v>358.9700012207031</v>
       </c>
       <c r="C221" t="n">
-        <v>363</v>
+        <v>362.1700134277344</v>
       </c>
       <c r="D221" t="n">
-        <v>353.8699951171875</v>
+        <v>358.2000122070312</v>
       </c>
       <c r="E221" t="n">
-        <v>357.5199890136719</v>
+        <v>359.239990234375</v>
       </c>
       <c r="F221" t="n">
-        <v>8477200</v>
+        <v>5269500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B222" t="n">
-        <v>358.9700012207031</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="C222" t="n">
-        <v>362.1700134277344</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="D222" t="n">
-        <v>358.2000122070312</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="E222" t="n">
-        <v>359.239990234375</v>
+        <v>356.2999877929688</v>
       </c>
       <c r="F222" t="n">
-        <v>5269500</v>
+        <v>5820100</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B223" t="n">
-        <v>362.8099975585938</v>
+        <v>355.760009765625</v>
       </c>
       <c r="C223" t="n">
-        <v>362.8099975585938</v>
+        <v>358.8500061035156</v>
       </c>
       <c r="D223" t="n">
-        <v>354.9500122070312</v>
+        <v>353.3299865722656</v>
       </c>
       <c r="E223" t="n">
-        <v>356.2999877929688</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F223" t="n">
-        <v>5820100</v>
+        <v>4566200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B224" t="n">
-        <v>355.760009765625</v>
+        <v>357.9599914550781</v>
       </c>
       <c r="C224" t="n">
-        <v>358.8500061035156</v>
+        <v>359.989990234375</v>
       </c>
       <c r="D224" t="n">
-        <v>353.3299865722656</v>
+        <v>356.5</v>
       </c>
       <c r="E224" t="n">
-        <v>357.5199890136719</v>
+        <v>359.7900085449219</v>
       </c>
       <c r="F224" t="n">
-        <v>4566200</v>
+        <v>5327500</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B225" t="n">
-        <v>357.9599914550781</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="C225" t="n">
-        <v>359.989990234375</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="D225" t="n">
-        <v>356.5</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="E225" t="n">
-        <v>359.7900085449219</v>
+        <v>362.0400085449219</v>
       </c>
       <c r="F225" t="n">
-        <v>5327500</v>
+        <v>4576500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B226" t="n">
-        <v>360.0499877929688</v>
+        <v>362.9700012207031</v>
       </c>
       <c r="C226" t="n">
-        <v>363.1199951171875</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="D226" t="n">
-        <v>358.6000061035156</v>
+        <v>361.2999877929688</v>
       </c>
       <c r="E226" t="n">
-        <v>362.0400085449219</v>
+        <v>365.1799926757812</v>
       </c>
       <c r="F226" t="n">
-        <v>4576500</v>
+        <v>4366800</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B227" t="n">
-        <v>362.9700012207031</v>
+        <v>366.5</v>
       </c>
       <c r="C227" t="n">
-        <v>366.0899963378906</v>
+        <v>366.5</v>
       </c>
       <c r="D227" t="n">
-        <v>361.2999877929688</v>
+        <v>361.5199890136719</v>
       </c>
       <c r="E227" t="n">
-        <v>365.1799926757812</v>
+        <v>363.1099853515625</v>
       </c>
       <c r="F227" t="n">
-        <v>4366800</v>
+        <v>5102700</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B228" t="n">
-        <v>366.5</v>
+        <v>363</v>
       </c>
       <c r="C228" t="n">
-        <v>366.5</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="D228" t="n">
-        <v>361.5199890136719</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="E228" t="n">
-        <v>363.1099853515625</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="F228" t="n">
-        <v>5102700</v>
+        <v>5058600</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B229" t="n">
-        <v>363</v>
+        <v>361.9400024414062</v>
       </c>
       <c r="C229" t="n">
-        <v>365.8999938964844</v>
+        <v>365.75</v>
       </c>
       <c r="D229" t="n">
-        <v>361.4500122070312</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="E229" t="n">
-        <v>362.8399963378906</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="F229" t="n">
-        <v>5058600</v>
+        <v>5282600</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B230" t="n">
-        <v>361.9400024414062</v>
+        <v>362.3399963378906</v>
       </c>
       <c r="C230" t="n">
-        <v>365.75</v>
+        <v>363.5700073242188</v>
       </c>
       <c r="D230" t="n">
-        <v>360.9599914550781</v>
+        <v>359.2699890136719</v>
       </c>
       <c r="E230" t="n">
-        <v>360.9599914550781</v>
+        <v>363.25</v>
       </c>
       <c r="F230" t="n">
-        <v>5282600</v>
+        <v>5525100</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B231" t="n">
-        <v>362.3399963378906</v>
+        <v>363.010009765625</v>
       </c>
       <c r="C231" t="n">
-        <v>363.5700073242188</v>
+        <v>363.0499877929688</v>
       </c>
       <c r="D231" t="n">
-        <v>359.2699890136719</v>
+        <v>355.6499938964844</v>
       </c>
       <c r="E231" t="n">
-        <v>363.25</v>
+        <v>357.260009765625</v>
       </c>
       <c r="F231" t="n">
-        <v>5525100</v>
+        <v>6696200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B232" t="n">
-        <v>363.010009765625</v>
+        <v>357.6000061035156</v>
       </c>
       <c r="C232" t="n">
-        <v>363.0499877929688</v>
+        <v>357.9500122070312</v>
       </c>
       <c r="D232" t="n">
-        <v>355.6499938964844</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E232" t="n">
-        <v>357.260009765625</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="F232" t="n">
-        <v>6696200</v>
+        <v>6799700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B233" t="n">
-        <v>357.6000061035156</v>
+        <v>354.0700073242188</v>
       </c>
       <c r="C233" t="n">
-        <v>357.9500122070312</v>
+        <v>356.8599853515625</v>
       </c>
       <c r="D233" t="n">
-        <v>351.5499877929688</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="E233" t="n">
-        <v>351.5499877929688</v>
+        <v>351.5799865722656</v>
       </c>
       <c r="F233" t="n">
-        <v>6799700</v>
+        <v>8112100</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B234" t="n">
-        <v>354.0700073242188</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C234" t="n">
-        <v>356.8599853515625</v>
+        <v>358.2799987792969</v>
       </c>
       <c r="D234" t="n">
-        <v>350.3699951171875</v>
+        <v>352.8200073242188</v>
       </c>
       <c r="E234" t="n">
-        <v>351.5799865722656</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="F234" t="n">
-        <v>8112100</v>
+        <v>4394400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B235" t="n">
-        <v>353.2999877929688</v>
+        <v>357</v>
       </c>
       <c r="C235" t="n">
-        <v>358.2799987792969</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D235" t="n">
-        <v>352.8200073242188</v>
+        <v>353.0700073242188</v>
       </c>
       <c r="E235" t="n">
-        <v>356.3900146484375</v>
+        <v>356.6900024414062</v>
       </c>
       <c r="F235" t="n">
-        <v>4394400</v>
+        <v>4298000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B236" t="n">
-        <v>357</v>
+        <v>356.5</v>
       </c>
       <c r="C236" t="n">
-        <v>357.3699951171875</v>
+        <v>358.3500061035156</v>
       </c>
       <c r="D236" t="n">
-        <v>353.0700073242188</v>
+        <v>354.6000061035156</v>
       </c>
       <c r="E236" t="n">
-        <v>356.6900024414062</v>
+        <v>356.5</v>
       </c>
       <c r="F236" t="n">
-        <v>4298000</v>
+        <v>5796500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B237" t="n">
-        <v>356.5</v>
+        <v>354.6799926757812</v>
       </c>
       <c r="C237" t="n">
-        <v>358.3500061035156</v>
+        <v>357.5700073242188</v>
       </c>
       <c r="D237" t="n">
-        <v>354.6000061035156</v>
+        <v>352.2300109863281</v>
       </c>
       <c r="E237" t="n">
-        <v>356.5</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="F237" t="n">
-        <v>5796500</v>
+        <v>5209900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B238" t="n">
-        <v>354.6799926757812</v>
+        <v>355.6700134277344</v>
       </c>
       <c r="C238" t="n">
-        <v>357.5700073242188</v>
+        <v>358.7300109863281</v>
       </c>
       <c r="D238" t="n">
-        <v>352.2300109863281</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="E238" t="n">
-        <v>354.2200012207031</v>
+        <v>357.6199951171875</v>
       </c>
       <c r="F238" t="n">
-        <v>5209900</v>
+        <v>3914500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B239" t="n">
-        <v>355.6700134277344</v>
+        <v>355.8999938964844</v>
       </c>
       <c r="C239" t="n">
-        <v>358.7300109863281</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="D239" t="n">
-        <v>354.2200012207031</v>
+        <v>354.7699890136719</v>
       </c>
       <c r="E239" t="n">
-        <v>357.6199951171875</v>
+        <v>356.0199890136719</v>
       </c>
       <c r="F239" t="n">
-        <v>3914500</v>
+        <v>7962900</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B240" t="n">
-        <v>355.8999938964844</v>
+        <v>355.7300109863281</v>
       </c>
       <c r="C240" t="n">
-        <v>357.7699890136719</v>
+        <v>359.9299926757812</v>
       </c>
       <c r="D240" t="n">
-        <v>354.7699890136719</v>
+        <v>354.1199951171875</v>
       </c>
       <c r="E240" t="n">
-        <v>356.0199890136719</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="F240" t="n">
-        <v>7962900</v>
+        <v>5079000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B241" t="n">
-        <v>355.7300109863281</v>
+        <v>357.5499877929688</v>
       </c>
       <c r="C241" t="n">
-        <v>359.9299926757812</v>
+        <v>361.4700012207031</v>
       </c>
       <c r="D241" t="n">
-        <v>354.1199951171875</v>
+        <v>353.7900085449219</v>
       </c>
       <c r="E241" t="n">
-        <v>354.9500122070312</v>
+        <v>356.2200012207031</v>
       </c>
       <c r="F241" t="n">
-        <v>5079000</v>
+        <v>5341400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B242" t="n">
-        <v>357.5499877929688</v>
+        <v>358.6799926757812</v>
       </c>
       <c r="C242" t="n">
-        <v>361.4700012207031</v>
+        <v>362.8500061035156</v>
       </c>
       <c r="D242" t="n">
-        <v>353.7900085449219</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="E242" t="n">
-        <v>356.2200012207031</v>
+        <v>362.0599975585938</v>
       </c>
       <c r="F242" t="n">
-        <v>5341400</v>
+        <v>5414200</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B243" t="n">
-        <v>358.6799926757812</v>
+        <v>361</v>
       </c>
       <c r="C243" t="n">
-        <v>362.8500061035156</v>
+        <v>362.8599853515625</v>
       </c>
       <c r="D243" t="n">
-        <v>356.3900146484375</v>
+        <v>355.2000122070312</v>
       </c>
       <c r="E243" t="n">
-        <v>362.0599975585938</v>
+        <v>358.6400146484375</v>
       </c>
       <c r="F243" t="n">
-        <v>5414200</v>
+        <v>4873500</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B244" t="n">
-        <v>361</v>
+        <v>357.1000061035156</v>
       </c>
       <c r="C244" t="n">
-        <v>362.8599853515625</v>
+        <v>358.5499877929688</v>
       </c>
       <c r="D244" t="n">
-        <v>355.2000122070312</v>
+        <v>353.2300109863281</v>
       </c>
       <c r="E244" t="n">
-        <v>358.6400146484375</v>
+        <v>353.510009765625</v>
       </c>
       <c r="F244" t="n">
-        <v>4873500</v>
+        <v>5631400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B245" t="n">
-        <v>357.1000061035156</v>
+        <v>352</v>
       </c>
       <c r="C245" t="n">
-        <v>358.5499877929688</v>
+        <v>356.3299865722656</v>
       </c>
       <c r="D245" t="n">
-        <v>353.2300109863281</v>
+        <v>348.6900024414062</v>
       </c>
       <c r="E245" t="n">
-        <v>353.510009765625</v>
+        <v>354.7099914550781</v>
       </c>
       <c r="F245" t="n">
-        <v>5631400</v>
+        <v>6318200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B246" t="n">
-        <v>352</v>
+        <v>353.510009765625</v>
       </c>
       <c r="C246" t="n">
-        <v>356.3299865722656</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="D246" t="n">
-        <v>348.6900024414062</v>
+        <v>351.1199951171875</v>
       </c>
       <c r="E246" t="n">
-        <v>354.7099914550781</v>
+        <v>353.5599975585938</v>
       </c>
       <c r="F246" t="n">
-        <v>6318200</v>
+        <v>4184200</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B247" t="n">
-        <v>353.510009765625</v>
+        <v>358.3200073242188</v>
       </c>
       <c r="C247" t="n">
-        <v>354.2200012207031</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="D247" t="n">
-        <v>351.1199951171875</v>
+        <v>354.7900085449219</v>
       </c>
       <c r="E247" t="n">
-        <v>353.5599975585938</v>
+        <v>356.2300109863281</v>
       </c>
       <c r="F247" t="n">
-        <v>4184200</v>
+        <v>5354600</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B248" t="n">
-        <v>358.3200073242188</v>
+        <v>354.2300109863281</v>
       </c>
       <c r="C248" t="n">
-        <v>360.0499877929688</v>
+        <v>355.2799987792969</v>
       </c>
       <c r="D248" t="n">
-        <v>354.7900085449219</v>
+        <v>347.5499877929688</v>
       </c>
       <c r="E248" t="n">
-        <v>356.2300109863281</v>
+        <v>350.1300048828125</v>
       </c>
       <c r="F248" t="n">
-        <v>5354600</v>
+        <v>9609900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B249" t="n">
-        <v>354.2300109863281</v>
+        <v>351</v>
       </c>
       <c r="C249" t="n">
-        <v>355.2799987792969</v>
+        <v>354.7000122070312</v>
       </c>
       <c r="D249" t="n">
-        <v>347.5499877929688</v>
+        <v>343.0700073242188</v>
       </c>
       <c r="E249" t="n">
-        <v>350.1300048828125</v>
+        <v>352.489990234375</v>
       </c>
       <c r="F249" t="n">
-        <v>9609900</v>
+        <v>14026500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B250" t="n">
-        <v>351</v>
+        <v>353.3800048828125</v>
       </c>
       <c r="C250" t="n">
-        <v>354.7000122070312</v>
+        <v>355.6000061035156</v>
       </c>
       <c r="D250" t="n">
-        <v>343.0700073242188</v>
+        <v>344.6900024414062</v>
       </c>
       <c r="E250" t="n">
-        <v>352.489990234375</v>
+        <v>348.9200134277344</v>
       </c>
       <c r="F250" t="n">
-        <v>14026500</v>
+        <v>8303400</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B251" t="n">
-        <v>353.3800048828125</v>
+        <v>352.25</v>
       </c>
       <c r="C251" t="n">
-        <v>355.6000061035156</v>
+        <v>353.489990234375</v>
       </c>
       <c r="D251" t="n">
-        <v>344.6900024414062</v>
+        <v>345.2699890136719</v>
       </c>
       <c r="E251" t="n">
-        <v>348.9200134277344</v>
+        <v>349.3099975585938</v>
       </c>
       <c r="F251" t="n">
-        <v>8303400</v>
+        <v>6480100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B252" t="n">
-        <v>352.25</v>
+        <v>347.8900146484375</v>
       </c>
       <c r="C252" t="n">
-        <v>353.489990234375</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="D252" t="n">
-        <v>345.2699890136719</v>
+        <v>345.010009765625</v>
       </c>
       <c r="E252" t="n">
-        <v>349.3099975585938</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="F252" t="n">
-        <v>6480100</v>
+        <v>18290400</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10017,37 +10017,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>349.67</v>
+      </c>
+      <c r="D2" t="n">
         <v>349.31</v>
       </c>
-      <c r="D2" t="n">
-        <v>348.92</v>
-      </c>
       <c r="E2" t="n">
-        <v>352.245</v>
+        <v>347.89</v>
       </c>
       <c r="F2" t="n">
-        <v>353.49</v>
+        <v>349.67</v>
       </c>
       <c r="G2" t="n">
-        <v>345.28</v>
+        <v>345.0676</v>
       </c>
       <c r="H2" t="n">
-        <v>6461018</v>
+        <v>18241892</v>
       </c>
       <c r="I2" t="n">
-        <v>7762854</v>
+        <v>7909596</v>
       </c>
       <c r="J2" t="n">
-        <v>928531021824</v>
+        <v>929488044032</v>
       </c>
       <c r="K2" t="n">
-        <v>14.946939</v>
+        <v>14.96875</v>
       </c>
       <c r="L2" t="n">
-        <v>13.9791155</v>
+        <v>13.993524</v>
       </c>
       <c r="M2" t="n">
-        <v>23.37</v>
+        <v>23.36</v>
       </c>
       <c r="N2" t="n">
         <v>366.5</v>
@@ -10087,7 +10087,7 @@
         <v>133.007</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.6262527</v>
+        <v>2.6289594</v>
       </c>
       <c r="Z2" t="n">
         <v>0.469</v>
@@ -10099,7 +10099,7 @@
         <v>186328006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>766459052032</v>
+        <v>767415943168</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:15:38</t>
+          <t>2026-09-19 15:21:22</t>
         </is>
       </c>
     </row>

--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45919</v>
+        <v>45925</v>
       </c>
       <c r="B2" t="n">
-        <v>307.7132209495945</v>
+        <v>308.2234768510796</v>
       </c>
       <c r="C2" t="n">
-        <v>309.8719053836384</v>
+        <v>309.7247551863121</v>
       </c>
       <c r="D2" t="n">
-        <v>303.3173070986313</v>
+        <v>305.947019653492</v>
       </c>
       <c r="E2" t="n">
-        <v>308.8710632324219</v>
+        <v>307.5660705566406</v>
       </c>
       <c r="F2" t="n">
-        <v>23568600</v>
+        <v>7083200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="B3" t="n">
-        <v>303.9845245259009</v>
+        <v>308.9888161441515</v>
       </c>
       <c r="C3" t="n">
-        <v>307.8113389670314</v>
+        <v>311.8441943720275</v>
       </c>
       <c r="D3" t="n">
-        <v>303.7490393091097</v>
+        <v>307.8113600348933</v>
       </c>
       <c r="E3" t="n">
-        <v>306.5749816894531</v>
+        <v>310.1270446777344</v>
       </c>
       <c r="F3" t="n">
-        <v>7520200</v>
+        <v>7258100</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45923</v>
+        <v>45929</v>
       </c>
       <c r="B4" t="n">
-        <v>305.9666409066948</v>
+        <v>311.1082857354447</v>
       </c>
       <c r="C4" t="n">
-        <v>310.3723467544506</v>
+        <v>312.0404647281687</v>
       </c>
       <c r="D4" t="n">
-        <v>304.7498973520222</v>
+        <v>307.7721150397051</v>
       </c>
       <c r="E4" t="n">
-        <v>306.8693542480469</v>
+        <v>309.7640075683594</v>
       </c>
       <c r="F4" t="n">
-        <v>8584400</v>
+        <v>6462400</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45924</v>
+        <v>45930</v>
       </c>
       <c r="B5" t="n">
-        <v>308.1547392588795</v>
+        <v>310.3134645283819</v>
       </c>
       <c r="C5" t="n">
-        <v>310.6372456892681</v>
+        <v>311.4516930034957</v>
       </c>
       <c r="D5" t="n">
-        <v>305.8194410309901</v>
+        <v>304.288708108424</v>
       </c>
       <c r="E5" t="n">
-        <v>307.5365905761719</v>
+        <v>309.5088500976562</v>
       </c>
       <c r="F5" t="n">
-        <v>7310500</v>
+        <v>11823300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45925</v>
+        <v>45931</v>
       </c>
       <c r="B6" t="n">
-        <v>308.2234462682717</v>
+        <v>308.0762861336198</v>
       </c>
       <c r="C6" t="n">
-        <v>309.7247244545431</v>
+        <v>308.6846429587351</v>
       </c>
       <c r="D6" t="n">
-        <v>305.9469892965607</v>
+        <v>301.6394301376976</v>
       </c>
       <c r="E6" t="n">
-        <v>307.5660400390625</v>
+        <v>304.8774719238281</v>
       </c>
       <c r="F6" t="n">
-        <v>7083200</v>
+        <v>9235200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45926</v>
+        <v>45932</v>
       </c>
       <c r="B7" t="n">
-        <v>308.9888161441515</v>
+        <v>304.1808160870063</v>
       </c>
       <c r="C7" t="n">
-        <v>311.8441943720275</v>
+        <v>304.7303016172636</v>
       </c>
       <c r="D7" t="n">
-        <v>307.8113600348933</v>
+        <v>300.393288685967</v>
       </c>
       <c r="E7" t="n">
-        <v>310.1270446777344</v>
+        <v>301.7767944335938</v>
       </c>
       <c r="F7" t="n">
-        <v>7258100</v>
+        <v>7600000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45929</v>
+        <v>45933</v>
       </c>
       <c r="B8" t="n">
-        <v>311.1082857354447</v>
+        <v>302.718779227698</v>
       </c>
       <c r="C8" t="n">
-        <v>312.0404647281687</v>
+        <v>305.8096426575195</v>
       </c>
       <c r="D8" t="n">
-        <v>307.7721150397051</v>
+        <v>302.4243927447969</v>
       </c>
       <c r="E8" t="n">
-        <v>309.7640075683594</v>
+        <v>304.2102355957031</v>
       </c>
       <c r="F8" t="n">
-        <v>6462400</v>
+        <v>6029900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,25 +651,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45930</v>
+        <v>45936</v>
       </c>
       <c r="B9" t="n">
-        <v>310.3134645283819</v>
+        <v>305.8371035459471</v>
       </c>
       <c r="C9" t="n">
-        <v>311.4516930034957</v>
+        <v>307.3851288987199</v>
       </c>
       <c r="D9" t="n">
-        <v>304.288708108424</v>
+        <v>300.8578215934895</v>
       </c>
       <c r="E9" t="n">
-        <v>309.5088500976562</v>
+        <v>304.8511047363281</v>
       </c>
       <c r="F9" t="n">
-        <v>11823300</v>
+        <v>7214500</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45931</v>
+        <v>45937</v>
       </c>
       <c r="B10" t="n">
-        <v>308.0762861336198</v>
+        <v>305.0187502270194</v>
       </c>
       <c r="C10" t="n">
-        <v>308.6846429587351</v>
+        <v>305.6695130787729</v>
       </c>
       <c r="D10" t="n">
-        <v>301.6394301376976</v>
+        <v>300.4338615931582</v>
       </c>
       <c r="E10" t="n">
-        <v>304.8774719238281</v>
+        <v>303.3819885253906</v>
       </c>
       <c r="F10" t="n">
-        <v>9235200</v>
+        <v>8454200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45932</v>
+        <v>45938</v>
       </c>
       <c r="B11" t="n">
-        <v>304.1808160870063</v>
+        <v>303.894722712774</v>
       </c>
       <c r="C11" t="n">
-        <v>304.7303016172636</v>
+        <v>304.4567493262524</v>
       </c>
       <c r="D11" t="n">
-        <v>300.393288685967</v>
+        <v>299.2999640741864</v>
       </c>
       <c r="E11" t="n">
-        <v>301.7767944335938</v>
+        <v>299.7732543945312</v>
       </c>
       <c r="F11" t="n">
-        <v>7600000</v>
+        <v>6489900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45933</v>
+        <v>45939</v>
       </c>
       <c r="B12" t="n">
-        <v>302.718779227698</v>
+        <v>300.7789375021521</v>
       </c>
       <c r="C12" t="n">
-        <v>305.8096426575195</v>
+        <v>303.7270945284432</v>
       </c>
       <c r="D12" t="n">
-        <v>302.4243927447969</v>
+        <v>299.1422058887319</v>
       </c>
       <c r="E12" t="n">
-        <v>304.2102355957031</v>
+        <v>301.2522277832031</v>
       </c>
       <c r="F12" t="n">
-        <v>6029900</v>
+        <v>7060300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,25 +755,25 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45936</v>
+        <v>45940</v>
       </c>
       <c r="B13" t="n">
-        <v>305.8371035459471</v>
+        <v>301.3804193716138</v>
       </c>
       <c r="C13" t="n">
-        <v>307.3851288987199</v>
+        <v>306.1230715472904</v>
       </c>
       <c r="D13" t="n">
-        <v>300.8578215934895</v>
+        <v>296.5983188157025</v>
       </c>
       <c r="E13" t="n">
-        <v>304.8511047363281</v>
+        <v>296.6772155761719</v>
       </c>
       <c r="F13" t="n">
-        <v>7214500</v>
+        <v>8597400</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45937</v>
+        <v>45943</v>
       </c>
       <c r="B14" t="n">
-        <v>305.0187502270194</v>
+        <v>301.321238204041</v>
       </c>
       <c r="C14" t="n">
-        <v>305.6695130787729</v>
+        <v>305.1271791148808</v>
       </c>
       <c r="D14" t="n">
-        <v>300.4338615931582</v>
+        <v>301.173344402637</v>
       </c>
       <c r="E14" t="n">
-        <v>303.3819885253906</v>
+        <v>303.6580505371094</v>
       </c>
       <c r="F14" t="n">
-        <v>8454200</v>
+        <v>10788700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45938</v>
+        <v>45944</v>
       </c>
       <c r="B15" t="n">
-        <v>303.8946917756213</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C15" t="n">
-        <v>304.4567183318842</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D15" t="n">
-        <v>299.2999336047902</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E15" t="n">
-        <v>299.7732238769531</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F15" t="n">
-        <v>6489900</v>
+        <v>16178800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45939</v>
+        <v>45945</v>
       </c>
       <c r="B16" t="n">
-        <v>300.7789679717848</v>
+        <v>302.1001843350741</v>
       </c>
       <c r="C16" t="n">
-        <v>303.7271252967313</v>
+        <v>307.7499381556482</v>
       </c>
       <c r="D16" t="n">
-        <v>299.1422361925597</v>
+        <v>301.1634734465224</v>
       </c>
       <c r="E16" t="n">
-        <v>301.2522583007812</v>
+        <v>301.4099731445312</v>
       </c>
       <c r="F16" t="n">
-        <v>7060300</v>
+        <v>11354800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45940</v>
+        <v>45946</v>
       </c>
       <c r="B17" t="n">
-        <v>301.3804193716138</v>
+        <v>301.0747572360179</v>
       </c>
       <c r="C17" t="n">
-        <v>306.1230715472904</v>
+        <v>304.3581201926382</v>
       </c>
       <c r="D17" t="n">
-        <v>296.5983188157025</v>
+        <v>292.9106878973514</v>
       </c>
       <c r="E17" t="n">
-        <v>296.6772155761719</v>
+        <v>294.360107421875</v>
       </c>
       <c r="F17" t="n">
-        <v>8597400</v>
+        <v>10549400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45943</v>
+        <v>45947</v>
       </c>
       <c r="B18" t="n">
-        <v>301.321238204041</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C18" t="n">
-        <v>305.1271791148808</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D18" t="n">
-        <v>301.173344402637</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E18" t="n">
-        <v>303.6580505371094</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F18" t="n">
-        <v>10788700</v>
+        <v>10153500</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="B19" t="n">
-        <v>301.5578902761218</v>
+        <v>294.3206459359216</v>
       </c>
       <c r="C19" t="n">
-        <v>302.7016525742085</v>
+        <v>299.4379821870563</v>
       </c>
       <c r="D19" t="n">
-        <v>290.0907186231138</v>
+        <v>293.9854099500461</v>
       </c>
       <c r="E19" t="n">
-        <v>297.8505249023438</v>
+        <v>298.1265869140625</v>
       </c>
       <c r="F19" t="n">
-        <v>16178800</v>
+        <v>6894900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45945</v>
+        <v>45951</v>
       </c>
       <c r="B20" t="n">
-        <v>302.1001843350741</v>
+        <v>297.436411288458</v>
       </c>
       <c r="C20" t="n">
-        <v>307.7499381556482</v>
+        <v>299.7929328501146</v>
       </c>
       <c r="D20" t="n">
-        <v>301.1634734465224</v>
+        <v>292.8416531202475</v>
       </c>
       <c r="E20" t="n">
-        <v>301.4099731445312</v>
+        <v>292.9303894042969</v>
       </c>
       <c r="F20" t="n">
-        <v>11354800</v>
+        <v>7372700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45946</v>
+        <v>45952</v>
       </c>
       <c r="B21" t="n">
-        <v>301.0747572360179</v>
+        <v>293.6008552074487</v>
       </c>
       <c r="C21" t="n">
-        <v>304.3581201926382</v>
+        <v>293.8868032880077</v>
       </c>
       <c r="D21" t="n">
-        <v>292.9106878973514</v>
+        <v>286.4721030595595</v>
       </c>
       <c r="E21" t="n">
-        <v>294.360107421875</v>
+        <v>289.9920959472656</v>
       </c>
       <c r="F21" t="n">
-        <v>10549400</v>
+        <v>8054100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="B22" t="n">
-        <v>294.9714335987563</v>
+        <v>290.2583437522712</v>
       </c>
       <c r="C22" t="n">
-        <v>295.3559575215809</v>
+        <v>292.2204718178062</v>
       </c>
       <c r="D22" t="n">
-        <v>290.0808874955599</v>
+        <v>288.4145307332595</v>
       </c>
       <c r="E22" t="n">
-        <v>293.3938293457031</v>
+        <v>290.4161071777344</v>
       </c>
       <c r="F22" t="n">
-        <v>10153500</v>
+        <v>5438800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45950</v>
+        <v>45954</v>
       </c>
       <c r="B23" t="n">
-        <v>294.3206760639065</v>
+        <v>291.9345194575729</v>
       </c>
       <c r="C23" t="n">
-        <v>299.4380128388747</v>
+        <v>298.3632510673837</v>
       </c>
       <c r="D23" t="n">
-        <v>293.9854400437148</v>
+        <v>291.3133654724136</v>
       </c>
       <c r="E23" t="n">
-        <v>298.1266174316406</v>
+        <v>296.2334899902344</v>
       </c>
       <c r="F23" t="n">
-        <v>6894900</v>
+        <v>7228300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="B24" t="n">
-        <v>297.436411288458</v>
+        <v>297.92941246883</v>
       </c>
       <c r="C24" t="n">
-        <v>299.7929328501146</v>
+        <v>300.2662249001909</v>
       </c>
       <c r="D24" t="n">
-        <v>292.8416531202475</v>
+        <v>296.7955198233114</v>
       </c>
       <c r="E24" t="n">
-        <v>292.9303894042969</v>
+        <v>299.8915405273438</v>
       </c>
       <c r="F24" t="n">
-        <v>7372700</v>
+        <v>5642200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45952</v>
+        <v>45958</v>
       </c>
       <c r="B25" t="n">
-        <v>293.6008552074487</v>
+        <v>300.5915953010157</v>
       </c>
       <c r="C25" t="n">
-        <v>293.8868032880077</v>
+        <v>303.6580673748709</v>
       </c>
       <c r="D25" t="n">
-        <v>286.4721030595595</v>
+        <v>298.915415308335</v>
       </c>
       <c r="E25" t="n">
-        <v>289.9920959472656</v>
+        <v>301.0845947265625</v>
       </c>
       <c r="F25" t="n">
-        <v>8054100</v>
+        <v>6336000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45953</v>
+        <v>45959</v>
       </c>
       <c r="B26" t="n">
-        <v>290.2583437522712</v>
+        <v>299.2605157595805</v>
       </c>
       <c r="C26" t="n">
-        <v>292.2204718178062</v>
+        <v>303.9341406042103</v>
       </c>
       <c r="D26" t="n">
-        <v>288.4145307332595</v>
+        <v>298.7675163425421</v>
       </c>
       <c r="E26" t="n">
-        <v>290.4161071777344</v>
+        <v>301.2325134277344</v>
       </c>
       <c r="F26" t="n">
-        <v>5438800</v>
+        <v>7520300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45954</v>
+        <v>45960</v>
       </c>
       <c r="B27" t="n">
-        <v>291.9345194575729</v>
+        <v>301.5085931686638</v>
       </c>
       <c r="C27" t="n">
-        <v>298.3632510673837</v>
+        <v>308.2330823767899</v>
       </c>
       <c r="D27" t="n">
-        <v>291.3133654724136</v>
+        <v>300.828251563059</v>
       </c>
       <c r="E27" t="n">
-        <v>296.2334899902344</v>
+        <v>305.1074829101562</v>
       </c>
       <c r="F27" t="n">
-        <v>7228300</v>
+        <v>7514600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45957</v>
+        <v>45961</v>
       </c>
       <c r="B28" t="n">
-        <v>297.9294427867379</v>
+        <v>304.2200828300273</v>
       </c>
       <c r="C28" t="n">
-        <v>300.2662554558976</v>
+        <v>308.4894444595929</v>
       </c>
       <c r="D28" t="n">
-        <v>296.7955500258321</v>
+        <v>302.9481359332913</v>
       </c>
       <c r="E28" t="n">
-        <v>299.8915710449219</v>
+        <v>306.7639465332031</v>
       </c>
       <c r="F28" t="n">
-        <v>5642200</v>
+        <v>7721300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45958</v>
+        <v>45964</v>
       </c>
       <c r="B29" t="n">
-        <v>300.5915953010157</v>
+        <v>306.6456604912348</v>
       </c>
       <c r="C29" t="n">
-        <v>303.6580673748709</v>
+        <v>307.9471862719047</v>
       </c>
       <c r="D29" t="n">
-        <v>298.915415308335</v>
+        <v>301.9227172950412</v>
       </c>
       <c r="E29" t="n">
-        <v>301.0845947265625</v>
+        <v>305.0187683105469</v>
       </c>
       <c r="F29" t="n">
-        <v>6336000</v>
+        <v>7770000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45959</v>
+        <v>45965</v>
       </c>
       <c r="B30" t="n">
-        <v>299.2605157595805</v>
+        <v>302.415720333495</v>
       </c>
       <c r="C30" t="n">
-        <v>303.9341406042103</v>
+        <v>307.8485840116909</v>
       </c>
       <c r="D30" t="n">
-        <v>298.7675163425421</v>
+        <v>300.8282765156093</v>
       </c>
       <c r="E30" t="n">
-        <v>301.2325134277344</v>
+        <v>304.920166015625</v>
       </c>
       <c r="F30" t="n">
-        <v>7520300</v>
+        <v>7085200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45960</v>
+        <v>45966</v>
       </c>
       <c r="B31" t="n">
-        <v>301.5085931686638</v>
+        <v>305.2751066360906</v>
       </c>
       <c r="C31" t="n">
-        <v>308.2330823767899</v>
+        <v>308.7162632770978</v>
       </c>
       <c r="D31" t="n">
-        <v>300.828251563059</v>
+        <v>301.3508502506656</v>
       </c>
       <c r="E31" t="n">
-        <v>305.1074829101562</v>
+        <v>307.3161315917969</v>
       </c>
       <c r="F31" t="n">
-        <v>7514600</v>
+        <v>6865200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45961</v>
+        <v>45967</v>
       </c>
       <c r="B32" t="n">
-        <v>304.2200828300273</v>
+        <v>306.6357687557767</v>
       </c>
       <c r="C32" t="n">
-        <v>308.4894444595929</v>
+        <v>310.4318702971036</v>
       </c>
       <c r="D32" t="n">
-        <v>302.9481359332913</v>
+        <v>305.9160088624015</v>
       </c>
       <c r="E32" t="n">
-        <v>306.7639465332031</v>
+        <v>309.0317687988281</v>
       </c>
       <c r="F32" t="n">
-        <v>7721300</v>
+        <v>7206100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45964</v>
+        <v>45968</v>
       </c>
       <c r="B33" t="n">
-        <v>306.6456298108837</v>
+        <v>307.5232049313688</v>
       </c>
       <c r="C33" t="n">
-        <v>307.947155461334</v>
+        <v>310.0276204199649</v>
       </c>
       <c r="D33" t="n">
-        <v>301.9226870872275</v>
+        <v>303.3327096940284</v>
       </c>
       <c r="E33" t="n">
-        <v>305.0187377929688</v>
+        <v>309.8106994628906</v>
       </c>
       <c r="F33" t="n">
-        <v>7770000</v>
+        <v>7302300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45965</v>
+        <v>45971</v>
       </c>
       <c r="B34" t="n">
-        <v>302.415720333495</v>
+        <v>310.5896337890794</v>
       </c>
       <c r="C34" t="n">
-        <v>307.8485840116909</v>
+        <v>315.0857860805166</v>
       </c>
       <c r="D34" t="n">
-        <v>300.8282765156093</v>
+        <v>309.8106862822301</v>
       </c>
       <c r="E34" t="n">
-        <v>304.920166015625</v>
+        <v>312.4531860351562</v>
       </c>
       <c r="F34" t="n">
-        <v>7085200</v>
+        <v>5794100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45966</v>
+        <v>45972</v>
       </c>
       <c r="B35" t="n">
-        <v>305.2751066360906</v>
+        <v>313.0546102409576</v>
       </c>
       <c r="C35" t="n">
-        <v>308.7162632770978</v>
+        <v>314.5828963020791</v>
       </c>
       <c r="D35" t="n">
-        <v>301.3508502506656</v>
+        <v>310.8656917625901</v>
       </c>
       <c r="E35" t="n">
-        <v>307.3161315917969</v>
+        <v>311.200927734375</v>
       </c>
       <c r="F35" t="n">
-        <v>6865200</v>
+        <v>5030200</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45967</v>
+        <v>45973</v>
       </c>
       <c r="B36" t="n">
-        <v>306.6357687557767</v>
+        <v>311.8320000281587</v>
       </c>
       <c r="C36" t="n">
-        <v>310.4318702971036</v>
+        <v>317.7381233989844</v>
       </c>
       <c r="D36" t="n">
-        <v>305.9160088624015</v>
+        <v>311.782682032414</v>
       </c>
       <c r="E36" t="n">
-        <v>309.0317687988281</v>
+        <v>315.9238891601562</v>
       </c>
       <c r="F36" t="n">
-        <v>7206100</v>
+        <v>10578300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45968</v>
+        <v>45974</v>
       </c>
       <c r="B37" t="n">
-        <v>307.5231746391179</v>
+        <v>314.7604626322791</v>
       </c>
       <c r="C37" t="n">
-        <v>310.0275898810191</v>
+        <v>316.1408551748796</v>
       </c>
       <c r="D37" t="n">
-        <v>303.3326798145578</v>
+        <v>304.7722882324798</v>
       </c>
       <c r="E37" t="n">
-        <v>309.8106689453125</v>
+        <v>305.14697265625</v>
       </c>
       <c r="F37" t="n">
-        <v>7302300</v>
+        <v>8973300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45971</v>
+        <v>45975</v>
       </c>
       <c r="B38" t="n">
-        <v>310.5896034535161</v>
+        <v>303.2044890700107</v>
       </c>
       <c r="C38" t="n">
-        <v>315.0857553058102</v>
+        <v>303.3326737235763</v>
       </c>
       <c r="D38" t="n">
-        <v>309.8106560227473</v>
+        <v>297.012418045434</v>
       </c>
       <c r="E38" t="n">
-        <v>312.4531555175781</v>
+        <v>299.3590698242188</v>
       </c>
       <c r="F38" t="n">
-        <v>5794100</v>
+        <v>10327000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45972</v>
+        <v>45978</v>
       </c>
       <c r="B39" t="n">
-        <v>313.054640940315</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C39" t="n">
-        <v>314.5829271513063</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D39" t="n">
-        <v>310.8657222472937</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E39" t="n">
-        <v>311.2009582519531</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F39" t="n">
-        <v>5030200</v>
+        <v>8344000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45973</v>
+        <v>45979</v>
       </c>
       <c r="B40" t="n">
-        <v>311.8320000281587</v>
+        <v>295.3066623130797</v>
       </c>
       <c r="C40" t="n">
-        <v>317.7381233989844</v>
+        <v>298.708370459316</v>
       </c>
       <c r="D40" t="n">
-        <v>311.782682032414</v>
+        <v>292.8613742767781</v>
       </c>
       <c r="E40" t="n">
-        <v>315.9238891601562</v>
+        <v>295.2179260253906</v>
       </c>
       <c r="F40" t="n">
-        <v>10578300</v>
+        <v>8077300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45974</v>
+        <v>45980</v>
       </c>
       <c r="B41" t="n">
-        <v>314.7604311532612</v>
+        <v>295.5432597963394</v>
       </c>
       <c r="C41" t="n">
-        <v>316.1408235578094</v>
+        <v>300.1873356382808</v>
       </c>
       <c r="D41" t="n">
-        <v>304.7722577523736</v>
+        <v>295.0798391737984</v>
       </c>
       <c r="E41" t="n">
-        <v>305.1469421386719</v>
+        <v>299.0238342285156</v>
       </c>
       <c r="F41" t="n">
-        <v>8973300</v>
+        <v>5546600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="B42" t="n">
-        <v>303.2045199796025</v>
+        <v>302.0508736933244</v>
       </c>
       <c r="C42" t="n">
-        <v>303.3327046462357</v>
+        <v>305.5807663052954</v>
       </c>
       <c r="D42" t="n">
-        <v>297.0124483237873</v>
+        <v>293.9854105998292</v>
       </c>
       <c r="E42" t="n">
-        <v>299.3591003417969</v>
+        <v>294.2023315429688</v>
       </c>
       <c r="F42" t="n">
-        <v>10327000</v>
+        <v>7501600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45978</v>
+        <v>45982</v>
       </c>
       <c r="B43" t="n">
-        <v>299.7436397411884</v>
+        <v>297.0715864028587</v>
       </c>
       <c r="C43" t="n">
-        <v>301.3113742461044</v>
+        <v>297.456110287291</v>
       </c>
       <c r="D43" t="n">
-        <v>293.5022804823602</v>
+        <v>288.7103057597054</v>
       </c>
       <c r="E43" t="n">
-        <v>296.1644592285156</v>
+        <v>293.8473510742188</v>
       </c>
       <c r="F43" t="n">
-        <v>8344000</v>
+        <v>11766800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45979</v>
+        <v>45985</v>
       </c>
       <c r="B44" t="n">
-        <v>295.3066623130797</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C44" t="n">
-        <v>298.708370459316</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D44" t="n">
-        <v>292.8613742767781</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E44" t="n">
-        <v>295.2179260253906</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F44" t="n">
-        <v>8077300</v>
+        <v>10940200</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45980</v>
+        <v>45986</v>
       </c>
       <c r="B45" t="n">
-        <v>295.5432899586994</v>
+        <v>295.848951187077</v>
       </c>
       <c r="C45" t="n">
-        <v>300.1873662746028</v>
+        <v>300.236658228506</v>
       </c>
       <c r="D45" t="n">
-        <v>295.0798692888629</v>
+        <v>291.4218258555586</v>
       </c>
       <c r="E45" t="n">
-        <v>299.0238647460938</v>
+        <v>298.7576599121094</v>
       </c>
       <c r="F45" t="n">
-        <v>5546600</v>
+        <v>8877200</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45981</v>
+        <v>45987</v>
       </c>
       <c r="B46" t="n">
-        <v>302.0509050250311</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C46" t="n">
-        <v>305.5807980031574</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D46" t="n">
-        <v>293.9854410949062</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E46" t="n">
-        <v>294.2023620605469</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F46" t="n">
-        <v>7501600</v>
+        <v>7910900</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B47" t="n">
-        <v>297.0715864028587</v>
+        <v>304.7722465716023</v>
       </c>
       <c r="C47" t="n">
-        <v>297.456110287291</v>
+        <v>309.3275563846455</v>
       </c>
       <c r="D47" t="n">
-        <v>288.7103057597054</v>
+        <v>303.9242719247256</v>
       </c>
       <c r="E47" t="n">
-        <v>293.8473510742188</v>
+        <v>308.6965026855469</v>
       </c>
       <c r="F47" t="n">
-        <v>11766800</v>
+        <v>4322400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45985</v>
+        <v>45992</v>
       </c>
       <c r="B48" t="n">
-        <v>294.0642973394352</v>
+        <v>308.5683309692949</v>
       </c>
       <c r="C48" t="n">
-        <v>295.6221924256846</v>
+        <v>309.6430660312097</v>
       </c>
       <c r="D48" t="n">
-        <v>290.386540762355</v>
+        <v>304.2200727283419</v>
       </c>
       <c r="E48" t="n">
-        <v>293.8276672363281</v>
+        <v>304.5947570800781</v>
       </c>
       <c r="F48" t="n">
-        <v>10940200</v>
+        <v>7727300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="B49" t="n">
-        <v>295.848951187077</v>
+        <v>304.4172805196406</v>
       </c>
       <c r="C49" t="n">
-        <v>300.236658228506</v>
+        <v>306.1329390093465</v>
       </c>
       <c r="D49" t="n">
-        <v>291.4218258555586</v>
+        <v>302.7903884074122</v>
       </c>
       <c r="E49" t="n">
-        <v>298.7576599121094</v>
+        <v>303.5693359375</v>
       </c>
       <c r="F49" t="n">
-        <v>8877200</v>
+        <v>7249000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B50" t="n">
-        <v>300.7296512123902</v>
+        <v>302.8988595387675</v>
       </c>
       <c r="C50" t="n">
-        <v>304.2102259719906</v>
+        <v>307.9865871384521</v>
       </c>
       <c r="D50" t="n">
-        <v>298.9548653069277</v>
+        <v>302.5044359255107</v>
       </c>
       <c r="E50" t="n">
-        <v>303.3327026367188</v>
+        <v>307.7598266601562</v>
       </c>
       <c r="F50" t="n">
-        <v>7910900</v>
+        <v>8535300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45989</v>
+        <v>45995</v>
       </c>
       <c r="B51" t="n">
-        <v>304.7722465716023</v>
+        <v>308.8740221323167</v>
       </c>
       <c r="C51" t="n">
-        <v>309.3275563846455</v>
+        <v>314.0307770729326</v>
       </c>
       <c r="D51" t="n">
-        <v>303.9242719247256</v>
+        <v>308.617652791837</v>
       </c>
       <c r="E51" t="n">
-        <v>308.6965026855469</v>
+        <v>311.6742553710938</v>
       </c>
       <c r="F51" t="n">
-        <v>4322400</v>
+        <v>9627800</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="B52" t="n">
-        <v>308.5683618849884</v>
+        <v>311.2206946896725</v>
       </c>
       <c r="C52" t="n">
-        <v>309.6430970545817</v>
+        <v>314.0209278419201</v>
       </c>
       <c r="D52" t="n">
-        <v>304.2201032083801</v>
+        <v>310.2741141188276</v>
       </c>
       <c r="E52" t="n">
-        <v>304.5947875976562</v>
+        <v>310.6290893554688</v>
       </c>
       <c r="F52" t="n">
-        <v>7727300</v>
+        <v>6518900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45993</v>
+        <v>45999</v>
       </c>
       <c r="B53" t="n">
-        <v>304.4172499168193</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C53" t="n">
-        <v>306.1329082340515</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D53" t="n">
-        <v>302.7903579681411</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E53" t="n">
-        <v>303.5693054199219</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F53" t="n">
-        <v>7249000</v>
+        <v>7417200</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="B54" t="n">
-        <v>302.8988595387675</v>
+        <v>310.5403783790639</v>
       </c>
       <c r="C54" t="n">
-        <v>307.9865871384521</v>
+        <v>314.336450228146</v>
       </c>
       <c r="D54" t="n">
-        <v>302.5044359255107</v>
+        <v>295.8193913272319</v>
       </c>
       <c r="E54" t="n">
-        <v>307.7598266601562</v>
+        <v>296.3025512695312</v>
       </c>
       <c r="F54" t="n">
-        <v>8535300</v>
+        <v>18049200</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45995</v>
+        <v>46001</v>
       </c>
       <c r="B55" t="n">
-        <v>308.8739918889233</v>
+        <v>296.292632599085</v>
       </c>
       <c r="C55" t="n">
-        <v>314.0307463246157</v>
+        <v>306.8329619363725</v>
       </c>
       <c r="D55" t="n">
-        <v>308.6176225735461</v>
+        <v>294.2811866679717</v>
       </c>
       <c r="E55" t="n">
-        <v>311.6742248535156</v>
+        <v>305.76806640625</v>
       </c>
       <c r="F55" t="n">
-        <v>9627800</v>
+        <v>18874100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="B56" t="n">
-        <v>311.2206641139725</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C56" t="n">
-        <v>314.0208969911127</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D56" t="n">
-        <v>310.2740836361238</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E56" t="n">
-        <v>310.6290588378906</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F56" t="n">
-        <v>6518900</v>
+        <v>9721900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45999</v>
+        <v>46003</v>
       </c>
       <c r="B57" t="n">
-        <v>310.6487980837529</v>
+        <v>315.2041261224818</v>
       </c>
       <c r="C57" t="n">
-        <v>312.0390600856641</v>
+        <v>315.7858618718594</v>
       </c>
       <c r="D57" t="n">
-        <v>308.9627484602848</v>
+        <v>312.1672627021157</v>
       </c>
       <c r="E57" t="n">
-        <v>310.7966918945312</v>
+        <v>314.0603637695312</v>
       </c>
       <c r="F57" t="n">
-        <v>7417200</v>
+        <v>8982900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="B58" t="n">
-        <v>310.5403783790639</v>
+        <v>315.115395356304</v>
       </c>
       <c r="C58" t="n">
-        <v>314.336450228146</v>
+        <v>318.3593402708456</v>
       </c>
       <c r="D58" t="n">
-        <v>295.8193913272319</v>
+        <v>313.9322146909975</v>
       </c>
       <c r="E58" t="n">
-        <v>296.3025512695312</v>
+        <v>315.5393676757812</v>
       </c>
       <c r="F58" t="n">
-        <v>18049200</v>
+        <v>10864100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="B59" t="n">
-        <v>296.2926621709551</v>
+        <v>314.6224027314819</v>
       </c>
       <c r="C59" t="n">
-        <v>306.8329925602339</v>
+        <v>315.0463750601788</v>
       </c>
       <c r="D59" t="n">
-        <v>294.2812160390869</v>
+        <v>309.9980652283745</v>
       </c>
       <c r="E59" t="n">
-        <v>305.7680969238281</v>
+        <v>311.1319580078125</v>
       </c>
       <c r="F59" t="n">
-        <v>18874100</v>
+        <v>8331300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="B60" t="n">
-        <v>304.9102649889192</v>
+        <v>313.971593609235</v>
       </c>
       <c r="C60" t="n">
-        <v>313.5476242674454</v>
+        <v>314.8984348971578</v>
       </c>
       <c r="D60" t="n">
-        <v>304.9102649889192</v>
+        <v>310.254388930852</v>
       </c>
       <c r="E60" t="n">
-        <v>312.9363098144531</v>
+        <v>310.5699157714844</v>
       </c>
       <c r="F60" t="n">
-        <v>9721900</v>
+        <v>8718700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46003</v>
+        <v>46009</v>
       </c>
       <c r="B61" t="n">
-        <v>315.2041261224818</v>
+        <v>311.575672673722</v>
       </c>
       <c r="C61" t="n">
-        <v>315.7858618718594</v>
+        <v>313.2518829489097</v>
       </c>
       <c r="D61" t="n">
-        <v>312.1672627021157</v>
+        <v>307.8485977928193</v>
       </c>
       <c r="E61" t="n">
-        <v>314.0603637695312</v>
+        <v>308.61767578125</v>
       </c>
       <c r="F61" t="n">
-        <v>8982900</v>
+        <v>11444900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="B62" t="n">
-        <v>315.1153648797306</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C62" t="n">
-        <v>318.3593094805321</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D62" t="n">
-        <v>313.9321843288561</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E62" t="n">
-        <v>315.5393371582031</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F62" t="n">
-        <v>10864100</v>
+        <v>24494400</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="B63" t="n">
-        <v>314.6223718715413</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="C63" t="n">
-        <v>315.0463441586525</v>
+        <v>318.7043994886834</v>
       </c>
       <c r="D63" t="n">
-        <v>309.9980348220149</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="E63" t="n">
-        <v>311.1319274902344</v>
+        <v>318.5663452148438</v>
       </c>
       <c r="F63" t="n">
-        <v>8331300</v>
+        <v>8354600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="B64" t="n">
-        <v>313.971593609235</v>
+        <v>319.0790830432475</v>
       </c>
       <c r="C64" t="n">
-        <v>314.8984348971578</v>
+        <v>323.1907116116738</v>
       </c>
       <c r="D64" t="n">
-        <v>310.254388930852</v>
+        <v>318.5663744582675</v>
       </c>
       <c r="E64" t="n">
-        <v>310.5699157714844</v>
+        <v>321.3666076660156</v>
       </c>
       <c r="F64" t="n">
-        <v>8718700</v>
+        <v>6668300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46009</v>
+        <v>46015</v>
       </c>
       <c r="B65" t="n">
-        <v>311.5756418636432</v>
+        <v>321.6722493328215</v>
       </c>
       <c r="C65" t="n">
-        <v>313.2518519730792</v>
+        <v>325.3697449529369</v>
       </c>
       <c r="D65" t="n">
-        <v>307.8485673512913</v>
+        <v>320.9426198260136</v>
       </c>
       <c r="E65" t="n">
-        <v>308.6176452636719</v>
+        <v>324.5612487792969</v>
       </c>
       <c r="F65" t="n">
-        <v>11444900</v>
+        <v>4289300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46010</v>
+        <v>46017</v>
       </c>
       <c r="B66" t="n">
-        <v>309.3965776494671</v>
+        <v>324.502058709128</v>
       </c>
       <c r="C66" t="n">
-        <v>314.099781180705</v>
+        <v>326.2275566521161</v>
       </c>
       <c r="D66" t="n">
-        <v>308.8049723403709</v>
+        <v>321.9680645986219</v>
       </c>
       <c r="E66" t="n">
-        <v>312.7686767578125</v>
+        <v>323.3188781738281</v>
       </c>
       <c r="F66" t="n">
-        <v>24494400</v>
+        <v>4158300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46013</v>
+        <v>46020</v>
       </c>
       <c r="B67" t="n">
-        <v>313.0644852104395</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C67" t="n">
-        <v>318.7043994886834</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D67" t="n">
-        <v>313.0644852104395</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E67" t="n">
-        <v>318.5663452148438</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F67" t="n">
-        <v>8354600</v>
+        <v>8635300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46014</v>
+        <v>46021</v>
       </c>
       <c r="B68" t="n">
-        <v>319.0790830432475</v>
+        <v>320.2623075229155</v>
       </c>
       <c r="C68" t="n">
-        <v>323.1907116116738</v>
+        <v>320.3904921972535</v>
       </c>
       <c r="D68" t="n">
-        <v>318.5663744582675</v>
+        <v>317.9747828016658</v>
       </c>
       <c r="E68" t="n">
-        <v>321.3666076660156</v>
+        <v>318.8917846679688</v>
       </c>
       <c r="F68" t="n">
-        <v>6668300</v>
+        <v>7904300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B69" t="n">
-        <v>321.6722795787551</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C69" t="n">
-        <v>325.3697755465356</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D69" t="n">
-        <v>320.9426500033422</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E69" t="n">
-        <v>324.561279296875</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F69" t="n">
-        <v>4289300</v>
+        <v>5048500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46017</v>
+        <v>46024</v>
       </c>
       <c r="B70" t="n">
-        <v>324.502058709128</v>
+        <v>317.9846252281575</v>
       </c>
       <c r="C70" t="n">
-        <v>326.2275566521161</v>
+        <v>321.1694123071354</v>
       </c>
       <c r="D70" t="n">
-        <v>321.9680645986219</v>
+        <v>316.2492576445291</v>
       </c>
       <c r="E70" t="n">
-        <v>323.3188781738281</v>
+        <v>320.9229125976562</v>
       </c>
       <c r="F70" t="n">
-        <v>4158300</v>
+        <v>8054000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46020</v>
+        <v>46027</v>
       </c>
       <c r="B71" t="n">
-        <v>322.4216288798564</v>
+        <v>320.9426586744551</v>
       </c>
       <c r="C71" t="n">
-        <v>323.1808371734579</v>
+        <v>332.5281463531796</v>
       </c>
       <c r="D71" t="n">
-        <v>319.0002116144308</v>
+        <v>320.637001406751</v>
       </c>
       <c r="E71" t="n">
-        <v>319.2171325683594</v>
+        <v>329.3630981445312</v>
       </c>
       <c r="F71" t="n">
-        <v>8635300</v>
+        <v>10752600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,25 +2289,25 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="B72" t="n">
-        <v>320.2623075229155</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C72" t="n">
-        <v>320.3904921972535</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D72" t="n">
-        <v>317.9747828016658</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E72" t="n">
-        <v>318.8917846679688</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F72" t="n">
-        <v>7904300</v>
+        <v>7660800</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B73" t="n">
-        <v>319.7988699190817</v>
+        <v>327.9764350864437</v>
       </c>
       <c r="C73" t="n">
-        <v>320.3313177342217</v>
+        <v>328.9767653957764</v>
       </c>
       <c r="D73" t="n">
-        <v>317.5310845539587</v>
+        <v>321.4989071734381</v>
       </c>
       <c r="E73" t="n">
-        <v>317.7085571289062</v>
+        <v>323.8660583496094</v>
       </c>
       <c r="F73" t="n">
-        <v>5048500</v>
+        <v>9815200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="B74" t="n">
-        <v>317.9846252281575</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C74" t="n">
-        <v>321.1694123071354</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D74" t="n">
-        <v>316.2492576445291</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E74" t="n">
-        <v>320.9229125976562</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F74" t="n">
-        <v>8054000</v>
+        <v>11737100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="B75" t="n">
-        <v>320.942628937084</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C75" t="n">
-        <v>332.5281155423397</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D75" t="n">
-        <v>320.636971697701</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E75" t="n">
-        <v>329.3630676269531</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F75" t="n">
-        <v>10752600</v>
+        <v>6738100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,25 +2393,25 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46028</v>
+        <v>46034</v>
       </c>
       <c r="B76" t="n">
-        <v>329.4422902981328</v>
+        <v>318.8049332018166</v>
       </c>
       <c r="C76" t="n">
-        <v>332.6612412306879</v>
+        <v>322.9053661093398</v>
       </c>
       <c r="D76" t="n">
-        <v>327.491109600743</v>
+        <v>318.1611490039577</v>
       </c>
       <c r="E76" t="n">
-        <v>331.4132690429688</v>
+        <v>321.3899841308594</v>
       </c>
       <c r="F76" t="n">
-        <v>7660800</v>
+        <v>12805100</v>
       </c>
       <c r="G76" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46029</v>
+        <v>46035</v>
       </c>
       <c r="B77" t="n">
-        <v>327.9764350864437</v>
+        <v>321.2017865718998</v>
       </c>
       <c r="C77" t="n">
-        <v>328.9767653957764</v>
+        <v>323.7373271836527</v>
       </c>
       <c r="D77" t="n">
-        <v>321.4989071734381</v>
+        <v>307.6029755260753</v>
       </c>
       <c r="E77" t="n">
-        <v>323.8660583496094</v>
+        <v>307.9298095703125</v>
       </c>
       <c r="F77" t="n">
-        <v>9815200</v>
+        <v>19371200</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46030</v>
+        <v>46036</v>
       </c>
       <c r="B78" t="n">
-        <v>323.2718313763784</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C78" t="n">
-        <v>328.2339475379842</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D78" t="n">
-        <v>322.5388804495614</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E78" t="n">
-        <v>326.6393432617188</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F78" t="n">
-        <v>11737100</v>
+        <v>25951500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46031</v>
+        <v>46037</v>
       </c>
       <c r="B79" t="n">
-        <v>326.1936353875406</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C79" t="n">
-        <v>328.7291759216584</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D79" t="n">
-        <v>325.0348299492433</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E79" t="n">
-        <v>326.0450744628906</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F79" t="n">
-        <v>6738100</v>
+        <v>14751400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46034</v>
+        <v>46038</v>
       </c>
       <c r="B80" t="n">
-        <v>318.8049332018166</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C80" t="n">
-        <v>322.9053661093398</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D80" t="n">
-        <v>318.1611490039577</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E80" t="n">
-        <v>321.3899841308594</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F80" t="n">
-        <v>12805100</v>
+        <v>14652500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="B81" t="n">
-        <v>321.2017865718998</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C81" t="n">
-        <v>323.7373271836527</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D81" t="n">
-        <v>307.6029755260753</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E81" t="n">
-        <v>307.9298095703125</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F81" t="n">
-        <v>19371200</v>
+        <v>12900600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B82" t="n">
-        <v>305.2556057077196</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C82" t="n">
-        <v>308.7815926253858</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D82" t="n">
-        <v>303.1954601804828</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E82" t="n">
-        <v>304.9287414550781</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F82" t="n">
-        <v>25951500</v>
+        <v>10270100</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="B83" t="n">
-        <v>305.5230197927318</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C83" t="n">
-        <v>309.95031666446</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D83" t="n">
-        <v>304.8098971346673</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E83" t="n">
-        <v>306.3054809570312</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F83" t="n">
-        <v>14751400</v>
+        <v>10535800</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="B84" t="n">
-        <v>307.385060616362</v>
+        <v>299.1148422218051</v>
       </c>
       <c r="C84" t="n">
-        <v>314.1795087286461</v>
+        <v>299.4813025896872</v>
       </c>
       <c r="D84" t="n">
-        <v>307.0383983149945</v>
+        <v>293.6773006232809</v>
       </c>
       <c r="E84" t="n">
-        <v>309.4848022460938</v>
+        <v>294.875732421875</v>
       </c>
       <c r="F84" t="n">
-        <v>14652500</v>
+        <v>11107900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="B85" t="n">
-        <v>303.2845981841295</v>
+        <v>294.9648788077786</v>
       </c>
       <c r="C85" t="n">
-        <v>308.1774060521912</v>
+        <v>298.8969527426069</v>
       </c>
       <c r="D85" t="n">
-        <v>298.9761500928895</v>
+        <v>294.6083325653198</v>
       </c>
       <c r="E85" t="n">
-        <v>299.8477478027344</v>
+        <v>298.1640319824219</v>
       </c>
       <c r="F85" t="n">
-        <v>12900600</v>
+        <v>11752700</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46043</v>
+        <v>46049</v>
       </c>
       <c r="B86" t="n">
-        <v>300.5311849469782</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C86" t="n">
-        <v>302.4823658305288</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D86" t="n">
-        <v>298.2729680555718</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E86" t="n">
-        <v>299.1544799804688</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F86" t="n">
-        <v>10270100</v>
+        <v>11527400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="B87" t="n">
-        <v>301.9474777854751</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C87" t="n">
-        <v>305.2555953909441</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D87" t="n">
-        <v>300.0062112868251</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E87" t="n">
-        <v>300.729248046875</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F87" t="n">
-        <v>10535800</v>
+        <v>9556700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46045</v>
+        <v>46051</v>
       </c>
       <c r="B88" t="n">
-        <v>299.1148422218051</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C88" t="n">
-        <v>299.4813025896872</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D88" t="n">
-        <v>293.6773006232809</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E88" t="n">
-        <v>294.875732421875</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F88" t="n">
-        <v>11107900</v>
+        <v>11580000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="B89" t="n">
-        <v>294.9648788077786</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C89" t="n">
-        <v>298.8969527426069</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D89" t="n">
-        <v>294.6083325653198</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E89" t="n">
-        <v>298.1640319824219</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F89" t="n">
-        <v>11752700</v>
+        <v>11953200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B90" t="n">
-        <v>298.4512235287846</v>
+        <v>301.5513012828864</v>
       </c>
       <c r="C90" t="n">
-        <v>299.0851237823749</v>
+        <v>306.3450582127215</v>
       </c>
       <c r="D90" t="n">
-        <v>295.3016109870806</v>
+        <v>298.4908255461663</v>
       </c>
       <c r="E90" t="n">
-        <v>297.4409790039062</v>
+        <v>305.1961669921875</v>
       </c>
       <c r="F90" t="n">
-        <v>11527400</v>
+        <v>9839400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46050</v>
+        <v>46056</v>
       </c>
       <c r="B91" t="n">
-        <v>297.4013222225187</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C91" t="n">
-        <v>299.0355829225425</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D91" t="n">
-        <v>295.2025300603667</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E91" t="n">
-        <v>297.8965454101562</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F91" t="n">
-        <v>9556700</v>
+        <v>12688000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="B92" t="n">
-        <v>299.5110006693188</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="C92" t="n">
-        <v>303.898671192008</v>
+        <v>316.2594719758441</v>
       </c>
       <c r="D92" t="n">
-        <v>299.3327275624257</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="E92" t="n">
-        <v>303.4926147460938</v>
+        <v>314.2389526367188</v>
       </c>
       <c r="F92" t="n">
-        <v>11580000</v>
+        <v>9848800</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46052</v>
+        <v>46058</v>
       </c>
       <c r="B93" t="n">
-        <v>302.333781642444</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C93" t="n">
-        <v>304.9881708986046</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D93" t="n">
-        <v>299.6694782493637</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E93" t="n">
-        <v>302.9676818847656</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F93" t="n">
-        <v>11953200</v>
+        <v>9388000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="B94" t="n">
-        <v>301.5513012828864</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C94" t="n">
-        <v>306.3450582127215</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D94" t="n">
-        <v>298.4908255461663</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E94" t="n">
-        <v>305.1961669921875</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F94" t="n">
-        <v>9839400</v>
+        <v>17797400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46056</v>
+        <v>46062</v>
       </c>
       <c r="B95" t="n">
-        <v>306.7709905338949</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C95" t="n">
-        <v>313.2286905211348</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D95" t="n">
-        <v>306.1470044328188</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E95" t="n">
-        <v>311.8420715332031</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F95" t="n">
-        <v>12688000</v>
+        <v>11477500</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="B96" t="n">
-        <v>311.4062901330092</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C96" t="n">
-        <v>316.2594719758441</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D96" t="n">
-        <v>311.4062901330092</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E96" t="n">
-        <v>314.2389526367188</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F96" t="n">
-        <v>9848800</v>
+        <v>9902200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="B97" t="n">
-        <v>311.9906259989966</v>
+        <v>320.1518827061323</v>
       </c>
       <c r="C97" t="n">
-        <v>312.9909865673853</v>
+        <v>322.1724018130651</v>
       </c>
       <c r="D97" t="n">
-        <v>302.6210112179966</v>
+        <v>305.7805260837019</v>
       </c>
       <c r="E97" t="n">
-        <v>307.1968688964844</v>
+        <v>307.8505554199219</v>
       </c>
       <c r="F97" t="n">
-        <v>9388000</v>
+        <v>8703500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46059</v>
+        <v>46065</v>
       </c>
       <c r="B98" t="n">
-        <v>311.7034102684662</v>
+        <v>309.2966374972976</v>
       </c>
       <c r="C98" t="n">
-        <v>321.1522783634816</v>
+        <v>310.6238322045743</v>
       </c>
       <c r="D98" t="n">
-        <v>311.7034102684662</v>
+        <v>297.1537535117247</v>
       </c>
       <c r="E98" t="n">
-        <v>319.3199462890625</v>
+        <v>299.7487487792969</v>
       </c>
       <c r="F98" t="n">
-        <v>17797400</v>
+        <v>13443400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="B99" t="n">
-        <v>318.2700781279603</v>
+        <v>295.6680782309701</v>
       </c>
       <c r="C99" t="n">
-        <v>323.2817350541263</v>
+        <v>301.3829738793206</v>
       </c>
       <c r="D99" t="n">
-        <v>317.0518180384032</v>
+        <v>293.6871852314235</v>
       </c>
       <c r="E99" t="n">
-        <v>319.0228271484375</v>
+        <v>299.6595764160156</v>
       </c>
       <c r="F99" t="n">
-        <v>11477500</v>
+        <v>9114500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46063</v>
+        <v>46070</v>
       </c>
       <c r="B100" t="n">
-        <v>319.4684837021083</v>
+        <v>299.8675850307636</v>
       </c>
       <c r="C100" t="n">
-        <v>323.014298845819</v>
+        <v>305.2952123797385</v>
       </c>
       <c r="D100" t="n">
-        <v>312.1094739861534</v>
+        <v>299.6100592744303</v>
       </c>
       <c r="E100" t="n">
-        <v>315.2392883300781</v>
+        <v>304.1958312988281</v>
       </c>
       <c r="F100" t="n">
-        <v>9902200</v>
+        <v>8896800</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B101" t="n">
-        <v>320.1518827061323</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C101" t="n">
-        <v>322.1724018130651</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D101" t="n">
-        <v>305.7805260837019</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E101" t="n">
-        <v>307.8505554199219</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F101" t="n">
-        <v>8703500</v>
+        <v>7209600</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B102" t="n">
-        <v>309.2966374972976</v>
+        <v>304.2354272061944</v>
       </c>
       <c r="C102" t="n">
-        <v>310.6238322045743</v>
+        <v>306.2262038721237</v>
       </c>
       <c r="D102" t="n">
-        <v>297.1537535117247</v>
+        <v>302.2049939958365</v>
       </c>
       <c r="E102" t="n">
-        <v>299.7487487792969</v>
+        <v>305.1069946289062</v>
       </c>
       <c r="F102" t="n">
-        <v>13443400</v>
+        <v>6737700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B103" t="n">
-        <v>295.6680782309701</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C103" t="n">
-        <v>301.3829738793206</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D103" t="n">
-        <v>293.6871852314235</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E103" t="n">
-        <v>299.6595764160156</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F103" t="n">
-        <v>9114500</v>
+        <v>7792700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="B104" t="n">
-        <v>299.8675850307636</v>
+        <v>305.8498457788994</v>
       </c>
       <c r="C104" t="n">
-        <v>305.2952123797385</v>
+        <v>308.0288400173425</v>
       </c>
       <c r="D104" t="n">
-        <v>299.6100592744303</v>
+        <v>292.2807478108573</v>
       </c>
       <c r="E104" t="n">
-        <v>304.1958312988281</v>
+        <v>294.8262023925781</v>
       </c>
       <c r="F104" t="n">
-        <v>8896800</v>
+        <v>12955400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46071</v>
+        <v>46077</v>
       </c>
       <c r="B105" t="n">
-        <v>305.5130974954087</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C105" t="n">
-        <v>309.2966101142475</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D105" t="n">
-        <v>304.2849535938903</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E105" t="n">
-        <v>305.8300476074219</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F105" t="n">
-        <v>7209600</v>
+        <v>13554100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46072</v>
+        <v>46078</v>
       </c>
       <c r="B106" t="n">
-        <v>304.2354272061944</v>
+        <v>295.7869507950724</v>
       </c>
       <c r="C106" t="n">
-        <v>306.2262038721237</v>
+        <v>300.7589812348872</v>
       </c>
       <c r="D106" t="n">
-        <v>302.2049939958365</v>
+        <v>294.1725181992404</v>
       </c>
       <c r="E106" t="n">
-        <v>305.1069946289062</v>
+        <v>300.4024047851562</v>
       </c>
       <c r="F106" t="n">
-        <v>6737700</v>
+        <v>8095500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46073</v>
+        <v>46079</v>
       </c>
       <c r="B107" t="n">
-        <v>305.4536802835111</v>
+        <v>301.670173133609</v>
       </c>
       <c r="C107" t="n">
-        <v>308.0288471084009</v>
+        <v>306.0578739762234</v>
       </c>
       <c r="D107" t="n">
-        <v>302.7596647203387</v>
+        <v>300.7391812579012</v>
       </c>
       <c r="E107" t="n">
-        <v>307.8208618164062</v>
+        <v>303.2053833007812</v>
       </c>
       <c r="F107" t="n">
-        <v>7792700</v>
+        <v>7007800</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46076</v>
+        <v>46080</v>
       </c>
       <c r="B108" t="n">
-        <v>305.8498457788994</v>
+        <v>297.1339389424841</v>
       </c>
       <c r="C108" t="n">
-        <v>308.0288400173425</v>
+        <v>300.0557680991628</v>
       </c>
       <c r="D108" t="n">
-        <v>292.2807478108573</v>
+        <v>291.636973162459</v>
       </c>
       <c r="E108" t="n">
-        <v>294.8262023925781</v>
+        <v>297.4310607910156</v>
       </c>
       <c r="F108" t="n">
-        <v>12955400</v>
+        <v>18620800</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="B109" t="n">
-        <v>293.9843218466586</v>
+        <v>291.9935267958635</v>
       </c>
       <c r="C109" t="n">
-        <v>296.886322684036</v>
+        <v>297.1141484397957</v>
       </c>
       <c r="D109" t="n">
-        <v>288.5962907533433</v>
+        <v>290.4088063693875</v>
       </c>
       <c r="E109" t="n">
-        <v>294.459716796875</v>
+        <v>294.7172546386719</v>
       </c>
       <c r="F109" t="n">
-        <v>13554100</v>
+        <v>8508900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="B110" t="n">
-        <v>295.7869507950724</v>
+        <v>289.4975898716125</v>
       </c>
       <c r="C110" t="n">
-        <v>300.7589812348872</v>
+        <v>299.5011046657454</v>
       </c>
       <c r="D110" t="n">
-        <v>294.1725181992404</v>
+        <v>286.7342359222354</v>
       </c>
       <c r="E110" t="n">
-        <v>300.4024047851562</v>
+        <v>297.3914489746094</v>
       </c>
       <c r="F110" t="n">
-        <v>8095500</v>
+        <v>10278200</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="B111" t="n">
-        <v>301.670173133609</v>
+        <v>297.1240288614248</v>
       </c>
       <c r="C111" t="n">
-        <v>306.0578739762234</v>
+        <v>298.1243894751821</v>
       </c>
       <c r="D111" t="n">
-        <v>300.7391812579012</v>
+        <v>292.993883980321</v>
       </c>
       <c r="E111" t="n">
-        <v>303.2053833007812</v>
+        <v>296.52978515625</v>
       </c>
       <c r="F111" t="n">
-        <v>7007800</v>
+        <v>8055700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46080</v>
+        <v>46086</v>
       </c>
       <c r="B112" t="n">
-        <v>297.1339389424841</v>
+        <v>295.1332451958745</v>
       </c>
       <c r="C112" t="n">
-        <v>300.0557680991628</v>
+        <v>298.3620800816865</v>
       </c>
       <c r="D112" t="n">
-        <v>291.636973162459</v>
+        <v>289.6362492414601</v>
       </c>
       <c r="E112" t="n">
-        <v>297.4310607910156</v>
+        <v>290.7455444335938</v>
       </c>
       <c r="F112" t="n">
-        <v>18620800</v>
+        <v>12732500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="B113" t="n">
-        <v>291.9935267958635</v>
+        <v>283.6044306839189</v>
       </c>
       <c r="C113" t="n">
-        <v>297.1141484397957</v>
+        <v>287.2195541533999</v>
       </c>
       <c r="D113" t="n">
-        <v>290.4088063693875</v>
+        <v>280.9995517042956</v>
       </c>
       <c r="E113" t="n">
-        <v>294.7172546386719</v>
+        <v>286.7144470214844</v>
       </c>
       <c r="F113" t="n">
-        <v>8508900</v>
+        <v>13496500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="B114" t="n">
-        <v>289.4975898716125</v>
+        <v>282.7724816341387</v>
       </c>
       <c r="C114" t="n">
-        <v>299.5011046657454</v>
+        <v>288.3189881947603</v>
       </c>
       <c r="D114" t="n">
-        <v>286.7342359222354</v>
+        <v>277.7707387954702</v>
       </c>
       <c r="E114" t="n">
-        <v>297.3914489746094</v>
+        <v>287.1502685546875</v>
       </c>
       <c r="F114" t="n">
-        <v>10278200</v>
+        <v>12241100</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46085</v>
+        <v>46091</v>
       </c>
       <c r="B115" t="n">
-        <v>297.1240288614248</v>
+        <v>286.5262662545288</v>
       </c>
       <c r="C115" t="n">
-        <v>298.1243894751821</v>
+        <v>289.9532025593205</v>
       </c>
       <c r="D115" t="n">
-        <v>292.993883980321</v>
+        <v>284.4364084963449</v>
       </c>
       <c r="E115" t="n">
-        <v>296.52978515625</v>
+        <v>285.9716186523438</v>
       </c>
       <c r="F115" t="n">
-        <v>8055700</v>
+        <v>8344900</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="B116" t="n">
-        <v>295.1332451958745</v>
+        <v>286.0508166178312</v>
       </c>
       <c r="C116" t="n">
-        <v>298.3620800816865</v>
+        <v>287.7048753720447</v>
       </c>
       <c r="D116" t="n">
-        <v>289.6362492414601</v>
+        <v>282.1385413260368</v>
       </c>
       <c r="E116" t="n">
-        <v>290.7455444335938</v>
+        <v>284.7731323242188</v>
       </c>
       <c r="F116" t="n">
-        <v>12732500</v>
+        <v>10205000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="B117" t="n">
-        <v>283.6044306839189</v>
+        <v>280.1279538528093</v>
       </c>
       <c r="C117" t="n">
-        <v>287.2195541533999</v>
+        <v>281.167940752382</v>
       </c>
       <c r="D117" t="n">
-        <v>280.9995517042956</v>
+        <v>276.4336079693154</v>
       </c>
       <c r="E117" t="n">
-        <v>286.7144470214844</v>
+        <v>280.1874084472656</v>
       </c>
       <c r="F117" t="n">
-        <v>13496500</v>
+        <v>13760500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="B118" t="n">
-        <v>282.7724816341387</v>
+        <v>281.9504072447318</v>
       </c>
       <c r="C118" t="n">
-        <v>288.3189881947603</v>
+        <v>284.4463214441296</v>
       </c>
       <c r="D118" t="n">
-        <v>277.7707387954702</v>
+        <v>280.2468381234208</v>
       </c>
       <c r="E118" t="n">
-        <v>287.1502685546875</v>
+        <v>280.7321472167969</v>
       </c>
       <c r="F118" t="n">
-        <v>12241100</v>
+        <v>9091200</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46091</v>
+        <v>46097</v>
       </c>
       <c r="B119" t="n">
-        <v>286.5262662545288</v>
+        <v>283.6044205599556</v>
       </c>
       <c r="C119" t="n">
-        <v>289.9532025593205</v>
+        <v>286.506421278288</v>
       </c>
       <c r="D119" t="n">
-        <v>284.4364084963449</v>
+        <v>281.8909373944359</v>
       </c>
       <c r="E119" t="n">
-        <v>285.9716186523438</v>
+        <v>283.4261474609375</v>
       </c>
       <c r="F119" t="n">
-        <v>8344900</v>
+        <v>8149000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46092</v>
+        <v>46098</v>
       </c>
       <c r="B120" t="n">
-        <v>286.0508166178312</v>
+        <v>286.2390279690733</v>
       </c>
       <c r="C120" t="n">
-        <v>287.7048753720447</v>
+        <v>288.9726698808299</v>
       </c>
       <c r="D120" t="n">
-        <v>282.1385413260368</v>
+        <v>283.2181783456238</v>
       </c>
       <c r="E120" t="n">
-        <v>284.7731323242188</v>
+        <v>284.1492004394531</v>
       </c>
       <c r="F120" t="n">
-        <v>10205000</v>
+        <v>8961200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46093</v>
+        <v>46099</v>
       </c>
       <c r="B121" t="n">
-        <v>280.1279538528093</v>
+        <v>284.0897484324327</v>
       </c>
       <c r="C121" t="n">
-        <v>281.167940752382</v>
+        <v>286.6451172582804</v>
       </c>
       <c r="D121" t="n">
-        <v>276.4336079693154</v>
+        <v>282.3960934275981</v>
       </c>
       <c r="E121" t="n">
-        <v>280.1874084472656</v>
+        <v>284.9910583496094</v>
       </c>
       <c r="F121" t="n">
-        <v>13760500</v>
+        <v>10057000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="B122" t="n">
-        <v>281.9504072447318</v>
+        <v>284.1392586396808</v>
       </c>
       <c r="C122" t="n">
-        <v>284.4463214441296</v>
+        <v>286.7441374214082</v>
       </c>
       <c r="D122" t="n">
-        <v>280.2468381234208</v>
+        <v>281.9008401776293</v>
       </c>
       <c r="E122" t="n">
-        <v>280.7321472167969</v>
+        <v>285.2188415527344</v>
       </c>
       <c r="F122" t="n">
-        <v>9091200</v>
+        <v>9846700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="B123" t="n">
-        <v>283.6044205599556</v>
+        <v>285.327825032355</v>
       </c>
       <c r="C123" t="n">
-        <v>286.506421278288</v>
+        <v>287.9327042603992</v>
       </c>
       <c r="D123" t="n">
-        <v>281.8909373944359</v>
+        <v>282.5446726819272</v>
       </c>
       <c r="E123" t="n">
-        <v>283.4261474609375</v>
+        <v>283.8223571777344</v>
       </c>
       <c r="F123" t="n">
-        <v>8149000</v>
+        <v>22436500</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="B124" t="n">
-        <v>286.2390279690733</v>
+        <v>291.4982779446762</v>
       </c>
       <c r="C124" t="n">
-        <v>288.9726698808299</v>
+        <v>292.9245231806114</v>
       </c>
       <c r="D124" t="n">
-        <v>283.2181783456238</v>
+        <v>285.2188513876401</v>
       </c>
       <c r="E124" t="n">
-        <v>284.1492004394531</v>
+        <v>287.1403198242188</v>
       </c>
       <c r="F124" t="n">
-        <v>8961200</v>
+        <v>11470800</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="B125" t="n">
-        <v>284.0897484324327</v>
+        <v>283.4360748065673</v>
       </c>
       <c r="C125" t="n">
-        <v>286.6451172582804</v>
+        <v>292.6571288676103</v>
       </c>
       <c r="D125" t="n">
-        <v>282.3960934275981</v>
+        <v>282.6436995084055</v>
       </c>
       <c r="E125" t="n">
-        <v>284.9910583496094</v>
+        <v>289.6065368652344</v>
       </c>
       <c r="F125" t="n">
-        <v>10057000</v>
+        <v>11092300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46100</v>
+        <v>46106</v>
       </c>
       <c r="B126" t="n">
-        <v>284.1392586396808</v>
+        <v>291.3398308899875</v>
       </c>
       <c r="C126" t="n">
-        <v>286.7441374214082</v>
+        <v>294.7965097163498</v>
       </c>
       <c r="D126" t="n">
-        <v>281.9008401776293</v>
+        <v>289.6461758443202</v>
       </c>
       <c r="E126" t="n">
-        <v>285.2188415527344</v>
+        <v>292.5977172851562</v>
       </c>
       <c r="F126" t="n">
-        <v>9846700</v>
+        <v>12188200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="B127" t="n">
-        <v>285.327825032355</v>
+        <v>289.7848205526045</v>
       </c>
       <c r="C127" t="n">
-        <v>287.9327042603992</v>
+        <v>292.1718002190451</v>
       </c>
       <c r="D127" t="n">
-        <v>282.5446726819272</v>
+        <v>287.9525187281419</v>
       </c>
       <c r="E127" t="n">
-        <v>283.8223571777344</v>
+        <v>288.8736267089844</v>
       </c>
       <c r="F127" t="n">
-        <v>22436500</v>
+        <v>8669200</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="B128" t="n">
-        <v>291.4982779446762</v>
+        <v>286.3777093696089</v>
       </c>
       <c r="C128" t="n">
-        <v>292.9245231806114</v>
+        <v>287.3384134369941</v>
       </c>
       <c r="D128" t="n">
-        <v>285.2188513876401</v>
+        <v>279.0582953832721</v>
       </c>
       <c r="E128" t="n">
-        <v>287.1403198242188</v>
+        <v>280.1378784179688</v>
       </c>
       <c r="F128" t="n">
-        <v>11470800</v>
+        <v>9873300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="B129" t="n">
-        <v>283.4360748065673</v>
+        <v>282.0197247859078</v>
       </c>
       <c r="C129" t="n">
-        <v>292.6571288676103</v>
+        <v>284.505755156032</v>
       </c>
       <c r="D129" t="n">
-        <v>282.6436995084055</v>
+        <v>279.6327451103039</v>
       </c>
       <c r="E129" t="n">
-        <v>289.6065368652344</v>
+        <v>281.0589904785156</v>
       </c>
       <c r="F129" t="n">
-        <v>11092300</v>
+        <v>11734400</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="B130" t="n">
-        <v>291.3398308899875</v>
+        <v>285.7140887250632</v>
       </c>
       <c r="C130" t="n">
-        <v>294.7965097163498</v>
+        <v>292.2510413422024</v>
       </c>
       <c r="D130" t="n">
-        <v>289.6461758443202</v>
+        <v>282.2277281014015</v>
       </c>
       <c r="E130" t="n">
-        <v>292.5977172851562</v>
+        <v>291.3497314453125</v>
       </c>
       <c r="F130" t="n">
-        <v>12188200</v>
+        <v>12956900</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B131" t="n">
-        <v>289.7848205526045</v>
+        <v>292.567989087923</v>
       </c>
       <c r="C131" t="n">
-        <v>292.1718002190451</v>
+        <v>295.8661624411999</v>
       </c>
       <c r="D131" t="n">
-        <v>287.9525187281419</v>
+        <v>290.1116710297465</v>
       </c>
       <c r="E131" t="n">
-        <v>288.8736267089844</v>
+        <v>292.5580749511719</v>
       </c>
       <c r="F131" t="n">
-        <v>8669200</v>
+        <v>11267200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="B132" t="n">
-        <v>286.3777093696089</v>
+        <v>289.1212191631598</v>
       </c>
       <c r="C132" t="n">
-        <v>287.3384134369941</v>
+        <v>292.7957669317203</v>
       </c>
       <c r="D132" t="n">
-        <v>279.0582953832721</v>
+        <v>285.9616926535428</v>
       </c>
       <c r="E132" t="n">
-        <v>280.1378784179688</v>
+        <v>291.7855224609375</v>
       </c>
       <c r="F132" t="n">
-        <v>9873300</v>
+        <v>6669300</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,25 +3875,25 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="B133" t="n">
-        <v>282.0197247859078</v>
+        <v>292.7412191857173</v>
       </c>
       <c r="C133" t="n">
-        <v>284.505755156032</v>
+        <v>295.4987855589938</v>
       </c>
       <c r="D133" t="n">
-        <v>279.6327451103039</v>
+        <v>291.8850906324002</v>
       </c>
       <c r="E133" t="n">
-        <v>281.0589904785156</v>
+        <v>294.125</v>
       </c>
       <c r="F133" t="n">
-        <v>11734400</v>
+        <v>7142600</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="B134" t="n">
-        <v>285.7140887250632</v>
+        <v>291.8253790066561</v>
       </c>
       <c r="C134" t="n">
-        <v>292.2510413422024</v>
+        <v>296.8427544058445</v>
       </c>
       <c r="D134" t="n">
-        <v>282.2277281014015</v>
+        <v>291.3873498301165</v>
       </c>
       <c r="E134" t="n">
-        <v>291.3497314453125</v>
+        <v>296.0662536621094</v>
       </c>
       <c r="F134" t="n">
-        <v>12956900</v>
+        <v>7849100</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B135" t="n">
-        <v>292.567989087923</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="C135" t="n">
-        <v>295.8661624411999</v>
+        <v>309.8640903908154</v>
       </c>
       <c r="D135" t="n">
-        <v>290.1116710297465</v>
+        <v>303.9606617936424</v>
       </c>
       <c r="E135" t="n">
-        <v>292.5580749511719</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="F135" t="n">
-        <v>11267200</v>
+        <v>10590200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="B136" t="n">
-        <v>289.1212191631598</v>
+        <v>305.5734164156603</v>
       </c>
       <c r="C136" t="n">
-        <v>292.7957669317203</v>
+        <v>309.8640846884941</v>
       </c>
       <c r="D136" t="n">
-        <v>285.9616926535428</v>
+        <v>304.73715687535</v>
       </c>
       <c r="E136" t="n">
-        <v>291.7855224609375</v>
+        <v>308.938232421875</v>
       </c>
       <c r="F136" t="n">
-        <v>6669300</v>
+        <v>6586600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,25 +3979,25 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="B137" t="n">
-        <v>292.7412191857173</v>
+        <v>308.6097380099313</v>
       </c>
       <c r="C137" t="n">
-        <v>295.4987855589938</v>
+        <v>308.9581744354404</v>
       </c>
       <c r="D137" t="n">
-        <v>291.8850906324002</v>
+        <v>305.344449093958</v>
       </c>
       <c r="E137" t="n">
-        <v>294.125</v>
+        <v>308.4803161621094</v>
       </c>
       <c r="F137" t="n">
-        <v>7142600</v>
+        <v>6069700</v>
       </c>
       <c r="G137" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="B138" t="n">
-        <v>291.8253790066561</v>
+        <v>306.0910825316173</v>
       </c>
       <c r="C138" t="n">
-        <v>296.8427544058445</v>
+        <v>312.3329523629397</v>
       </c>
       <c r="D138" t="n">
-        <v>291.3873498301165</v>
+        <v>304.0900871089203</v>
       </c>
       <c r="E138" t="n">
-        <v>296.0662536621094</v>
+        <v>312.2732238769531</v>
       </c>
       <c r="F138" t="n">
-        <v>7849100</v>
+        <v>8318200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="B139" t="n">
-        <v>306.5888366699219</v>
+        <v>308.4305432499699</v>
       </c>
       <c r="C139" t="n">
-        <v>309.8640903908154</v>
+        <v>312.9103618924516</v>
       </c>
       <c r="D139" t="n">
-        <v>303.9606617936424</v>
+        <v>307.4847916064935</v>
       </c>
       <c r="E139" t="n">
-        <v>306.5888366699219</v>
+        <v>309.7247009277344</v>
       </c>
       <c r="F139" t="n">
-        <v>10590200</v>
+        <v>11455500</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="B140" t="n">
-        <v>305.5734164156603</v>
+        <v>312.5420354159922</v>
       </c>
       <c r="C140" t="n">
-        <v>309.8640846884941</v>
+        <v>312.8307129741003</v>
       </c>
       <c r="D140" t="n">
-        <v>304.73715687535</v>
+        <v>302.8954898881459</v>
       </c>
       <c r="E140" t="n">
-        <v>308.938232421875</v>
+        <v>304.5579833984375</v>
       </c>
       <c r="F140" t="n">
-        <v>6586600</v>
+        <v>9885800</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="B141" t="n">
-        <v>308.6097380099313</v>
+        <v>303.9805907681049</v>
       </c>
       <c r="C141" t="n">
-        <v>308.9581744354404</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="D141" t="n">
-        <v>305.344449093958</v>
+        <v>303.8312695552229</v>
       </c>
       <c r="E141" t="n">
-        <v>308.4803161621094</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="F141" t="n">
-        <v>6069700</v>
+        <v>8208600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="B142" t="n">
-        <v>306.0910825316173</v>
+        <v>311.068653468178</v>
       </c>
       <c r="C142" t="n">
-        <v>312.3329523629397</v>
+        <v>313.4877482505245</v>
       </c>
       <c r="D142" t="n">
-        <v>304.0900871089203</v>
+        <v>308.6993222963794</v>
       </c>
       <c r="E142" t="n">
-        <v>312.2732238769531</v>
+        <v>308.8984375</v>
       </c>
       <c r="F142" t="n">
-        <v>8318200</v>
+        <v>11082400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="B143" t="n">
-        <v>308.4305432499699</v>
+        <v>309.4559416581444</v>
       </c>
       <c r="C143" t="n">
-        <v>312.9103618924516</v>
+        <v>315.7077766193834</v>
       </c>
       <c r="D143" t="n">
-        <v>307.4847916064935</v>
+        <v>308.9780833700189</v>
       </c>
       <c r="E143" t="n">
-        <v>309.7247009277344</v>
+        <v>315.5683898925781</v>
       </c>
       <c r="F143" t="n">
-        <v>11455500</v>
+        <v>10772000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="B144" t="n">
-        <v>312.5420354159922</v>
+        <v>316.0661368489313</v>
       </c>
       <c r="C144" t="n">
-        <v>312.8307129741003</v>
+        <v>318.8038038717339</v>
       </c>
       <c r="D144" t="n">
-        <v>302.8954898881459</v>
+        <v>311.3474041387296</v>
       </c>
       <c r="E144" t="n">
-        <v>304.5579833984375</v>
+        <v>311.5962829589844</v>
       </c>
       <c r="F144" t="n">
-        <v>9885800</v>
+        <v>7084300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="B145" t="n">
-        <v>303.9805907681049</v>
+        <v>313.4379903862348</v>
       </c>
       <c r="C145" t="n">
-        <v>308.5599670410156</v>
+        <v>313.7366328164263</v>
       </c>
       <c r="D145" t="n">
-        <v>303.8312695552229</v>
+        <v>310.5410372905177</v>
       </c>
       <c r="E145" t="n">
-        <v>308.5599670410156</v>
+        <v>311.6161804199219</v>
       </c>
       <c r="F145" t="n">
-        <v>8208600</v>
+        <v>5545900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="B146" t="n">
-        <v>311.068653468178</v>
+        <v>312.1139549773267</v>
       </c>
       <c r="C146" t="n">
-        <v>313.4877482505245</v>
+        <v>313.5773637260273</v>
       </c>
       <c r="D146" t="n">
-        <v>308.6993222963794</v>
+        <v>307.5047445243564</v>
       </c>
       <c r="E146" t="n">
-        <v>308.8984375</v>
+        <v>310.2921752929688</v>
       </c>
       <c r="F146" t="n">
-        <v>11082400</v>
+        <v>6969700</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="B147" t="n">
-        <v>309.4559416581444</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="C147" t="n">
-        <v>315.7077766193834</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="D147" t="n">
-        <v>308.9780833700189</v>
+        <v>306.5092257615542</v>
       </c>
       <c r="E147" t="n">
-        <v>315.5683898925781</v>
+        <v>306.8974609375</v>
       </c>
       <c r="F147" t="n">
-        <v>10772000</v>
+        <v>5215300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B148" t="n">
-        <v>316.0661368489313</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="C148" t="n">
-        <v>318.8038038717339</v>
+        <v>311.1781431330245</v>
       </c>
       <c r="D148" t="n">
-        <v>311.3474041387296</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="E148" t="n">
-        <v>311.5962829589844</v>
+        <v>310.232421875</v>
       </c>
       <c r="F148" t="n">
-        <v>7084300</v>
+        <v>7925300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="B149" t="n">
-        <v>313.4379903862348</v>
+        <v>313.7864355589005</v>
       </c>
       <c r="C149" t="n">
-        <v>313.7366328164263</v>
+        <v>314.035314384572</v>
       </c>
       <c r="D149" t="n">
-        <v>310.5410372905177</v>
+        <v>309.7745101043047</v>
       </c>
       <c r="E149" t="n">
-        <v>311.6161804199219</v>
+        <v>310.0532531738281</v>
       </c>
       <c r="F149" t="n">
-        <v>5545900</v>
+        <v>7398600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="B150" t="n">
-        <v>312.1139549773267</v>
+        <v>309.1771855961317</v>
       </c>
       <c r="C150" t="n">
-        <v>313.5773637260273</v>
+        <v>310.6505287563671</v>
       </c>
       <c r="D150" t="n">
-        <v>307.5047445243564</v>
+        <v>305.9118967162461</v>
       </c>
       <c r="E150" t="n">
-        <v>310.2921752929688</v>
+        <v>307.8630981445312</v>
       </c>
       <c r="F150" t="n">
-        <v>6969700</v>
+        <v>8031800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="B151" t="n">
-        <v>309.7545850384977</v>
+        <v>305.6928786901284</v>
       </c>
       <c r="C151" t="n">
-        <v>309.7545850384977</v>
+        <v>312.6913497643884</v>
       </c>
       <c r="D151" t="n">
-        <v>306.5092257615542</v>
+        <v>305.1951210592971</v>
       </c>
       <c r="E151" t="n">
-        <v>306.8974609375</v>
+        <v>311.8252563476562</v>
       </c>
       <c r="F151" t="n">
-        <v>5215300</v>
+        <v>8865400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="B152" t="n">
-        <v>305.5037244427344</v>
+        <v>312.5420381202088</v>
       </c>
       <c r="C152" t="n">
-        <v>311.1781431330245</v>
+        <v>314.6624601726697</v>
       </c>
       <c r="D152" t="n">
-        <v>305.5037244427344</v>
+        <v>310.431520181067</v>
       </c>
       <c r="E152" t="n">
-        <v>310.232421875</v>
+        <v>311.0686645507812</v>
       </c>
       <c r="F152" t="n">
-        <v>7925300</v>
+        <v>6135400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="B153" t="n">
-        <v>313.7864355589005</v>
+        <v>309.2269452093906</v>
       </c>
       <c r="C153" t="n">
-        <v>314.035314384572</v>
+        <v>309.2568094519629</v>
       </c>
       <c r="D153" t="n">
-        <v>309.7745101043047</v>
+        <v>305.1353920734132</v>
       </c>
       <c r="E153" t="n">
-        <v>310.0532531738281</v>
+        <v>306.270263671875</v>
       </c>
       <c r="F153" t="n">
-        <v>7398600</v>
+        <v>7338200</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="B154" t="n">
-        <v>309.1771855961317</v>
+        <v>306.3299974055641</v>
       </c>
       <c r="C154" t="n">
-        <v>310.6505287563671</v>
+        <v>309.5753869306937</v>
       </c>
       <c r="D154" t="n">
-        <v>305.9118967162461</v>
+        <v>305.42407485773</v>
       </c>
       <c r="E154" t="n">
-        <v>307.8630981445312</v>
+        <v>308.0124206542969</v>
       </c>
       <c r="F154" t="n">
-        <v>8031800</v>
+        <v>6316800</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="B155" t="n">
-        <v>305.6928786901284</v>
+        <v>310.0532528884956</v>
       </c>
       <c r="C155" t="n">
-        <v>312.6913497643884</v>
+        <v>314.8416790595512</v>
       </c>
       <c r="D155" t="n">
-        <v>305.1951210592971</v>
+        <v>309.9536952821754</v>
       </c>
       <c r="E155" t="n">
-        <v>311.8252563476562</v>
+        <v>313.4877624511719</v>
       </c>
       <c r="F155" t="n">
-        <v>8865400</v>
+        <v>8629500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="B156" t="n">
-        <v>312.5420381202088</v>
+        <v>313.2388767644321</v>
       </c>
       <c r="C156" t="n">
-        <v>314.6624601726697</v>
+        <v>314.8814709002291</v>
       </c>
       <c r="D156" t="n">
-        <v>310.431520181067</v>
+        <v>304.7670623908274</v>
       </c>
       <c r="E156" t="n">
-        <v>311.0686645507812</v>
+        <v>304.8964538574219</v>
       </c>
       <c r="F156" t="n">
-        <v>6135400</v>
+        <v>8359600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="B157" t="n">
-        <v>309.2269452093906</v>
+        <v>306.8675912418493</v>
       </c>
       <c r="C157" t="n">
-        <v>309.2568094519629</v>
+        <v>307.6042628420606</v>
       </c>
       <c r="D157" t="n">
-        <v>305.1353920734132</v>
+        <v>299.1523476664256</v>
       </c>
       <c r="E157" t="n">
-        <v>306.270263671875</v>
+        <v>300.7451782226562</v>
       </c>
       <c r="F157" t="n">
-        <v>7338200</v>
+        <v>9464300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="B158" t="n">
-        <v>306.3299974055641</v>
+        <v>300.7451596100784</v>
       </c>
       <c r="C158" t="n">
-        <v>309.5753869306937</v>
+        <v>301.8302675742967</v>
       </c>
       <c r="D158" t="n">
-        <v>305.42407485773</v>
+        <v>297.5395993270601</v>
       </c>
       <c r="E158" t="n">
-        <v>308.0124206542969</v>
+        <v>298.6545715332031</v>
       </c>
       <c r="F158" t="n">
-        <v>6316800</v>
+        <v>9512000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="B159" t="n">
-        <v>310.0532528884956</v>
+        <v>298.6744753830843</v>
       </c>
       <c r="C159" t="n">
-        <v>314.8416790595512</v>
+        <v>304.6873960201211</v>
       </c>
       <c r="D159" t="n">
-        <v>309.9536952821754</v>
+        <v>294.2245209852311</v>
       </c>
       <c r="E159" t="n">
-        <v>313.4877624511719</v>
+        <v>303.5126953125</v>
       </c>
       <c r="F159" t="n">
-        <v>8629500</v>
+        <v>9498200</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="B160" t="n">
-        <v>313.2388767644321</v>
+        <v>300.9144028967509</v>
       </c>
       <c r="C160" t="n">
-        <v>314.8814709002291</v>
+        <v>301.6411400127173</v>
       </c>
       <c r="D160" t="n">
-        <v>304.7670623908274</v>
+        <v>298.7242874353194</v>
       </c>
       <c r="E160" t="n">
-        <v>304.8964538574219</v>
+        <v>298.9034729003906</v>
       </c>
       <c r="F160" t="n">
-        <v>8359600</v>
+        <v>7709500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="B161" t="n">
-        <v>306.8675912418493</v>
+        <v>300.8945046380796</v>
       </c>
       <c r="C161" t="n">
-        <v>307.6042628420606</v>
+        <v>302.387777613951</v>
       </c>
       <c r="D161" t="n">
-        <v>299.1523476664256</v>
+        <v>297.4699295162906</v>
       </c>
       <c r="E161" t="n">
-        <v>300.7451782226562</v>
+        <v>298.5650024414062</v>
       </c>
       <c r="F161" t="n">
-        <v>9464300</v>
+        <v>7364300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B162" t="n">
-        <v>300.7451596100784</v>
+        <v>298.8636262885424</v>
       </c>
       <c r="C162" t="n">
-        <v>301.8302675742967</v>
+        <v>299.4410421498196</v>
       </c>
       <c r="D162" t="n">
-        <v>297.5395993270601</v>
+        <v>295.1205095874812</v>
       </c>
       <c r="E162" t="n">
-        <v>298.6545715332031</v>
+        <v>296.4743957519531</v>
       </c>
       <c r="F162" t="n">
-        <v>9512000</v>
+        <v>8699300</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B163" t="n">
-        <v>298.6744753830843</v>
+        <v>296.6635495230975</v>
       </c>
       <c r="C163" t="n">
-        <v>304.6873960201211</v>
+        <v>299.908939014877</v>
       </c>
       <c r="D163" t="n">
-        <v>294.2245209852311</v>
+        <v>295.8870488301784</v>
       </c>
       <c r="E163" t="n">
-        <v>303.5126953125</v>
+        <v>299.3813171386719</v>
       </c>
       <c r="F163" t="n">
-        <v>9498200</v>
+        <v>7546300</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B164" t="n">
-        <v>300.9144028967509</v>
+        <v>299.7396822358739</v>
       </c>
       <c r="C164" t="n">
-        <v>301.6411400127173</v>
+        <v>300.436555061437</v>
       </c>
       <c r="D164" t="n">
-        <v>298.7242874353194</v>
+        <v>293.935841710235</v>
       </c>
       <c r="E164" t="n">
-        <v>298.9034729003906</v>
+        <v>294.3738708496094</v>
       </c>
       <c r="F164" t="n">
-        <v>7709500</v>
+        <v>8066900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B165" t="n">
-        <v>300.8945046380796</v>
+        <v>295.3694126574367</v>
       </c>
       <c r="C165" t="n">
-        <v>302.387777613951</v>
+        <v>301.57145376365</v>
       </c>
       <c r="D165" t="n">
-        <v>297.4699295162906</v>
+        <v>292.3530024013792</v>
       </c>
       <c r="E165" t="n">
-        <v>298.5650024414062</v>
+        <v>300.625732421875</v>
       </c>
       <c r="F165" t="n">
-        <v>7364300</v>
+        <v>9327000</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B166" t="n">
-        <v>298.8636262885424</v>
+        <v>299.8790926087445</v>
       </c>
       <c r="C166" t="n">
-        <v>299.4410421498196</v>
+        <v>302.6167597554335</v>
       </c>
       <c r="D166" t="n">
-        <v>295.1205095874812</v>
+        <v>298.8636475324957</v>
       </c>
       <c r="E166" t="n">
-        <v>296.4743957519531</v>
+        <v>301.6411437988281</v>
       </c>
       <c r="F166" t="n">
-        <v>8699300</v>
+        <v>7874400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="B167" t="n">
-        <v>296.6635495230975</v>
+        <v>303.3135932887391</v>
       </c>
       <c r="C167" t="n">
-        <v>299.908939014877</v>
+        <v>306.0711901040885</v>
       </c>
       <c r="D167" t="n">
-        <v>295.8870488301784</v>
+        <v>302.4773640852478</v>
       </c>
       <c r="E167" t="n">
-        <v>299.3813171386719</v>
+        <v>305.0059814453125</v>
       </c>
       <c r="F167" t="n">
-        <v>7546300</v>
+        <v>5973900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B168" t="n">
-        <v>299.7396822358739</v>
+        <v>307.1065011172144</v>
       </c>
       <c r="C168" t="n">
-        <v>300.436555061437</v>
+        <v>308.5400455607295</v>
       </c>
       <c r="D168" t="n">
-        <v>293.935841710235</v>
+        <v>304.0701916446211</v>
       </c>
       <c r="E168" t="n">
-        <v>294.3738708496094</v>
+        <v>305.3643493652344</v>
       </c>
       <c r="F168" t="n">
-        <v>8066900</v>
+        <v>7725400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="B169" t="n">
-        <v>295.3694126574367</v>
+        <v>303.6321536663258</v>
       </c>
       <c r="C169" t="n">
-        <v>301.57145376365</v>
+        <v>304.5281113223131</v>
       </c>
       <c r="D169" t="n">
-        <v>292.3530024013792</v>
+        <v>294.4236375305438</v>
       </c>
       <c r="E169" t="n">
-        <v>300.625732421875</v>
+        <v>297.9378051757812</v>
       </c>
       <c r="F169" t="n">
-        <v>9327000</v>
+        <v>11779200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="B170" t="n">
-        <v>299.8790926087445</v>
+        <v>296.2354906683788</v>
       </c>
       <c r="C170" t="n">
-        <v>302.6167597554335</v>
+        <v>299.7197941661088</v>
       </c>
       <c r="D170" t="n">
-        <v>298.8636475324957</v>
+        <v>294.4236455581874</v>
       </c>
       <c r="E170" t="n">
-        <v>301.6411437988281</v>
+        <v>295.3992614746094</v>
       </c>
       <c r="F170" t="n">
-        <v>7874400</v>
+        <v>9757700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B171" t="n">
-        <v>303.3135932887391</v>
+        <v>295.070728717322</v>
       </c>
       <c r="C171" t="n">
-        <v>306.0711901040885</v>
+        <v>298.5351328968941</v>
       </c>
       <c r="D171" t="n">
-        <v>302.4773640852478</v>
+        <v>293.8761285862639</v>
       </c>
       <c r="E171" t="n">
-        <v>305.0059814453125</v>
+        <v>297.9676818847656</v>
       </c>
       <c r="F171" t="n">
-        <v>5973900</v>
+        <v>13969000</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="B172" t="n">
-        <v>307.1065011172144</v>
+        <v>296.3549462063085</v>
       </c>
       <c r="C172" t="n">
-        <v>308.5400455607295</v>
+        <v>298.2065900448191</v>
       </c>
       <c r="D172" t="n">
-        <v>304.0701916446211</v>
+        <v>293.9457858606032</v>
       </c>
       <c r="E172" t="n">
-        <v>305.3643493652344</v>
+        <v>295.2499084472656</v>
       </c>
       <c r="F172" t="n">
-        <v>7725400</v>
+        <v>7930000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46169</v>
+        <v>46175</v>
       </c>
       <c r="B173" t="n">
-        <v>303.6321536663258</v>
+        <v>295.170270518017</v>
       </c>
       <c r="C173" t="n">
-        <v>304.5281113223131</v>
+        <v>300.7152977310929</v>
       </c>
       <c r="D173" t="n">
-        <v>294.4236375305438</v>
+        <v>293.9457758280521</v>
       </c>
       <c r="E173" t="n">
-        <v>297.9378051757812</v>
+        <v>299.6102600097656</v>
       </c>
       <c r="F173" t="n">
-        <v>11779200</v>
+        <v>8296200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="B174" t="n">
-        <v>296.2354906683788</v>
+        <v>298.5749714904202</v>
       </c>
       <c r="C174" t="n">
-        <v>299.7197941661088</v>
+        <v>300.6058008918799</v>
       </c>
       <c r="D174" t="n">
-        <v>294.4236455581874</v>
+        <v>295.2300241797341</v>
       </c>
       <c r="E174" t="n">
-        <v>295.3992614746094</v>
+        <v>299.5007934570312</v>
       </c>
       <c r="F174" t="n">
-        <v>9757700</v>
+        <v>7003900</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="B175" t="n">
-        <v>295.070728717322</v>
+        <v>304.3688300919619</v>
       </c>
       <c r="C175" t="n">
-        <v>298.5351328968941</v>
+        <v>311.5066879726736</v>
       </c>
       <c r="D175" t="n">
-        <v>293.8761285862639</v>
+        <v>303.0746723882986</v>
       </c>
       <c r="E175" t="n">
-        <v>297.9676818847656</v>
+        <v>309.4957580566406</v>
       </c>
       <c r="F175" t="n">
-        <v>13969000</v>
+        <v>10345200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="B176" t="n">
-        <v>296.3549462063085</v>
+        <v>312.8805189963161</v>
       </c>
       <c r="C176" t="n">
-        <v>298.2065900448191</v>
+        <v>313.5873263681962</v>
       </c>
       <c r="D176" t="n">
-        <v>293.9457858606032</v>
+        <v>308.211549706599</v>
       </c>
       <c r="E176" t="n">
-        <v>295.2499084472656</v>
+        <v>310.9691162109375</v>
       </c>
       <c r="F176" t="n">
-        <v>7930000</v>
+        <v>9118800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="B177" t="n">
-        <v>295.170270518017</v>
+        <v>311.8451695343703</v>
       </c>
       <c r="C177" t="n">
-        <v>300.7152977310929</v>
+        <v>314.881479064701</v>
       </c>
       <c r="D177" t="n">
-        <v>293.9457758280521</v>
+        <v>309.3862455138746</v>
       </c>
       <c r="E177" t="n">
-        <v>299.6102600097656</v>
+        <v>309.7147521972656</v>
       </c>
       <c r="F177" t="n">
-        <v>8296200</v>
+        <v>6827000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="B178" t="n">
-        <v>298.5749714904202</v>
+        <v>312.1040028799189</v>
       </c>
       <c r="C178" t="n">
-        <v>300.6058008918799</v>
+        <v>315.0009559692908</v>
       </c>
       <c r="D178" t="n">
-        <v>295.2300241797341</v>
+        <v>307.6241841525692</v>
       </c>
       <c r="E178" t="n">
-        <v>299.5007934570312</v>
+        <v>311.2976379394531</v>
       </c>
       <c r="F178" t="n">
-        <v>7003900</v>
+        <v>11594600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="B179" t="n">
-        <v>304.3688300919619</v>
+        <v>311.1582462393224</v>
       </c>
       <c r="C179" t="n">
-        <v>311.5066879726736</v>
+        <v>313.3384270822022</v>
       </c>
       <c r="D179" t="n">
-        <v>303.0746723882986</v>
+        <v>307.6440785979976</v>
       </c>
       <c r="E179" t="n">
-        <v>309.4957580566406</v>
+        <v>307.7536010742188</v>
       </c>
       <c r="F179" t="n">
-        <v>10345200</v>
+        <v>7446200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B180" t="n">
-        <v>312.8805189963161</v>
+        <v>308.1717081621576</v>
       </c>
       <c r="C180" t="n">
-        <v>313.5873263681962</v>
+        <v>313.3085706612414</v>
       </c>
       <c r="D180" t="n">
-        <v>308.211549706599</v>
+        <v>307.4947650619962</v>
       </c>
       <c r="E180" t="n">
-        <v>310.9691162109375</v>
+        <v>312.0840759277344</v>
       </c>
       <c r="F180" t="n">
-        <v>9118800</v>
+        <v>9116600</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="B181" t="n">
-        <v>311.8451695343703</v>
+        <v>314.5529794375797</v>
       </c>
       <c r="C181" t="n">
-        <v>314.881479064701</v>
+        <v>319.8590627688811</v>
       </c>
       <c r="D181" t="n">
-        <v>309.3862455138746</v>
+        <v>314.1348496322589</v>
       </c>
       <c r="E181" t="n">
-        <v>309.7147521972656</v>
+        <v>319.2816772460938</v>
       </c>
       <c r="F181" t="n">
-        <v>6827000</v>
+        <v>7426200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="B182" t="n">
-        <v>312.1040028799189</v>
+        <v>322.4673390673774</v>
       </c>
       <c r="C182" t="n">
-        <v>315.0009559692908</v>
+        <v>324.4583697274161</v>
       </c>
       <c r="D182" t="n">
-        <v>307.6241841525692</v>
+        <v>317.4101041776777</v>
       </c>
       <c r="E182" t="n">
-        <v>311.2976379394531</v>
+        <v>317.9675903320312</v>
       </c>
       <c r="F182" t="n">
-        <v>11594600</v>
+        <v>7988900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="B183" t="n">
-        <v>311.1582462393224</v>
+        <v>322.8455866314347</v>
       </c>
       <c r="C183" t="n">
-        <v>313.3384270822022</v>
+        <v>330.2621874699331</v>
       </c>
       <c r="D183" t="n">
-        <v>307.6440785979976</v>
+        <v>322.5668435738929</v>
       </c>
       <c r="E183" t="n">
-        <v>307.7536010742188</v>
+        <v>329.6549377441406</v>
       </c>
       <c r="F183" t="n">
-        <v>7446200</v>
+        <v>11094900</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="B184" t="n">
-        <v>308.1717081621576</v>
+        <v>330.6902497468859</v>
       </c>
       <c r="C184" t="n">
-        <v>313.3085706612414</v>
+        <v>336.2551763704633</v>
       </c>
       <c r="D184" t="n">
-        <v>307.4947650619962</v>
+        <v>330.0133066656099</v>
       </c>
       <c r="E184" t="n">
-        <v>312.0840759277344</v>
+        <v>331.9645080566406</v>
       </c>
       <c r="F184" t="n">
-        <v>9116600</v>
+        <v>12246400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="B185" t="n">
-        <v>314.5529794375797</v>
+        <v>335.4388795655989</v>
       </c>
       <c r="C185" t="n">
-        <v>319.8590627688811</v>
+        <v>336.5737511659094</v>
       </c>
       <c r="D185" t="n">
-        <v>314.1348496322589</v>
+        <v>322.7062308624821</v>
       </c>
       <c r="E185" t="n">
-        <v>319.2816772460938</v>
+        <v>323.761474609375</v>
       </c>
       <c r="F185" t="n">
-        <v>7426200</v>
+        <v>20111000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B186" t="n">
-        <v>322.4673390673774</v>
+        <v>328.221392261561</v>
       </c>
       <c r="C186" t="n">
-        <v>324.4583697274161</v>
+        <v>331.2776010100568</v>
       </c>
       <c r="D186" t="n">
-        <v>317.4101041776777</v>
+        <v>325.2846101022313</v>
       </c>
       <c r="E186" t="n">
-        <v>317.9675903320312</v>
+        <v>329.993408203125</v>
       </c>
       <c r="F186" t="n">
-        <v>7988900</v>
+        <v>10182500</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="B187" t="n">
-        <v>322.8455866314347</v>
+        <v>327.9924099173137</v>
       </c>
       <c r="C187" t="n">
-        <v>330.2621874699331</v>
+        <v>333.8659438033595</v>
       </c>
       <c r="D187" t="n">
-        <v>322.5668435738929</v>
+        <v>325.7425357353925</v>
       </c>
       <c r="E187" t="n">
-        <v>329.6549377441406</v>
+        <v>332.6414794921875</v>
       </c>
       <c r="F187" t="n">
-        <v>11094900</v>
+        <v>7582200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="B188" t="n">
-        <v>330.6902497468859</v>
+        <v>331.5762891678024</v>
       </c>
       <c r="C188" t="n">
-        <v>336.2551763704633</v>
+        <v>333.0297330031709</v>
       </c>
       <c r="D188" t="n">
-        <v>330.0133066656099</v>
+        <v>328.291070440402</v>
       </c>
       <c r="E188" t="n">
-        <v>331.9645080566406</v>
+        <v>331.95458984375</v>
       </c>
       <c r="F188" t="n">
-        <v>12246400</v>
+        <v>7907400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="B189" t="n">
-        <v>335.4388795655989</v>
+        <v>333.4577793441399</v>
       </c>
       <c r="C189" t="n">
-        <v>336.5737511659094</v>
+        <v>341.909724468194</v>
       </c>
       <c r="D189" t="n">
-        <v>322.7062308624821</v>
+        <v>333.2586945227413</v>
       </c>
       <c r="E189" t="n">
-        <v>323.761474609375</v>
+        <v>333.6170654296875</v>
       </c>
       <c r="F189" t="n">
-        <v>20111000</v>
+        <v>10043100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="B190" t="n">
-        <v>328.221392261561</v>
+        <v>334.4931229022353</v>
       </c>
       <c r="C190" t="n">
-        <v>331.2776010100568</v>
+        <v>334.8913229247855</v>
       </c>
       <c r="D190" t="n">
-        <v>325.2846101022313</v>
+        <v>326.0312433050061</v>
       </c>
       <c r="E190" t="n">
-        <v>329.993408203125</v>
+        <v>327.5742797851562</v>
       </c>
       <c r="F190" t="n">
-        <v>10182500</v>
+        <v>17640900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="B191" t="n">
-        <v>327.9924099173137</v>
+        <v>326.8077430430495</v>
       </c>
       <c r="C191" t="n">
-        <v>333.8659438033595</v>
+        <v>330.8993264933345</v>
       </c>
       <c r="D191" t="n">
-        <v>325.7425357353925</v>
+        <v>325.7325999471821</v>
       </c>
       <c r="E191" t="n">
-        <v>332.6414794921875</v>
+        <v>327.9127807617188</v>
       </c>
       <c r="F191" t="n">
-        <v>7582200</v>
+        <v>7981800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46197</v>
+        <v>46203</v>
       </c>
       <c r="B192" t="n">
-        <v>331.5762891678024</v>
+        <v>327.4150312810326</v>
       </c>
       <c r="C192" t="n">
-        <v>333.0297330031709</v>
+        <v>328.9580677951163</v>
       </c>
       <c r="D192" t="n">
-        <v>328.291070440402</v>
+        <v>325.2149206632551</v>
       </c>
       <c r="E192" t="n">
-        <v>331.95458984375</v>
+        <v>325.8619995117188</v>
       </c>
       <c r="F192" t="n">
-        <v>7907400</v>
+        <v>8080100</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46198</v>
+        <v>46204</v>
       </c>
       <c r="B193" t="n">
-        <v>333.4577793441399</v>
+        <v>326.8973584256916</v>
       </c>
       <c r="C193" t="n">
-        <v>341.909724468194</v>
+        <v>334.1347741939035</v>
       </c>
       <c r="D193" t="n">
-        <v>333.2586945227413</v>
+        <v>323.5524415571975</v>
       </c>
       <c r="E193" t="n">
-        <v>333.6170654296875</v>
+        <v>332.5718078613281</v>
       </c>
       <c r="F193" t="n">
-        <v>10043100</v>
+        <v>15210200</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46199</v>
+        <v>46205</v>
       </c>
       <c r="B194" t="n">
-        <v>334.4931229022353</v>
+        <v>336.5040683580973</v>
       </c>
       <c r="C194" t="n">
-        <v>334.8913229247855</v>
+        <v>338.4751995750331</v>
       </c>
       <c r="D194" t="n">
-        <v>326.0312433050061</v>
+        <v>330.2820977776739</v>
       </c>
       <c r="E194" t="n">
-        <v>327.5742797851562</v>
+        <v>332.9700012207031</v>
       </c>
       <c r="F194" t="n">
-        <v>17640900</v>
+        <v>8413900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,25 +5487,25 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="B195" t="n">
-        <v>326.8077430430495</v>
+        <v>335</v>
       </c>
       <c r="C195" t="n">
-        <v>330.8993264933345</v>
+        <v>339.7200012207031</v>
       </c>
       <c r="D195" t="n">
-        <v>325.7325999471821</v>
+        <v>334.1099853515625</v>
       </c>
       <c r="E195" t="n">
-        <v>327.9127807617188</v>
+        <v>337.7200012207031</v>
       </c>
       <c r="F195" t="n">
-        <v>7981800</v>
+        <v>8673500</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B196" t="n">
-        <v>327.4150312810326</v>
+        <v>340.9800109863281</v>
       </c>
       <c r="C196" t="n">
-        <v>328.9580677951163</v>
+        <v>341.3999938964844</v>
       </c>
       <c r="D196" t="n">
-        <v>325.2149206632551</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E196" t="n">
-        <v>325.8619995117188</v>
+        <v>339.2200012207031</v>
       </c>
       <c r="F196" t="n">
-        <v>8080100</v>
+        <v>7115800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="B197" t="n">
-        <v>326.8973584256916</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="C197" t="n">
-        <v>334.1347741939035</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="D197" t="n">
-        <v>323.5524415571975</v>
+        <v>330.1300048828125</v>
       </c>
       <c r="E197" t="n">
-        <v>332.5718078613281</v>
+        <v>330.6199951171875</v>
       </c>
       <c r="F197" t="n">
-        <v>15210200</v>
+        <v>18505200</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="B198" t="n">
-        <v>336.5040683580973</v>
+        <v>331.4599914550781</v>
       </c>
       <c r="C198" t="n">
-        <v>338.4751995750331</v>
+        <v>337</v>
       </c>
       <c r="D198" t="n">
-        <v>330.2820977776739</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="E198" t="n">
-        <v>332.9700012207031</v>
+        <v>335.4700012207031</v>
       </c>
       <c r="F198" t="n">
-        <v>8413900</v>
+        <v>15570600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,25 +5591,25 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B199" t="n">
-        <v>335</v>
+        <v>337.4700012207031</v>
       </c>
       <c r="C199" t="n">
-        <v>339.7200012207031</v>
+        <v>338.5899963378906</v>
       </c>
       <c r="D199" t="n">
-        <v>334.1099853515625</v>
+        <v>335.7699890136719</v>
       </c>
       <c r="E199" t="n">
-        <v>337.7200012207031</v>
+        <v>336.4700012207031</v>
       </c>
       <c r="F199" t="n">
-        <v>8673500</v>
+        <v>6299000</v>
       </c>
       <c r="G199" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B200" t="n">
-        <v>340.9800109863281</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="C200" t="n">
-        <v>341.3999938964844</v>
+        <v>338.3500061035156</v>
       </c>
       <c r="D200" t="n">
-        <v>337.0899963378906</v>
+        <v>332.5</v>
       </c>
       <c r="E200" t="n">
-        <v>339.2200012207031</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="F200" t="n">
-        <v>7115800</v>
+        <v>7120300</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="B201" t="n">
-        <v>336.5299987792969</v>
+        <v>327</v>
       </c>
       <c r="C201" t="n">
-        <v>336.5299987792969</v>
+        <v>344.7300109863281</v>
       </c>
       <c r="D201" t="n">
-        <v>330.1300048828125</v>
+        <v>325.75</v>
       </c>
       <c r="E201" t="n">
-        <v>330.6199951171875</v>
+        <v>342.8900146484375</v>
       </c>
       <c r="F201" t="n">
-        <v>18505200</v>
+        <v>14537900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>331.4599914550781</v>
+        <v>345.8500061035156</v>
       </c>
       <c r="C202" t="n">
-        <v>337</v>
+        <v>351.239990234375</v>
       </c>
       <c r="D202" t="n">
-        <v>330.8099975585938</v>
+        <v>344.0499877929688</v>
       </c>
       <c r="E202" t="n">
-        <v>335.4700012207031</v>
+        <v>346.9100036621094</v>
       </c>
       <c r="F202" t="n">
-        <v>15570600</v>
+        <v>10750000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B203" t="n">
-        <v>337.4700012207031</v>
+        <v>349.2799987792969</v>
       </c>
       <c r="C203" t="n">
-        <v>338.5899963378906</v>
+        <v>349.3399963378906</v>
       </c>
       <c r="D203" t="n">
-        <v>335.7699890136719</v>
+        <v>341.1099853515625</v>
       </c>
       <c r="E203" t="n">
-        <v>336.4700012207031</v>
+        <v>343.1499938964844</v>
       </c>
       <c r="F203" t="n">
-        <v>6299000</v>
+        <v>12432400</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="B204" t="n">
-        <v>338.3399963378906</v>
+        <v>339.0299987792969</v>
       </c>
       <c r="C204" t="n">
-        <v>338.3500061035156</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="D204" t="n">
-        <v>332.5</v>
+        <v>335.0499877929688</v>
       </c>
       <c r="E204" t="n">
-        <v>334.5299987792969</v>
+        <v>341.1000061035156</v>
       </c>
       <c r="F204" t="n">
-        <v>7120300</v>
+        <v>9250900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B205" t="n">
-        <v>327</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="C205" t="n">
-        <v>344.7300109863281</v>
+        <v>344.260009765625</v>
       </c>
       <c r="D205" t="n">
-        <v>325.75</v>
+        <v>337.3699951171875</v>
       </c>
       <c r="E205" t="n">
-        <v>342.8900146484375</v>
+        <v>338.8699951171875</v>
       </c>
       <c r="F205" t="n">
-        <v>14537900</v>
+        <v>7723300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="B206" t="n">
-        <v>345.8500061035156</v>
+        <v>340.1199951171875</v>
       </c>
       <c r="C206" t="n">
-        <v>351.239990234375</v>
+        <v>345.739990234375</v>
       </c>
       <c r="D206" t="n">
-        <v>344.0499877929688</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E206" t="n">
-        <v>346.9100036621094</v>
+        <v>345.2300109863281</v>
       </c>
       <c r="F206" t="n">
-        <v>10750000</v>
+        <v>6015300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="B207" t="n">
-        <v>349.2799987792969</v>
+        <v>345.0700073242188</v>
       </c>
       <c r="C207" t="n">
-        <v>349.3399963378906</v>
+        <v>349.0700073242188</v>
       </c>
       <c r="D207" t="n">
-        <v>341.1099853515625</v>
+        <v>344.25</v>
       </c>
       <c r="E207" t="n">
-        <v>343.1499938964844</v>
+        <v>348.2099914550781</v>
       </c>
       <c r="F207" t="n">
-        <v>12432400</v>
+        <v>8040200</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="B208" t="n">
-        <v>339.0299987792969</v>
+        <v>346.5799865722656</v>
       </c>
       <c r="C208" t="n">
-        <v>346.1300048828125</v>
+        <v>349.9200134277344</v>
       </c>
       <c r="D208" t="n">
-        <v>335.0499877929688</v>
+        <v>345.4200134277344</v>
       </c>
       <c r="E208" t="n">
-        <v>341.1000061035156</v>
+        <v>349.8999938964844</v>
       </c>
       <c r="F208" t="n">
-        <v>9250900</v>
+        <v>10913000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B209" t="n">
-        <v>341.7999877929688</v>
+        <v>350.6400146484375</v>
       </c>
       <c r="C209" t="n">
-        <v>344.260009765625</v>
+        <v>353.3699951171875</v>
       </c>
       <c r="D209" t="n">
-        <v>337.3699951171875</v>
+        <v>347.5</v>
       </c>
       <c r="E209" t="n">
-        <v>338.8699951171875</v>
+        <v>353.2099914550781</v>
       </c>
       <c r="F209" t="n">
-        <v>7723300</v>
+        <v>7520800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B210" t="n">
-        <v>340.1199951171875</v>
+        <v>357.8900146484375</v>
       </c>
       <c r="C210" t="n">
-        <v>345.739990234375</v>
+        <v>359.0499877929688</v>
       </c>
       <c r="D210" t="n">
-        <v>337.2999877929688</v>
+        <v>352.5799865722656</v>
       </c>
       <c r="E210" t="n">
-        <v>345.2300109863281</v>
+        <v>356.2000122070312</v>
       </c>
       <c r="F210" t="n">
-        <v>6015300</v>
+        <v>7884900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B211" t="n">
-        <v>345.0700073242188</v>
+        <v>357.2999877929688</v>
       </c>
       <c r="C211" t="n">
-        <v>349.0700073242188</v>
+        <v>359.2999877929688</v>
       </c>
       <c r="D211" t="n">
-        <v>344.25</v>
+        <v>354.1499938964844</v>
       </c>
       <c r="E211" t="n">
-        <v>348.2099914550781</v>
+        <v>357.3099975585938</v>
       </c>
       <c r="F211" t="n">
-        <v>8040200</v>
+        <v>6533800</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="B212" t="n">
-        <v>346.5799865722656</v>
+        <v>356.5</v>
       </c>
       <c r="C212" t="n">
-        <v>349.9200134277344</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D212" t="n">
-        <v>345.4200134277344</v>
+        <v>343.7799987792969</v>
       </c>
       <c r="E212" t="n">
-        <v>349.8999938964844</v>
+        <v>344.7099914550781</v>
       </c>
       <c r="F212" t="n">
-        <v>10913000</v>
+        <v>8265300</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B213" t="n">
-        <v>350.6400146484375</v>
+        <v>347.5400085449219</v>
       </c>
       <c r="C213" t="n">
-        <v>353.3699951171875</v>
+        <v>352.2799987792969</v>
       </c>
       <c r="D213" t="n">
-        <v>347.5</v>
+        <v>345.3699951171875</v>
       </c>
       <c r="E213" t="n">
-        <v>353.2099914550781</v>
+        <v>350.8500061035156</v>
       </c>
       <c r="F213" t="n">
-        <v>7520800</v>
+        <v>7606500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B214" t="n">
-        <v>357.8900146484375</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C214" t="n">
-        <v>359.0499877929688</v>
+        <v>354.4700012207031</v>
       </c>
       <c r="D214" t="n">
-        <v>352.5799865722656</v>
+        <v>349.7000122070312</v>
       </c>
       <c r="E214" t="n">
-        <v>356.2000122070312</v>
+        <v>351.7900085449219</v>
       </c>
       <c r="F214" t="n">
-        <v>7884900</v>
+        <v>6603400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B215" t="n">
-        <v>357.2999877929688</v>
+        <v>353.75</v>
       </c>
       <c r="C215" t="n">
-        <v>359.2999877929688</v>
+        <v>355.6199951171875</v>
       </c>
       <c r="D215" t="n">
-        <v>354.1499938964844</v>
+        <v>350.8399963378906</v>
       </c>
       <c r="E215" t="n">
-        <v>357.3099975585938</v>
+        <v>352.6400146484375</v>
       </c>
       <c r="F215" t="n">
-        <v>6533800</v>
+        <v>6436600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="B216" t="n">
-        <v>356.5</v>
+        <v>355</v>
       </c>
       <c r="C216" t="n">
-        <v>357.3699951171875</v>
+        <v>363</v>
       </c>
       <c r="D216" t="n">
-        <v>343.7799987792969</v>
+        <v>353.8699951171875</v>
       </c>
       <c r="E216" t="n">
-        <v>344.7099914550781</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F216" t="n">
-        <v>8265300</v>
+        <v>8477200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B217" t="n">
-        <v>347.5400085449219</v>
+        <v>358.9700012207031</v>
       </c>
       <c r="C217" t="n">
-        <v>352.2799987792969</v>
+        <v>362.1700134277344</v>
       </c>
       <c r="D217" t="n">
-        <v>345.3699951171875</v>
+        <v>358.2000122070312</v>
       </c>
       <c r="E217" t="n">
-        <v>350.8500061035156</v>
+        <v>359.239990234375</v>
       </c>
       <c r="F217" t="n">
-        <v>7606500</v>
+        <v>5269500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B218" t="n">
-        <v>353.2999877929688</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="C218" t="n">
-        <v>354.4700012207031</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="D218" t="n">
-        <v>349.7000122070312</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="E218" t="n">
-        <v>351.7900085449219</v>
+        <v>356.2999877929688</v>
       </c>
       <c r="F218" t="n">
-        <v>6603400</v>
+        <v>5820100</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B219" t="n">
-        <v>353.75</v>
+        <v>355.760009765625</v>
       </c>
       <c r="C219" t="n">
-        <v>355.6199951171875</v>
+        <v>358.8500061035156</v>
       </c>
       <c r="D219" t="n">
-        <v>350.8399963378906</v>
+        <v>353.3299865722656</v>
       </c>
       <c r="E219" t="n">
-        <v>352.6400146484375</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F219" t="n">
-        <v>6436600</v>
+        <v>4566200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B220" t="n">
-        <v>355</v>
+        <v>357.9599914550781</v>
       </c>
       <c r="C220" t="n">
-        <v>363</v>
+        <v>359.989990234375</v>
       </c>
       <c r="D220" t="n">
-        <v>353.8699951171875</v>
+        <v>356.5</v>
       </c>
       <c r="E220" t="n">
-        <v>357.5199890136719</v>
+        <v>359.7900085449219</v>
       </c>
       <c r="F220" t="n">
-        <v>8477200</v>
+        <v>5327500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B221" t="n">
-        <v>358.9700012207031</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="C221" t="n">
-        <v>362.1700134277344</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="D221" t="n">
-        <v>358.2000122070312</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="E221" t="n">
-        <v>359.239990234375</v>
+        <v>362.0400085449219</v>
       </c>
       <c r="F221" t="n">
-        <v>5269500</v>
+        <v>4576500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="B222" t="n">
-        <v>362.8099975585938</v>
+        <v>362.9700012207031</v>
       </c>
       <c r="C222" t="n">
-        <v>362.8099975585938</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="D222" t="n">
-        <v>354.9500122070312</v>
+        <v>361.2999877929688</v>
       </c>
       <c r="E222" t="n">
-        <v>356.2999877929688</v>
+        <v>365.1799926757812</v>
       </c>
       <c r="F222" t="n">
-        <v>5820100</v>
+        <v>4366800</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B223" t="n">
-        <v>355.760009765625</v>
+        <v>366.5</v>
       </c>
       <c r="C223" t="n">
-        <v>358.8500061035156</v>
+        <v>366.5</v>
       </c>
       <c r="D223" t="n">
-        <v>353.3299865722656</v>
+        <v>361.5199890136719</v>
       </c>
       <c r="E223" t="n">
-        <v>357.5199890136719</v>
+        <v>363.1099853515625</v>
       </c>
       <c r="F223" t="n">
-        <v>4566200</v>
+        <v>5102700</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B224" t="n">
-        <v>357.9599914550781</v>
+        <v>363</v>
       </c>
       <c r="C224" t="n">
-        <v>359.989990234375</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="D224" t="n">
-        <v>356.5</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="E224" t="n">
-        <v>359.7900085449219</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="F224" t="n">
-        <v>5327500</v>
+        <v>5058600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="B225" t="n">
-        <v>360.0499877929688</v>
+        <v>361.9400024414062</v>
       </c>
       <c r="C225" t="n">
-        <v>363.1199951171875</v>
+        <v>365.75</v>
       </c>
       <c r="D225" t="n">
-        <v>358.6000061035156</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="E225" t="n">
-        <v>362.0400085449219</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="F225" t="n">
-        <v>4576500</v>
+        <v>5282600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B226" t="n">
-        <v>362.9700012207031</v>
+        <v>362.3399963378906</v>
       </c>
       <c r="C226" t="n">
-        <v>366.0899963378906</v>
+        <v>363.5700073242188</v>
       </c>
       <c r="D226" t="n">
-        <v>361.2999877929688</v>
+        <v>359.2699890136719</v>
       </c>
       <c r="E226" t="n">
-        <v>365.1799926757812</v>
+        <v>363.25</v>
       </c>
       <c r="F226" t="n">
-        <v>4366800</v>
+        <v>5525100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B227" t="n">
-        <v>366.5</v>
+        <v>363.010009765625</v>
       </c>
       <c r="C227" t="n">
-        <v>366.5</v>
+        <v>363.0499877929688</v>
       </c>
       <c r="D227" t="n">
-        <v>361.5199890136719</v>
+        <v>355.6499938964844</v>
       </c>
       <c r="E227" t="n">
-        <v>363.1099853515625</v>
+        <v>357.260009765625</v>
       </c>
       <c r="F227" t="n">
-        <v>5102700</v>
+        <v>6696200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B228" t="n">
-        <v>363</v>
+        <v>357.6000061035156</v>
       </c>
       <c r="C228" t="n">
-        <v>365.8999938964844</v>
+        <v>357.9500122070312</v>
       </c>
       <c r="D228" t="n">
-        <v>361.4500122070312</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E228" t="n">
-        <v>362.8399963378906</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="F228" t="n">
-        <v>5058600</v>
+        <v>6799700</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B229" t="n">
-        <v>361.9400024414062</v>
+        <v>354.0700073242188</v>
       </c>
       <c r="C229" t="n">
-        <v>365.75</v>
+        <v>356.8599853515625</v>
       </c>
       <c r="D229" t="n">
-        <v>360.9599914550781</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="E229" t="n">
-        <v>360.9599914550781</v>
+        <v>351.5799865722656</v>
       </c>
       <c r="F229" t="n">
-        <v>5282600</v>
+        <v>8112100</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B230" t="n">
-        <v>362.3399963378906</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C230" t="n">
-        <v>363.5700073242188</v>
+        <v>358.2799987792969</v>
       </c>
       <c r="D230" t="n">
-        <v>359.2699890136719</v>
+        <v>352.8200073242188</v>
       </c>
       <c r="E230" t="n">
-        <v>363.25</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="F230" t="n">
-        <v>5525100</v>
+        <v>4394400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="B231" t="n">
-        <v>363.010009765625</v>
+        <v>357</v>
       </c>
       <c r="C231" t="n">
-        <v>363.0499877929688</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D231" t="n">
-        <v>355.6499938964844</v>
+        <v>353.0700073242188</v>
       </c>
       <c r="E231" t="n">
-        <v>357.260009765625</v>
+        <v>356.6900024414062</v>
       </c>
       <c r="F231" t="n">
-        <v>6696200</v>
+        <v>4298000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B232" t="n">
-        <v>357.6000061035156</v>
+        <v>356.5</v>
       </c>
       <c r="C232" t="n">
-        <v>357.9500122070312</v>
+        <v>358.3500061035156</v>
       </c>
       <c r="D232" t="n">
-        <v>351.5499877929688</v>
+        <v>354.6000061035156</v>
       </c>
       <c r="E232" t="n">
-        <v>351.5499877929688</v>
+        <v>356.5</v>
       </c>
       <c r="F232" t="n">
-        <v>6799700</v>
+        <v>5796500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B233" t="n">
-        <v>354.0700073242188</v>
+        <v>354.6799926757812</v>
       </c>
       <c r="C233" t="n">
-        <v>356.8599853515625</v>
+        <v>357.5700073242188</v>
       </c>
       <c r="D233" t="n">
-        <v>350.3699951171875</v>
+        <v>352.2300109863281</v>
       </c>
       <c r="E233" t="n">
-        <v>351.5799865722656</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="F233" t="n">
-        <v>8112100</v>
+        <v>5209900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B234" t="n">
-        <v>353.2999877929688</v>
+        <v>355.6700134277344</v>
       </c>
       <c r="C234" t="n">
-        <v>358.2799987792969</v>
+        <v>358.7300109863281</v>
       </c>
       <c r="D234" t="n">
-        <v>352.8200073242188</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="E234" t="n">
-        <v>356.3900146484375</v>
+        <v>357.6199951171875</v>
       </c>
       <c r="F234" t="n">
-        <v>4394400</v>
+        <v>3914500</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B235" t="n">
-        <v>357</v>
+        <v>355.8999938964844</v>
       </c>
       <c r="C235" t="n">
-        <v>357.3699951171875</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="D235" t="n">
-        <v>353.0700073242188</v>
+        <v>354.7699890136719</v>
       </c>
       <c r="E235" t="n">
-        <v>356.6900024414062</v>
+        <v>356.0199890136719</v>
       </c>
       <c r="F235" t="n">
-        <v>4298000</v>
+        <v>7962900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="B236" t="n">
-        <v>356.5</v>
+        <v>355.7300109863281</v>
       </c>
       <c r="C236" t="n">
-        <v>358.3500061035156</v>
+        <v>359.9299926757812</v>
       </c>
       <c r="D236" t="n">
-        <v>354.6000061035156</v>
+        <v>354.1199951171875</v>
       </c>
       <c r="E236" t="n">
-        <v>356.5</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="F236" t="n">
-        <v>5796500</v>
+        <v>5079000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="B237" t="n">
-        <v>354.6799926757812</v>
+        <v>357.5499877929688</v>
       </c>
       <c r="C237" t="n">
-        <v>357.5700073242188</v>
+        <v>361.4700012207031</v>
       </c>
       <c r="D237" t="n">
-        <v>352.2300109863281</v>
+        <v>353.7900085449219</v>
       </c>
       <c r="E237" t="n">
-        <v>354.2200012207031</v>
+        <v>356.2200012207031</v>
       </c>
       <c r="F237" t="n">
-        <v>5209900</v>
+        <v>5341400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B238" t="n">
-        <v>355.6700134277344</v>
+        <v>358.6799926757812</v>
       </c>
       <c r="C238" t="n">
-        <v>358.7300109863281</v>
+        <v>362.8500061035156</v>
       </c>
       <c r="D238" t="n">
-        <v>354.2200012207031</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="E238" t="n">
-        <v>357.6199951171875</v>
+        <v>362.0599975585938</v>
       </c>
       <c r="F238" t="n">
-        <v>3914500</v>
+        <v>5414200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B239" t="n">
-        <v>355.8999938964844</v>
+        <v>361</v>
       </c>
       <c r="C239" t="n">
-        <v>357.7699890136719</v>
+        <v>362.8599853515625</v>
       </c>
       <c r="D239" t="n">
-        <v>354.7699890136719</v>
+        <v>355.2000122070312</v>
       </c>
       <c r="E239" t="n">
-        <v>356.0199890136719</v>
+        <v>358.6400146484375</v>
       </c>
       <c r="F239" t="n">
-        <v>7962900</v>
+        <v>4873500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B240" t="n">
-        <v>355.7300109863281</v>
+        <v>357.1000061035156</v>
       </c>
       <c r="C240" t="n">
-        <v>359.9299926757812</v>
+        <v>358.5499877929688</v>
       </c>
       <c r="D240" t="n">
-        <v>354.1199951171875</v>
+        <v>353.2300109863281</v>
       </c>
       <c r="E240" t="n">
-        <v>354.9500122070312</v>
+        <v>353.510009765625</v>
       </c>
       <c r="F240" t="n">
-        <v>5079000</v>
+        <v>5631400</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B241" t="n">
-        <v>357.5499877929688</v>
+        <v>352</v>
       </c>
       <c r="C241" t="n">
-        <v>361.4700012207031</v>
+        <v>356.3299865722656</v>
       </c>
       <c r="D241" t="n">
-        <v>353.7900085449219</v>
+        <v>348.6900024414062</v>
       </c>
       <c r="E241" t="n">
-        <v>356.2200012207031</v>
+        <v>354.7099914550781</v>
       </c>
       <c r="F241" t="n">
-        <v>5341400</v>
+        <v>6318200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B242" t="n">
-        <v>358.6799926757812</v>
+        <v>353.510009765625</v>
       </c>
       <c r="C242" t="n">
-        <v>362.8500061035156</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="D242" t="n">
-        <v>356.3900146484375</v>
+        <v>351.1199951171875</v>
       </c>
       <c r="E242" t="n">
-        <v>362.0599975585938</v>
+        <v>353.5599975585938</v>
       </c>
       <c r="F242" t="n">
-        <v>5414200</v>
+        <v>4184200</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B243" t="n">
-        <v>361</v>
+        <v>358.3200073242188</v>
       </c>
       <c r="C243" t="n">
-        <v>362.8599853515625</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="D243" t="n">
-        <v>355.2000122070312</v>
+        <v>354.7900085449219</v>
       </c>
       <c r="E243" t="n">
-        <v>358.6400146484375</v>
+        <v>356.2300109863281</v>
       </c>
       <c r="F243" t="n">
-        <v>4873500</v>
+        <v>5354600</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B244" t="n">
-        <v>357.1000061035156</v>
+        <v>354.2300109863281</v>
       </c>
       <c r="C244" t="n">
-        <v>358.5499877929688</v>
+        <v>355.2799987792969</v>
       </c>
       <c r="D244" t="n">
-        <v>353.2300109863281</v>
+        <v>347.5499877929688</v>
       </c>
       <c r="E244" t="n">
-        <v>353.510009765625</v>
+        <v>350.1300048828125</v>
       </c>
       <c r="F244" t="n">
-        <v>5631400</v>
+        <v>9609900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B245" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C245" t="n">
-        <v>356.3299865722656</v>
+        <v>354.7000122070312</v>
       </c>
       <c r="D245" t="n">
-        <v>348.6900024414062</v>
+        <v>343.0700073242188</v>
       </c>
       <c r="E245" t="n">
-        <v>354.7099914550781</v>
+        <v>352.489990234375</v>
       </c>
       <c r="F245" t="n">
-        <v>6318200</v>
+        <v>14026500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="B246" t="n">
-        <v>353.510009765625</v>
+        <v>353.3800048828125</v>
       </c>
       <c r="C246" t="n">
-        <v>354.2200012207031</v>
+        <v>355.6000061035156</v>
       </c>
       <c r="D246" t="n">
-        <v>351.1199951171875</v>
+        <v>344.6900024414062</v>
       </c>
       <c r="E246" t="n">
-        <v>353.5599975585938</v>
+        <v>348.9200134277344</v>
       </c>
       <c r="F246" t="n">
-        <v>4184200</v>
+        <v>8303400</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="B247" t="n">
-        <v>358.3200073242188</v>
+        <v>352.25</v>
       </c>
       <c r="C247" t="n">
-        <v>360.0499877929688</v>
+        <v>353.489990234375</v>
       </c>
       <c r="D247" t="n">
-        <v>354.7900085449219</v>
+        <v>345.2699890136719</v>
       </c>
       <c r="E247" t="n">
-        <v>356.2300109863281</v>
+        <v>349.3099975585938</v>
       </c>
       <c r="F247" t="n">
-        <v>5354600</v>
+        <v>6480100</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B248" t="n">
-        <v>354.2300109863281</v>
+        <v>347.8900146484375</v>
       </c>
       <c r="C248" t="n">
-        <v>355.2799987792969</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="D248" t="n">
-        <v>347.5499877929688</v>
+        <v>345.010009765625</v>
       </c>
       <c r="E248" t="n">
-        <v>350.1300048828125</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="F248" t="n">
-        <v>9609900</v>
+        <v>18312400</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B249" t="n">
-        <v>351</v>
+        <v>353.6700134277344</v>
       </c>
       <c r="C249" t="n">
-        <v>354.7000122070312</v>
+        <v>354.5</v>
       </c>
       <c r="D249" t="n">
-        <v>343.0700073242188</v>
+        <v>350.0799865722656</v>
       </c>
       <c r="E249" t="n">
-        <v>352.489990234375</v>
+        <v>352.0400085449219</v>
       </c>
       <c r="F249" t="n">
-        <v>14026500</v>
+        <v>6414700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B250" t="n">
-        <v>353.3800048828125</v>
+        <v>352</v>
       </c>
       <c r="C250" t="n">
-        <v>355.6000061035156</v>
+        <v>352.1000061035156</v>
       </c>
       <c r="D250" t="n">
-        <v>344.6900024414062</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E250" t="n">
-        <v>348.9200134277344</v>
+        <v>340</v>
       </c>
       <c r="F250" t="n">
-        <v>8303400</v>
+        <v>11485600</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B251" t="n">
-        <v>352.25</v>
+        <v>337.6099853515625</v>
       </c>
       <c r="C251" t="n">
-        <v>353.489990234375</v>
+        <v>341.4400024414062</v>
       </c>
       <c r="D251" t="n">
-        <v>345.2699890136719</v>
+        <v>336.9800109863281</v>
       </c>
       <c r="E251" t="n">
-        <v>349.3099975585938</v>
+        <v>337.5299987792969</v>
       </c>
       <c r="F251" t="n">
-        <v>6480100</v>
+        <v>7068500</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B252" t="n">
-        <v>347.8900146484375</v>
+        <v>338.1199951171875</v>
       </c>
       <c r="C252" t="n">
-        <v>349.6700134277344</v>
+        <v>339.3699951171875</v>
       </c>
       <c r="D252" t="n">
-        <v>345.010009765625</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="E252" t="n">
-        <v>349.6700134277344</v>
+        <v>338.5599975585938</v>
       </c>
       <c r="F252" t="n">
-        <v>18290400</v>
+        <v>6934300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10017,37 +10017,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>349.67</v>
+        <v>338.56</v>
       </c>
       <c r="D2" t="n">
-        <v>349.31</v>
+        <v>337.53</v>
       </c>
       <c r="E2" t="n">
-        <v>347.89</v>
+        <v>338.12</v>
       </c>
       <c r="F2" t="n">
-        <v>349.67</v>
+        <v>339.37</v>
       </c>
       <c r="G2" t="n">
-        <v>345.0676</v>
+        <v>335.28</v>
       </c>
       <c r="H2" t="n">
-        <v>18241892</v>
+        <v>6931795</v>
       </c>
       <c r="I2" t="n">
-        <v>7909596</v>
+        <v>7898782</v>
       </c>
       <c r="J2" t="n">
-        <v>929488044032</v>
+        <v>899955556352</v>
       </c>
       <c r="K2" t="n">
-        <v>14.96875</v>
+        <v>14.474562</v>
       </c>
       <c r="L2" t="n">
-        <v>13.993524</v>
+        <v>13.548909</v>
       </c>
       <c r="M2" t="n">
-        <v>23.36</v>
+        <v>23.39</v>
       </c>
       <c r="N2" t="n">
         <v>366.5</v>
@@ -10059,7 +10059,7 @@
         <v>0.975</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
         <v>0.34921002</v>
@@ -10087,7 +10087,7 @@
         <v>133.007</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.6289594</v>
+        <v>2.54543</v>
       </c>
       <c r="Z2" t="n">
         <v>0.469</v>
@@ -10099,7 +10099,7 @@
         <v>186328006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>767415943168</v>
+        <v>737883521024</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:22</t>
+          <t>2026-09-25 14:29:10</t>
         </is>
       </c>
     </row>

--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B2" t="n">
-        <v>308.2234768510796</v>
+        <v>308.988785738579</v>
       </c>
       <c r="C2" t="n">
-        <v>309.7247551863121</v>
+        <v>311.8441636854759</v>
       </c>
       <c r="D2" t="n">
-        <v>305.947019653492</v>
+        <v>307.8113297451866</v>
       </c>
       <c r="E2" t="n">
-        <v>307.5660705566406</v>
+        <v>310.1270141601562</v>
       </c>
       <c r="F2" t="n">
-        <v>7083200</v>
+        <v>7258100</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B3" t="n">
-        <v>308.9888161441515</v>
+        <v>311.1082857354447</v>
       </c>
       <c r="C3" t="n">
-        <v>311.8441943720275</v>
+        <v>312.0404647281687</v>
       </c>
       <c r="D3" t="n">
-        <v>307.8113600348933</v>
+        <v>307.7721150397051</v>
       </c>
       <c r="E3" t="n">
-        <v>310.1270446777344</v>
+        <v>309.7640075683594</v>
       </c>
       <c r="F3" t="n">
-        <v>7258100</v>
+        <v>6462400</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B4" t="n">
-        <v>311.1082857354447</v>
+        <v>310.3134645283819</v>
       </c>
       <c r="C4" t="n">
-        <v>312.0404647281687</v>
+        <v>311.4516930034957</v>
       </c>
       <c r="D4" t="n">
-        <v>307.7721150397051</v>
+        <v>304.288708108424</v>
       </c>
       <c r="E4" t="n">
-        <v>309.7640075683594</v>
+        <v>309.5088500976562</v>
       </c>
       <c r="F4" t="n">
-        <v>6462400</v>
+        <v>11823300</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B5" t="n">
-        <v>310.3134645283819</v>
+        <v>308.0762861336198</v>
       </c>
       <c r="C5" t="n">
-        <v>311.4516930034957</v>
+        <v>308.6846429587351</v>
       </c>
       <c r="D5" t="n">
-        <v>304.288708108424</v>
+        <v>301.6394301376976</v>
       </c>
       <c r="E5" t="n">
-        <v>309.5088500976562</v>
+        <v>304.8774719238281</v>
       </c>
       <c r="F5" t="n">
-        <v>11823300</v>
+        <v>9235200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B6" t="n">
-        <v>308.0762861336198</v>
+        <v>304.1808160870063</v>
       </c>
       <c r="C6" t="n">
-        <v>308.6846429587351</v>
+        <v>304.7303016172636</v>
       </c>
       <c r="D6" t="n">
-        <v>301.6394301376976</v>
+        <v>300.393288685967</v>
       </c>
       <c r="E6" t="n">
-        <v>304.8774719238281</v>
+        <v>301.7767944335938</v>
       </c>
       <c r="F6" t="n">
-        <v>9235200</v>
+        <v>7600000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B7" t="n">
-        <v>304.1808160870063</v>
+        <v>302.7187488597389</v>
       </c>
       <c r="C7" t="n">
-        <v>304.7303016172636</v>
+        <v>305.8096119794931</v>
       </c>
       <c r="D7" t="n">
-        <v>300.393288685967</v>
+        <v>302.4243624063698</v>
       </c>
       <c r="E7" t="n">
-        <v>301.7767944335938</v>
+        <v>304.210205078125</v>
       </c>
       <c r="F7" t="n">
-        <v>7600000</v>
+        <v>6029900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,25 +625,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B8" t="n">
-        <v>302.718779227698</v>
+        <v>305.8371035459471</v>
       </c>
       <c r="C8" t="n">
-        <v>305.8096426575195</v>
+        <v>307.3851288987199</v>
       </c>
       <c r="D8" t="n">
-        <v>302.4243927447969</v>
+        <v>300.8578215934895</v>
       </c>
       <c r="E8" t="n">
-        <v>304.2102355957031</v>
+        <v>304.8511047363281</v>
       </c>
       <c r="F8" t="n">
-        <v>6029900</v>
+        <v>7214500</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -651,25 +651,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B9" t="n">
-        <v>305.8371035459471</v>
+        <v>305.0187809092415</v>
       </c>
       <c r="C9" t="n">
-        <v>307.3851288987199</v>
+        <v>305.6695438264559</v>
       </c>
       <c r="D9" t="n">
-        <v>300.8578215934895</v>
+        <v>300.4338918141804</v>
       </c>
       <c r="E9" t="n">
-        <v>304.8511047363281</v>
+        <v>303.3820190429688</v>
       </c>
       <c r="F9" t="n">
-        <v>7214500</v>
+        <v>8454200</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B10" t="n">
-        <v>305.0187502270194</v>
+        <v>303.8946608384686</v>
       </c>
       <c r="C10" t="n">
-        <v>305.6695130787729</v>
+        <v>304.4566873375159</v>
       </c>
       <c r="D10" t="n">
-        <v>300.4338615931582</v>
+        <v>299.2999031353941</v>
       </c>
       <c r="E10" t="n">
-        <v>303.3819885253906</v>
+        <v>299.773193359375</v>
       </c>
       <c r="F10" t="n">
-        <v>8454200</v>
+        <v>6489900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B11" t="n">
-        <v>303.894722712774</v>
+        <v>300.7789375021521</v>
       </c>
       <c r="C11" t="n">
-        <v>304.4567493262524</v>
+        <v>303.7270945284432</v>
       </c>
       <c r="D11" t="n">
-        <v>299.2999640741864</v>
+        <v>299.1422058887319</v>
       </c>
       <c r="E11" t="n">
-        <v>299.7732543945312</v>
+        <v>301.2522277832031</v>
       </c>
       <c r="F11" t="n">
-        <v>6489900</v>
+        <v>7060300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B12" t="n">
-        <v>300.7789375021521</v>
+        <v>301.3803883702425</v>
       </c>
       <c r="C12" t="n">
-        <v>303.7270945284432</v>
+        <v>306.1230400580682</v>
       </c>
       <c r="D12" t="n">
-        <v>299.1422058887319</v>
+        <v>296.59828830624</v>
       </c>
       <c r="E12" t="n">
-        <v>301.2522277832031</v>
+        <v>296.6771850585938</v>
       </c>
       <c r="F12" t="n">
-        <v>7060300</v>
+        <v>8597400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B13" t="n">
-        <v>301.3804193716138</v>
+        <v>301.3212684867699</v>
       </c>
       <c r="C13" t="n">
-        <v>306.1230715472904</v>
+        <v>305.1272097801061</v>
       </c>
       <c r="D13" t="n">
-        <v>296.5983188157025</v>
+        <v>301.1733746705027</v>
       </c>
       <c r="E13" t="n">
-        <v>296.6772155761719</v>
+        <v>303.6580810546875</v>
       </c>
       <c r="F13" t="n">
-        <v>8597400</v>
+        <v>10788700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B14" t="n">
-        <v>301.321238204041</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C14" t="n">
-        <v>305.1271791148808</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D14" t="n">
-        <v>301.173344402637</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E14" t="n">
-        <v>303.6580505371094</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F14" t="n">
-        <v>10788700</v>
+        <v>16178800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B15" t="n">
-        <v>301.5578902761218</v>
+        <v>302.1002149225357</v>
       </c>
       <c r="C15" t="n">
-        <v>302.7016525742085</v>
+        <v>307.7499693151439</v>
       </c>
       <c r="D15" t="n">
-        <v>290.0907186231138</v>
+        <v>301.1635039391426</v>
       </c>
       <c r="E15" t="n">
-        <v>297.8505249023438</v>
+        <v>301.4100036621094</v>
       </c>
       <c r="F15" t="n">
-        <v>16178800</v>
+        <v>11354800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B16" t="n">
-        <v>302.1001843350741</v>
+        <v>301.0747260223031</v>
       </c>
       <c r="C16" t="n">
-        <v>307.7499381556482</v>
+        <v>304.358088638523</v>
       </c>
       <c r="D16" t="n">
-        <v>301.1634734465224</v>
+        <v>292.9106575300408</v>
       </c>
       <c r="E16" t="n">
-        <v>301.4099731445312</v>
+        <v>294.3600769042969</v>
       </c>
       <c r="F16" t="n">
-        <v>11354800</v>
+        <v>10549400</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B17" t="n">
-        <v>301.0747572360179</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C17" t="n">
-        <v>304.3581201926382</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D17" t="n">
-        <v>292.9106878973514</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E17" t="n">
-        <v>294.360107421875</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F17" t="n">
-        <v>10549400</v>
+        <v>10153500</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B18" t="n">
-        <v>294.9714335987563</v>
+        <v>294.3206459359216</v>
       </c>
       <c r="C18" t="n">
-        <v>295.3559575215809</v>
+        <v>299.4379821870563</v>
       </c>
       <c r="D18" t="n">
-        <v>290.0808874955599</v>
+        <v>293.9854099500461</v>
       </c>
       <c r="E18" t="n">
-        <v>293.3938293457031</v>
+        <v>298.1265869140625</v>
       </c>
       <c r="F18" t="n">
-        <v>10153500</v>
+        <v>6894900</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B19" t="n">
-        <v>294.3206459359216</v>
+        <v>297.4363803014411</v>
       </c>
       <c r="C19" t="n">
-        <v>299.4379821870563</v>
+        <v>299.7929016175946</v>
       </c>
       <c r="D19" t="n">
-        <v>293.9854099500461</v>
+        <v>292.841622611914</v>
       </c>
       <c r="E19" t="n">
-        <v>298.1265869140625</v>
+        <v>292.9303588867188</v>
       </c>
       <c r="F19" t="n">
-        <v>6894900</v>
+        <v>7372700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B20" t="n">
-        <v>297.436411288458</v>
+        <v>293.6008861047978</v>
       </c>
       <c r="C20" t="n">
-        <v>299.7929328501146</v>
+        <v>293.8868342154489</v>
       </c>
       <c r="D20" t="n">
-        <v>292.8416531202475</v>
+        <v>286.4721332067081</v>
       </c>
       <c r="E20" t="n">
-        <v>292.9303894042969</v>
+        <v>289.9921264648438</v>
       </c>
       <c r="F20" t="n">
-        <v>7372700</v>
+        <v>8054100</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B21" t="n">
-        <v>293.6008552074487</v>
+        <v>290.2583742532713</v>
       </c>
       <c r="C21" t="n">
-        <v>293.8868032880077</v>
+        <v>292.220502524991</v>
       </c>
       <c r="D21" t="n">
-        <v>286.4721030595595</v>
+        <v>288.4145610405075</v>
       </c>
       <c r="E21" t="n">
-        <v>289.9920959472656</v>
+        <v>290.4161376953125</v>
       </c>
       <c r="F21" t="n">
-        <v>8054100</v>
+        <v>5438800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B22" t="n">
-        <v>290.2583437522712</v>
+        <v>291.9345194575729</v>
       </c>
       <c r="C22" t="n">
-        <v>292.2204718178062</v>
+        <v>298.3632510673837</v>
       </c>
       <c r="D22" t="n">
-        <v>288.4145307332595</v>
+        <v>291.3133654724136</v>
       </c>
       <c r="E22" t="n">
-        <v>290.4161071777344</v>
+        <v>296.2334899902344</v>
       </c>
       <c r="F22" t="n">
-        <v>5438800</v>
+        <v>7228300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B23" t="n">
-        <v>291.9345194575729</v>
+        <v>297.92941246883</v>
       </c>
       <c r="C23" t="n">
-        <v>298.3632510673837</v>
+        <v>300.2662249001909</v>
       </c>
       <c r="D23" t="n">
-        <v>291.3133654724136</v>
+        <v>296.7955198233114</v>
       </c>
       <c r="E23" t="n">
-        <v>296.2334899902344</v>
+        <v>299.8915405273438</v>
       </c>
       <c r="F23" t="n">
-        <v>7228300</v>
+        <v>5642200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B24" t="n">
-        <v>297.92941246883</v>
+        <v>300.5916257686241</v>
       </c>
       <c r="C24" t="n">
-        <v>300.2662249001909</v>
+        <v>303.6580981532932</v>
       </c>
       <c r="D24" t="n">
-        <v>296.7955198233114</v>
+        <v>298.9154456060477</v>
       </c>
       <c r="E24" t="n">
-        <v>299.8915405273438</v>
+        <v>301.0846252441406</v>
       </c>
       <c r="F24" t="n">
-        <v>5642200</v>
+        <v>6336000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B25" t="n">
-        <v>300.5915953010157</v>
+        <v>299.2605460773775</v>
       </c>
       <c r="C25" t="n">
-        <v>303.6580673748709</v>
+        <v>303.9341713954877</v>
       </c>
       <c r="D25" t="n">
-        <v>298.915415308335</v>
+        <v>298.7675466103937</v>
       </c>
       <c r="E25" t="n">
-        <v>301.0845947265625</v>
+        <v>301.2325439453125</v>
       </c>
       <c r="F25" t="n">
-        <v>6336000</v>
+        <v>7520300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B26" t="n">
-        <v>299.2605157595805</v>
+        <v>301.5085931686638</v>
       </c>
       <c r="C26" t="n">
-        <v>303.9341406042103</v>
+        <v>308.2330823767899</v>
       </c>
       <c r="D26" t="n">
-        <v>298.7675163425421</v>
+        <v>300.828251563059</v>
       </c>
       <c r="E26" t="n">
-        <v>301.2325134277344</v>
+        <v>305.1074829101562</v>
       </c>
       <c r="F26" t="n">
-        <v>7520300</v>
+        <v>7514600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B27" t="n">
-        <v>301.5085931686638</v>
+        <v>304.2200828300273</v>
       </c>
       <c r="C27" t="n">
-        <v>308.2330823767899</v>
+        <v>308.4894444595929</v>
       </c>
       <c r="D27" t="n">
-        <v>300.828251563059</v>
+        <v>302.9481359332913</v>
       </c>
       <c r="E27" t="n">
-        <v>305.1074829101562</v>
+        <v>306.7639465332031</v>
       </c>
       <c r="F27" t="n">
-        <v>7514600</v>
+        <v>7721300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B28" t="n">
-        <v>304.2200828300273</v>
+        <v>306.6456604912348</v>
       </c>
       <c r="C28" t="n">
-        <v>308.4894444595929</v>
+        <v>307.9471862719047</v>
       </c>
       <c r="D28" t="n">
-        <v>302.9481359332913</v>
+        <v>301.9227172950412</v>
       </c>
       <c r="E28" t="n">
-        <v>306.7639465332031</v>
+        <v>305.0187683105469</v>
       </c>
       <c r="F28" t="n">
-        <v>7721300</v>
+        <v>7770000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B29" t="n">
-        <v>306.6456604912348</v>
+        <v>302.415720333495</v>
       </c>
       <c r="C29" t="n">
-        <v>307.9471862719047</v>
+        <v>307.8485840116909</v>
       </c>
       <c r="D29" t="n">
-        <v>301.9227172950412</v>
+        <v>300.8282765156093</v>
       </c>
       <c r="E29" t="n">
-        <v>305.0187683105469</v>
+        <v>304.920166015625</v>
       </c>
       <c r="F29" t="n">
-        <v>7770000</v>
+        <v>7085200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B30" t="n">
-        <v>302.415720333495</v>
+        <v>305.2751066360906</v>
       </c>
       <c r="C30" t="n">
-        <v>307.8485840116909</v>
+        <v>308.7162632770978</v>
       </c>
       <c r="D30" t="n">
-        <v>300.8282765156093</v>
+        <v>301.3508502506656</v>
       </c>
       <c r="E30" t="n">
-        <v>304.920166015625</v>
+        <v>307.3161315917969</v>
       </c>
       <c r="F30" t="n">
-        <v>7085200</v>
+        <v>6865200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B31" t="n">
-        <v>305.2751066360906</v>
+        <v>306.6357990367445</v>
       </c>
       <c r="C31" t="n">
-        <v>308.7162632770978</v>
+        <v>310.4319009529449</v>
       </c>
       <c r="D31" t="n">
-        <v>301.3508502506656</v>
+        <v>305.9160390722913</v>
       </c>
       <c r="E31" t="n">
-        <v>307.3161315917969</v>
+        <v>309.0317993164062</v>
       </c>
       <c r="F31" t="n">
-        <v>6865200</v>
+        <v>7206100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B32" t="n">
-        <v>306.6357687557767</v>
+        <v>307.5232049313688</v>
       </c>
       <c r="C32" t="n">
-        <v>310.4318702971036</v>
+        <v>310.0276204199649</v>
       </c>
       <c r="D32" t="n">
-        <v>305.9160088624015</v>
+        <v>303.3327096940284</v>
       </c>
       <c r="E32" t="n">
-        <v>309.0317687988281</v>
+        <v>309.8106994628906</v>
       </c>
       <c r="F32" t="n">
-        <v>7206100</v>
+        <v>7302300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B33" t="n">
-        <v>307.5232049313688</v>
+        <v>310.5896641246428</v>
       </c>
       <c r="C33" t="n">
-        <v>310.0276204199649</v>
+        <v>315.0858168552232</v>
       </c>
       <c r="D33" t="n">
-        <v>303.3327096940284</v>
+        <v>309.810716541713</v>
       </c>
       <c r="E33" t="n">
-        <v>309.8106994628906</v>
+        <v>312.4532165527344</v>
       </c>
       <c r="F33" t="n">
-        <v>7302300</v>
+        <v>5794100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B34" t="n">
-        <v>310.5896337890794</v>
+        <v>313.054640940315</v>
       </c>
       <c r="C34" t="n">
-        <v>315.0857860805166</v>
+        <v>314.5829271513063</v>
       </c>
       <c r="D34" t="n">
-        <v>309.8106862822301</v>
+        <v>310.8657222472937</v>
       </c>
       <c r="E34" t="n">
-        <v>312.4531860351562</v>
+        <v>311.2009582519531</v>
       </c>
       <c r="F34" t="n">
-        <v>5794100</v>
+        <v>5030200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B35" t="n">
-        <v>313.0546102409576</v>
+        <v>311.8320000281587</v>
       </c>
       <c r="C35" t="n">
-        <v>314.5828963020791</v>
+        <v>317.7381233989844</v>
       </c>
       <c r="D35" t="n">
-        <v>310.8656917625901</v>
+        <v>311.782682032414</v>
       </c>
       <c r="E35" t="n">
-        <v>311.200927734375</v>
+        <v>315.9238891601562</v>
       </c>
       <c r="F35" t="n">
-        <v>5030200</v>
+        <v>10578300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B36" t="n">
-        <v>311.8320000281587</v>
+        <v>314.7604311532612</v>
       </c>
       <c r="C36" t="n">
-        <v>317.7381233989844</v>
+        <v>316.1408235578094</v>
       </c>
       <c r="D36" t="n">
-        <v>311.782682032414</v>
+        <v>304.7722577523736</v>
       </c>
       <c r="E36" t="n">
-        <v>315.9238891601562</v>
+        <v>305.1469421386719</v>
       </c>
       <c r="F36" t="n">
-        <v>10578300</v>
+        <v>8973300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B37" t="n">
-        <v>314.7604626322791</v>
+        <v>303.2045199796025</v>
       </c>
       <c r="C37" t="n">
-        <v>316.1408551748796</v>
+        <v>303.3327046462357</v>
       </c>
       <c r="D37" t="n">
-        <v>304.7722882324798</v>
+        <v>297.0124483237873</v>
       </c>
       <c r="E37" t="n">
-        <v>305.14697265625</v>
+        <v>299.3591003417969</v>
       </c>
       <c r="F37" t="n">
-        <v>8973300</v>
+        <v>10327000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B38" t="n">
-        <v>303.2044890700107</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C38" t="n">
-        <v>303.3326737235763</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D38" t="n">
-        <v>297.012418045434</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E38" t="n">
-        <v>299.3590698242188</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F38" t="n">
-        <v>10327000</v>
+        <v>8344000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B39" t="n">
-        <v>299.7436397411884</v>
+        <v>295.3066623130797</v>
       </c>
       <c r="C39" t="n">
-        <v>301.3113742461044</v>
+        <v>298.708370459316</v>
       </c>
       <c r="D39" t="n">
-        <v>293.5022804823602</v>
+        <v>292.8613742767781</v>
       </c>
       <c r="E39" t="n">
-        <v>296.1644592285156</v>
+        <v>295.2179260253906</v>
       </c>
       <c r="F39" t="n">
-        <v>8344000</v>
+        <v>8077300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B40" t="n">
-        <v>295.3066623130797</v>
+        <v>295.5432899586994</v>
       </c>
       <c r="C40" t="n">
-        <v>298.708370459316</v>
+        <v>300.1873662746028</v>
       </c>
       <c r="D40" t="n">
-        <v>292.8613742767781</v>
+        <v>295.0798692888629</v>
       </c>
       <c r="E40" t="n">
-        <v>295.2179260253906</v>
+        <v>299.0238647460938</v>
       </c>
       <c r="F40" t="n">
-        <v>8077300</v>
+        <v>5546600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B41" t="n">
-        <v>295.5432597963394</v>
+        <v>302.0509050250311</v>
       </c>
       <c r="C41" t="n">
-        <v>300.1873356382808</v>
+        <v>305.5807980031574</v>
       </c>
       <c r="D41" t="n">
-        <v>295.0798391737984</v>
+        <v>293.9854410949062</v>
       </c>
       <c r="E41" t="n">
-        <v>299.0238342285156</v>
+        <v>294.2023620605469</v>
       </c>
       <c r="F41" t="n">
-        <v>5546600</v>
+        <v>7501600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B42" t="n">
-        <v>302.0508736933244</v>
+        <v>297.0715864028587</v>
       </c>
       <c r="C42" t="n">
-        <v>305.5807663052954</v>
+        <v>297.456110287291</v>
       </c>
       <c r="D42" t="n">
-        <v>293.9854105998292</v>
+        <v>288.7103057597054</v>
       </c>
       <c r="E42" t="n">
-        <v>294.2023315429688</v>
+        <v>293.8473510742188</v>
       </c>
       <c r="F42" t="n">
-        <v>7501600</v>
+        <v>11766800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B43" t="n">
-        <v>297.0715864028587</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C43" t="n">
-        <v>297.456110287291</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D43" t="n">
-        <v>288.7103057597054</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E43" t="n">
-        <v>293.8473510742188</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F43" t="n">
-        <v>11766800</v>
+        <v>10940200</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B44" t="n">
-        <v>294.0642973394352</v>
+        <v>295.8489209666184</v>
       </c>
       <c r="C44" t="n">
-        <v>295.6221924256846</v>
+        <v>300.2366275598507</v>
       </c>
       <c r="D44" t="n">
-        <v>290.386540762355</v>
+        <v>291.4217960873232</v>
       </c>
       <c r="E44" t="n">
-        <v>293.8276672363281</v>
+        <v>298.7576293945312</v>
       </c>
       <c r="F44" t="n">
-        <v>10940200</v>
+        <v>8877200</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B45" t="n">
-        <v>295.848951187077</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C45" t="n">
-        <v>300.236658228506</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D45" t="n">
-        <v>291.4218258555586</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E45" t="n">
-        <v>298.7576599121094</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F45" t="n">
-        <v>8877200</v>
+        <v>7910900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B46" t="n">
-        <v>300.7296512123902</v>
+        <v>304.7722767012305</v>
       </c>
       <c r="C46" t="n">
-        <v>304.2102259719906</v>
+        <v>309.3275869646093</v>
       </c>
       <c r="D46" t="n">
-        <v>298.9548653069277</v>
+        <v>303.9243019705234</v>
       </c>
       <c r="E46" t="n">
-        <v>303.3327026367188</v>
+        <v>308.696533203125</v>
       </c>
       <c r="F46" t="n">
-        <v>7910900</v>
+        <v>4322400</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B47" t="n">
-        <v>304.7722465716023</v>
+        <v>308.5683928006819</v>
       </c>
       <c r="C47" t="n">
-        <v>309.3275563846455</v>
+        <v>309.6431280779537</v>
       </c>
       <c r="D47" t="n">
-        <v>303.9242719247256</v>
+        <v>304.2201336884183</v>
       </c>
       <c r="E47" t="n">
-        <v>308.6965026855469</v>
+        <v>304.5948181152344</v>
       </c>
       <c r="F47" t="n">
-        <v>4322400</v>
+        <v>7727300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B48" t="n">
-        <v>308.5683309692949</v>
+        <v>304.4172805196406</v>
       </c>
       <c r="C48" t="n">
-        <v>309.6430660312097</v>
+        <v>306.1329390093465</v>
       </c>
       <c r="D48" t="n">
-        <v>304.2200727283419</v>
+        <v>302.7903884074122</v>
       </c>
       <c r="E48" t="n">
-        <v>304.5947570800781</v>
+        <v>303.5693359375</v>
       </c>
       <c r="F48" t="n">
-        <v>7727300</v>
+        <v>7249000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B49" t="n">
-        <v>304.4172805196406</v>
+        <v>302.8988595387675</v>
       </c>
       <c r="C49" t="n">
-        <v>306.1329390093465</v>
+        <v>307.9865871384521</v>
       </c>
       <c r="D49" t="n">
-        <v>302.7903884074122</v>
+        <v>302.5044359255107</v>
       </c>
       <c r="E49" t="n">
-        <v>303.5693359375</v>
+        <v>307.7598266601562</v>
       </c>
       <c r="F49" t="n">
-        <v>7249000</v>
+        <v>8535300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B50" t="n">
-        <v>302.8988595387675</v>
+        <v>308.8740221323167</v>
       </c>
       <c r="C50" t="n">
-        <v>307.9865871384521</v>
+        <v>314.0307770729326</v>
       </c>
       <c r="D50" t="n">
-        <v>302.5044359255107</v>
+        <v>308.617652791837</v>
       </c>
       <c r="E50" t="n">
-        <v>307.7598266601562</v>
+        <v>311.6742553710938</v>
       </c>
       <c r="F50" t="n">
-        <v>8535300</v>
+        <v>9627800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B51" t="n">
-        <v>308.8740221323167</v>
+        <v>311.2207252653726</v>
       </c>
       <c r="C51" t="n">
-        <v>314.0307770729326</v>
+        <v>314.0209586927274</v>
       </c>
       <c r="D51" t="n">
-        <v>308.617652791837</v>
+        <v>310.2741446015314</v>
       </c>
       <c r="E51" t="n">
-        <v>311.6742553710938</v>
+        <v>310.6291198730469</v>
       </c>
       <c r="F51" t="n">
-        <v>9627800</v>
+        <v>6518900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B52" t="n">
-        <v>311.2206946896725</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C52" t="n">
-        <v>314.0209278419201</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D52" t="n">
-        <v>310.2741141188276</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E52" t="n">
-        <v>310.6290893554688</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F52" t="n">
-        <v>6518900</v>
+        <v>7417200</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B53" t="n">
-        <v>310.6487980837529</v>
+        <v>310.5403783790639</v>
       </c>
       <c r="C53" t="n">
-        <v>312.0390600856641</v>
+        <v>314.336450228146</v>
       </c>
       <c r="D53" t="n">
-        <v>308.9627484602848</v>
+        <v>295.8193913272319</v>
       </c>
       <c r="E53" t="n">
-        <v>310.7966918945312</v>
+        <v>296.3025512695312</v>
       </c>
       <c r="F53" t="n">
-        <v>7417200</v>
+        <v>18049200</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B54" t="n">
-        <v>310.5403783790639</v>
+        <v>296.292632599085</v>
       </c>
       <c r="C54" t="n">
-        <v>314.336450228146</v>
+        <v>306.8329619363725</v>
       </c>
       <c r="D54" t="n">
-        <v>295.8193913272319</v>
+        <v>294.2811866679717</v>
       </c>
       <c r="E54" t="n">
-        <v>296.3025512695312</v>
+        <v>305.76806640625</v>
       </c>
       <c r="F54" t="n">
-        <v>18049200</v>
+        <v>18874100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B55" t="n">
-        <v>296.292632599085</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C55" t="n">
-        <v>306.8329619363725</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D55" t="n">
-        <v>294.2811866679717</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E55" t="n">
-        <v>305.76806640625</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F55" t="n">
-        <v>18874100</v>
+        <v>9721900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B56" t="n">
-        <v>304.9102649889192</v>
+        <v>315.2040954937631</v>
       </c>
       <c r="C56" t="n">
-        <v>313.5476242674454</v>
+        <v>315.7858311866128</v>
       </c>
       <c r="D56" t="n">
-        <v>304.9102649889192</v>
+        <v>312.1672323684923</v>
       </c>
       <c r="E56" t="n">
-        <v>312.9363098144531</v>
+        <v>314.0603332519531</v>
       </c>
       <c r="F56" t="n">
-        <v>9721900</v>
+        <v>8982900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B57" t="n">
-        <v>315.2041261224818</v>
+        <v>315.115395356304</v>
       </c>
       <c r="C57" t="n">
-        <v>315.7858618718594</v>
+        <v>318.3593402708456</v>
       </c>
       <c r="D57" t="n">
-        <v>312.1672627021157</v>
+        <v>313.9322146909975</v>
       </c>
       <c r="E57" t="n">
-        <v>314.0603637695312</v>
+        <v>315.5393676757812</v>
       </c>
       <c r="F57" t="n">
-        <v>8982900</v>
+        <v>10864100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B58" t="n">
-        <v>315.115395356304</v>
+        <v>314.6223718715413</v>
       </c>
       <c r="C58" t="n">
-        <v>318.3593402708456</v>
+        <v>315.0463441586525</v>
       </c>
       <c r="D58" t="n">
-        <v>313.9322146909975</v>
+        <v>309.9980348220149</v>
       </c>
       <c r="E58" t="n">
-        <v>315.5393676757812</v>
+        <v>311.1319274902344</v>
       </c>
       <c r="F58" t="n">
-        <v>10864100</v>
+        <v>8331300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B59" t="n">
-        <v>314.6224027314819</v>
+        <v>313.9716244610726</v>
       </c>
       <c r="C59" t="n">
-        <v>315.0463750601788</v>
+        <v>314.8984658400699</v>
       </c>
       <c r="D59" t="n">
-        <v>309.9980652283745</v>
+        <v>310.2544194174254</v>
       </c>
       <c r="E59" t="n">
-        <v>311.1319580078125</v>
+        <v>310.5699462890625</v>
       </c>
       <c r="F59" t="n">
-        <v>8331300</v>
+        <v>8718700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B60" t="n">
-        <v>313.971593609235</v>
+        <v>311.5756418636432</v>
       </c>
       <c r="C60" t="n">
-        <v>314.8984348971578</v>
+        <v>313.2518519730792</v>
       </c>
       <c r="D60" t="n">
-        <v>310.254388930852</v>
+        <v>307.8485673512913</v>
       </c>
       <c r="E60" t="n">
-        <v>310.5699157714844</v>
+        <v>308.6176452636719</v>
       </c>
       <c r="F60" t="n">
-        <v>8718700</v>
+        <v>11444900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B61" t="n">
-        <v>311.575672673722</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C61" t="n">
-        <v>313.2518829489097</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D61" t="n">
-        <v>307.8485977928193</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E61" t="n">
-        <v>308.61767578125</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F61" t="n">
-        <v>11444900</v>
+        <v>24494400</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B62" t="n">
-        <v>309.3965776494671</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="C62" t="n">
-        <v>314.099781180705</v>
+        <v>318.7043994886834</v>
       </c>
       <c r="D62" t="n">
-        <v>308.8049723403709</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="E62" t="n">
-        <v>312.7686767578125</v>
+        <v>318.5663452148438</v>
       </c>
       <c r="F62" t="n">
-        <v>24494400</v>
+        <v>8354600</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B63" t="n">
-        <v>313.0644852104395</v>
+        <v>319.0790830432475</v>
       </c>
       <c r="C63" t="n">
-        <v>318.7043994886834</v>
+        <v>323.1907116116738</v>
       </c>
       <c r="D63" t="n">
-        <v>313.0644852104395</v>
+        <v>318.5663744582675</v>
       </c>
       <c r="E63" t="n">
-        <v>318.5663452148438</v>
+        <v>321.3666076660156</v>
       </c>
       <c r="F63" t="n">
-        <v>8354600</v>
+        <v>6668300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B64" t="n">
-        <v>319.0790830432475</v>
+        <v>321.6722493328215</v>
       </c>
       <c r="C64" t="n">
-        <v>323.1907116116738</v>
+        <v>325.3697449529369</v>
       </c>
       <c r="D64" t="n">
-        <v>318.5663744582675</v>
+        <v>320.9426198260136</v>
       </c>
       <c r="E64" t="n">
-        <v>321.3666076660156</v>
+        <v>324.5612487792969</v>
       </c>
       <c r="F64" t="n">
-        <v>6668300</v>
+        <v>4289300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B65" t="n">
-        <v>321.6722493328215</v>
+        <v>324.5020893383847</v>
       </c>
       <c r="C65" t="n">
-        <v>325.3697449529369</v>
+        <v>326.22758744424</v>
       </c>
       <c r="D65" t="n">
-        <v>320.9426198260136</v>
+        <v>321.9680949886989</v>
       </c>
       <c r="E65" t="n">
-        <v>324.5612487792969</v>
+        <v>323.3189086914062</v>
       </c>
       <c r="F65" t="n">
-        <v>4289300</v>
+        <v>4158300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B66" t="n">
-        <v>324.502058709128</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C66" t="n">
-        <v>326.2275566521161</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D66" t="n">
-        <v>321.9680645986219</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E66" t="n">
-        <v>323.3188781738281</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F66" t="n">
-        <v>4158300</v>
+        <v>8635300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B67" t="n">
-        <v>322.4216288798564</v>
+        <v>320.2622768741799</v>
       </c>
       <c r="C67" t="n">
-        <v>323.1808371734579</v>
+        <v>320.3904615362508</v>
       </c>
       <c r="D67" t="n">
-        <v>319.0002116144308</v>
+        <v>317.9747523718436</v>
       </c>
       <c r="E67" t="n">
-        <v>319.2171325683594</v>
+        <v>318.8917541503906</v>
       </c>
       <c r="F67" t="n">
-        <v>8635300</v>
+        <v>7904300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B68" t="n">
-        <v>320.2623075229155</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C68" t="n">
-        <v>320.3904921972535</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D68" t="n">
-        <v>317.9747828016658</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E68" t="n">
-        <v>318.8917846679688</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F68" t="n">
-        <v>7904300</v>
+        <v>5048500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B69" t="n">
-        <v>319.7988699190817</v>
+        <v>317.9846252281575</v>
       </c>
       <c r="C69" t="n">
-        <v>320.3313177342217</v>
+        <v>321.1694123071354</v>
       </c>
       <c r="D69" t="n">
-        <v>317.5310845539587</v>
+        <v>316.2492576445291</v>
       </c>
       <c r="E69" t="n">
-        <v>317.7085571289062</v>
+        <v>320.9229125976562</v>
       </c>
       <c r="F69" t="n">
-        <v>5048500</v>
+        <v>8054000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B70" t="n">
-        <v>317.9846252281575</v>
+        <v>320.942628937084</v>
       </c>
       <c r="C70" t="n">
-        <v>321.1694123071354</v>
+        <v>332.5281155423397</v>
       </c>
       <c r="D70" t="n">
-        <v>316.2492576445291</v>
+        <v>320.636971697701</v>
       </c>
       <c r="E70" t="n">
-        <v>320.9229125976562</v>
+        <v>329.3630676269531</v>
       </c>
       <c r="F70" t="n">
-        <v>8054000</v>
+        <v>10752600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,25 +2263,25 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B71" t="n">
-        <v>320.9426586744551</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C71" t="n">
-        <v>332.5281463531796</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D71" t="n">
-        <v>320.637001406751</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E71" t="n">
-        <v>329.3630981445312</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F71" t="n">
-        <v>10752600</v>
+        <v>7660800</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2289,25 +2289,25 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B72" t="n">
-        <v>329.4422902981328</v>
+        <v>327.9764659913386</v>
       </c>
       <c r="C72" t="n">
-        <v>332.6612412306879</v>
+        <v>328.9767963949314</v>
       </c>
       <c r="D72" t="n">
-        <v>327.491109600743</v>
+        <v>321.4989374679619</v>
       </c>
       <c r="E72" t="n">
-        <v>331.4132690429688</v>
+        <v>323.8660888671875</v>
       </c>
       <c r="F72" t="n">
-        <v>7660800</v>
+        <v>9815200</v>
       </c>
       <c r="G72" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B73" t="n">
-        <v>327.9764350864437</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C73" t="n">
-        <v>328.9767653957764</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D73" t="n">
-        <v>321.4989071734381</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E73" t="n">
-        <v>323.8660583496094</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F73" t="n">
-        <v>9815200</v>
+        <v>11737100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B74" t="n">
-        <v>323.2718313763784</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C74" t="n">
-        <v>328.2339475379842</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D74" t="n">
-        <v>322.5388804495614</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E74" t="n">
-        <v>326.6393432617188</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F74" t="n">
-        <v>11737100</v>
+        <v>6738100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B75" t="n">
-        <v>326.1936353875406</v>
+        <v>318.8049029297019</v>
       </c>
       <c r="C75" t="n">
-        <v>328.7291759216584</v>
+        <v>322.9053354478686</v>
       </c>
       <c r="D75" t="n">
-        <v>325.0348299492433</v>
+        <v>318.1611187929736</v>
       </c>
       <c r="E75" t="n">
-        <v>326.0450744628906</v>
+        <v>321.3899536132812</v>
       </c>
       <c r="F75" t="n">
-        <v>6738100</v>
+        <v>12805100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B76" t="n">
-        <v>318.8049332018166</v>
+        <v>321.2017547389941</v>
       </c>
       <c r="C76" t="n">
-        <v>322.9053661093398</v>
+        <v>323.7372950994605</v>
       </c>
       <c r="D76" t="n">
-        <v>318.1611490039577</v>
+        <v>307.6029450408882</v>
       </c>
       <c r="E76" t="n">
-        <v>321.3899841308594</v>
+        <v>307.9297790527344</v>
       </c>
       <c r="F76" t="n">
-        <v>12805100</v>
+        <v>19371200</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B77" t="n">
-        <v>321.2017865718998</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C77" t="n">
-        <v>323.7373271836527</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D77" t="n">
-        <v>307.6029755260753</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E77" t="n">
-        <v>307.9298095703125</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F77" t="n">
-        <v>19371200</v>
+        <v>25951500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B78" t="n">
-        <v>305.2556057077196</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C78" t="n">
-        <v>308.7815926253858</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D78" t="n">
-        <v>303.1954601804828</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E78" t="n">
-        <v>304.9287414550781</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F78" t="n">
-        <v>25951500</v>
+        <v>14751400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B79" t="n">
-        <v>305.5230197927318</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C79" t="n">
-        <v>309.95031666446</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D79" t="n">
-        <v>304.8098971346673</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E79" t="n">
-        <v>306.3054809570312</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F79" t="n">
-        <v>14751400</v>
+        <v>14652500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B80" t="n">
-        <v>307.385060616362</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C80" t="n">
-        <v>314.1795087286461</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D80" t="n">
-        <v>307.0383983149945</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E80" t="n">
-        <v>309.4848022460938</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F80" t="n">
-        <v>14652500</v>
+        <v>12900600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B81" t="n">
-        <v>303.2845981841295</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C81" t="n">
-        <v>308.1774060521912</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D81" t="n">
-        <v>298.9761500928895</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E81" t="n">
-        <v>299.8477478027344</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F81" t="n">
-        <v>12900600</v>
+        <v>10270100</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B82" t="n">
-        <v>300.5311849469782</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C82" t="n">
-        <v>302.4823658305288</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D82" t="n">
-        <v>298.2729680555718</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E82" t="n">
-        <v>299.1544799804688</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F82" t="n">
-        <v>10270100</v>
+        <v>10535800</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B83" t="n">
-        <v>301.9474777854751</v>
+        <v>299.1148112655088</v>
       </c>
       <c r="C83" t="n">
-        <v>305.2555953909441</v>
+        <v>299.4812715954647</v>
       </c>
       <c r="D83" t="n">
-        <v>300.0062112868251</v>
+        <v>293.6772702297321</v>
       </c>
       <c r="E83" t="n">
-        <v>300.729248046875</v>
+        <v>294.8757019042969</v>
       </c>
       <c r="F83" t="n">
-        <v>10535800</v>
+        <v>11107900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B84" t="n">
-        <v>299.1148422218051</v>
+        <v>294.9648486176391</v>
       </c>
       <c r="C84" t="n">
-        <v>299.4813025896872</v>
+        <v>298.8969221500132</v>
       </c>
       <c r="D84" t="n">
-        <v>293.6773006232809</v>
+        <v>294.6083024116733</v>
       </c>
       <c r="E84" t="n">
-        <v>294.875732421875</v>
+        <v>298.1640014648438</v>
       </c>
       <c r="F84" t="n">
-        <v>11107900</v>
+        <v>11752700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B85" t="n">
-        <v>294.9648788077786</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C85" t="n">
-        <v>298.8969527426069</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D85" t="n">
-        <v>294.6083325653198</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E85" t="n">
-        <v>298.1640319824219</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F85" t="n">
-        <v>11752700</v>
+        <v>11527400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B86" t="n">
-        <v>298.4512235287846</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C86" t="n">
-        <v>299.0851237823749</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D86" t="n">
-        <v>295.3016109870806</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E86" t="n">
-        <v>297.4409790039062</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F86" t="n">
-        <v>11527400</v>
+        <v>9556700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B87" t="n">
-        <v>297.4013222225187</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C87" t="n">
-        <v>299.0355829225425</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D87" t="n">
-        <v>295.2025300603667</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E87" t="n">
-        <v>297.8965454101562</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F87" t="n">
-        <v>9556700</v>
+        <v>11580000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B88" t="n">
-        <v>299.5110006693188</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C88" t="n">
-        <v>303.898671192008</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D88" t="n">
-        <v>299.3327275624257</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E88" t="n">
-        <v>303.4926147460938</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F88" t="n">
-        <v>11580000</v>
+        <v>11953200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B89" t="n">
-        <v>302.333781642444</v>
+        <v>301.5513314360023</v>
       </c>
       <c r="C89" t="n">
-        <v>304.9881708986046</v>
+        <v>306.3450888451811</v>
       </c>
       <c r="D89" t="n">
-        <v>299.6694782493637</v>
+        <v>298.4908553932551</v>
       </c>
       <c r="E89" t="n">
-        <v>302.9676818847656</v>
+        <v>305.1961975097656</v>
       </c>
       <c r="F89" t="n">
-        <v>11953200</v>
+        <v>9839400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B90" t="n">
-        <v>301.5513012828864</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C90" t="n">
-        <v>306.3450582127215</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D90" t="n">
-        <v>298.4908255461663</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E90" t="n">
-        <v>305.1961669921875</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F90" t="n">
-        <v>9839400</v>
+        <v>12688000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B91" t="n">
-        <v>306.7709905338949</v>
+        <v>311.4062598905275</v>
       </c>
       <c r="C91" t="n">
-        <v>313.2286905211348</v>
+        <v>316.2594412620415</v>
       </c>
       <c r="D91" t="n">
-        <v>306.1470044328188</v>
+        <v>311.4062598905275</v>
       </c>
       <c r="E91" t="n">
-        <v>311.8420715332031</v>
+        <v>314.2389221191406</v>
       </c>
       <c r="F91" t="n">
-        <v>12688000</v>
+        <v>9848800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B92" t="n">
-        <v>311.4062901330092</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C92" t="n">
-        <v>316.2594719758441</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D92" t="n">
-        <v>311.4062901330092</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E92" t="n">
-        <v>314.2389526367188</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F92" t="n">
-        <v>9848800</v>
+        <v>9388000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B93" t="n">
-        <v>311.9906259989966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C93" t="n">
-        <v>312.9909865673853</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D93" t="n">
-        <v>302.6210112179966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E93" t="n">
-        <v>307.1968688964844</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F93" t="n">
-        <v>9388000</v>
+        <v>17797400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B94" t="n">
-        <v>311.7034102684662</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C94" t="n">
-        <v>321.1522783634816</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D94" t="n">
-        <v>311.7034102684662</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E94" t="n">
-        <v>319.3199462890625</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F94" t="n">
-        <v>17797400</v>
+        <v>11477500</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B95" t="n">
-        <v>318.2700781279603</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C95" t="n">
-        <v>323.2817350541263</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D95" t="n">
-        <v>317.0518180384032</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E95" t="n">
-        <v>319.0228271484375</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F95" t="n">
-        <v>11477500</v>
+        <v>9902200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B96" t="n">
-        <v>319.4684837021083</v>
+        <v>320.1519144431551</v>
       </c>
       <c r="C96" t="n">
-        <v>323.014298845819</v>
+        <v>322.1724337503843</v>
       </c>
       <c r="D96" t="n">
-        <v>312.1094739861534</v>
+        <v>305.7805563960757</v>
       </c>
       <c r="E96" t="n">
-        <v>315.2392883300781</v>
+        <v>307.8505859375</v>
       </c>
       <c r="F96" t="n">
-        <v>9902200</v>
+        <v>8703500</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B97" t="n">
-        <v>320.1518827061323</v>
+        <v>309.2966060076438</v>
       </c>
       <c r="C97" t="n">
-        <v>322.1724018130651</v>
+        <v>310.6238005797982</v>
       </c>
       <c r="D97" t="n">
-        <v>305.7805260837019</v>
+        <v>297.1537232583444</v>
       </c>
       <c r="E97" t="n">
-        <v>307.8505554199219</v>
+        <v>299.7487182617188</v>
       </c>
       <c r="F97" t="n">
-        <v>8703500</v>
+        <v>13443400</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B98" t="n">
-        <v>309.2966374972976</v>
+        <v>295.6680481198895</v>
       </c>
       <c r="C98" t="n">
-        <v>310.6238322045743</v>
+        <v>301.3829431862302</v>
       </c>
       <c r="D98" t="n">
-        <v>297.1537535117247</v>
+        <v>293.6871553220786</v>
       </c>
       <c r="E98" t="n">
-        <v>299.7487487792969</v>
+        <v>299.6595458984375</v>
       </c>
       <c r="F98" t="n">
-        <v>13443400</v>
+        <v>9114500</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B99" t="n">
-        <v>295.6680782309701</v>
+        <v>299.8675549474044</v>
       </c>
       <c r="C99" t="n">
-        <v>301.3829738793206</v>
+        <v>305.2951817518681</v>
       </c>
       <c r="D99" t="n">
-        <v>293.6871852314235</v>
+        <v>299.6100292169066</v>
       </c>
       <c r="E99" t="n">
-        <v>299.6595764160156</v>
+        <v>304.19580078125</v>
       </c>
       <c r="F99" t="n">
-        <v>9114500</v>
+        <v>8896800</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B100" t="n">
-        <v>299.8675850307636</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C100" t="n">
-        <v>305.2952123797385</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D100" t="n">
-        <v>299.6100592744303</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E100" t="n">
-        <v>304.1958312988281</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F100" t="n">
-        <v>8896800</v>
+        <v>7209600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B101" t="n">
-        <v>305.5130974954087</v>
+        <v>304.2354576365961</v>
       </c>
       <c r="C101" t="n">
-        <v>309.2966101142475</v>
+        <v>306.226234501648</v>
       </c>
       <c r="D101" t="n">
-        <v>304.2849535938903</v>
+        <v>302.2050242231491</v>
       </c>
       <c r="E101" t="n">
-        <v>305.8300476074219</v>
+        <v>305.1070251464844</v>
       </c>
       <c r="F101" t="n">
-        <v>7209600</v>
+        <v>6737700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B102" t="n">
-        <v>304.2354272061944</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C102" t="n">
-        <v>306.2262038721237</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D102" t="n">
-        <v>302.2049939958365</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E102" t="n">
-        <v>305.1069946289062</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F102" t="n">
-        <v>6737700</v>
+        <v>7792700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B103" t="n">
-        <v>305.4536802835111</v>
+        <v>305.8498774375392</v>
       </c>
       <c r="C103" t="n">
-        <v>308.0288471084009</v>
+        <v>308.028871901531</v>
       </c>
       <c r="D103" t="n">
-        <v>302.7596647203387</v>
+        <v>292.2807780649544</v>
       </c>
       <c r="E103" t="n">
-        <v>307.8208618164062</v>
+        <v>294.8262329101562</v>
       </c>
       <c r="F103" t="n">
-        <v>7792700</v>
+        <v>12955400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B104" t="n">
-        <v>305.8498457788994</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C104" t="n">
-        <v>308.0288400173425</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D104" t="n">
-        <v>292.2807478108573</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E104" t="n">
-        <v>294.8262023925781</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F104" t="n">
-        <v>12955400</v>
+        <v>13554100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B105" t="n">
-        <v>293.9843218466586</v>
+        <v>295.7869207463737</v>
       </c>
       <c r="C105" t="n">
-        <v>296.886322684036</v>
+        <v>300.7589506810849</v>
       </c>
       <c r="D105" t="n">
-        <v>288.5962907533433</v>
+        <v>294.1724883145502</v>
       </c>
       <c r="E105" t="n">
-        <v>294.459716796875</v>
+        <v>300.4023742675781</v>
       </c>
       <c r="F105" t="n">
-        <v>13554100</v>
+        <v>8095500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B106" t="n">
-        <v>295.7869507950724</v>
+        <v>301.670173133609</v>
       </c>
       <c r="C106" t="n">
-        <v>300.7589812348872</v>
+        <v>306.0578739762234</v>
       </c>
       <c r="D106" t="n">
-        <v>294.1725181992404</v>
+        <v>300.7391812579012</v>
       </c>
       <c r="E106" t="n">
-        <v>300.4024047851562</v>
+        <v>303.2053833007812</v>
       </c>
       <c r="F106" t="n">
-        <v>8095500</v>
+        <v>7007800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B107" t="n">
-        <v>301.670173133609</v>
+        <v>297.1339389424841</v>
       </c>
       <c r="C107" t="n">
-        <v>306.0578739762234</v>
+        <v>300.0557680991628</v>
       </c>
       <c r="D107" t="n">
-        <v>300.7391812579012</v>
+        <v>291.636973162459</v>
       </c>
       <c r="E107" t="n">
-        <v>303.2053833007812</v>
+        <v>297.4310607910156</v>
       </c>
       <c r="F107" t="n">
-        <v>7007800</v>
+        <v>18620800</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B108" t="n">
-        <v>297.1339389424841</v>
+        <v>291.9935267958635</v>
       </c>
       <c r="C108" t="n">
-        <v>300.0557680991628</v>
+        <v>297.1141484397957</v>
       </c>
       <c r="D108" t="n">
-        <v>291.636973162459</v>
+        <v>290.4088063693875</v>
       </c>
       <c r="E108" t="n">
-        <v>297.4310607910156</v>
+        <v>294.7172546386719</v>
       </c>
       <c r="F108" t="n">
-        <v>18620800</v>
+        <v>8508900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B109" t="n">
-        <v>291.9935267958635</v>
+        <v>289.4975898716125</v>
       </c>
       <c r="C109" t="n">
-        <v>297.1141484397957</v>
+        <v>299.5011046657454</v>
       </c>
       <c r="D109" t="n">
-        <v>290.4088063693875</v>
+        <v>286.7342359222354</v>
       </c>
       <c r="E109" t="n">
-        <v>294.7172546386719</v>
+        <v>297.3914489746094</v>
       </c>
       <c r="F109" t="n">
-        <v>8508900</v>
+        <v>10278200</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B110" t="n">
-        <v>289.4975898716125</v>
+        <v>297.1240288614248</v>
       </c>
       <c r="C110" t="n">
-        <v>299.5011046657454</v>
+        <v>298.1243894751821</v>
       </c>
       <c r="D110" t="n">
-        <v>286.7342359222354</v>
+        <v>292.993883980321</v>
       </c>
       <c r="E110" t="n">
-        <v>297.3914489746094</v>
+        <v>296.52978515625</v>
       </c>
       <c r="F110" t="n">
-        <v>10278200</v>
+        <v>8055700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B111" t="n">
-        <v>297.1240288614248</v>
+        <v>295.1332451958745</v>
       </c>
       <c r="C111" t="n">
-        <v>298.1243894751821</v>
+        <v>298.3620800816865</v>
       </c>
       <c r="D111" t="n">
-        <v>292.993883980321</v>
+        <v>289.6362492414601</v>
       </c>
       <c r="E111" t="n">
-        <v>296.52978515625</v>
+        <v>290.7455444335938</v>
       </c>
       <c r="F111" t="n">
-        <v>8055700</v>
+        <v>12732500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B112" t="n">
-        <v>295.1332451958745</v>
+        <v>283.6044306839189</v>
       </c>
       <c r="C112" t="n">
-        <v>298.3620800816865</v>
+        <v>287.2195541533999</v>
       </c>
       <c r="D112" t="n">
-        <v>289.6362492414601</v>
+        <v>280.9995517042956</v>
       </c>
       <c r="E112" t="n">
-        <v>290.7455444335938</v>
+        <v>286.7144470214844</v>
       </c>
       <c r="F112" t="n">
-        <v>12732500</v>
+        <v>13496500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B113" t="n">
-        <v>283.6044306839189</v>
+        <v>282.7724816341387</v>
       </c>
       <c r="C113" t="n">
-        <v>287.2195541533999</v>
+        <v>288.3189881947603</v>
       </c>
       <c r="D113" t="n">
-        <v>280.9995517042956</v>
+        <v>277.7707387954702</v>
       </c>
       <c r="E113" t="n">
-        <v>286.7144470214844</v>
+        <v>287.1502685546875</v>
       </c>
       <c r="F113" t="n">
-        <v>13496500</v>
+        <v>12241100</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B114" t="n">
-        <v>282.7724816341387</v>
+        <v>286.5262662545288</v>
       </c>
       <c r="C114" t="n">
-        <v>288.3189881947603</v>
+        <v>289.9532025593205</v>
       </c>
       <c r="D114" t="n">
-        <v>277.7707387954702</v>
+        <v>284.4364084963449</v>
       </c>
       <c r="E114" t="n">
-        <v>287.1502685546875</v>
+        <v>285.9716186523438</v>
       </c>
       <c r="F114" t="n">
-        <v>12241100</v>
+        <v>8344900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B115" t="n">
-        <v>286.5262662545288</v>
+        <v>286.0508472723319</v>
       </c>
       <c r="C115" t="n">
-        <v>289.9532025593205</v>
+        <v>287.7049062038017</v>
       </c>
       <c r="D115" t="n">
-        <v>284.4364084963449</v>
+        <v>282.1385715612803</v>
       </c>
       <c r="E115" t="n">
-        <v>285.9716186523438</v>
+        <v>284.7731628417969</v>
       </c>
       <c r="F115" t="n">
-        <v>8344900</v>
+        <v>10205000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B116" t="n">
-        <v>286.0508166178312</v>
+        <v>280.1279843639117</v>
       </c>
       <c r="C116" t="n">
-        <v>287.7048753720447</v>
+        <v>281.1679713767581</v>
       </c>
       <c r="D116" t="n">
-        <v>282.1385413260368</v>
+        <v>276.4336380780354</v>
       </c>
       <c r="E116" t="n">
-        <v>284.7731323242188</v>
+        <v>280.1874389648438</v>
       </c>
       <c r="F116" t="n">
-        <v>10205000</v>
+        <v>13760500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B117" t="n">
-        <v>280.1279538528093</v>
+        <v>281.9504072447318</v>
       </c>
       <c r="C117" t="n">
-        <v>281.167940752382</v>
+        <v>284.4463214441296</v>
       </c>
       <c r="D117" t="n">
-        <v>276.4336079693154</v>
+        <v>280.2468381234208</v>
       </c>
       <c r="E117" t="n">
-        <v>280.1874084472656</v>
+        <v>280.7321472167969</v>
       </c>
       <c r="F117" t="n">
-        <v>13760500</v>
+        <v>9091200</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B118" t="n">
-        <v>281.9504072447318</v>
+        <v>283.6044205599556</v>
       </c>
       <c r="C118" t="n">
-        <v>284.4463214441296</v>
+        <v>286.506421278288</v>
       </c>
       <c r="D118" t="n">
-        <v>280.2468381234208</v>
+        <v>281.8909373944359</v>
       </c>
       <c r="E118" t="n">
-        <v>280.7321472167969</v>
+        <v>283.4261474609375</v>
       </c>
       <c r="F118" t="n">
-        <v>9091200</v>
+        <v>8149000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B119" t="n">
-        <v>283.6044205599556</v>
+        <v>286.2390279690733</v>
       </c>
       <c r="C119" t="n">
-        <v>286.506421278288</v>
+        <v>288.9726698808299</v>
       </c>
       <c r="D119" t="n">
-        <v>281.8909373944359</v>
+        <v>283.2181783456238</v>
       </c>
       <c r="E119" t="n">
-        <v>283.4261474609375</v>
+        <v>284.1492004394531</v>
       </c>
       <c r="F119" t="n">
-        <v>8149000</v>
+        <v>8961200</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B120" t="n">
-        <v>286.2390279690733</v>
+        <v>284.0897180113691</v>
       </c>
       <c r="C120" t="n">
-        <v>288.9726698808299</v>
+        <v>286.6450865635814</v>
       </c>
       <c r="D120" t="n">
-        <v>283.2181783456238</v>
+        <v>282.3960631878955</v>
       </c>
       <c r="E120" t="n">
-        <v>284.1492004394531</v>
+        <v>284.9910278320312</v>
       </c>
       <c r="F120" t="n">
-        <v>8961200</v>
+        <v>10057000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B121" t="n">
-        <v>284.0897484324327</v>
+        <v>284.1392890417467</v>
       </c>
       <c r="C121" t="n">
-        <v>286.6451172582804</v>
+        <v>286.7441681021885</v>
       </c>
       <c r="D121" t="n">
-        <v>282.3960934275981</v>
+        <v>281.900870340191</v>
       </c>
       <c r="E121" t="n">
-        <v>284.9910583496094</v>
+        <v>285.2188720703125</v>
       </c>
       <c r="F121" t="n">
-        <v>10057000</v>
+        <v>9846700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B122" t="n">
-        <v>284.1392586396808</v>
+        <v>285.3277943529036</v>
       </c>
       <c r="C122" t="n">
-        <v>286.7441374214082</v>
+        <v>287.9326733008621</v>
       </c>
       <c r="D122" t="n">
-        <v>281.9008401776293</v>
+        <v>282.5446423017302</v>
       </c>
       <c r="E122" t="n">
-        <v>285.2188415527344</v>
+        <v>283.8223266601562</v>
       </c>
       <c r="F122" t="n">
-        <v>9846700</v>
+        <v>22436500</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B123" t="n">
-        <v>285.327825032355</v>
+        <v>291.4982779446762</v>
       </c>
       <c r="C123" t="n">
-        <v>287.9327042603992</v>
+        <v>292.9245231806114</v>
       </c>
       <c r="D123" t="n">
-        <v>282.5446726819272</v>
+        <v>285.2188513876401</v>
       </c>
       <c r="E123" t="n">
-        <v>283.8223571777344</v>
+        <v>287.1403198242188</v>
       </c>
       <c r="F123" t="n">
-        <v>22436500</v>
+        <v>11470800</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B124" t="n">
-        <v>291.4982779446762</v>
+        <v>283.4360748065673</v>
       </c>
       <c r="C124" t="n">
-        <v>292.9245231806114</v>
+        <v>292.6571288676103</v>
       </c>
       <c r="D124" t="n">
-        <v>285.2188513876401</v>
+        <v>282.6436995084055</v>
       </c>
       <c r="E124" t="n">
-        <v>287.1403198242188</v>
+        <v>289.6065368652344</v>
       </c>
       <c r="F124" t="n">
-        <v>11470800</v>
+        <v>11092300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B125" t="n">
-        <v>283.4360748065673</v>
+        <v>291.3398308899875</v>
       </c>
       <c r="C125" t="n">
-        <v>292.6571288676103</v>
+        <v>294.7965097163498</v>
       </c>
       <c r="D125" t="n">
-        <v>282.6436995084055</v>
+        <v>289.6461758443202</v>
       </c>
       <c r="E125" t="n">
-        <v>289.6065368652344</v>
+        <v>292.5977172851562</v>
       </c>
       <c r="F125" t="n">
-        <v>11092300</v>
+        <v>12188200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B126" t="n">
-        <v>291.3398308899875</v>
+        <v>289.7847899387647</v>
       </c>
       <c r="C126" t="n">
-        <v>294.7965097163498</v>
+        <v>292.1717693530369</v>
       </c>
       <c r="D126" t="n">
-        <v>289.6461758443202</v>
+        <v>287.9524883078727</v>
       </c>
       <c r="E126" t="n">
-        <v>292.5977172851562</v>
+        <v>288.8735961914062</v>
       </c>
       <c r="F126" t="n">
-        <v>12188200</v>
+        <v>8669200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B127" t="n">
-        <v>289.7848205526045</v>
+        <v>286.3777093696089</v>
       </c>
       <c r="C127" t="n">
-        <v>292.1718002190451</v>
+        <v>287.3384134369941</v>
       </c>
       <c r="D127" t="n">
-        <v>287.9525187281419</v>
+        <v>279.0582953832721</v>
       </c>
       <c r="E127" t="n">
-        <v>288.8736267089844</v>
+        <v>280.1378784179688</v>
       </c>
       <c r="F127" t="n">
-        <v>8669200</v>
+        <v>9873300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B128" t="n">
-        <v>286.3777093696089</v>
+        <v>282.0197247859078</v>
       </c>
       <c r="C128" t="n">
-        <v>287.3384134369941</v>
+        <v>284.505755156032</v>
       </c>
       <c r="D128" t="n">
-        <v>279.0582953832721</v>
+        <v>279.6327451103039</v>
       </c>
       <c r="E128" t="n">
-        <v>280.1378784179688</v>
+        <v>281.0589904785156</v>
       </c>
       <c r="F128" t="n">
-        <v>9873300</v>
+        <v>11734400</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B129" t="n">
-        <v>282.0197247859078</v>
+        <v>285.7140887250632</v>
       </c>
       <c r="C129" t="n">
-        <v>284.505755156032</v>
+        <v>292.2510413422024</v>
       </c>
       <c r="D129" t="n">
-        <v>279.6327451103039</v>
+        <v>282.2277281014015</v>
       </c>
       <c r="E129" t="n">
-        <v>281.0589904785156</v>
+        <v>291.3497314453125</v>
       </c>
       <c r="F129" t="n">
-        <v>11734400</v>
+        <v>12956900</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B130" t="n">
-        <v>285.7140887250632</v>
+        <v>292.567989087923</v>
       </c>
       <c r="C130" t="n">
-        <v>292.2510413422024</v>
+        <v>295.8661624411999</v>
       </c>
       <c r="D130" t="n">
-        <v>282.2277281014015</v>
+        <v>290.1116710297465</v>
       </c>
       <c r="E130" t="n">
-        <v>291.3497314453125</v>
+        <v>292.5580749511719</v>
       </c>
       <c r="F130" t="n">
-        <v>12956900</v>
+        <v>11267200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B131" t="n">
-        <v>292.567989087923</v>
+        <v>289.1212191631598</v>
       </c>
       <c r="C131" t="n">
-        <v>295.8661624411999</v>
+        <v>292.7957669317203</v>
       </c>
       <c r="D131" t="n">
-        <v>290.1116710297465</v>
+        <v>285.9616926535428</v>
       </c>
       <c r="E131" t="n">
-        <v>292.5580749511719</v>
+        <v>291.7855224609375</v>
       </c>
       <c r="F131" t="n">
-        <v>11267200</v>
+        <v>6669300</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,25 +3849,25 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B132" t="n">
-        <v>289.1212191631598</v>
+        <v>292.7412191857173</v>
       </c>
       <c r="C132" t="n">
-        <v>292.7957669317203</v>
+        <v>295.4987855589938</v>
       </c>
       <c r="D132" t="n">
-        <v>285.9616926535428</v>
+        <v>291.8850906324002</v>
       </c>
       <c r="E132" t="n">
-        <v>291.7855224609375</v>
+        <v>294.125</v>
       </c>
       <c r="F132" t="n">
-        <v>6669300</v>
+        <v>7142600</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -3875,25 +3875,25 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B133" t="n">
-        <v>292.7412191857173</v>
+        <v>291.8253790066561</v>
       </c>
       <c r="C133" t="n">
-        <v>295.4987855589938</v>
+        <v>296.8427544058445</v>
       </c>
       <c r="D133" t="n">
-        <v>291.8850906324002</v>
+        <v>291.3873498301165</v>
       </c>
       <c r="E133" t="n">
-        <v>294.125</v>
+        <v>296.0662536621094</v>
       </c>
       <c r="F133" t="n">
-        <v>7142600</v>
+        <v>7849100</v>
       </c>
       <c r="G133" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B134" t="n">
-        <v>291.8253790066561</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="C134" t="n">
-        <v>296.8427544058445</v>
+        <v>309.8640903908154</v>
       </c>
       <c r="D134" t="n">
-        <v>291.3873498301165</v>
+        <v>303.9606617936424</v>
       </c>
       <c r="E134" t="n">
-        <v>296.0662536621094</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="F134" t="n">
-        <v>7849100</v>
+        <v>10590200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B135" t="n">
-        <v>306.5888366699219</v>
+        <v>305.5734164156603</v>
       </c>
       <c r="C135" t="n">
-        <v>309.8640903908154</v>
+        <v>309.8640846884941</v>
       </c>
       <c r="D135" t="n">
-        <v>303.9606617936424</v>
+        <v>304.73715687535</v>
       </c>
       <c r="E135" t="n">
-        <v>306.5888366699219</v>
+        <v>308.938232421875</v>
       </c>
       <c r="F135" t="n">
-        <v>10590200</v>
+        <v>6586600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B136" t="n">
-        <v>305.5734164156603</v>
+        <v>308.6097380099313</v>
       </c>
       <c r="C136" t="n">
-        <v>309.8640846884941</v>
+        <v>308.9581744354404</v>
       </c>
       <c r="D136" t="n">
-        <v>304.73715687535</v>
+        <v>305.344449093958</v>
       </c>
       <c r="E136" t="n">
-        <v>308.938232421875</v>
+        <v>308.4803161621094</v>
       </c>
       <c r="F136" t="n">
-        <v>6586600</v>
+        <v>6069700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B137" t="n">
-        <v>308.6097380099313</v>
+        <v>306.0910825316173</v>
       </c>
       <c r="C137" t="n">
-        <v>308.9581744354404</v>
+        <v>312.3329523629397</v>
       </c>
       <c r="D137" t="n">
-        <v>305.344449093958</v>
+        <v>304.0900871089203</v>
       </c>
       <c r="E137" t="n">
-        <v>308.4803161621094</v>
+        <v>312.2732238769531</v>
       </c>
       <c r="F137" t="n">
-        <v>6069700</v>
+        <v>8318200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B138" t="n">
-        <v>306.0910825316173</v>
+        <v>308.4305432499699</v>
       </c>
       <c r="C138" t="n">
-        <v>312.3329523629397</v>
+        <v>312.9103618924516</v>
       </c>
       <c r="D138" t="n">
-        <v>304.0900871089203</v>
+        <v>307.4847916064935</v>
       </c>
       <c r="E138" t="n">
-        <v>312.2732238769531</v>
+        <v>309.7247009277344</v>
       </c>
       <c r="F138" t="n">
-        <v>8318200</v>
+        <v>11455500</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B139" t="n">
-        <v>308.4305432499699</v>
+        <v>312.5420354159922</v>
       </c>
       <c r="C139" t="n">
-        <v>312.9103618924516</v>
+        <v>312.8307129741003</v>
       </c>
       <c r="D139" t="n">
-        <v>307.4847916064935</v>
+        <v>302.8954898881459</v>
       </c>
       <c r="E139" t="n">
-        <v>309.7247009277344</v>
+        <v>304.5579833984375</v>
       </c>
       <c r="F139" t="n">
-        <v>11455500</v>
+        <v>9885800</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B140" t="n">
-        <v>312.5420354159922</v>
+        <v>303.9805907681049</v>
       </c>
       <c r="C140" t="n">
-        <v>312.8307129741003</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="D140" t="n">
-        <v>302.8954898881459</v>
+        <v>303.8312695552229</v>
       </c>
       <c r="E140" t="n">
-        <v>304.5579833984375</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="F140" t="n">
-        <v>9885800</v>
+        <v>8208600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B141" t="n">
-        <v>303.9805907681049</v>
+        <v>311.068653468178</v>
       </c>
       <c r="C141" t="n">
-        <v>308.5599670410156</v>
+        <v>313.4877482505245</v>
       </c>
       <c r="D141" t="n">
-        <v>303.8312695552229</v>
+        <v>308.6993222963794</v>
       </c>
       <c r="E141" t="n">
-        <v>308.5599670410156</v>
+        <v>308.8984375</v>
       </c>
       <c r="F141" t="n">
-        <v>8208600</v>
+        <v>11082400</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B142" t="n">
-        <v>311.068653468178</v>
+        <v>309.4559416581444</v>
       </c>
       <c r="C142" t="n">
-        <v>313.4877482505245</v>
+        <v>315.7077766193834</v>
       </c>
       <c r="D142" t="n">
-        <v>308.6993222963794</v>
+        <v>308.9780833700189</v>
       </c>
       <c r="E142" t="n">
-        <v>308.8984375</v>
+        <v>315.5683898925781</v>
       </c>
       <c r="F142" t="n">
-        <v>11082400</v>
+        <v>10772000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B143" t="n">
-        <v>309.4559416581444</v>
+        <v>316.0661368489313</v>
       </c>
       <c r="C143" t="n">
-        <v>315.7077766193834</v>
+        <v>318.8038038717339</v>
       </c>
       <c r="D143" t="n">
-        <v>308.9780833700189</v>
+        <v>311.3474041387296</v>
       </c>
       <c r="E143" t="n">
-        <v>315.5683898925781</v>
+        <v>311.5962829589844</v>
       </c>
       <c r="F143" t="n">
-        <v>10772000</v>
+        <v>7084300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B144" t="n">
-        <v>316.0661368489313</v>
+        <v>313.4379903862348</v>
       </c>
       <c r="C144" t="n">
-        <v>318.8038038717339</v>
+        <v>313.7366328164263</v>
       </c>
       <c r="D144" t="n">
-        <v>311.3474041387296</v>
+        <v>310.5410372905177</v>
       </c>
       <c r="E144" t="n">
-        <v>311.5962829589844</v>
+        <v>311.6161804199219</v>
       </c>
       <c r="F144" t="n">
-        <v>7084300</v>
+        <v>5545900</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B145" t="n">
-        <v>313.4379903862348</v>
+        <v>312.1139549773267</v>
       </c>
       <c r="C145" t="n">
-        <v>313.7366328164263</v>
+        <v>313.5773637260273</v>
       </c>
       <c r="D145" t="n">
-        <v>310.5410372905177</v>
+        <v>307.5047445243564</v>
       </c>
       <c r="E145" t="n">
-        <v>311.6161804199219</v>
+        <v>310.2921752929688</v>
       </c>
       <c r="F145" t="n">
-        <v>5545900</v>
+        <v>6969700</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B146" t="n">
-        <v>312.1139549773267</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="C146" t="n">
-        <v>313.5773637260273</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="D146" t="n">
-        <v>307.5047445243564</v>
+        <v>306.5092257615542</v>
       </c>
       <c r="E146" t="n">
-        <v>310.2921752929688</v>
+        <v>306.8974609375</v>
       </c>
       <c r="F146" t="n">
-        <v>6969700</v>
+        <v>5215300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B147" t="n">
-        <v>309.7545850384977</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="C147" t="n">
-        <v>309.7545850384977</v>
+        <v>311.1781431330245</v>
       </c>
       <c r="D147" t="n">
-        <v>306.5092257615542</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="E147" t="n">
-        <v>306.8974609375</v>
+        <v>310.232421875</v>
       </c>
       <c r="F147" t="n">
-        <v>5215300</v>
+        <v>7925300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B148" t="n">
-        <v>305.5037244427344</v>
+        <v>313.7864355589005</v>
       </c>
       <c r="C148" t="n">
-        <v>311.1781431330245</v>
+        <v>314.035314384572</v>
       </c>
       <c r="D148" t="n">
-        <v>305.5037244427344</v>
+        <v>309.7745101043047</v>
       </c>
       <c r="E148" t="n">
-        <v>310.232421875</v>
+        <v>310.0532531738281</v>
       </c>
       <c r="F148" t="n">
-        <v>7925300</v>
+        <v>7398600</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B149" t="n">
-        <v>313.7864355589005</v>
+        <v>309.1771855961317</v>
       </c>
       <c r="C149" t="n">
-        <v>314.035314384572</v>
+        <v>310.6505287563671</v>
       </c>
       <c r="D149" t="n">
-        <v>309.7745101043047</v>
+        <v>305.9118967162461</v>
       </c>
       <c r="E149" t="n">
-        <v>310.0532531738281</v>
+        <v>307.8630981445312</v>
       </c>
       <c r="F149" t="n">
-        <v>7398600</v>
+        <v>8031800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B150" t="n">
-        <v>309.1771855961317</v>
+        <v>305.6928786901284</v>
       </c>
       <c r="C150" t="n">
-        <v>310.6505287563671</v>
+        <v>312.6913497643884</v>
       </c>
       <c r="D150" t="n">
-        <v>305.9118967162461</v>
+        <v>305.1951210592971</v>
       </c>
       <c r="E150" t="n">
-        <v>307.8630981445312</v>
+        <v>311.8252563476562</v>
       </c>
       <c r="F150" t="n">
-        <v>8031800</v>
+        <v>8865400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B151" t="n">
-        <v>305.6928786901284</v>
+        <v>312.5420381202088</v>
       </c>
       <c r="C151" t="n">
-        <v>312.6913497643884</v>
+        <v>314.6624601726697</v>
       </c>
       <c r="D151" t="n">
-        <v>305.1951210592971</v>
+        <v>310.431520181067</v>
       </c>
       <c r="E151" t="n">
-        <v>311.8252563476562</v>
+        <v>311.0686645507812</v>
       </c>
       <c r="F151" t="n">
-        <v>8865400</v>
+        <v>6135400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B152" t="n">
-        <v>312.5420381202088</v>
+        <v>309.2269452093906</v>
       </c>
       <c r="C152" t="n">
-        <v>314.6624601726697</v>
+        <v>309.2568094519629</v>
       </c>
       <c r="D152" t="n">
-        <v>310.431520181067</v>
+        <v>305.1353920734132</v>
       </c>
       <c r="E152" t="n">
-        <v>311.0686645507812</v>
+        <v>306.270263671875</v>
       </c>
       <c r="F152" t="n">
-        <v>6135400</v>
+        <v>7338200</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B153" t="n">
-        <v>309.2269452093906</v>
+        <v>306.3299974055641</v>
       </c>
       <c r="C153" t="n">
-        <v>309.2568094519629</v>
+        <v>309.5753869306937</v>
       </c>
       <c r="D153" t="n">
-        <v>305.1353920734132</v>
+        <v>305.42407485773</v>
       </c>
       <c r="E153" t="n">
-        <v>306.270263671875</v>
+        <v>308.0124206542969</v>
       </c>
       <c r="F153" t="n">
-        <v>7338200</v>
+        <v>6316800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B154" t="n">
-        <v>306.3299974055641</v>
+        <v>310.0532528884956</v>
       </c>
       <c r="C154" t="n">
-        <v>309.5753869306937</v>
+        <v>314.8416790595512</v>
       </c>
       <c r="D154" t="n">
-        <v>305.42407485773</v>
+        <v>309.9536952821754</v>
       </c>
       <c r="E154" t="n">
-        <v>308.0124206542969</v>
+        <v>313.4877624511719</v>
       </c>
       <c r="F154" t="n">
-        <v>6316800</v>
+        <v>8629500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B155" t="n">
-        <v>310.0532528884956</v>
+        <v>313.2388767644321</v>
       </c>
       <c r="C155" t="n">
-        <v>314.8416790595512</v>
+        <v>314.8814709002291</v>
       </c>
       <c r="D155" t="n">
-        <v>309.9536952821754</v>
+        <v>304.7670623908274</v>
       </c>
       <c r="E155" t="n">
-        <v>313.4877624511719</v>
+        <v>304.8964538574219</v>
       </c>
       <c r="F155" t="n">
-        <v>8629500</v>
+        <v>8359600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B156" t="n">
-        <v>313.2388767644321</v>
+        <v>306.8675912418493</v>
       </c>
       <c r="C156" t="n">
-        <v>314.8814709002291</v>
+        <v>307.6042628420606</v>
       </c>
       <c r="D156" t="n">
-        <v>304.7670623908274</v>
+        <v>299.1523476664256</v>
       </c>
       <c r="E156" t="n">
-        <v>304.8964538574219</v>
+        <v>300.7451782226562</v>
       </c>
       <c r="F156" t="n">
-        <v>8359600</v>
+        <v>9464300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B157" t="n">
-        <v>306.8675912418493</v>
+        <v>300.7451596100784</v>
       </c>
       <c r="C157" t="n">
-        <v>307.6042628420606</v>
+        <v>301.8302675742967</v>
       </c>
       <c r="D157" t="n">
-        <v>299.1523476664256</v>
+        <v>297.5395993270601</v>
       </c>
       <c r="E157" t="n">
-        <v>300.7451782226562</v>
+        <v>298.6545715332031</v>
       </c>
       <c r="F157" t="n">
-        <v>9464300</v>
+        <v>9512000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B158" t="n">
-        <v>300.7451596100784</v>
+        <v>298.6744753830843</v>
       </c>
       <c r="C158" t="n">
-        <v>301.8302675742967</v>
+        <v>304.6873960201211</v>
       </c>
       <c r="D158" t="n">
-        <v>297.5395993270601</v>
+        <v>294.2245209852311</v>
       </c>
       <c r="E158" t="n">
-        <v>298.6545715332031</v>
+        <v>303.5126953125</v>
       </c>
       <c r="F158" t="n">
-        <v>9512000</v>
+        <v>9498200</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B159" t="n">
-        <v>298.6744753830843</v>
+        <v>300.9144028967509</v>
       </c>
       <c r="C159" t="n">
-        <v>304.6873960201211</v>
+        <v>301.6411400127173</v>
       </c>
       <c r="D159" t="n">
-        <v>294.2245209852311</v>
+        <v>298.7242874353194</v>
       </c>
       <c r="E159" t="n">
-        <v>303.5126953125</v>
+        <v>298.9034729003906</v>
       </c>
       <c r="F159" t="n">
-        <v>9498200</v>
+        <v>7709500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B160" t="n">
-        <v>300.9144028967509</v>
+        <v>300.8945046380796</v>
       </c>
       <c r="C160" t="n">
-        <v>301.6411400127173</v>
+        <v>302.387777613951</v>
       </c>
       <c r="D160" t="n">
-        <v>298.7242874353194</v>
+        <v>297.4699295162906</v>
       </c>
       <c r="E160" t="n">
-        <v>298.9034729003906</v>
+        <v>298.5650024414062</v>
       </c>
       <c r="F160" t="n">
-        <v>7709500</v>
+        <v>7364300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B161" t="n">
-        <v>300.8945046380796</v>
+        <v>298.8636262885424</v>
       </c>
       <c r="C161" t="n">
-        <v>302.387777613951</v>
+        <v>299.4410421498196</v>
       </c>
       <c r="D161" t="n">
-        <v>297.4699295162906</v>
+        <v>295.1205095874812</v>
       </c>
       <c r="E161" t="n">
-        <v>298.5650024414062</v>
+        <v>296.4743957519531</v>
       </c>
       <c r="F161" t="n">
-        <v>7364300</v>
+        <v>8699300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B162" t="n">
-        <v>298.8636262885424</v>
+        <v>296.6635495230975</v>
       </c>
       <c r="C162" t="n">
-        <v>299.4410421498196</v>
+        <v>299.908939014877</v>
       </c>
       <c r="D162" t="n">
-        <v>295.1205095874812</v>
+        <v>295.8870488301784</v>
       </c>
       <c r="E162" t="n">
-        <v>296.4743957519531</v>
+        <v>299.3813171386719</v>
       </c>
       <c r="F162" t="n">
-        <v>8699300</v>
+        <v>7546300</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B163" t="n">
-        <v>296.6635495230975</v>
+        <v>299.7396822358739</v>
       </c>
       <c r="C163" t="n">
-        <v>299.908939014877</v>
+        <v>300.436555061437</v>
       </c>
       <c r="D163" t="n">
-        <v>295.8870488301784</v>
+        <v>293.935841710235</v>
       </c>
       <c r="E163" t="n">
-        <v>299.3813171386719</v>
+        <v>294.3738708496094</v>
       </c>
       <c r="F163" t="n">
-        <v>7546300</v>
+        <v>8066900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B164" t="n">
-        <v>299.7396822358739</v>
+        <v>295.3694126574367</v>
       </c>
       <c r="C164" t="n">
-        <v>300.436555061437</v>
+        <v>301.57145376365</v>
       </c>
       <c r="D164" t="n">
-        <v>293.935841710235</v>
+        <v>292.3530024013792</v>
       </c>
       <c r="E164" t="n">
-        <v>294.3738708496094</v>
+        <v>300.625732421875</v>
       </c>
       <c r="F164" t="n">
-        <v>8066900</v>
+        <v>9327000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B165" t="n">
-        <v>295.3694126574367</v>
+        <v>299.8790926087445</v>
       </c>
       <c r="C165" t="n">
-        <v>301.57145376365</v>
+        <v>302.6167597554335</v>
       </c>
       <c r="D165" t="n">
-        <v>292.3530024013792</v>
+        <v>298.8636475324957</v>
       </c>
       <c r="E165" t="n">
-        <v>300.625732421875</v>
+        <v>301.6411437988281</v>
       </c>
       <c r="F165" t="n">
-        <v>9327000</v>
+        <v>7874400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B166" t="n">
-        <v>299.8790926087445</v>
+        <v>303.3135932887391</v>
       </c>
       <c r="C166" t="n">
-        <v>302.6167597554335</v>
+        <v>306.0711901040885</v>
       </c>
       <c r="D166" t="n">
-        <v>298.8636475324957</v>
+        <v>302.4773640852478</v>
       </c>
       <c r="E166" t="n">
-        <v>301.6411437988281</v>
+        <v>305.0059814453125</v>
       </c>
       <c r="F166" t="n">
-        <v>7874400</v>
+        <v>5973900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B167" t="n">
-        <v>303.3135932887391</v>
+        <v>307.1065011172144</v>
       </c>
       <c r="C167" t="n">
-        <v>306.0711901040885</v>
+        <v>308.5400455607295</v>
       </c>
       <c r="D167" t="n">
-        <v>302.4773640852478</v>
+        <v>304.0701916446211</v>
       </c>
       <c r="E167" t="n">
-        <v>305.0059814453125</v>
+        <v>305.3643493652344</v>
       </c>
       <c r="F167" t="n">
-        <v>5973900</v>
+        <v>7725400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B168" t="n">
-        <v>307.1065011172144</v>
+        <v>303.6321536663258</v>
       </c>
       <c r="C168" t="n">
-        <v>308.5400455607295</v>
+        <v>304.5281113223131</v>
       </c>
       <c r="D168" t="n">
-        <v>304.0701916446211</v>
+        <v>294.4236375305438</v>
       </c>
       <c r="E168" t="n">
-        <v>305.3643493652344</v>
+        <v>297.9378051757812</v>
       </c>
       <c r="F168" t="n">
-        <v>7725400</v>
+        <v>11779200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B169" t="n">
-        <v>303.6321536663258</v>
+        <v>296.2354906683788</v>
       </c>
       <c r="C169" t="n">
-        <v>304.5281113223131</v>
+        <v>299.7197941661088</v>
       </c>
       <c r="D169" t="n">
-        <v>294.4236375305438</v>
+        <v>294.4236455581874</v>
       </c>
       <c r="E169" t="n">
-        <v>297.9378051757812</v>
+        <v>295.3992614746094</v>
       </c>
       <c r="F169" t="n">
-        <v>11779200</v>
+        <v>9757700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B170" t="n">
-        <v>296.2354906683788</v>
+        <v>295.070728717322</v>
       </c>
       <c r="C170" t="n">
-        <v>299.7197941661088</v>
+        <v>298.5351328968941</v>
       </c>
       <c r="D170" t="n">
-        <v>294.4236455581874</v>
+        <v>293.8761285862639</v>
       </c>
       <c r="E170" t="n">
-        <v>295.3992614746094</v>
+        <v>297.9676818847656</v>
       </c>
       <c r="F170" t="n">
-        <v>9757700</v>
+        <v>13969000</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B171" t="n">
-        <v>295.070728717322</v>
+        <v>296.3549462063085</v>
       </c>
       <c r="C171" t="n">
-        <v>298.5351328968941</v>
+        <v>298.2065900448191</v>
       </c>
       <c r="D171" t="n">
-        <v>293.8761285862639</v>
+        <v>293.9457858606032</v>
       </c>
       <c r="E171" t="n">
-        <v>297.9676818847656</v>
+        <v>295.2499084472656</v>
       </c>
       <c r="F171" t="n">
-        <v>13969000</v>
+        <v>7930000</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B172" t="n">
-        <v>296.3549462063085</v>
+        <v>295.170270518017</v>
       </c>
       <c r="C172" t="n">
-        <v>298.2065900448191</v>
+        <v>300.7152977310929</v>
       </c>
       <c r="D172" t="n">
-        <v>293.9457858606032</v>
+        <v>293.9457758280521</v>
       </c>
       <c r="E172" t="n">
-        <v>295.2499084472656</v>
+        <v>299.6102600097656</v>
       </c>
       <c r="F172" t="n">
-        <v>7930000</v>
+        <v>8296200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B173" t="n">
-        <v>295.170270518017</v>
+        <v>298.5749714904202</v>
       </c>
       <c r="C173" t="n">
-        <v>300.7152977310929</v>
+        <v>300.6058008918799</v>
       </c>
       <c r="D173" t="n">
-        <v>293.9457758280521</v>
+        <v>295.2300241797341</v>
       </c>
       <c r="E173" t="n">
-        <v>299.6102600097656</v>
+        <v>299.5007934570312</v>
       </c>
       <c r="F173" t="n">
-        <v>8296200</v>
+        <v>7003900</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B174" t="n">
-        <v>298.5749714904202</v>
+        <v>304.3688300919619</v>
       </c>
       <c r="C174" t="n">
-        <v>300.6058008918799</v>
+        <v>311.5066879726736</v>
       </c>
       <c r="D174" t="n">
-        <v>295.2300241797341</v>
+        <v>303.0746723882986</v>
       </c>
       <c r="E174" t="n">
-        <v>299.5007934570312</v>
+        <v>309.4957580566406</v>
       </c>
       <c r="F174" t="n">
-        <v>7003900</v>
+        <v>10345200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B175" t="n">
-        <v>304.3688300919619</v>
+        <v>312.8805189963161</v>
       </c>
       <c r="C175" t="n">
-        <v>311.5066879726736</v>
+        <v>313.5873263681962</v>
       </c>
       <c r="D175" t="n">
-        <v>303.0746723882986</v>
+        <v>308.211549706599</v>
       </c>
       <c r="E175" t="n">
-        <v>309.4957580566406</v>
+        <v>310.9691162109375</v>
       </c>
       <c r="F175" t="n">
-        <v>10345200</v>
+        <v>9118800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B176" t="n">
-        <v>312.8805189963161</v>
+        <v>311.8451695343703</v>
       </c>
       <c r="C176" t="n">
-        <v>313.5873263681962</v>
+        <v>314.881479064701</v>
       </c>
       <c r="D176" t="n">
-        <v>308.211549706599</v>
+        <v>309.3862455138746</v>
       </c>
       <c r="E176" t="n">
-        <v>310.9691162109375</v>
+        <v>309.7147521972656</v>
       </c>
       <c r="F176" t="n">
-        <v>9118800</v>
+        <v>6827000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B177" t="n">
-        <v>311.8451695343703</v>
+        <v>312.1040028799189</v>
       </c>
       <c r="C177" t="n">
-        <v>314.881479064701</v>
+        <v>315.0009559692908</v>
       </c>
       <c r="D177" t="n">
-        <v>309.3862455138746</v>
+        <v>307.6241841525692</v>
       </c>
       <c r="E177" t="n">
-        <v>309.7147521972656</v>
+        <v>311.2976379394531</v>
       </c>
       <c r="F177" t="n">
-        <v>6827000</v>
+        <v>11594600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B178" t="n">
-        <v>312.1040028799189</v>
+        <v>311.1582462393224</v>
       </c>
       <c r="C178" t="n">
-        <v>315.0009559692908</v>
+        <v>313.3384270822022</v>
       </c>
       <c r="D178" t="n">
-        <v>307.6241841525692</v>
+        <v>307.6440785979976</v>
       </c>
       <c r="E178" t="n">
-        <v>311.2976379394531</v>
+        <v>307.7536010742188</v>
       </c>
       <c r="F178" t="n">
-        <v>11594600</v>
+        <v>7446200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B179" t="n">
-        <v>311.1582462393224</v>
+        <v>308.1717081621576</v>
       </c>
       <c r="C179" t="n">
-        <v>313.3384270822022</v>
+        <v>313.3085706612414</v>
       </c>
       <c r="D179" t="n">
-        <v>307.6440785979976</v>
+        <v>307.4947650619962</v>
       </c>
       <c r="E179" t="n">
-        <v>307.7536010742188</v>
+        <v>312.0840759277344</v>
       </c>
       <c r="F179" t="n">
-        <v>7446200</v>
+        <v>9116600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B180" t="n">
-        <v>308.1717081621576</v>
+        <v>314.5529794375797</v>
       </c>
       <c r="C180" t="n">
-        <v>313.3085706612414</v>
+        <v>319.8590627688811</v>
       </c>
       <c r="D180" t="n">
-        <v>307.4947650619962</v>
+        <v>314.1348496322589</v>
       </c>
       <c r="E180" t="n">
-        <v>312.0840759277344</v>
+        <v>319.2816772460938</v>
       </c>
       <c r="F180" t="n">
-        <v>9116600</v>
+        <v>7426200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B181" t="n">
-        <v>314.5529794375797</v>
+        <v>322.4673390673774</v>
       </c>
       <c r="C181" t="n">
-        <v>319.8590627688811</v>
+        <v>324.4583697274161</v>
       </c>
       <c r="D181" t="n">
-        <v>314.1348496322589</v>
+        <v>317.4101041776777</v>
       </c>
       <c r="E181" t="n">
-        <v>319.2816772460938</v>
+        <v>317.9675903320312</v>
       </c>
       <c r="F181" t="n">
-        <v>7426200</v>
+        <v>7988900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B182" t="n">
-        <v>322.4673390673774</v>
+        <v>322.8455866314347</v>
       </c>
       <c r="C182" t="n">
-        <v>324.4583697274161</v>
+        <v>330.2621874699331</v>
       </c>
       <c r="D182" t="n">
-        <v>317.4101041776777</v>
+        <v>322.5668435738929</v>
       </c>
       <c r="E182" t="n">
-        <v>317.9675903320312</v>
+        <v>329.6549377441406</v>
       </c>
       <c r="F182" t="n">
-        <v>7988900</v>
+        <v>11094900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B183" t="n">
-        <v>322.8455866314347</v>
+        <v>330.6902497468859</v>
       </c>
       <c r="C183" t="n">
-        <v>330.2621874699331</v>
+        <v>336.2551763704633</v>
       </c>
       <c r="D183" t="n">
-        <v>322.5668435738929</v>
+        <v>330.0133066656099</v>
       </c>
       <c r="E183" t="n">
-        <v>329.6549377441406</v>
+        <v>331.9645080566406</v>
       </c>
       <c r="F183" t="n">
-        <v>11094900</v>
+        <v>12246400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B184" t="n">
-        <v>330.6902497468859</v>
+        <v>335.4388795655989</v>
       </c>
       <c r="C184" t="n">
-        <v>336.2551763704633</v>
+        <v>336.5737511659094</v>
       </c>
       <c r="D184" t="n">
-        <v>330.0133066656099</v>
+        <v>322.7062308624821</v>
       </c>
       <c r="E184" t="n">
-        <v>331.9645080566406</v>
+        <v>323.761474609375</v>
       </c>
       <c r="F184" t="n">
-        <v>12246400</v>
+        <v>20111000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B185" t="n">
-        <v>335.4388795655989</v>
+        <v>328.221392261561</v>
       </c>
       <c r="C185" t="n">
-        <v>336.5737511659094</v>
+        <v>331.2776010100568</v>
       </c>
       <c r="D185" t="n">
-        <v>322.7062308624821</v>
+        <v>325.2846101022313</v>
       </c>
       <c r="E185" t="n">
-        <v>323.761474609375</v>
+        <v>329.993408203125</v>
       </c>
       <c r="F185" t="n">
-        <v>20111000</v>
+        <v>10182500</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B186" t="n">
-        <v>328.221392261561</v>
+        <v>327.9924099173137</v>
       </c>
       <c r="C186" t="n">
-        <v>331.2776010100568</v>
+        <v>333.8659438033595</v>
       </c>
       <c r="D186" t="n">
-        <v>325.2846101022313</v>
+        <v>325.7425357353925</v>
       </c>
       <c r="E186" t="n">
-        <v>329.993408203125</v>
+        <v>332.6414794921875</v>
       </c>
       <c r="F186" t="n">
-        <v>10182500</v>
+        <v>7582200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B187" t="n">
-        <v>327.9924099173137</v>
+        <v>331.5762891678024</v>
       </c>
       <c r="C187" t="n">
-        <v>333.8659438033595</v>
+        <v>333.0297330031709</v>
       </c>
       <c r="D187" t="n">
-        <v>325.7425357353925</v>
+        <v>328.291070440402</v>
       </c>
       <c r="E187" t="n">
-        <v>332.6414794921875</v>
+        <v>331.95458984375</v>
       </c>
       <c r="F187" t="n">
-        <v>7582200</v>
+        <v>7907400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B188" t="n">
-        <v>331.5762891678024</v>
+        <v>333.4577793441399</v>
       </c>
       <c r="C188" t="n">
-        <v>333.0297330031709</v>
+        <v>341.909724468194</v>
       </c>
       <c r="D188" t="n">
-        <v>328.291070440402</v>
+        <v>333.2586945227413</v>
       </c>
       <c r="E188" t="n">
-        <v>331.95458984375</v>
+        <v>333.6170654296875</v>
       </c>
       <c r="F188" t="n">
-        <v>7907400</v>
+        <v>10043100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B189" t="n">
-        <v>333.4577793441399</v>
+        <v>334.4931229022353</v>
       </c>
       <c r="C189" t="n">
-        <v>341.909724468194</v>
+        <v>334.8913229247855</v>
       </c>
       <c r="D189" t="n">
-        <v>333.2586945227413</v>
+        <v>326.0312433050061</v>
       </c>
       <c r="E189" t="n">
-        <v>333.6170654296875</v>
+        <v>327.5742797851562</v>
       </c>
       <c r="F189" t="n">
-        <v>10043100</v>
+        <v>17640900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B190" t="n">
-        <v>334.4931229022353</v>
+        <v>326.8077430430495</v>
       </c>
       <c r="C190" t="n">
-        <v>334.8913229247855</v>
+        <v>330.8993264933345</v>
       </c>
       <c r="D190" t="n">
-        <v>326.0312433050061</v>
+        <v>325.7325999471821</v>
       </c>
       <c r="E190" t="n">
-        <v>327.5742797851562</v>
+        <v>327.9127807617188</v>
       </c>
       <c r="F190" t="n">
-        <v>17640900</v>
+        <v>7981800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B191" t="n">
-        <v>326.8077430430495</v>
+        <v>327.4150312810326</v>
       </c>
       <c r="C191" t="n">
-        <v>330.8993264933345</v>
+        <v>328.9580677951163</v>
       </c>
       <c r="D191" t="n">
-        <v>325.7325999471821</v>
+        <v>325.2149206632551</v>
       </c>
       <c r="E191" t="n">
-        <v>327.9127807617188</v>
+        <v>325.8619995117188</v>
       </c>
       <c r="F191" t="n">
-        <v>7981800</v>
+        <v>8080100</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B192" t="n">
-        <v>327.4150312810326</v>
+        <v>326.8973584256916</v>
       </c>
       <c r="C192" t="n">
-        <v>328.9580677951163</v>
+        <v>334.1347741939035</v>
       </c>
       <c r="D192" t="n">
-        <v>325.2149206632551</v>
+        <v>323.5524415571975</v>
       </c>
       <c r="E192" t="n">
-        <v>325.8619995117188</v>
+        <v>332.5718078613281</v>
       </c>
       <c r="F192" t="n">
-        <v>8080100</v>
+        <v>15210200</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B193" t="n">
-        <v>326.8973584256916</v>
+        <v>336.5040683580973</v>
       </c>
       <c r="C193" t="n">
-        <v>334.1347741939035</v>
+        <v>338.4751995750331</v>
       </c>
       <c r="D193" t="n">
-        <v>323.5524415571975</v>
+        <v>330.2820977776739</v>
       </c>
       <c r="E193" t="n">
-        <v>332.5718078613281</v>
+        <v>332.9700012207031</v>
       </c>
       <c r="F193" t="n">
-        <v>15210200</v>
+        <v>8413900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,25 +5461,25 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B194" t="n">
-        <v>336.5040683580973</v>
+        <v>335</v>
       </c>
       <c r="C194" t="n">
-        <v>338.4751995750331</v>
+        <v>339.7200012207031</v>
       </c>
       <c r="D194" t="n">
-        <v>330.2820977776739</v>
+        <v>334.1099853515625</v>
       </c>
       <c r="E194" t="n">
-        <v>332.9700012207031</v>
+        <v>337.7200012207031</v>
       </c>
       <c r="F194" t="n">
-        <v>8413900</v>
+        <v>8673500</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -5487,25 +5487,25 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B195" t="n">
-        <v>335</v>
+        <v>340.9800109863281</v>
       </c>
       <c r="C195" t="n">
-        <v>339.7200012207031</v>
+        <v>341.3999938964844</v>
       </c>
       <c r="D195" t="n">
-        <v>334.1099853515625</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E195" t="n">
-        <v>337.7200012207031</v>
+        <v>339.2200012207031</v>
       </c>
       <c r="F195" t="n">
-        <v>8673500</v>
+        <v>7115800</v>
       </c>
       <c r="G195" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B196" t="n">
-        <v>340.9800109863281</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="C196" t="n">
-        <v>341.3999938964844</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="D196" t="n">
-        <v>337.0899963378906</v>
+        <v>330.1300048828125</v>
       </c>
       <c r="E196" t="n">
-        <v>339.2200012207031</v>
+        <v>330.6199951171875</v>
       </c>
       <c r="F196" t="n">
-        <v>7115800</v>
+        <v>18505200</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B197" t="n">
-        <v>336.5299987792969</v>
+        <v>331.4599914550781</v>
       </c>
       <c r="C197" t="n">
-        <v>336.5299987792969</v>
+        <v>337</v>
       </c>
       <c r="D197" t="n">
-        <v>330.1300048828125</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="E197" t="n">
-        <v>330.6199951171875</v>
+        <v>335.4700012207031</v>
       </c>
       <c r="F197" t="n">
-        <v>18505200</v>
+        <v>15570600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B198" t="n">
-        <v>331.4599914550781</v>
+        <v>337.4700012207031</v>
       </c>
       <c r="C198" t="n">
-        <v>337</v>
+        <v>338.5899963378906</v>
       </c>
       <c r="D198" t="n">
-        <v>330.8099975585938</v>
+        <v>335.7699890136719</v>
       </c>
       <c r="E198" t="n">
-        <v>335.4700012207031</v>
+        <v>336.4700012207031</v>
       </c>
       <c r="F198" t="n">
-        <v>15570600</v>
+        <v>6299000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B199" t="n">
-        <v>337.4700012207031</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="C199" t="n">
-        <v>338.5899963378906</v>
+        <v>338.3500061035156</v>
       </c>
       <c r="D199" t="n">
-        <v>335.7699890136719</v>
+        <v>332.5</v>
       </c>
       <c r="E199" t="n">
-        <v>336.4700012207031</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="F199" t="n">
-        <v>6299000</v>
+        <v>7120300</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B200" t="n">
-        <v>338.3399963378906</v>
+        <v>327</v>
       </c>
       <c r="C200" t="n">
-        <v>338.3500061035156</v>
+        <v>344.7300109863281</v>
       </c>
       <c r="D200" t="n">
-        <v>332.5</v>
+        <v>325.75</v>
       </c>
       <c r="E200" t="n">
-        <v>334.5299987792969</v>
+        <v>342.8900146484375</v>
       </c>
       <c r="F200" t="n">
-        <v>7120300</v>
+        <v>14537900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>327</v>
+        <v>345.8500061035156</v>
       </c>
       <c r="C201" t="n">
-        <v>344.7300109863281</v>
+        <v>351.239990234375</v>
       </c>
       <c r="D201" t="n">
-        <v>325.75</v>
+        <v>344.0499877929688</v>
       </c>
       <c r="E201" t="n">
-        <v>342.8900146484375</v>
+        <v>346.9100036621094</v>
       </c>
       <c r="F201" t="n">
-        <v>14537900</v>
+        <v>10750000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B202" t="n">
-        <v>345.8500061035156</v>
+        <v>349.2799987792969</v>
       </c>
       <c r="C202" t="n">
-        <v>351.239990234375</v>
+        <v>349.3399963378906</v>
       </c>
       <c r="D202" t="n">
-        <v>344.0499877929688</v>
+        <v>341.1099853515625</v>
       </c>
       <c r="E202" t="n">
-        <v>346.9100036621094</v>
+        <v>343.1499938964844</v>
       </c>
       <c r="F202" t="n">
-        <v>10750000</v>
+        <v>12432400</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B203" t="n">
-        <v>349.2799987792969</v>
+        <v>339.0299987792969</v>
       </c>
       <c r="C203" t="n">
-        <v>349.3399963378906</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="D203" t="n">
-        <v>341.1099853515625</v>
+        <v>335.0499877929688</v>
       </c>
       <c r="E203" t="n">
-        <v>343.1499938964844</v>
+        <v>341.1000061035156</v>
       </c>
       <c r="F203" t="n">
-        <v>12432400</v>
+        <v>9250900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B204" t="n">
-        <v>339.0299987792969</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="C204" t="n">
-        <v>346.1300048828125</v>
+        <v>344.260009765625</v>
       </c>
       <c r="D204" t="n">
-        <v>335.0499877929688</v>
+        <v>337.3699951171875</v>
       </c>
       <c r="E204" t="n">
-        <v>341.1000061035156</v>
+        <v>338.8699951171875</v>
       </c>
       <c r="F204" t="n">
-        <v>9250900</v>
+        <v>7723300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B205" t="n">
-        <v>341.7999877929688</v>
+        <v>340.1199951171875</v>
       </c>
       <c r="C205" t="n">
-        <v>344.260009765625</v>
+        <v>345.739990234375</v>
       </c>
       <c r="D205" t="n">
-        <v>337.3699951171875</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E205" t="n">
-        <v>338.8699951171875</v>
+        <v>345.2300109863281</v>
       </c>
       <c r="F205" t="n">
-        <v>7723300</v>
+        <v>6015300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B206" t="n">
-        <v>340.1199951171875</v>
+        <v>345.0700073242188</v>
       </c>
       <c r="C206" t="n">
-        <v>345.739990234375</v>
+        <v>349.0700073242188</v>
       </c>
       <c r="D206" t="n">
-        <v>337.2999877929688</v>
+        <v>344.25</v>
       </c>
       <c r="E206" t="n">
-        <v>345.2300109863281</v>
+        <v>348.2099914550781</v>
       </c>
       <c r="F206" t="n">
-        <v>6015300</v>
+        <v>8040200</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B207" t="n">
-        <v>345.0700073242188</v>
+        <v>346.5799865722656</v>
       </c>
       <c r="C207" t="n">
-        <v>349.0700073242188</v>
+        <v>349.9200134277344</v>
       </c>
       <c r="D207" t="n">
-        <v>344.25</v>
+        <v>345.4200134277344</v>
       </c>
       <c r="E207" t="n">
-        <v>348.2099914550781</v>
+        <v>349.8999938964844</v>
       </c>
       <c r="F207" t="n">
-        <v>8040200</v>
+        <v>10913000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B208" t="n">
-        <v>346.5799865722656</v>
+        <v>350.6400146484375</v>
       </c>
       <c r="C208" t="n">
-        <v>349.9200134277344</v>
+        <v>353.3699951171875</v>
       </c>
       <c r="D208" t="n">
-        <v>345.4200134277344</v>
+        <v>347.5</v>
       </c>
       <c r="E208" t="n">
-        <v>349.8999938964844</v>
+        <v>353.2099914550781</v>
       </c>
       <c r="F208" t="n">
-        <v>10913000</v>
+        <v>7520800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B209" t="n">
-        <v>350.6400146484375</v>
+        <v>357.8900146484375</v>
       </c>
       <c r="C209" t="n">
-        <v>353.3699951171875</v>
+        <v>359.0499877929688</v>
       </c>
       <c r="D209" t="n">
-        <v>347.5</v>
+        <v>352.5799865722656</v>
       </c>
       <c r="E209" t="n">
-        <v>353.2099914550781</v>
+        <v>356.2000122070312</v>
       </c>
       <c r="F209" t="n">
-        <v>7520800</v>
+        <v>7884900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B210" t="n">
-        <v>357.8900146484375</v>
+        <v>357.2999877929688</v>
       </c>
       <c r="C210" t="n">
-        <v>359.0499877929688</v>
+        <v>359.2999877929688</v>
       </c>
       <c r="D210" t="n">
-        <v>352.5799865722656</v>
+        <v>354.1499938964844</v>
       </c>
       <c r="E210" t="n">
-        <v>356.2000122070312</v>
+        <v>357.3099975585938</v>
       </c>
       <c r="F210" t="n">
-        <v>7884900</v>
+        <v>6533800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B211" t="n">
-        <v>357.2999877929688</v>
+        <v>356.5</v>
       </c>
       <c r="C211" t="n">
-        <v>359.2999877929688</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D211" t="n">
-        <v>354.1499938964844</v>
+        <v>343.7799987792969</v>
       </c>
       <c r="E211" t="n">
-        <v>357.3099975585938</v>
+        <v>344.7099914550781</v>
       </c>
       <c r="F211" t="n">
-        <v>6533800</v>
+        <v>8265300</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B212" t="n">
-        <v>356.5</v>
+        <v>347.5400085449219</v>
       </c>
       <c r="C212" t="n">
-        <v>357.3699951171875</v>
+        <v>352.2799987792969</v>
       </c>
       <c r="D212" t="n">
-        <v>343.7799987792969</v>
+        <v>345.3699951171875</v>
       </c>
       <c r="E212" t="n">
-        <v>344.7099914550781</v>
+        <v>350.8500061035156</v>
       </c>
       <c r="F212" t="n">
-        <v>8265300</v>
+        <v>7606500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B213" t="n">
-        <v>347.5400085449219</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C213" t="n">
-        <v>352.2799987792969</v>
+        <v>354.4700012207031</v>
       </c>
       <c r="D213" t="n">
-        <v>345.3699951171875</v>
+        <v>349.7000122070312</v>
       </c>
       <c r="E213" t="n">
-        <v>350.8500061035156</v>
+        <v>351.7900085449219</v>
       </c>
       <c r="F213" t="n">
-        <v>7606500</v>
+        <v>6603400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B214" t="n">
-        <v>353.2999877929688</v>
+        <v>353.75</v>
       </c>
       <c r="C214" t="n">
-        <v>354.4700012207031</v>
+        <v>355.6199951171875</v>
       </c>
       <c r="D214" t="n">
-        <v>349.7000122070312</v>
+        <v>350.8399963378906</v>
       </c>
       <c r="E214" t="n">
-        <v>351.7900085449219</v>
+        <v>352.6400146484375</v>
       </c>
       <c r="F214" t="n">
-        <v>6603400</v>
+        <v>6436600</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B215" t="n">
-        <v>353.75</v>
+        <v>355</v>
       </c>
       <c r="C215" t="n">
-        <v>355.6199951171875</v>
+        <v>363</v>
       </c>
       <c r="D215" t="n">
-        <v>350.8399963378906</v>
+        <v>353.8699951171875</v>
       </c>
       <c r="E215" t="n">
-        <v>352.6400146484375</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F215" t="n">
-        <v>6436600</v>
+        <v>8477200</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B216" t="n">
-        <v>355</v>
+        <v>358.9700012207031</v>
       </c>
       <c r="C216" t="n">
-        <v>363</v>
+        <v>362.1700134277344</v>
       </c>
       <c r="D216" t="n">
-        <v>353.8699951171875</v>
+        <v>358.2000122070312</v>
       </c>
       <c r="E216" t="n">
-        <v>357.5199890136719</v>
+        <v>359.239990234375</v>
       </c>
       <c r="F216" t="n">
-        <v>8477200</v>
+        <v>5269500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B217" t="n">
-        <v>358.9700012207031</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="C217" t="n">
-        <v>362.1700134277344</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="D217" t="n">
-        <v>358.2000122070312</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="E217" t="n">
-        <v>359.239990234375</v>
+        <v>356.2999877929688</v>
       </c>
       <c r="F217" t="n">
-        <v>5269500</v>
+        <v>5820100</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B218" t="n">
-        <v>362.8099975585938</v>
+        <v>355.760009765625</v>
       </c>
       <c r="C218" t="n">
-        <v>362.8099975585938</v>
+        <v>358.8500061035156</v>
       </c>
       <c r="D218" t="n">
-        <v>354.9500122070312</v>
+        <v>353.3299865722656</v>
       </c>
       <c r="E218" t="n">
-        <v>356.2999877929688</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F218" t="n">
-        <v>5820100</v>
+        <v>4566200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B219" t="n">
-        <v>355.760009765625</v>
+        <v>357.9599914550781</v>
       </c>
       <c r="C219" t="n">
-        <v>358.8500061035156</v>
+        <v>359.989990234375</v>
       </c>
       <c r="D219" t="n">
-        <v>353.3299865722656</v>
+        <v>356.5</v>
       </c>
       <c r="E219" t="n">
-        <v>357.5199890136719</v>
+        <v>359.7900085449219</v>
       </c>
       <c r="F219" t="n">
-        <v>4566200</v>
+        <v>5327500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B220" t="n">
-        <v>357.9599914550781</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="C220" t="n">
-        <v>359.989990234375</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="D220" t="n">
-        <v>356.5</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="E220" t="n">
-        <v>359.7900085449219</v>
+        <v>362.0400085449219</v>
       </c>
       <c r="F220" t="n">
-        <v>5327500</v>
+        <v>4576500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B221" t="n">
-        <v>360.0499877929688</v>
+        <v>362.9700012207031</v>
       </c>
       <c r="C221" t="n">
-        <v>363.1199951171875</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="D221" t="n">
-        <v>358.6000061035156</v>
+        <v>361.2999877929688</v>
       </c>
       <c r="E221" t="n">
-        <v>362.0400085449219</v>
+        <v>365.1799926757812</v>
       </c>
       <c r="F221" t="n">
-        <v>4576500</v>
+        <v>4366800</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B222" t="n">
-        <v>362.9700012207031</v>
+        <v>366.5</v>
       </c>
       <c r="C222" t="n">
-        <v>366.0899963378906</v>
+        <v>366.5</v>
       </c>
       <c r="D222" t="n">
-        <v>361.2999877929688</v>
+        <v>361.5199890136719</v>
       </c>
       <c r="E222" t="n">
-        <v>365.1799926757812</v>
+        <v>363.1099853515625</v>
       </c>
       <c r="F222" t="n">
-        <v>4366800</v>
+        <v>5102700</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B223" t="n">
-        <v>366.5</v>
+        <v>363</v>
       </c>
       <c r="C223" t="n">
-        <v>366.5</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="D223" t="n">
-        <v>361.5199890136719</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="E223" t="n">
-        <v>363.1099853515625</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="F223" t="n">
-        <v>5102700</v>
+        <v>5058600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B224" t="n">
-        <v>363</v>
+        <v>361.9400024414062</v>
       </c>
       <c r="C224" t="n">
-        <v>365.8999938964844</v>
+        <v>365.75</v>
       </c>
       <c r="D224" t="n">
-        <v>361.4500122070312</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="E224" t="n">
-        <v>362.8399963378906</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="F224" t="n">
-        <v>5058600</v>
+        <v>5282600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B225" t="n">
-        <v>361.9400024414062</v>
+        <v>362.3399963378906</v>
       </c>
       <c r="C225" t="n">
-        <v>365.75</v>
+        <v>363.5700073242188</v>
       </c>
       <c r="D225" t="n">
-        <v>360.9599914550781</v>
+        <v>359.2699890136719</v>
       </c>
       <c r="E225" t="n">
-        <v>360.9599914550781</v>
+        <v>363.25</v>
       </c>
       <c r="F225" t="n">
-        <v>5282600</v>
+        <v>5525100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B226" t="n">
-        <v>362.3399963378906</v>
+        <v>363.010009765625</v>
       </c>
       <c r="C226" t="n">
-        <v>363.5700073242188</v>
+        <v>363.0499877929688</v>
       </c>
       <c r="D226" t="n">
-        <v>359.2699890136719</v>
+        <v>355.6499938964844</v>
       </c>
       <c r="E226" t="n">
-        <v>363.25</v>
+        <v>357.260009765625</v>
       </c>
       <c r="F226" t="n">
-        <v>5525100</v>
+        <v>6696200</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B227" t="n">
-        <v>363.010009765625</v>
+        <v>357.6000061035156</v>
       </c>
       <c r="C227" t="n">
-        <v>363.0499877929688</v>
+        <v>357.9500122070312</v>
       </c>
       <c r="D227" t="n">
-        <v>355.6499938964844</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E227" t="n">
-        <v>357.260009765625</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="F227" t="n">
-        <v>6696200</v>
+        <v>6799700</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B228" t="n">
-        <v>357.6000061035156</v>
+        <v>354.0700073242188</v>
       </c>
       <c r="C228" t="n">
-        <v>357.9500122070312</v>
+        <v>356.8599853515625</v>
       </c>
       <c r="D228" t="n">
-        <v>351.5499877929688</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="E228" t="n">
-        <v>351.5499877929688</v>
+        <v>351.5799865722656</v>
       </c>
       <c r="F228" t="n">
-        <v>6799700</v>
+        <v>8112100</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B229" t="n">
-        <v>354.0700073242188</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C229" t="n">
-        <v>356.8599853515625</v>
+        <v>358.2799987792969</v>
       </c>
       <c r="D229" t="n">
-        <v>350.3699951171875</v>
+        <v>352.8200073242188</v>
       </c>
       <c r="E229" t="n">
-        <v>351.5799865722656</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="F229" t="n">
-        <v>8112100</v>
+        <v>4394400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B230" t="n">
-        <v>353.2999877929688</v>
+        <v>357</v>
       </c>
       <c r="C230" t="n">
-        <v>358.2799987792969</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D230" t="n">
-        <v>352.8200073242188</v>
+        <v>353.0700073242188</v>
       </c>
       <c r="E230" t="n">
-        <v>356.3900146484375</v>
+        <v>356.6900024414062</v>
       </c>
       <c r="F230" t="n">
-        <v>4394400</v>
+        <v>4298000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B231" t="n">
-        <v>357</v>
+        <v>356.5</v>
       </c>
       <c r="C231" t="n">
-        <v>357.3699951171875</v>
+        <v>358.3500061035156</v>
       </c>
       <c r="D231" t="n">
-        <v>353.0700073242188</v>
+        <v>354.6000061035156</v>
       </c>
       <c r="E231" t="n">
-        <v>356.6900024414062</v>
+        <v>356.5</v>
       </c>
       <c r="F231" t="n">
-        <v>4298000</v>
+        <v>5796500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B232" t="n">
-        <v>356.5</v>
+        <v>354.6799926757812</v>
       </c>
       <c r="C232" t="n">
-        <v>358.3500061035156</v>
+        <v>357.5700073242188</v>
       </c>
       <c r="D232" t="n">
-        <v>354.6000061035156</v>
+        <v>352.2300109863281</v>
       </c>
       <c r="E232" t="n">
-        <v>356.5</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="F232" t="n">
-        <v>5796500</v>
+        <v>5209900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B233" t="n">
-        <v>354.6799926757812</v>
+        <v>355.6700134277344</v>
       </c>
       <c r="C233" t="n">
-        <v>357.5700073242188</v>
+        <v>358.7300109863281</v>
       </c>
       <c r="D233" t="n">
-        <v>352.2300109863281</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="E233" t="n">
-        <v>354.2200012207031</v>
+        <v>357.6199951171875</v>
       </c>
       <c r="F233" t="n">
-        <v>5209900</v>
+        <v>3914500</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B234" t="n">
-        <v>355.6700134277344</v>
+        <v>355.8999938964844</v>
       </c>
       <c r="C234" t="n">
-        <v>358.7300109863281</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="D234" t="n">
-        <v>354.2200012207031</v>
+        <v>354.7699890136719</v>
       </c>
       <c r="E234" t="n">
-        <v>357.6199951171875</v>
+        <v>356.0199890136719</v>
       </c>
       <c r="F234" t="n">
-        <v>3914500</v>
+        <v>7962900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B235" t="n">
-        <v>355.8999938964844</v>
+        <v>355.7300109863281</v>
       </c>
       <c r="C235" t="n">
-        <v>357.7699890136719</v>
+        <v>359.9299926757812</v>
       </c>
       <c r="D235" t="n">
-        <v>354.7699890136719</v>
+        <v>354.1199951171875</v>
       </c>
       <c r="E235" t="n">
-        <v>356.0199890136719</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="F235" t="n">
-        <v>7962900</v>
+        <v>5079000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B236" t="n">
-        <v>355.7300109863281</v>
+        <v>357.5499877929688</v>
       </c>
       <c r="C236" t="n">
-        <v>359.9299926757812</v>
+        <v>361.4700012207031</v>
       </c>
       <c r="D236" t="n">
-        <v>354.1199951171875</v>
+        <v>353.7900085449219</v>
       </c>
       <c r="E236" t="n">
-        <v>354.9500122070312</v>
+        <v>356.2200012207031</v>
       </c>
       <c r="F236" t="n">
-        <v>5079000</v>
+        <v>5341400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B237" t="n">
-        <v>357.5499877929688</v>
+        <v>358.6799926757812</v>
       </c>
       <c r="C237" t="n">
-        <v>361.4700012207031</v>
+        <v>362.8500061035156</v>
       </c>
       <c r="D237" t="n">
-        <v>353.7900085449219</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="E237" t="n">
-        <v>356.2200012207031</v>
+        <v>362.0599975585938</v>
       </c>
       <c r="F237" t="n">
-        <v>5341400</v>
+        <v>5414200</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B238" t="n">
-        <v>358.6799926757812</v>
+        <v>361</v>
       </c>
       <c r="C238" t="n">
-        <v>362.8500061035156</v>
+        <v>362.8599853515625</v>
       </c>
       <c r="D238" t="n">
-        <v>356.3900146484375</v>
+        <v>355.2000122070312</v>
       </c>
       <c r="E238" t="n">
-        <v>362.0599975585938</v>
+        <v>358.6400146484375</v>
       </c>
       <c r="F238" t="n">
-        <v>5414200</v>
+        <v>4873500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B239" t="n">
-        <v>361</v>
+        <v>357.1000061035156</v>
       </c>
       <c r="C239" t="n">
-        <v>362.8599853515625</v>
+        <v>358.5499877929688</v>
       </c>
       <c r="D239" t="n">
-        <v>355.2000122070312</v>
+        <v>353.2300109863281</v>
       </c>
       <c r="E239" t="n">
-        <v>358.6400146484375</v>
+        <v>353.510009765625</v>
       </c>
       <c r="F239" t="n">
-        <v>4873500</v>
+        <v>5631400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B240" t="n">
-        <v>357.1000061035156</v>
+        <v>352</v>
       </c>
       <c r="C240" t="n">
-        <v>358.5499877929688</v>
+        <v>356.3299865722656</v>
       </c>
       <c r="D240" t="n">
-        <v>353.2300109863281</v>
+        <v>348.6900024414062</v>
       </c>
       <c r="E240" t="n">
-        <v>353.510009765625</v>
+        <v>354.7099914550781</v>
       </c>
       <c r="F240" t="n">
-        <v>5631400</v>
+        <v>6318200</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B241" t="n">
-        <v>352</v>
+        <v>353.510009765625</v>
       </c>
       <c r="C241" t="n">
-        <v>356.3299865722656</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="D241" t="n">
-        <v>348.6900024414062</v>
+        <v>351.1199951171875</v>
       </c>
       <c r="E241" t="n">
-        <v>354.7099914550781</v>
+        <v>353.5599975585938</v>
       </c>
       <c r="F241" t="n">
-        <v>6318200</v>
+        <v>4184200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B242" t="n">
-        <v>353.510009765625</v>
+        <v>358.3200073242188</v>
       </c>
       <c r="C242" t="n">
-        <v>354.2200012207031</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="D242" t="n">
-        <v>351.1199951171875</v>
+        <v>354.7900085449219</v>
       </c>
       <c r="E242" t="n">
-        <v>353.5599975585938</v>
+        <v>356.2300109863281</v>
       </c>
       <c r="F242" t="n">
-        <v>4184200</v>
+        <v>5354600</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B243" t="n">
-        <v>358.3200073242188</v>
+        <v>354.2300109863281</v>
       </c>
       <c r="C243" t="n">
-        <v>360.0499877929688</v>
+        <v>355.2799987792969</v>
       </c>
       <c r="D243" t="n">
-        <v>354.7900085449219</v>
+        <v>347.5499877929688</v>
       </c>
       <c r="E243" t="n">
-        <v>356.2300109863281</v>
+        <v>350.1300048828125</v>
       </c>
       <c r="F243" t="n">
-        <v>5354600</v>
+        <v>9609900</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B244" t="n">
-        <v>354.2300109863281</v>
+        <v>351</v>
       </c>
       <c r="C244" t="n">
-        <v>355.2799987792969</v>
+        <v>354.7000122070312</v>
       </c>
       <c r="D244" t="n">
-        <v>347.5499877929688</v>
+        <v>343.0700073242188</v>
       </c>
       <c r="E244" t="n">
-        <v>350.1300048828125</v>
+        <v>352.489990234375</v>
       </c>
       <c r="F244" t="n">
-        <v>9609900</v>
+        <v>14026500</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B245" t="n">
-        <v>351</v>
+        <v>353.3800048828125</v>
       </c>
       <c r="C245" t="n">
-        <v>354.7000122070312</v>
+        <v>355.6000061035156</v>
       </c>
       <c r="D245" t="n">
-        <v>343.0700073242188</v>
+        <v>344.6900024414062</v>
       </c>
       <c r="E245" t="n">
-        <v>352.489990234375</v>
+        <v>348.9200134277344</v>
       </c>
       <c r="F245" t="n">
-        <v>14026500</v>
+        <v>8303400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B246" t="n">
-        <v>353.3800048828125</v>
+        <v>352.25</v>
       </c>
       <c r="C246" t="n">
-        <v>355.6000061035156</v>
+        <v>353.489990234375</v>
       </c>
       <c r="D246" t="n">
-        <v>344.6900024414062</v>
+        <v>345.2699890136719</v>
       </c>
       <c r="E246" t="n">
-        <v>348.9200134277344</v>
+        <v>349.3099975585938</v>
       </c>
       <c r="F246" t="n">
-        <v>8303400</v>
+        <v>6480100</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B247" t="n">
-        <v>352.25</v>
+        <v>347.8900146484375</v>
       </c>
       <c r="C247" t="n">
-        <v>353.489990234375</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="D247" t="n">
-        <v>345.2699890136719</v>
+        <v>345.010009765625</v>
       </c>
       <c r="E247" t="n">
-        <v>349.3099975585938</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="F247" t="n">
-        <v>6480100</v>
+        <v>18312400</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B248" t="n">
-        <v>347.8900146484375</v>
+        <v>353.6700134277344</v>
       </c>
       <c r="C248" t="n">
-        <v>349.6700134277344</v>
+        <v>354.5</v>
       </c>
       <c r="D248" t="n">
-        <v>345.010009765625</v>
+        <v>350.0799865722656</v>
       </c>
       <c r="E248" t="n">
-        <v>349.6700134277344</v>
+        <v>352.0400085449219</v>
       </c>
       <c r="F248" t="n">
-        <v>18312400</v>
+        <v>6414700</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B249" t="n">
-        <v>353.6700134277344</v>
+        <v>352</v>
       </c>
       <c r="C249" t="n">
-        <v>354.5</v>
+        <v>352.1000061035156</v>
       </c>
       <c r="D249" t="n">
-        <v>350.0799865722656</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E249" t="n">
-        <v>352.0400085449219</v>
+        <v>340</v>
       </c>
       <c r="F249" t="n">
-        <v>6414700</v>
+        <v>11485600</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B250" t="n">
-        <v>352</v>
+        <v>337.6099853515625</v>
       </c>
       <c r="C250" t="n">
-        <v>352.1000061035156</v>
+        <v>341.4400024414062</v>
       </c>
       <c r="D250" t="n">
-        <v>337.2999877929688</v>
+        <v>336.9800109863281</v>
       </c>
       <c r="E250" t="n">
-        <v>340</v>
+        <v>337.5299987792969</v>
       </c>
       <c r="F250" t="n">
-        <v>11485600</v>
+        <v>7068500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B251" t="n">
-        <v>337.6099853515625</v>
+        <v>338.1199951171875</v>
       </c>
       <c r="C251" t="n">
-        <v>341.4400024414062</v>
+        <v>339.3699951171875</v>
       </c>
       <c r="D251" t="n">
-        <v>336.9800109863281</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="E251" t="n">
-        <v>337.5299987792969</v>
+        <v>338.5599975585938</v>
       </c>
       <c r="F251" t="n">
-        <v>7068500</v>
+        <v>6934300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B252" t="n">
-        <v>338.1199951171875</v>
+        <v>340.7699890136719</v>
       </c>
       <c r="C252" t="n">
-        <v>339.3699951171875</v>
+        <v>343.3099975585938</v>
       </c>
       <c r="D252" t="n">
-        <v>335.2799987792969</v>
+        <v>338.6400146484375</v>
       </c>
       <c r="E252" t="n">
-        <v>338.5599975585938</v>
+        <v>343.0599975585938</v>
       </c>
       <c r="F252" t="n">
-        <v>6934300</v>
+        <v>11460300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10017,37 +10017,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>343.06</v>
+      </c>
+      <c r="D2" t="n">
         <v>338.56</v>
       </c>
-      <c r="D2" t="n">
-        <v>337.53</v>
-      </c>
       <c r="E2" t="n">
-        <v>338.12</v>
+        <v>340.765</v>
       </c>
       <c r="F2" t="n">
-        <v>339.37</v>
+        <v>343.265</v>
       </c>
       <c r="G2" t="n">
-        <v>335.28</v>
+        <v>338.64</v>
       </c>
       <c r="H2" t="n">
-        <v>6931795</v>
+        <v>9864277</v>
       </c>
       <c r="I2" t="n">
-        <v>7898782</v>
+        <v>7691509</v>
       </c>
       <c r="J2" t="n">
-        <v>899955556352</v>
+        <v>911917383680</v>
       </c>
       <c r="K2" t="n">
-        <v>14.474562</v>
+        <v>14.704672</v>
       </c>
       <c r="L2" t="n">
-        <v>13.548909</v>
+        <v>13.728995</v>
       </c>
       <c r="M2" t="n">
-        <v>23.39</v>
+        <v>23.33</v>
       </c>
       <c r="N2" t="n">
         <v>366.5</v>
@@ -10059,7 +10059,7 @@
         <v>0.975</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R2" t="n">
         <v>0.34921002</v>
@@ -10087,7 +10087,7 @@
         <v>133.007</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.54543</v>
+        <v>2.5792627</v>
       </c>
       <c r="Z2" t="n">
         <v>0.469</v>
@@ -10099,7 +10099,7 @@
         <v>186328006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>737883521024</v>
+        <v>749845348352</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:29:10</t>
+          <t>2026-09-26 14:49:42</t>
         </is>
       </c>
     </row>

--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B2" t="n">
-        <v>308.988785738579</v>
+        <v>311.1082550854298</v>
       </c>
       <c r="C2" t="n">
-        <v>311.8441636854759</v>
+        <v>312.0404339863167</v>
       </c>
       <c r="D2" t="n">
-        <v>307.8113297451866</v>
+        <v>307.7720847183659</v>
       </c>
       <c r="E2" t="n">
-        <v>310.1270141601562</v>
+        <v>309.7639770507812</v>
       </c>
       <c r="F2" t="n">
-        <v>7258100</v>
+        <v>6462400</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B3" t="n">
-        <v>311.1082857354447</v>
+        <v>310.3134645283819</v>
       </c>
       <c r="C3" t="n">
-        <v>312.0404647281687</v>
+        <v>311.4516930034957</v>
       </c>
       <c r="D3" t="n">
-        <v>307.7721150397051</v>
+        <v>304.288708108424</v>
       </c>
       <c r="E3" t="n">
-        <v>309.7640075683594</v>
+        <v>309.5088500976562</v>
       </c>
       <c r="F3" t="n">
-        <v>6462400</v>
+        <v>11823300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B4" t="n">
-        <v>310.3134645283819</v>
+        <v>308.0762861336198</v>
       </c>
       <c r="C4" t="n">
-        <v>311.4516930034957</v>
+        <v>308.6846429587351</v>
       </c>
       <c r="D4" t="n">
-        <v>304.288708108424</v>
+        <v>301.6394301376976</v>
       </c>
       <c r="E4" t="n">
-        <v>309.5088500976562</v>
+        <v>304.8774719238281</v>
       </c>
       <c r="F4" t="n">
-        <v>11823300</v>
+        <v>9235200</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B5" t="n">
-        <v>308.0762861336198</v>
+        <v>304.1808160870063</v>
       </c>
       <c r="C5" t="n">
-        <v>308.6846429587351</v>
+        <v>304.7303016172636</v>
       </c>
       <c r="D5" t="n">
-        <v>301.6394301376976</v>
+        <v>300.393288685967</v>
       </c>
       <c r="E5" t="n">
-        <v>304.8774719238281</v>
+        <v>301.7767944335938</v>
       </c>
       <c r="F5" t="n">
-        <v>9235200</v>
+        <v>7600000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B6" t="n">
-        <v>304.1808160870063</v>
+        <v>302.7187488597389</v>
       </c>
       <c r="C6" t="n">
-        <v>304.7303016172636</v>
+        <v>305.8096119794931</v>
       </c>
       <c r="D6" t="n">
-        <v>300.393288685967</v>
+        <v>302.4243624063698</v>
       </c>
       <c r="E6" t="n">
-        <v>301.7767944335938</v>
+        <v>304.210205078125</v>
       </c>
       <c r="F6" t="n">
-        <v>7600000</v>
+        <v>6029900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,25 +599,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B7" t="n">
-        <v>302.7187488597389</v>
+        <v>305.8371035459471</v>
       </c>
       <c r="C7" t="n">
-        <v>305.8096119794931</v>
+        <v>307.3851288987199</v>
       </c>
       <c r="D7" t="n">
-        <v>302.4243624063698</v>
+        <v>300.8578215934895</v>
       </c>
       <c r="E7" t="n">
-        <v>304.210205078125</v>
+        <v>304.8511047363281</v>
       </c>
       <c r="F7" t="n">
-        <v>6029900</v>
+        <v>7214500</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -625,25 +625,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B8" t="n">
-        <v>305.8371035459471</v>
+        <v>305.0187809092415</v>
       </c>
       <c r="C8" t="n">
-        <v>307.3851288987199</v>
+        <v>305.6695438264559</v>
       </c>
       <c r="D8" t="n">
-        <v>300.8578215934895</v>
+        <v>300.4338918141804</v>
       </c>
       <c r="E8" t="n">
-        <v>304.8511047363281</v>
+        <v>303.3820190429688</v>
       </c>
       <c r="F8" t="n">
-        <v>7214500</v>
+        <v>8454200</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B9" t="n">
-        <v>305.0187809092415</v>
+        <v>303.8946917756213</v>
       </c>
       <c r="C9" t="n">
-        <v>305.6695438264559</v>
+        <v>304.4567183318842</v>
       </c>
       <c r="D9" t="n">
-        <v>300.4338918141804</v>
+        <v>299.2999336047902</v>
       </c>
       <c r="E9" t="n">
-        <v>303.3820190429688</v>
+        <v>299.7732238769531</v>
       </c>
       <c r="F9" t="n">
-        <v>8454200</v>
+        <v>6489900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B10" t="n">
-        <v>303.8946608384686</v>
+        <v>300.7789070325195</v>
       </c>
       <c r="C10" t="n">
-        <v>304.4566873375159</v>
+        <v>303.7270637601551</v>
       </c>
       <c r="D10" t="n">
-        <v>299.2999031353941</v>
+        <v>299.1421755849041</v>
       </c>
       <c r="E10" t="n">
-        <v>299.773193359375</v>
+        <v>301.252197265625</v>
       </c>
       <c r="F10" t="n">
-        <v>6489900</v>
+        <v>7060300</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B11" t="n">
-        <v>300.7789375021521</v>
+        <v>301.3804193716138</v>
       </c>
       <c r="C11" t="n">
-        <v>303.7270945284432</v>
+        <v>306.1230715472904</v>
       </c>
       <c r="D11" t="n">
-        <v>299.1422058887319</v>
+        <v>296.5983188157025</v>
       </c>
       <c r="E11" t="n">
-        <v>301.2522277832031</v>
+        <v>296.6772155761719</v>
       </c>
       <c r="F11" t="n">
-        <v>7060300</v>
+        <v>8597400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B12" t="n">
-        <v>301.3803883702425</v>
+        <v>301.3212684867699</v>
       </c>
       <c r="C12" t="n">
-        <v>306.1230400580682</v>
+        <v>305.1272097801061</v>
       </c>
       <c r="D12" t="n">
-        <v>296.59828830624</v>
+        <v>301.1733746705027</v>
       </c>
       <c r="E12" t="n">
-        <v>296.6771850585938</v>
+        <v>303.6580810546875</v>
       </c>
       <c r="F12" t="n">
-        <v>8597400</v>
+        <v>10788700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B13" t="n">
-        <v>301.3212684867699</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C13" t="n">
-        <v>305.1272097801061</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D13" t="n">
-        <v>301.1733746705027</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E13" t="n">
-        <v>303.6580810546875</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F13" t="n">
-        <v>10788700</v>
+        <v>16178800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B14" t="n">
-        <v>301.5578902761218</v>
+        <v>302.1002149225357</v>
       </c>
       <c r="C14" t="n">
-        <v>302.7016525742085</v>
+        <v>307.7499693151439</v>
       </c>
       <c r="D14" t="n">
-        <v>290.0907186231138</v>
+        <v>301.1635039391426</v>
       </c>
       <c r="E14" t="n">
-        <v>297.8505249023438</v>
+        <v>301.4100036621094</v>
       </c>
       <c r="F14" t="n">
-        <v>16178800</v>
+        <v>11354800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B15" t="n">
-        <v>302.1002149225357</v>
+        <v>301.0747260223031</v>
       </c>
       <c r="C15" t="n">
-        <v>307.7499693151439</v>
+        <v>304.358088638523</v>
       </c>
       <c r="D15" t="n">
-        <v>301.1635039391426</v>
+        <v>292.9106575300408</v>
       </c>
       <c r="E15" t="n">
-        <v>301.4100036621094</v>
+        <v>294.3600769042969</v>
       </c>
       <c r="F15" t="n">
-        <v>11354800</v>
+        <v>10549400</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B16" t="n">
-        <v>301.0747260223031</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C16" t="n">
-        <v>304.358088638523</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D16" t="n">
-        <v>292.9106575300408</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E16" t="n">
-        <v>294.3600769042969</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F16" t="n">
-        <v>10549400</v>
+        <v>10153500</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B17" t="n">
-        <v>294.9714335987563</v>
+        <v>294.3206459359216</v>
       </c>
       <c r="C17" t="n">
-        <v>295.3559575215809</v>
+        <v>299.4379821870563</v>
       </c>
       <c r="D17" t="n">
-        <v>290.0808874955599</v>
+        <v>293.9854099500461</v>
       </c>
       <c r="E17" t="n">
-        <v>293.3938293457031</v>
+        <v>298.1265869140625</v>
       </c>
       <c r="F17" t="n">
-        <v>10153500</v>
+        <v>6894900</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B18" t="n">
-        <v>294.3206459359216</v>
+        <v>297.4363803014411</v>
       </c>
       <c r="C18" t="n">
-        <v>299.4379821870563</v>
+        <v>299.7929016175946</v>
       </c>
       <c r="D18" t="n">
-        <v>293.9854099500461</v>
+        <v>292.841622611914</v>
       </c>
       <c r="E18" t="n">
-        <v>298.1265869140625</v>
+        <v>292.9303588867188</v>
       </c>
       <c r="F18" t="n">
-        <v>6894900</v>
+        <v>7372700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B19" t="n">
-        <v>297.4363803014411</v>
+        <v>293.6008861047978</v>
       </c>
       <c r="C19" t="n">
-        <v>299.7929016175946</v>
+        <v>293.8868342154489</v>
       </c>
       <c r="D19" t="n">
-        <v>292.841622611914</v>
+        <v>286.4721332067081</v>
       </c>
       <c r="E19" t="n">
-        <v>292.9303588867188</v>
+        <v>289.9921264648438</v>
       </c>
       <c r="F19" t="n">
-        <v>7372700</v>
+        <v>8054100</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B20" t="n">
-        <v>293.6008861047978</v>
+        <v>290.2583437522712</v>
       </c>
       <c r="C20" t="n">
-        <v>293.8868342154489</v>
+        <v>292.2204718178062</v>
       </c>
       <c r="D20" t="n">
-        <v>286.4721332067081</v>
+        <v>288.4145307332595</v>
       </c>
       <c r="E20" t="n">
-        <v>289.9921264648438</v>
+        <v>290.4161071777344</v>
       </c>
       <c r="F20" t="n">
-        <v>8054100</v>
+        <v>5438800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B21" t="n">
-        <v>290.2583742532713</v>
+        <v>291.9345194575729</v>
       </c>
       <c r="C21" t="n">
-        <v>292.220502524991</v>
+        <v>298.3632510673837</v>
       </c>
       <c r="D21" t="n">
-        <v>288.4145610405075</v>
+        <v>291.3133654724136</v>
       </c>
       <c r="E21" t="n">
-        <v>290.4161376953125</v>
+        <v>296.2334899902344</v>
       </c>
       <c r="F21" t="n">
-        <v>5438800</v>
+        <v>7228300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B22" t="n">
-        <v>291.9345194575729</v>
+        <v>297.92941246883</v>
       </c>
       <c r="C22" t="n">
-        <v>298.3632510673837</v>
+        <v>300.2662249001909</v>
       </c>
       <c r="D22" t="n">
-        <v>291.3133654724136</v>
+        <v>296.7955198233114</v>
       </c>
       <c r="E22" t="n">
-        <v>296.2334899902344</v>
+        <v>299.8915405273438</v>
       </c>
       <c r="F22" t="n">
-        <v>7228300</v>
+        <v>5642200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B23" t="n">
-        <v>297.92941246883</v>
+        <v>300.5915953010157</v>
       </c>
       <c r="C23" t="n">
-        <v>300.2662249001909</v>
+        <v>303.6580673748709</v>
       </c>
       <c r="D23" t="n">
-        <v>296.7955198233114</v>
+        <v>298.915415308335</v>
       </c>
       <c r="E23" t="n">
-        <v>299.8915405273438</v>
+        <v>301.0845947265625</v>
       </c>
       <c r="F23" t="n">
-        <v>5642200</v>
+        <v>6336000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B24" t="n">
-        <v>300.5916257686241</v>
+        <v>299.2605157595805</v>
       </c>
       <c r="C24" t="n">
-        <v>303.6580981532932</v>
+        <v>303.9341406042103</v>
       </c>
       <c r="D24" t="n">
-        <v>298.9154456060477</v>
+        <v>298.7675163425421</v>
       </c>
       <c r="E24" t="n">
-        <v>301.0846252441406</v>
+        <v>301.2325134277344</v>
       </c>
       <c r="F24" t="n">
-        <v>6336000</v>
+        <v>7520300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B25" t="n">
-        <v>299.2605460773775</v>
+        <v>301.5086233262724</v>
       </c>
       <c r="C25" t="n">
-        <v>303.9341713954877</v>
+        <v>308.233113206998</v>
       </c>
       <c r="D25" t="n">
-        <v>298.7675466103937</v>
+        <v>300.8282816526182</v>
       </c>
       <c r="E25" t="n">
-        <v>301.2325439453125</v>
+        <v>305.1075134277344</v>
       </c>
       <c r="F25" t="n">
-        <v>7520300</v>
+        <v>7514600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B26" t="n">
-        <v>301.5085931686638</v>
+        <v>304.220113094536</v>
       </c>
       <c r="C26" t="n">
-        <v>308.2330823767899</v>
+        <v>308.4894751488275</v>
       </c>
       <c r="D26" t="n">
-        <v>300.828251563059</v>
+        <v>302.9481660712639</v>
       </c>
       <c r="E26" t="n">
-        <v>305.1074829101562</v>
+        <v>306.7639770507812</v>
       </c>
       <c r="F26" t="n">
-        <v>7514600</v>
+        <v>7721300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B27" t="n">
-        <v>304.2200828300273</v>
+        <v>306.6456604912348</v>
       </c>
       <c r="C27" t="n">
-        <v>308.4894444595929</v>
+        <v>307.9471862719047</v>
       </c>
       <c r="D27" t="n">
-        <v>302.9481359332913</v>
+        <v>301.9227172950412</v>
       </c>
       <c r="E27" t="n">
-        <v>306.7639465332031</v>
+        <v>305.0187683105469</v>
       </c>
       <c r="F27" t="n">
-        <v>7721300</v>
+        <v>7770000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B28" t="n">
-        <v>306.6456604912348</v>
+        <v>302.415720333495</v>
       </c>
       <c r="C28" t="n">
-        <v>307.9471862719047</v>
+        <v>307.8485840116909</v>
       </c>
       <c r="D28" t="n">
-        <v>301.9227172950412</v>
+        <v>300.8282765156093</v>
       </c>
       <c r="E28" t="n">
-        <v>305.0187683105469</v>
+        <v>304.920166015625</v>
       </c>
       <c r="F28" t="n">
-        <v>7770000</v>
+        <v>7085200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B29" t="n">
-        <v>302.415720333495</v>
+        <v>305.2750763211935</v>
       </c>
       <c r="C29" t="n">
-        <v>307.8485840116909</v>
+        <v>308.7162326204817</v>
       </c>
       <c r="D29" t="n">
-        <v>300.8282765156093</v>
+        <v>301.350820325461</v>
       </c>
       <c r="E29" t="n">
-        <v>304.920166015625</v>
+        <v>307.3161010742188</v>
       </c>
       <c r="F29" t="n">
-        <v>7085200</v>
+        <v>6865200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B30" t="n">
-        <v>305.2751066360906</v>
+        <v>306.6357990367445</v>
       </c>
       <c r="C30" t="n">
-        <v>308.7162632770978</v>
+        <v>310.4319009529449</v>
       </c>
       <c r="D30" t="n">
-        <v>301.3508502506656</v>
+        <v>305.9160390722913</v>
       </c>
       <c r="E30" t="n">
-        <v>307.3161315917969</v>
+        <v>309.0317993164062</v>
       </c>
       <c r="F30" t="n">
-        <v>6865200</v>
+        <v>7206100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B31" t="n">
-        <v>306.6357990367445</v>
+        <v>307.5231746391179</v>
       </c>
       <c r="C31" t="n">
-        <v>310.4319009529449</v>
+        <v>310.0275898810191</v>
       </c>
       <c r="D31" t="n">
-        <v>305.9160390722913</v>
+        <v>303.3326798145578</v>
       </c>
       <c r="E31" t="n">
-        <v>309.0317993164062</v>
+        <v>309.8106689453125</v>
       </c>
       <c r="F31" t="n">
-        <v>7206100</v>
+        <v>7302300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B32" t="n">
-        <v>307.5232049313688</v>
+        <v>310.5896641246428</v>
       </c>
       <c r="C32" t="n">
-        <v>310.0276204199649</v>
+        <v>315.0858168552232</v>
       </c>
       <c r="D32" t="n">
-        <v>303.3327096940284</v>
+        <v>309.810716541713</v>
       </c>
       <c r="E32" t="n">
-        <v>309.8106994628906</v>
+        <v>312.4532165527344</v>
       </c>
       <c r="F32" t="n">
-        <v>7302300</v>
+        <v>5794100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B33" t="n">
-        <v>310.5896641246428</v>
+        <v>313.054640940315</v>
       </c>
       <c r="C33" t="n">
-        <v>315.0858168552232</v>
+        <v>314.5829271513063</v>
       </c>
       <c r="D33" t="n">
-        <v>309.810716541713</v>
+        <v>310.8657222472937</v>
       </c>
       <c r="E33" t="n">
-        <v>312.4532165527344</v>
+        <v>311.2009582519531</v>
       </c>
       <c r="F33" t="n">
-        <v>5794100</v>
+        <v>5030200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B34" t="n">
-        <v>313.054640940315</v>
+        <v>311.8320301504691</v>
       </c>
       <c r="C34" t="n">
-        <v>314.5829271513063</v>
+        <v>317.7381540918137</v>
       </c>
       <c r="D34" t="n">
-        <v>310.8657222472937</v>
+        <v>311.7827121499603</v>
       </c>
       <c r="E34" t="n">
-        <v>311.2009582519531</v>
+        <v>315.9239196777344</v>
       </c>
       <c r="F34" t="n">
-        <v>5030200</v>
+        <v>10578300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B35" t="n">
-        <v>311.8320000281587</v>
+        <v>314.7604311532612</v>
       </c>
       <c r="C35" t="n">
-        <v>317.7381233989844</v>
+        <v>316.1408235578094</v>
       </c>
       <c r="D35" t="n">
-        <v>311.782682032414</v>
+        <v>304.7722577523736</v>
       </c>
       <c r="E35" t="n">
-        <v>315.9238891601562</v>
+        <v>305.1469421386719</v>
       </c>
       <c r="F35" t="n">
-        <v>10578300</v>
+        <v>8973300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B36" t="n">
-        <v>314.7604311532612</v>
+        <v>303.2045199796025</v>
       </c>
       <c r="C36" t="n">
-        <v>316.1408235578094</v>
+        <v>303.3327046462357</v>
       </c>
       <c r="D36" t="n">
-        <v>304.7722577523736</v>
+        <v>297.0124483237873</v>
       </c>
       <c r="E36" t="n">
-        <v>305.1469421386719</v>
+        <v>299.3591003417969</v>
       </c>
       <c r="F36" t="n">
-        <v>8973300</v>
+        <v>10327000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B37" t="n">
-        <v>303.2045199796025</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C37" t="n">
-        <v>303.3327046462357</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D37" t="n">
-        <v>297.0124483237873</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E37" t="n">
-        <v>299.3591003417969</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F37" t="n">
-        <v>10327000</v>
+        <v>8344000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B38" t="n">
-        <v>299.7436397411884</v>
+        <v>295.3066317863286</v>
       </c>
       <c r="C38" t="n">
-        <v>301.3113742461044</v>
+        <v>298.70833958092</v>
       </c>
       <c r="D38" t="n">
-        <v>293.5022804823602</v>
+        <v>292.8613440028039</v>
       </c>
       <c r="E38" t="n">
-        <v>296.1644592285156</v>
+        <v>295.2178955078125</v>
       </c>
       <c r="F38" t="n">
-        <v>8344000</v>
+        <v>8077300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B39" t="n">
-        <v>295.3066623130797</v>
+        <v>295.5432899586994</v>
       </c>
       <c r="C39" t="n">
-        <v>298.708370459316</v>
+        <v>300.1873662746028</v>
       </c>
       <c r="D39" t="n">
-        <v>292.8613742767781</v>
+        <v>295.0798692888629</v>
       </c>
       <c r="E39" t="n">
-        <v>295.2179260253906</v>
+        <v>299.0238647460938</v>
       </c>
       <c r="F39" t="n">
-        <v>8077300</v>
+        <v>5546600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B40" t="n">
-        <v>295.5432899586994</v>
+        <v>302.0508736933244</v>
       </c>
       <c r="C40" t="n">
-        <v>300.1873662746028</v>
+        <v>305.5807663052954</v>
       </c>
       <c r="D40" t="n">
-        <v>295.0798692888629</v>
+        <v>293.9854105998292</v>
       </c>
       <c r="E40" t="n">
-        <v>299.0238647460938</v>
+        <v>294.2023315429688</v>
       </c>
       <c r="F40" t="n">
-        <v>5546600</v>
+        <v>7501600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B41" t="n">
-        <v>302.0509050250311</v>
+        <v>297.0715864028587</v>
       </c>
       <c r="C41" t="n">
-        <v>305.5807980031574</v>
+        <v>297.456110287291</v>
       </c>
       <c r="D41" t="n">
-        <v>293.9854410949062</v>
+        <v>288.7103057597054</v>
       </c>
       <c r="E41" t="n">
-        <v>294.2023620605469</v>
+        <v>293.8473510742188</v>
       </c>
       <c r="F41" t="n">
-        <v>7501600</v>
+        <v>11766800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B42" t="n">
-        <v>297.0715864028587</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C42" t="n">
-        <v>297.456110287291</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D42" t="n">
-        <v>288.7103057597054</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E42" t="n">
-        <v>293.8473510742188</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F42" t="n">
-        <v>11766800</v>
+        <v>10940200</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B43" t="n">
-        <v>294.0642973394352</v>
+        <v>295.8489209666184</v>
       </c>
       <c r="C43" t="n">
-        <v>295.6221924256846</v>
+        <v>300.2366275598507</v>
       </c>
       <c r="D43" t="n">
-        <v>290.386540762355</v>
+        <v>291.4217960873232</v>
       </c>
       <c r="E43" t="n">
-        <v>293.8276672363281</v>
+        <v>298.7576293945312</v>
       </c>
       <c r="F43" t="n">
-        <v>10940200</v>
+        <v>8877200</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B44" t="n">
-        <v>295.8489209666184</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C44" t="n">
-        <v>300.2366275598507</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D44" t="n">
-        <v>291.4217960873232</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E44" t="n">
-        <v>298.7576293945312</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F44" t="n">
-        <v>8877200</v>
+        <v>7910900</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B45" t="n">
-        <v>300.7296512123902</v>
+        <v>304.7722767012305</v>
       </c>
       <c r="C45" t="n">
-        <v>304.2102259719906</v>
+        <v>309.3275869646093</v>
       </c>
       <c r="D45" t="n">
-        <v>298.9548653069277</v>
+        <v>303.9243019705234</v>
       </c>
       <c r="E45" t="n">
-        <v>303.3327026367188</v>
+        <v>308.696533203125</v>
       </c>
       <c r="F45" t="n">
-        <v>7910900</v>
+        <v>4322400</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B46" t="n">
-        <v>304.7722767012305</v>
+        <v>308.5683618849884</v>
       </c>
       <c r="C46" t="n">
-        <v>309.3275869646093</v>
+        <v>309.6430970545817</v>
       </c>
       <c r="D46" t="n">
-        <v>303.9243019705234</v>
+        <v>304.2201032083801</v>
       </c>
       <c r="E46" t="n">
-        <v>308.696533203125</v>
+        <v>304.5947875976562</v>
       </c>
       <c r="F46" t="n">
-        <v>4322400</v>
+        <v>7727300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B47" t="n">
-        <v>308.5683928006819</v>
+        <v>304.4172805196406</v>
       </c>
       <c r="C47" t="n">
-        <v>309.6431280779537</v>
+        <v>306.1329390093465</v>
       </c>
       <c r="D47" t="n">
-        <v>304.2201336884183</v>
+        <v>302.7903884074122</v>
       </c>
       <c r="E47" t="n">
-        <v>304.5948181152344</v>
+        <v>303.5693359375</v>
       </c>
       <c r="F47" t="n">
-        <v>7727300</v>
+        <v>7249000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B48" t="n">
-        <v>304.4172805196406</v>
+        <v>302.8988595387675</v>
       </c>
       <c r="C48" t="n">
-        <v>306.1329390093465</v>
+        <v>307.9865871384521</v>
       </c>
       <c r="D48" t="n">
-        <v>302.7903884074122</v>
+        <v>302.5044359255107</v>
       </c>
       <c r="E48" t="n">
-        <v>303.5693359375</v>
+        <v>307.7598266601562</v>
       </c>
       <c r="F48" t="n">
-        <v>7249000</v>
+        <v>8535300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B49" t="n">
-        <v>302.8988595387675</v>
+        <v>308.8740221323167</v>
       </c>
       <c r="C49" t="n">
-        <v>307.9865871384521</v>
+        <v>314.0307770729326</v>
       </c>
       <c r="D49" t="n">
-        <v>302.5044359255107</v>
+        <v>308.617652791837</v>
       </c>
       <c r="E49" t="n">
-        <v>307.7598266601562</v>
+        <v>311.6742553710938</v>
       </c>
       <c r="F49" t="n">
-        <v>8535300</v>
+        <v>9627800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B50" t="n">
-        <v>308.8740221323167</v>
+        <v>311.2206946896725</v>
       </c>
       <c r="C50" t="n">
-        <v>314.0307770729326</v>
+        <v>314.0209278419201</v>
       </c>
       <c r="D50" t="n">
-        <v>308.617652791837</v>
+        <v>310.2741141188276</v>
       </c>
       <c r="E50" t="n">
-        <v>311.6742553710938</v>
+        <v>310.6290893554688</v>
       </c>
       <c r="F50" t="n">
-        <v>9627800</v>
+        <v>6518900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B51" t="n">
-        <v>311.2207252653726</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C51" t="n">
-        <v>314.0209586927274</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D51" t="n">
-        <v>310.2741446015314</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E51" t="n">
-        <v>310.6291198730469</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F51" t="n">
-        <v>6518900</v>
+        <v>7417200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B52" t="n">
-        <v>310.6487980837529</v>
+        <v>310.5403463950657</v>
       </c>
       <c r="C52" t="n">
-        <v>312.0390600856641</v>
+        <v>314.3364178531727</v>
       </c>
       <c r="D52" t="n">
-        <v>308.9627484602848</v>
+        <v>295.8193608594167</v>
       </c>
       <c r="E52" t="n">
-        <v>310.7966918945312</v>
+        <v>296.3025207519531</v>
       </c>
       <c r="F52" t="n">
-        <v>7417200</v>
+        <v>18049200</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B53" t="n">
-        <v>310.5403783790639</v>
+        <v>296.2926621709551</v>
       </c>
       <c r="C53" t="n">
-        <v>314.336450228146</v>
+        <v>306.8329925602339</v>
       </c>
       <c r="D53" t="n">
-        <v>295.8193913272319</v>
+        <v>294.2812160390869</v>
       </c>
       <c r="E53" t="n">
-        <v>296.3025512695312</v>
+        <v>305.7680969238281</v>
       </c>
       <c r="F53" t="n">
-        <v>18049200</v>
+        <v>18874100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B54" t="n">
-        <v>296.292632599085</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C54" t="n">
-        <v>306.8329619363725</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D54" t="n">
-        <v>294.2811866679717</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E54" t="n">
-        <v>305.76806640625</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F54" t="n">
-        <v>18874100</v>
+        <v>9721900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B55" t="n">
-        <v>304.9102649889192</v>
+        <v>315.2040954937631</v>
       </c>
       <c r="C55" t="n">
-        <v>313.5476242674454</v>
+        <v>315.7858311866128</v>
       </c>
       <c r="D55" t="n">
-        <v>304.9102649889192</v>
+        <v>312.1672323684923</v>
       </c>
       <c r="E55" t="n">
-        <v>312.9363098144531</v>
+        <v>314.0603332519531</v>
       </c>
       <c r="F55" t="n">
-        <v>9721900</v>
+        <v>8982900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B56" t="n">
-        <v>315.2040954937631</v>
+        <v>315.115395356304</v>
       </c>
       <c r="C56" t="n">
-        <v>315.7858311866128</v>
+        <v>318.3593402708456</v>
       </c>
       <c r="D56" t="n">
-        <v>312.1672323684923</v>
+        <v>313.9322146909975</v>
       </c>
       <c r="E56" t="n">
-        <v>314.0603332519531</v>
+        <v>315.5393676757812</v>
       </c>
       <c r="F56" t="n">
-        <v>8982900</v>
+        <v>10864100</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B57" t="n">
-        <v>315.115395356304</v>
+        <v>314.6223410116007</v>
       </c>
       <c r="C57" t="n">
-        <v>318.3593402708456</v>
+        <v>315.0463132571263</v>
       </c>
       <c r="D57" t="n">
-        <v>313.9322146909975</v>
+        <v>309.9980044156554</v>
       </c>
       <c r="E57" t="n">
-        <v>315.5393676757812</v>
+        <v>311.1318969726562</v>
       </c>
       <c r="F57" t="n">
-        <v>10864100</v>
+        <v>8331300</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B58" t="n">
-        <v>314.6223718715413</v>
+        <v>313.9716244610726</v>
       </c>
       <c r="C58" t="n">
-        <v>315.0463441586525</v>
+        <v>314.8984658400699</v>
       </c>
       <c r="D58" t="n">
-        <v>309.9980348220149</v>
+        <v>310.2544194174254</v>
       </c>
       <c r="E58" t="n">
-        <v>311.1319274902344</v>
+        <v>310.5699462890625</v>
       </c>
       <c r="F58" t="n">
-        <v>8331300</v>
+        <v>8718700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B59" t="n">
-        <v>313.9716244610726</v>
+        <v>311.5756418636432</v>
       </c>
       <c r="C59" t="n">
-        <v>314.8984658400699</v>
+        <v>313.2518519730792</v>
       </c>
       <c r="D59" t="n">
-        <v>310.2544194174254</v>
+        <v>307.8485673512913</v>
       </c>
       <c r="E59" t="n">
-        <v>310.5699462890625</v>
+        <v>308.6176452636719</v>
       </c>
       <c r="F59" t="n">
-        <v>8718700</v>
+        <v>11444900</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B60" t="n">
-        <v>311.5756418636432</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C60" t="n">
-        <v>313.2518519730792</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D60" t="n">
-        <v>307.8485673512913</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E60" t="n">
-        <v>308.6176452636719</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F60" t="n">
-        <v>11444900</v>
+        <v>24494400</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B61" t="n">
-        <v>309.3965776494671</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="C61" t="n">
-        <v>314.099781180705</v>
+        <v>318.7043994886834</v>
       </c>
       <c r="D61" t="n">
-        <v>308.8049723403709</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="E61" t="n">
-        <v>312.7686767578125</v>
+        <v>318.5663452148438</v>
       </c>
       <c r="F61" t="n">
-        <v>24494400</v>
+        <v>8354600</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B62" t="n">
-        <v>313.0644852104395</v>
+        <v>319.0790830432475</v>
       </c>
       <c r="C62" t="n">
-        <v>318.7043994886834</v>
+        <v>323.1907116116738</v>
       </c>
       <c r="D62" t="n">
-        <v>313.0644852104395</v>
+        <v>318.5663744582675</v>
       </c>
       <c r="E62" t="n">
-        <v>318.5663452148438</v>
+        <v>321.3666076660156</v>
       </c>
       <c r="F62" t="n">
-        <v>8354600</v>
+        <v>6668300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B63" t="n">
-        <v>319.0790830432475</v>
+        <v>321.6722493328215</v>
       </c>
       <c r="C63" t="n">
-        <v>323.1907116116738</v>
+        <v>325.3697449529369</v>
       </c>
       <c r="D63" t="n">
-        <v>318.5663744582675</v>
+        <v>320.9426198260136</v>
       </c>
       <c r="E63" t="n">
-        <v>321.3666076660156</v>
+        <v>324.5612487792969</v>
       </c>
       <c r="F63" t="n">
-        <v>6668300</v>
+        <v>4289300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B64" t="n">
-        <v>321.6722493328215</v>
+        <v>324.502058709128</v>
       </c>
       <c r="C64" t="n">
-        <v>325.3697449529369</v>
+        <v>326.2275566521161</v>
       </c>
       <c r="D64" t="n">
-        <v>320.9426198260136</v>
+        <v>321.9680645986219</v>
       </c>
       <c r="E64" t="n">
-        <v>324.5612487792969</v>
+        <v>323.3188781738281</v>
       </c>
       <c r="F64" t="n">
-        <v>4289300</v>
+        <v>4158300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B65" t="n">
-        <v>324.5020893383847</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C65" t="n">
-        <v>326.22758744424</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D65" t="n">
-        <v>321.9680949886989</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E65" t="n">
-        <v>323.3189086914062</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F65" t="n">
-        <v>4158300</v>
+        <v>8635300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B66" t="n">
-        <v>322.4216288798564</v>
+        <v>320.2622768741799</v>
       </c>
       <c r="C66" t="n">
-        <v>323.1808371734579</v>
+        <v>320.3904615362508</v>
       </c>
       <c r="D66" t="n">
-        <v>319.0002116144308</v>
+        <v>317.9747523718436</v>
       </c>
       <c r="E66" t="n">
-        <v>319.2171325683594</v>
+        <v>318.8917541503906</v>
       </c>
       <c r="F66" t="n">
-        <v>8635300</v>
+        <v>7904300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B67" t="n">
-        <v>320.2622768741799</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C67" t="n">
-        <v>320.3904615362508</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D67" t="n">
-        <v>317.9747523718436</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E67" t="n">
-        <v>318.8917541503906</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F67" t="n">
-        <v>7904300</v>
+        <v>5048500</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B68" t="n">
-        <v>319.7988699190817</v>
+        <v>317.9846554663246</v>
       </c>
       <c r="C68" t="n">
-        <v>320.3313177342217</v>
+        <v>321.169442848154</v>
       </c>
       <c r="D68" t="n">
-        <v>317.5310845539587</v>
+        <v>316.2492877176746</v>
       </c>
       <c r="E68" t="n">
-        <v>317.7085571289062</v>
+        <v>320.9229431152344</v>
       </c>
       <c r="F68" t="n">
-        <v>5048500</v>
+        <v>8054000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B69" t="n">
-        <v>317.9846252281575</v>
+        <v>320.942628937084</v>
       </c>
       <c r="C69" t="n">
-        <v>321.1694123071354</v>
+        <v>332.5281155423397</v>
       </c>
       <c r="D69" t="n">
-        <v>316.2492576445291</v>
+        <v>320.636971697701</v>
       </c>
       <c r="E69" t="n">
-        <v>320.9229125976562</v>
+        <v>329.3630676269531</v>
       </c>
       <c r="F69" t="n">
-        <v>8054000</v>
+        <v>10752600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,25 +2237,25 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B70" t="n">
-        <v>320.942628937084</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C70" t="n">
-        <v>332.5281155423397</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D70" t="n">
-        <v>320.636971697701</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E70" t="n">
-        <v>329.3630676269531</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F70" t="n">
-        <v>10752600</v>
+        <v>7660800</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2263,25 +2263,25 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B71" t="n">
-        <v>329.4422902981328</v>
+        <v>327.9764659913386</v>
       </c>
       <c r="C71" t="n">
-        <v>332.6612412306879</v>
+        <v>328.9767963949314</v>
       </c>
       <c r="D71" t="n">
-        <v>327.491109600743</v>
+        <v>321.4989374679619</v>
       </c>
       <c r="E71" t="n">
-        <v>331.4132690429688</v>
+        <v>323.8660888671875</v>
       </c>
       <c r="F71" t="n">
-        <v>7660800</v>
+        <v>9815200</v>
       </c>
       <c r="G71" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B72" t="n">
-        <v>327.9764659913386</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C72" t="n">
-        <v>328.9767963949314</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D72" t="n">
-        <v>321.4989374679619</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E72" t="n">
-        <v>323.8660888671875</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F72" t="n">
-        <v>9815200</v>
+        <v>11737100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B73" t="n">
-        <v>323.2718313763784</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C73" t="n">
-        <v>328.2339475379842</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D73" t="n">
-        <v>322.5388804495614</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E73" t="n">
-        <v>326.6393432617188</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F73" t="n">
-        <v>11737100</v>
+        <v>6738100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B74" t="n">
-        <v>326.1936353875406</v>
+        <v>318.8049029297019</v>
       </c>
       <c r="C74" t="n">
-        <v>328.7291759216584</v>
+        <v>322.9053354478686</v>
       </c>
       <c r="D74" t="n">
-        <v>325.0348299492433</v>
+        <v>318.1611187929736</v>
       </c>
       <c r="E74" t="n">
-        <v>326.0450744628906</v>
+        <v>321.3899536132812</v>
       </c>
       <c r="F74" t="n">
-        <v>6738100</v>
+        <v>12805100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B75" t="n">
-        <v>318.8049029297019</v>
+        <v>321.2017547389941</v>
       </c>
       <c r="C75" t="n">
-        <v>322.9053354478686</v>
+        <v>323.7372950994605</v>
       </c>
       <c r="D75" t="n">
-        <v>318.1611187929736</v>
+        <v>307.6029450408882</v>
       </c>
       <c r="E75" t="n">
-        <v>321.3899536132812</v>
+        <v>307.9297790527344</v>
       </c>
       <c r="F75" t="n">
-        <v>12805100</v>
+        <v>19371200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B76" t="n">
-        <v>321.2017547389941</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C76" t="n">
-        <v>323.7372950994605</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D76" t="n">
-        <v>307.6029450408882</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E76" t="n">
-        <v>307.9297790527344</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F76" t="n">
-        <v>19371200</v>
+        <v>25951500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B77" t="n">
-        <v>305.2556057077196</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C77" t="n">
-        <v>308.7815926253858</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D77" t="n">
-        <v>303.1954601804828</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E77" t="n">
-        <v>304.9287414550781</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F77" t="n">
-        <v>25951500</v>
+        <v>14751400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B78" t="n">
-        <v>305.5230197927318</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C78" t="n">
-        <v>309.95031666446</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D78" t="n">
-        <v>304.8098971346673</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E78" t="n">
-        <v>306.3054809570312</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F78" t="n">
-        <v>14751400</v>
+        <v>14652500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B79" t="n">
-        <v>307.385060616362</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C79" t="n">
-        <v>314.1795087286461</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D79" t="n">
-        <v>307.0383983149945</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E79" t="n">
-        <v>309.4848022460938</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F79" t="n">
-        <v>14652500</v>
+        <v>12900600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B80" t="n">
-        <v>303.2845981841295</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C80" t="n">
-        <v>308.1774060521912</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D80" t="n">
-        <v>298.9761500928895</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E80" t="n">
-        <v>299.8477478027344</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F80" t="n">
-        <v>12900600</v>
+        <v>10270100</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B81" t="n">
-        <v>300.5311849469782</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C81" t="n">
-        <v>302.4823658305288</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D81" t="n">
-        <v>298.2729680555718</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E81" t="n">
-        <v>299.1544799804688</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F81" t="n">
-        <v>10270100</v>
+        <v>10535800</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B82" t="n">
-        <v>301.9474777854751</v>
+        <v>299.1148112655088</v>
       </c>
       <c r="C82" t="n">
-        <v>305.2555953909441</v>
+        <v>299.4812715954647</v>
       </c>
       <c r="D82" t="n">
-        <v>300.0062112868251</v>
+        <v>293.6772702297321</v>
       </c>
       <c r="E82" t="n">
-        <v>300.729248046875</v>
+        <v>294.8757019042969</v>
       </c>
       <c r="F82" t="n">
-        <v>10535800</v>
+        <v>11107900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B83" t="n">
-        <v>299.1148112655088</v>
+        <v>294.9648486176391</v>
       </c>
       <c r="C83" t="n">
-        <v>299.4812715954647</v>
+        <v>298.8969221500132</v>
       </c>
       <c r="D83" t="n">
-        <v>293.6772702297321</v>
+        <v>294.6083024116733</v>
       </c>
       <c r="E83" t="n">
-        <v>294.8757019042969</v>
+        <v>298.1640014648438</v>
       </c>
       <c r="F83" t="n">
-        <v>11107900</v>
+        <v>11752700</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B84" t="n">
-        <v>294.9648486176391</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C84" t="n">
-        <v>298.8969221500132</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D84" t="n">
-        <v>294.6083024116733</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E84" t="n">
-        <v>298.1640014648438</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F84" t="n">
-        <v>11752700</v>
+        <v>11527400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B85" t="n">
-        <v>298.4512235287846</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C85" t="n">
-        <v>299.0851237823749</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D85" t="n">
-        <v>295.3016109870806</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E85" t="n">
-        <v>297.4409790039062</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F85" t="n">
-        <v>11527400</v>
+        <v>9556700</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B86" t="n">
-        <v>297.4013222225187</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C86" t="n">
-        <v>299.0355829225425</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D86" t="n">
-        <v>295.2025300603667</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E86" t="n">
-        <v>297.8965454101562</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F86" t="n">
-        <v>9556700</v>
+        <v>11580000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B87" t="n">
-        <v>299.5110006693188</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C87" t="n">
-        <v>303.898671192008</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D87" t="n">
-        <v>299.3327275624257</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E87" t="n">
-        <v>303.4926147460938</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F87" t="n">
-        <v>11580000</v>
+        <v>11953200</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B88" t="n">
-        <v>302.333781642444</v>
+        <v>301.5513314360023</v>
       </c>
       <c r="C88" t="n">
-        <v>304.9881708986046</v>
+        <v>306.3450888451811</v>
       </c>
       <c r="D88" t="n">
-        <v>299.6694782493637</v>
+        <v>298.4908553932551</v>
       </c>
       <c r="E88" t="n">
-        <v>302.9676818847656</v>
+        <v>305.1961975097656</v>
       </c>
       <c r="F88" t="n">
-        <v>11953200</v>
+        <v>9839400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B89" t="n">
-        <v>301.5513314360023</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C89" t="n">
-        <v>306.3450888451811</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D89" t="n">
-        <v>298.4908553932551</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E89" t="n">
-        <v>305.1961975097656</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F89" t="n">
-        <v>9839400</v>
+        <v>12688000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B90" t="n">
-        <v>306.7709905338949</v>
+        <v>311.4062598905275</v>
       </c>
       <c r="C90" t="n">
-        <v>313.2286905211348</v>
+        <v>316.2594412620415</v>
       </c>
       <c r="D90" t="n">
-        <v>306.1470044328188</v>
+        <v>311.4062598905275</v>
       </c>
       <c r="E90" t="n">
-        <v>311.8420715332031</v>
+        <v>314.2389221191406</v>
       </c>
       <c r="F90" t="n">
-        <v>12688000</v>
+        <v>9848800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B91" t="n">
-        <v>311.4062598905275</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C91" t="n">
-        <v>316.2594412620415</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D91" t="n">
-        <v>311.4062598905275</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E91" t="n">
-        <v>314.2389221191406</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F91" t="n">
-        <v>9848800</v>
+        <v>9388000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B92" t="n">
-        <v>311.9906259989966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C92" t="n">
-        <v>312.9909865673853</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D92" t="n">
-        <v>302.6210112179966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E92" t="n">
-        <v>307.1968688964844</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F92" t="n">
-        <v>9388000</v>
+        <v>17797400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B93" t="n">
-        <v>311.7034102684662</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C93" t="n">
-        <v>321.1522783634816</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D93" t="n">
-        <v>311.7034102684662</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E93" t="n">
-        <v>319.3199462890625</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F93" t="n">
-        <v>17797400</v>
+        <v>11477500</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B94" t="n">
-        <v>318.2700781279603</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C94" t="n">
-        <v>323.2817350541263</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D94" t="n">
-        <v>317.0518180384032</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E94" t="n">
-        <v>319.0228271484375</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F94" t="n">
-        <v>11477500</v>
+        <v>9902200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B95" t="n">
-        <v>319.4684837021083</v>
+        <v>320.1519144431551</v>
       </c>
       <c r="C95" t="n">
-        <v>323.014298845819</v>
+        <v>322.1724337503843</v>
       </c>
       <c r="D95" t="n">
-        <v>312.1094739861534</v>
+        <v>305.7805563960757</v>
       </c>
       <c r="E95" t="n">
-        <v>315.2392883300781</v>
+        <v>307.8505859375</v>
       </c>
       <c r="F95" t="n">
-        <v>9902200</v>
+        <v>8703500</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B96" t="n">
-        <v>320.1519144431551</v>
+        <v>309.2966060076438</v>
       </c>
       <c r="C96" t="n">
-        <v>322.1724337503843</v>
+        <v>310.6238005797982</v>
       </c>
       <c r="D96" t="n">
-        <v>305.7805563960757</v>
+        <v>297.1537232583444</v>
       </c>
       <c r="E96" t="n">
-        <v>307.8505859375</v>
+        <v>299.7487182617188</v>
       </c>
       <c r="F96" t="n">
-        <v>8703500</v>
+        <v>13443400</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B97" t="n">
-        <v>309.2966060076438</v>
+        <v>295.6680481198895</v>
       </c>
       <c r="C97" t="n">
-        <v>310.6238005797982</v>
+        <v>301.3829431862302</v>
       </c>
       <c r="D97" t="n">
-        <v>297.1537232583444</v>
+        <v>293.6871553220786</v>
       </c>
       <c r="E97" t="n">
-        <v>299.7487182617188</v>
+        <v>299.6595458984375</v>
       </c>
       <c r="F97" t="n">
-        <v>13443400</v>
+        <v>9114500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B98" t="n">
-        <v>295.6680481198895</v>
+        <v>299.8675549474044</v>
       </c>
       <c r="C98" t="n">
-        <v>301.3829431862302</v>
+        <v>305.2951817518681</v>
       </c>
       <c r="D98" t="n">
-        <v>293.6871553220786</v>
+        <v>299.6100292169066</v>
       </c>
       <c r="E98" t="n">
-        <v>299.6595458984375</v>
+        <v>304.19580078125</v>
       </c>
       <c r="F98" t="n">
-        <v>9114500</v>
+        <v>8896800</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B99" t="n">
-        <v>299.8675549474044</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C99" t="n">
-        <v>305.2951817518681</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D99" t="n">
-        <v>299.6100292169066</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E99" t="n">
-        <v>304.19580078125</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F99" t="n">
-        <v>8896800</v>
+        <v>7209600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B100" t="n">
-        <v>305.5130974954087</v>
+        <v>304.2354576365961</v>
       </c>
       <c r="C100" t="n">
-        <v>309.2966101142475</v>
+        <v>306.226234501648</v>
       </c>
       <c r="D100" t="n">
-        <v>304.2849535938903</v>
+        <v>302.2050242231491</v>
       </c>
       <c r="E100" t="n">
-        <v>305.8300476074219</v>
+        <v>305.1070251464844</v>
       </c>
       <c r="F100" t="n">
-        <v>7209600</v>
+        <v>6737700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B101" t="n">
-        <v>304.2354576365961</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C101" t="n">
-        <v>306.226234501648</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D101" t="n">
-        <v>302.2050242231491</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E101" t="n">
-        <v>305.1070251464844</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F101" t="n">
-        <v>6737700</v>
+        <v>7792700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B102" t="n">
-        <v>305.4536802835111</v>
+        <v>305.8498774375392</v>
       </c>
       <c r="C102" t="n">
-        <v>308.0288471084009</v>
+        <v>308.028871901531</v>
       </c>
       <c r="D102" t="n">
-        <v>302.7596647203387</v>
+        <v>292.2807780649544</v>
       </c>
       <c r="E102" t="n">
-        <v>307.8208618164062</v>
+        <v>294.8262329101562</v>
       </c>
       <c r="F102" t="n">
-        <v>7792700</v>
+        <v>12955400</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B103" t="n">
-        <v>305.8498774375392</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C103" t="n">
-        <v>308.028871901531</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D103" t="n">
-        <v>292.2807780649544</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E103" t="n">
-        <v>294.8262329101562</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F103" t="n">
-        <v>12955400</v>
+        <v>13554100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B104" t="n">
-        <v>293.9843218466586</v>
+        <v>295.7869207463737</v>
       </c>
       <c r="C104" t="n">
-        <v>296.886322684036</v>
+        <v>300.7589506810849</v>
       </c>
       <c r="D104" t="n">
-        <v>288.5962907533433</v>
+        <v>294.1724883145502</v>
       </c>
       <c r="E104" t="n">
-        <v>294.459716796875</v>
+        <v>300.4023742675781</v>
       </c>
       <c r="F104" t="n">
-        <v>13554100</v>
+        <v>8095500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B105" t="n">
-        <v>295.7869207463737</v>
+        <v>301.670173133609</v>
       </c>
       <c r="C105" t="n">
-        <v>300.7589506810849</v>
+        <v>306.0578739762234</v>
       </c>
       <c r="D105" t="n">
-        <v>294.1724883145502</v>
+        <v>300.7391812579012</v>
       </c>
       <c r="E105" t="n">
-        <v>300.4023742675781</v>
+        <v>303.2053833007812</v>
       </c>
       <c r="F105" t="n">
-        <v>8095500</v>
+        <v>7007800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B106" t="n">
-        <v>301.670173133609</v>
+        <v>297.1339389424841</v>
       </c>
       <c r="C106" t="n">
-        <v>306.0578739762234</v>
+        <v>300.0557680991628</v>
       </c>
       <c r="D106" t="n">
-        <v>300.7391812579012</v>
+        <v>291.636973162459</v>
       </c>
       <c r="E106" t="n">
-        <v>303.2053833007812</v>
+        <v>297.4310607910156</v>
       </c>
       <c r="F106" t="n">
-        <v>7007800</v>
+        <v>18620800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B107" t="n">
-        <v>297.1339389424841</v>
+        <v>291.9935267958635</v>
       </c>
       <c r="C107" t="n">
-        <v>300.0557680991628</v>
+        <v>297.1141484397957</v>
       </c>
       <c r="D107" t="n">
-        <v>291.636973162459</v>
+        <v>290.4088063693875</v>
       </c>
       <c r="E107" t="n">
-        <v>297.4310607910156</v>
+        <v>294.7172546386719</v>
       </c>
       <c r="F107" t="n">
-        <v>18620800</v>
+        <v>8508900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B108" t="n">
-        <v>291.9935267958635</v>
+        <v>289.4975898716125</v>
       </c>
       <c r="C108" t="n">
-        <v>297.1141484397957</v>
+        <v>299.5011046657454</v>
       </c>
       <c r="D108" t="n">
-        <v>290.4088063693875</v>
+        <v>286.7342359222354</v>
       </c>
       <c r="E108" t="n">
-        <v>294.7172546386719</v>
+        <v>297.3914489746094</v>
       </c>
       <c r="F108" t="n">
-        <v>8508900</v>
+        <v>10278200</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B109" t="n">
-        <v>289.4975898716125</v>
+        <v>297.1240288614248</v>
       </c>
       <c r="C109" t="n">
-        <v>299.5011046657454</v>
+        <v>298.1243894751821</v>
       </c>
       <c r="D109" t="n">
-        <v>286.7342359222354</v>
+        <v>292.993883980321</v>
       </c>
       <c r="E109" t="n">
-        <v>297.3914489746094</v>
+        <v>296.52978515625</v>
       </c>
       <c r="F109" t="n">
-        <v>10278200</v>
+        <v>8055700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B110" t="n">
-        <v>297.1240288614248</v>
+        <v>295.1332451958745</v>
       </c>
       <c r="C110" t="n">
-        <v>298.1243894751821</v>
+        <v>298.3620800816865</v>
       </c>
       <c r="D110" t="n">
-        <v>292.993883980321</v>
+        <v>289.6362492414601</v>
       </c>
       <c r="E110" t="n">
-        <v>296.52978515625</v>
+        <v>290.7455444335938</v>
       </c>
       <c r="F110" t="n">
-        <v>8055700</v>
+        <v>12732500</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B111" t="n">
-        <v>295.1332451958745</v>
+        <v>283.6044306839189</v>
       </c>
       <c r="C111" t="n">
-        <v>298.3620800816865</v>
+        <v>287.2195541533999</v>
       </c>
       <c r="D111" t="n">
-        <v>289.6362492414601</v>
+        <v>280.9995517042956</v>
       </c>
       <c r="E111" t="n">
-        <v>290.7455444335938</v>
+        <v>286.7144470214844</v>
       </c>
       <c r="F111" t="n">
-        <v>12732500</v>
+        <v>13496500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B112" t="n">
-        <v>283.6044306839189</v>
+        <v>282.7724816341387</v>
       </c>
       <c r="C112" t="n">
-        <v>287.2195541533999</v>
+        <v>288.3189881947603</v>
       </c>
       <c r="D112" t="n">
-        <v>280.9995517042956</v>
+        <v>277.7707387954702</v>
       </c>
       <c r="E112" t="n">
-        <v>286.7144470214844</v>
+        <v>287.1502685546875</v>
       </c>
       <c r="F112" t="n">
-        <v>13496500</v>
+        <v>12241100</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B113" t="n">
-        <v>282.7724816341387</v>
+        <v>286.5262662545288</v>
       </c>
       <c r="C113" t="n">
-        <v>288.3189881947603</v>
+        <v>289.9532025593205</v>
       </c>
       <c r="D113" t="n">
-        <v>277.7707387954702</v>
+        <v>284.4364084963449</v>
       </c>
       <c r="E113" t="n">
-        <v>287.1502685546875</v>
+        <v>285.9716186523438</v>
       </c>
       <c r="F113" t="n">
-        <v>12241100</v>
+        <v>8344900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B114" t="n">
-        <v>286.5262662545288</v>
+        <v>286.0508472723319</v>
       </c>
       <c r="C114" t="n">
-        <v>289.9532025593205</v>
+        <v>287.7049062038017</v>
       </c>
       <c r="D114" t="n">
-        <v>284.4364084963449</v>
+        <v>282.1385715612803</v>
       </c>
       <c r="E114" t="n">
-        <v>285.9716186523438</v>
+        <v>284.7731628417969</v>
       </c>
       <c r="F114" t="n">
-        <v>8344900</v>
+        <v>10205000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B115" t="n">
-        <v>286.0508472723319</v>
+        <v>280.1279843639117</v>
       </c>
       <c r="C115" t="n">
-        <v>287.7049062038017</v>
+        <v>281.1679713767581</v>
       </c>
       <c r="D115" t="n">
-        <v>282.1385715612803</v>
+        <v>276.4336380780354</v>
       </c>
       <c r="E115" t="n">
-        <v>284.7731628417969</v>
+        <v>280.1874389648438</v>
       </c>
       <c r="F115" t="n">
-        <v>10205000</v>
+        <v>13760500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B116" t="n">
-        <v>280.1279843639117</v>
+        <v>281.9504072447318</v>
       </c>
       <c r="C116" t="n">
-        <v>281.1679713767581</v>
+        <v>284.4463214441296</v>
       </c>
       <c r="D116" t="n">
-        <v>276.4336380780354</v>
+        <v>280.2468381234208</v>
       </c>
       <c r="E116" t="n">
-        <v>280.1874389648438</v>
+        <v>280.7321472167969</v>
       </c>
       <c r="F116" t="n">
-        <v>13760500</v>
+        <v>9091200</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B117" t="n">
-        <v>281.9504072447318</v>
+        <v>283.6044205599556</v>
       </c>
       <c r="C117" t="n">
-        <v>284.4463214441296</v>
+        <v>286.506421278288</v>
       </c>
       <c r="D117" t="n">
-        <v>280.2468381234208</v>
+        <v>281.8909373944359</v>
       </c>
       <c r="E117" t="n">
-        <v>280.7321472167969</v>
+        <v>283.4261474609375</v>
       </c>
       <c r="F117" t="n">
-        <v>9091200</v>
+        <v>8149000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B118" t="n">
-        <v>283.6044205599556</v>
+        <v>286.2390279690733</v>
       </c>
       <c r="C118" t="n">
-        <v>286.506421278288</v>
+        <v>288.9726698808299</v>
       </c>
       <c r="D118" t="n">
-        <v>281.8909373944359</v>
+        <v>283.2181783456238</v>
       </c>
       <c r="E118" t="n">
-        <v>283.4261474609375</v>
+        <v>284.1492004394531</v>
       </c>
       <c r="F118" t="n">
-        <v>8149000</v>
+        <v>8961200</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B119" t="n">
-        <v>286.2390279690733</v>
+        <v>284.0897180113691</v>
       </c>
       <c r="C119" t="n">
-        <v>288.9726698808299</v>
+        <v>286.6450865635814</v>
       </c>
       <c r="D119" t="n">
-        <v>283.2181783456238</v>
+        <v>282.3960631878955</v>
       </c>
       <c r="E119" t="n">
-        <v>284.1492004394531</v>
+        <v>284.9910278320312</v>
       </c>
       <c r="F119" t="n">
-        <v>8961200</v>
+        <v>10057000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B120" t="n">
-        <v>284.0897180113691</v>
+        <v>284.1392890417467</v>
       </c>
       <c r="C120" t="n">
-        <v>286.6450865635814</v>
+        <v>286.7441681021885</v>
       </c>
       <c r="D120" t="n">
-        <v>282.3960631878955</v>
+        <v>281.900870340191</v>
       </c>
       <c r="E120" t="n">
-        <v>284.9910278320312</v>
+        <v>285.2188720703125</v>
       </c>
       <c r="F120" t="n">
-        <v>10057000</v>
+        <v>9846700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B121" t="n">
-        <v>284.1392890417467</v>
+        <v>285.3277943529036</v>
       </c>
       <c r="C121" t="n">
-        <v>286.7441681021885</v>
+        <v>287.9326733008621</v>
       </c>
       <c r="D121" t="n">
-        <v>281.900870340191</v>
+        <v>282.5446423017302</v>
       </c>
       <c r="E121" t="n">
-        <v>285.2188720703125</v>
+        <v>283.8223266601562</v>
       </c>
       <c r="F121" t="n">
-        <v>9846700</v>
+        <v>22436500</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B122" t="n">
-        <v>285.3277943529036</v>
+        <v>291.4982779446762</v>
       </c>
       <c r="C122" t="n">
-        <v>287.9326733008621</v>
+        <v>292.9245231806114</v>
       </c>
       <c r="D122" t="n">
-        <v>282.5446423017302</v>
+        <v>285.2188513876401</v>
       </c>
       <c r="E122" t="n">
-        <v>283.8223266601562</v>
+        <v>287.1403198242188</v>
       </c>
       <c r="F122" t="n">
-        <v>22436500</v>
+        <v>11470800</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B123" t="n">
-        <v>291.4982779446762</v>
+        <v>283.4360748065673</v>
       </c>
       <c r="C123" t="n">
-        <v>292.9245231806114</v>
+        <v>292.6571288676103</v>
       </c>
       <c r="D123" t="n">
-        <v>285.2188513876401</v>
+        <v>282.6436995084055</v>
       </c>
       <c r="E123" t="n">
-        <v>287.1403198242188</v>
+        <v>289.6065368652344</v>
       </c>
       <c r="F123" t="n">
-        <v>11470800</v>
+        <v>11092300</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B124" t="n">
-        <v>283.4360748065673</v>
+        <v>291.3398308899875</v>
       </c>
       <c r="C124" t="n">
-        <v>292.6571288676103</v>
+        <v>294.7965097163498</v>
       </c>
       <c r="D124" t="n">
-        <v>282.6436995084055</v>
+        <v>289.6461758443202</v>
       </c>
       <c r="E124" t="n">
-        <v>289.6065368652344</v>
+        <v>292.5977172851562</v>
       </c>
       <c r="F124" t="n">
-        <v>11092300</v>
+        <v>12188200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B125" t="n">
-        <v>291.3398308899875</v>
+        <v>289.7847899387647</v>
       </c>
       <c r="C125" t="n">
-        <v>294.7965097163498</v>
+        <v>292.1717693530369</v>
       </c>
       <c r="D125" t="n">
-        <v>289.6461758443202</v>
+        <v>287.9524883078727</v>
       </c>
       <c r="E125" t="n">
-        <v>292.5977172851562</v>
+        <v>288.8735961914062</v>
       </c>
       <c r="F125" t="n">
-        <v>12188200</v>
+        <v>8669200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B126" t="n">
-        <v>289.7847899387647</v>
+        <v>286.3777093696089</v>
       </c>
       <c r="C126" t="n">
-        <v>292.1717693530369</v>
+        <v>287.3384134369941</v>
       </c>
       <c r="D126" t="n">
-        <v>287.9524883078727</v>
+        <v>279.0582953832721</v>
       </c>
       <c r="E126" t="n">
-        <v>288.8735961914062</v>
+        <v>280.1378784179688</v>
       </c>
       <c r="F126" t="n">
-        <v>8669200</v>
+        <v>9873300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B127" t="n">
-        <v>286.3777093696089</v>
+        <v>282.0197247859078</v>
       </c>
       <c r="C127" t="n">
-        <v>287.3384134369941</v>
+        <v>284.505755156032</v>
       </c>
       <c r="D127" t="n">
-        <v>279.0582953832721</v>
+        <v>279.6327451103039</v>
       </c>
       <c r="E127" t="n">
-        <v>280.1378784179688</v>
+        <v>281.0589904785156</v>
       </c>
       <c r="F127" t="n">
-        <v>9873300</v>
+        <v>11734400</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B128" t="n">
-        <v>282.0197247859078</v>
+        <v>285.7140887250632</v>
       </c>
       <c r="C128" t="n">
-        <v>284.505755156032</v>
+        <v>292.2510413422024</v>
       </c>
       <c r="D128" t="n">
-        <v>279.6327451103039</v>
+        <v>282.2277281014015</v>
       </c>
       <c r="E128" t="n">
-        <v>281.0589904785156</v>
+        <v>291.3497314453125</v>
       </c>
       <c r="F128" t="n">
-        <v>11734400</v>
+        <v>12956900</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B129" t="n">
-        <v>285.7140887250632</v>
+        <v>292.567989087923</v>
       </c>
       <c r="C129" t="n">
-        <v>292.2510413422024</v>
+        <v>295.8661624411999</v>
       </c>
       <c r="D129" t="n">
-        <v>282.2277281014015</v>
+        <v>290.1116710297465</v>
       </c>
       <c r="E129" t="n">
-        <v>291.3497314453125</v>
+        <v>292.5580749511719</v>
       </c>
       <c r="F129" t="n">
-        <v>12956900</v>
+        <v>11267200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B130" t="n">
-        <v>292.567989087923</v>
+        <v>289.1212191631598</v>
       </c>
       <c r="C130" t="n">
-        <v>295.8661624411999</v>
+        <v>292.7957669317203</v>
       </c>
       <c r="D130" t="n">
-        <v>290.1116710297465</v>
+        <v>285.9616926535428</v>
       </c>
       <c r="E130" t="n">
-        <v>292.5580749511719</v>
+        <v>291.7855224609375</v>
       </c>
       <c r="F130" t="n">
-        <v>11267200</v>
+        <v>6669300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,25 +3823,25 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B131" t="n">
-        <v>289.1212191631598</v>
+        <v>292.7412191857173</v>
       </c>
       <c r="C131" t="n">
-        <v>292.7957669317203</v>
+        <v>295.4987855589938</v>
       </c>
       <c r="D131" t="n">
-        <v>285.9616926535428</v>
+        <v>291.8850906324002</v>
       </c>
       <c r="E131" t="n">
-        <v>291.7855224609375</v>
+        <v>294.125</v>
       </c>
       <c r="F131" t="n">
-        <v>6669300</v>
+        <v>7142600</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -3849,25 +3849,25 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B132" t="n">
-        <v>292.7412191857173</v>
+        <v>291.8253790066561</v>
       </c>
       <c r="C132" t="n">
-        <v>295.4987855589938</v>
+        <v>296.8427544058445</v>
       </c>
       <c r="D132" t="n">
-        <v>291.8850906324002</v>
+        <v>291.3873498301165</v>
       </c>
       <c r="E132" t="n">
-        <v>294.125</v>
+        <v>296.0662536621094</v>
       </c>
       <c r="F132" t="n">
-        <v>7142600</v>
+        <v>7849100</v>
       </c>
       <c r="G132" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B133" t="n">
-        <v>291.8253790066561</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="C133" t="n">
-        <v>296.8427544058445</v>
+        <v>309.8640903908154</v>
       </c>
       <c r="D133" t="n">
-        <v>291.3873498301165</v>
+        <v>303.9606617936424</v>
       </c>
       <c r="E133" t="n">
-        <v>296.0662536621094</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="F133" t="n">
-        <v>7849100</v>
+        <v>10590200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B134" t="n">
-        <v>306.5888366699219</v>
+        <v>305.5734164156603</v>
       </c>
       <c r="C134" t="n">
-        <v>309.8640903908154</v>
+        <v>309.8640846884941</v>
       </c>
       <c r="D134" t="n">
-        <v>303.9606617936424</v>
+        <v>304.73715687535</v>
       </c>
       <c r="E134" t="n">
-        <v>306.5888366699219</v>
+        <v>308.938232421875</v>
       </c>
       <c r="F134" t="n">
-        <v>10590200</v>
+        <v>6586600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B135" t="n">
-        <v>305.5734164156603</v>
+        <v>308.6097380099313</v>
       </c>
       <c r="C135" t="n">
-        <v>309.8640846884941</v>
+        <v>308.9581744354404</v>
       </c>
       <c r="D135" t="n">
-        <v>304.73715687535</v>
+        <v>305.344449093958</v>
       </c>
       <c r="E135" t="n">
-        <v>308.938232421875</v>
+        <v>308.4803161621094</v>
       </c>
       <c r="F135" t="n">
-        <v>6586600</v>
+        <v>6069700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B136" t="n">
-        <v>308.6097380099313</v>
+        <v>306.0910825316173</v>
       </c>
       <c r="C136" t="n">
-        <v>308.9581744354404</v>
+        <v>312.3329523629397</v>
       </c>
       <c r="D136" t="n">
-        <v>305.344449093958</v>
+        <v>304.0900871089203</v>
       </c>
       <c r="E136" t="n">
-        <v>308.4803161621094</v>
+        <v>312.2732238769531</v>
       </c>
       <c r="F136" t="n">
-        <v>6069700</v>
+        <v>8318200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B137" t="n">
-        <v>306.0910825316173</v>
+        <v>308.4305432499699</v>
       </c>
       <c r="C137" t="n">
-        <v>312.3329523629397</v>
+        <v>312.9103618924516</v>
       </c>
       <c r="D137" t="n">
-        <v>304.0900871089203</v>
+        <v>307.4847916064935</v>
       </c>
       <c r="E137" t="n">
-        <v>312.2732238769531</v>
+        <v>309.7247009277344</v>
       </c>
       <c r="F137" t="n">
-        <v>8318200</v>
+        <v>11455500</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B138" t="n">
-        <v>308.4305432499699</v>
+        <v>312.5420354159922</v>
       </c>
       <c r="C138" t="n">
-        <v>312.9103618924516</v>
+        <v>312.8307129741003</v>
       </c>
       <c r="D138" t="n">
-        <v>307.4847916064935</v>
+        <v>302.8954898881459</v>
       </c>
       <c r="E138" t="n">
-        <v>309.7247009277344</v>
+        <v>304.5579833984375</v>
       </c>
       <c r="F138" t="n">
-        <v>11455500</v>
+        <v>9885800</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B139" t="n">
-        <v>312.5420354159922</v>
+        <v>303.9805907681049</v>
       </c>
       <c r="C139" t="n">
-        <v>312.8307129741003</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="D139" t="n">
-        <v>302.8954898881459</v>
+        <v>303.8312695552229</v>
       </c>
       <c r="E139" t="n">
-        <v>304.5579833984375</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="F139" t="n">
-        <v>9885800</v>
+        <v>8208600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B140" t="n">
-        <v>303.9805907681049</v>
+        <v>311.068653468178</v>
       </c>
       <c r="C140" t="n">
-        <v>308.5599670410156</v>
+        <v>313.4877482505245</v>
       </c>
       <c r="D140" t="n">
-        <v>303.8312695552229</v>
+        <v>308.6993222963794</v>
       </c>
       <c r="E140" t="n">
-        <v>308.5599670410156</v>
+        <v>308.8984375</v>
       </c>
       <c r="F140" t="n">
-        <v>8208600</v>
+        <v>11082400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B141" t="n">
-        <v>311.068653468178</v>
+        <v>309.4559416581444</v>
       </c>
       <c r="C141" t="n">
-        <v>313.4877482505245</v>
+        <v>315.7077766193834</v>
       </c>
       <c r="D141" t="n">
-        <v>308.6993222963794</v>
+        <v>308.9780833700189</v>
       </c>
       <c r="E141" t="n">
-        <v>308.8984375</v>
+        <v>315.5683898925781</v>
       </c>
       <c r="F141" t="n">
-        <v>11082400</v>
+        <v>10772000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B142" t="n">
-        <v>309.4559416581444</v>
+        <v>316.0661368489313</v>
       </c>
       <c r="C142" t="n">
-        <v>315.7077766193834</v>
+        <v>318.8038038717339</v>
       </c>
       <c r="D142" t="n">
-        <v>308.9780833700189</v>
+        <v>311.3474041387296</v>
       </c>
       <c r="E142" t="n">
-        <v>315.5683898925781</v>
+        <v>311.5962829589844</v>
       </c>
       <c r="F142" t="n">
-        <v>10772000</v>
+        <v>7084300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B143" t="n">
-        <v>316.0661368489313</v>
+        <v>313.4379903862348</v>
       </c>
       <c r="C143" t="n">
-        <v>318.8038038717339</v>
+        <v>313.7366328164263</v>
       </c>
       <c r="D143" t="n">
-        <v>311.3474041387296</v>
+        <v>310.5410372905177</v>
       </c>
       <c r="E143" t="n">
-        <v>311.5962829589844</v>
+        <v>311.6161804199219</v>
       </c>
       <c r="F143" t="n">
-        <v>7084300</v>
+        <v>5545900</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B144" t="n">
-        <v>313.4379903862348</v>
+        <v>312.1139549773267</v>
       </c>
       <c r="C144" t="n">
-        <v>313.7366328164263</v>
+        <v>313.5773637260273</v>
       </c>
       <c r="D144" t="n">
-        <v>310.5410372905177</v>
+        <v>307.5047445243564</v>
       </c>
       <c r="E144" t="n">
-        <v>311.6161804199219</v>
+        <v>310.2921752929688</v>
       </c>
       <c r="F144" t="n">
-        <v>5545900</v>
+        <v>6969700</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B145" t="n">
-        <v>312.1139549773267</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="C145" t="n">
-        <v>313.5773637260273</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="D145" t="n">
-        <v>307.5047445243564</v>
+        <v>306.5092257615542</v>
       </c>
       <c r="E145" t="n">
-        <v>310.2921752929688</v>
+        <v>306.8974609375</v>
       </c>
       <c r="F145" t="n">
-        <v>6969700</v>
+        <v>5215300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B146" t="n">
-        <v>309.7545850384977</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="C146" t="n">
-        <v>309.7545850384977</v>
+        <v>311.1781431330245</v>
       </c>
       <c r="D146" t="n">
-        <v>306.5092257615542</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="E146" t="n">
-        <v>306.8974609375</v>
+        <v>310.232421875</v>
       </c>
       <c r="F146" t="n">
-        <v>5215300</v>
+        <v>7925300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B147" t="n">
-        <v>305.5037244427344</v>
+        <v>313.7864355589005</v>
       </c>
       <c r="C147" t="n">
-        <v>311.1781431330245</v>
+        <v>314.035314384572</v>
       </c>
       <c r="D147" t="n">
-        <v>305.5037244427344</v>
+        <v>309.7745101043047</v>
       </c>
       <c r="E147" t="n">
-        <v>310.232421875</v>
+        <v>310.0532531738281</v>
       </c>
       <c r="F147" t="n">
-        <v>7925300</v>
+        <v>7398600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B148" t="n">
-        <v>313.7864355589005</v>
+        <v>309.1771855961317</v>
       </c>
       <c r="C148" t="n">
-        <v>314.035314384572</v>
+        <v>310.6505287563671</v>
       </c>
       <c r="D148" t="n">
-        <v>309.7745101043047</v>
+        <v>305.9118967162461</v>
       </c>
       <c r="E148" t="n">
-        <v>310.0532531738281</v>
+        <v>307.8630981445312</v>
       </c>
       <c r="F148" t="n">
-        <v>7398600</v>
+        <v>8031800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B149" t="n">
-        <v>309.1771855961317</v>
+        <v>305.6928786901284</v>
       </c>
       <c r="C149" t="n">
-        <v>310.6505287563671</v>
+        <v>312.6913497643884</v>
       </c>
       <c r="D149" t="n">
-        <v>305.9118967162461</v>
+        <v>305.1951210592971</v>
       </c>
       <c r="E149" t="n">
-        <v>307.8630981445312</v>
+        <v>311.8252563476562</v>
       </c>
       <c r="F149" t="n">
-        <v>8031800</v>
+        <v>8865400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B150" t="n">
-        <v>305.6928786901284</v>
+        <v>312.5420381202088</v>
       </c>
       <c r="C150" t="n">
-        <v>312.6913497643884</v>
+        <v>314.6624601726697</v>
       </c>
       <c r="D150" t="n">
-        <v>305.1951210592971</v>
+        <v>310.431520181067</v>
       </c>
       <c r="E150" t="n">
-        <v>311.8252563476562</v>
+        <v>311.0686645507812</v>
       </c>
       <c r="F150" t="n">
-        <v>8865400</v>
+        <v>6135400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B151" t="n">
-        <v>312.5420381202088</v>
+        <v>309.2269452093906</v>
       </c>
       <c r="C151" t="n">
-        <v>314.6624601726697</v>
+        <v>309.2568094519629</v>
       </c>
       <c r="D151" t="n">
-        <v>310.431520181067</v>
+        <v>305.1353920734132</v>
       </c>
       <c r="E151" t="n">
-        <v>311.0686645507812</v>
+        <v>306.270263671875</v>
       </c>
       <c r="F151" t="n">
-        <v>6135400</v>
+        <v>7338200</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B152" t="n">
-        <v>309.2269452093906</v>
+        <v>306.3299974055641</v>
       </c>
       <c r="C152" t="n">
-        <v>309.2568094519629</v>
+        <v>309.5753869306937</v>
       </c>
       <c r="D152" t="n">
-        <v>305.1353920734132</v>
+        <v>305.42407485773</v>
       </c>
       <c r="E152" t="n">
-        <v>306.270263671875</v>
+        <v>308.0124206542969</v>
       </c>
       <c r="F152" t="n">
-        <v>7338200</v>
+        <v>6316800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B153" t="n">
-        <v>306.3299974055641</v>
+        <v>310.0532528884956</v>
       </c>
       <c r="C153" t="n">
-        <v>309.5753869306937</v>
+        <v>314.8416790595512</v>
       </c>
       <c r="D153" t="n">
-        <v>305.42407485773</v>
+        <v>309.9536952821754</v>
       </c>
       <c r="E153" t="n">
-        <v>308.0124206542969</v>
+        <v>313.4877624511719</v>
       </c>
       <c r="F153" t="n">
-        <v>6316800</v>
+        <v>8629500</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B154" t="n">
-        <v>310.0532528884956</v>
+        <v>313.2388767644321</v>
       </c>
       <c r="C154" t="n">
-        <v>314.8416790595512</v>
+        <v>314.8814709002291</v>
       </c>
       <c r="D154" t="n">
-        <v>309.9536952821754</v>
+        <v>304.7670623908274</v>
       </c>
       <c r="E154" t="n">
-        <v>313.4877624511719</v>
+        <v>304.8964538574219</v>
       </c>
       <c r="F154" t="n">
-        <v>8629500</v>
+        <v>8359600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B155" t="n">
-        <v>313.2388767644321</v>
+        <v>306.8675912418493</v>
       </c>
       <c r="C155" t="n">
-        <v>314.8814709002291</v>
+        <v>307.6042628420606</v>
       </c>
       <c r="D155" t="n">
-        <v>304.7670623908274</v>
+        <v>299.1523476664256</v>
       </c>
       <c r="E155" t="n">
-        <v>304.8964538574219</v>
+        <v>300.7451782226562</v>
       </c>
       <c r="F155" t="n">
-        <v>8359600</v>
+        <v>9464300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B156" t="n">
-        <v>306.8675912418493</v>
+        <v>300.7451596100784</v>
       </c>
       <c r="C156" t="n">
-        <v>307.6042628420606</v>
+        <v>301.8302675742967</v>
       </c>
       <c r="D156" t="n">
-        <v>299.1523476664256</v>
+        <v>297.5395993270601</v>
       </c>
       <c r="E156" t="n">
-        <v>300.7451782226562</v>
+        <v>298.6545715332031</v>
       </c>
       <c r="F156" t="n">
-        <v>9464300</v>
+        <v>9512000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B157" t="n">
-        <v>300.7451596100784</v>
+        <v>298.6744753830843</v>
       </c>
       <c r="C157" t="n">
-        <v>301.8302675742967</v>
+        <v>304.6873960201211</v>
       </c>
       <c r="D157" t="n">
-        <v>297.5395993270601</v>
+        <v>294.2245209852311</v>
       </c>
       <c r="E157" t="n">
-        <v>298.6545715332031</v>
+        <v>303.5126953125</v>
       </c>
       <c r="F157" t="n">
-        <v>9512000</v>
+        <v>9498200</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B158" t="n">
-        <v>298.6744753830843</v>
+        <v>300.9144028967509</v>
       </c>
       <c r="C158" t="n">
-        <v>304.6873960201211</v>
+        <v>301.6411400127173</v>
       </c>
       <c r="D158" t="n">
-        <v>294.2245209852311</v>
+        <v>298.7242874353194</v>
       </c>
       <c r="E158" t="n">
-        <v>303.5126953125</v>
+        <v>298.9034729003906</v>
       </c>
       <c r="F158" t="n">
-        <v>9498200</v>
+        <v>7709500</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B159" t="n">
-        <v>300.9144028967509</v>
+        <v>300.8945046380796</v>
       </c>
       <c r="C159" t="n">
-        <v>301.6411400127173</v>
+        <v>302.387777613951</v>
       </c>
       <c r="D159" t="n">
-        <v>298.7242874353194</v>
+        <v>297.4699295162906</v>
       </c>
       <c r="E159" t="n">
-        <v>298.9034729003906</v>
+        <v>298.5650024414062</v>
       </c>
       <c r="F159" t="n">
-        <v>7709500</v>
+        <v>7364300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B160" t="n">
-        <v>300.8945046380796</v>
+        <v>298.8636262885424</v>
       </c>
       <c r="C160" t="n">
-        <v>302.387777613951</v>
+        <v>299.4410421498196</v>
       </c>
       <c r="D160" t="n">
-        <v>297.4699295162906</v>
+        <v>295.1205095874812</v>
       </c>
       <c r="E160" t="n">
-        <v>298.5650024414062</v>
+        <v>296.4743957519531</v>
       </c>
       <c r="F160" t="n">
-        <v>7364300</v>
+        <v>8699300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B161" t="n">
-        <v>298.8636262885424</v>
+        <v>296.6635495230975</v>
       </c>
       <c r="C161" t="n">
-        <v>299.4410421498196</v>
+        <v>299.908939014877</v>
       </c>
       <c r="D161" t="n">
-        <v>295.1205095874812</v>
+        <v>295.8870488301784</v>
       </c>
       <c r="E161" t="n">
-        <v>296.4743957519531</v>
+        <v>299.3813171386719</v>
       </c>
       <c r="F161" t="n">
-        <v>8699300</v>
+        <v>7546300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B162" t="n">
-        <v>296.6635495230975</v>
+        <v>299.7396822358739</v>
       </c>
       <c r="C162" t="n">
-        <v>299.908939014877</v>
+        <v>300.436555061437</v>
       </c>
       <c r="D162" t="n">
-        <v>295.8870488301784</v>
+        <v>293.935841710235</v>
       </c>
       <c r="E162" t="n">
-        <v>299.3813171386719</v>
+        <v>294.3738708496094</v>
       </c>
       <c r="F162" t="n">
-        <v>7546300</v>
+        <v>8066900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B163" t="n">
-        <v>299.7396822358739</v>
+        <v>295.3694126574367</v>
       </c>
       <c r="C163" t="n">
-        <v>300.436555061437</v>
+        <v>301.57145376365</v>
       </c>
       <c r="D163" t="n">
-        <v>293.935841710235</v>
+        <v>292.3530024013792</v>
       </c>
       <c r="E163" t="n">
-        <v>294.3738708496094</v>
+        <v>300.625732421875</v>
       </c>
       <c r="F163" t="n">
-        <v>8066900</v>
+        <v>9327000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B164" t="n">
-        <v>295.3694126574367</v>
+        <v>299.8790926087445</v>
       </c>
       <c r="C164" t="n">
-        <v>301.57145376365</v>
+        <v>302.6167597554335</v>
       </c>
       <c r="D164" t="n">
-        <v>292.3530024013792</v>
+        <v>298.8636475324957</v>
       </c>
       <c r="E164" t="n">
-        <v>300.625732421875</v>
+        <v>301.6411437988281</v>
       </c>
       <c r="F164" t="n">
-        <v>9327000</v>
+        <v>7874400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B165" t="n">
-        <v>299.8790926087445</v>
+        <v>303.3135932887391</v>
       </c>
       <c r="C165" t="n">
-        <v>302.6167597554335</v>
+        <v>306.0711901040885</v>
       </c>
       <c r="D165" t="n">
-        <v>298.8636475324957</v>
+        <v>302.4773640852478</v>
       </c>
       <c r="E165" t="n">
-        <v>301.6411437988281</v>
+        <v>305.0059814453125</v>
       </c>
       <c r="F165" t="n">
-        <v>7874400</v>
+        <v>5973900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B166" t="n">
-        <v>303.3135932887391</v>
+        <v>307.1065011172144</v>
       </c>
       <c r="C166" t="n">
-        <v>306.0711901040885</v>
+        <v>308.5400455607295</v>
       </c>
       <c r="D166" t="n">
-        <v>302.4773640852478</v>
+        <v>304.0701916446211</v>
       </c>
       <c r="E166" t="n">
-        <v>305.0059814453125</v>
+        <v>305.3643493652344</v>
       </c>
       <c r="F166" t="n">
-        <v>5973900</v>
+        <v>7725400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B167" t="n">
-        <v>307.1065011172144</v>
+        <v>303.6321536663258</v>
       </c>
       <c r="C167" t="n">
-        <v>308.5400455607295</v>
+        <v>304.5281113223131</v>
       </c>
       <c r="D167" t="n">
-        <v>304.0701916446211</v>
+        <v>294.4236375305438</v>
       </c>
       <c r="E167" t="n">
-        <v>305.3643493652344</v>
+        <v>297.9378051757812</v>
       </c>
       <c r="F167" t="n">
-        <v>7725400</v>
+        <v>11779200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B168" t="n">
-        <v>303.6321536663258</v>
+        <v>296.2354906683788</v>
       </c>
       <c r="C168" t="n">
-        <v>304.5281113223131</v>
+        <v>299.7197941661088</v>
       </c>
       <c r="D168" t="n">
-        <v>294.4236375305438</v>
+        <v>294.4236455581874</v>
       </c>
       <c r="E168" t="n">
-        <v>297.9378051757812</v>
+        <v>295.3992614746094</v>
       </c>
       <c r="F168" t="n">
-        <v>11779200</v>
+        <v>9757700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B169" t="n">
-        <v>296.2354906683788</v>
+        <v>295.070728717322</v>
       </c>
       <c r="C169" t="n">
-        <v>299.7197941661088</v>
+        <v>298.5351328968941</v>
       </c>
       <c r="D169" t="n">
-        <v>294.4236455581874</v>
+        <v>293.8761285862639</v>
       </c>
       <c r="E169" t="n">
-        <v>295.3992614746094</v>
+        <v>297.9676818847656</v>
       </c>
       <c r="F169" t="n">
-        <v>9757700</v>
+        <v>13969000</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B170" t="n">
-        <v>295.070728717322</v>
+        <v>296.3549462063085</v>
       </c>
       <c r="C170" t="n">
-        <v>298.5351328968941</v>
+        <v>298.2065900448191</v>
       </c>
       <c r="D170" t="n">
-        <v>293.8761285862639</v>
+        <v>293.9457858606032</v>
       </c>
       <c r="E170" t="n">
-        <v>297.9676818847656</v>
+        <v>295.2499084472656</v>
       </c>
       <c r="F170" t="n">
-        <v>13969000</v>
+        <v>7930000</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B171" t="n">
-        <v>296.3549462063085</v>
+        <v>295.170270518017</v>
       </c>
       <c r="C171" t="n">
-        <v>298.2065900448191</v>
+        <v>300.7152977310929</v>
       </c>
       <c r="D171" t="n">
-        <v>293.9457858606032</v>
+        <v>293.9457758280521</v>
       </c>
       <c r="E171" t="n">
-        <v>295.2499084472656</v>
+        <v>299.6102600097656</v>
       </c>
       <c r="F171" t="n">
-        <v>7930000</v>
+        <v>8296200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B172" t="n">
-        <v>295.170270518017</v>
+        <v>298.5749714904202</v>
       </c>
       <c r="C172" t="n">
-        <v>300.7152977310929</v>
+        <v>300.6058008918799</v>
       </c>
       <c r="D172" t="n">
-        <v>293.9457758280521</v>
+        <v>295.2300241797341</v>
       </c>
       <c r="E172" t="n">
-        <v>299.6102600097656</v>
+        <v>299.5007934570312</v>
       </c>
       <c r="F172" t="n">
-        <v>8296200</v>
+        <v>7003900</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B173" t="n">
-        <v>298.5749714904202</v>
+        <v>304.3688300919619</v>
       </c>
       <c r="C173" t="n">
-        <v>300.6058008918799</v>
+        <v>311.5066879726736</v>
       </c>
       <c r="D173" t="n">
-        <v>295.2300241797341</v>
+        <v>303.0746723882986</v>
       </c>
       <c r="E173" t="n">
-        <v>299.5007934570312</v>
+        <v>309.4957580566406</v>
       </c>
       <c r="F173" t="n">
-        <v>7003900</v>
+        <v>10345200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B174" t="n">
-        <v>304.3688300919619</v>
+        <v>312.8805189963161</v>
       </c>
       <c r="C174" t="n">
-        <v>311.5066879726736</v>
+        <v>313.5873263681962</v>
       </c>
       <c r="D174" t="n">
-        <v>303.0746723882986</v>
+        <v>308.211549706599</v>
       </c>
       <c r="E174" t="n">
-        <v>309.4957580566406</v>
+        <v>310.9691162109375</v>
       </c>
       <c r="F174" t="n">
-        <v>10345200</v>
+        <v>9118800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B175" t="n">
-        <v>312.8805189963161</v>
+        <v>311.8451695343703</v>
       </c>
       <c r="C175" t="n">
-        <v>313.5873263681962</v>
+        <v>314.881479064701</v>
       </c>
       <c r="D175" t="n">
-        <v>308.211549706599</v>
+        <v>309.3862455138746</v>
       </c>
       <c r="E175" t="n">
-        <v>310.9691162109375</v>
+        <v>309.7147521972656</v>
       </c>
       <c r="F175" t="n">
-        <v>9118800</v>
+        <v>6827000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B176" t="n">
-        <v>311.8451695343703</v>
+        <v>312.1040028799189</v>
       </c>
       <c r="C176" t="n">
-        <v>314.881479064701</v>
+        <v>315.0009559692908</v>
       </c>
       <c r="D176" t="n">
-        <v>309.3862455138746</v>
+        <v>307.6241841525692</v>
       </c>
       <c r="E176" t="n">
-        <v>309.7147521972656</v>
+        <v>311.2976379394531</v>
       </c>
       <c r="F176" t="n">
-        <v>6827000</v>
+        <v>11594600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B177" t="n">
-        <v>312.1040028799189</v>
+        <v>311.1582462393224</v>
       </c>
       <c r="C177" t="n">
-        <v>315.0009559692908</v>
+        <v>313.3384270822022</v>
       </c>
       <c r="D177" t="n">
-        <v>307.6241841525692</v>
+        <v>307.6440785979976</v>
       </c>
       <c r="E177" t="n">
-        <v>311.2976379394531</v>
+        <v>307.7536010742188</v>
       </c>
       <c r="F177" t="n">
-        <v>11594600</v>
+        <v>7446200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B178" t="n">
-        <v>311.1582462393224</v>
+        <v>308.1717081621576</v>
       </c>
       <c r="C178" t="n">
-        <v>313.3384270822022</v>
+        <v>313.3085706612414</v>
       </c>
       <c r="D178" t="n">
-        <v>307.6440785979976</v>
+        <v>307.4947650619962</v>
       </c>
       <c r="E178" t="n">
-        <v>307.7536010742188</v>
+        <v>312.0840759277344</v>
       </c>
       <c r="F178" t="n">
-        <v>7446200</v>
+        <v>9116600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B179" t="n">
-        <v>308.1717081621576</v>
+        <v>314.5529794375797</v>
       </c>
       <c r="C179" t="n">
-        <v>313.3085706612414</v>
+        <v>319.8590627688811</v>
       </c>
       <c r="D179" t="n">
-        <v>307.4947650619962</v>
+        <v>314.1348496322589</v>
       </c>
       <c r="E179" t="n">
-        <v>312.0840759277344</v>
+        <v>319.2816772460938</v>
       </c>
       <c r="F179" t="n">
-        <v>9116600</v>
+        <v>7426200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B180" t="n">
-        <v>314.5529794375797</v>
+        <v>322.4673390673774</v>
       </c>
       <c r="C180" t="n">
-        <v>319.8590627688811</v>
+        <v>324.4583697274161</v>
       </c>
       <c r="D180" t="n">
-        <v>314.1348496322589</v>
+        <v>317.4101041776777</v>
       </c>
       <c r="E180" t="n">
-        <v>319.2816772460938</v>
+        <v>317.9675903320312</v>
       </c>
       <c r="F180" t="n">
-        <v>7426200</v>
+        <v>7988900</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B181" t="n">
-        <v>322.4673390673774</v>
+        <v>322.8455866314347</v>
       </c>
       <c r="C181" t="n">
-        <v>324.4583697274161</v>
+        <v>330.2621874699331</v>
       </c>
       <c r="D181" t="n">
-        <v>317.4101041776777</v>
+        <v>322.5668435738929</v>
       </c>
       <c r="E181" t="n">
-        <v>317.9675903320312</v>
+        <v>329.6549377441406</v>
       </c>
       <c r="F181" t="n">
-        <v>7988900</v>
+        <v>11094900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B182" t="n">
-        <v>322.8455866314347</v>
+        <v>330.6902497468859</v>
       </c>
       <c r="C182" t="n">
-        <v>330.2621874699331</v>
+        <v>336.2551763704633</v>
       </c>
       <c r="D182" t="n">
-        <v>322.5668435738929</v>
+        <v>330.0133066656099</v>
       </c>
       <c r="E182" t="n">
-        <v>329.6549377441406</v>
+        <v>331.9645080566406</v>
       </c>
       <c r="F182" t="n">
-        <v>11094900</v>
+        <v>12246400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B183" t="n">
-        <v>330.6902497468859</v>
+        <v>335.4388795655989</v>
       </c>
       <c r="C183" t="n">
-        <v>336.2551763704633</v>
+        <v>336.5737511659094</v>
       </c>
       <c r="D183" t="n">
-        <v>330.0133066656099</v>
+        <v>322.7062308624821</v>
       </c>
       <c r="E183" t="n">
-        <v>331.9645080566406</v>
+        <v>323.761474609375</v>
       </c>
       <c r="F183" t="n">
-        <v>12246400</v>
+        <v>20111000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B184" t="n">
-        <v>335.4388795655989</v>
+        <v>328.221392261561</v>
       </c>
       <c r="C184" t="n">
-        <v>336.5737511659094</v>
+        <v>331.2776010100568</v>
       </c>
       <c r="D184" t="n">
-        <v>322.7062308624821</v>
+        <v>325.2846101022313</v>
       </c>
       <c r="E184" t="n">
-        <v>323.761474609375</v>
+        <v>329.993408203125</v>
       </c>
       <c r="F184" t="n">
-        <v>20111000</v>
+        <v>10182500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B185" t="n">
-        <v>328.221392261561</v>
+        <v>327.9924099173137</v>
       </c>
       <c r="C185" t="n">
-        <v>331.2776010100568</v>
+        <v>333.8659438033595</v>
       </c>
       <c r="D185" t="n">
-        <v>325.2846101022313</v>
+        <v>325.7425357353925</v>
       </c>
       <c r="E185" t="n">
-        <v>329.993408203125</v>
+        <v>332.6414794921875</v>
       </c>
       <c r="F185" t="n">
-        <v>10182500</v>
+        <v>7582200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B186" t="n">
-        <v>327.9924099173137</v>
+        <v>331.5762891678024</v>
       </c>
       <c r="C186" t="n">
-        <v>333.8659438033595</v>
+        <v>333.0297330031709</v>
       </c>
       <c r="D186" t="n">
-        <v>325.7425357353925</v>
+        <v>328.291070440402</v>
       </c>
       <c r="E186" t="n">
-        <v>332.6414794921875</v>
+        <v>331.95458984375</v>
       </c>
       <c r="F186" t="n">
-        <v>7582200</v>
+        <v>7907400</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B187" t="n">
-        <v>331.5762891678024</v>
+        <v>333.4577793441399</v>
       </c>
       <c r="C187" t="n">
-        <v>333.0297330031709</v>
+        <v>341.909724468194</v>
       </c>
       <c r="D187" t="n">
-        <v>328.291070440402</v>
+        <v>333.2586945227413</v>
       </c>
       <c r="E187" t="n">
-        <v>331.95458984375</v>
+        <v>333.6170654296875</v>
       </c>
       <c r="F187" t="n">
-        <v>7907400</v>
+        <v>10043100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B188" t="n">
-        <v>333.4577793441399</v>
+        <v>334.4931229022353</v>
       </c>
       <c r="C188" t="n">
-        <v>341.909724468194</v>
+        <v>334.8913229247855</v>
       </c>
       <c r="D188" t="n">
-        <v>333.2586945227413</v>
+        <v>326.0312433050061</v>
       </c>
       <c r="E188" t="n">
-        <v>333.6170654296875</v>
+        <v>327.5742797851562</v>
       </c>
       <c r="F188" t="n">
-        <v>10043100</v>
+        <v>17640900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B189" t="n">
-        <v>334.4931229022353</v>
+        <v>326.8077430430495</v>
       </c>
       <c r="C189" t="n">
-        <v>334.8913229247855</v>
+        <v>330.8993264933345</v>
       </c>
       <c r="D189" t="n">
-        <v>326.0312433050061</v>
+        <v>325.7325999471821</v>
       </c>
       <c r="E189" t="n">
-        <v>327.5742797851562</v>
+        <v>327.9127807617188</v>
       </c>
       <c r="F189" t="n">
-        <v>17640900</v>
+        <v>7981800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B190" t="n">
-        <v>326.8077430430495</v>
+        <v>327.4150312810326</v>
       </c>
       <c r="C190" t="n">
-        <v>330.8993264933345</v>
+        <v>328.9580677951163</v>
       </c>
       <c r="D190" t="n">
-        <v>325.7325999471821</v>
+        <v>325.2149206632551</v>
       </c>
       <c r="E190" t="n">
-        <v>327.9127807617188</v>
+        <v>325.8619995117188</v>
       </c>
       <c r="F190" t="n">
-        <v>7981800</v>
+        <v>8080100</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B191" t="n">
-        <v>327.4150312810326</v>
+        <v>326.8973584256916</v>
       </c>
       <c r="C191" t="n">
-        <v>328.9580677951163</v>
+        <v>334.1347741939035</v>
       </c>
       <c r="D191" t="n">
-        <v>325.2149206632551</v>
+        <v>323.5524415571975</v>
       </c>
       <c r="E191" t="n">
-        <v>325.8619995117188</v>
+        <v>332.5718078613281</v>
       </c>
       <c r="F191" t="n">
-        <v>8080100</v>
+        <v>15210200</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B192" t="n">
-        <v>326.8973584256916</v>
+        <v>336.5040683580973</v>
       </c>
       <c r="C192" t="n">
-        <v>334.1347741939035</v>
+        <v>338.4751995750331</v>
       </c>
       <c r="D192" t="n">
-        <v>323.5524415571975</v>
+        <v>330.2820977776739</v>
       </c>
       <c r="E192" t="n">
-        <v>332.5718078613281</v>
+        <v>332.9700012207031</v>
       </c>
       <c r="F192" t="n">
-        <v>15210200</v>
+        <v>8413900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,25 +5435,25 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B193" t="n">
-        <v>336.5040683580973</v>
+        <v>335</v>
       </c>
       <c r="C193" t="n">
-        <v>338.4751995750331</v>
+        <v>339.7200012207031</v>
       </c>
       <c r="D193" t="n">
-        <v>330.2820977776739</v>
+        <v>334.1099853515625</v>
       </c>
       <c r="E193" t="n">
-        <v>332.9700012207031</v>
+        <v>337.7200012207031</v>
       </c>
       <c r="F193" t="n">
-        <v>8413900</v>
+        <v>8673500</v>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5461,25 +5461,25 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B194" t="n">
-        <v>335</v>
+        <v>340.9800109863281</v>
       </c>
       <c r="C194" t="n">
-        <v>339.7200012207031</v>
+        <v>341.3999938964844</v>
       </c>
       <c r="D194" t="n">
-        <v>334.1099853515625</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E194" t="n">
-        <v>337.7200012207031</v>
+        <v>339.2200012207031</v>
       </c>
       <c r="F194" t="n">
-        <v>8673500</v>
+        <v>7115800</v>
       </c>
       <c r="G194" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B195" t="n">
-        <v>340.9800109863281</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="C195" t="n">
-        <v>341.3999938964844</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="D195" t="n">
-        <v>337.0899963378906</v>
+        <v>330.1300048828125</v>
       </c>
       <c r="E195" t="n">
-        <v>339.2200012207031</v>
+        <v>330.6199951171875</v>
       </c>
       <c r="F195" t="n">
-        <v>7115800</v>
+        <v>18505200</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B196" t="n">
-        <v>336.5299987792969</v>
+        <v>331.4599914550781</v>
       </c>
       <c r="C196" t="n">
-        <v>336.5299987792969</v>
+        <v>337</v>
       </c>
       <c r="D196" t="n">
-        <v>330.1300048828125</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="E196" t="n">
-        <v>330.6199951171875</v>
+        <v>335.4700012207031</v>
       </c>
       <c r="F196" t="n">
-        <v>18505200</v>
+        <v>15570600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B197" t="n">
-        <v>331.4599914550781</v>
+        <v>337.4700012207031</v>
       </c>
       <c r="C197" t="n">
-        <v>337</v>
+        <v>338.5899963378906</v>
       </c>
       <c r="D197" t="n">
-        <v>330.8099975585938</v>
+        <v>335.7699890136719</v>
       </c>
       <c r="E197" t="n">
-        <v>335.4700012207031</v>
+        <v>336.4700012207031</v>
       </c>
       <c r="F197" t="n">
-        <v>15570600</v>
+        <v>6299000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B198" t="n">
-        <v>337.4700012207031</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="C198" t="n">
-        <v>338.5899963378906</v>
+        <v>338.3500061035156</v>
       </c>
       <c r="D198" t="n">
-        <v>335.7699890136719</v>
+        <v>332.5</v>
       </c>
       <c r="E198" t="n">
-        <v>336.4700012207031</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="F198" t="n">
-        <v>6299000</v>
+        <v>7120300</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B199" t="n">
-        <v>338.3399963378906</v>
+        <v>327</v>
       </c>
       <c r="C199" t="n">
-        <v>338.3500061035156</v>
+        <v>344.7300109863281</v>
       </c>
       <c r="D199" t="n">
-        <v>332.5</v>
+        <v>325.75</v>
       </c>
       <c r="E199" t="n">
-        <v>334.5299987792969</v>
+        <v>342.8900146484375</v>
       </c>
       <c r="F199" t="n">
-        <v>7120300</v>
+        <v>14537900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>327</v>
+        <v>345.8500061035156</v>
       </c>
       <c r="C200" t="n">
-        <v>344.7300109863281</v>
+        <v>351.239990234375</v>
       </c>
       <c r="D200" t="n">
-        <v>325.75</v>
+        <v>344.0499877929688</v>
       </c>
       <c r="E200" t="n">
-        <v>342.8900146484375</v>
+        <v>346.9100036621094</v>
       </c>
       <c r="F200" t="n">
-        <v>14537900</v>
+        <v>10750000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B201" t="n">
-        <v>345.8500061035156</v>
+        <v>349.2799987792969</v>
       </c>
       <c r="C201" t="n">
-        <v>351.239990234375</v>
+        <v>349.3399963378906</v>
       </c>
       <c r="D201" t="n">
-        <v>344.0499877929688</v>
+        <v>341.1099853515625</v>
       </c>
       <c r="E201" t="n">
-        <v>346.9100036621094</v>
+        <v>343.1499938964844</v>
       </c>
       <c r="F201" t="n">
-        <v>10750000</v>
+        <v>12432400</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B202" t="n">
-        <v>349.2799987792969</v>
+        <v>339.0299987792969</v>
       </c>
       <c r="C202" t="n">
-        <v>349.3399963378906</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="D202" t="n">
-        <v>341.1099853515625</v>
+        <v>335.0499877929688</v>
       </c>
       <c r="E202" t="n">
-        <v>343.1499938964844</v>
+        <v>341.1000061035156</v>
       </c>
       <c r="F202" t="n">
-        <v>12432400</v>
+        <v>9250900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B203" t="n">
-        <v>339.0299987792969</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="C203" t="n">
-        <v>346.1300048828125</v>
+        <v>344.260009765625</v>
       </c>
       <c r="D203" t="n">
-        <v>335.0499877929688</v>
+        <v>337.3699951171875</v>
       </c>
       <c r="E203" t="n">
-        <v>341.1000061035156</v>
+        <v>338.8699951171875</v>
       </c>
       <c r="F203" t="n">
-        <v>9250900</v>
+        <v>7723300</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B204" t="n">
-        <v>341.7999877929688</v>
+        <v>340.1199951171875</v>
       </c>
       <c r="C204" t="n">
-        <v>344.260009765625</v>
+        <v>345.739990234375</v>
       </c>
       <c r="D204" t="n">
-        <v>337.3699951171875</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E204" t="n">
-        <v>338.8699951171875</v>
+        <v>345.2300109863281</v>
       </c>
       <c r="F204" t="n">
-        <v>7723300</v>
+        <v>6015300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B205" t="n">
-        <v>340.1199951171875</v>
+        <v>345.0700073242188</v>
       </c>
       <c r="C205" t="n">
-        <v>345.739990234375</v>
+        <v>349.0700073242188</v>
       </c>
       <c r="D205" t="n">
-        <v>337.2999877929688</v>
+        <v>344.25</v>
       </c>
       <c r="E205" t="n">
-        <v>345.2300109863281</v>
+        <v>348.2099914550781</v>
       </c>
       <c r="F205" t="n">
-        <v>6015300</v>
+        <v>8040200</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B206" t="n">
-        <v>345.0700073242188</v>
+        <v>346.5799865722656</v>
       </c>
       <c r="C206" t="n">
-        <v>349.0700073242188</v>
+        <v>349.9200134277344</v>
       </c>
       <c r="D206" t="n">
-        <v>344.25</v>
+        <v>345.4200134277344</v>
       </c>
       <c r="E206" t="n">
-        <v>348.2099914550781</v>
+        <v>349.8999938964844</v>
       </c>
       <c r="F206" t="n">
-        <v>8040200</v>
+        <v>10913000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B207" t="n">
-        <v>346.5799865722656</v>
+        <v>350.6400146484375</v>
       </c>
       <c r="C207" t="n">
-        <v>349.9200134277344</v>
+        <v>353.3699951171875</v>
       </c>
       <c r="D207" t="n">
-        <v>345.4200134277344</v>
+        <v>347.5</v>
       </c>
       <c r="E207" t="n">
-        <v>349.8999938964844</v>
+        <v>353.2099914550781</v>
       </c>
       <c r="F207" t="n">
-        <v>10913000</v>
+        <v>7520800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B208" t="n">
-        <v>350.6400146484375</v>
+        <v>357.8900146484375</v>
       </c>
       <c r="C208" t="n">
-        <v>353.3699951171875</v>
+        <v>359.0499877929688</v>
       </c>
       <c r="D208" t="n">
-        <v>347.5</v>
+        <v>352.5799865722656</v>
       </c>
       <c r="E208" t="n">
-        <v>353.2099914550781</v>
+        <v>356.2000122070312</v>
       </c>
       <c r="F208" t="n">
-        <v>7520800</v>
+        <v>7884900</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B209" t="n">
-        <v>357.8900146484375</v>
+        <v>357.2999877929688</v>
       </c>
       <c r="C209" t="n">
-        <v>359.0499877929688</v>
+        <v>359.2999877929688</v>
       </c>
       <c r="D209" t="n">
-        <v>352.5799865722656</v>
+        <v>354.1499938964844</v>
       </c>
       <c r="E209" t="n">
-        <v>356.2000122070312</v>
+        <v>357.3099975585938</v>
       </c>
       <c r="F209" t="n">
-        <v>7884900</v>
+        <v>6533800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B210" t="n">
-        <v>357.2999877929688</v>
+        <v>356.5</v>
       </c>
       <c r="C210" t="n">
-        <v>359.2999877929688</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D210" t="n">
-        <v>354.1499938964844</v>
+        <v>343.7799987792969</v>
       </c>
       <c r="E210" t="n">
-        <v>357.3099975585938</v>
+        <v>344.7099914550781</v>
       </c>
       <c r="F210" t="n">
-        <v>6533800</v>
+        <v>8265300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B211" t="n">
-        <v>356.5</v>
+        <v>347.5400085449219</v>
       </c>
       <c r="C211" t="n">
-        <v>357.3699951171875</v>
+        <v>352.2799987792969</v>
       </c>
       <c r="D211" t="n">
-        <v>343.7799987792969</v>
+        <v>345.3699951171875</v>
       </c>
       <c r="E211" t="n">
-        <v>344.7099914550781</v>
+        <v>350.8500061035156</v>
       </c>
       <c r="F211" t="n">
-        <v>8265300</v>
+        <v>7606500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B212" t="n">
-        <v>347.5400085449219</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C212" t="n">
-        <v>352.2799987792969</v>
+        <v>354.4700012207031</v>
       </c>
       <c r="D212" t="n">
-        <v>345.3699951171875</v>
+        <v>349.7000122070312</v>
       </c>
       <c r="E212" t="n">
-        <v>350.8500061035156</v>
+        <v>351.7900085449219</v>
       </c>
       <c r="F212" t="n">
-        <v>7606500</v>
+        <v>6603400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B213" t="n">
-        <v>353.2999877929688</v>
+        <v>353.75</v>
       </c>
       <c r="C213" t="n">
-        <v>354.4700012207031</v>
+        <v>355.6199951171875</v>
       </c>
       <c r="D213" t="n">
-        <v>349.7000122070312</v>
+        <v>350.8399963378906</v>
       </c>
       <c r="E213" t="n">
-        <v>351.7900085449219</v>
+        <v>352.6400146484375</v>
       </c>
       <c r="F213" t="n">
-        <v>6603400</v>
+        <v>6436600</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B214" t="n">
-        <v>353.75</v>
+        <v>355</v>
       </c>
       <c r="C214" t="n">
-        <v>355.6199951171875</v>
+        <v>363</v>
       </c>
       <c r="D214" t="n">
-        <v>350.8399963378906</v>
+        <v>353.8699951171875</v>
       </c>
       <c r="E214" t="n">
-        <v>352.6400146484375</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F214" t="n">
-        <v>6436600</v>
+        <v>8477200</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B215" t="n">
-        <v>355</v>
+        <v>358.9700012207031</v>
       </c>
       <c r="C215" t="n">
-        <v>363</v>
+        <v>362.1700134277344</v>
       </c>
       <c r="D215" t="n">
-        <v>353.8699951171875</v>
+        <v>358.2000122070312</v>
       </c>
       <c r="E215" t="n">
-        <v>357.5199890136719</v>
+        <v>359.239990234375</v>
       </c>
       <c r="F215" t="n">
-        <v>8477200</v>
+        <v>5269500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B216" t="n">
-        <v>358.9700012207031</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="C216" t="n">
-        <v>362.1700134277344</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="D216" t="n">
-        <v>358.2000122070312</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="E216" t="n">
-        <v>359.239990234375</v>
+        <v>356.2999877929688</v>
       </c>
       <c r="F216" t="n">
-        <v>5269500</v>
+        <v>5820100</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B217" t="n">
-        <v>362.8099975585938</v>
+        <v>355.760009765625</v>
       </c>
       <c r="C217" t="n">
-        <v>362.8099975585938</v>
+        <v>358.8500061035156</v>
       </c>
       <c r="D217" t="n">
-        <v>354.9500122070312</v>
+        <v>353.3299865722656</v>
       </c>
       <c r="E217" t="n">
-        <v>356.2999877929688</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F217" t="n">
-        <v>5820100</v>
+        <v>4566200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B218" t="n">
-        <v>355.760009765625</v>
+        <v>357.9599914550781</v>
       </c>
       <c r="C218" t="n">
-        <v>358.8500061035156</v>
+        <v>359.989990234375</v>
       </c>
       <c r="D218" t="n">
-        <v>353.3299865722656</v>
+        <v>356.5</v>
       </c>
       <c r="E218" t="n">
-        <v>357.5199890136719</v>
+        <v>359.7900085449219</v>
       </c>
       <c r="F218" t="n">
-        <v>4566200</v>
+        <v>5327500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B219" t="n">
-        <v>357.9599914550781</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="C219" t="n">
-        <v>359.989990234375</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="D219" t="n">
-        <v>356.5</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="E219" t="n">
-        <v>359.7900085449219</v>
+        <v>362.0400085449219</v>
       </c>
       <c r="F219" t="n">
-        <v>5327500</v>
+        <v>4576500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B220" t="n">
-        <v>360.0499877929688</v>
+        <v>362.9700012207031</v>
       </c>
       <c r="C220" t="n">
-        <v>363.1199951171875</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="D220" t="n">
-        <v>358.6000061035156</v>
+        <v>361.2999877929688</v>
       </c>
       <c r="E220" t="n">
-        <v>362.0400085449219</v>
+        <v>365.1799926757812</v>
       </c>
       <c r="F220" t="n">
-        <v>4576500</v>
+        <v>4366800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B221" t="n">
-        <v>362.9700012207031</v>
+        <v>366.5</v>
       </c>
       <c r="C221" t="n">
-        <v>366.0899963378906</v>
+        <v>366.5</v>
       </c>
       <c r="D221" t="n">
-        <v>361.2999877929688</v>
+        <v>361.5199890136719</v>
       </c>
       <c r="E221" t="n">
-        <v>365.1799926757812</v>
+        <v>363.1099853515625</v>
       </c>
       <c r="F221" t="n">
-        <v>4366800</v>
+        <v>5102700</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B222" t="n">
-        <v>366.5</v>
+        <v>363</v>
       </c>
       <c r="C222" t="n">
-        <v>366.5</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="D222" t="n">
-        <v>361.5199890136719</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="E222" t="n">
-        <v>363.1099853515625</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="F222" t="n">
-        <v>5102700</v>
+        <v>5058600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B223" t="n">
-        <v>363</v>
+        <v>361.9400024414062</v>
       </c>
       <c r="C223" t="n">
-        <v>365.8999938964844</v>
+        <v>365.75</v>
       </c>
       <c r="D223" t="n">
-        <v>361.4500122070312</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="E223" t="n">
-        <v>362.8399963378906</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="F223" t="n">
-        <v>5058600</v>
+        <v>5282600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B224" t="n">
-        <v>361.9400024414062</v>
+        <v>362.3399963378906</v>
       </c>
       <c r="C224" t="n">
-        <v>365.75</v>
+        <v>363.5700073242188</v>
       </c>
       <c r="D224" t="n">
-        <v>360.9599914550781</v>
+        <v>359.2699890136719</v>
       </c>
       <c r="E224" t="n">
-        <v>360.9599914550781</v>
+        <v>363.25</v>
       </c>
       <c r="F224" t="n">
-        <v>5282600</v>
+        <v>5525100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B225" t="n">
-        <v>362.3399963378906</v>
+        <v>363.010009765625</v>
       </c>
       <c r="C225" t="n">
-        <v>363.5700073242188</v>
+        <v>363.0499877929688</v>
       </c>
       <c r="D225" t="n">
-        <v>359.2699890136719</v>
+        <v>355.6499938964844</v>
       </c>
       <c r="E225" t="n">
-        <v>363.25</v>
+        <v>357.260009765625</v>
       </c>
       <c r="F225" t="n">
-        <v>5525100</v>
+        <v>6696200</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B226" t="n">
-        <v>363.010009765625</v>
+        <v>357.6000061035156</v>
       </c>
       <c r="C226" t="n">
-        <v>363.0499877929688</v>
+        <v>357.9500122070312</v>
       </c>
       <c r="D226" t="n">
-        <v>355.6499938964844</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E226" t="n">
-        <v>357.260009765625</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="F226" t="n">
-        <v>6696200</v>
+        <v>6799700</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B227" t="n">
-        <v>357.6000061035156</v>
+        <v>354.0700073242188</v>
       </c>
       <c r="C227" t="n">
-        <v>357.9500122070312</v>
+        <v>356.8599853515625</v>
       </c>
       <c r="D227" t="n">
-        <v>351.5499877929688</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="E227" t="n">
-        <v>351.5499877929688</v>
+        <v>351.5799865722656</v>
       </c>
       <c r="F227" t="n">
-        <v>6799700</v>
+        <v>8112100</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B228" t="n">
-        <v>354.0700073242188</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C228" t="n">
-        <v>356.8599853515625</v>
+        <v>358.2799987792969</v>
       </c>
       <c r="D228" t="n">
-        <v>350.3699951171875</v>
+        <v>352.8200073242188</v>
       </c>
       <c r="E228" t="n">
-        <v>351.5799865722656</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="F228" t="n">
-        <v>8112100</v>
+        <v>4394400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B229" t="n">
-        <v>353.2999877929688</v>
+        <v>357</v>
       </c>
       <c r="C229" t="n">
-        <v>358.2799987792969</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D229" t="n">
-        <v>352.8200073242188</v>
+        <v>353.0700073242188</v>
       </c>
       <c r="E229" t="n">
-        <v>356.3900146484375</v>
+        <v>356.6900024414062</v>
       </c>
       <c r="F229" t="n">
-        <v>4394400</v>
+        <v>4298000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B230" t="n">
-        <v>357</v>
+        <v>356.5</v>
       </c>
       <c r="C230" t="n">
-        <v>357.3699951171875</v>
+        <v>358.3500061035156</v>
       </c>
       <c r="D230" t="n">
-        <v>353.0700073242188</v>
+        <v>354.6000061035156</v>
       </c>
       <c r="E230" t="n">
-        <v>356.6900024414062</v>
+        <v>356.5</v>
       </c>
       <c r="F230" t="n">
-        <v>4298000</v>
+        <v>5796500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B231" t="n">
-        <v>356.5</v>
+        <v>354.6799926757812</v>
       </c>
       <c r="C231" t="n">
-        <v>358.3500061035156</v>
+        <v>357.5700073242188</v>
       </c>
       <c r="D231" t="n">
-        <v>354.6000061035156</v>
+        <v>352.2300109863281</v>
       </c>
       <c r="E231" t="n">
-        <v>356.5</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="F231" t="n">
-        <v>5796500</v>
+        <v>5209900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B232" t="n">
-        <v>354.6799926757812</v>
+        <v>355.6700134277344</v>
       </c>
       <c r="C232" t="n">
-        <v>357.5700073242188</v>
+        <v>358.7300109863281</v>
       </c>
       <c r="D232" t="n">
-        <v>352.2300109863281</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="E232" t="n">
-        <v>354.2200012207031</v>
+        <v>357.6199951171875</v>
       </c>
       <c r="F232" t="n">
-        <v>5209900</v>
+        <v>3914500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B233" t="n">
-        <v>355.6700134277344</v>
+        <v>355.8999938964844</v>
       </c>
       <c r="C233" t="n">
-        <v>358.7300109863281</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="D233" t="n">
-        <v>354.2200012207031</v>
+        <v>354.7699890136719</v>
       </c>
       <c r="E233" t="n">
-        <v>357.6199951171875</v>
+        <v>356.0199890136719</v>
       </c>
       <c r="F233" t="n">
-        <v>3914500</v>
+        <v>7962900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B234" t="n">
-        <v>355.8999938964844</v>
+        <v>355.7300109863281</v>
       </c>
       <c r="C234" t="n">
-        <v>357.7699890136719</v>
+        <v>359.9299926757812</v>
       </c>
       <c r="D234" t="n">
-        <v>354.7699890136719</v>
+        <v>354.1199951171875</v>
       </c>
       <c r="E234" t="n">
-        <v>356.0199890136719</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="F234" t="n">
-        <v>7962900</v>
+        <v>5079000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B235" t="n">
-        <v>355.7300109863281</v>
+        <v>357.5499877929688</v>
       </c>
       <c r="C235" t="n">
-        <v>359.9299926757812</v>
+        <v>361.4700012207031</v>
       </c>
       <c r="D235" t="n">
-        <v>354.1199951171875</v>
+        <v>353.7900085449219</v>
       </c>
       <c r="E235" t="n">
-        <v>354.9500122070312</v>
+        <v>356.2200012207031</v>
       </c>
       <c r="F235" t="n">
-        <v>5079000</v>
+        <v>5341400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B236" t="n">
-        <v>357.5499877929688</v>
+        <v>358.6799926757812</v>
       </c>
       <c r="C236" t="n">
-        <v>361.4700012207031</v>
+        <v>362.8500061035156</v>
       </c>
       <c r="D236" t="n">
-        <v>353.7900085449219</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="E236" t="n">
-        <v>356.2200012207031</v>
+        <v>362.0599975585938</v>
       </c>
       <c r="F236" t="n">
-        <v>5341400</v>
+        <v>5414200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B237" t="n">
-        <v>358.6799926757812</v>
+        <v>361</v>
       </c>
       <c r="C237" t="n">
-        <v>362.8500061035156</v>
+        <v>362.8599853515625</v>
       </c>
       <c r="D237" t="n">
-        <v>356.3900146484375</v>
+        <v>355.2000122070312</v>
       </c>
       <c r="E237" t="n">
-        <v>362.0599975585938</v>
+        <v>358.6400146484375</v>
       </c>
       <c r="F237" t="n">
-        <v>5414200</v>
+        <v>4873500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B238" t="n">
-        <v>361</v>
+        <v>357.1000061035156</v>
       </c>
       <c r="C238" t="n">
-        <v>362.8599853515625</v>
+        <v>358.5499877929688</v>
       </c>
       <c r="D238" t="n">
-        <v>355.2000122070312</v>
+        <v>353.2300109863281</v>
       </c>
       <c r="E238" t="n">
-        <v>358.6400146484375</v>
+        <v>353.510009765625</v>
       </c>
       <c r="F238" t="n">
-        <v>4873500</v>
+        <v>5631400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B239" t="n">
-        <v>357.1000061035156</v>
+        <v>352</v>
       </c>
       <c r="C239" t="n">
-        <v>358.5499877929688</v>
+        <v>356.3299865722656</v>
       </c>
       <c r="D239" t="n">
-        <v>353.2300109863281</v>
+        <v>348.6900024414062</v>
       </c>
       <c r="E239" t="n">
-        <v>353.510009765625</v>
+        <v>354.7099914550781</v>
       </c>
       <c r="F239" t="n">
-        <v>5631400</v>
+        <v>6318200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B240" t="n">
-        <v>352</v>
+        <v>353.510009765625</v>
       </c>
       <c r="C240" t="n">
-        <v>356.3299865722656</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="D240" t="n">
-        <v>348.6900024414062</v>
+        <v>351.1199951171875</v>
       </c>
       <c r="E240" t="n">
-        <v>354.7099914550781</v>
+        <v>353.5599975585938</v>
       </c>
       <c r="F240" t="n">
-        <v>6318200</v>
+        <v>4184200</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B241" t="n">
-        <v>353.510009765625</v>
+        <v>358.3200073242188</v>
       </c>
       <c r="C241" t="n">
-        <v>354.2200012207031</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="D241" t="n">
-        <v>351.1199951171875</v>
+        <v>354.7900085449219</v>
       </c>
       <c r="E241" t="n">
-        <v>353.5599975585938</v>
+        <v>356.2300109863281</v>
       </c>
       <c r="F241" t="n">
-        <v>4184200</v>
+        <v>5354600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B242" t="n">
-        <v>358.3200073242188</v>
+        <v>354.2300109863281</v>
       </c>
       <c r="C242" t="n">
-        <v>360.0499877929688</v>
+        <v>355.2799987792969</v>
       </c>
       <c r="D242" t="n">
-        <v>354.7900085449219</v>
+        <v>347.5499877929688</v>
       </c>
       <c r="E242" t="n">
-        <v>356.2300109863281</v>
+        <v>350.1300048828125</v>
       </c>
       <c r="F242" t="n">
-        <v>5354600</v>
+        <v>9609900</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B243" t="n">
-        <v>354.2300109863281</v>
+        <v>351</v>
       </c>
       <c r="C243" t="n">
-        <v>355.2799987792969</v>
+        <v>354.7000122070312</v>
       </c>
       <c r="D243" t="n">
-        <v>347.5499877929688</v>
+        <v>343.0700073242188</v>
       </c>
       <c r="E243" t="n">
-        <v>350.1300048828125</v>
+        <v>352.489990234375</v>
       </c>
       <c r="F243" t="n">
-        <v>9609900</v>
+        <v>14026500</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B244" t="n">
-        <v>351</v>
+        <v>353.3800048828125</v>
       </c>
       <c r="C244" t="n">
-        <v>354.7000122070312</v>
+        <v>355.6000061035156</v>
       </c>
       <c r="D244" t="n">
-        <v>343.0700073242188</v>
+        <v>344.6900024414062</v>
       </c>
       <c r="E244" t="n">
-        <v>352.489990234375</v>
+        <v>348.9200134277344</v>
       </c>
       <c r="F244" t="n">
-        <v>14026500</v>
+        <v>8303400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B245" t="n">
-        <v>353.3800048828125</v>
+        <v>352.25</v>
       </c>
       <c r="C245" t="n">
-        <v>355.6000061035156</v>
+        <v>353.489990234375</v>
       </c>
       <c r="D245" t="n">
-        <v>344.6900024414062</v>
+        <v>345.2699890136719</v>
       </c>
       <c r="E245" t="n">
-        <v>348.9200134277344</v>
+        <v>349.3099975585938</v>
       </c>
       <c r="F245" t="n">
-        <v>8303400</v>
+        <v>6480100</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B246" t="n">
-        <v>352.25</v>
+        <v>347.8900146484375</v>
       </c>
       <c r="C246" t="n">
-        <v>353.489990234375</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="D246" t="n">
-        <v>345.2699890136719</v>
+        <v>345.010009765625</v>
       </c>
       <c r="E246" t="n">
-        <v>349.3099975585938</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="F246" t="n">
-        <v>6480100</v>
+        <v>18312400</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B247" t="n">
-        <v>347.8900146484375</v>
+        <v>353.6700134277344</v>
       </c>
       <c r="C247" t="n">
-        <v>349.6700134277344</v>
+        <v>354.5</v>
       </c>
       <c r="D247" t="n">
-        <v>345.010009765625</v>
+        <v>350.0799865722656</v>
       </c>
       <c r="E247" t="n">
-        <v>349.6700134277344</v>
+        <v>352.0400085449219</v>
       </c>
       <c r="F247" t="n">
-        <v>18312400</v>
+        <v>6414700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B248" t="n">
-        <v>353.6700134277344</v>
+        <v>352</v>
       </c>
       <c r="C248" t="n">
-        <v>354.5</v>
+        <v>352.1000061035156</v>
       </c>
       <c r="D248" t="n">
-        <v>350.0799865722656</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E248" t="n">
-        <v>352.0400085449219</v>
+        <v>340</v>
       </c>
       <c r="F248" t="n">
-        <v>6414700</v>
+        <v>11485600</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B249" t="n">
-        <v>352</v>
+        <v>337.6099853515625</v>
       </c>
       <c r="C249" t="n">
-        <v>352.1000061035156</v>
+        <v>341.4400024414062</v>
       </c>
       <c r="D249" t="n">
-        <v>337.2999877929688</v>
+        <v>336.9800109863281</v>
       </c>
       <c r="E249" t="n">
-        <v>340</v>
+        <v>337.5299987792969</v>
       </c>
       <c r="F249" t="n">
-        <v>11485600</v>
+        <v>7068500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B250" t="n">
-        <v>337.6099853515625</v>
+        <v>338.1199951171875</v>
       </c>
       <c r="C250" t="n">
-        <v>341.4400024414062</v>
+        <v>339.3699951171875</v>
       </c>
       <c r="D250" t="n">
-        <v>336.9800109863281</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="E250" t="n">
-        <v>337.5299987792969</v>
+        <v>338.5599975585938</v>
       </c>
       <c r="F250" t="n">
-        <v>7068500</v>
+        <v>6934300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B251" t="n">
-        <v>338.1199951171875</v>
+        <v>340.7699890136719</v>
       </c>
       <c r="C251" t="n">
-        <v>339.3699951171875</v>
+        <v>343.3099975585938</v>
       </c>
       <c r="D251" t="n">
-        <v>335.2799987792969</v>
+        <v>338.6400146484375</v>
       </c>
       <c r="E251" t="n">
-        <v>338.5599975585938</v>
+        <v>343.0599975585938</v>
       </c>
       <c r="F251" t="n">
-        <v>6934300</v>
+        <v>11460300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B252" t="n">
-        <v>340.7699890136719</v>
+        <v>341.8299865722656</v>
       </c>
       <c r="C252" t="n">
-        <v>343.3099975585938</v>
+        <v>342</v>
       </c>
       <c r="D252" t="n">
-        <v>338.6400146484375</v>
+        <v>336.2999877929688</v>
       </c>
       <c r="E252" t="n">
-        <v>343.0599975585938</v>
+        <v>336.5899963378906</v>
       </c>
       <c r="F252" t="n">
-        <v>11460300</v>
+        <v>9790100</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10017,37 +10017,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>336.59</v>
+      </c>
+      <c r="D2" t="n">
         <v>343.06</v>
       </c>
-      <c r="D2" t="n">
-        <v>338.56</v>
-      </c>
       <c r="E2" t="n">
-        <v>340.765</v>
+        <v>341.83</v>
       </c>
       <c r="F2" t="n">
-        <v>343.265</v>
+        <v>342</v>
       </c>
       <c r="G2" t="n">
-        <v>338.64</v>
+        <v>336.3</v>
       </c>
       <c r="H2" t="n">
-        <v>9864277</v>
+        <v>9769705</v>
       </c>
       <c r="I2" t="n">
-        <v>7691509</v>
+        <v>7780034</v>
       </c>
       <c r="J2" t="n">
-        <v>911917383680</v>
+        <v>894718902272</v>
       </c>
       <c r="K2" t="n">
-        <v>14.704672</v>
+        <v>14.704675</v>
       </c>
       <c r="L2" t="n">
-        <v>13.728995</v>
+        <v>13.436978</v>
       </c>
       <c r="M2" t="n">
-        <v>23.33</v>
+        <v>22.89</v>
       </c>
       <c r="N2" t="n">
         <v>366.5</v>
@@ -10059,7 +10059,7 @@
         <v>0.975</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="R2" t="n">
         <v>0.34921002</v>
@@ -10087,7 +10087,7 @@
         <v>133.007</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.5792627</v>
+        <v>2.5306187</v>
       </c>
       <c r="Z2" t="n">
         <v>0.469</v>
@@ -10099,7 +10099,7 @@
         <v>186328006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>749845348352</v>
+        <v>732646866944</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:42</t>
+          <t>2026-09-29 13:24:38</t>
         </is>
       </c>
     </row>

--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B2" t="n">
-        <v>311.1082550854298</v>
+        <v>310.3134645283819</v>
       </c>
       <c r="C2" t="n">
-        <v>312.0404339863167</v>
+        <v>311.4516930034957</v>
       </c>
       <c r="D2" t="n">
-        <v>307.7720847183659</v>
+        <v>304.288708108424</v>
       </c>
       <c r="E2" t="n">
-        <v>309.7639770507812</v>
+        <v>309.5088500976562</v>
       </c>
       <c r="F2" t="n">
-        <v>6462400</v>
+        <v>11823300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B3" t="n">
-        <v>310.3134645283819</v>
+        <v>308.0763169713923</v>
       </c>
       <c r="C3" t="n">
-        <v>311.4516930034957</v>
+        <v>308.6846738574029</v>
       </c>
       <c r="D3" t="n">
-        <v>304.288708108424</v>
+        <v>301.6394603311547</v>
       </c>
       <c r="E3" t="n">
-        <v>309.5088500976562</v>
+        <v>304.8775024414062</v>
       </c>
       <c r="F3" t="n">
-        <v>11823300</v>
+        <v>9235200</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B4" t="n">
-        <v>308.0762861336198</v>
+        <v>304.1808160870063</v>
       </c>
       <c r="C4" t="n">
-        <v>308.6846429587351</v>
+        <v>304.7303016172636</v>
       </c>
       <c r="D4" t="n">
-        <v>301.6394301376976</v>
+        <v>300.393288685967</v>
       </c>
       <c r="E4" t="n">
-        <v>304.8774719238281</v>
+        <v>301.7767944335938</v>
       </c>
       <c r="F4" t="n">
-        <v>9235200</v>
+        <v>7600000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B5" t="n">
-        <v>304.1808160870063</v>
+        <v>302.7188095956571</v>
       </c>
       <c r="C5" t="n">
-        <v>304.7303016172636</v>
+        <v>305.809673335546</v>
       </c>
       <c r="D5" t="n">
-        <v>300.393288685967</v>
+        <v>302.4244230832239</v>
       </c>
       <c r="E5" t="n">
-        <v>301.7767944335938</v>
+        <v>304.2102661132812</v>
       </c>
       <c r="F5" t="n">
-        <v>7600000</v>
+        <v>6029900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,25 +573,25 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B6" t="n">
-        <v>302.7187488597389</v>
+        <v>305.8371035459471</v>
       </c>
       <c r="C6" t="n">
-        <v>305.8096119794931</v>
+        <v>307.3851288987199</v>
       </c>
       <c r="D6" t="n">
-        <v>302.4243624063698</v>
+        <v>300.8578215934895</v>
       </c>
       <c r="E6" t="n">
-        <v>304.210205078125</v>
+        <v>304.8511047363281</v>
       </c>
       <c r="F6" t="n">
-        <v>6029900</v>
+        <v>7214500</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -599,25 +599,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B7" t="n">
-        <v>305.8371035459471</v>
+        <v>305.0187502270194</v>
       </c>
       <c r="C7" t="n">
-        <v>307.3851288987199</v>
+        <v>305.6695130787729</v>
       </c>
       <c r="D7" t="n">
-        <v>300.8578215934895</v>
+        <v>300.4338615931582</v>
       </c>
       <c r="E7" t="n">
-        <v>304.8511047363281</v>
+        <v>303.3819885253906</v>
       </c>
       <c r="F7" t="n">
-        <v>7214500</v>
+        <v>8454200</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B8" t="n">
-        <v>305.0187809092415</v>
+        <v>303.894722712774</v>
       </c>
       <c r="C8" t="n">
-        <v>305.6695438264559</v>
+        <v>304.4567493262524</v>
       </c>
       <c r="D8" t="n">
-        <v>300.4338918141804</v>
+        <v>299.2999640741864</v>
       </c>
       <c r="E8" t="n">
-        <v>303.3820190429688</v>
+        <v>299.7732543945312</v>
       </c>
       <c r="F8" t="n">
-        <v>8454200</v>
+        <v>6489900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B9" t="n">
-        <v>303.8946917756213</v>
+        <v>300.7789375021521</v>
       </c>
       <c r="C9" t="n">
-        <v>304.4567183318842</v>
+        <v>303.7270945284432</v>
       </c>
       <c r="D9" t="n">
-        <v>299.2999336047902</v>
+        <v>299.1422058887319</v>
       </c>
       <c r="E9" t="n">
-        <v>299.7732238769531</v>
+        <v>301.2522277832031</v>
       </c>
       <c r="F9" t="n">
-        <v>6489900</v>
+        <v>7060300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B10" t="n">
-        <v>300.7789070325195</v>
+        <v>301.3804193716138</v>
       </c>
       <c r="C10" t="n">
-        <v>303.7270637601551</v>
+        <v>306.1230715472904</v>
       </c>
       <c r="D10" t="n">
-        <v>299.1421755849041</v>
+        <v>296.5983188157025</v>
       </c>
       <c r="E10" t="n">
-        <v>301.252197265625</v>
+        <v>296.6772155761719</v>
       </c>
       <c r="F10" t="n">
-        <v>7060300</v>
+        <v>8597400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B11" t="n">
-        <v>301.3804193716138</v>
+        <v>301.321238204041</v>
       </c>
       <c r="C11" t="n">
-        <v>306.1230715472904</v>
+        <v>305.1271791148808</v>
       </c>
       <c r="D11" t="n">
-        <v>296.5983188157025</v>
+        <v>301.173344402637</v>
       </c>
       <c r="E11" t="n">
-        <v>296.6772155761719</v>
+        <v>303.6580505371094</v>
       </c>
       <c r="F11" t="n">
-        <v>8597400</v>
+        <v>10788700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B12" t="n">
-        <v>301.3212684867699</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C12" t="n">
-        <v>305.1272097801061</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D12" t="n">
-        <v>301.1733746705027</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E12" t="n">
-        <v>303.6580810546875</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F12" t="n">
-        <v>10788700</v>
+        <v>16178800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B13" t="n">
-        <v>301.5578902761218</v>
+        <v>302.1001843350741</v>
       </c>
       <c r="C13" t="n">
-        <v>302.7016525742085</v>
+        <v>307.7499381556482</v>
       </c>
       <c r="D13" t="n">
-        <v>290.0907186231138</v>
+        <v>301.1634734465224</v>
       </c>
       <c r="E13" t="n">
-        <v>297.8505249023438</v>
+        <v>301.4099731445312</v>
       </c>
       <c r="F13" t="n">
-        <v>16178800</v>
+        <v>11354800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B14" t="n">
-        <v>302.1002149225357</v>
+        <v>301.0747572360179</v>
       </c>
       <c r="C14" t="n">
-        <v>307.7499693151439</v>
+        <v>304.3581201926382</v>
       </c>
       <c r="D14" t="n">
-        <v>301.1635039391426</v>
+        <v>292.9106878973514</v>
       </c>
       <c r="E14" t="n">
-        <v>301.4100036621094</v>
+        <v>294.360107421875</v>
       </c>
       <c r="F14" t="n">
-        <v>11354800</v>
+        <v>10549400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B15" t="n">
-        <v>301.0747260223031</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C15" t="n">
-        <v>304.358088638523</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D15" t="n">
-        <v>292.9106575300408</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E15" t="n">
-        <v>294.3600769042969</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F15" t="n">
-        <v>10549400</v>
+        <v>10153500</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B16" t="n">
-        <v>294.9714335987563</v>
+        <v>294.3206459359216</v>
       </c>
       <c r="C16" t="n">
-        <v>295.3559575215809</v>
+        <v>299.4379821870563</v>
       </c>
       <c r="D16" t="n">
-        <v>290.0808874955599</v>
+        <v>293.9854099500461</v>
       </c>
       <c r="E16" t="n">
-        <v>293.3938293457031</v>
+        <v>298.1265869140625</v>
       </c>
       <c r="F16" t="n">
-        <v>10153500</v>
+        <v>6894900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B17" t="n">
-        <v>294.3206459359216</v>
+        <v>297.436411288458</v>
       </c>
       <c r="C17" t="n">
-        <v>299.4379821870563</v>
+        <v>299.7929328501146</v>
       </c>
       <c r="D17" t="n">
-        <v>293.9854099500461</v>
+        <v>292.8416531202475</v>
       </c>
       <c r="E17" t="n">
-        <v>298.1265869140625</v>
+        <v>292.9303894042969</v>
       </c>
       <c r="F17" t="n">
-        <v>6894900</v>
+        <v>7372700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B18" t="n">
-        <v>297.4363803014411</v>
+        <v>293.6008552074487</v>
       </c>
       <c r="C18" t="n">
-        <v>299.7929016175946</v>
+        <v>293.8868032880077</v>
       </c>
       <c r="D18" t="n">
-        <v>292.841622611914</v>
+        <v>286.4721030595595</v>
       </c>
       <c r="E18" t="n">
-        <v>292.9303588867188</v>
+        <v>289.9920959472656</v>
       </c>
       <c r="F18" t="n">
-        <v>7372700</v>
+        <v>8054100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B19" t="n">
-        <v>293.6008861047978</v>
+        <v>290.2583437522712</v>
       </c>
       <c r="C19" t="n">
-        <v>293.8868342154489</v>
+        <v>292.2204718178062</v>
       </c>
       <c r="D19" t="n">
-        <v>286.4721332067081</v>
+        <v>288.4145307332595</v>
       </c>
       <c r="E19" t="n">
-        <v>289.9921264648438</v>
+        <v>290.4161071777344</v>
       </c>
       <c r="F19" t="n">
-        <v>8054100</v>
+        <v>5438800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B20" t="n">
-        <v>290.2583437522712</v>
+        <v>291.9345194575729</v>
       </c>
       <c r="C20" t="n">
-        <v>292.2204718178062</v>
+        <v>298.3632510673837</v>
       </c>
       <c r="D20" t="n">
-        <v>288.4145307332595</v>
+        <v>291.3133654724136</v>
       </c>
       <c r="E20" t="n">
-        <v>290.4161071777344</v>
+        <v>296.2334899902344</v>
       </c>
       <c r="F20" t="n">
-        <v>5438800</v>
+        <v>7228300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B21" t="n">
-        <v>291.9345194575729</v>
+        <v>297.92941246883</v>
       </c>
       <c r="C21" t="n">
-        <v>298.3632510673837</v>
+        <v>300.2662249001909</v>
       </c>
       <c r="D21" t="n">
-        <v>291.3133654724136</v>
+        <v>296.7955198233114</v>
       </c>
       <c r="E21" t="n">
-        <v>296.2334899902344</v>
+        <v>299.8915405273438</v>
       </c>
       <c r="F21" t="n">
-        <v>7228300</v>
+        <v>5642200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B22" t="n">
-        <v>297.92941246883</v>
+        <v>300.5915953010157</v>
       </c>
       <c r="C22" t="n">
-        <v>300.2662249001909</v>
+        <v>303.6580673748709</v>
       </c>
       <c r="D22" t="n">
-        <v>296.7955198233114</v>
+        <v>298.915415308335</v>
       </c>
       <c r="E22" t="n">
-        <v>299.8915405273438</v>
+        <v>301.0845947265625</v>
       </c>
       <c r="F22" t="n">
-        <v>5642200</v>
+        <v>6336000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B23" t="n">
-        <v>300.5915953010157</v>
+        <v>299.2605157595805</v>
       </c>
       <c r="C23" t="n">
-        <v>303.6580673748709</v>
+        <v>303.9341406042103</v>
       </c>
       <c r="D23" t="n">
-        <v>298.915415308335</v>
+        <v>298.7675163425421</v>
       </c>
       <c r="E23" t="n">
-        <v>301.0845947265625</v>
+        <v>301.2325134277344</v>
       </c>
       <c r="F23" t="n">
-        <v>6336000</v>
+        <v>7520300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B24" t="n">
-        <v>299.2605157595805</v>
+        <v>301.5085931686638</v>
       </c>
       <c r="C24" t="n">
-        <v>303.9341406042103</v>
+        <v>308.2330823767899</v>
       </c>
       <c r="D24" t="n">
-        <v>298.7675163425421</v>
+        <v>300.828251563059</v>
       </c>
       <c r="E24" t="n">
-        <v>301.2325134277344</v>
+        <v>305.1074829101562</v>
       </c>
       <c r="F24" t="n">
-        <v>7520300</v>
+        <v>7514600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B25" t="n">
-        <v>301.5086233262724</v>
+        <v>304.2200828300273</v>
       </c>
       <c r="C25" t="n">
-        <v>308.233113206998</v>
+        <v>308.4894444595929</v>
       </c>
       <c r="D25" t="n">
-        <v>300.8282816526182</v>
+        <v>302.9481359332913</v>
       </c>
       <c r="E25" t="n">
-        <v>305.1075134277344</v>
+        <v>306.7639465332031</v>
       </c>
       <c r="F25" t="n">
-        <v>7514600</v>
+        <v>7721300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B26" t="n">
-        <v>304.220113094536</v>
+        <v>306.6456604912348</v>
       </c>
       <c r="C26" t="n">
-        <v>308.4894751488275</v>
+        <v>307.9471862719047</v>
       </c>
       <c r="D26" t="n">
-        <v>302.9481660712639</v>
+        <v>301.9227172950412</v>
       </c>
       <c r="E26" t="n">
-        <v>306.7639770507812</v>
+        <v>305.0187683105469</v>
       </c>
       <c r="F26" t="n">
-        <v>7721300</v>
+        <v>7770000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B27" t="n">
-        <v>306.6456604912348</v>
+        <v>302.415720333495</v>
       </c>
       <c r="C27" t="n">
-        <v>307.9471862719047</v>
+        <v>307.8485840116909</v>
       </c>
       <c r="D27" t="n">
-        <v>301.9227172950412</v>
+        <v>300.8282765156093</v>
       </c>
       <c r="E27" t="n">
-        <v>305.0187683105469</v>
+        <v>304.920166015625</v>
       </c>
       <c r="F27" t="n">
-        <v>7770000</v>
+        <v>7085200</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B28" t="n">
-        <v>302.415720333495</v>
+        <v>305.2751066360906</v>
       </c>
       <c r="C28" t="n">
-        <v>307.8485840116909</v>
+        <v>308.7162632770978</v>
       </c>
       <c r="D28" t="n">
-        <v>300.8282765156093</v>
+        <v>301.3508502506656</v>
       </c>
       <c r="E28" t="n">
-        <v>304.920166015625</v>
+        <v>307.3161315917969</v>
       </c>
       <c r="F28" t="n">
-        <v>7085200</v>
+        <v>6865200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B29" t="n">
-        <v>305.2750763211935</v>
+        <v>306.6357687557767</v>
       </c>
       <c r="C29" t="n">
-        <v>308.7162326204817</v>
+        <v>310.4318702971036</v>
       </c>
       <c r="D29" t="n">
-        <v>301.350820325461</v>
+        <v>305.9160088624015</v>
       </c>
       <c r="E29" t="n">
-        <v>307.3161010742188</v>
+        <v>309.0317687988281</v>
       </c>
       <c r="F29" t="n">
-        <v>6865200</v>
+        <v>7206100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B30" t="n">
-        <v>306.6357990367445</v>
+        <v>307.5232049313688</v>
       </c>
       <c r="C30" t="n">
-        <v>310.4319009529449</v>
+        <v>310.0276204199649</v>
       </c>
       <c r="D30" t="n">
-        <v>305.9160390722913</v>
+        <v>303.3327096940284</v>
       </c>
       <c r="E30" t="n">
-        <v>309.0317993164062</v>
+        <v>309.8106994628906</v>
       </c>
       <c r="F30" t="n">
-        <v>7206100</v>
+        <v>7302300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B31" t="n">
-        <v>307.5231746391179</v>
+        <v>310.5896337890794</v>
       </c>
       <c r="C31" t="n">
-        <v>310.0275898810191</v>
+        <v>315.0857860805166</v>
       </c>
       <c r="D31" t="n">
-        <v>303.3326798145578</v>
+        <v>309.8106862822301</v>
       </c>
       <c r="E31" t="n">
-        <v>309.8106689453125</v>
+        <v>312.4531860351562</v>
       </c>
       <c r="F31" t="n">
-        <v>7302300</v>
+        <v>5794100</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B32" t="n">
-        <v>310.5896641246428</v>
+        <v>313.0546102409576</v>
       </c>
       <c r="C32" t="n">
-        <v>315.0858168552232</v>
+        <v>314.5828963020791</v>
       </c>
       <c r="D32" t="n">
-        <v>309.810716541713</v>
+        <v>310.8656917625901</v>
       </c>
       <c r="E32" t="n">
-        <v>312.4532165527344</v>
+        <v>311.200927734375</v>
       </c>
       <c r="F32" t="n">
-        <v>5794100</v>
+        <v>5030200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B33" t="n">
-        <v>313.054640940315</v>
+        <v>311.8320000281587</v>
       </c>
       <c r="C33" t="n">
-        <v>314.5829271513063</v>
+        <v>317.7381233989844</v>
       </c>
       <c r="D33" t="n">
-        <v>310.8657222472937</v>
+        <v>311.782682032414</v>
       </c>
       <c r="E33" t="n">
-        <v>311.2009582519531</v>
+        <v>315.9238891601562</v>
       </c>
       <c r="F33" t="n">
-        <v>5030200</v>
+        <v>10578300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B34" t="n">
-        <v>311.8320301504691</v>
+        <v>314.7604626322791</v>
       </c>
       <c r="C34" t="n">
-        <v>317.7381540918137</v>
+        <v>316.1408551748796</v>
       </c>
       <c r="D34" t="n">
-        <v>311.7827121499603</v>
+        <v>304.7722882324798</v>
       </c>
       <c r="E34" t="n">
-        <v>315.9239196777344</v>
+        <v>305.14697265625</v>
       </c>
       <c r="F34" t="n">
-        <v>10578300</v>
+        <v>8973300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B35" t="n">
-        <v>314.7604311532612</v>
+        <v>303.2044890700107</v>
       </c>
       <c r="C35" t="n">
-        <v>316.1408235578094</v>
+        <v>303.3326737235763</v>
       </c>
       <c r="D35" t="n">
-        <v>304.7722577523736</v>
+        <v>297.012418045434</v>
       </c>
       <c r="E35" t="n">
-        <v>305.1469421386719</v>
+        <v>299.3590698242188</v>
       </c>
       <c r="F35" t="n">
-        <v>8973300</v>
+        <v>10327000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B36" t="n">
-        <v>303.2045199796025</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C36" t="n">
-        <v>303.3327046462357</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D36" t="n">
-        <v>297.0124483237873</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E36" t="n">
-        <v>299.3591003417969</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F36" t="n">
-        <v>10327000</v>
+        <v>8344000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B37" t="n">
-        <v>299.7436397411884</v>
+        <v>295.3066623130797</v>
       </c>
       <c r="C37" t="n">
-        <v>301.3113742461044</v>
+        <v>298.708370459316</v>
       </c>
       <c r="D37" t="n">
-        <v>293.5022804823602</v>
+        <v>292.8613742767781</v>
       </c>
       <c r="E37" t="n">
-        <v>296.1644592285156</v>
+        <v>295.2179260253906</v>
       </c>
       <c r="F37" t="n">
-        <v>8344000</v>
+        <v>8077300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B38" t="n">
-        <v>295.3066317863286</v>
+        <v>295.5432597963394</v>
       </c>
       <c r="C38" t="n">
-        <v>298.70833958092</v>
+        <v>300.1873356382808</v>
       </c>
       <c r="D38" t="n">
-        <v>292.8613440028039</v>
+        <v>295.0798391737984</v>
       </c>
       <c r="E38" t="n">
-        <v>295.2178955078125</v>
+        <v>299.0238342285156</v>
       </c>
       <c r="F38" t="n">
-        <v>8077300</v>
+        <v>5546600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B39" t="n">
-        <v>295.5432899586994</v>
+        <v>302.0508736933244</v>
       </c>
       <c r="C39" t="n">
-        <v>300.1873662746028</v>
+        <v>305.5807663052954</v>
       </c>
       <c r="D39" t="n">
-        <v>295.0798692888629</v>
+        <v>293.9854105998292</v>
       </c>
       <c r="E39" t="n">
-        <v>299.0238647460938</v>
+        <v>294.2023315429688</v>
       </c>
       <c r="F39" t="n">
-        <v>5546600</v>
+        <v>7501600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B40" t="n">
-        <v>302.0508736933244</v>
+        <v>297.0715864028587</v>
       </c>
       <c r="C40" t="n">
-        <v>305.5807663052954</v>
+        <v>297.456110287291</v>
       </c>
       <c r="D40" t="n">
-        <v>293.9854105998292</v>
+        <v>288.7103057597054</v>
       </c>
       <c r="E40" t="n">
-        <v>294.2023315429688</v>
+        <v>293.8473510742188</v>
       </c>
       <c r="F40" t="n">
-        <v>7501600</v>
+        <v>11766800</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B41" t="n">
-        <v>297.0715864028587</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C41" t="n">
-        <v>297.456110287291</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D41" t="n">
-        <v>288.7103057597054</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E41" t="n">
-        <v>293.8473510742188</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F41" t="n">
-        <v>11766800</v>
+        <v>10940200</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B42" t="n">
-        <v>294.0642973394352</v>
+        <v>295.848951187077</v>
       </c>
       <c r="C42" t="n">
-        <v>295.6221924256846</v>
+        <v>300.236658228506</v>
       </c>
       <c r="D42" t="n">
-        <v>290.386540762355</v>
+        <v>291.4218258555586</v>
       </c>
       <c r="E42" t="n">
-        <v>293.8276672363281</v>
+        <v>298.7576599121094</v>
       </c>
       <c r="F42" t="n">
-        <v>10940200</v>
+        <v>8877200</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B43" t="n">
-        <v>295.8489209666184</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C43" t="n">
-        <v>300.2366275598507</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D43" t="n">
-        <v>291.4217960873232</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E43" t="n">
-        <v>298.7576293945312</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F43" t="n">
-        <v>8877200</v>
+        <v>7910900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B44" t="n">
-        <v>300.7296512123902</v>
+        <v>304.7722465716023</v>
       </c>
       <c r="C44" t="n">
-        <v>304.2102259719906</v>
+        <v>309.3275563846455</v>
       </c>
       <c r="D44" t="n">
-        <v>298.9548653069277</v>
+        <v>303.9242719247256</v>
       </c>
       <c r="E44" t="n">
-        <v>303.3327026367188</v>
+        <v>308.6965026855469</v>
       </c>
       <c r="F44" t="n">
-        <v>7910900</v>
+        <v>4322400</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B45" t="n">
-        <v>304.7722767012305</v>
+        <v>308.5683309692949</v>
       </c>
       <c r="C45" t="n">
-        <v>309.3275869646093</v>
+        <v>309.6430660312097</v>
       </c>
       <c r="D45" t="n">
-        <v>303.9243019705234</v>
+        <v>304.2200727283419</v>
       </c>
       <c r="E45" t="n">
-        <v>308.696533203125</v>
+        <v>304.5947570800781</v>
       </c>
       <c r="F45" t="n">
-        <v>4322400</v>
+        <v>7727300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B46" t="n">
-        <v>308.5683618849884</v>
+        <v>304.4172805196406</v>
       </c>
       <c r="C46" t="n">
-        <v>309.6430970545817</v>
+        <v>306.1329390093465</v>
       </c>
       <c r="D46" t="n">
-        <v>304.2201032083801</v>
+        <v>302.7903884074122</v>
       </c>
       <c r="E46" t="n">
-        <v>304.5947875976562</v>
+        <v>303.5693359375</v>
       </c>
       <c r="F46" t="n">
-        <v>7727300</v>
+        <v>7249000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B47" t="n">
-        <v>304.4172805196406</v>
+        <v>302.8988595387675</v>
       </c>
       <c r="C47" t="n">
-        <v>306.1329390093465</v>
+        <v>307.9865871384521</v>
       </c>
       <c r="D47" t="n">
-        <v>302.7903884074122</v>
+        <v>302.5044359255107</v>
       </c>
       <c r="E47" t="n">
-        <v>303.5693359375</v>
+        <v>307.7598266601562</v>
       </c>
       <c r="F47" t="n">
-        <v>7249000</v>
+        <v>8535300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B48" t="n">
-        <v>302.8988595387675</v>
+        <v>308.8740221323167</v>
       </c>
       <c r="C48" t="n">
-        <v>307.9865871384521</v>
+        <v>314.0307770729326</v>
       </c>
       <c r="D48" t="n">
-        <v>302.5044359255107</v>
+        <v>308.617652791837</v>
       </c>
       <c r="E48" t="n">
-        <v>307.7598266601562</v>
+        <v>311.6742553710938</v>
       </c>
       <c r="F48" t="n">
-        <v>8535300</v>
+        <v>9627800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B49" t="n">
-        <v>308.8740221323167</v>
+        <v>311.2206946896725</v>
       </c>
       <c r="C49" t="n">
-        <v>314.0307770729326</v>
+        <v>314.0209278419201</v>
       </c>
       <c r="D49" t="n">
-        <v>308.617652791837</v>
+        <v>310.2741141188276</v>
       </c>
       <c r="E49" t="n">
-        <v>311.6742553710938</v>
+        <v>310.6290893554688</v>
       </c>
       <c r="F49" t="n">
-        <v>9627800</v>
+        <v>6518900</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B50" t="n">
-        <v>311.2206946896725</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C50" t="n">
-        <v>314.0209278419201</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D50" t="n">
-        <v>310.2741141188276</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E50" t="n">
-        <v>310.6290893554688</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F50" t="n">
-        <v>6518900</v>
+        <v>7417200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B51" t="n">
-        <v>310.6487980837529</v>
+        <v>310.5403783790639</v>
       </c>
       <c r="C51" t="n">
-        <v>312.0390600856641</v>
+        <v>314.336450228146</v>
       </c>
       <c r="D51" t="n">
-        <v>308.9627484602848</v>
+        <v>295.8193913272319</v>
       </c>
       <c r="E51" t="n">
-        <v>310.7966918945312</v>
+        <v>296.3025512695312</v>
       </c>
       <c r="F51" t="n">
-        <v>7417200</v>
+        <v>18049200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B52" t="n">
-        <v>310.5403463950657</v>
+        <v>296.292632599085</v>
       </c>
       <c r="C52" t="n">
-        <v>314.3364178531727</v>
+        <v>306.8329619363725</v>
       </c>
       <c r="D52" t="n">
-        <v>295.8193608594167</v>
+        <v>294.2811866679717</v>
       </c>
       <c r="E52" t="n">
-        <v>296.3025207519531</v>
+        <v>305.76806640625</v>
       </c>
       <c r="F52" t="n">
-        <v>18049200</v>
+        <v>18874100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B53" t="n">
-        <v>296.2926621709551</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C53" t="n">
-        <v>306.8329925602339</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D53" t="n">
-        <v>294.2812160390869</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E53" t="n">
-        <v>305.7680969238281</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F53" t="n">
-        <v>18874100</v>
+        <v>9721900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B54" t="n">
-        <v>304.9102649889192</v>
+        <v>315.2041261224818</v>
       </c>
       <c r="C54" t="n">
-        <v>313.5476242674454</v>
+        <v>315.7858618718594</v>
       </c>
       <c r="D54" t="n">
-        <v>304.9102649889192</v>
+        <v>312.1672627021157</v>
       </c>
       <c r="E54" t="n">
-        <v>312.9363098144531</v>
+        <v>314.0603637695312</v>
       </c>
       <c r="F54" t="n">
-        <v>9721900</v>
+        <v>8982900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B55" t="n">
-        <v>315.2040954937631</v>
+        <v>315.115395356304</v>
       </c>
       <c r="C55" t="n">
-        <v>315.7858311866128</v>
+        <v>318.3593402708456</v>
       </c>
       <c r="D55" t="n">
-        <v>312.1672323684923</v>
+        <v>313.9322146909975</v>
       </c>
       <c r="E55" t="n">
-        <v>314.0603332519531</v>
+        <v>315.5393676757812</v>
       </c>
       <c r="F55" t="n">
-        <v>8982900</v>
+        <v>10864100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B56" t="n">
-        <v>315.115395356304</v>
+        <v>314.6224027314819</v>
       </c>
       <c r="C56" t="n">
-        <v>318.3593402708456</v>
+        <v>315.0463750601788</v>
       </c>
       <c r="D56" t="n">
-        <v>313.9322146909975</v>
+        <v>309.9980652283745</v>
       </c>
       <c r="E56" t="n">
-        <v>315.5393676757812</v>
+        <v>311.1319580078125</v>
       </c>
       <c r="F56" t="n">
-        <v>10864100</v>
+        <v>8331300</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B57" t="n">
-        <v>314.6223410116007</v>
+        <v>313.971593609235</v>
       </c>
       <c r="C57" t="n">
-        <v>315.0463132571263</v>
+        <v>314.8984348971578</v>
       </c>
       <c r="D57" t="n">
-        <v>309.9980044156554</v>
+        <v>310.254388930852</v>
       </c>
       <c r="E57" t="n">
-        <v>311.1318969726562</v>
+        <v>310.5699157714844</v>
       </c>
       <c r="F57" t="n">
-        <v>8331300</v>
+        <v>8718700</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B58" t="n">
-        <v>313.9716244610726</v>
+        <v>311.575672673722</v>
       </c>
       <c r="C58" t="n">
-        <v>314.8984658400699</v>
+        <v>313.2518829489097</v>
       </c>
       <c r="D58" t="n">
-        <v>310.2544194174254</v>
+        <v>307.8485977928193</v>
       </c>
       <c r="E58" t="n">
-        <v>310.5699462890625</v>
+        <v>308.61767578125</v>
       </c>
       <c r="F58" t="n">
-        <v>8718700</v>
+        <v>11444900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B59" t="n">
-        <v>311.5756418636432</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C59" t="n">
-        <v>313.2518519730792</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D59" t="n">
-        <v>307.8485673512913</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E59" t="n">
-        <v>308.6176452636719</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F59" t="n">
-        <v>11444900</v>
+        <v>24494400</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B60" t="n">
-        <v>309.3965776494671</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="C60" t="n">
-        <v>314.099781180705</v>
+        <v>318.7043994886834</v>
       </c>
       <c r="D60" t="n">
-        <v>308.8049723403709</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="E60" t="n">
-        <v>312.7686767578125</v>
+        <v>318.5663452148438</v>
       </c>
       <c r="F60" t="n">
-        <v>24494400</v>
+        <v>8354600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B61" t="n">
-        <v>313.0644852104395</v>
+        <v>319.0790830432475</v>
       </c>
       <c r="C61" t="n">
-        <v>318.7043994886834</v>
+        <v>323.1907116116738</v>
       </c>
       <c r="D61" t="n">
-        <v>313.0644852104395</v>
+        <v>318.5663744582675</v>
       </c>
       <c r="E61" t="n">
-        <v>318.5663452148438</v>
+        <v>321.3666076660156</v>
       </c>
       <c r="F61" t="n">
-        <v>8354600</v>
+        <v>6668300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B62" t="n">
-        <v>319.0790830432475</v>
+        <v>321.6722493328215</v>
       </c>
       <c r="C62" t="n">
-        <v>323.1907116116738</v>
+        <v>325.3697449529369</v>
       </c>
       <c r="D62" t="n">
-        <v>318.5663744582675</v>
+        <v>320.9426198260136</v>
       </c>
       <c r="E62" t="n">
-        <v>321.3666076660156</v>
+        <v>324.5612487792969</v>
       </c>
       <c r="F62" t="n">
-        <v>6668300</v>
+        <v>4289300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B63" t="n">
-        <v>321.6722493328215</v>
+        <v>324.502058709128</v>
       </c>
       <c r="C63" t="n">
-        <v>325.3697449529369</v>
+        <v>326.2275566521161</v>
       </c>
       <c r="D63" t="n">
-        <v>320.9426198260136</v>
+        <v>321.9680645986219</v>
       </c>
       <c r="E63" t="n">
-        <v>324.5612487792969</v>
+        <v>323.3188781738281</v>
       </c>
       <c r="F63" t="n">
-        <v>4289300</v>
+        <v>4158300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B64" t="n">
-        <v>324.502058709128</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C64" t="n">
-        <v>326.2275566521161</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D64" t="n">
-        <v>321.9680645986219</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E64" t="n">
-        <v>323.3188781738281</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F64" t="n">
-        <v>4158300</v>
+        <v>8635300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B65" t="n">
-        <v>322.4216288798564</v>
+        <v>320.2623075229155</v>
       </c>
       <c r="C65" t="n">
-        <v>323.1808371734579</v>
+        <v>320.3904921972535</v>
       </c>
       <c r="D65" t="n">
-        <v>319.0002116144308</v>
+        <v>317.9747828016658</v>
       </c>
       <c r="E65" t="n">
-        <v>319.2171325683594</v>
+        <v>318.8917846679688</v>
       </c>
       <c r="F65" t="n">
-        <v>8635300</v>
+        <v>7904300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B66" t="n">
-        <v>320.2622768741799</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C66" t="n">
-        <v>320.3904615362508</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D66" t="n">
-        <v>317.9747523718436</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E66" t="n">
-        <v>318.8917541503906</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F66" t="n">
-        <v>7904300</v>
+        <v>5048500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B67" t="n">
-        <v>319.7988699190817</v>
+        <v>317.9846252281575</v>
       </c>
       <c r="C67" t="n">
-        <v>320.3313177342217</v>
+        <v>321.1694123071354</v>
       </c>
       <c r="D67" t="n">
-        <v>317.5310845539587</v>
+        <v>316.2492576445291</v>
       </c>
       <c r="E67" t="n">
-        <v>317.7085571289062</v>
+        <v>320.9229125976562</v>
       </c>
       <c r="F67" t="n">
-        <v>5048500</v>
+        <v>8054000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B68" t="n">
-        <v>317.9846554663246</v>
+        <v>320.9426586744551</v>
       </c>
       <c r="C68" t="n">
-        <v>321.169442848154</v>
+        <v>332.5281463531796</v>
       </c>
       <c r="D68" t="n">
-        <v>316.2492877176746</v>
+        <v>320.637001406751</v>
       </c>
       <c r="E68" t="n">
-        <v>320.9229431152344</v>
+        <v>329.3630981445312</v>
       </c>
       <c r="F68" t="n">
-        <v>8054000</v>
+        <v>10752600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,25 +2211,25 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B69" t="n">
-        <v>320.942628937084</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C69" t="n">
-        <v>332.5281155423397</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D69" t="n">
-        <v>320.636971697701</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E69" t="n">
-        <v>329.3630676269531</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F69" t="n">
-        <v>10752600</v>
+        <v>7660800</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2237,25 +2237,25 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B70" t="n">
-        <v>329.4422902981328</v>
+        <v>327.9764350864437</v>
       </c>
       <c r="C70" t="n">
-        <v>332.6612412306879</v>
+        <v>328.9767653957764</v>
       </c>
       <c r="D70" t="n">
-        <v>327.491109600743</v>
+        <v>321.4989071734381</v>
       </c>
       <c r="E70" t="n">
-        <v>331.4132690429688</v>
+        <v>323.8660583496094</v>
       </c>
       <c r="F70" t="n">
-        <v>7660800</v>
+        <v>9815200</v>
       </c>
       <c r="G70" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B71" t="n">
-        <v>327.9764659913386</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C71" t="n">
-        <v>328.9767963949314</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D71" t="n">
-        <v>321.4989374679619</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E71" t="n">
-        <v>323.8660888671875</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F71" t="n">
-        <v>9815200</v>
+        <v>11737100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B72" t="n">
-        <v>323.2718313763784</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C72" t="n">
-        <v>328.2339475379842</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D72" t="n">
-        <v>322.5388804495614</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E72" t="n">
-        <v>326.6393432617188</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F72" t="n">
-        <v>11737100</v>
+        <v>6738100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B73" t="n">
-        <v>326.1936353875406</v>
+        <v>318.8049332018166</v>
       </c>
       <c r="C73" t="n">
-        <v>328.7291759216584</v>
+        <v>322.9053661093398</v>
       </c>
       <c r="D73" t="n">
-        <v>325.0348299492433</v>
+        <v>318.1611490039577</v>
       </c>
       <c r="E73" t="n">
-        <v>326.0450744628906</v>
+        <v>321.3899841308594</v>
       </c>
       <c r="F73" t="n">
-        <v>6738100</v>
+        <v>12805100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B74" t="n">
-        <v>318.8049029297019</v>
+        <v>321.2017865718998</v>
       </c>
       <c r="C74" t="n">
-        <v>322.9053354478686</v>
+        <v>323.7373271836527</v>
       </c>
       <c r="D74" t="n">
-        <v>318.1611187929736</v>
+        <v>307.6029755260753</v>
       </c>
       <c r="E74" t="n">
-        <v>321.3899536132812</v>
+        <v>307.9298095703125</v>
       </c>
       <c r="F74" t="n">
-        <v>12805100</v>
+        <v>19371200</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B75" t="n">
-        <v>321.2017547389941</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C75" t="n">
-        <v>323.7372950994605</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D75" t="n">
-        <v>307.6029450408882</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E75" t="n">
-        <v>307.9297790527344</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F75" t="n">
-        <v>19371200</v>
+        <v>25951500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B76" t="n">
-        <v>305.2556057077196</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C76" t="n">
-        <v>308.7815926253858</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D76" t="n">
-        <v>303.1954601804828</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E76" t="n">
-        <v>304.9287414550781</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F76" t="n">
-        <v>25951500</v>
+        <v>14751400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B77" t="n">
-        <v>305.5230197927318</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C77" t="n">
-        <v>309.95031666446</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D77" t="n">
-        <v>304.8098971346673</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E77" t="n">
-        <v>306.3054809570312</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F77" t="n">
-        <v>14751400</v>
+        <v>14652500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B78" t="n">
-        <v>307.385060616362</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C78" t="n">
-        <v>314.1795087286461</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D78" t="n">
-        <v>307.0383983149945</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E78" t="n">
-        <v>309.4848022460938</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F78" t="n">
-        <v>14652500</v>
+        <v>12900600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B79" t="n">
-        <v>303.2845981841295</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C79" t="n">
-        <v>308.1774060521912</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D79" t="n">
-        <v>298.9761500928895</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E79" t="n">
-        <v>299.8477478027344</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F79" t="n">
-        <v>12900600</v>
+        <v>10270100</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B80" t="n">
-        <v>300.5311849469782</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C80" t="n">
-        <v>302.4823658305288</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D80" t="n">
-        <v>298.2729680555718</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E80" t="n">
-        <v>299.1544799804688</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F80" t="n">
-        <v>10270100</v>
+        <v>10535800</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B81" t="n">
-        <v>301.9474777854751</v>
+        <v>299.1148422218051</v>
       </c>
       <c r="C81" t="n">
-        <v>305.2555953909441</v>
+        <v>299.4813025896872</v>
       </c>
       <c r="D81" t="n">
-        <v>300.0062112868251</v>
+        <v>293.6773006232809</v>
       </c>
       <c r="E81" t="n">
-        <v>300.729248046875</v>
+        <v>294.875732421875</v>
       </c>
       <c r="F81" t="n">
-        <v>10535800</v>
+        <v>11107900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B82" t="n">
-        <v>299.1148112655088</v>
+        <v>294.9648788077786</v>
       </c>
       <c r="C82" t="n">
-        <v>299.4812715954647</v>
+        <v>298.8969527426069</v>
       </c>
       <c r="D82" t="n">
-        <v>293.6772702297321</v>
+        <v>294.6083325653198</v>
       </c>
       <c r="E82" t="n">
-        <v>294.8757019042969</v>
+        <v>298.1640319824219</v>
       </c>
       <c r="F82" t="n">
-        <v>11107900</v>
+        <v>11752700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B83" t="n">
-        <v>294.9648486176391</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C83" t="n">
-        <v>298.8969221500132</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D83" t="n">
-        <v>294.6083024116733</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E83" t="n">
-        <v>298.1640014648438</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F83" t="n">
-        <v>11752700</v>
+        <v>11527400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B84" t="n">
-        <v>298.4512235287846</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C84" t="n">
-        <v>299.0851237823749</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D84" t="n">
-        <v>295.3016109870806</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E84" t="n">
-        <v>297.4409790039062</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F84" t="n">
-        <v>11527400</v>
+        <v>9556700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B85" t="n">
-        <v>297.4013222225187</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C85" t="n">
-        <v>299.0355829225425</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D85" t="n">
-        <v>295.2025300603667</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E85" t="n">
-        <v>297.8965454101562</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F85" t="n">
-        <v>9556700</v>
+        <v>11580000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B86" t="n">
-        <v>299.5110006693188</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C86" t="n">
-        <v>303.898671192008</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D86" t="n">
-        <v>299.3327275624257</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E86" t="n">
-        <v>303.4926147460938</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F86" t="n">
-        <v>11580000</v>
+        <v>11953200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B87" t="n">
-        <v>302.333781642444</v>
+        <v>301.5513012828864</v>
       </c>
       <c r="C87" t="n">
-        <v>304.9881708986046</v>
+        <v>306.3450582127215</v>
       </c>
       <c r="D87" t="n">
-        <v>299.6694782493637</v>
+        <v>298.4908255461663</v>
       </c>
       <c r="E87" t="n">
-        <v>302.9676818847656</v>
+        <v>305.1961669921875</v>
       </c>
       <c r="F87" t="n">
-        <v>11953200</v>
+        <v>9839400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B88" t="n">
-        <v>301.5513314360023</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C88" t="n">
-        <v>306.3450888451811</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D88" t="n">
-        <v>298.4908553932551</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E88" t="n">
-        <v>305.1961975097656</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F88" t="n">
-        <v>9839400</v>
+        <v>12688000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B89" t="n">
-        <v>306.7709905338949</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="C89" t="n">
-        <v>313.2286905211348</v>
+        <v>316.2594719758441</v>
       </c>
       <c r="D89" t="n">
-        <v>306.1470044328188</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="E89" t="n">
-        <v>311.8420715332031</v>
+        <v>314.2389526367188</v>
       </c>
       <c r="F89" t="n">
-        <v>12688000</v>
+        <v>9848800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B90" t="n">
-        <v>311.4062598905275</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C90" t="n">
-        <v>316.2594412620415</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D90" t="n">
-        <v>311.4062598905275</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E90" t="n">
-        <v>314.2389221191406</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F90" t="n">
-        <v>9848800</v>
+        <v>9388000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B91" t="n">
-        <v>311.9906259989966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C91" t="n">
-        <v>312.9909865673853</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D91" t="n">
-        <v>302.6210112179966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E91" t="n">
-        <v>307.1968688964844</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F91" t="n">
-        <v>9388000</v>
+        <v>17797400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B92" t="n">
-        <v>311.7034102684662</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C92" t="n">
-        <v>321.1522783634816</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D92" t="n">
-        <v>311.7034102684662</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E92" t="n">
-        <v>319.3199462890625</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F92" t="n">
-        <v>17797400</v>
+        <v>11477500</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B93" t="n">
-        <v>318.2700781279603</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C93" t="n">
-        <v>323.2817350541263</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D93" t="n">
-        <v>317.0518180384032</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E93" t="n">
-        <v>319.0228271484375</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F93" t="n">
-        <v>11477500</v>
+        <v>9902200</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B94" t="n">
-        <v>319.4684837021083</v>
+        <v>320.1518827061323</v>
       </c>
       <c r="C94" t="n">
-        <v>323.014298845819</v>
+        <v>322.1724018130651</v>
       </c>
       <c r="D94" t="n">
-        <v>312.1094739861534</v>
+        <v>305.7805260837019</v>
       </c>
       <c r="E94" t="n">
-        <v>315.2392883300781</v>
+        <v>307.8505554199219</v>
       </c>
       <c r="F94" t="n">
-        <v>9902200</v>
+        <v>8703500</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B95" t="n">
-        <v>320.1519144431551</v>
+        <v>309.2966374972976</v>
       </c>
       <c r="C95" t="n">
-        <v>322.1724337503843</v>
+        <v>310.6238322045743</v>
       </c>
       <c r="D95" t="n">
-        <v>305.7805563960757</v>
+        <v>297.1537535117247</v>
       </c>
       <c r="E95" t="n">
-        <v>307.8505859375</v>
+        <v>299.7487487792969</v>
       </c>
       <c r="F95" t="n">
-        <v>8703500</v>
+        <v>13443400</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B96" t="n">
-        <v>309.2966060076438</v>
+        <v>295.6680782309701</v>
       </c>
       <c r="C96" t="n">
-        <v>310.6238005797982</v>
+        <v>301.3829738793206</v>
       </c>
       <c r="D96" t="n">
-        <v>297.1537232583444</v>
+        <v>293.6871852314235</v>
       </c>
       <c r="E96" t="n">
-        <v>299.7487182617188</v>
+        <v>299.6595764160156</v>
       </c>
       <c r="F96" t="n">
-        <v>13443400</v>
+        <v>9114500</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B97" t="n">
-        <v>295.6680481198895</v>
+        <v>299.8675850307636</v>
       </c>
       <c r="C97" t="n">
-        <v>301.3829431862302</v>
+        <v>305.2952123797385</v>
       </c>
       <c r="D97" t="n">
-        <v>293.6871553220786</v>
+        <v>299.6100592744303</v>
       </c>
       <c r="E97" t="n">
-        <v>299.6595458984375</v>
+        <v>304.1958312988281</v>
       </c>
       <c r="F97" t="n">
-        <v>9114500</v>
+        <v>8896800</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B98" t="n">
-        <v>299.8675549474044</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C98" t="n">
-        <v>305.2951817518681</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D98" t="n">
-        <v>299.6100292169066</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E98" t="n">
-        <v>304.19580078125</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F98" t="n">
-        <v>8896800</v>
+        <v>7209600</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B99" t="n">
-        <v>305.5130974954087</v>
+        <v>304.2354272061944</v>
       </c>
       <c r="C99" t="n">
-        <v>309.2966101142475</v>
+        <v>306.2262038721237</v>
       </c>
       <c r="D99" t="n">
-        <v>304.2849535938903</v>
+        <v>302.2049939958365</v>
       </c>
       <c r="E99" t="n">
-        <v>305.8300476074219</v>
+        <v>305.1069946289062</v>
       </c>
       <c r="F99" t="n">
-        <v>7209600</v>
+        <v>6737700</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B100" t="n">
-        <v>304.2354576365961</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C100" t="n">
-        <v>306.226234501648</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D100" t="n">
-        <v>302.2050242231491</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E100" t="n">
-        <v>305.1070251464844</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F100" t="n">
-        <v>6737700</v>
+        <v>7792700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B101" t="n">
-        <v>305.4536802835111</v>
+        <v>305.8498457788994</v>
       </c>
       <c r="C101" t="n">
-        <v>308.0288471084009</v>
+        <v>308.0288400173425</v>
       </c>
       <c r="D101" t="n">
-        <v>302.7596647203387</v>
+        <v>292.2807478108573</v>
       </c>
       <c r="E101" t="n">
-        <v>307.8208618164062</v>
+        <v>294.8262023925781</v>
       </c>
       <c r="F101" t="n">
-        <v>7792700</v>
+        <v>12955400</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B102" t="n">
-        <v>305.8498774375392</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C102" t="n">
-        <v>308.028871901531</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D102" t="n">
-        <v>292.2807780649544</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E102" t="n">
-        <v>294.8262329101562</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F102" t="n">
-        <v>12955400</v>
+        <v>13554100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B103" t="n">
-        <v>293.9843218466586</v>
+        <v>295.7869507950724</v>
       </c>
       <c r="C103" t="n">
-        <v>296.886322684036</v>
+        <v>300.7589812348872</v>
       </c>
       <c r="D103" t="n">
-        <v>288.5962907533433</v>
+        <v>294.1725181992404</v>
       </c>
       <c r="E103" t="n">
-        <v>294.459716796875</v>
+        <v>300.4024047851562</v>
       </c>
       <c r="F103" t="n">
-        <v>13554100</v>
+        <v>8095500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B104" t="n">
-        <v>295.7869207463737</v>
+        <v>301.670173133609</v>
       </c>
       <c r="C104" t="n">
-        <v>300.7589506810849</v>
+        <v>306.0578739762234</v>
       </c>
       <c r="D104" t="n">
-        <v>294.1724883145502</v>
+        <v>300.7391812579012</v>
       </c>
       <c r="E104" t="n">
-        <v>300.4023742675781</v>
+        <v>303.2053833007812</v>
       </c>
       <c r="F104" t="n">
-        <v>8095500</v>
+        <v>7007800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B105" t="n">
-        <v>301.670173133609</v>
+        <v>297.1339389424841</v>
       </c>
       <c r="C105" t="n">
-        <v>306.0578739762234</v>
+        <v>300.0557680991628</v>
       </c>
       <c r="D105" t="n">
-        <v>300.7391812579012</v>
+        <v>291.636973162459</v>
       </c>
       <c r="E105" t="n">
-        <v>303.2053833007812</v>
+        <v>297.4310607910156</v>
       </c>
       <c r="F105" t="n">
-        <v>7007800</v>
+        <v>18620800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B106" t="n">
-        <v>297.1339389424841</v>
+        <v>291.9935267958635</v>
       </c>
       <c r="C106" t="n">
-        <v>300.0557680991628</v>
+        <v>297.1141484397957</v>
       </c>
       <c r="D106" t="n">
-        <v>291.636973162459</v>
+        <v>290.4088063693875</v>
       </c>
       <c r="E106" t="n">
-        <v>297.4310607910156</v>
+        <v>294.7172546386719</v>
       </c>
       <c r="F106" t="n">
-        <v>18620800</v>
+        <v>8508900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B107" t="n">
-        <v>291.9935267958635</v>
+        <v>289.4975898716125</v>
       </c>
       <c r="C107" t="n">
-        <v>297.1141484397957</v>
+        <v>299.5011046657454</v>
       </c>
       <c r="D107" t="n">
-        <v>290.4088063693875</v>
+        <v>286.7342359222354</v>
       </c>
       <c r="E107" t="n">
-        <v>294.7172546386719</v>
+        <v>297.3914489746094</v>
       </c>
       <c r="F107" t="n">
-        <v>8508900</v>
+        <v>10278200</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B108" t="n">
-        <v>289.4975898716125</v>
+        <v>297.1240288614248</v>
       </c>
       <c r="C108" t="n">
-        <v>299.5011046657454</v>
+        <v>298.1243894751821</v>
       </c>
       <c r="D108" t="n">
-        <v>286.7342359222354</v>
+        <v>292.993883980321</v>
       </c>
       <c r="E108" t="n">
-        <v>297.3914489746094</v>
+        <v>296.52978515625</v>
       </c>
       <c r="F108" t="n">
-        <v>10278200</v>
+        <v>8055700</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B109" t="n">
-        <v>297.1240288614248</v>
+        <v>295.1332451958745</v>
       </c>
       <c r="C109" t="n">
-        <v>298.1243894751821</v>
+        <v>298.3620800816865</v>
       </c>
       <c r="D109" t="n">
-        <v>292.993883980321</v>
+        <v>289.6362492414601</v>
       </c>
       <c r="E109" t="n">
-        <v>296.52978515625</v>
+        <v>290.7455444335938</v>
       </c>
       <c r="F109" t="n">
-        <v>8055700</v>
+        <v>12732500</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B110" t="n">
-        <v>295.1332451958745</v>
+        <v>283.6044306839189</v>
       </c>
       <c r="C110" t="n">
-        <v>298.3620800816865</v>
+        <v>287.2195541533999</v>
       </c>
       <c r="D110" t="n">
-        <v>289.6362492414601</v>
+        <v>280.9995517042956</v>
       </c>
       <c r="E110" t="n">
-        <v>290.7455444335938</v>
+        <v>286.7144470214844</v>
       </c>
       <c r="F110" t="n">
-        <v>12732500</v>
+        <v>13496500</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B111" t="n">
-        <v>283.6044306839189</v>
+        <v>282.7724816341387</v>
       </c>
       <c r="C111" t="n">
-        <v>287.2195541533999</v>
+        <v>288.3189881947603</v>
       </c>
       <c r="D111" t="n">
-        <v>280.9995517042956</v>
+        <v>277.7707387954702</v>
       </c>
       <c r="E111" t="n">
-        <v>286.7144470214844</v>
+        <v>287.1502685546875</v>
       </c>
       <c r="F111" t="n">
-        <v>13496500</v>
+        <v>12241100</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B112" t="n">
-        <v>282.7724816341387</v>
+        <v>286.5262662545288</v>
       </c>
       <c r="C112" t="n">
-        <v>288.3189881947603</v>
+        <v>289.9532025593205</v>
       </c>
       <c r="D112" t="n">
-        <v>277.7707387954702</v>
+        <v>284.4364084963449</v>
       </c>
       <c r="E112" t="n">
-        <v>287.1502685546875</v>
+        <v>285.9716186523438</v>
       </c>
       <c r="F112" t="n">
-        <v>12241100</v>
+        <v>8344900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B113" t="n">
-        <v>286.5262662545288</v>
+        <v>286.0508166178312</v>
       </c>
       <c r="C113" t="n">
-        <v>289.9532025593205</v>
+        <v>287.7048753720447</v>
       </c>
       <c r="D113" t="n">
-        <v>284.4364084963449</v>
+        <v>282.1385413260368</v>
       </c>
       <c r="E113" t="n">
-        <v>285.9716186523438</v>
+        <v>284.7731323242188</v>
       </c>
       <c r="F113" t="n">
-        <v>8344900</v>
+        <v>10205000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B114" t="n">
-        <v>286.0508472723319</v>
+        <v>280.1279538528093</v>
       </c>
       <c r="C114" t="n">
-        <v>287.7049062038017</v>
+        <v>281.167940752382</v>
       </c>
       <c r="D114" t="n">
-        <v>282.1385715612803</v>
+        <v>276.4336079693154</v>
       </c>
       <c r="E114" t="n">
-        <v>284.7731628417969</v>
+        <v>280.1874084472656</v>
       </c>
       <c r="F114" t="n">
-        <v>10205000</v>
+        <v>13760500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B115" t="n">
-        <v>280.1279843639117</v>
+        <v>281.9504072447318</v>
       </c>
       <c r="C115" t="n">
-        <v>281.1679713767581</v>
+        <v>284.4463214441296</v>
       </c>
       <c r="D115" t="n">
-        <v>276.4336380780354</v>
+        <v>280.2468381234208</v>
       </c>
       <c r="E115" t="n">
-        <v>280.1874389648438</v>
+        <v>280.7321472167969</v>
       </c>
       <c r="F115" t="n">
-        <v>13760500</v>
+        <v>9091200</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B116" t="n">
-        <v>281.9504072447318</v>
+        <v>283.6044205599556</v>
       </c>
       <c r="C116" t="n">
-        <v>284.4463214441296</v>
+        <v>286.506421278288</v>
       </c>
       <c r="D116" t="n">
-        <v>280.2468381234208</v>
+        <v>281.8909373944359</v>
       </c>
       <c r="E116" t="n">
-        <v>280.7321472167969</v>
+        <v>283.4261474609375</v>
       </c>
       <c r="F116" t="n">
-        <v>9091200</v>
+        <v>8149000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B117" t="n">
-        <v>283.6044205599556</v>
+        <v>286.2390279690733</v>
       </c>
       <c r="C117" t="n">
-        <v>286.506421278288</v>
+        <v>288.9726698808299</v>
       </c>
       <c r="D117" t="n">
-        <v>281.8909373944359</v>
+        <v>283.2181783456238</v>
       </c>
       <c r="E117" t="n">
-        <v>283.4261474609375</v>
+        <v>284.1492004394531</v>
       </c>
       <c r="F117" t="n">
-        <v>8149000</v>
+        <v>8961200</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B118" t="n">
-        <v>286.2390279690733</v>
+        <v>284.0897484324327</v>
       </c>
       <c r="C118" t="n">
-        <v>288.9726698808299</v>
+        <v>286.6451172582804</v>
       </c>
       <c r="D118" t="n">
-        <v>283.2181783456238</v>
+        <v>282.3960934275981</v>
       </c>
       <c r="E118" t="n">
-        <v>284.1492004394531</v>
+        <v>284.9910583496094</v>
       </c>
       <c r="F118" t="n">
-        <v>8961200</v>
+        <v>10057000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B119" t="n">
-        <v>284.0897180113691</v>
+        <v>284.1392586396808</v>
       </c>
       <c r="C119" t="n">
-        <v>286.6450865635814</v>
+        <v>286.7441374214082</v>
       </c>
       <c r="D119" t="n">
-        <v>282.3960631878955</v>
+        <v>281.9008401776293</v>
       </c>
       <c r="E119" t="n">
-        <v>284.9910278320312</v>
+        <v>285.2188415527344</v>
       </c>
       <c r="F119" t="n">
-        <v>10057000</v>
+        <v>9846700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B120" t="n">
-        <v>284.1392890417467</v>
+        <v>285.327825032355</v>
       </c>
       <c r="C120" t="n">
-        <v>286.7441681021885</v>
+        <v>287.9327042603992</v>
       </c>
       <c r="D120" t="n">
-        <v>281.900870340191</v>
+        <v>282.5446726819272</v>
       </c>
       <c r="E120" t="n">
-        <v>285.2188720703125</v>
+        <v>283.8223571777344</v>
       </c>
       <c r="F120" t="n">
-        <v>9846700</v>
+        <v>22436500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B121" t="n">
-        <v>285.3277943529036</v>
+        <v>291.4982779446762</v>
       </c>
       <c r="C121" t="n">
-        <v>287.9326733008621</v>
+        <v>292.9245231806114</v>
       </c>
       <c r="D121" t="n">
-        <v>282.5446423017302</v>
+        <v>285.2188513876401</v>
       </c>
       <c r="E121" t="n">
-        <v>283.8223266601562</v>
+        <v>287.1403198242188</v>
       </c>
       <c r="F121" t="n">
-        <v>22436500</v>
+        <v>11470800</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B122" t="n">
-        <v>291.4982779446762</v>
+        <v>283.4360748065673</v>
       </c>
       <c r="C122" t="n">
-        <v>292.9245231806114</v>
+        <v>292.6571288676103</v>
       </c>
       <c r="D122" t="n">
-        <v>285.2188513876401</v>
+        <v>282.6436995084055</v>
       </c>
       <c r="E122" t="n">
-        <v>287.1403198242188</v>
+        <v>289.6065368652344</v>
       </c>
       <c r="F122" t="n">
-        <v>11470800</v>
+        <v>11092300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B123" t="n">
-        <v>283.4360748065673</v>
+        <v>291.3398308899875</v>
       </c>
       <c r="C123" t="n">
-        <v>292.6571288676103</v>
+        <v>294.7965097163498</v>
       </c>
       <c r="D123" t="n">
-        <v>282.6436995084055</v>
+        <v>289.6461758443202</v>
       </c>
       <c r="E123" t="n">
-        <v>289.6065368652344</v>
+        <v>292.5977172851562</v>
       </c>
       <c r="F123" t="n">
-        <v>11092300</v>
+        <v>12188200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B124" t="n">
-        <v>291.3398308899875</v>
+        <v>289.7848205526045</v>
       </c>
       <c r="C124" t="n">
-        <v>294.7965097163498</v>
+        <v>292.1718002190451</v>
       </c>
       <c r="D124" t="n">
-        <v>289.6461758443202</v>
+        <v>287.9525187281419</v>
       </c>
       <c r="E124" t="n">
-        <v>292.5977172851562</v>
+        <v>288.8736267089844</v>
       </c>
       <c r="F124" t="n">
-        <v>12188200</v>
+        <v>8669200</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B125" t="n">
-        <v>289.7847899387647</v>
+        <v>286.3777093696089</v>
       </c>
       <c r="C125" t="n">
-        <v>292.1717693530369</v>
+        <v>287.3384134369941</v>
       </c>
       <c r="D125" t="n">
-        <v>287.9524883078727</v>
+        <v>279.0582953832721</v>
       </c>
       <c r="E125" t="n">
-        <v>288.8735961914062</v>
+        <v>280.1378784179688</v>
       </c>
       <c r="F125" t="n">
-        <v>8669200</v>
+        <v>9873300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B126" t="n">
-        <v>286.3777093696089</v>
+        <v>282.0197247859078</v>
       </c>
       <c r="C126" t="n">
-        <v>287.3384134369941</v>
+        <v>284.505755156032</v>
       </c>
       <c r="D126" t="n">
-        <v>279.0582953832721</v>
+        <v>279.6327451103039</v>
       </c>
       <c r="E126" t="n">
-        <v>280.1378784179688</v>
+        <v>281.0589904785156</v>
       </c>
       <c r="F126" t="n">
-        <v>9873300</v>
+        <v>11734400</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B127" t="n">
-        <v>282.0197247859078</v>
+        <v>285.7140887250632</v>
       </c>
       <c r="C127" t="n">
-        <v>284.505755156032</v>
+        <v>292.2510413422024</v>
       </c>
       <c r="D127" t="n">
-        <v>279.6327451103039</v>
+        <v>282.2277281014015</v>
       </c>
       <c r="E127" t="n">
-        <v>281.0589904785156</v>
+        <v>291.3497314453125</v>
       </c>
       <c r="F127" t="n">
-        <v>11734400</v>
+        <v>12956900</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B128" t="n">
-        <v>285.7140887250632</v>
+        <v>292.567989087923</v>
       </c>
       <c r="C128" t="n">
-        <v>292.2510413422024</v>
+        <v>295.8661624411999</v>
       </c>
       <c r="D128" t="n">
-        <v>282.2277281014015</v>
+        <v>290.1116710297465</v>
       </c>
       <c r="E128" t="n">
-        <v>291.3497314453125</v>
+        <v>292.5580749511719</v>
       </c>
       <c r="F128" t="n">
-        <v>12956900</v>
+        <v>11267200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B129" t="n">
-        <v>292.567989087923</v>
+        <v>289.1212191631598</v>
       </c>
       <c r="C129" t="n">
-        <v>295.8661624411999</v>
+        <v>292.7957669317203</v>
       </c>
       <c r="D129" t="n">
-        <v>290.1116710297465</v>
+        <v>285.9616926535428</v>
       </c>
       <c r="E129" t="n">
-        <v>292.5580749511719</v>
+        <v>291.7855224609375</v>
       </c>
       <c r="F129" t="n">
-        <v>11267200</v>
+        <v>6669300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,25 +3797,25 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B130" t="n">
-        <v>289.1212191631598</v>
+        <v>292.7412191857173</v>
       </c>
       <c r="C130" t="n">
-        <v>292.7957669317203</v>
+        <v>295.4987855589938</v>
       </c>
       <c r="D130" t="n">
-        <v>285.9616926535428</v>
+        <v>291.8850906324002</v>
       </c>
       <c r="E130" t="n">
-        <v>291.7855224609375</v>
+        <v>294.125</v>
       </c>
       <c r="F130" t="n">
-        <v>6669300</v>
+        <v>7142600</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -3823,25 +3823,25 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B131" t="n">
-        <v>292.7412191857173</v>
+        <v>291.8253790066561</v>
       </c>
       <c r="C131" t="n">
-        <v>295.4987855589938</v>
+        <v>296.8427544058445</v>
       </c>
       <c r="D131" t="n">
-        <v>291.8850906324002</v>
+        <v>291.3873498301165</v>
       </c>
       <c r="E131" t="n">
-        <v>294.125</v>
+        <v>296.0662536621094</v>
       </c>
       <c r="F131" t="n">
-        <v>7142600</v>
+        <v>7849100</v>
       </c>
       <c r="G131" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B132" t="n">
-        <v>291.8253790066561</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="C132" t="n">
-        <v>296.8427544058445</v>
+        <v>309.8640903908154</v>
       </c>
       <c r="D132" t="n">
-        <v>291.3873498301165</v>
+        <v>303.9606617936424</v>
       </c>
       <c r="E132" t="n">
-        <v>296.0662536621094</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="F132" t="n">
-        <v>7849100</v>
+        <v>10590200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B133" t="n">
-        <v>306.5888366699219</v>
+        <v>305.5734164156603</v>
       </c>
       <c r="C133" t="n">
-        <v>309.8640903908154</v>
+        <v>309.8640846884941</v>
       </c>
       <c r="D133" t="n">
-        <v>303.9606617936424</v>
+        <v>304.73715687535</v>
       </c>
       <c r="E133" t="n">
-        <v>306.5888366699219</v>
+        <v>308.938232421875</v>
       </c>
       <c r="F133" t="n">
-        <v>10590200</v>
+        <v>6586600</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B134" t="n">
-        <v>305.5734164156603</v>
+        <v>308.6097380099313</v>
       </c>
       <c r="C134" t="n">
-        <v>309.8640846884941</v>
+        <v>308.9581744354404</v>
       </c>
       <c r="D134" t="n">
-        <v>304.73715687535</v>
+        <v>305.344449093958</v>
       </c>
       <c r="E134" t="n">
-        <v>308.938232421875</v>
+        <v>308.4803161621094</v>
       </c>
       <c r="F134" t="n">
-        <v>6586600</v>
+        <v>6069700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B135" t="n">
-        <v>308.6097380099313</v>
+        <v>306.0910825316173</v>
       </c>
       <c r="C135" t="n">
-        <v>308.9581744354404</v>
+        <v>312.3329523629397</v>
       </c>
       <c r="D135" t="n">
-        <v>305.344449093958</v>
+        <v>304.0900871089203</v>
       </c>
       <c r="E135" t="n">
-        <v>308.4803161621094</v>
+        <v>312.2732238769531</v>
       </c>
       <c r="F135" t="n">
-        <v>6069700</v>
+        <v>8318200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B136" t="n">
-        <v>306.0910825316173</v>
+        <v>308.4305432499699</v>
       </c>
       <c r="C136" t="n">
-        <v>312.3329523629397</v>
+        <v>312.9103618924516</v>
       </c>
       <c r="D136" t="n">
-        <v>304.0900871089203</v>
+        <v>307.4847916064935</v>
       </c>
       <c r="E136" t="n">
-        <v>312.2732238769531</v>
+        <v>309.7247009277344</v>
       </c>
       <c r="F136" t="n">
-        <v>8318200</v>
+        <v>11455500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B137" t="n">
-        <v>308.4305432499699</v>
+        <v>312.5420354159922</v>
       </c>
       <c r="C137" t="n">
-        <v>312.9103618924516</v>
+        <v>312.8307129741003</v>
       </c>
       <c r="D137" t="n">
-        <v>307.4847916064935</v>
+        <v>302.8954898881459</v>
       </c>
       <c r="E137" t="n">
-        <v>309.7247009277344</v>
+        <v>304.5579833984375</v>
       </c>
       <c r="F137" t="n">
-        <v>11455500</v>
+        <v>9885800</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B138" t="n">
-        <v>312.5420354159922</v>
+        <v>303.9805907681049</v>
       </c>
       <c r="C138" t="n">
-        <v>312.8307129741003</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="D138" t="n">
-        <v>302.8954898881459</v>
+        <v>303.8312695552229</v>
       </c>
       <c r="E138" t="n">
-        <v>304.5579833984375</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="F138" t="n">
-        <v>9885800</v>
+        <v>8208600</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B139" t="n">
-        <v>303.9805907681049</v>
+        <v>311.068653468178</v>
       </c>
       <c r="C139" t="n">
-        <v>308.5599670410156</v>
+        <v>313.4877482505245</v>
       </c>
       <c r="D139" t="n">
-        <v>303.8312695552229</v>
+        <v>308.6993222963794</v>
       </c>
       <c r="E139" t="n">
-        <v>308.5599670410156</v>
+        <v>308.8984375</v>
       </c>
       <c r="F139" t="n">
-        <v>8208600</v>
+        <v>11082400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B140" t="n">
-        <v>311.068653468178</v>
+        <v>309.4559416581444</v>
       </c>
       <c r="C140" t="n">
-        <v>313.4877482505245</v>
+        <v>315.7077766193834</v>
       </c>
       <c r="D140" t="n">
-        <v>308.6993222963794</v>
+        <v>308.9780833700189</v>
       </c>
       <c r="E140" t="n">
-        <v>308.8984375</v>
+        <v>315.5683898925781</v>
       </c>
       <c r="F140" t="n">
-        <v>11082400</v>
+        <v>10772000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B141" t="n">
-        <v>309.4559416581444</v>
+        <v>316.0661368489313</v>
       </c>
       <c r="C141" t="n">
-        <v>315.7077766193834</v>
+        <v>318.8038038717339</v>
       </c>
       <c r="D141" t="n">
-        <v>308.9780833700189</v>
+        <v>311.3474041387296</v>
       </c>
       <c r="E141" t="n">
-        <v>315.5683898925781</v>
+        <v>311.5962829589844</v>
       </c>
       <c r="F141" t="n">
-        <v>10772000</v>
+        <v>7084300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B142" t="n">
-        <v>316.0661368489313</v>
+        <v>313.4379903862348</v>
       </c>
       <c r="C142" t="n">
-        <v>318.8038038717339</v>
+        <v>313.7366328164263</v>
       </c>
       <c r="D142" t="n">
-        <v>311.3474041387296</v>
+        <v>310.5410372905177</v>
       </c>
       <c r="E142" t="n">
-        <v>311.5962829589844</v>
+        <v>311.6161804199219</v>
       </c>
       <c r="F142" t="n">
-        <v>7084300</v>
+        <v>5545900</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B143" t="n">
-        <v>313.4379903862348</v>
+        <v>312.1139549773267</v>
       </c>
       <c r="C143" t="n">
-        <v>313.7366328164263</v>
+        <v>313.5773637260273</v>
       </c>
       <c r="D143" t="n">
-        <v>310.5410372905177</v>
+        <v>307.5047445243564</v>
       </c>
       <c r="E143" t="n">
-        <v>311.6161804199219</v>
+        <v>310.2921752929688</v>
       </c>
       <c r="F143" t="n">
-        <v>5545900</v>
+        <v>6969700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B144" t="n">
-        <v>312.1139549773267</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="C144" t="n">
-        <v>313.5773637260273</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="D144" t="n">
-        <v>307.5047445243564</v>
+        <v>306.5092257615542</v>
       </c>
       <c r="E144" t="n">
-        <v>310.2921752929688</v>
+        <v>306.8974609375</v>
       </c>
       <c r="F144" t="n">
-        <v>6969700</v>
+        <v>5215300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B145" t="n">
-        <v>309.7545850384977</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="C145" t="n">
-        <v>309.7545850384977</v>
+        <v>311.1781431330245</v>
       </c>
       <c r="D145" t="n">
-        <v>306.5092257615542</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="E145" t="n">
-        <v>306.8974609375</v>
+        <v>310.232421875</v>
       </c>
       <c r="F145" t="n">
-        <v>5215300</v>
+        <v>7925300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B146" t="n">
-        <v>305.5037244427344</v>
+        <v>313.7864355589005</v>
       </c>
       <c r="C146" t="n">
-        <v>311.1781431330245</v>
+        <v>314.035314384572</v>
       </c>
       <c r="D146" t="n">
-        <v>305.5037244427344</v>
+        <v>309.7745101043047</v>
       </c>
       <c r="E146" t="n">
-        <v>310.232421875</v>
+        <v>310.0532531738281</v>
       </c>
       <c r="F146" t="n">
-        <v>7925300</v>
+        <v>7398600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B147" t="n">
-        <v>313.7864355589005</v>
+        <v>309.1771855961317</v>
       </c>
       <c r="C147" t="n">
-        <v>314.035314384572</v>
+        <v>310.6505287563671</v>
       </c>
       <c r="D147" t="n">
-        <v>309.7745101043047</v>
+        <v>305.9118967162461</v>
       </c>
       <c r="E147" t="n">
-        <v>310.0532531738281</v>
+        <v>307.8630981445312</v>
       </c>
       <c r="F147" t="n">
-        <v>7398600</v>
+        <v>8031800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B148" t="n">
-        <v>309.1771855961317</v>
+        <v>305.6928786901284</v>
       </c>
       <c r="C148" t="n">
-        <v>310.6505287563671</v>
+        <v>312.6913497643884</v>
       </c>
       <c r="D148" t="n">
-        <v>305.9118967162461</v>
+        <v>305.1951210592971</v>
       </c>
       <c r="E148" t="n">
-        <v>307.8630981445312</v>
+        <v>311.8252563476562</v>
       </c>
       <c r="F148" t="n">
-        <v>8031800</v>
+        <v>8865400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B149" t="n">
-        <v>305.6928786901284</v>
+        <v>312.5420381202088</v>
       </c>
       <c r="C149" t="n">
-        <v>312.6913497643884</v>
+        <v>314.6624601726697</v>
       </c>
       <c r="D149" t="n">
-        <v>305.1951210592971</v>
+        <v>310.431520181067</v>
       </c>
       <c r="E149" t="n">
-        <v>311.8252563476562</v>
+        <v>311.0686645507812</v>
       </c>
       <c r="F149" t="n">
-        <v>8865400</v>
+        <v>6135400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B150" t="n">
-        <v>312.5420381202088</v>
+        <v>309.2269452093906</v>
       </c>
       <c r="C150" t="n">
-        <v>314.6624601726697</v>
+        <v>309.2568094519629</v>
       </c>
       <c r="D150" t="n">
-        <v>310.431520181067</v>
+        <v>305.1353920734132</v>
       </c>
       <c r="E150" t="n">
-        <v>311.0686645507812</v>
+        <v>306.270263671875</v>
       </c>
       <c r="F150" t="n">
-        <v>6135400</v>
+        <v>7338200</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B151" t="n">
-        <v>309.2269452093906</v>
+        <v>306.3299974055641</v>
       </c>
       <c r="C151" t="n">
-        <v>309.2568094519629</v>
+        <v>309.5753869306937</v>
       </c>
       <c r="D151" t="n">
-        <v>305.1353920734132</v>
+        <v>305.42407485773</v>
       </c>
       <c r="E151" t="n">
-        <v>306.270263671875</v>
+        <v>308.0124206542969</v>
       </c>
       <c r="F151" t="n">
-        <v>7338200</v>
+        <v>6316800</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B152" t="n">
-        <v>306.3299974055641</v>
+        <v>310.0532528884956</v>
       </c>
       <c r="C152" t="n">
-        <v>309.5753869306937</v>
+        <v>314.8416790595512</v>
       </c>
       <c r="D152" t="n">
-        <v>305.42407485773</v>
+        <v>309.9536952821754</v>
       </c>
       <c r="E152" t="n">
-        <v>308.0124206542969</v>
+        <v>313.4877624511719</v>
       </c>
       <c r="F152" t="n">
-        <v>6316800</v>
+        <v>8629500</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B153" t="n">
-        <v>310.0532528884956</v>
+        <v>313.2388767644321</v>
       </c>
       <c r="C153" t="n">
-        <v>314.8416790595512</v>
+        <v>314.8814709002291</v>
       </c>
       <c r="D153" t="n">
-        <v>309.9536952821754</v>
+        <v>304.7670623908274</v>
       </c>
       <c r="E153" t="n">
-        <v>313.4877624511719</v>
+        <v>304.8964538574219</v>
       </c>
       <c r="F153" t="n">
-        <v>8629500</v>
+        <v>8359600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B154" t="n">
-        <v>313.2388767644321</v>
+        <v>306.8675912418493</v>
       </c>
       <c r="C154" t="n">
-        <v>314.8814709002291</v>
+        <v>307.6042628420606</v>
       </c>
       <c r="D154" t="n">
-        <v>304.7670623908274</v>
+        <v>299.1523476664256</v>
       </c>
       <c r="E154" t="n">
-        <v>304.8964538574219</v>
+        <v>300.7451782226562</v>
       </c>
       <c r="F154" t="n">
-        <v>8359600</v>
+        <v>9464300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B155" t="n">
-        <v>306.8675912418493</v>
+        <v>300.7451596100784</v>
       </c>
       <c r="C155" t="n">
-        <v>307.6042628420606</v>
+        <v>301.8302675742967</v>
       </c>
       <c r="D155" t="n">
-        <v>299.1523476664256</v>
+        <v>297.5395993270601</v>
       </c>
       <c r="E155" t="n">
-        <v>300.7451782226562</v>
+        <v>298.6545715332031</v>
       </c>
       <c r="F155" t="n">
-        <v>9464300</v>
+        <v>9512000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B156" t="n">
-        <v>300.7451596100784</v>
+        <v>298.6744753830843</v>
       </c>
       <c r="C156" t="n">
-        <v>301.8302675742967</v>
+        <v>304.6873960201211</v>
       </c>
       <c r="D156" t="n">
-        <v>297.5395993270601</v>
+        <v>294.2245209852311</v>
       </c>
       <c r="E156" t="n">
-        <v>298.6545715332031</v>
+        <v>303.5126953125</v>
       </c>
       <c r="F156" t="n">
-        <v>9512000</v>
+        <v>9498200</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B157" t="n">
-        <v>298.6744753830843</v>
+        <v>300.9144028967509</v>
       </c>
       <c r="C157" t="n">
-        <v>304.6873960201211</v>
+        <v>301.6411400127173</v>
       </c>
       <c r="D157" t="n">
-        <v>294.2245209852311</v>
+        <v>298.7242874353194</v>
       </c>
       <c r="E157" t="n">
-        <v>303.5126953125</v>
+        <v>298.9034729003906</v>
       </c>
       <c r="F157" t="n">
-        <v>9498200</v>
+        <v>7709500</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B158" t="n">
-        <v>300.9144028967509</v>
+        <v>300.8945046380796</v>
       </c>
       <c r="C158" t="n">
-        <v>301.6411400127173</v>
+        <v>302.387777613951</v>
       </c>
       <c r="D158" t="n">
-        <v>298.7242874353194</v>
+        <v>297.4699295162906</v>
       </c>
       <c r="E158" t="n">
-        <v>298.9034729003906</v>
+        <v>298.5650024414062</v>
       </c>
       <c r="F158" t="n">
-        <v>7709500</v>
+        <v>7364300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B159" t="n">
-        <v>300.8945046380796</v>
+        <v>298.8636262885424</v>
       </c>
       <c r="C159" t="n">
-        <v>302.387777613951</v>
+        <v>299.4410421498196</v>
       </c>
       <c r="D159" t="n">
-        <v>297.4699295162906</v>
+        <v>295.1205095874812</v>
       </c>
       <c r="E159" t="n">
-        <v>298.5650024414062</v>
+        <v>296.4743957519531</v>
       </c>
       <c r="F159" t="n">
-        <v>7364300</v>
+        <v>8699300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B160" t="n">
-        <v>298.8636262885424</v>
+        <v>296.6635495230975</v>
       </c>
       <c r="C160" t="n">
-        <v>299.4410421498196</v>
+        <v>299.908939014877</v>
       </c>
       <c r="D160" t="n">
-        <v>295.1205095874812</v>
+        <v>295.8870488301784</v>
       </c>
       <c r="E160" t="n">
-        <v>296.4743957519531</v>
+        <v>299.3813171386719</v>
       </c>
       <c r="F160" t="n">
-        <v>8699300</v>
+        <v>7546300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B161" t="n">
-        <v>296.6635495230975</v>
+        <v>299.7396822358739</v>
       </c>
       <c r="C161" t="n">
-        <v>299.908939014877</v>
+        <v>300.436555061437</v>
       </c>
       <c r="D161" t="n">
-        <v>295.8870488301784</v>
+        <v>293.935841710235</v>
       </c>
       <c r="E161" t="n">
-        <v>299.3813171386719</v>
+        <v>294.3738708496094</v>
       </c>
       <c r="F161" t="n">
-        <v>7546300</v>
+        <v>8066900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B162" t="n">
-        <v>299.7396822358739</v>
+        <v>295.3694126574367</v>
       </c>
       <c r="C162" t="n">
-        <v>300.436555061437</v>
+        <v>301.57145376365</v>
       </c>
       <c r="D162" t="n">
-        <v>293.935841710235</v>
+        <v>292.3530024013792</v>
       </c>
       <c r="E162" t="n">
-        <v>294.3738708496094</v>
+        <v>300.625732421875</v>
       </c>
       <c r="F162" t="n">
-        <v>8066900</v>
+        <v>9327000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B163" t="n">
-        <v>295.3694126574367</v>
+        <v>299.8790926087445</v>
       </c>
       <c r="C163" t="n">
-        <v>301.57145376365</v>
+        <v>302.6167597554335</v>
       </c>
       <c r="D163" t="n">
-        <v>292.3530024013792</v>
+        <v>298.8636475324957</v>
       </c>
       <c r="E163" t="n">
-        <v>300.625732421875</v>
+        <v>301.6411437988281</v>
       </c>
       <c r="F163" t="n">
-        <v>9327000</v>
+        <v>7874400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B164" t="n">
-        <v>299.8790926087445</v>
+        <v>303.3135932887391</v>
       </c>
       <c r="C164" t="n">
-        <v>302.6167597554335</v>
+        <v>306.0711901040885</v>
       </c>
       <c r="D164" t="n">
-        <v>298.8636475324957</v>
+        <v>302.4773640852478</v>
       </c>
       <c r="E164" t="n">
-        <v>301.6411437988281</v>
+        <v>305.0059814453125</v>
       </c>
       <c r="F164" t="n">
-        <v>7874400</v>
+        <v>5973900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B165" t="n">
-        <v>303.3135932887391</v>
+        <v>307.1065011172144</v>
       </c>
       <c r="C165" t="n">
-        <v>306.0711901040885</v>
+        <v>308.5400455607295</v>
       </c>
       <c r="D165" t="n">
-        <v>302.4773640852478</v>
+        <v>304.0701916446211</v>
       </c>
       <c r="E165" t="n">
-        <v>305.0059814453125</v>
+        <v>305.3643493652344</v>
       </c>
       <c r="F165" t="n">
-        <v>5973900</v>
+        <v>7725400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B166" t="n">
-        <v>307.1065011172144</v>
+        <v>303.6321536663258</v>
       </c>
       <c r="C166" t="n">
-        <v>308.5400455607295</v>
+        <v>304.5281113223131</v>
       </c>
       <c r="D166" t="n">
-        <v>304.0701916446211</v>
+        <v>294.4236375305438</v>
       </c>
       <c r="E166" t="n">
-        <v>305.3643493652344</v>
+        <v>297.9378051757812</v>
       </c>
       <c r="F166" t="n">
-        <v>7725400</v>
+        <v>11779200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B167" t="n">
-        <v>303.6321536663258</v>
+        <v>296.2354906683788</v>
       </c>
       <c r="C167" t="n">
-        <v>304.5281113223131</v>
+        <v>299.7197941661088</v>
       </c>
       <c r="D167" t="n">
-        <v>294.4236375305438</v>
+        <v>294.4236455581874</v>
       </c>
       <c r="E167" t="n">
-        <v>297.9378051757812</v>
+        <v>295.3992614746094</v>
       </c>
       <c r="F167" t="n">
-        <v>11779200</v>
+        <v>9757700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B168" t="n">
-        <v>296.2354906683788</v>
+        <v>295.070728717322</v>
       </c>
       <c r="C168" t="n">
-        <v>299.7197941661088</v>
+        <v>298.5351328968941</v>
       </c>
       <c r="D168" t="n">
-        <v>294.4236455581874</v>
+        <v>293.8761285862639</v>
       </c>
       <c r="E168" t="n">
-        <v>295.3992614746094</v>
+        <v>297.9676818847656</v>
       </c>
       <c r="F168" t="n">
-        <v>9757700</v>
+        <v>13969000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B169" t="n">
-        <v>295.070728717322</v>
+        <v>296.3549462063085</v>
       </c>
       <c r="C169" t="n">
-        <v>298.5351328968941</v>
+        <v>298.2065900448191</v>
       </c>
       <c r="D169" t="n">
-        <v>293.8761285862639</v>
+        <v>293.9457858606032</v>
       </c>
       <c r="E169" t="n">
-        <v>297.9676818847656</v>
+        <v>295.2499084472656</v>
       </c>
       <c r="F169" t="n">
-        <v>13969000</v>
+        <v>7930000</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B170" t="n">
-        <v>296.3549462063085</v>
+        <v>295.170270518017</v>
       </c>
       <c r="C170" t="n">
-        <v>298.2065900448191</v>
+        <v>300.7152977310929</v>
       </c>
       <c r="D170" t="n">
-        <v>293.9457858606032</v>
+        <v>293.9457758280521</v>
       </c>
       <c r="E170" t="n">
-        <v>295.2499084472656</v>
+        <v>299.6102600097656</v>
       </c>
       <c r="F170" t="n">
-        <v>7930000</v>
+        <v>8296200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B171" t="n">
-        <v>295.170270518017</v>
+        <v>298.5749714904202</v>
       </c>
       <c r="C171" t="n">
-        <v>300.7152977310929</v>
+        <v>300.6058008918799</v>
       </c>
       <c r="D171" t="n">
-        <v>293.9457758280521</v>
+        <v>295.2300241797341</v>
       </c>
       <c r="E171" t="n">
-        <v>299.6102600097656</v>
+        <v>299.5007934570312</v>
       </c>
       <c r="F171" t="n">
-        <v>8296200</v>
+        <v>7003900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B172" t="n">
-        <v>298.5749714904202</v>
+        <v>304.3688300919619</v>
       </c>
       <c r="C172" t="n">
-        <v>300.6058008918799</v>
+        <v>311.5066879726736</v>
       </c>
       <c r="D172" t="n">
-        <v>295.2300241797341</v>
+        <v>303.0746723882986</v>
       </c>
       <c r="E172" t="n">
-        <v>299.5007934570312</v>
+        <v>309.4957580566406</v>
       </c>
       <c r="F172" t="n">
-        <v>7003900</v>
+        <v>10345200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B173" t="n">
-        <v>304.3688300919619</v>
+        <v>312.8805189963161</v>
       </c>
       <c r="C173" t="n">
-        <v>311.5066879726736</v>
+        <v>313.5873263681962</v>
       </c>
       <c r="D173" t="n">
-        <v>303.0746723882986</v>
+        <v>308.211549706599</v>
       </c>
       <c r="E173" t="n">
-        <v>309.4957580566406</v>
+        <v>310.9691162109375</v>
       </c>
       <c r="F173" t="n">
-        <v>10345200</v>
+        <v>9118800</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B174" t="n">
-        <v>312.8805189963161</v>
+        <v>311.8451695343703</v>
       </c>
       <c r="C174" t="n">
-        <v>313.5873263681962</v>
+        <v>314.881479064701</v>
       </c>
       <c r="D174" t="n">
-        <v>308.211549706599</v>
+        <v>309.3862455138746</v>
       </c>
       <c r="E174" t="n">
-        <v>310.9691162109375</v>
+        <v>309.7147521972656</v>
       </c>
       <c r="F174" t="n">
-        <v>9118800</v>
+        <v>6827000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B175" t="n">
-        <v>311.8451695343703</v>
+        <v>312.1040028799189</v>
       </c>
       <c r="C175" t="n">
-        <v>314.881479064701</v>
+        <v>315.0009559692908</v>
       </c>
       <c r="D175" t="n">
-        <v>309.3862455138746</v>
+        <v>307.6241841525692</v>
       </c>
       <c r="E175" t="n">
-        <v>309.7147521972656</v>
+        <v>311.2976379394531</v>
       </c>
       <c r="F175" t="n">
-        <v>6827000</v>
+        <v>11594600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B176" t="n">
-        <v>312.1040028799189</v>
+        <v>311.1582462393224</v>
       </c>
       <c r="C176" t="n">
-        <v>315.0009559692908</v>
+        <v>313.3384270822022</v>
       </c>
       <c r="D176" t="n">
-        <v>307.6241841525692</v>
+        <v>307.6440785979976</v>
       </c>
       <c r="E176" t="n">
-        <v>311.2976379394531</v>
+        <v>307.7536010742188</v>
       </c>
       <c r="F176" t="n">
-        <v>11594600</v>
+        <v>7446200</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B177" t="n">
-        <v>311.1582462393224</v>
+        <v>308.1717081621576</v>
       </c>
       <c r="C177" t="n">
-        <v>313.3384270822022</v>
+        <v>313.3085706612414</v>
       </c>
       <c r="D177" t="n">
-        <v>307.6440785979976</v>
+        <v>307.4947650619962</v>
       </c>
       <c r="E177" t="n">
-        <v>307.7536010742188</v>
+        <v>312.0840759277344</v>
       </c>
       <c r="F177" t="n">
-        <v>7446200</v>
+        <v>9116600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B178" t="n">
-        <v>308.1717081621576</v>
+        <v>314.5529794375797</v>
       </c>
       <c r="C178" t="n">
-        <v>313.3085706612414</v>
+        <v>319.8590627688811</v>
       </c>
       <c r="D178" t="n">
-        <v>307.4947650619962</v>
+        <v>314.1348496322589</v>
       </c>
       <c r="E178" t="n">
-        <v>312.0840759277344</v>
+        <v>319.2816772460938</v>
       </c>
       <c r="F178" t="n">
-        <v>9116600</v>
+        <v>7426200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B179" t="n">
-        <v>314.5529794375797</v>
+        <v>322.4673390673774</v>
       </c>
       <c r="C179" t="n">
-        <v>319.8590627688811</v>
+        <v>324.4583697274161</v>
       </c>
       <c r="D179" t="n">
-        <v>314.1348496322589</v>
+        <v>317.4101041776777</v>
       </c>
       <c r="E179" t="n">
-        <v>319.2816772460938</v>
+        <v>317.9675903320312</v>
       </c>
       <c r="F179" t="n">
-        <v>7426200</v>
+        <v>7988900</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B180" t="n">
-        <v>322.4673390673774</v>
+        <v>322.8455866314347</v>
       </c>
       <c r="C180" t="n">
-        <v>324.4583697274161</v>
+        <v>330.2621874699331</v>
       </c>
       <c r="D180" t="n">
-        <v>317.4101041776777</v>
+        <v>322.5668435738929</v>
       </c>
       <c r="E180" t="n">
-        <v>317.9675903320312</v>
+        <v>329.6549377441406</v>
       </c>
       <c r="F180" t="n">
-        <v>7988900</v>
+        <v>11094900</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B181" t="n">
-        <v>322.8455866314347</v>
+        <v>330.6902497468859</v>
       </c>
       <c r="C181" t="n">
-        <v>330.2621874699331</v>
+        <v>336.2551763704633</v>
       </c>
       <c r="D181" t="n">
-        <v>322.5668435738929</v>
+        <v>330.0133066656099</v>
       </c>
       <c r="E181" t="n">
-        <v>329.6549377441406</v>
+        <v>331.9645080566406</v>
       </c>
       <c r="F181" t="n">
-        <v>11094900</v>
+        <v>12246400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B182" t="n">
-        <v>330.6902497468859</v>
+        <v>335.4388795655989</v>
       </c>
       <c r="C182" t="n">
-        <v>336.2551763704633</v>
+        <v>336.5737511659094</v>
       </c>
       <c r="D182" t="n">
-        <v>330.0133066656099</v>
+        <v>322.7062308624821</v>
       </c>
       <c r="E182" t="n">
-        <v>331.9645080566406</v>
+        <v>323.761474609375</v>
       </c>
       <c r="F182" t="n">
-        <v>12246400</v>
+        <v>20111000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B183" t="n">
-        <v>335.4388795655989</v>
+        <v>328.221392261561</v>
       </c>
       <c r="C183" t="n">
-        <v>336.5737511659094</v>
+        <v>331.2776010100568</v>
       </c>
       <c r="D183" t="n">
-        <v>322.7062308624821</v>
+        <v>325.2846101022313</v>
       </c>
       <c r="E183" t="n">
-        <v>323.761474609375</v>
+        <v>329.993408203125</v>
       </c>
       <c r="F183" t="n">
-        <v>20111000</v>
+        <v>10182500</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B184" t="n">
-        <v>328.221392261561</v>
+        <v>327.9924099173137</v>
       </c>
       <c r="C184" t="n">
-        <v>331.2776010100568</v>
+        <v>333.8659438033595</v>
       </c>
       <c r="D184" t="n">
-        <v>325.2846101022313</v>
+        <v>325.7425357353925</v>
       </c>
       <c r="E184" t="n">
-        <v>329.993408203125</v>
+        <v>332.6414794921875</v>
       </c>
       <c r="F184" t="n">
-        <v>10182500</v>
+        <v>7582200</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B185" t="n">
-        <v>327.9924099173137</v>
+        <v>331.5762891678024</v>
       </c>
       <c r="C185" t="n">
-        <v>333.8659438033595</v>
+        <v>333.0297330031709</v>
       </c>
       <c r="D185" t="n">
-        <v>325.7425357353925</v>
+        <v>328.291070440402</v>
       </c>
       <c r="E185" t="n">
-        <v>332.6414794921875</v>
+        <v>331.95458984375</v>
       </c>
       <c r="F185" t="n">
-        <v>7582200</v>
+        <v>7907400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B186" t="n">
-        <v>331.5762891678024</v>
+        <v>333.4577793441399</v>
       </c>
       <c r="C186" t="n">
-        <v>333.0297330031709</v>
+        <v>341.909724468194</v>
       </c>
       <c r="D186" t="n">
-        <v>328.291070440402</v>
+        <v>333.2586945227413</v>
       </c>
       <c r="E186" t="n">
-        <v>331.95458984375</v>
+        <v>333.6170654296875</v>
       </c>
       <c r="F186" t="n">
-        <v>7907400</v>
+        <v>10043100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B187" t="n">
-        <v>333.4577793441399</v>
+        <v>334.4931229022353</v>
       </c>
       <c r="C187" t="n">
-        <v>341.909724468194</v>
+        <v>334.8913229247855</v>
       </c>
       <c r="D187" t="n">
-        <v>333.2586945227413</v>
+        <v>326.0312433050061</v>
       </c>
       <c r="E187" t="n">
-        <v>333.6170654296875</v>
+        <v>327.5742797851562</v>
       </c>
       <c r="F187" t="n">
-        <v>10043100</v>
+        <v>17640900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B188" t="n">
-        <v>334.4931229022353</v>
+        <v>326.8077430430495</v>
       </c>
       <c r="C188" t="n">
-        <v>334.8913229247855</v>
+        <v>330.8993264933345</v>
       </c>
       <c r="D188" t="n">
-        <v>326.0312433050061</v>
+        <v>325.7325999471821</v>
       </c>
       <c r="E188" t="n">
-        <v>327.5742797851562</v>
+        <v>327.9127807617188</v>
       </c>
       <c r="F188" t="n">
-        <v>17640900</v>
+        <v>7981800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B189" t="n">
-        <v>326.8077430430495</v>
+        <v>327.4150312810326</v>
       </c>
       <c r="C189" t="n">
-        <v>330.8993264933345</v>
+        <v>328.9580677951163</v>
       </c>
       <c r="D189" t="n">
-        <v>325.7325999471821</v>
+        <v>325.2149206632551</v>
       </c>
       <c r="E189" t="n">
-        <v>327.9127807617188</v>
+        <v>325.8619995117188</v>
       </c>
       <c r="F189" t="n">
-        <v>7981800</v>
+        <v>8080100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B190" t="n">
-        <v>327.4150312810326</v>
+        <v>326.8973584256916</v>
       </c>
       <c r="C190" t="n">
-        <v>328.9580677951163</v>
+        <v>334.1347741939035</v>
       </c>
       <c r="D190" t="n">
-        <v>325.2149206632551</v>
+        <v>323.5524415571975</v>
       </c>
       <c r="E190" t="n">
-        <v>325.8619995117188</v>
+        <v>332.5718078613281</v>
       </c>
       <c r="F190" t="n">
-        <v>8080100</v>
+        <v>15210200</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B191" t="n">
-        <v>326.8973584256916</v>
+        <v>336.5040683580973</v>
       </c>
       <c r="C191" t="n">
-        <v>334.1347741939035</v>
+        <v>338.4751995750331</v>
       </c>
       <c r="D191" t="n">
-        <v>323.5524415571975</v>
+        <v>330.2820977776739</v>
       </c>
       <c r="E191" t="n">
-        <v>332.5718078613281</v>
+        <v>332.9700012207031</v>
       </c>
       <c r="F191" t="n">
-        <v>15210200</v>
+        <v>8413900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,25 +5409,25 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B192" t="n">
-        <v>336.5040683580973</v>
+        <v>335</v>
       </c>
       <c r="C192" t="n">
-        <v>338.4751995750331</v>
+        <v>339.7200012207031</v>
       </c>
       <c r="D192" t="n">
-        <v>330.2820977776739</v>
+        <v>334.1099853515625</v>
       </c>
       <c r="E192" t="n">
-        <v>332.9700012207031</v>
+        <v>337.7200012207031</v>
       </c>
       <c r="F192" t="n">
-        <v>8413900</v>
+        <v>8673500</v>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5435,25 +5435,25 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B193" t="n">
-        <v>335</v>
+        <v>340.9800109863281</v>
       </c>
       <c r="C193" t="n">
-        <v>339.7200012207031</v>
+        <v>341.3999938964844</v>
       </c>
       <c r="D193" t="n">
-        <v>334.1099853515625</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E193" t="n">
-        <v>337.7200012207031</v>
+        <v>339.2200012207031</v>
       </c>
       <c r="F193" t="n">
-        <v>8673500</v>
+        <v>7115800</v>
       </c>
       <c r="G193" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B194" t="n">
-        <v>340.9800109863281</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="C194" t="n">
-        <v>341.3999938964844</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="D194" t="n">
-        <v>337.0899963378906</v>
+        <v>330.1300048828125</v>
       </c>
       <c r="E194" t="n">
-        <v>339.2200012207031</v>
+        <v>330.6199951171875</v>
       </c>
       <c r="F194" t="n">
-        <v>7115800</v>
+        <v>18505200</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B195" t="n">
-        <v>336.5299987792969</v>
+        <v>331.4599914550781</v>
       </c>
       <c r="C195" t="n">
-        <v>336.5299987792969</v>
+        <v>337</v>
       </c>
       <c r="D195" t="n">
-        <v>330.1300048828125</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="E195" t="n">
-        <v>330.6199951171875</v>
+        <v>335.4700012207031</v>
       </c>
       <c r="F195" t="n">
-        <v>18505200</v>
+        <v>15570600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B196" t="n">
-        <v>331.4599914550781</v>
+        <v>337.4700012207031</v>
       </c>
       <c r="C196" t="n">
-        <v>337</v>
+        <v>338.5899963378906</v>
       </c>
       <c r="D196" t="n">
-        <v>330.8099975585938</v>
+        <v>335.7699890136719</v>
       </c>
       <c r="E196" t="n">
-        <v>335.4700012207031</v>
+        <v>336.4700012207031</v>
       </c>
       <c r="F196" t="n">
-        <v>15570600</v>
+        <v>6299000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B197" t="n">
-        <v>337.4700012207031</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="C197" t="n">
-        <v>338.5899963378906</v>
+        <v>338.3500061035156</v>
       </c>
       <c r="D197" t="n">
-        <v>335.7699890136719</v>
+        <v>332.5</v>
       </c>
       <c r="E197" t="n">
-        <v>336.4700012207031</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="F197" t="n">
-        <v>6299000</v>
+        <v>7120300</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B198" t="n">
-        <v>338.3399963378906</v>
+        <v>327</v>
       </c>
       <c r="C198" t="n">
-        <v>338.3500061035156</v>
+        <v>344.7300109863281</v>
       </c>
       <c r="D198" t="n">
-        <v>332.5</v>
+        <v>325.75</v>
       </c>
       <c r="E198" t="n">
-        <v>334.5299987792969</v>
+        <v>342.8900146484375</v>
       </c>
       <c r="F198" t="n">
-        <v>7120300</v>
+        <v>14537900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>327</v>
+        <v>345.8500061035156</v>
       </c>
       <c r="C199" t="n">
-        <v>344.7300109863281</v>
+        <v>351.239990234375</v>
       </c>
       <c r="D199" t="n">
-        <v>325.75</v>
+        <v>344.0499877929688</v>
       </c>
       <c r="E199" t="n">
-        <v>342.8900146484375</v>
+        <v>346.9100036621094</v>
       </c>
       <c r="F199" t="n">
-        <v>14537900</v>
+        <v>10750000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B200" t="n">
-        <v>345.8500061035156</v>
+        <v>349.2799987792969</v>
       </c>
       <c r="C200" t="n">
-        <v>351.239990234375</v>
+        <v>349.3399963378906</v>
       </c>
       <c r="D200" t="n">
-        <v>344.0499877929688</v>
+        <v>341.1099853515625</v>
       </c>
       <c r="E200" t="n">
-        <v>346.9100036621094</v>
+        <v>343.1499938964844</v>
       </c>
       <c r="F200" t="n">
-        <v>10750000</v>
+        <v>12432400</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B201" t="n">
-        <v>349.2799987792969</v>
+        <v>339.0299987792969</v>
       </c>
       <c r="C201" t="n">
-        <v>349.3399963378906</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="D201" t="n">
-        <v>341.1099853515625</v>
+        <v>335.0499877929688</v>
       </c>
       <c r="E201" t="n">
-        <v>343.1499938964844</v>
+        <v>341.1000061035156</v>
       </c>
       <c r="F201" t="n">
-        <v>12432400</v>
+        <v>9250900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B202" t="n">
-        <v>339.0299987792969</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="C202" t="n">
-        <v>346.1300048828125</v>
+        <v>344.260009765625</v>
       </c>
       <c r="D202" t="n">
-        <v>335.0499877929688</v>
+        <v>337.3699951171875</v>
       </c>
       <c r="E202" t="n">
-        <v>341.1000061035156</v>
+        <v>338.8699951171875</v>
       </c>
       <c r="F202" t="n">
-        <v>9250900</v>
+        <v>7723300</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B203" t="n">
-        <v>341.7999877929688</v>
+        <v>340.1199951171875</v>
       </c>
       <c r="C203" t="n">
-        <v>344.260009765625</v>
+        <v>345.739990234375</v>
       </c>
       <c r="D203" t="n">
-        <v>337.3699951171875</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E203" t="n">
-        <v>338.8699951171875</v>
+        <v>345.2300109863281</v>
       </c>
       <c r="F203" t="n">
-        <v>7723300</v>
+        <v>6015300</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B204" t="n">
-        <v>340.1199951171875</v>
+        <v>345.0700073242188</v>
       </c>
       <c r="C204" t="n">
-        <v>345.739990234375</v>
+        <v>349.0700073242188</v>
       </c>
       <c r="D204" t="n">
-        <v>337.2999877929688</v>
+        <v>344.25</v>
       </c>
       <c r="E204" t="n">
-        <v>345.2300109863281</v>
+        <v>348.2099914550781</v>
       </c>
       <c r="F204" t="n">
-        <v>6015300</v>
+        <v>8040200</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B205" t="n">
-        <v>345.0700073242188</v>
+        <v>346.5799865722656</v>
       </c>
       <c r="C205" t="n">
-        <v>349.0700073242188</v>
+        <v>349.9200134277344</v>
       </c>
       <c r="D205" t="n">
-        <v>344.25</v>
+        <v>345.4200134277344</v>
       </c>
       <c r="E205" t="n">
-        <v>348.2099914550781</v>
+        <v>349.8999938964844</v>
       </c>
       <c r="F205" t="n">
-        <v>8040200</v>
+        <v>10913000</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B206" t="n">
-        <v>346.5799865722656</v>
+        <v>350.6400146484375</v>
       </c>
       <c r="C206" t="n">
-        <v>349.9200134277344</v>
+        <v>353.3699951171875</v>
       </c>
       <c r="D206" t="n">
-        <v>345.4200134277344</v>
+        <v>347.5</v>
       </c>
       <c r="E206" t="n">
-        <v>349.8999938964844</v>
+        <v>353.2099914550781</v>
       </c>
       <c r="F206" t="n">
-        <v>10913000</v>
+        <v>7520800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B207" t="n">
-        <v>350.6400146484375</v>
+        <v>357.8900146484375</v>
       </c>
       <c r="C207" t="n">
-        <v>353.3699951171875</v>
+        <v>359.0499877929688</v>
       </c>
       <c r="D207" t="n">
-        <v>347.5</v>
+        <v>352.5799865722656</v>
       </c>
       <c r="E207" t="n">
-        <v>353.2099914550781</v>
+        <v>356.2000122070312</v>
       </c>
       <c r="F207" t="n">
-        <v>7520800</v>
+        <v>7884900</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B208" t="n">
-        <v>357.8900146484375</v>
+        <v>357.2999877929688</v>
       </c>
       <c r="C208" t="n">
-        <v>359.0499877929688</v>
+        <v>359.2999877929688</v>
       </c>
       <c r="D208" t="n">
-        <v>352.5799865722656</v>
+        <v>354.1499938964844</v>
       </c>
       <c r="E208" t="n">
-        <v>356.2000122070312</v>
+        <v>357.3099975585938</v>
       </c>
       <c r="F208" t="n">
-        <v>7884900</v>
+        <v>6533800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B209" t="n">
-        <v>357.2999877929688</v>
+        <v>356.5</v>
       </c>
       <c r="C209" t="n">
-        <v>359.2999877929688</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D209" t="n">
-        <v>354.1499938964844</v>
+        <v>343.7799987792969</v>
       </c>
       <c r="E209" t="n">
-        <v>357.3099975585938</v>
+        <v>344.7099914550781</v>
       </c>
       <c r="F209" t="n">
-        <v>6533800</v>
+        <v>8265300</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B210" t="n">
-        <v>356.5</v>
+        <v>347.5400085449219</v>
       </c>
       <c r="C210" t="n">
-        <v>357.3699951171875</v>
+        <v>352.2799987792969</v>
       </c>
       <c r="D210" t="n">
-        <v>343.7799987792969</v>
+        <v>345.3699951171875</v>
       </c>
       <c r="E210" t="n">
-        <v>344.7099914550781</v>
+        <v>350.8500061035156</v>
       </c>
       <c r="F210" t="n">
-        <v>8265300</v>
+        <v>7606500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B211" t="n">
-        <v>347.5400085449219</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C211" t="n">
-        <v>352.2799987792969</v>
+        <v>354.4700012207031</v>
       </c>
       <c r="D211" t="n">
-        <v>345.3699951171875</v>
+        <v>349.7000122070312</v>
       </c>
       <c r="E211" t="n">
-        <v>350.8500061035156</v>
+        <v>351.7900085449219</v>
       </c>
       <c r="F211" t="n">
-        <v>7606500</v>
+        <v>6603400</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B212" t="n">
-        <v>353.2999877929688</v>
+        <v>353.75</v>
       </c>
       <c r="C212" t="n">
-        <v>354.4700012207031</v>
+        <v>355.6199951171875</v>
       </c>
       <c r="D212" t="n">
-        <v>349.7000122070312</v>
+        <v>350.8399963378906</v>
       </c>
       <c r="E212" t="n">
-        <v>351.7900085449219</v>
+        <v>352.6400146484375</v>
       </c>
       <c r="F212" t="n">
-        <v>6603400</v>
+        <v>6436600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B213" t="n">
-        <v>353.75</v>
+        <v>355</v>
       </c>
       <c r="C213" t="n">
-        <v>355.6199951171875</v>
+        <v>363</v>
       </c>
       <c r="D213" t="n">
-        <v>350.8399963378906</v>
+        <v>353.8699951171875</v>
       </c>
       <c r="E213" t="n">
-        <v>352.6400146484375</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F213" t="n">
-        <v>6436600</v>
+        <v>8477200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B214" t="n">
-        <v>355</v>
+        <v>358.9700012207031</v>
       </c>
       <c r="C214" t="n">
-        <v>363</v>
+        <v>362.1700134277344</v>
       </c>
       <c r="D214" t="n">
-        <v>353.8699951171875</v>
+        <v>358.2000122070312</v>
       </c>
       <c r="E214" t="n">
-        <v>357.5199890136719</v>
+        <v>359.239990234375</v>
       </c>
       <c r="F214" t="n">
-        <v>8477200</v>
+        <v>5269500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B215" t="n">
-        <v>358.9700012207031</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="C215" t="n">
-        <v>362.1700134277344</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="D215" t="n">
-        <v>358.2000122070312</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="E215" t="n">
-        <v>359.239990234375</v>
+        <v>356.2999877929688</v>
       </c>
       <c r="F215" t="n">
-        <v>5269500</v>
+        <v>5820100</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B216" t="n">
-        <v>362.8099975585938</v>
+        <v>355.760009765625</v>
       </c>
       <c r="C216" t="n">
-        <v>362.8099975585938</v>
+        <v>358.8500061035156</v>
       </c>
       <c r="D216" t="n">
-        <v>354.9500122070312</v>
+        <v>353.3299865722656</v>
       </c>
       <c r="E216" t="n">
-        <v>356.2999877929688</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F216" t="n">
-        <v>5820100</v>
+        <v>4566200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B217" t="n">
-        <v>355.760009765625</v>
+        <v>357.9599914550781</v>
       </c>
       <c r="C217" t="n">
-        <v>358.8500061035156</v>
+        <v>359.989990234375</v>
       </c>
       <c r="D217" t="n">
-        <v>353.3299865722656</v>
+        <v>356.5</v>
       </c>
       <c r="E217" t="n">
-        <v>357.5199890136719</v>
+        <v>359.7900085449219</v>
       </c>
       <c r="F217" t="n">
-        <v>4566200</v>
+        <v>5327500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B218" t="n">
-        <v>357.9599914550781</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="C218" t="n">
-        <v>359.989990234375</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="D218" t="n">
-        <v>356.5</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="E218" t="n">
-        <v>359.7900085449219</v>
+        <v>362.0400085449219</v>
       </c>
       <c r="F218" t="n">
-        <v>5327500</v>
+        <v>4576500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B219" t="n">
-        <v>360.0499877929688</v>
+        <v>362.9700012207031</v>
       </c>
       <c r="C219" t="n">
-        <v>363.1199951171875</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="D219" t="n">
-        <v>358.6000061035156</v>
+        <v>361.2999877929688</v>
       </c>
       <c r="E219" t="n">
-        <v>362.0400085449219</v>
+        <v>365.1799926757812</v>
       </c>
       <c r="F219" t="n">
-        <v>4576500</v>
+        <v>4366800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B220" t="n">
-        <v>362.9700012207031</v>
+        <v>366.5</v>
       </c>
       <c r="C220" t="n">
-        <v>366.0899963378906</v>
+        <v>366.5</v>
       </c>
       <c r="D220" t="n">
-        <v>361.2999877929688</v>
+        <v>361.5199890136719</v>
       </c>
       <c r="E220" t="n">
-        <v>365.1799926757812</v>
+        <v>363.1099853515625</v>
       </c>
       <c r="F220" t="n">
-        <v>4366800</v>
+        <v>5102700</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B221" t="n">
-        <v>366.5</v>
+        <v>363</v>
       </c>
       <c r="C221" t="n">
-        <v>366.5</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="D221" t="n">
-        <v>361.5199890136719</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="E221" t="n">
-        <v>363.1099853515625</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="F221" t="n">
-        <v>5102700</v>
+        <v>5058600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B222" t="n">
-        <v>363</v>
+        <v>361.9400024414062</v>
       </c>
       <c r="C222" t="n">
-        <v>365.8999938964844</v>
+        <v>365.75</v>
       </c>
       <c r="D222" t="n">
-        <v>361.4500122070312</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="E222" t="n">
-        <v>362.8399963378906</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="F222" t="n">
-        <v>5058600</v>
+        <v>5282600</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B223" t="n">
-        <v>361.9400024414062</v>
+        <v>362.3399963378906</v>
       </c>
       <c r="C223" t="n">
-        <v>365.75</v>
+        <v>363.5700073242188</v>
       </c>
       <c r="D223" t="n">
-        <v>360.9599914550781</v>
+        <v>359.2699890136719</v>
       </c>
       <c r="E223" t="n">
-        <v>360.9599914550781</v>
+        <v>363.25</v>
       </c>
       <c r="F223" t="n">
-        <v>5282600</v>
+        <v>5525100</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B224" t="n">
-        <v>362.3399963378906</v>
+        <v>363.010009765625</v>
       </c>
       <c r="C224" t="n">
-        <v>363.5700073242188</v>
+        <v>363.0499877929688</v>
       </c>
       <c r="D224" t="n">
-        <v>359.2699890136719</v>
+        <v>355.6499938964844</v>
       </c>
       <c r="E224" t="n">
-        <v>363.25</v>
+        <v>357.260009765625</v>
       </c>
       <c r="F224" t="n">
-        <v>5525100</v>
+        <v>6696200</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B225" t="n">
-        <v>363.010009765625</v>
+        <v>357.6000061035156</v>
       </c>
       <c r="C225" t="n">
-        <v>363.0499877929688</v>
+        <v>357.9500122070312</v>
       </c>
       <c r="D225" t="n">
-        <v>355.6499938964844</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E225" t="n">
-        <v>357.260009765625</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="F225" t="n">
-        <v>6696200</v>
+        <v>6799700</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B226" t="n">
-        <v>357.6000061035156</v>
+        <v>354.0700073242188</v>
       </c>
       <c r="C226" t="n">
-        <v>357.9500122070312</v>
+        <v>356.8599853515625</v>
       </c>
       <c r="D226" t="n">
-        <v>351.5499877929688</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="E226" t="n">
-        <v>351.5499877929688</v>
+        <v>351.5799865722656</v>
       </c>
       <c r="F226" t="n">
-        <v>6799700</v>
+        <v>8112100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B227" t="n">
-        <v>354.0700073242188</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C227" t="n">
-        <v>356.8599853515625</v>
+        <v>358.2799987792969</v>
       </c>
       <c r="D227" t="n">
-        <v>350.3699951171875</v>
+        <v>352.8200073242188</v>
       </c>
       <c r="E227" t="n">
-        <v>351.5799865722656</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="F227" t="n">
-        <v>8112100</v>
+        <v>4394400</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B228" t="n">
-        <v>353.2999877929688</v>
+        <v>357</v>
       </c>
       <c r="C228" t="n">
-        <v>358.2799987792969</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D228" t="n">
-        <v>352.8200073242188</v>
+        <v>353.0700073242188</v>
       </c>
       <c r="E228" t="n">
-        <v>356.3900146484375</v>
+        <v>356.6900024414062</v>
       </c>
       <c r="F228" t="n">
-        <v>4394400</v>
+        <v>4298000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B229" t="n">
-        <v>357</v>
+        <v>356.5</v>
       </c>
       <c r="C229" t="n">
-        <v>357.3699951171875</v>
+        <v>358.3500061035156</v>
       </c>
       <c r="D229" t="n">
-        <v>353.0700073242188</v>
+        <v>354.6000061035156</v>
       </c>
       <c r="E229" t="n">
-        <v>356.6900024414062</v>
+        <v>356.5</v>
       </c>
       <c r="F229" t="n">
-        <v>4298000</v>
+        <v>5796500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B230" t="n">
-        <v>356.5</v>
+        <v>354.6799926757812</v>
       </c>
       <c r="C230" t="n">
-        <v>358.3500061035156</v>
+        <v>357.5700073242188</v>
       </c>
       <c r="D230" t="n">
-        <v>354.6000061035156</v>
+        <v>352.2300109863281</v>
       </c>
       <c r="E230" t="n">
-        <v>356.5</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="F230" t="n">
-        <v>5796500</v>
+        <v>5209900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B231" t="n">
-        <v>354.6799926757812</v>
+        <v>355.6700134277344</v>
       </c>
       <c r="C231" t="n">
-        <v>357.5700073242188</v>
+        <v>358.7300109863281</v>
       </c>
       <c r="D231" t="n">
-        <v>352.2300109863281</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="E231" t="n">
-        <v>354.2200012207031</v>
+        <v>357.6199951171875</v>
       </c>
       <c r="F231" t="n">
-        <v>5209900</v>
+        <v>3914500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B232" t="n">
-        <v>355.6700134277344</v>
+        <v>355.8999938964844</v>
       </c>
       <c r="C232" t="n">
-        <v>358.7300109863281</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="D232" t="n">
-        <v>354.2200012207031</v>
+        <v>354.7699890136719</v>
       </c>
       <c r="E232" t="n">
-        <v>357.6199951171875</v>
+        <v>356.0199890136719</v>
       </c>
       <c r="F232" t="n">
-        <v>3914500</v>
+        <v>7962900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B233" t="n">
-        <v>355.8999938964844</v>
+        <v>355.7300109863281</v>
       </c>
       <c r="C233" t="n">
-        <v>357.7699890136719</v>
+        <v>359.9299926757812</v>
       </c>
       <c r="D233" t="n">
-        <v>354.7699890136719</v>
+        <v>354.1199951171875</v>
       </c>
       <c r="E233" t="n">
-        <v>356.0199890136719</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="F233" t="n">
-        <v>7962900</v>
+        <v>5079000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B234" t="n">
-        <v>355.7300109863281</v>
+        <v>357.5499877929688</v>
       </c>
       <c r="C234" t="n">
-        <v>359.9299926757812</v>
+        <v>361.4700012207031</v>
       </c>
       <c r="D234" t="n">
-        <v>354.1199951171875</v>
+        <v>353.7900085449219</v>
       </c>
       <c r="E234" t="n">
-        <v>354.9500122070312</v>
+        <v>356.2200012207031</v>
       </c>
       <c r="F234" t="n">
-        <v>5079000</v>
+        <v>5341400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B235" t="n">
-        <v>357.5499877929688</v>
+        <v>358.6799926757812</v>
       </c>
       <c r="C235" t="n">
-        <v>361.4700012207031</v>
+        <v>362.8500061035156</v>
       </c>
       <c r="D235" t="n">
-        <v>353.7900085449219</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="E235" t="n">
-        <v>356.2200012207031</v>
+        <v>362.0599975585938</v>
       </c>
       <c r="F235" t="n">
-        <v>5341400</v>
+        <v>5414200</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B236" t="n">
-        <v>358.6799926757812</v>
+        <v>361</v>
       </c>
       <c r="C236" t="n">
-        <v>362.8500061035156</v>
+        <v>362.8599853515625</v>
       </c>
       <c r="D236" t="n">
-        <v>356.3900146484375</v>
+        <v>355.2000122070312</v>
       </c>
       <c r="E236" t="n">
-        <v>362.0599975585938</v>
+        <v>358.6400146484375</v>
       </c>
       <c r="F236" t="n">
-        <v>5414200</v>
+        <v>4873500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B237" t="n">
-        <v>361</v>
+        <v>357.1000061035156</v>
       </c>
       <c r="C237" t="n">
-        <v>362.8599853515625</v>
+        <v>358.5499877929688</v>
       </c>
       <c r="D237" t="n">
-        <v>355.2000122070312</v>
+        <v>353.2300109863281</v>
       </c>
       <c r="E237" t="n">
-        <v>358.6400146484375</v>
+        <v>353.510009765625</v>
       </c>
       <c r="F237" t="n">
-        <v>4873500</v>
+        <v>5631400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B238" t="n">
-        <v>357.1000061035156</v>
+        <v>352</v>
       </c>
       <c r="C238" t="n">
-        <v>358.5499877929688</v>
+        <v>356.3299865722656</v>
       </c>
       <c r="D238" t="n">
-        <v>353.2300109863281</v>
+        <v>348.6900024414062</v>
       </c>
       <c r="E238" t="n">
-        <v>353.510009765625</v>
+        <v>354.7099914550781</v>
       </c>
       <c r="F238" t="n">
-        <v>5631400</v>
+        <v>6318200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B239" t="n">
-        <v>352</v>
+        <v>353.510009765625</v>
       </c>
       <c r="C239" t="n">
-        <v>356.3299865722656</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="D239" t="n">
-        <v>348.6900024414062</v>
+        <v>351.1199951171875</v>
       </c>
       <c r="E239" t="n">
-        <v>354.7099914550781</v>
+        <v>353.5599975585938</v>
       </c>
       <c r="F239" t="n">
-        <v>6318200</v>
+        <v>4184200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B240" t="n">
-        <v>353.510009765625</v>
+        <v>358.3200073242188</v>
       </c>
       <c r="C240" t="n">
-        <v>354.2200012207031</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="D240" t="n">
-        <v>351.1199951171875</v>
+        <v>354.7900085449219</v>
       </c>
       <c r="E240" t="n">
-        <v>353.5599975585938</v>
+        <v>356.2300109863281</v>
       </c>
       <c r="F240" t="n">
-        <v>4184200</v>
+        <v>5354600</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B241" t="n">
-        <v>358.3200073242188</v>
+        <v>354.2300109863281</v>
       </c>
       <c r="C241" t="n">
-        <v>360.0499877929688</v>
+        <v>355.2799987792969</v>
       </c>
       <c r="D241" t="n">
-        <v>354.7900085449219</v>
+        <v>347.5499877929688</v>
       </c>
       <c r="E241" t="n">
-        <v>356.2300109863281</v>
+        <v>350.1300048828125</v>
       </c>
       <c r="F241" t="n">
-        <v>5354600</v>
+        <v>9609900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B242" t="n">
-        <v>354.2300109863281</v>
+        <v>351</v>
       </c>
       <c r="C242" t="n">
-        <v>355.2799987792969</v>
+        <v>354.7000122070312</v>
       </c>
       <c r="D242" t="n">
-        <v>347.5499877929688</v>
+        <v>343.0700073242188</v>
       </c>
       <c r="E242" t="n">
-        <v>350.1300048828125</v>
+        <v>352.489990234375</v>
       </c>
       <c r="F242" t="n">
-        <v>9609900</v>
+        <v>14026500</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B243" t="n">
-        <v>351</v>
+        <v>353.3800048828125</v>
       </c>
       <c r="C243" t="n">
-        <v>354.7000122070312</v>
+        <v>355.6000061035156</v>
       </c>
       <c r="D243" t="n">
-        <v>343.0700073242188</v>
+        <v>344.6900024414062</v>
       </c>
       <c r="E243" t="n">
-        <v>352.489990234375</v>
+        <v>348.9200134277344</v>
       </c>
       <c r="F243" t="n">
-        <v>14026500</v>
+        <v>8303400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B244" t="n">
-        <v>353.3800048828125</v>
+        <v>352.25</v>
       </c>
       <c r="C244" t="n">
-        <v>355.6000061035156</v>
+        <v>353.489990234375</v>
       </c>
       <c r="D244" t="n">
-        <v>344.6900024414062</v>
+        <v>345.2699890136719</v>
       </c>
       <c r="E244" t="n">
-        <v>348.9200134277344</v>
+        <v>349.3099975585938</v>
       </c>
       <c r="F244" t="n">
-        <v>8303400</v>
+        <v>6480100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B245" t="n">
-        <v>352.25</v>
+        <v>347.8900146484375</v>
       </c>
       <c r="C245" t="n">
-        <v>353.489990234375</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="D245" t="n">
-        <v>345.2699890136719</v>
+        <v>345.010009765625</v>
       </c>
       <c r="E245" t="n">
-        <v>349.3099975585938</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="F245" t="n">
-        <v>6480100</v>
+        <v>18312400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B246" t="n">
-        <v>347.8900146484375</v>
+        <v>353.6700134277344</v>
       </c>
       <c r="C246" t="n">
-        <v>349.6700134277344</v>
+        <v>354.5</v>
       </c>
       <c r="D246" t="n">
-        <v>345.010009765625</v>
+        <v>350.0799865722656</v>
       </c>
       <c r="E246" t="n">
-        <v>349.6700134277344</v>
+        <v>352.0400085449219</v>
       </c>
       <c r="F246" t="n">
-        <v>18312400</v>
+        <v>6414700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B247" t="n">
-        <v>353.6700134277344</v>
+        <v>352</v>
       </c>
       <c r="C247" t="n">
-        <v>354.5</v>
+        <v>352.1000061035156</v>
       </c>
       <c r="D247" t="n">
-        <v>350.0799865722656</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E247" t="n">
-        <v>352.0400085449219</v>
+        <v>340</v>
       </c>
       <c r="F247" t="n">
-        <v>6414700</v>
+        <v>11485600</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B248" t="n">
-        <v>352</v>
+        <v>337.6099853515625</v>
       </c>
       <c r="C248" t="n">
-        <v>352.1000061035156</v>
+        <v>341.4400024414062</v>
       </c>
       <c r="D248" t="n">
-        <v>337.2999877929688</v>
+        <v>336.9800109863281</v>
       </c>
       <c r="E248" t="n">
-        <v>340</v>
+        <v>337.5299987792969</v>
       </c>
       <c r="F248" t="n">
-        <v>11485600</v>
+        <v>7068500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B249" t="n">
-        <v>337.6099853515625</v>
+        <v>338.1199951171875</v>
       </c>
       <c r="C249" t="n">
-        <v>341.4400024414062</v>
+        <v>339.3699951171875</v>
       </c>
       <c r="D249" t="n">
-        <v>336.9800109863281</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="E249" t="n">
-        <v>337.5299987792969</v>
+        <v>338.5599975585938</v>
       </c>
       <c r="F249" t="n">
-        <v>7068500</v>
+        <v>6934300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B250" t="n">
-        <v>338.1199951171875</v>
+        <v>340.7699890136719</v>
       </c>
       <c r="C250" t="n">
-        <v>339.3699951171875</v>
+        <v>343.3099975585938</v>
       </c>
       <c r="D250" t="n">
-        <v>335.2799987792969</v>
+        <v>338.6400146484375</v>
       </c>
       <c r="E250" t="n">
-        <v>338.5599975585938</v>
+        <v>343.0599975585938</v>
       </c>
       <c r="F250" t="n">
-        <v>6934300</v>
+        <v>11460300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B251" t="n">
-        <v>340.7699890136719</v>
+        <v>341.8299865722656</v>
       </c>
       <c r="C251" t="n">
-        <v>343.3099975585938</v>
+        <v>342</v>
       </c>
       <c r="D251" t="n">
-        <v>338.6400146484375</v>
+        <v>336.2999877929688</v>
       </c>
       <c r="E251" t="n">
-        <v>343.0599975585938</v>
+        <v>336.5899963378906</v>
       </c>
       <c r="F251" t="n">
-        <v>11460300</v>
+        <v>10483700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B252" t="n">
-        <v>341.8299865722656</v>
+        <v>337</v>
       </c>
       <c r="C252" t="n">
-        <v>342</v>
+        <v>338.75</v>
       </c>
       <c r="D252" t="n">
-        <v>336.2999877929688</v>
+        <v>333.3299865722656</v>
       </c>
       <c r="E252" t="n">
-        <v>336.5899963378906</v>
+        <v>334.9800109863281</v>
       </c>
       <c r="F252" t="n">
-        <v>9790100</v>
+        <v>7254900</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10017,37 +10017,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>334.98</v>
+      </c>
+      <c r="D2" t="n">
         <v>336.59</v>
       </c>
-      <c r="D2" t="n">
-        <v>343.06</v>
-      </c>
       <c r="E2" t="n">
-        <v>341.83</v>
+        <v>337</v>
       </c>
       <c r="F2" t="n">
-        <v>342</v>
+        <v>338.75</v>
       </c>
       <c r="G2" t="n">
-        <v>336.3</v>
+        <v>333.33</v>
       </c>
       <c r="H2" t="n">
-        <v>9769705</v>
+        <v>6022965</v>
       </c>
       <c r="I2" t="n">
-        <v>7780034</v>
+        <v>7777946</v>
       </c>
       <c r="J2" t="n">
-        <v>894718902272</v>
+        <v>890439270400</v>
       </c>
       <c r="K2" t="n">
-        <v>14.704675</v>
+        <v>14.432573</v>
       </c>
       <c r="L2" t="n">
-        <v>13.436978</v>
+        <v>13.372706</v>
       </c>
       <c r="M2" t="n">
-        <v>22.89</v>
+        <v>23.21</v>
       </c>
       <c r="N2" t="n">
         <v>366.5</v>
@@ -10059,7 +10059,7 @@
         <v>0.975</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
         <v>0.34921002</v>
@@ -10087,7 +10087,7 @@
         <v>133.007</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.5306187</v>
+        <v>2.5185142</v>
       </c>
       <c r="Z2" t="n">
         <v>0.469</v>
@@ -10099,7 +10099,7 @@
         <v>186328006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>732646866944</v>
+        <v>728367235072</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24:38</t>
+          <t>2026-09-30 16:07:03</t>
         </is>
       </c>
     </row>

--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B2" t="n">
-        <v>310.3134645283819</v>
+        <v>308.0762861336198</v>
       </c>
       <c r="C2" t="n">
-        <v>311.4516930034957</v>
+        <v>308.6846429587351</v>
       </c>
       <c r="D2" t="n">
-        <v>304.288708108424</v>
+        <v>301.6394301376976</v>
       </c>
       <c r="E2" t="n">
-        <v>309.5088500976562</v>
+        <v>304.8774719238281</v>
       </c>
       <c r="F2" t="n">
-        <v>11823300</v>
+        <v>9235200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B3" t="n">
-        <v>308.0763169713923</v>
+        <v>304.1807853263183</v>
       </c>
       <c r="C3" t="n">
-        <v>308.6846738574029</v>
+        <v>304.7302708010082</v>
       </c>
       <c r="D3" t="n">
-        <v>301.6394603311547</v>
+        <v>300.3932583082978</v>
       </c>
       <c r="E3" t="n">
-        <v>304.8775024414062</v>
+        <v>301.7767639160156</v>
       </c>
       <c r="F3" t="n">
-        <v>9235200</v>
+        <v>7600000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B4" t="n">
-        <v>304.1808160870063</v>
+        <v>302.718779227698</v>
       </c>
       <c r="C4" t="n">
-        <v>304.7303016172636</v>
+        <v>305.8096426575195</v>
       </c>
       <c r="D4" t="n">
-        <v>300.393288685967</v>
+        <v>302.4243927447969</v>
       </c>
       <c r="E4" t="n">
-        <v>301.7767944335938</v>
+        <v>304.2102355957031</v>
       </c>
       <c r="F4" t="n">
-        <v>7600000</v>
+        <v>6029900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,25 +547,25 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B5" t="n">
-        <v>302.7188095956571</v>
+        <v>305.8371035459471</v>
       </c>
       <c r="C5" t="n">
-        <v>305.809673335546</v>
+        <v>307.3851288987199</v>
       </c>
       <c r="D5" t="n">
-        <v>302.4244230832239</v>
+        <v>300.8578215934895</v>
       </c>
       <c r="E5" t="n">
-        <v>304.2102661132812</v>
+        <v>304.8511047363281</v>
       </c>
       <c r="F5" t="n">
-        <v>6029900</v>
+        <v>7214500</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -573,25 +573,25 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B6" t="n">
-        <v>305.8371035459471</v>
+        <v>305.0187502270194</v>
       </c>
       <c r="C6" t="n">
-        <v>307.3851288987199</v>
+        <v>305.6695130787729</v>
       </c>
       <c r="D6" t="n">
-        <v>300.8578215934895</v>
+        <v>300.4338615931582</v>
       </c>
       <c r="E6" t="n">
-        <v>304.8511047363281</v>
+        <v>303.3819885253906</v>
       </c>
       <c r="F6" t="n">
-        <v>7214500</v>
+        <v>8454200</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B7" t="n">
-        <v>305.0187502270194</v>
+        <v>303.8946917756213</v>
       </c>
       <c r="C7" t="n">
-        <v>305.6695130787729</v>
+        <v>304.4567183318842</v>
       </c>
       <c r="D7" t="n">
-        <v>300.4338615931582</v>
+        <v>299.2999336047902</v>
       </c>
       <c r="E7" t="n">
-        <v>303.3819885253906</v>
+        <v>299.7732238769531</v>
       </c>
       <c r="F7" t="n">
-        <v>8454200</v>
+        <v>6489900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B8" t="n">
-        <v>303.894722712774</v>
+        <v>300.7789375021521</v>
       </c>
       <c r="C8" t="n">
-        <v>304.4567493262524</v>
+        <v>303.7270945284432</v>
       </c>
       <c r="D8" t="n">
-        <v>299.2999640741864</v>
+        <v>299.1422058887319</v>
       </c>
       <c r="E8" t="n">
-        <v>299.7732543945312</v>
+        <v>301.2522277832031</v>
       </c>
       <c r="F8" t="n">
-        <v>6489900</v>
+        <v>7060300</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B9" t="n">
-        <v>300.7789375021521</v>
+        <v>301.380450372985</v>
       </c>
       <c r="C9" t="n">
-        <v>303.7270945284432</v>
+        <v>306.1231030365125</v>
       </c>
       <c r="D9" t="n">
-        <v>299.1422058887319</v>
+        <v>296.5983493251649</v>
       </c>
       <c r="E9" t="n">
-        <v>301.2522277832031</v>
+        <v>296.67724609375</v>
       </c>
       <c r="F9" t="n">
-        <v>7060300</v>
+        <v>8597400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B10" t="n">
-        <v>301.3804193716138</v>
+        <v>301.3212684867699</v>
       </c>
       <c r="C10" t="n">
-        <v>306.1230715472904</v>
+        <v>305.1272097801061</v>
       </c>
       <c r="D10" t="n">
-        <v>296.5983188157025</v>
+        <v>301.1733746705027</v>
       </c>
       <c r="E10" t="n">
-        <v>296.6772155761719</v>
+        <v>303.6580810546875</v>
       </c>
       <c r="F10" t="n">
-        <v>8597400</v>
+        <v>10788700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B11" t="n">
-        <v>301.321238204041</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C11" t="n">
-        <v>305.1271791148808</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D11" t="n">
-        <v>301.173344402637</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E11" t="n">
-        <v>303.6580505371094</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F11" t="n">
-        <v>10788700</v>
+        <v>16178800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B12" t="n">
-        <v>301.5578902761218</v>
+        <v>302.1001843350741</v>
       </c>
       <c r="C12" t="n">
-        <v>302.7016525742085</v>
+        <v>307.7499381556482</v>
       </c>
       <c r="D12" t="n">
-        <v>290.0907186231138</v>
+        <v>301.1634734465224</v>
       </c>
       <c r="E12" t="n">
-        <v>297.8505249023438</v>
+        <v>301.4099731445312</v>
       </c>
       <c r="F12" t="n">
-        <v>16178800</v>
+        <v>11354800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B13" t="n">
-        <v>302.1001843350741</v>
+        <v>301.0747572360179</v>
       </c>
       <c r="C13" t="n">
-        <v>307.7499381556482</v>
+        <v>304.3581201926382</v>
       </c>
       <c r="D13" t="n">
-        <v>301.1634734465224</v>
+        <v>292.9106878973514</v>
       </c>
       <c r="E13" t="n">
-        <v>301.4099731445312</v>
+        <v>294.360107421875</v>
       </c>
       <c r="F13" t="n">
-        <v>11354800</v>
+        <v>10549400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B14" t="n">
-        <v>301.0747572360179</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C14" t="n">
-        <v>304.3581201926382</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D14" t="n">
-        <v>292.9106878973514</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E14" t="n">
-        <v>294.360107421875</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F14" t="n">
-        <v>10549400</v>
+        <v>10153500</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B15" t="n">
-        <v>294.9714335987563</v>
+        <v>294.3206459359216</v>
       </c>
       <c r="C15" t="n">
-        <v>295.3559575215809</v>
+        <v>299.4379821870563</v>
       </c>
       <c r="D15" t="n">
-        <v>290.0808874955599</v>
+        <v>293.9854099500461</v>
       </c>
       <c r="E15" t="n">
-        <v>293.3938293457031</v>
+        <v>298.1265869140625</v>
       </c>
       <c r="F15" t="n">
-        <v>10153500</v>
+        <v>6894900</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B16" t="n">
-        <v>294.3206459359216</v>
+        <v>297.436411288458</v>
       </c>
       <c r="C16" t="n">
-        <v>299.4379821870563</v>
+        <v>299.7929328501146</v>
       </c>
       <c r="D16" t="n">
-        <v>293.9854099500461</v>
+        <v>292.8416531202475</v>
       </c>
       <c r="E16" t="n">
-        <v>298.1265869140625</v>
+        <v>292.9303894042969</v>
       </c>
       <c r="F16" t="n">
-        <v>6894900</v>
+        <v>7372700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B17" t="n">
-        <v>297.436411288458</v>
+        <v>293.6008861047978</v>
       </c>
       <c r="C17" t="n">
-        <v>299.7929328501146</v>
+        <v>293.8868342154489</v>
       </c>
       <c r="D17" t="n">
-        <v>292.8416531202475</v>
+        <v>286.4721332067081</v>
       </c>
       <c r="E17" t="n">
-        <v>292.9303894042969</v>
+        <v>289.9921264648438</v>
       </c>
       <c r="F17" t="n">
-        <v>7372700</v>
+        <v>8054100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B18" t="n">
-        <v>293.6008552074487</v>
+        <v>290.2583437522712</v>
       </c>
       <c r="C18" t="n">
-        <v>293.8868032880077</v>
+        <v>292.2204718178062</v>
       </c>
       <c r="D18" t="n">
-        <v>286.4721030595595</v>
+        <v>288.4145307332595</v>
       </c>
       <c r="E18" t="n">
-        <v>289.9920959472656</v>
+        <v>290.4161071777344</v>
       </c>
       <c r="F18" t="n">
-        <v>8054100</v>
+        <v>5438800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B19" t="n">
-        <v>290.2583437522712</v>
+        <v>291.9345194575729</v>
       </c>
       <c r="C19" t="n">
-        <v>292.2204718178062</v>
+        <v>298.3632510673837</v>
       </c>
       <c r="D19" t="n">
-        <v>288.4145307332595</v>
+        <v>291.3133654724136</v>
       </c>
       <c r="E19" t="n">
-        <v>290.4161071777344</v>
+        <v>296.2334899902344</v>
       </c>
       <c r="F19" t="n">
-        <v>5438800</v>
+        <v>7228300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B20" t="n">
-        <v>291.9345194575729</v>
+        <v>297.9294427867379</v>
       </c>
       <c r="C20" t="n">
-        <v>298.3632510673837</v>
+        <v>300.2662554558976</v>
       </c>
       <c r="D20" t="n">
-        <v>291.3133654724136</v>
+        <v>296.7955500258321</v>
       </c>
       <c r="E20" t="n">
-        <v>296.2334899902344</v>
+        <v>299.8915710449219</v>
       </c>
       <c r="F20" t="n">
-        <v>7228300</v>
+        <v>5642200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B21" t="n">
-        <v>297.92941246883</v>
+        <v>300.5915953010157</v>
       </c>
       <c r="C21" t="n">
-        <v>300.2662249001909</v>
+        <v>303.6580673748709</v>
       </c>
       <c r="D21" t="n">
-        <v>296.7955198233114</v>
+        <v>298.915415308335</v>
       </c>
       <c r="E21" t="n">
-        <v>299.8915405273438</v>
+        <v>301.0845947265625</v>
       </c>
       <c r="F21" t="n">
-        <v>5642200</v>
+        <v>6336000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B22" t="n">
-        <v>300.5915953010157</v>
+        <v>299.2605157595805</v>
       </c>
       <c r="C22" t="n">
-        <v>303.6580673748709</v>
+        <v>303.9341406042103</v>
       </c>
       <c r="D22" t="n">
-        <v>298.915415308335</v>
+        <v>298.7675163425421</v>
       </c>
       <c r="E22" t="n">
-        <v>301.0845947265625</v>
+        <v>301.2325134277344</v>
       </c>
       <c r="F22" t="n">
-        <v>6336000</v>
+        <v>7520300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B23" t="n">
-        <v>299.2605157595805</v>
+        <v>301.5085931686638</v>
       </c>
       <c r="C23" t="n">
-        <v>303.9341406042103</v>
+        <v>308.2330823767899</v>
       </c>
       <c r="D23" t="n">
-        <v>298.7675163425421</v>
+        <v>300.828251563059</v>
       </c>
       <c r="E23" t="n">
-        <v>301.2325134277344</v>
+        <v>305.1074829101562</v>
       </c>
       <c r="F23" t="n">
-        <v>7520300</v>
+        <v>7514600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B24" t="n">
-        <v>301.5085931686638</v>
+        <v>304.2200828300273</v>
       </c>
       <c r="C24" t="n">
-        <v>308.2330823767899</v>
+        <v>308.4894444595929</v>
       </c>
       <c r="D24" t="n">
-        <v>300.828251563059</v>
+        <v>302.9481359332913</v>
       </c>
       <c r="E24" t="n">
-        <v>305.1074829101562</v>
+        <v>306.7639465332031</v>
       </c>
       <c r="F24" t="n">
-        <v>7514600</v>
+        <v>7721300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B25" t="n">
-        <v>304.2200828300273</v>
+        <v>306.6456298108837</v>
       </c>
       <c r="C25" t="n">
-        <v>308.4894444595929</v>
+        <v>307.947155461334</v>
       </c>
       <c r="D25" t="n">
-        <v>302.9481359332913</v>
+        <v>301.9226870872275</v>
       </c>
       <c r="E25" t="n">
-        <v>306.7639465332031</v>
+        <v>305.0187377929688</v>
       </c>
       <c r="F25" t="n">
-        <v>7721300</v>
+        <v>7770000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B26" t="n">
-        <v>306.6456604912348</v>
+        <v>302.4156900665715</v>
       </c>
       <c r="C26" t="n">
-        <v>307.9471862719047</v>
+        <v>307.8485532010255</v>
       </c>
       <c r="D26" t="n">
-        <v>301.9227172950412</v>
+        <v>300.8282464075632</v>
       </c>
       <c r="E26" t="n">
-        <v>305.0187683105469</v>
+        <v>304.9201354980469</v>
       </c>
       <c r="F26" t="n">
-        <v>7770000</v>
+        <v>7085200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B27" t="n">
-        <v>302.415720333495</v>
+        <v>305.2750763211935</v>
       </c>
       <c r="C27" t="n">
-        <v>307.8485840116909</v>
+        <v>308.7162326204817</v>
       </c>
       <c r="D27" t="n">
-        <v>300.8282765156093</v>
+        <v>301.350820325461</v>
       </c>
       <c r="E27" t="n">
-        <v>304.920166015625</v>
+        <v>307.3161010742188</v>
       </c>
       <c r="F27" t="n">
-        <v>7085200</v>
+        <v>6865200</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B28" t="n">
-        <v>305.2751066360906</v>
+        <v>306.6357687557767</v>
       </c>
       <c r="C28" t="n">
-        <v>308.7162632770978</v>
+        <v>310.4318702971036</v>
       </c>
       <c r="D28" t="n">
-        <v>301.3508502506656</v>
+        <v>305.9160088624015</v>
       </c>
       <c r="E28" t="n">
-        <v>307.3161315917969</v>
+        <v>309.0317687988281</v>
       </c>
       <c r="F28" t="n">
-        <v>6865200</v>
+        <v>7206100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B29" t="n">
-        <v>306.6357687557767</v>
+        <v>307.5231746391179</v>
       </c>
       <c r="C29" t="n">
-        <v>310.4318702971036</v>
+        <v>310.0275898810191</v>
       </c>
       <c r="D29" t="n">
-        <v>305.9160088624015</v>
+        <v>303.3326798145578</v>
       </c>
       <c r="E29" t="n">
-        <v>309.0317687988281</v>
+        <v>309.8106689453125</v>
       </c>
       <c r="F29" t="n">
-        <v>7206100</v>
+        <v>7302300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B30" t="n">
-        <v>307.5232049313688</v>
+        <v>310.5896337890794</v>
       </c>
       <c r="C30" t="n">
-        <v>310.0276204199649</v>
+        <v>315.0857860805166</v>
       </c>
       <c r="D30" t="n">
-        <v>303.3327096940284</v>
+        <v>309.8106862822301</v>
       </c>
       <c r="E30" t="n">
-        <v>309.8106994628906</v>
+        <v>312.4531860351562</v>
       </c>
       <c r="F30" t="n">
-        <v>7302300</v>
+        <v>5794100</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B31" t="n">
-        <v>310.5896337890794</v>
+        <v>313.054640940315</v>
       </c>
       <c r="C31" t="n">
-        <v>315.0857860805166</v>
+        <v>314.5829271513063</v>
       </c>
       <c r="D31" t="n">
-        <v>309.8106862822301</v>
+        <v>310.8657222472937</v>
       </c>
       <c r="E31" t="n">
-        <v>312.4531860351562</v>
+        <v>311.2009582519531</v>
       </c>
       <c r="F31" t="n">
-        <v>5794100</v>
+        <v>5030200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B32" t="n">
-        <v>313.0546102409576</v>
+        <v>311.8320000281587</v>
       </c>
       <c r="C32" t="n">
-        <v>314.5828963020791</v>
+        <v>317.7381233989844</v>
       </c>
       <c r="D32" t="n">
-        <v>310.8656917625901</v>
+        <v>311.782682032414</v>
       </c>
       <c r="E32" t="n">
-        <v>311.200927734375</v>
+        <v>315.9238891601562</v>
       </c>
       <c r="F32" t="n">
-        <v>5030200</v>
+        <v>10578300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B33" t="n">
-        <v>311.8320000281587</v>
+        <v>314.7604311532612</v>
       </c>
       <c r="C33" t="n">
-        <v>317.7381233989844</v>
+        <v>316.1408235578094</v>
       </c>
       <c r="D33" t="n">
-        <v>311.782682032414</v>
+        <v>304.7722577523736</v>
       </c>
       <c r="E33" t="n">
-        <v>315.9238891601562</v>
+        <v>305.1469421386719</v>
       </c>
       <c r="F33" t="n">
-        <v>10578300</v>
+        <v>8973300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B34" t="n">
-        <v>314.7604626322791</v>
+        <v>303.2045199796025</v>
       </c>
       <c r="C34" t="n">
-        <v>316.1408551748796</v>
+        <v>303.3327046462357</v>
       </c>
       <c r="D34" t="n">
-        <v>304.7722882324798</v>
+        <v>297.0124483237873</v>
       </c>
       <c r="E34" t="n">
-        <v>305.14697265625</v>
+        <v>299.3591003417969</v>
       </c>
       <c r="F34" t="n">
-        <v>8973300</v>
+        <v>10327000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B35" t="n">
-        <v>303.2044890700107</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C35" t="n">
-        <v>303.3326737235763</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D35" t="n">
-        <v>297.012418045434</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E35" t="n">
-        <v>299.3590698242188</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F35" t="n">
-        <v>10327000</v>
+        <v>8344000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B36" t="n">
-        <v>299.7436397411884</v>
+        <v>295.3066317863286</v>
       </c>
       <c r="C36" t="n">
-        <v>301.3113742461044</v>
+        <v>298.70833958092</v>
       </c>
       <c r="D36" t="n">
-        <v>293.5022804823602</v>
+        <v>292.8613440028039</v>
       </c>
       <c r="E36" t="n">
-        <v>296.1644592285156</v>
+        <v>295.2178955078125</v>
       </c>
       <c r="F36" t="n">
-        <v>8344000</v>
+        <v>8077300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B37" t="n">
-        <v>295.3066623130797</v>
+        <v>295.5432899586994</v>
       </c>
       <c r="C37" t="n">
-        <v>298.708370459316</v>
+        <v>300.1873662746028</v>
       </c>
       <c r="D37" t="n">
-        <v>292.8613742767781</v>
+        <v>295.0798692888629</v>
       </c>
       <c r="E37" t="n">
-        <v>295.2179260253906</v>
+        <v>299.0238647460938</v>
       </c>
       <c r="F37" t="n">
-        <v>8077300</v>
+        <v>5546600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B38" t="n">
-        <v>295.5432597963394</v>
+        <v>302.0508736933244</v>
       </c>
       <c r="C38" t="n">
-        <v>300.1873356382808</v>
+        <v>305.5807663052954</v>
       </c>
       <c r="D38" t="n">
-        <v>295.0798391737984</v>
+        <v>293.9854105998292</v>
       </c>
       <c r="E38" t="n">
-        <v>299.0238342285156</v>
+        <v>294.2023315429688</v>
       </c>
       <c r="F38" t="n">
-        <v>5546600</v>
+        <v>7501600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B39" t="n">
-        <v>302.0508736933244</v>
+        <v>297.0715864028587</v>
       </c>
       <c r="C39" t="n">
-        <v>305.5807663052954</v>
+        <v>297.456110287291</v>
       </c>
       <c r="D39" t="n">
-        <v>293.9854105998292</v>
+        <v>288.7103057597054</v>
       </c>
       <c r="E39" t="n">
-        <v>294.2023315429688</v>
+        <v>293.8473510742188</v>
       </c>
       <c r="F39" t="n">
-        <v>7501600</v>
+        <v>11766800</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B40" t="n">
-        <v>297.0715864028587</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C40" t="n">
-        <v>297.456110287291</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D40" t="n">
-        <v>288.7103057597054</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E40" t="n">
-        <v>293.8473510742188</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F40" t="n">
-        <v>11766800</v>
+        <v>10940200</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B41" t="n">
-        <v>294.0642973394352</v>
+        <v>295.848951187077</v>
       </c>
       <c r="C41" t="n">
-        <v>295.6221924256846</v>
+        <v>300.236658228506</v>
       </c>
       <c r="D41" t="n">
-        <v>290.386540762355</v>
+        <v>291.4218258555586</v>
       </c>
       <c r="E41" t="n">
-        <v>293.8276672363281</v>
+        <v>298.7576599121094</v>
       </c>
       <c r="F41" t="n">
-        <v>10940200</v>
+        <v>8877200</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B42" t="n">
-        <v>295.848951187077</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C42" t="n">
-        <v>300.236658228506</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D42" t="n">
-        <v>291.4218258555586</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E42" t="n">
-        <v>298.7576599121094</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F42" t="n">
-        <v>8877200</v>
+        <v>7910900</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B43" t="n">
-        <v>300.7296512123902</v>
+        <v>304.7722465716023</v>
       </c>
       <c r="C43" t="n">
-        <v>304.2102259719906</v>
+        <v>309.3275563846455</v>
       </c>
       <c r="D43" t="n">
-        <v>298.9548653069277</v>
+        <v>303.9242719247256</v>
       </c>
       <c r="E43" t="n">
-        <v>303.3327026367188</v>
+        <v>308.6965026855469</v>
       </c>
       <c r="F43" t="n">
-        <v>7910900</v>
+        <v>4322400</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B44" t="n">
-        <v>304.7722465716023</v>
+        <v>308.5683618849884</v>
       </c>
       <c r="C44" t="n">
-        <v>309.3275563846455</v>
+        <v>309.6430970545817</v>
       </c>
       <c r="D44" t="n">
-        <v>303.9242719247256</v>
+        <v>304.2201032083801</v>
       </c>
       <c r="E44" t="n">
-        <v>308.6965026855469</v>
+        <v>304.5947875976562</v>
       </c>
       <c r="F44" t="n">
-        <v>4322400</v>
+        <v>7727300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B45" t="n">
-        <v>308.5683309692949</v>
+        <v>304.4172805196406</v>
       </c>
       <c r="C45" t="n">
-        <v>309.6430660312097</v>
+        <v>306.1329390093465</v>
       </c>
       <c r="D45" t="n">
-        <v>304.2200727283419</v>
+        <v>302.7903884074122</v>
       </c>
       <c r="E45" t="n">
-        <v>304.5947570800781</v>
+        <v>303.5693359375</v>
       </c>
       <c r="F45" t="n">
-        <v>7727300</v>
+        <v>7249000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B46" t="n">
-        <v>304.4172805196406</v>
+        <v>302.8988895743303</v>
       </c>
       <c r="C46" t="n">
-        <v>306.1329390093465</v>
+        <v>307.9866176785159</v>
       </c>
       <c r="D46" t="n">
-        <v>302.7903884074122</v>
+        <v>302.5044659219624</v>
       </c>
       <c r="E46" t="n">
-        <v>303.5693359375</v>
+        <v>307.7598571777344</v>
       </c>
       <c r="F46" t="n">
-        <v>7249000</v>
+        <v>8535300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B47" t="n">
-        <v>302.8988595387675</v>
+        <v>308.8739918889233</v>
       </c>
       <c r="C47" t="n">
-        <v>307.9865871384521</v>
+        <v>314.0307463246157</v>
       </c>
       <c r="D47" t="n">
-        <v>302.5044359255107</v>
+        <v>308.6176225735461</v>
       </c>
       <c r="E47" t="n">
-        <v>307.7598266601562</v>
+        <v>311.6742248535156</v>
       </c>
       <c r="F47" t="n">
-        <v>8535300</v>
+        <v>9627800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B48" t="n">
-        <v>308.8740221323167</v>
+        <v>311.2206641139725</v>
       </c>
       <c r="C48" t="n">
-        <v>314.0307770729326</v>
+        <v>314.0208969911127</v>
       </c>
       <c r="D48" t="n">
-        <v>308.617652791837</v>
+        <v>310.2740836361238</v>
       </c>
       <c r="E48" t="n">
-        <v>311.6742553710938</v>
+        <v>310.6290588378906</v>
       </c>
       <c r="F48" t="n">
-        <v>9627800</v>
+        <v>6518900</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B49" t="n">
-        <v>311.2206946896725</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C49" t="n">
-        <v>314.0209278419201</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D49" t="n">
-        <v>310.2741141188276</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E49" t="n">
-        <v>310.6290893554688</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F49" t="n">
-        <v>6518900</v>
+        <v>7417200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B50" t="n">
-        <v>310.6487980837529</v>
+        <v>310.5403783790639</v>
       </c>
       <c r="C50" t="n">
-        <v>312.0390600856641</v>
+        <v>314.336450228146</v>
       </c>
       <c r="D50" t="n">
-        <v>308.9627484602848</v>
+        <v>295.8193913272319</v>
       </c>
       <c r="E50" t="n">
-        <v>310.7966918945312</v>
+        <v>296.3025512695312</v>
       </c>
       <c r="F50" t="n">
-        <v>7417200</v>
+        <v>18049200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B51" t="n">
-        <v>310.5403783790639</v>
+        <v>296.2926621709551</v>
       </c>
       <c r="C51" t="n">
-        <v>314.336450228146</v>
+        <v>306.8329925602339</v>
       </c>
       <c r="D51" t="n">
-        <v>295.8193913272319</v>
+        <v>294.2812160390869</v>
       </c>
       <c r="E51" t="n">
-        <v>296.3025512695312</v>
+        <v>305.7680969238281</v>
       </c>
       <c r="F51" t="n">
-        <v>18049200</v>
+        <v>18874100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B52" t="n">
-        <v>296.292632599085</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C52" t="n">
-        <v>306.8329619363725</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D52" t="n">
-        <v>294.2811866679717</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E52" t="n">
-        <v>305.76806640625</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F52" t="n">
-        <v>18874100</v>
+        <v>9721900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B53" t="n">
-        <v>304.9102649889192</v>
+        <v>315.2040954937631</v>
       </c>
       <c r="C53" t="n">
-        <v>313.5476242674454</v>
+        <v>315.7858311866128</v>
       </c>
       <c r="D53" t="n">
-        <v>304.9102649889192</v>
+        <v>312.1672323684923</v>
       </c>
       <c r="E53" t="n">
-        <v>312.9363098144531</v>
+        <v>314.0603332519531</v>
       </c>
       <c r="F53" t="n">
-        <v>9721900</v>
+        <v>8982900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B54" t="n">
-        <v>315.2041261224818</v>
+        <v>315.1153648797306</v>
       </c>
       <c r="C54" t="n">
-        <v>315.7858618718594</v>
+        <v>318.3593094805321</v>
       </c>
       <c r="D54" t="n">
-        <v>312.1672627021157</v>
+        <v>313.9321843288561</v>
       </c>
       <c r="E54" t="n">
-        <v>314.0603637695312</v>
+        <v>315.5393371582031</v>
       </c>
       <c r="F54" t="n">
-        <v>8982900</v>
+        <v>10864100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B55" t="n">
-        <v>315.115395356304</v>
+        <v>314.6223718715413</v>
       </c>
       <c r="C55" t="n">
-        <v>318.3593402708456</v>
+        <v>315.0463441586525</v>
       </c>
       <c r="D55" t="n">
-        <v>313.9322146909975</v>
+        <v>309.9980348220149</v>
       </c>
       <c r="E55" t="n">
-        <v>315.5393676757812</v>
+        <v>311.1319274902344</v>
       </c>
       <c r="F55" t="n">
-        <v>10864100</v>
+        <v>8331300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B56" t="n">
-        <v>314.6224027314819</v>
+        <v>313.971593609235</v>
       </c>
       <c r="C56" t="n">
-        <v>315.0463750601788</v>
+        <v>314.8984348971578</v>
       </c>
       <c r="D56" t="n">
-        <v>309.9980652283745</v>
+        <v>310.254388930852</v>
       </c>
       <c r="E56" t="n">
-        <v>311.1319580078125</v>
+        <v>310.5699157714844</v>
       </c>
       <c r="F56" t="n">
-        <v>8331300</v>
+        <v>8718700</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B57" t="n">
-        <v>313.971593609235</v>
+        <v>311.5756418636432</v>
       </c>
       <c r="C57" t="n">
-        <v>314.8984348971578</v>
+        <v>313.2518519730792</v>
       </c>
       <c r="D57" t="n">
-        <v>310.254388930852</v>
+        <v>307.8485673512913</v>
       </c>
       <c r="E57" t="n">
-        <v>310.5699157714844</v>
+        <v>308.6176452636719</v>
       </c>
       <c r="F57" t="n">
-        <v>8718700</v>
+        <v>11444900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B58" t="n">
-        <v>311.575672673722</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C58" t="n">
-        <v>313.2518829489097</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D58" t="n">
-        <v>307.8485977928193</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E58" t="n">
-        <v>308.61767578125</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F58" t="n">
-        <v>11444900</v>
+        <v>24494400</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B59" t="n">
-        <v>309.3965776494671</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="C59" t="n">
-        <v>314.099781180705</v>
+        <v>318.7043994886834</v>
       </c>
       <c r="D59" t="n">
-        <v>308.8049723403709</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="E59" t="n">
-        <v>312.7686767578125</v>
+        <v>318.5663452148438</v>
       </c>
       <c r="F59" t="n">
-        <v>24494400</v>
+        <v>8354600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B60" t="n">
-        <v>313.0644852104395</v>
+        <v>319.079052742897</v>
       </c>
       <c r="C60" t="n">
-        <v>318.7043994886834</v>
+        <v>323.1906809208754</v>
       </c>
       <c r="D60" t="n">
-        <v>313.0644852104395</v>
+        <v>318.5663442066048</v>
       </c>
       <c r="E60" t="n">
-        <v>318.5663452148438</v>
+        <v>321.3665771484375</v>
       </c>
       <c r="F60" t="n">
-        <v>8354600</v>
+        <v>6668300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B61" t="n">
-        <v>319.0790830432475</v>
+        <v>321.6722493328215</v>
       </c>
       <c r="C61" t="n">
-        <v>323.1907116116738</v>
+        <v>325.3697449529369</v>
       </c>
       <c r="D61" t="n">
-        <v>318.5663744582675</v>
+        <v>320.9426198260136</v>
       </c>
       <c r="E61" t="n">
-        <v>321.3666076660156</v>
+        <v>324.5612487792969</v>
       </c>
       <c r="F61" t="n">
-        <v>6668300</v>
+        <v>4289300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B62" t="n">
-        <v>321.6722493328215</v>
+        <v>324.5020893383847</v>
       </c>
       <c r="C62" t="n">
-        <v>325.3697449529369</v>
+        <v>326.22758744424</v>
       </c>
       <c r="D62" t="n">
-        <v>320.9426198260136</v>
+        <v>321.9680949886989</v>
       </c>
       <c r="E62" t="n">
-        <v>324.5612487792969</v>
+        <v>323.3189086914062</v>
       </c>
       <c r="F62" t="n">
-        <v>4289300</v>
+        <v>4158300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B63" t="n">
-        <v>324.502058709128</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C63" t="n">
-        <v>326.2275566521161</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D63" t="n">
-        <v>321.9680645986219</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E63" t="n">
-        <v>323.3188781738281</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F63" t="n">
-        <v>4158300</v>
+        <v>8635300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B64" t="n">
-        <v>322.4216288798564</v>
+        <v>320.2622768741799</v>
       </c>
       <c r="C64" t="n">
-        <v>323.1808371734579</v>
+        <v>320.3904615362508</v>
       </c>
       <c r="D64" t="n">
-        <v>319.0002116144308</v>
+        <v>317.9747523718436</v>
       </c>
       <c r="E64" t="n">
-        <v>319.2171325683594</v>
+        <v>318.8917541503906</v>
       </c>
       <c r="F64" t="n">
-        <v>8635300</v>
+        <v>7904300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B65" t="n">
-        <v>320.2623075229155</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C65" t="n">
-        <v>320.3904921972535</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D65" t="n">
-        <v>317.9747828016658</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E65" t="n">
-        <v>318.8917846679688</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F65" t="n">
-        <v>7904300</v>
+        <v>5048500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B66" t="n">
-        <v>319.7988699190817</v>
+        <v>317.9846252281575</v>
       </c>
       <c r="C66" t="n">
-        <v>320.3313177342217</v>
+        <v>321.1694123071354</v>
       </c>
       <c r="D66" t="n">
-        <v>317.5310845539587</v>
+        <v>316.2492576445291</v>
       </c>
       <c r="E66" t="n">
-        <v>317.7085571289062</v>
+        <v>320.9229125976562</v>
       </c>
       <c r="F66" t="n">
-        <v>5048500</v>
+        <v>8054000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B67" t="n">
-        <v>317.9846252281575</v>
+        <v>320.942599199713</v>
       </c>
       <c r="C67" t="n">
-        <v>321.1694123071354</v>
+        <v>332.5280847314999</v>
       </c>
       <c r="D67" t="n">
-        <v>316.2492576445291</v>
+        <v>320.6369419886511</v>
       </c>
       <c r="E67" t="n">
-        <v>320.9229125976562</v>
+        <v>329.363037109375</v>
       </c>
       <c r="F67" t="n">
-        <v>8054000</v>
+        <v>10752600</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,25 +2185,25 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B68" t="n">
-        <v>320.9426586744551</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C68" t="n">
-        <v>332.5281463531796</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D68" t="n">
-        <v>320.637001406751</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E68" t="n">
-        <v>329.3630981445312</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F68" t="n">
-        <v>10752600</v>
+        <v>7660800</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2211,25 +2211,25 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B69" t="n">
-        <v>329.4422902981328</v>
+        <v>327.9764350864437</v>
       </c>
       <c r="C69" t="n">
-        <v>332.6612412306879</v>
+        <v>328.9767653957764</v>
       </c>
       <c r="D69" t="n">
-        <v>327.491109600743</v>
+        <v>321.4989071734381</v>
       </c>
       <c r="E69" t="n">
-        <v>331.4132690429688</v>
+        <v>323.8660583496094</v>
       </c>
       <c r="F69" t="n">
-        <v>7660800</v>
+        <v>9815200</v>
       </c>
       <c r="G69" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B70" t="n">
-        <v>327.9764350864437</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C70" t="n">
-        <v>328.9767653957764</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D70" t="n">
-        <v>321.4989071734381</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E70" t="n">
-        <v>323.8660583496094</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F70" t="n">
-        <v>9815200</v>
+        <v>11737100</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B71" t="n">
-        <v>323.2718313763784</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C71" t="n">
-        <v>328.2339475379842</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D71" t="n">
-        <v>322.5388804495614</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E71" t="n">
-        <v>326.6393432617188</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F71" t="n">
-        <v>11737100</v>
+        <v>6738100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B72" t="n">
-        <v>326.1936353875406</v>
+        <v>318.8049332018166</v>
       </c>
       <c r="C72" t="n">
-        <v>328.7291759216584</v>
+        <v>322.9053661093398</v>
       </c>
       <c r="D72" t="n">
-        <v>325.0348299492433</v>
+        <v>318.1611490039577</v>
       </c>
       <c r="E72" t="n">
-        <v>326.0450744628906</v>
+        <v>321.3899841308594</v>
       </c>
       <c r="F72" t="n">
-        <v>6738100</v>
+        <v>12805100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B73" t="n">
-        <v>318.8049332018166</v>
+        <v>321.2017865718998</v>
       </c>
       <c r="C73" t="n">
-        <v>322.9053661093398</v>
+        <v>323.7373271836527</v>
       </c>
       <c r="D73" t="n">
-        <v>318.1611490039577</v>
+        <v>307.6029755260753</v>
       </c>
       <c r="E73" t="n">
-        <v>321.3899841308594</v>
+        <v>307.9298095703125</v>
       </c>
       <c r="F73" t="n">
-        <v>12805100</v>
+        <v>19371200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B74" t="n">
-        <v>321.2017865718998</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C74" t="n">
-        <v>323.7373271836527</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D74" t="n">
-        <v>307.6029755260753</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E74" t="n">
-        <v>307.9298095703125</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F74" t="n">
-        <v>19371200</v>
+        <v>25951500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B75" t="n">
-        <v>305.2556057077196</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C75" t="n">
-        <v>308.7815926253858</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D75" t="n">
-        <v>303.1954601804828</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E75" t="n">
-        <v>304.9287414550781</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F75" t="n">
-        <v>25951500</v>
+        <v>14751400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B76" t="n">
-        <v>305.5230197927318</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C76" t="n">
-        <v>309.95031666446</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D76" t="n">
-        <v>304.8098971346673</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E76" t="n">
-        <v>306.3054809570312</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F76" t="n">
-        <v>14751400</v>
+        <v>14652500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B77" t="n">
-        <v>307.385060616362</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C77" t="n">
-        <v>314.1795087286461</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D77" t="n">
-        <v>307.0383983149945</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E77" t="n">
-        <v>309.4848022460938</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F77" t="n">
-        <v>14652500</v>
+        <v>12900600</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B78" t="n">
-        <v>303.2845981841295</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C78" t="n">
-        <v>308.1774060521912</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D78" t="n">
-        <v>298.9761500928895</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E78" t="n">
-        <v>299.8477478027344</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F78" t="n">
-        <v>12900600</v>
+        <v>10270100</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B79" t="n">
-        <v>300.5311849469782</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C79" t="n">
-        <v>302.4823658305288</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D79" t="n">
-        <v>298.2729680555718</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E79" t="n">
-        <v>299.1544799804688</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F79" t="n">
-        <v>10270100</v>
+        <v>10535800</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B80" t="n">
-        <v>301.9474777854751</v>
+        <v>299.1148422218051</v>
       </c>
       <c r="C80" t="n">
-        <v>305.2555953909441</v>
+        <v>299.4813025896872</v>
       </c>
       <c r="D80" t="n">
-        <v>300.0062112868251</v>
+        <v>293.6773006232809</v>
       </c>
       <c r="E80" t="n">
-        <v>300.729248046875</v>
+        <v>294.875732421875</v>
       </c>
       <c r="F80" t="n">
-        <v>10535800</v>
+        <v>11107900</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B81" t="n">
-        <v>299.1148422218051</v>
+        <v>294.9648788077786</v>
       </c>
       <c r="C81" t="n">
-        <v>299.4813025896872</v>
+        <v>298.8969527426069</v>
       </c>
       <c r="D81" t="n">
-        <v>293.6773006232809</v>
+        <v>294.6083325653198</v>
       </c>
       <c r="E81" t="n">
-        <v>294.875732421875</v>
+        <v>298.1640319824219</v>
       </c>
       <c r="F81" t="n">
-        <v>11107900</v>
+        <v>11752700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B82" t="n">
-        <v>294.9648788077786</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C82" t="n">
-        <v>298.8969527426069</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D82" t="n">
-        <v>294.6083325653198</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E82" t="n">
-        <v>298.1640319824219</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F82" t="n">
-        <v>11752700</v>
+        <v>11527400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B83" t="n">
-        <v>298.4512235287846</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C83" t="n">
-        <v>299.0851237823749</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D83" t="n">
-        <v>295.3016109870806</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E83" t="n">
-        <v>297.4409790039062</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F83" t="n">
-        <v>11527400</v>
+        <v>9556700</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B84" t="n">
-        <v>297.4013222225187</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C84" t="n">
-        <v>299.0355829225425</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D84" t="n">
-        <v>295.2025300603667</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E84" t="n">
-        <v>297.8965454101562</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F84" t="n">
-        <v>9556700</v>
+        <v>11580000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B85" t="n">
-        <v>299.5110006693188</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C85" t="n">
-        <v>303.898671192008</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D85" t="n">
-        <v>299.3327275624257</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E85" t="n">
-        <v>303.4926147460938</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F85" t="n">
-        <v>11580000</v>
+        <v>11953200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B86" t="n">
-        <v>302.333781642444</v>
+        <v>301.5513012828864</v>
       </c>
       <c r="C86" t="n">
-        <v>304.9881708986046</v>
+        <v>306.3450582127215</v>
       </c>
       <c r="D86" t="n">
-        <v>299.6694782493637</v>
+        <v>298.4908255461663</v>
       </c>
       <c r="E86" t="n">
-        <v>302.9676818847656</v>
+        <v>305.1961669921875</v>
       </c>
       <c r="F86" t="n">
-        <v>11953200</v>
+        <v>9839400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B87" t="n">
-        <v>301.5513012828864</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C87" t="n">
-        <v>306.3450582127215</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D87" t="n">
-        <v>298.4908255461663</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E87" t="n">
-        <v>305.1961669921875</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F87" t="n">
-        <v>9839400</v>
+        <v>12688000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B88" t="n">
-        <v>306.7709905338949</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="C88" t="n">
-        <v>313.2286905211348</v>
+        <v>316.2594719758441</v>
       </c>
       <c r="D88" t="n">
-        <v>306.1470044328188</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="E88" t="n">
-        <v>311.8420715332031</v>
+        <v>314.2389526367188</v>
       </c>
       <c r="F88" t="n">
-        <v>12688000</v>
+        <v>9848800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B89" t="n">
-        <v>311.4062901330092</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C89" t="n">
-        <v>316.2594719758441</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D89" t="n">
-        <v>311.4062901330092</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E89" t="n">
-        <v>314.2389526367188</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F89" t="n">
-        <v>9848800</v>
+        <v>9388000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B90" t="n">
-        <v>311.9906259989966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C90" t="n">
-        <v>312.9909865673853</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D90" t="n">
-        <v>302.6210112179966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E90" t="n">
-        <v>307.1968688964844</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F90" t="n">
-        <v>9388000</v>
+        <v>17797400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B91" t="n">
-        <v>311.7034102684662</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C91" t="n">
-        <v>321.1522783634816</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D91" t="n">
-        <v>311.7034102684662</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E91" t="n">
-        <v>319.3199462890625</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F91" t="n">
-        <v>17797400</v>
+        <v>11477500</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B92" t="n">
-        <v>318.2700781279603</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C92" t="n">
-        <v>323.2817350541263</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D92" t="n">
-        <v>317.0518180384032</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E92" t="n">
-        <v>319.0228271484375</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F92" t="n">
-        <v>11477500</v>
+        <v>9902200</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B93" t="n">
-        <v>319.4684837021083</v>
+        <v>320.1518827061323</v>
       </c>
       <c r="C93" t="n">
-        <v>323.014298845819</v>
+        <v>322.1724018130651</v>
       </c>
       <c r="D93" t="n">
-        <v>312.1094739861534</v>
+        <v>305.7805260837019</v>
       </c>
       <c r="E93" t="n">
-        <v>315.2392883300781</v>
+        <v>307.8505554199219</v>
       </c>
       <c r="F93" t="n">
-        <v>9902200</v>
+        <v>8703500</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B94" t="n">
-        <v>320.1518827061323</v>
+        <v>309.2966374972976</v>
       </c>
       <c r="C94" t="n">
-        <v>322.1724018130651</v>
+        <v>310.6238322045743</v>
       </c>
       <c r="D94" t="n">
-        <v>305.7805260837019</v>
+        <v>297.1537535117247</v>
       </c>
       <c r="E94" t="n">
-        <v>307.8505554199219</v>
+        <v>299.7487487792969</v>
       </c>
       <c r="F94" t="n">
-        <v>8703500</v>
+        <v>13443400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B95" t="n">
-        <v>309.2966374972976</v>
+        <v>295.6680782309701</v>
       </c>
       <c r="C95" t="n">
-        <v>310.6238322045743</v>
+        <v>301.3829738793206</v>
       </c>
       <c r="D95" t="n">
-        <v>297.1537535117247</v>
+        <v>293.6871852314235</v>
       </c>
       <c r="E95" t="n">
-        <v>299.7487487792969</v>
+        <v>299.6595764160156</v>
       </c>
       <c r="F95" t="n">
-        <v>13443400</v>
+        <v>9114500</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B96" t="n">
-        <v>295.6680782309701</v>
+        <v>299.8675850307636</v>
       </c>
       <c r="C96" t="n">
-        <v>301.3829738793206</v>
+        <v>305.2952123797385</v>
       </c>
       <c r="D96" t="n">
-        <v>293.6871852314235</v>
+        <v>299.6100592744303</v>
       </c>
       <c r="E96" t="n">
-        <v>299.6595764160156</v>
+        <v>304.1958312988281</v>
       </c>
       <c r="F96" t="n">
-        <v>9114500</v>
+        <v>8896800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B97" t="n">
-        <v>299.8675850307636</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C97" t="n">
-        <v>305.2952123797385</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D97" t="n">
-        <v>299.6100592744303</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E97" t="n">
-        <v>304.1958312988281</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F97" t="n">
-        <v>8896800</v>
+        <v>7209600</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B98" t="n">
-        <v>305.5130974954087</v>
+        <v>304.2354272061944</v>
       </c>
       <c r="C98" t="n">
-        <v>309.2966101142475</v>
+        <v>306.2262038721237</v>
       </c>
       <c r="D98" t="n">
-        <v>304.2849535938903</v>
+        <v>302.2049939958365</v>
       </c>
       <c r="E98" t="n">
-        <v>305.8300476074219</v>
+        <v>305.1069946289062</v>
       </c>
       <c r="F98" t="n">
-        <v>7209600</v>
+        <v>6737700</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B99" t="n">
-        <v>304.2354272061944</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C99" t="n">
-        <v>306.2262038721237</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D99" t="n">
-        <v>302.2049939958365</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E99" t="n">
-        <v>305.1069946289062</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F99" t="n">
-        <v>6737700</v>
+        <v>7792700</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B100" t="n">
-        <v>305.4536802835111</v>
+        <v>305.8498457788994</v>
       </c>
       <c r="C100" t="n">
-        <v>308.0288471084009</v>
+        <v>308.0288400173425</v>
       </c>
       <c r="D100" t="n">
-        <v>302.7596647203387</v>
+        <v>292.2807478108573</v>
       </c>
       <c r="E100" t="n">
-        <v>307.8208618164062</v>
+        <v>294.8262023925781</v>
       </c>
       <c r="F100" t="n">
-        <v>7792700</v>
+        <v>12955400</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B101" t="n">
-        <v>305.8498457788994</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C101" t="n">
-        <v>308.0288400173425</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D101" t="n">
-        <v>292.2807478108573</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E101" t="n">
-        <v>294.8262023925781</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F101" t="n">
-        <v>12955400</v>
+        <v>13554100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B102" t="n">
-        <v>293.9843218466586</v>
+        <v>295.7869507950724</v>
       </c>
       <c r="C102" t="n">
-        <v>296.886322684036</v>
+        <v>300.7589812348872</v>
       </c>
       <c r="D102" t="n">
-        <v>288.5962907533433</v>
+        <v>294.1725181992404</v>
       </c>
       <c r="E102" t="n">
-        <v>294.459716796875</v>
+        <v>300.4024047851562</v>
       </c>
       <c r="F102" t="n">
-        <v>13554100</v>
+        <v>8095500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B103" t="n">
-        <v>295.7869507950724</v>
+        <v>301.670173133609</v>
       </c>
       <c r="C103" t="n">
-        <v>300.7589812348872</v>
+        <v>306.0578739762234</v>
       </c>
       <c r="D103" t="n">
-        <v>294.1725181992404</v>
+        <v>300.7391812579012</v>
       </c>
       <c r="E103" t="n">
-        <v>300.4024047851562</v>
+        <v>303.2053833007812</v>
       </c>
       <c r="F103" t="n">
-        <v>8095500</v>
+        <v>7007800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B104" t="n">
-        <v>301.670173133609</v>
+        <v>297.1339389424841</v>
       </c>
       <c r="C104" t="n">
-        <v>306.0578739762234</v>
+        <v>300.0557680991628</v>
       </c>
       <c r="D104" t="n">
-        <v>300.7391812579012</v>
+        <v>291.636973162459</v>
       </c>
       <c r="E104" t="n">
-        <v>303.2053833007812</v>
+        <v>297.4310607910156</v>
       </c>
       <c r="F104" t="n">
-        <v>7007800</v>
+        <v>18620800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B105" t="n">
-        <v>297.1339389424841</v>
+        <v>291.9935267958635</v>
       </c>
       <c r="C105" t="n">
-        <v>300.0557680991628</v>
+        <v>297.1141484397957</v>
       </c>
       <c r="D105" t="n">
-        <v>291.636973162459</v>
+        <v>290.4088063693875</v>
       </c>
       <c r="E105" t="n">
-        <v>297.4310607910156</v>
+        <v>294.7172546386719</v>
       </c>
       <c r="F105" t="n">
-        <v>18620800</v>
+        <v>8508900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B106" t="n">
-        <v>291.9935267958635</v>
+        <v>289.4975898716125</v>
       </c>
       <c r="C106" t="n">
-        <v>297.1141484397957</v>
+        <v>299.5011046657454</v>
       </c>
       <c r="D106" t="n">
-        <v>290.4088063693875</v>
+        <v>286.7342359222354</v>
       </c>
       <c r="E106" t="n">
-        <v>294.7172546386719</v>
+        <v>297.3914489746094</v>
       </c>
       <c r="F106" t="n">
-        <v>8508900</v>
+        <v>10278200</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B107" t="n">
-        <v>289.4975898716125</v>
+        <v>297.1240288614248</v>
       </c>
       <c r="C107" t="n">
-        <v>299.5011046657454</v>
+        <v>298.1243894751821</v>
       </c>
       <c r="D107" t="n">
-        <v>286.7342359222354</v>
+        <v>292.993883980321</v>
       </c>
       <c r="E107" t="n">
-        <v>297.3914489746094</v>
+        <v>296.52978515625</v>
       </c>
       <c r="F107" t="n">
-        <v>10278200</v>
+        <v>8055700</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B108" t="n">
-        <v>297.1240288614248</v>
+        <v>295.1332451958745</v>
       </c>
       <c r="C108" t="n">
-        <v>298.1243894751821</v>
+        <v>298.3620800816865</v>
       </c>
       <c r="D108" t="n">
-        <v>292.993883980321</v>
+        <v>289.6362492414601</v>
       </c>
       <c r="E108" t="n">
-        <v>296.52978515625</v>
+        <v>290.7455444335938</v>
       </c>
       <c r="F108" t="n">
-        <v>8055700</v>
+        <v>12732500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B109" t="n">
-        <v>295.1332451958745</v>
+        <v>283.6044306839189</v>
       </c>
       <c r="C109" t="n">
-        <v>298.3620800816865</v>
+        <v>287.2195541533999</v>
       </c>
       <c r="D109" t="n">
-        <v>289.6362492414601</v>
+        <v>280.9995517042956</v>
       </c>
       <c r="E109" t="n">
-        <v>290.7455444335938</v>
+        <v>286.7144470214844</v>
       </c>
       <c r="F109" t="n">
-        <v>12732500</v>
+        <v>13496500</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B110" t="n">
-        <v>283.6044306839189</v>
+        <v>282.7724816341387</v>
       </c>
       <c r="C110" t="n">
-        <v>287.2195541533999</v>
+        <v>288.3189881947603</v>
       </c>
       <c r="D110" t="n">
-        <v>280.9995517042956</v>
+        <v>277.7707387954702</v>
       </c>
       <c r="E110" t="n">
-        <v>286.7144470214844</v>
+        <v>287.1502685546875</v>
       </c>
       <c r="F110" t="n">
-        <v>13496500</v>
+        <v>12241100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B111" t="n">
-        <v>282.7724816341387</v>
+        <v>286.5262662545288</v>
       </c>
       <c r="C111" t="n">
-        <v>288.3189881947603</v>
+        <v>289.9532025593205</v>
       </c>
       <c r="D111" t="n">
-        <v>277.7707387954702</v>
+        <v>284.4364084963449</v>
       </c>
       <c r="E111" t="n">
-        <v>287.1502685546875</v>
+        <v>285.9716186523438</v>
       </c>
       <c r="F111" t="n">
-        <v>12241100</v>
+        <v>8344900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B112" t="n">
-        <v>286.5262662545288</v>
+        <v>286.0508166178312</v>
       </c>
       <c r="C112" t="n">
-        <v>289.9532025593205</v>
+        <v>287.7048753720447</v>
       </c>
       <c r="D112" t="n">
-        <v>284.4364084963449</v>
+        <v>282.1385413260368</v>
       </c>
       <c r="E112" t="n">
-        <v>285.9716186523438</v>
+        <v>284.7731323242188</v>
       </c>
       <c r="F112" t="n">
-        <v>8344900</v>
+        <v>10205000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B113" t="n">
-        <v>286.0508166178312</v>
+        <v>280.1279538528093</v>
       </c>
       <c r="C113" t="n">
-        <v>287.7048753720447</v>
+        <v>281.167940752382</v>
       </c>
       <c r="D113" t="n">
-        <v>282.1385413260368</v>
+        <v>276.4336079693154</v>
       </c>
       <c r="E113" t="n">
-        <v>284.7731323242188</v>
+        <v>280.1874084472656</v>
       </c>
       <c r="F113" t="n">
-        <v>10205000</v>
+        <v>13760500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B114" t="n">
-        <v>280.1279538528093</v>
+        <v>281.9504072447318</v>
       </c>
       <c r="C114" t="n">
-        <v>281.167940752382</v>
+        <v>284.4463214441296</v>
       </c>
       <c r="D114" t="n">
-        <v>276.4336079693154</v>
+        <v>280.2468381234208</v>
       </c>
       <c r="E114" t="n">
-        <v>280.1874084472656</v>
+        <v>280.7321472167969</v>
       </c>
       <c r="F114" t="n">
-        <v>13760500</v>
+        <v>9091200</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B115" t="n">
-        <v>281.9504072447318</v>
+        <v>283.6044205599556</v>
       </c>
       <c r="C115" t="n">
-        <v>284.4463214441296</v>
+        <v>286.506421278288</v>
       </c>
       <c r="D115" t="n">
-        <v>280.2468381234208</v>
+        <v>281.8909373944359</v>
       </c>
       <c r="E115" t="n">
-        <v>280.7321472167969</v>
+        <v>283.4261474609375</v>
       </c>
       <c r="F115" t="n">
-        <v>9091200</v>
+        <v>8149000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B116" t="n">
-        <v>283.6044205599556</v>
+        <v>286.2390279690733</v>
       </c>
       <c r="C116" t="n">
-        <v>286.506421278288</v>
+        <v>288.9726698808299</v>
       </c>
       <c r="D116" t="n">
-        <v>281.8909373944359</v>
+        <v>283.2181783456238</v>
       </c>
       <c r="E116" t="n">
-        <v>283.4261474609375</v>
+        <v>284.1492004394531</v>
       </c>
       <c r="F116" t="n">
-        <v>8149000</v>
+        <v>8961200</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B117" t="n">
-        <v>286.2390279690733</v>
+        <v>284.0897484324327</v>
       </c>
       <c r="C117" t="n">
-        <v>288.9726698808299</v>
+        <v>286.6451172582804</v>
       </c>
       <c r="D117" t="n">
-        <v>283.2181783456238</v>
+        <v>282.3960934275981</v>
       </c>
       <c r="E117" t="n">
-        <v>284.1492004394531</v>
+        <v>284.9910583496094</v>
       </c>
       <c r="F117" t="n">
-        <v>8961200</v>
+        <v>10057000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B118" t="n">
-        <v>284.0897484324327</v>
+        <v>284.1392586396808</v>
       </c>
       <c r="C118" t="n">
-        <v>286.6451172582804</v>
+        <v>286.7441374214082</v>
       </c>
       <c r="D118" t="n">
-        <v>282.3960934275981</v>
+        <v>281.9008401776293</v>
       </c>
       <c r="E118" t="n">
-        <v>284.9910583496094</v>
+        <v>285.2188415527344</v>
       </c>
       <c r="F118" t="n">
-        <v>10057000</v>
+        <v>9846700</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B119" t="n">
-        <v>284.1392586396808</v>
+        <v>285.327825032355</v>
       </c>
       <c r="C119" t="n">
-        <v>286.7441374214082</v>
+        <v>287.9327042603992</v>
       </c>
       <c r="D119" t="n">
-        <v>281.9008401776293</v>
+        <v>282.5446726819272</v>
       </c>
       <c r="E119" t="n">
-        <v>285.2188415527344</v>
+        <v>283.8223571777344</v>
       </c>
       <c r="F119" t="n">
-        <v>9846700</v>
+        <v>22436500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B120" t="n">
-        <v>285.327825032355</v>
+        <v>291.4982779446762</v>
       </c>
       <c r="C120" t="n">
-        <v>287.9327042603992</v>
+        <v>292.9245231806114</v>
       </c>
       <c r="D120" t="n">
-        <v>282.5446726819272</v>
+        <v>285.2188513876401</v>
       </c>
       <c r="E120" t="n">
-        <v>283.8223571777344</v>
+        <v>287.1403198242188</v>
       </c>
       <c r="F120" t="n">
-        <v>22436500</v>
+        <v>11470800</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B121" t="n">
-        <v>291.4982779446762</v>
+        <v>283.4360748065673</v>
       </c>
       <c r="C121" t="n">
-        <v>292.9245231806114</v>
+        <v>292.6571288676103</v>
       </c>
       <c r="D121" t="n">
-        <v>285.2188513876401</v>
+        <v>282.6436995084055</v>
       </c>
       <c r="E121" t="n">
-        <v>287.1403198242188</v>
+        <v>289.6065368652344</v>
       </c>
       <c r="F121" t="n">
-        <v>11470800</v>
+        <v>11092300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B122" t="n">
-        <v>283.4360748065673</v>
+        <v>291.3398308899875</v>
       </c>
       <c r="C122" t="n">
-        <v>292.6571288676103</v>
+        <v>294.7965097163498</v>
       </c>
       <c r="D122" t="n">
-        <v>282.6436995084055</v>
+        <v>289.6461758443202</v>
       </c>
       <c r="E122" t="n">
-        <v>289.6065368652344</v>
+        <v>292.5977172851562</v>
       </c>
       <c r="F122" t="n">
-        <v>11092300</v>
+        <v>12188200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B123" t="n">
-        <v>291.3398308899875</v>
+        <v>289.7848205526045</v>
       </c>
       <c r="C123" t="n">
-        <v>294.7965097163498</v>
+        <v>292.1718002190451</v>
       </c>
       <c r="D123" t="n">
-        <v>289.6461758443202</v>
+        <v>287.9525187281419</v>
       </c>
       <c r="E123" t="n">
-        <v>292.5977172851562</v>
+        <v>288.8736267089844</v>
       </c>
       <c r="F123" t="n">
-        <v>12188200</v>
+        <v>8669200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B124" t="n">
-        <v>289.7848205526045</v>
+        <v>286.3777093696089</v>
       </c>
       <c r="C124" t="n">
-        <v>292.1718002190451</v>
+        <v>287.3384134369941</v>
       </c>
       <c r="D124" t="n">
-        <v>287.9525187281419</v>
+        <v>279.0582953832721</v>
       </c>
       <c r="E124" t="n">
-        <v>288.8736267089844</v>
+        <v>280.1378784179688</v>
       </c>
       <c r="F124" t="n">
-        <v>8669200</v>
+        <v>9873300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B125" t="n">
-        <v>286.3777093696089</v>
+        <v>282.0197247859078</v>
       </c>
       <c r="C125" t="n">
-        <v>287.3384134369941</v>
+        <v>284.505755156032</v>
       </c>
       <c r="D125" t="n">
-        <v>279.0582953832721</v>
+        <v>279.6327451103039</v>
       </c>
       <c r="E125" t="n">
-        <v>280.1378784179688</v>
+        <v>281.0589904785156</v>
       </c>
       <c r="F125" t="n">
-        <v>9873300</v>
+        <v>11734400</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B126" t="n">
-        <v>282.0197247859078</v>
+        <v>285.7140887250632</v>
       </c>
       <c r="C126" t="n">
-        <v>284.505755156032</v>
+        <v>292.2510413422024</v>
       </c>
       <c r="D126" t="n">
-        <v>279.6327451103039</v>
+        <v>282.2277281014015</v>
       </c>
       <c r="E126" t="n">
-        <v>281.0589904785156</v>
+        <v>291.3497314453125</v>
       </c>
       <c r="F126" t="n">
-        <v>11734400</v>
+        <v>12956900</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B127" t="n">
-        <v>285.7140887250632</v>
+        <v>292.567989087923</v>
       </c>
       <c r="C127" t="n">
-        <v>292.2510413422024</v>
+        <v>295.8661624411999</v>
       </c>
       <c r="D127" t="n">
-        <v>282.2277281014015</v>
+        <v>290.1116710297465</v>
       </c>
       <c r="E127" t="n">
-        <v>291.3497314453125</v>
+        <v>292.5580749511719</v>
       </c>
       <c r="F127" t="n">
-        <v>12956900</v>
+        <v>11267200</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B128" t="n">
-        <v>292.567989087923</v>
+        <v>289.1212191631598</v>
       </c>
       <c r="C128" t="n">
-        <v>295.8661624411999</v>
+        <v>292.7957669317203</v>
       </c>
       <c r="D128" t="n">
-        <v>290.1116710297465</v>
+        <v>285.9616926535428</v>
       </c>
       <c r="E128" t="n">
-        <v>292.5580749511719</v>
+        <v>291.7855224609375</v>
       </c>
       <c r="F128" t="n">
-        <v>11267200</v>
+        <v>6669300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,25 +3771,25 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B129" t="n">
-        <v>289.1212191631598</v>
+        <v>292.7412191857173</v>
       </c>
       <c r="C129" t="n">
-        <v>292.7957669317203</v>
+        <v>295.4987855589938</v>
       </c>
       <c r="D129" t="n">
-        <v>285.9616926535428</v>
+        <v>291.8850906324002</v>
       </c>
       <c r="E129" t="n">
-        <v>291.7855224609375</v>
+        <v>294.125</v>
       </c>
       <c r="F129" t="n">
-        <v>6669300</v>
+        <v>7142600</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -3797,25 +3797,25 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B130" t="n">
-        <v>292.7412191857173</v>
+        <v>291.8253790066561</v>
       </c>
       <c r="C130" t="n">
-        <v>295.4987855589938</v>
+        <v>296.8427544058445</v>
       </c>
       <c r="D130" t="n">
-        <v>291.8850906324002</v>
+        <v>291.3873498301165</v>
       </c>
       <c r="E130" t="n">
-        <v>294.125</v>
+        <v>296.0662536621094</v>
       </c>
       <c r="F130" t="n">
-        <v>7142600</v>
+        <v>7849100</v>
       </c>
       <c r="G130" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B131" t="n">
-        <v>291.8253790066561</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="C131" t="n">
-        <v>296.8427544058445</v>
+        <v>309.8640903908154</v>
       </c>
       <c r="D131" t="n">
-        <v>291.3873498301165</v>
+        <v>303.9606617936424</v>
       </c>
       <c r="E131" t="n">
-        <v>296.0662536621094</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="F131" t="n">
-        <v>7849100</v>
+        <v>10590200</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B132" t="n">
-        <v>306.5888366699219</v>
+        <v>305.5734164156603</v>
       </c>
       <c r="C132" t="n">
-        <v>309.8640903908154</v>
+        <v>309.8640846884941</v>
       </c>
       <c r="D132" t="n">
-        <v>303.9606617936424</v>
+        <v>304.73715687535</v>
       </c>
       <c r="E132" t="n">
-        <v>306.5888366699219</v>
+        <v>308.938232421875</v>
       </c>
       <c r="F132" t="n">
-        <v>10590200</v>
+        <v>6586600</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B133" t="n">
-        <v>305.5734164156603</v>
+        <v>308.6097380099313</v>
       </c>
       <c r="C133" t="n">
-        <v>309.8640846884941</v>
+        <v>308.9581744354404</v>
       </c>
       <c r="D133" t="n">
-        <v>304.73715687535</v>
+        <v>305.344449093958</v>
       </c>
       <c r="E133" t="n">
-        <v>308.938232421875</v>
+        <v>308.4803161621094</v>
       </c>
       <c r="F133" t="n">
-        <v>6586600</v>
+        <v>6069700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B134" t="n">
-        <v>308.6097380099313</v>
+        <v>306.0910825316173</v>
       </c>
       <c r="C134" t="n">
-        <v>308.9581744354404</v>
+        <v>312.3329523629397</v>
       </c>
       <c r="D134" t="n">
-        <v>305.344449093958</v>
+        <v>304.0900871089203</v>
       </c>
       <c r="E134" t="n">
-        <v>308.4803161621094</v>
+        <v>312.2732238769531</v>
       </c>
       <c r="F134" t="n">
-        <v>6069700</v>
+        <v>8318200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B135" t="n">
-        <v>306.0910825316173</v>
+        <v>308.4305432499699</v>
       </c>
       <c r="C135" t="n">
-        <v>312.3329523629397</v>
+        <v>312.9103618924516</v>
       </c>
       <c r="D135" t="n">
-        <v>304.0900871089203</v>
+        <v>307.4847916064935</v>
       </c>
       <c r="E135" t="n">
-        <v>312.2732238769531</v>
+        <v>309.7247009277344</v>
       </c>
       <c r="F135" t="n">
-        <v>8318200</v>
+        <v>11455500</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B136" t="n">
-        <v>308.4305432499699</v>
+        <v>312.5420354159922</v>
       </c>
       <c r="C136" t="n">
-        <v>312.9103618924516</v>
+        <v>312.8307129741003</v>
       </c>
       <c r="D136" t="n">
-        <v>307.4847916064935</v>
+        <v>302.8954898881459</v>
       </c>
       <c r="E136" t="n">
-        <v>309.7247009277344</v>
+        <v>304.5579833984375</v>
       </c>
       <c r="F136" t="n">
-        <v>11455500</v>
+        <v>9885800</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B137" t="n">
-        <v>312.5420354159922</v>
+        <v>303.9805907681049</v>
       </c>
       <c r="C137" t="n">
-        <v>312.8307129741003</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="D137" t="n">
-        <v>302.8954898881459</v>
+        <v>303.8312695552229</v>
       </c>
       <c r="E137" t="n">
-        <v>304.5579833984375</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="F137" t="n">
-        <v>9885800</v>
+        <v>8208600</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B138" t="n">
-        <v>303.9805907681049</v>
+        <v>311.068653468178</v>
       </c>
       <c r="C138" t="n">
-        <v>308.5599670410156</v>
+        <v>313.4877482505245</v>
       </c>
       <c r="D138" t="n">
-        <v>303.8312695552229</v>
+        <v>308.6993222963794</v>
       </c>
       <c r="E138" t="n">
-        <v>308.5599670410156</v>
+        <v>308.8984375</v>
       </c>
       <c r="F138" t="n">
-        <v>8208600</v>
+        <v>11082400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B139" t="n">
-        <v>311.068653468178</v>
+        <v>309.4559416581444</v>
       </c>
       <c r="C139" t="n">
-        <v>313.4877482505245</v>
+        <v>315.7077766193834</v>
       </c>
       <c r="D139" t="n">
-        <v>308.6993222963794</v>
+        <v>308.9780833700189</v>
       </c>
       <c r="E139" t="n">
-        <v>308.8984375</v>
+        <v>315.5683898925781</v>
       </c>
       <c r="F139" t="n">
-        <v>11082400</v>
+        <v>10772000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B140" t="n">
-        <v>309.4559416581444</v>
+        <v>316.0661368489313</v>
       </c>
       <c r="C140" t="n">
-        <v>315.7077766193834</v>
+        <v>318.8038038717339</v>
       </c>
       <c r="D140" t="n">
-        <v>308.9780833700189</v>
+        <v>311.3474041387296</v>
       </c>
       <c r="E140" t="n">
-        <v>315.5683898925781</v>
+        <v>311.5962829589844</v>
       </c>
       <c r="F140" t="n">
-        <v>10772000</v>
+        <v>7084300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B141" t="n">
-        <v>316.0661368489313</v>
+        <v>313.4379903862348</v>
       </c>
       <c r="C141" t="n">
-        <v>318.8038038717339</v>
+        <v>313.7366328164263</v>
       </c>
       <c r="D141" t="n">
-        <v>311.3474041387296</v>
+        <v>310.5410372905177</v>
       </c>
       <c r="E141" t="n">
-        <v>311.5962829589844</v>
+        <v>311.6161804199219</v>
       </c>
       <c r="F141" t="n">
-        <v>7084300</v>
+        <v>5545900</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B142" t="n">
-        <v>313.4379903862348</v>
+        <v>312.1139549773267</v>
       </c>
       <c r="C142" t="n">
-        <v>313.7366328164263</v>
+        <v>313.5773637260273</v>
       </c>
       <c r="D142" t="n">
-        <v>310.5410372905177</v>
+        <v>307.5047445243564</v>
       </c>
       <c r="E142" t="n">
-        <v>311.6161804199219</v>
+        <v>310.2921752929688</v>
       </c>
       <c r="F142" t="n">
-        <v>5545900</v>
+        <v>6969700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B143" t="n">
-        <v>312.1139549773267</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="C143" t="n">
-        <v>313.5773637260273</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="D143" t="n">
-        <v>307.5047445243564</v>
+        <v>306.5092257615542</v>
       </c>
       <c r="E143" t="n">
-        <v>310.2921752929688</v>
+        <v>306.8974609375</v>
       </c>
       <c r="F143" t="n">
-        <v>6969700</v>
+        <v>5215300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B144" t="n">
-        <v>309.7545850384977</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="C144" t="n">
-        <v>309.7545850384977</v>
+        <v>311.1781431330245</v>
       </c>
       <c r="D144" t="n">
-        <v>306.5092257615542</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="E144" t="n">
-        <v>306.8974609375</v>
+        <v>310.232421875</v>
       </c>
       <c r="F144" t="n">
-        <v>5215300</v>
+        <v>7925300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B145" t="n">
-        <v>305.5037244427344</v>
+        <v>313.7864355589005</v>
       </c>
       <c r="C145" t="n">
-        <v>311.1781431330245</v>
+        <v>314.035314384572</v>
       </c>
       <c r="D145" t="n">
-        <v>305.5037244427344</v>
+        <v>309.7745101043047</v>
       </c>
       <c r="E145" t="n">
-        <v>310.232421875</v>
+        <v>310.0532531738281</v>
       </c>
       <c r="F145" t="n">
-        <v>7925300</v>
+        <v>7398600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B146" t="n">
-        <v>313.7864355589005</v>
+        <v>309.1771855961317</v>
       </c>
       <c r="C146" t="n">
-        <v>314.035314384572</v>
+        <v>310.6505287563671</v>
       </c>
       <c r="D146" t="n">
-        <v>309.7745101043047</v>
+        <v>305.9118967162461</v>
       </c>
       <c r="E146" t="n">
-        <v>310.0532531738281</v>
+        <v>307.8630981445312</v>
       </c>
       <c r="F146" t="n">
-        <v>7398600</v>
+        <v>8031800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B147" t="n">
-        <v>309.1771855961317</v>
+        <v>305.6928786901284</v>
       </c>
       <c r="C147" t="n">
-        <v>310.6505287563671</v>
+        <v>312.6913497643884</v>
       </c>
       <c r="D147" t="n">
-        <v>305.9118967162461</v>
+        <v>305.1951210592971</v>
       </c>
       <c r="E147" t="n">
-        <v>307.8630981445312</v>
+        <v>311.8252563476562</v>
       </c>
       <c r="F147" t="n">
-        <v>8031800</v>
+        <v>8865400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B148" t="n">
-        <v>305.6928786901284</v>
+        <v>312.5420381202088</v>
       </c>
       <c r="C148" t="n">
-        <v>312.6913497643884</v>
+        <v>314.6624601726697</v>
       </c>
       <c r="D148" t="n">
-        <v>305.1951210592971</v>
+        <v>310.431520181067</v>
       </c>
       <c r="E148" t="n">
-        <v>311.8252563476562</v>
+        <v>311.0686645507812</v>
       </c>
       <c r="F148" t="n">
-        <v>8865400</v>
+        <v>6135400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B149" t="n">
-        <v>312.5420381202088</v>
+        <v>309.2269452093906</v>
       </c>
       <c r="C149" t="n">
-        <v>314.6624601726697</v>
+        <v>309.2568094519629</v>
       </c>
       <c r="D149" t="n">
-        <v>310.431520181067</v>
+        <v>305.1353920734132</v>
       </c>
       <c r="E149" t="n">
-        <v>311.0686645507812</v>
+        <v>306.270263671875</v>
       </c>
       <c r="F149" t="n">
-        <v>6135400</v>
+        <v>7338200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B150" t="n">
-        <v>309.2269452093906</v>
+        <v>306.3299974055641</v>
       </c>
       <c r="C150" t="n">
-        <v>309.2568094519629</v>
+        <v>309.5753869306937</v>
       </c>
       <c r="D150" t="n">
-        <v>305.1353920734132</v>
+        <v>305.42407485773</v>
       </c>
       <c r="E150" t="n">
-        <v>306.270263671875</v>
+        <v>308.0124206542969</v>
       </c>
       <c r="F150" t="n">
-        <v>7338200</v>
+        <v>6316800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B151" t="n">
-        <v>306.3299974055641</v>
+        <v>310.0532528884956</v>
       </c>
       <c r="C151" t="n">
-        <v>309.5753869306937</v>
+        <v>314.8416790595512</v>
       </c>
       <c r="D151" t="n">
-        <v>305.42407485773</v>
+        <v>309.9536952821754</v>
       </c>
       <c r="E151" t="n">
-        <v>308.0124206542969</v>
+        <v>313.4877624511719</v>
       </c>
       <c r="F151" t="n">
-        <v>6316800</v>
+        <v>8629500</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B152" t="n">
-        <v>310.0532528884956</v>
+        <v>313.2388767644321</v>
       </c>
       <c r="C152" t="n">
-        <v>314.8416790595512</v>
+        <v>314.8814709002291</v>
       </c>
       <c r="D152" t="n">
-        <v>309.9536952821754</v>
+        <v>304.7670623908274</v>
       </c>
       <c r="E152" t="n">
-        <v>313.4877624511719</v>
+        <v>304.8964538574219</v>
       </c>
       <c r="F152" t="n">
-        <v>8629500</v>
+        <v>8359600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B153" t="n">
-        <v>313.2388767644321</v>
+        <v>306.8675912418493</v>
       </c>
       <c r="C153" t="n">
-        <v>314.8814709002291</v>
+        <v>307.6042628420606</v>
       </c>
       <c r="D153" t="n">
-        <v>304.7670623908274</v>
+        <v>299.1523476664256</v>
       </c>
       <c r="E153" t="n">
-        <v>304.8964538574219</v>
+        <v>300.7451782226562</v>
       </c>
       <c r="F153" t="n">
-        <v>8359600</v>
+        <v>9464300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B154" t="n">
-        <v>306.8675912418493</v>
+        <v>300.7451596100784</v>
       </c>
       <c r="C154" t="n">
-        <v>307.6042628420606</v>
+        <v>301.8302675742967</v>
       </c>
       <c r="D154" t="n">
-        <v>299.1523476664256</v>
+        <v>297.5395993270601</v>
       </c>
       <c r="E154" t="n">
-        <v>300.7451782226562</v>
+        <v>298.6545715332031</v>
       </c>
       <c r="F154" t="n">
-        <v>9464300</v>
+        <v>9512000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B155" t="n">
-        <v>300.7451596100784</v>
+        <v>298.6744753830843</v>
       </c>
       <c r="C155" t="n">
-        <v>301.8302675742967</v>
+        <v>304.6873960201211</v>
       </c>
       <c r="D155" t="n">
-        <v>297.5395993270601</v>
+        <v>294.2245209852311</v>
       </c>
       <c r="E155" t="n">
-        <v>298.6545715332031</v>
+        <v>303.5126953125</v>
       </c>
       <c r="F155" t="n">
-        <v>9512000</v>
+        <v>9498200</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B156" t="n">
-        <v>298.6744753830843</v>
+        <v>300.9144028967509</v>
       </c>
       <c r="C156" t="n">
-        <v>304.6873960201211</v>
+        <v>301.6411400127173</v>
       </c>
       <c r="D156" t="n">
-        <v>294.2245209852311</v>
+        <v>298.7242874353194</v>
       </c>
       <c r="E156" t="n">
-        <v>303.5126953125</v>
+        <v>298.9034729003906</v>
       </c>
       <c r="F156" t="n">
-        <v>9498200</v>
+        <v>7709500</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B157" t="n">
-        <v>300.9144028967509</v>
+        <v>300.8945046380796</v>
       </c>
       <c r="C157" t="n">
-        <v>301.6411400127173</v>
+        <v>302.387777613951</v>
       </c>
       <c r="D157" t="n">
-        <v>298.7242874353194</v>
+        <v>297.4699295162906</v>
       </c>
       <c r="E157" t="n">
-        <v>298.9034729003906</v>
+        <v>298.5650024414062</v>
       </c>
       <c r="F157" t="n">
-        <v>7709500</v>
+        <v>7364300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B158" t="n">
-        <v>300.8945046380796</v>
+        <v>298.8636262885424</v>
       </c>
       <c r="C158" t="n">
-        <v>302.387777613951</v>
+        <v>299.4410421498196</v>
       </c>
       <c r="D158" t="n">
-        <v>297.4699295162906</v>
+        <v>295.1205095874812</v>
       </c>
       <c r="E158" t="n">
-        <v>298.5650024414062</v>
+        <v>296.4743957519531</v>
       </c>
       <c r="F158" t="n">
-        <v>7364300</v>
+        <v>8699300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B159" t="n">
-        <v>298.8636262885424</v>
+        <v>296.6635495230975</v>
       </c>
       <c r="C159" t="n">
-        <v>299.4410421498196</v>
+        <v>299.908939014877</v>
       </c>
       <c r="D159" t="n">
-        <v>295.1205095874812</v>
+        <v>295.8870488301784</v>
       </c>
       <c r="E159" t="n">
-        <v>296.4743957519531</v>
+        <v>299.3813171386719</v>
       </c>
       <c r="F159" t="n">
-        <v>8699300</v>
+        <v>7546300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B160" t="n">
-        <v>296.6635495230975</v>
+        <v>299.7396822358739</v>
       </c>
       <c r="C160" t="n">
-        <v>299.908939014877</v>
+        <v>300.436555061437</v>
       </c>
       <c r="D160" t="n">
-        <v>295.8870488301784</v>
+        <v>293.935841710235</v>
       </c>
       <c r="E160" t="n">
-        <v>299.3813171386719</v>
+        <v>294.3738708496094</v>
       </c>
       <c r="F160" t="n">
-        <v>7546300</v>
+        <v>8066900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B161" t="n">
-        <v>299.7396822358739</v>
+        <v>295.3694126574367</v>
       </c>
       <c r="C161" t="n">
-        <v>300.436555061437</v>
+        <v>301.57145376365</v>
       </c>
       <c r="D161" t="n">
-        <v>293.935841710235</v>
+        <v>292.3530024013792</v>
       </c>
       <c r="E161" t="n">
-        <v>294.3738708496094</v>
+        <v>300.625732421875</v>
       </c>
       <c r="F161" t="n">
-        <v>8066900</v>
+        <v>9327000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B162" t="n">
-        <v>295.3694126574367</v>
+        <v>299.8790926087445</v>
       </c>
       <c r="C162" t="n">
-        <v>301.57145376365</v>
+        <v>302.6167597554335</v>
       </c>
       <c r="D162" t="n">
-        <v>292.3530024013792</v>
+        <v>298.8636475324957</v>
       </c>
       <c r="E162" t="n">
-        <v>300.625732421875</v>
+        <v>301.6411437988281</v>
       </c>
       <c r="F162" t="n">
-        <v>9327000</v>
+        <v>7874400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B163" t="n">
-        <v>299.8790926087445</v>
+        <v>303.3135932887391</v>
       </c>
       <c r="C163" t="n">
-        <v>302.6167597554335</v>
+        <v>306.0711901040885</v>
       </c>
       <c r="D163" t="n">
-        <v>298.8636475324957</v>
+        <v>302.4773640852478</v>
       </c>
       <c r="E163" t="n">
-        <v>301.6411437988281</v>
+        <v>305.0059814453125</v>
       </c>
       <c r="F163" t="n">
-        <v>7874400</v>
+        <v>5973900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B164" t="n">
-        <v>303.3135932887391</v>
+        <v>307.1065011172144</v>
       </c>
       <c r="C164" t="n">
-        <v>306.0711901040885</v>
+        <v>308.5400455607295</v>
       </c>
       <c r="D164" t="n">
-        <v>302.4773640852478</v>
+        <v>304.0701916446211</v>
       </c>
       <c r="E164" t="n">
-        <v>305.0059814453125</v>
+        <v>305.3643493652344</v>
       </c>
       <c r="F164" t="n">
-        <v>5973900</v>
+        <v>7725400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B165" t="n">
-        <v>307.1065011172144</v>
+        <v>303.6321536663258</v>
       </c>
       <c r="C165" t="n">
-        <v>308.5400455607295</v>
+        <v>304.5281113223131</v>
       </c>
       <c r="D165" t="n">
-        <v>304.0701916446211</v>
+        <v>294.4236375305438</v>
       </c>
       <c r="E165" t="n">
-        <v>305.3643493652344</v>
+        <v>297.9378051757812</v>
       </c>
       <c r="F165" t="n">
-        <v>7725400</v>
+        <v>11779200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B166" t="n">
-        <v>303.6321536663258</v>
+        <v>296.2354906683788</v>
       </c>
       <c r="C166" t="n">
-        <v>304.5281113223131</v>
+        <v>299.7197941661088</v>
       </c>
       <c r="D166" t="n">
-        <v>294.4236375305438</v>
+        <v>294.4236455581874</v>
       </c>
       <c r="E166" t="n">
-        <v>297.9378051757812</v>
+        <v>295.3992614746094</v>
       </c>
       <c r="F166" t="n">
-        <v>11779200</v>
+        <v>9757700</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B167" t="n">
-        <v>296.2354906683788</v>
+        <v>295.070728717322</v>
       </c>
       <c r="C167" t="n">
-        <v>299.7197941661088</v>
+        <v>298.5351328968941</v>
       </c>
       <c r="D167" t="n">
-        <v>294.4236455581874</v>
+        <v>293.8761285862639</v>
       </c>
       <c r="E167" t="n">
-        <v>295.3992614746094</v>
+        <v>297.9676818847656</v>
       </c>
       <c r="F167" t="n">
-        <v>9757700</v>
+        <v>13969000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B168" t="n">
-        <v>295.070728717322</v>
+        <v>296.3549462063085</v>
       </c>
       <c r="C168" t="n">
-        <v>298.5351328968941</v>
+        <v>298.2065900448191</v>
       </c>
       <c r="D168" t="n">
-        <v>293.8761285862639</v>
+        <v>293.9457858606032</v>
       </c>
       <c r="E168" t="n">
-        <v>297.9676818847656</v>
+        <v>295.2499084472656</v>
       </c>
       <c r="F168" t="n">
-        <v>13969000</v>
+        <v>7930000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B169" t="n">
-        <v>296.3549462063085</v>
+        <v>295.170270518017</v>
       </c>
       <c r="C169" t="n">
-        <v>298.2065900448191</v>
+        <v>300.7152977310929</v>
       </c>
       <c r="D169" t="n">
-        <v>293.9457858606032</v>
+        <v>293.9457758280521</v>
       </c>
       <c r="E169" t="n">
-        <v>295.2499084472656</v>
+        <v>299.6102600097656</v>
       </c>
       <c r="F169" t="n">
-        <v>7930000</v>
+        <v>8296200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B170" t="n">
-        <v>295.170270518017</v>
+        <v>298.5749714904202</v>
       </c>
       <c r="C170" t="n">
-        <v>300.7152977310929</v>
+        <v>300.6058008918799</v>
       </c>
       <c r="D170" t="n">
-        <v>293.9457758280521</v>
+        <v>295.2300241797341</v>
       </c>
       <c r="E170" t="n">
-        <v>299.6102600097656</v>
+        <v>299.5007934570312</v>
       </c>
       <c r="F170" t="n">
-        <v>8296200</v>
+        <v>7003900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B171" t="n">
-        <v>298.5749714904202</v>
+        <v>304.3688300919619</v>
       </c>
       <c r="C171" t="n">
-        <v>300.6058008918799</v>
+        <v>311.5066879726736</v>
       </c>
       <c r="D171" t="n">
-        <v>295.2300241797341</v>
+        <v>303.0746723882986</v>
       </c>
       <c r="E171" t="n">
-        <v>299.5007934570312</v>
+        <v>309.4957580566406</v>
       </c>
       <c r="F171" t="n">
-        <v>7003900</v>
+        <v>10345200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B172" t="n">
-        <v>304.3688300919619</v>
+        <v>312.8805189963161</v>
       </c>
       <c r="C172" t="n">
-        <v>311.5066879726736</v>
+        <v>313.5873263681962</v>
       </c>
       <c r="D172" t="n">
-        <v>303.0746723882986</v>
+        <v>308.211549706599</v>
       </c>
       <c r="E172" t="n">
-        <v>309.4957580566406</v>
+        <v>310.9691162109375</v>
       </c>
       <c r="F172" t="n">
-        <v>10345200</v>
+        <v>9118800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B173" t="n">
-        <v>312.8805189963161</v>
+        <v>311.8451695343703</v>
       </c>
       <c r="C173" t="n">
-        <v>313.5873263681962</v>
+        <v>314.881479064701</v>
       </c>
       <c r="D173" t="n">
-        <v>308.211549706599</v>
+        <v>309.3862455138746</v>
       </c>
       <c r="E173" t="n">
-        <v>310.9691162109375</v>
+        <v>309.7147521972656</v>
       </c>
       <c r="F173" t="n">
-        <v>9118800</v>
+        <v>6827000</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B174" t="n">
-        <v>311.8451695343703</v>
+        <v>312.1040028799189</v>
       </c>
       <c r="C174" t="n">
-        <v>314.881479064701</v>
+        <v>315.0009559692908</v>
       </c>
       <c r="D174" t="n">
-        <v>309.3862455138746</v>
+        <v>307.6241841525692</v>
       </c>
       <c r="E174" t="n">
-        <v>309.7147521972656</v>
+        <v>311.2976379394531</v>
       </c>
       <c r="F174" t="n">
-        <v>6827000</v>
+        <v>11594600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B175" t="n">
-        <v>312.1040028799189</v>
+        <v>311.1582462393224</v>
       </c>
       <c r="C175" t="n">
-        <v>315.0009559692908</v>
+        <v>313.3384270822022</v>
       </c>
       <c r="D175" t="n">
-        <v>307.6241841525692</v>
+        <v>307.6440785979976</v>
       </c>
       <c r="E175" t="n">
-        <v>311.2976379394531</v>
+        <v>307.7536010742188</v>
       </c>
       <c r="F175" t="n">
-        <v>11594600</v>
+        <v>7446200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B176" t="n">
-        <v>311.1582462393224</v>
+        <v>308.1717081621576</v>
       </c>
       <c r="C176" t="n">
-        <v>313.3384270822022</v>
+        <v>313.3085706612414</v>
       </c>
       <c r="D176" t="n">
-        <v>307.6440785979976</v>
+        <v>307.4947650619962</v>
       </c>
       <c r="E176" t="n">
-        <v>307.7536010742188</v>
+        <v>312.0840759277344</v>
       </c>
       <c r="F176" t="n">
-        <v>7446200</v>
+        <v>9116600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B177" t="n">
-        <v>308.1717081621576</v>
+        <v>314.5529794375797</v>
       </c>
       <c r="C177" t="n">
-        <v>313.3085706612414</v>
+        <v>319.8590627688811</v>
       </c>
       <c r="D177" t="n">
-        <v>307.4947650619962</v>
+        <v>314.1348496322589</v>
       </c>
       <c r="E177" t="n">
-        <v>312.0840759277344</v>
+        <v>319.2816772460938</v>
       </c>
       <c r="F177" t="n">
-        <v>9116600</v>
+        <v>7426200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B178" t="n">
-        <v>314.5529794375797</v>
+        <v>322.4673390673774</v>
       </c>
       <c r="C178" t="n">
-        <v>319.8590627688811</v>
+        <v>324.4583697274161</v>
       </c>
       <c r="D178" t="n">
-        <v>314.1348496322589</v>
+        <v>317.4101041776777</v>
       </c>
       <c r="E178" t="n">
-        <v>319.2816772460938</v>
+        <v>317.9675903320312</v>
       </c>
       <c r="F178" t="n">
-        <v>7426200</v>
+        <v>7988900</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B179" t="n">
-        <v>322.4673390673774</v>
+        <v>322.8455866314347</v>
       </c>
       <c r="C179" t="n">
-        <v>324.4583697274161</v>
+        <v>330.2621874699331</v>
       </c>
       <c r="D179" t="n">
-        <v>317.4101041776777</v>
+        <v>322.5668435738929</v>
       </c>
       <c r="E179" t="n">
-        <v>317.9675903320312</v>
+        <v>329.6549377441406</v>
       </c>
       <c r="F179" t="n">
-        <v>7988900</v>
+        <v>11094900</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B180" t="n">
-        <v>322.8455866314347</v>
+        <v>330.6902497468859</v>
       </c>
       <c r="C180" t="n">
-        <v>330.2621874699331</v>
+        <v>336.2551763704633</v>
       </c>
       <c r="D180" t="n">
-        <v>322.5668435738929</v>
+        <v>330.0133066656099</v>
       </c>
       <c r="E180" t="n">
-        <v>329.6549377441406</v>
+        <v>331.9645080566406</v>
       </c>
       <c r="F180" t="n">
-        <v>11094900</v>
+        <v>12246400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B181" t="n">
-        <v>330.6902497468859</v>
+        <v>335.4388795655989</v>
       </c>
       <c r="C181" t="n">
-        <v>336.2551763704633</v>
+        <v>336.5737511659094</v>
       </c>
       <c r="D181" t="n">
-        <v>330.0133066656099</v>
+        <v>322.7062308624821</v>
       </c>
       <c r="E181" t="n">
-        <v>331.9645080566406</v>
+        <v>323.761474609375</v>
       </c>
       <c r="F181" t="n">
-        <v>12246400</v>
+        <v>20111000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B182" t="n">
-        <v>335.4388795655989</v>
+        <v>328.221392261561</v>
       </c>
       <c r="C182" t="n">
-        <v>336.5737511659094</v>
+        <v>331.2776010100568</v>
       </c>
       <c r="D182" t="n">
-        <v>322.7062308624821</v>
+        <v>325.2846101022313</v>
       </c>
       <c r="E182" t="n">
-        <v>323.761474609375</v>
+        <v>329.993408203125</v>
       </c>
       <c r="F182" t="n">
-        <v>20111000</v>
+        <v>10182500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B183" t="n">
-        <v>328.221392261561</v>
+        <v>327.9924099173137</v>
       </c>
       <c r="C183" t="n">
-        <v>331.2776010100568</v>
+        <v>333.8659438033595</v>
       </c>
       <c r="D183" t="n">
-        <v>325.2846101022313</v>
+        <v>325.7425357353925</v>
       </c>
       <c r="E183" t="n">
-        <v>329.993408203125</v>
+        <v>332.6414794921875</v>
       </c>
       <c r="F183" t="n">
-        <v>10182500</v>
+        <v>7582200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B184" t="n">
-        <v>327.9924099173137</v>
+        <v>331.5762891678024</v>
       </c>
       <c r="C184" t="n">
-        <v>333.8659438033595</v>
+        <v>333.0297330031709</v>
       </c>
       <c r="D184" t="n">
-        <v>325.7425357353925</v>
+        <v>328.291070440402</v>
       </c>
       <c r="E184" t="n">
-        <v>332.6414794921875</v>
+        <v>331.95458984375</v>
       </c>
       <c r="F184" t="n">
-        <v>7582200</v>
+        <v>7907400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B185" t="n">
-        <v>331.5762891678024</v>
+        <v>333.4577793441399</v>
       </c>
       <c r="C185" t="n">
-        <v>333.0297330031709</v>
+        <v>341.909724468194</v>
       </c>
       <c r="D185" t="n">
-        <v>328.291070440402</v>
+        <v>333.2586945227413</v>
       </c>
       <c r="E185" t="n">
-        <v>331.95458984375</v>
+        <v>333.6170654296875</v>
       </c>
       <c r="F185" t="n">
-        <v>7907400</v>
+        <v>10043100</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B186" t="n">
-        <v>333.4577793441399</v>
+        <v>334.4931229022353</v>
       </c>
       <c r="C186" t="n">
-        <v>341.909724468194</v>
+        <v>334.8913229247855</v>
       </c>
       <c r="D186" t="n">
-        <v>333.2586945227413</v>
+        <v>326.0312433050061</v>
       </c>
       <c r="E186" t="n">
-        <v>333.6170654296875</v>
+        <v>327.5742797851562</v>
       </c>
       <c r="F186" t="n">
-        <v>10043100</v>
+        <v>17640900</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B187" t="n">
-        <v>334.4931229022353</v>
+        <v>326.8077430430495</v>
       </c>
       <c r="C187" t="n">
-        <v>334.8913229247855</v>
+        <v>330.8993264933345</v>
       </c>
       <c r="D187" t="n">
-        <v>326.0312433050061</v>
+        <v>325.7325999471821</v>
       </c>
       <c r="E187" t="n">
-        <v>327.5742797851562</v>
+        <v>327.9127807617188</v>
       </c>
       <c r="F187" t="n">
-        <v>17640900</v>
+        <v>7981800</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B188" t="n">
-        <v>326.8077430430495</v>
+        <v>327.4150312810326</v>
       </c>
       <c r="C188" t="n">
-        <v>330.8993264933345</v>
+        <v>328.9580677951163</v>
       </c>
       <c r="D188" t="n">
-        <v>325.7325999471821</v>
+        <v>325.2149206632551</v>
       </c>
       <c r="E188" t="n">
-        <v>327.9127807617188</v>
+        <v>325.8619995117188</v>
       </c>
       <c r="F188" t="n">
-        <v>7981800</v>
+        <v>8080100</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B189" t="n">
-        <v>327.4150312810326</v>
+        <v>326.8973584256916</v>
       </c>
       <c r="C189" t="n">
-        <v>328.9580677951163</v>
+        <v>334.1347741939035</v>
       </c>
       <c r="D189" t="n">
-        <v>325.2149206632551</v>
+        <v>323.5524415571975</v>
       </c>
       <c r="E189" t="n">
-        <v>325.8619995117188</v>
+        <v>332.5718078613281</v>
       </c>
       <c r="F189" t="n">
-        <v>8080100</v>
+        <v>15210200</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B190" t="n">
-        <v>326.8973584256916</v>
+        <v>336.5040683580973</v>
       </c>
       <c r="C190" t="n">
-        <v>334.1347741939035</v>
+        <v>338.4751995750331</v>
       </c>
       <c r="D190" t="n">
-        <v>323.5524415571975</v>
+        <v>330.2820977776739</v>
       </c>
       <c r="E190" t="n">
-        <v>332.5718078613281</v>
+        <v>332.9700012207031</v>
       </c>
       <c r="F190" t="n">
-        <v>15210200</v>
+        <v>8413900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,25 +5383,25 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B191" t="n">
-        <v>336.5040683580973</v>
+        <v>335</v>
       </c>
       <c r="C191" t="n">
-        <v>338.4751995750331</v>
+        <v>339.7200012207031</v>
       </c>
       <c r="D191" t="n">
-        <v>330.2820977776739</v>
+        <v>334.1099853515625</v>
       </c>
       <c r="E191" t="n">
-        <v>332.9700012207031</v>
+        <v>337.7200012207031</v>
       </c>
       <c r="F191" t="n">
-        <v>8413900</v>
+        <v>8673500</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5409,25 +5409,25 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B192" t="n">
-        <v>335</v>
+        <v>340.9800109863281</v>
       </c>
       <c r="C192" t="n">
-        <v>339.7200012207031</v>
+        <v>341.3999938964844</v>
       </c>
       <c r="D192" t="n">
-        <v>334.1099853515625</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E192" t="n">
-        <v>337.7200012207031</v>
+        <v>339.2200012207031</v>
       </c>
       <c r="F192" t="n">
-        <v>8673500</v>
+        <v>7115800</v>
       </c>
       <c r="G192" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B193" t="n">
-        <v>340.9800109863281</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="C193" t="n">
-        <v>341.3999938964844</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="D193" t="n">
-        <v>337.0899963378906</v>
+        <v>330.1300048828125</v>
       </c>
       <c r="E193" t="n">
-        <v>339.2200012207031</v>
+        <v>330.6199951171875</v>
       </c>
       <c r="F193" t="n">
-        <v>7115800</v>
+        <v>18505200</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B194" t="n">
-        <v>336.5299987792969</v>
+        <v>331.4599914550781</v>
       </c>
       <c r="C194" t="n">
-        <v>336.5299987792969</v>
+        <v>337</v>
       </c>
       <c r="D194" t="n">
-        <v>330.1300048828125</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="E194" t="n">
-        <v>330.6199951171875</v>
+        <v>335.4700012207031</v>
       </c>
       <c r="F194" t="n">
-        <v>18505200</v>
+        <v>15570600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B195" t="n">
-        <v>331.4599914550781</v>
+        <v>337.4700012207031</v>
       </c>
       <c r="C195" t="n">
-        <v>337</v>
+        <v>338.5899963378906</v>
       </c>
       <c r="D195" t="n">
-        <v>330.8099975585938</v>
+        <v>335.7699890136719</v>
       </c>
       <c r="E195" t="n">
-        <v>335.4700012207031</v>
+        <v>336.4700012207031</v>
       </c>
       <c r="F195" t="n">
-        <v>15570600</v>
+        <v>6299000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B196" t="n">
-        <v>337.4700012207031</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="C196" t="n">
-        <v>338.5899963378906</v>
+        <v>338.3500061035156</v>
       </c>
       <c r="D196" t="n">
-        <v>335.7699890136719</v>
+        <v>332.5</v>
       </c>
       <c r="E196" t="n">
-        <v>336.4700012207031</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="F196" t="n">
-        <v>6299000</v>
+        <v>7120300</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B197" t="n">
-        <v>338.3399963378906</v>
+        <v>327</v>
       </c>
       <c r="C197" t="n">
-        <v>338.3500061035156</v>
+        <v>344.7300109863281</v>
       </c>
       <c r="D197" t="n">
-        <v>332.5</v>
+        <v>325.75</v>
       </c>
       <c r="E197" t="n">
-        <v>334.5299987792969</v>
+        <v>342.8900146484375</v>
       </c>
       <c r="F197" t="n">
-        <v>7120300</v>
+        <v>14537900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>327</v>
+        <v>345.8500061035156</v>
       </c>
       <c r="C198" t="n">
-        <v>344.7300109863281</v>
+        <v>351.239990234375</v>
       </c>
       <c r="D198" t="n">
-        <v>325.75</v>
+        <v>344.0499877929688</v>
       </c>
       <c r="E198" t="n">
-        <v>342.8900146484375</v>
+        <v>346.9100036621094</v>
       </c>
       <c r="F198" t="n">
-        <v>14537900</v>
+        <v>10750000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B199" t="n">
-        <v>345.8500061035156</v>
+        <v>349.2799987792969</v>
       </c>
       <c r="C199" t="n">
-        <v>351.239990234375</v>
+        <v>349.3399963378906</v>
       </c>
       <c r="D199" t="n">
-        <v>344.0499877929688</v>
+        <v>341.1099853515625</v>
       </c>
       <c r="E199" t="n">
-        <v>346.9100036621094</v>
+        <v>343.1499938964844</v>
       </c>
       <c r="F199" t="n">
-        <v>10750000</v>
+        <v>12432400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B200" t="n">
-        <v>349.2799987792969</v>
+        <v>339.0299987792969</v>
       </c>
       <c r="C200" t="n">
-        <v>349.3399963378906</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="D200" t="n">
-        <v>341.1099853515625</v>
+        <v>335.0499877929688</v>
       </c>
       <c r="E200" t="n">
-        <v>343.1499938964844</v>
+        <v>341.1000061035156</v>
       </c>
       <c r="F200" t="n">
-        <v>12432400</v>
+        <v>9250900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B201" t="n">
-        <v>339.0299987792969</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="C201" t="n">
-        <v>346.1300048828125</v>
+        <v>344.260009765625</v>
       </c>
       <c r="D201" t="n">
-        <v>335.0499877929688</v>
+        <v>337.3699951171875</v>
       </c>
       <c r="E201" t="n">
-        <v>341.1000061035156</v>
+        <v>338.8699951171875</v>
       </c>
       <c r="F201" t="n">
-        <v>9250900</v>
+        <v>7723300</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B202" t="n">
-        <v>341.7999877929688</v>
+        <v>340.1199951171875</v>
       </c>
       <c r="C202" t="n">
-        <v>344.260009765625</v>
+        <v>345.739990234375</v>
       </c>
       <c r="D202" t="n">
-        <v>337.3699951171875</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E202" t="n">
-        <v>338.8699951171875</v>
+        <v>345.2300109863281</v>
       </c>
       <c r="F202" t="n">
-        <v>7723300</v>
+        <v>6015300</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B203" t="n">
-        <v>340.1199951171875</v>
+        <v>345.0700073242188</v>
       </c>
       <c r="C203" t="n">
-        <v>345.739990234375</v>
+        <v>349.0700073242188</v>
       </c>
       <c r="D203" t="n">
-        <v>337.2999877929688</v>
+        <v>344.25</v>
       </c>
       <c r="E203" t="n">
-        <v>345.2300109863281</v>
+        <v>348.2099914550781</v>
       </c>
       <c r="F203" t="n">
-        <v>6015300</v>
+        <v>8040200</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B204" t="n">
-        <v>345.0700073242188</v>
+        <v>346.5799865722656</v>
       </c>
       <c r="C204" t="n">
-        <v>349.0700073242188</v>
+        <v>349.9200134277344</v>
       </c>
       <c r="D204" t="n">
-        <v>344.25</v>
+        <v>345.4200134277344</v>
       </c>
       <c r="E204" t="n">
-        <v>348.2099914550781</v>
+        <v>349.8999938964844</v>
       </c>
       <c r="F204" t="n">
-        <v>8040200</v>
+        <v>10913000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B205" t="n">
-        <v>346.5799865722656</v>
+        <v>350.6400146484375</v>
       </c>
       <c r="C205" t="n">
-        <v>349.9200134277344</v>
+        <v>353.3699951171875</v>
       </c>
       <c r="D205" t="n">
-        <v>345.4200134277344</v>
+        <v>347.5</v>
       </c>
       <c r="E205" t="n">
-        <v>349.8999938964844</v>
+        <v>353.2099914550781</v>
       </c>
       <c r="F205" t="n">
-        <v>10913000</v>
+        <v>7520800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B206" t="n">
-        <v>350.6400146484375</v>
+        <v>357.8900146484375</v>
       </c>
       <c r="C206" t="n">
-        <v>353.3699951171875</v>
+        <v>359.0499877929688</v>
       </c>
       <c r="D206" t="n">
-        <v>347.5</v>
+        <v>352.5799865722656</v>
       </c>
       <c r="E206" t="n">
-        <v>353.2099914550781</v>
+        <v>356.2000122070312</v>
       </c>
       <c r="F206" t="n">
-        <v>7520800</v>
+        <v>7884900</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B207" t="n">
-        <v>357.8900146484375</v>
+        <v>357.2999877929688</v>
       </c>
       <c r="C207" t="n">
-        <v>359.0499877929688</v>
+        <v>359.2999877929688</v>
       </c>
       <c r="D207" t="n">
-        <v>352.5799865722656</v>
+        <v>354.1499938964844</v>
       </c>
       <c r="E207" t="n">
-        <v>356.2000122070312</v>
+        <v>357.3099975585938</v>
       </c>
       <c r="F207" t="n">
-        <v>7884900</v>
+        <v>6533800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B208" t="n">
-        <v>357.2999877929688</v>
+        <v>356.5</v>
       </c>
       <c r="C208" t="n">
-        <v>359.2999877929688</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D208" t="n">
-        <v>354.1499938964844</v>
+        <v>343.7799987792969</v>
       </c>
       <c r="E208" t="n">
-        <v>357.3099975585938</v>
+        <v>344.7099914550781</v>
       </c>
       <c r="F208" t="n">
-        <v>6533800</v>
+        <v>8265300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B209" t="n">
-        <v>356.5</v>
+        <v>347.5400085449219</v>
       </c>
       <c r="C209" t="n">
-        <v>357.3699951171875</v>
+        <v>352.2799987792969</v>
       </c>
       <c r="D209" t="n">
-        <v>343.7799987792969</v>
+        <v>345.3699951171875</v>
       </c>
       <c r="E209" t="n">
-        <v>344.7099914550781</v>
+        <v>350.8500061035156</v>
       </c>
       <c r="F209" t="n">
-        <v>8265300</v>
+        <v>7606500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B210" t="n">
-        <v>347.5400085449219</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C210" t="n">
-        <v>352.2799987792969</v>
+        <v>354.4700012207031</v>
       </c>
       <c r="D210" t="n">
-        <v>345.3699951171875</v>
+        <v>349.7000122070312</v>
       </c>
       <c r="E210" t="n">
-        <v>350.8500061035156</v>
+        <v>351.7900085449219</v>
       </c>
       <c r="F210" t="n">
-        <v>7606500</v>
+        <v>6603400</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B211" t="n">
-        <v>353.2999877929688</v>
+        <v>353.75</v>
       </c>
       <c r="C211" t="n">
-        <v>354.4700012207031</v>
+        <v>355.6199951171875</v>
       </c>
       <c r="D211" t="n">
-        <v>349.7000122070312</v>
+        <v>350.8399963378906</v>
       </c>
       <c r="E211" t="n">
-        <v>351.7900085449219</v>
+        <v>352.6400146484375</v>
       </c>
       <c r="F211" t="n">
-        <v>6603400</v>
+        <v>6436600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B212" t="n">
-        <v>353.75</v>
+        <v>355</v>
       </c>
       <c r="C212" t="n">
-        <v>355.6199951171875</v>
+        <v>363</v>
       </c>
       <c r="D212" t="n">
-        <v>350.8399963378906</v>
+        <v>353.8699951171875</v>
       </c>
       <c r="E212" t="n">
-        <v>352.6400146484375</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F212" t="n">
-        <v>6436600</v>
+        <v>8477200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B213" t="n">
-        <v>355</v>
+        <v>358.9700012207031</v>
       </c>
       <c r="C213" t="n">
-        <v>363</v>
+        <v>362.1700134277344</v>
       </c>
       <c r="D213" t="n">
-        <v>353.8699951171875</v>
+        <v>358.2000122070312</v>
       </c>
       <c r="E213" t="n">
-        <v>357.5199890136719</v>
+        <v>359.239990234375</v>
       </c>
       <c r="F213" t="n">
-        <v>8477200</v>
+        <v>5269500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B214" t="n">
-        <v>358.9700012207031</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="C214" t="n">
-        <v>362.1700134277344</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="D214" t="n">
-        <v>358.2000122070312</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="E214" t="n">
-        <v>359.239990234375</v>
+        <v>356.2999877929688</v>
       </c>
       <c r="F214" t="n">
-        <v>5269500</v>
+        <v>5820100</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B215" t="n">
-        <v>362.8099975585938</v>
+        <v>355.760009765625</v>
       </c>
       <c r="C215" t="n">
-        <v>362.8099975585938</v>
+        <v>358.8500061035156</v>
       </c>
       <c r="D215" t="n">
-        <v>354.9500122070312</v>
+        <v>353.3299865722656</v>
       </c>
       <c r="E215" t="n">
-        <v>356.2999877929688</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F215" t="n">
-        <v>5820100</v>
+        <v>4566200</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B216" t="n">
-        <v>355.760009765625</v>
+        <v>357.9599914550781</v>
       </c>
       <c r="C216" t="n">
-        <v>358.8500061035156</v>
+        <v>359.989990234375</v>
       </c>
       <c r="D216" t="n">
-        <v>353.3299865722656</v>
+        <v>356.5</v>
       </c>
       <c r="E216" t="n">
-        <v>357.5199890136719</v>
+        <v>359.7900085449219</v>
       </c>
       <c r="F216" t="n">
-        <v>4566200</v>
+        <v>5327500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B217" t="n">
-        <v>357.9599914550781</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="C217" t="n">
-        <v>359.989990234375</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="D217" t="n">
-        <v>356.5</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="E217" t="n">
-        <v>359.7900085449219</v>
+        <v>362.0400085449219</v>
       </c>
       <c r="F217" t="n">
-        <v>5327500</v>
+        <v>4576500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B218" t="n">
-        <v>360.0499877929688</v>
+        <v>362.9700012207031</v>
       </c>
       <c r="C218" t="n">
-        <v>363.1199951171875</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="D218" t="n">
-        <v>358.6000061035156</v>
+        <v>361.2999877929688</v>
       </c>
       <c r="E218" t="n">
-        <v>362.0400085449219</v>
+        <v>365.1799926757812</v>
       </c>
       <c r="F218" t="n">
-        <v>4576500</v>
+        <v>4366800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B219" t="n">
-        <v>362.9700012207031</v>
+        <v>366.5</v>
       </c>
       <c r="C219" t="n">
-        <v>366.0899963378906</v>
+        <v>366.5</v>
       </c>
       <c r="D219" t="n">
-        <v>361.2999877929688</v>
+        <v>361.5199890136719</v>
       </c>
       <c r="E219" t="n">
-        <v>365.1799926757812</v>
+        <v>363.1099853515625</v>
       </c>
       <c r="F219" t="n">
-        <v>4366800</v>
+        <v>5102700</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B220" t="n">
-        <v>366.5</v>
+        <v>363</v>
       </c>
       <c r="C220" t="n">
-        <v>366.5</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="D220" t="n">
-        <v>361.5199890136719</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="E220" t="n">
-        <v>363.1099853515625</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="F220" t="n">
-        <v>5102700</v>
+        <v>5058600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B221" t="n">
-        <v>363</v>
+        <v>361.9400024414062</v>
       </c>
       <c r="C221" t="n">
-        <v>365.8999938964844</v>
+        <v>365.75</v>
       </c>
       <c r="D221" t="n">
-        <v>361.4500122070312</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="E221" t="n">
-        <v>362.8399963378906</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="F221" t="n">
-        <v>5058600</v>
+        <v>5282600</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B222" t="n">
-        <v>361.9400024414062</v>
+        <v>362.3399963378906</v>
       </c>
       <c r="C222" t="n">
-        <v>365.75</v>
+        <v>363.5700073242188</v>
       </c>
       <c r="D222" t="n">
-        <v>360.9599914550781</v>
+        <v>359.2699890136719</v>
       </c>
       <c r="E222" t="n">
-        <v>360.9599914550781</v>
+        <v>363.25</v>
       </c>
       <c r="F222" t="n">
-        <v>5282600</v>
+        <v>5525100</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B223" t="n">
-        <v>362.3399963378906</v>
+        <v>363.010009765625</v>
       </c>
       <c r="C223" t="n">
-        <v>363.5700073242188</v>
+        <v>363.0499877929688</v>
       </c>
       <c r="D223" t="n">
-        <v>359.2699890136719</v>
+        <v>355.6499938964844</v>
       </c>
       <c r="E223" t="n">
-        <v>363.25</v>
+        <v>357.260009765625</v>
       </c>
       <c r="F223" t="n">
-        <v>5525100</v>
+        <v>6696200</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B224" t="n">
-        <v>363.010009765625</v>
+        <v>357.6000061035156</v>
       </c>
       <c r="C224" t="n">
-        <v>363.0499877929688</v>
+        <v>357.9500122070312</v>
       </c>
       <c r="D224" t="n">
-        <v>355.6499938964844</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E224" t="n">
-        <v>357.260009765625</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="F224" t="n">
-        <v>6696200</v>
+        <v>6799700</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B225" t="n">
-        <v>357.6000061035156</v>
+        <v>354.0700073242188</v>
       </c>
       <c r="C225" t="n">
-        <v>357.9500122070312</v>
+        <v>356.8599853515625</v>
       </c>
       <c r="D225" t="n">
-        <v>351.5499877929688</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="E225" t="n">
-        <v>351.5499877929688</v>
+        <v>351.5799865722656</v>
       </c>
       <c r="F225" t="n">
-        <v>6799700</v>
+        <v>8112100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B226" t="n">
-        <v>354.0700073242188</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C226" t="n">
-        <v>356.8599853515625</v>
+        <v>358.2799987792969</v>
       </c>
       <c r="D226" t="n">
-        <v>350.3699951171875</v>
+        <v>352.8200073242188</v>
       </c>
       <c r="E226" t="n">
-        <v>351.5799865722656</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="F226" t="n">
-        <v>8112100</v>
+        <v>4394400</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B227" t="n">
-        <v>353.2999877929688</v>
+        <v>357</v>
       </c>
       <c r="C227" t="n">
-        <v>358.2799987792969</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D227" t="n">
-        <v>352.8200073242188</v>
+        <v>353.0700073242188</v>
       </c>
       <c r="E227" t="n">
-        <v>356.3900146484375</v>
+        <v>356.6900024414062</v>
       </c>
       <c r="F227" t="n">
-        <v>4394400</v>
+        <v>4298000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B228" t="n">
-        <v>357</v>
+        <v>356.5</v>
       </c>
       <c r="C228" t="n">
-        <v>357.3699951171875</v>
+        <v>358.3500061035156</v>
       </c>
       <c r="D228" t="n">
-        <v>353.0700073242188</v>
+        <v>354.6000061035156</v>
       </c>
       <c r="E228" t="n">
-        <v>356.6900024414062</v>
+        <v>356.5</v>
       </c>
       <c r="F228" t="n">
-        <v>4298000</v>
+        <v>5796500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B229" t="n">
-        <v>356.5</v>
+        <v>354.6799926757812</v>
       </c>
       <c r="C229" t="n">
-        <v>358.3500061035156</v>
+        <v>357.5700073242188</v>
       </c>
       <c r="D229" t="n">
-        <v>354.6000061035156</v>
+        <v>352.2300109863281</v>
       </c>
       <c r="E229" t="n">
-        <v>356.5</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="F229" t="n">
-        <v>5796500</v>
+        <v>5209900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B230" t="n">
-        <v>354.6799926757812</v>
+        <v>355.6700134277344</v>
       </c>
       <c r="C230" t="n">
-        <v>357.5700073242188</v>
+        <v>358.7300109863281</v>
       </c>
       <c r="D230" t="n">
-        <v>352.2300109863281</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="E230" t="n">
-        <v>354.2200012207031</v>
+        <v>357.6199951171875</v>
       </c>
       <c r="F230" t="n">
-        <v>5209900</v>
+        <v>3914500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B231" t="n">
-        <v>355.6700134277344</v>
+        <v>355.8999938964844</v>
       </c>
       <c r="C231" t="n">
-        <v>358.7300109863281</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="D231" t="n">
-        <v>354.2200012207031</v>
+        <v>354.7699890136719</v>
       </c>
       <c r="E231" t="n">
-        <v>357.6199951171875</v>
+        <v>356.0199890136719</v>
       </c>
       <c r="F231" t="n">
-        <v>3914500</v>
+        <v>7962900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B232" t="n">
-        <v>355.8999938964844</v>
+        <v>355.7300109863281</v>
       </c>
       <c r="C232" t="n">
-        <v>357.7699890136719</v>
+        <v>359.9299926757812</v>
       </c>
       <c r="D232" t="n">
-        <v>354.7699890136719</v>
+        <v>354.1199951171875</v>
       </c>
       <c r="E232" t="n">
-        <v>356.0199890136719</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="F232" t="n">
-        <v>7962900</v>
+        <v>5079000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B233" t="n">
-        <v>355.7300109863281</v>
+        <v>357.5499877929688</v>
       </c>
       <c r="C233" t="n">
-        <v>359.9299926757812</v>
+        <v>361.4700012207031</v>
       </c>
       <c r="D233" t="n">
-        <v>354.1199951171875</v>
+        <v>353.7900085449219</v>
       </c>
       <c r="E233" t="n">
-        <v>354.9500122070312</v>
+        <v>356.2200012207031</v>
       </c>
       <c r="F233" t="n">
-        <v>5079000</v>
+        <v>5341400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B234" t="n">
-        <v>357.5499877929688</v>
+        <v>358.6799926757812</v>
       </c>
       <c r="C234" t="n">
-        <v>361.4700012207031</v>
+        <v>362.8500061035156</v>
       </c>
       <c r="D234" t="n">
-        <v>353.7900085449219</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="E234" t="n">
-        <v>356.2200012207031</v>
+        <v>362.0599975585938</v>
       </c>
       <c r="F234" t="n">
-        <v>5341400</v>
+        <v>5414200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B235" t="n">
-        <v>358.6799926757812</v>
+        <v>361</v>
       </c>
       <c r="C235" t="n">
-        <v>362.8500061035156</v>
+        <v>362.8599853515625</v>
       </c>
       <c r="D235" t="n">
-        <v>356.3900146484375</v>
+        <v>355.2000122070312</v>
       </c>
       <c r="E235" t="n">
-        <v>362.0599975585938</v>
+        <v>358.6400146484375</v>
       </c>
       <c r="F235" t="n">
-        <v>5414200</v>
+        <v>4873500</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B236" t="n">
-        <v>361</v>
+        <v>357.1000061035156</v>
       </c>
       <c r="C236" t="n">
-        <v>362.8599853515625</v>
+        <v>358.5499877929688</v>
       </c>
       <c r="D236" t="n">
-        <v>355.2000122070312</v>
+        <v>353.2300109863281</v>
       </c>
       <c r="E236" t="n">
-        <v>358.6400146484375</v>
+        <v>353.510009765625</v>
       </c>
       <c r="F236" t="n">
-        <v>4873500</v>
+        <v>5631400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B237" t="n">
-        <v>357.1000061035156</v>
+        <v>352</v>
       </c>
       <c r="C237" t="n">
-        <v>358.5499877929688</v>
+        <v>356.3299865722656</v>
       </c>
       <c r="D237" t="n">
-        <v>353.2300109863281</v>
+        <v>348.6900024414062</v>
       </c>
       <c r="E237" t="n">
-        <v>353.510009765625</v>
+        <v>354.7099914550781</v>
       </c>
       <c r="F237" t="n">
-        <v>5631400</v>
+        <v>6318200</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B238" t="n">
-        <v>352</v>
+        <v>353.510009765625</v>
       </c>
       <c r="C238" t="n">
-        <v>356.3299865722656</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="D238" t="n">
-        <v>348.6900024414062</v>
+        <v>351.1199951171875</v>
       </c>
       <c r="E238" t="n">
-        <v>354.7099914550781</v>
+        <v>353.5599975585938</v>
       </c>
       <c r="F238" t="n">
-        <v>6318200</v>
+        <v>4184200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B239" t="n">
-        <v>353.510009765625</v>
+        <v>358.3200073242188</v>
       </c>
       <c r="C239" t="n">
-        <v>354.2200012207031</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="D239" t="n">
-        <v>351.1199951171875</v>
+        <v>354.7900085449219</v>
       </c>
       <c r="E239" t="n">
-        <v>353.5599975585938</v>
+        <v>356.2300109863281</v>
       </c>
       <c r="F239" t="n">
-        <v>4184200</v>
+        <v>5354600</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B240" t="n">
-        <v>358.3200073242188</v>
+        <v>354.2300109863281</v>
       </c>
       <c r="C240" t="n">
-        <v>360.0499877929688</v>
+        <v>355.2799987792969</v>
       </c>
       <c r="D240" t="n">
-        <v>354.7900085449219</v>
+        <v>347.5499877929688</v>
       </c>
       <c r="E240" t="n">
-        <v>356.2300109863281</v>
+        <v>350.1300048828125</v>
       </c>
       <c r="F240" t="n">
-        <v>5354600</v>
+        <v>9609900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B241" t="n">
-        <v>354.2300109863281</v>
+        <v>351</v>
       </c>
       <c r="C241" t="n">
-        <v>355.2799987792969</v>
+        <v>354.7000122070312</v>
       </c>
       <c r="D241" t="n">
-        <v>347.5499877929688</v>
+        <v>343.0700073242188</v>
       </c>
       <c r="E241" t="n">
-        <v>350.1300048828125</v>
+        <v>352.489990234375</v>
       </c>
       <c r="F241" t="n">
-        <v>9609900</v>
+        <v>14026500</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B242" t="n">
-        <v>351</v>
+        <v>353.3800048828125</v>
       </c>
       <c r="C242" t="n">
-        <v>354.7000122070312</v>
+        <v>355.6000061035156</v>
       </c>
       <c r="D242" t="n">
-        <v>343.0700073242188</v>
+        <v>344.6900024414062</v>
       </c>
       <c r="E242" t="n">
-        <v>352.489990234375</v>
+        <v>348.9200134277344</v>
       </c>
       <c r="F242" t="n">
-        <v>14026500</v>
+        <v>8303400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B243" t="n">
-        <v>353.3800048828125</v>
+        <v>352.25</v>
       </c>
       <c r="C243" t="n">
-        <v>355.6000061035156</v>
+        <v>353.489990234375</v>
       </c>
       <c r="D243" t="n">
-        <v>344.6900024414062</v>
+        <v>345.2699890136719</v>
       </c>
       <c r="E243" t="n">
-        <v>348.9200134277344</v>
+        <v>349.3099975585938</v>
       </c>
       <c r="F243" t="n">
-        <v>8303400</v>
+        <v>6480100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B244" t="n">
-        <v>352.25</v>
+        <v>347.8900146484375</v>
       </c>
       <c r="C244" t="n">
-        <v>353.489990234375</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="D244" t="n">
-        <v>345.2699890136719</v>
+        <v>345.010009765625</v>
       </c>
       <c r="E244" t="n">
-        <v>349.3099975585938</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="F244" t="n">
-        <v>6480100</v>
+        <v>18312400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B245" t="n">
-        <v>347.8900146484375</v>
+        <v>353.6700134277344</v>
       </c>
       <c r="C245" t="n">
-        <v>349.6700134277344</v>
+        <v>354.5</v>
       </c>
       <c r="D245" t="n">
-        <v>345.010009765625</v>
+        <v>350.0799865722656</v>
       </c>
       <c r="E245" t="n">
-        <v>349.6700134277344</v>
+        <v>352.0400085449219</v>
       </c>
       <c r="F245" t="n">
-        <v>18312400</v>
+        <v>6414700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B246" t="n">
-        <v>353.6700134277344</v>
+        <v>352</v>
       </c>
       <c r="C246" t="n">
-        <v>354.5</v>
+        <v>352.1000061035156</v>
       </c>
       <c r="D246" t="n">
-        <v>350.0799865722656</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E246" t="n">
-        <v>352.0400085449219</v>
+        <v>340</v>
       </c>
       <c r="F246" t="n">
-        <v>6414700</v>
+        <v>11485600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B247" t="n">
-        <v>352</v>
+        <v>337.6099853515625</v>
       </c>
       <c r="C247" t="n">
-        <v>352.1000061035156</v>
+        <v>341.4400024414062</v>
       </c>
       <c r="D247" t="n">
-        <v>337.2999877929688</v>
+        <v>336.9800109863281</v>
       </c>
       <c r="E247" t="n">
-        <v>340</v>
+        <v>337.5299987792969</v>
       </c>
       <c r="F247" t="n">
-        <v>11485600</v>
+        <v>7068500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B248" t="n">
-        <v>337.6099853515625</v>
+        <v>338.1199951171875</v>
       </c>
       <c r="C248" t="n">
-        <v>341.4400024414062</v>
+        <v>339.3699951171875</v>
       </c>
       <c r="D248" t="n">
-        <v>336.9800109863281</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="E248" t="n">
-        <v>337.5299987792969</v>
+        <v>338.5599975585938</v>
       </c>
       <c r="F248" t="n">
-        <v>7068500</v>
+        <v>6934300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B249" t="n">
-        <v>338.1199951171875</v>
+        <v>340.7699890136719</v>
       </c>
       <c r="C249" t="n">
-        <v>339.3699951171875</v>
+        <v>343.3099975585938</v>
       </c>
       <c r="D249" t="n">
-        <v>335.2799987792969</v>
+        <v>338.6400146484375</v>
       </c>
       <c r="E249" t="n">
-        <v>338.5599975585938</v>
+        <v>343.0599975585938</v>
       </c>
       <c r="F249" t="n">
-        <v>6934300</v>
+        <v>11460300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B250" t="n">
-        <v>340.7699890136719</v>
+        <v>341.8299865722656</v>
       </c>
       <c r="C250" t="n">
-        <v>343.3099975585938</v>
+        <v>342</v>
       </c>
       <c r="D250" t="n">
-        <v>338.6400146484375</v>
+        <v>336.2999877929688</v>
       </c>
       <c r="E250" t="n">
-        <v>343.0599975585938</v>
+        <v>336.5899963378906</v>
       </c>
       <c r="F250" t="n">
-        <v>11460300</v>
+        <v>10483700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B251" t="n">
-        <v>341.8299865722656</v>
+        <v>337</v>
       </c>
       <c r="C251" t="n">
-        <v>342</v>
+        <v>338.75</v>
       </c>
       <c r="D251" t="n">
-        <v>336.2999877929688</v>
+        <v>333.3299865722656</v>
       </c>
       <c r="E251" t="n">
-        <v>336.5899963378906</v>
+        <v>334.9800109863281</v>
       </c>
       <c r="F251" t="n">
-        <v>10483700</v>
+        <v>7254900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B252" t="n">
-        <v>337</v>
+        <v>334.8900146484375</v>
       </c>
       <c r="C252" t="n">
-        <v>338.75</v>
+        <v>336.3399963378906</v>
       </c>
       <c r="D252" t="n">
-        <v>333.3299865722656</v>
+        <v>330.8299865722656</v>
       </c>
       <c r="E252" t="n">
-        <v>334.9800109863281</v>
+        <v>330.8299865722656</v>
       </c>
       <c r="F252" t="n">
-        <v>7254900</v>
+        <v>9113300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10017,37 +10017,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>330.83</v>
+      </c>
+      <c r="D2" t="n">
         <v>334.98</v>
       </c>
-      <c r="D2" t="n">
-        <v>336.59</v>
-      </c>
       <c r="E2" t="n">
-        <v>337</v>
+        <v>334.89</v>
       </c>
       <c r="F2" t="n">
-        <v>338.75</v>
+        <v>336.34</v>
       </c>
       <c r="G2" t="n">
-        <v>333.33</v>
+        <v>330.83</v>
       </c>
       <c r="H2" t="n">
-        <v>6022965</v>
+        <v>9109409</v>
       </c>
       <c r="I2" t="n">
-        <v>7777946</v>
+        <v>7658070</v>
       </c>
       <c r="J2" t="n">
-        <v>890439270400</v>
+        <v>879407726592</v>
       </c>
       <c r="K2" t="n">
-        <v>14.432573</v>
+        <v>14.346487</v>
       </c>
       <c r="L2" t="n">
-        <v>13.372706</v>
+        <v>13.207034</v>
       </c>
       <c r="M2" t="n">
-        <v>23.21</v>
+        <v>23.06</v>
       </c>
       <c r="N2" t="n">
         <v>366.5</v>
@@ -10059,7 +10059,7 @@
         <v>0.975</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R2" t="n">
         <v>0.34921002</v>
@@ -10087,7 +10087,7 @@
         <v>133.007</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.5185142</v>
+        <v>2.4873126</v>
       </c>
       <c r="Z2" t="n">
         <v>0.469</v>
@@ -10099,7 +10099,7 @@
         <v>186328006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>728367235072</v>
+        <v>717335756800</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:07:03</t>
+          <t>2026-10-01 17:02:45</t>
         </is>
       </c>
     </row>

--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B2" t="n">
-        <v>308.0762861336198</v>
+        <v>304.1807853263183</v>
       </c>
       <c r="C2" t="n">
-        <v>308.6846429587351</v>
+        <v>304.7302708010082</v>
       </c>
       <c r="D2" t="n">
-        <v>301.6394301376976</v>
+        <v>300.3932583082978</v>
       </c>
       <c r="E2" t="n">
-        <v>304.8774719238281</v>
+        <v>301.7767639160156</v>
       </c>
       <c r="F2" t="n">
-        <v>9235200</v>
+        <v>7600000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B3" t="n">
-        <v>304.1807853263183</v>
+        <v>302.7187488597389</v>
       </c>
       <c r="C3" t="n">
-        <v>304.7302708010082</v>
+        <v>305.8096119794931</v>
       </c>
       <c r="D3" t="n">
-        <v>300.3932583082978</v>
+        <v>302.4243624063698</v>
       </c>
       <c r="E3" t="n">
-        <v>301.7767639160156</v>
+        <v>304.210205078125</v>
       </c>
       <c r="F3" t="n">
-        <v>7600000</v>
+        <v>6029900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,25 +521,25 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B4" t="n">
-        <v>302.718779227698</v>
+        <v>305.8371035459471</v>
       </c>
       <c r="C4" t="n">
-        <v>305.8096426575195</v>
+        <v>307.3851288987199</v>
       </c>
       <c r="D4" t="n">
-        <v>302.4243927447969</v>
+        <v>300.8578215934895</v>
       </c>
       <c r="E4" t="n">
-        <v>304.2102355957031</v>
+        <v>304.8511047363281</v>
       </c>
       <c r="F4" t="n">
-        <v>6029900</v>
+        <v>7214500</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -547,25 +547,25 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B5" t="n">
-        <v>305.8371035459471</v>
+        <v>305.0187809092415</v>
       </c>
       <c r="C5" t="n">
-        <v>307.3851288987199</v>
+        <v>305.6695438264559</v>
       </c>
       <c r="D5" t="n">
-        <v>300.8578215934895</v>
+        <v>300.4338918141804</v>
       </c>
       <c r="E5" t="n">
-        <v>304.8511047363281</v>
+        <v>303.3820190429688</v>
       </c>
       <c r="F5" t="n">
-        <v>7214500</v>
+        <v>8454200</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B6" t="n">
-        <v>305.0187502270194</v>
+        <v>303.8946917756213</v>
       </c>
       <c r="C6" t="n">
-        <v>305.6695130787729</v>
+        <v>304.4567183318842</v>
       </c>
       <c r="D6" t="n">
-        <v>300.4338615931582</v>
+        <v>299.2999336047902</v>
       </c>
       <c r="E6" t="n">
-        <v>303.3819885253906</v>
+        <v>299.7732238769531</v>
       </c>
       <c r="F6" t="n">
-        <v>8454200</v>
+        <v>6489900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B7" t="n">
-        <v>303.8946917756213</v>
+        <v>300.7789070325195</v>
       </c>
       <c r="C7" t="n">
-        <v>304.4567183318842</v>
+        <v>303.7270637601551</v>
       </c>
       <c r="D7" t="n">
-        <v>299.2999336047902</v>
+        <v>299.1421755849041</v>
       </c>
       <c r="E7" t="n">
-        <v>299.7732238769531</v>
+        <v>301.252197265625</v>
       </c>
       <c r="F7" t="n">
-        <v>6489900</v>
+        <v>7060300</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B8" t="n">
-        <v>300.7789375021521</v>
+        <v>301.3804193716138</v>
       </c>
       <c r="C8" t="n">
-        <v>303.7270945284432</v>
+        <v>306.1230715472904</v>
       </c>
       <c r="D8" t="n">
-        <v>299.1422058887319</v>
+        <v>296.5983188157025</v>
       </c>
       <c r="E8" t="n">
-        <v>301.2522277832031</v>
+        <v>296.6772155761719</v>
       </c>
       <c r="F8" t="n">
-        <v>7060300</v>
+        <v>8597400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B9" t="n">
-        <v>301.380450372985</v>
+        <v>301.3212684867699</v>
       </c>
       <c r="C9" t="n">
-        <v>306.1231030365125</v>
+        <v>305.1272097801061</v>
       </c>
       <c r="D9" t="n">
-        <v>296.5983493251649</v>
+        <v>301.1733746705027</v>
       </c>
       <c r="E9" t="n">
-        <v>296.67724609375</v>
+        <v>303.6580810546875</v>
       </c>
       <c r="F9" t="n">
-        <v>8597400</v>
+        <v>10788700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B10" t="n">
-        <v>301.3212684867699</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C10" t="n">
-        <v>305.1272097801061</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D10" t="n">
-        <v>301.1733746705027</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E10" t="n">
-        <v>303.6580810546875</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F10" t="n">
-        <v>10788700</v>
+        <v>16178800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B11" t="n">
-        <v>301.5578902761218</v>
+        <v>302.1002149225357</v>
       </c>
       <c r="C11" t="n">
-        <v>302.7016525742085</v>
+        <v>307.7499693151439</v>
       </c>
       <c r="D11" t="n">
-        <v>290.0907186231138</v>
+        <v>301.1635039391426</v>
       </c>
       <c r="E11" t="n">
-        <v>297.8505249023438</v>
+        <v>301.4100036621094</v>
       </c>
       <c r="F11" t="n">
-        <v>16178800</v>
+        <v>11354800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B12" t="n">
-        <v>302.1001843350741</v>
+        <v>301.0747260223031</v>
       </c>
       <c r="C12" t="n">
-        <v>307.7499381556482</v>
+        <v>304.358088638523</v>
       </c>
       <c r="D12" t="n">
-        <v>301.1634734465224</v>
+        <v>292.9106575300408</v>
       </c>
       <c r="E12" t="n">
-        <v>301.4099731445312</v>
+        <v>294.3600769042969</v>
       </c>
       <c r="F12" t="n">
-        <v>11354800</v>
+        <v>10549400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B13" t="n">
-        <v>301.0747572360179</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C13" t="n">
-        <v>304.3581201926382</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D13" t="n">
-        <v>292.9106878973514</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E13" t="n">
-        <v>294.360107421875</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F13" t="n">
-        <v>10549400</v>
+        <v>10153500</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B14" t="n">
-        <v>294.9714335987563</v>
+        <v>294.3206459359216</v>
       </c>
       <c r="C14" t="n">
-        <v>295.3559575215809</v>
+        <v>299.4379821870563</v>
       </c>
       <c r="D14" t="n">
-        <v>290.0808874955599</v>
+        <v>293.9854099500461</v>
       </c>
       <c r="E14" t="n">
-        <v>293.3938293457031</v>
+        <v>298.1265869140625</v>
       </c>
       <c r="F14" t="n">
-        <v>10153500</v>
+        <v>6894900</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B15" t="n">
-        <v>294.3206459359216</v>
+        <v>297.4363803014411</v>
       </c>
       <c r="C15" t="n">
-        <v>299.4379821870563</v>
+        <v>299.7929016175946</v>
       </c>
       <c r="D15" t="n">
-        <v>293.9854099500461</v>
+        <v>292.841622611914</v>
       </c>
       <c r="E15" t="n">
-        <v>298.1265869140625</v>
+        <v>292.9303588867188</v>
       </c>
       <c r="F15" t="n">
-        <v>6894900</v>
+        <v>7372700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B16" t="n">
-        <v>297.436411288458</v>
+        <v>293.6008861047978</v>
       </c>
       <c r="C16" t="n">
-        <v>299.7929328501146</v>
+        <v>293.8868342154489</v>
       </c>
       <c r="D16" t="n">
-        <v>292.8416531202475</v>
+        <v>286.4721332067081</v>
       </c>
       <c r="E16" t="n">
-        <v>292.9303894042969</v>
+        <v>289.9921264648438</v>
       </c>
       <c r="F16" t="n">
-        <v>7372700</v>
+        <v>8054100</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B17" t="n">
-        <v>293.6008861047978</v>
+        <v>290.2583437522712</v>
       </c>
       <c r="C17" t="n">
-        <v>293.8868342154489</v>
+        <v>292.2204718178062</v>
       </c>
       <c r="D17" t="n">
-        <v>286.4721332067081</v>
+        <v>288.4145307332595</v>
       </c>
       <c r="E17" t="n">
-        <v>289.9921264648438</v>
+        <v>290.4161071777344</v>
       </c>
       <c r="F17" t="n">
-        <v>8054100</v>
+        <v>5438800</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B18" t="n">
-        <v>290.2583437522712</v>
+        <v>291.9345194575729</v>
       </c>
       <c r="C18" t="n">
-        <v>292.2204718178062</v>
+        <v>298.3632510673837</v>
       </c>
       <c r="D18" t="n">
-        <v>288.4145307332595</v>
+        <v>291.3133654724136</v>
       </c>
       <c r="E18" t="n">
-        <v>290.4161071777344</v>
+        <v>296.2334899902344</v>
       </c>
       <c r="F18" t="n">
-        <v>5438800</v>
+        <v>7228300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B19" t="n">
-        <v>291.9345194575729</v>
+        <v>297.92941246883</v>
       </c>
       <c r="C19" t="n">
-        <v>298.3632510673837</v>
+        <v>300.2662249001909</v>
       </c>
       <c r="D19" t="n">
-        <v>291.3133654724136</v>
+        <v>296.7955198233114</v>
       </c>
       <c r="E19" t="n">
-        <v>296.2334899902344</v>
+        <v>299.8915405273438</v>
       </c>
       <c r="F19" t="n">
-        <v>7228300</v>
+        <v>5642200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B20" t="n">
-        <v>297.9294427867379</v>
+        <v>300.5915953010157</v>
       </c>
       <c r="C20" t="n">
-        <v>300.2662554558976</v>
+        <v>303.6580673748709</v>
       </c>
       <c r="D20" t="n">
-        <v>296.7955500258321</v>
+        <v>298.915415308335</v>
       </c>
       <c r="E20" t="n">
-        <v>299.8915710449219</v>
+        <v>301.0845947265625</v>
       </c>
       <c r="F20" t="n">
-        <v>5642200</v>
+        <v>6336000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B21" t="n">
-        <v>300.5915953010157</v>
+        <v>299.2605157595805</v>
       </c>
       <c r="C21" t="n">
-        <v>303.6580673748709</v>
+        <v>303.9341406042103</v>
       </c>
       <c r="D21" t="n">
-        <v>298.915415308335</v>
+        <v>298.7675163425421</v>
       </c>
       <c r="E21" t="n">
-        <v>301.0845947265625</v>
+        <v>301.2325134277344</v>
       </c>
       <c r="F21" t="n">
-        <v>6336000</v>
+        <v>7520300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B22" t="n">
-        <v>299.2605157595805</v>
+        <v>301.5086233262724</v>
       </c>
       <c r="C22" t="n">
-        <v>303.9341406042103</v>
+        <v>308.233113206998</v>
       </c>
       <c r="D22" t="n">
-        <v>298.7675163425421</v>
+        <v>300.8282816526182</v>
       </c>
       <c r="E22" t="n">
-        <v>301.2325134277344</v>
+        <v>305.1075134277344</v>
       </c>
       <c r="F22" t="n">
-        <v>7520300</v>
+        <v>7514600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B23" t="n">
-        <v>301.5085931686638</v>
+        <v>304.220113094536</v>
       </c>
       <c r="C23" t="n">
-        <v>308.2330823767899</v>
+        <v>308.4894751488275</v>
       </c>
       <c r="D23" t="n">
-        <v>300.828251563059</v>
+        <v>302.9481660712639</v>
       </c>
       <c r="E23" t="n">
-        <v>305.1074829101562</v>
+        <v>306.7639770507812</v>
       </c>
       <c r="F23" t="n">
-        <v>7514600</v>
+        <v>7721300</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B24" t="n">
-        <v>304.2200828300273</v>
+        <v>306.6456604912348</v>
       </c>
       <c r="C24" t="n">
-        <v>308.4894444595929</v>
+        <v>307.9471862719047</v>
       </c>
       <c r="D24" t="n">
-        <v>302.9481359332913</v>
+        <v>301.9227172950412</v>
       </c>
       <c r="E24" t="n">
-        <v>306.7639465332031</v>
+        <v>305.0187683105469</v>
       </c>
       <c r="F24" t="n">
-        <v>7721300</v>
+        <v>7770000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B25" t="n">
-        <v>306.6456298108837</v>
+        <v>302.415720333495</v>
       </c>
       <c r="C25" t="n">
-        <v>307.947155461334</v>
+        <v>307.8485840116909</v>
       </c>
       <c r="D25" t="n">
-        <v>301.9226870872275</v>
+        <v>300.8282765156093</v>
       </c>
       <c r="E25" t="n">
-        <v>305.0187377929688</v>
+        <v>304.920166015625</v>
       </c>
       <c r="F25" t="n">
-        <v>7770000</v>
+        <v>7085200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B26" t="n">
-        <v>302.4156900665715</v>
+        <v>305.2750763211935</v>
       </c>
       <c r="C26" t="n">
-        <v>307.8485532010255</v>
+        <v>308.7162326204817</v>
       </c>
       <c r="D26" t="n">
-        <v>300.8282464075632</v>
+        <v>301.350820325461</v>
       </c>
       <c r="E26" t="n">
-        <v>304.9201354980469</v>
+        <v>307.3161010742188</v>
       </c>
       <c r="F26" t="n">
-        <v>7085200</v>
+        <v>6865200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B27" t="n">
-        <v>305.2750763211935</v>
+        <v>306.6357990367445</v>
       </c>
       <c r="C27" t="n">
-        <v>308.7162326204817</v>
+        <v>310.4319009529449</v>
       </c>
       <c r="D27" t="n">
-        <v>301.350820325461</v>
+        <v>305.9160390722913</v>
       </c>
       <c r="E27" t="n">
-        <v>307.3161010742188</v>
+        <v>309.0317993164062</v>
       </c>
       <c r="F27" t="n">
-        <v>6865200</v>
+        <v>7206100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B28" t="n">
-        <v>306.6357687557767</v>
+        <v>307.5231746391179</v>
       </c>
       <c r="C28" t="n">
-        <v>310.4318702971036</v>
+        <v>310.0275898810191</v>
       </c>
       <c r="D28" t="n">
-        <v>305.9160088624015</v>
+        <v>303.3326798145578</v>
       </c>
       <c r="E28" t="n">
-        <v>309.0317687988281</v>
+        <v>309.8106689453125</v>
       </c>
       <c r="F28" t="n">
-        <v>7206100</v>
+        <v>7302300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B29" t="n">
-        <v>307.5231746391179</v>
+        <v>310.5896641246428</v>
       </c>
       <c r="C29" t="n">
-        <v>310.0275898810191</v>
+        <v>315.0858168552232</v>
       </c>
       <c r="D29" t="n">
-        <v>303.3326798145578</v>
+        <v>309.810716541713</v>
       </c>
       <c r="E29" t="n">
-        <v>309.8106689453125</v>
+        <v>312.4532165527344</v>
       </c>
       <c r="F29" t="n">
-        <v>7302300</v>
+        <v>5794100</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B30" t="n">
-        <v>310.5896337890794</v>
+        <v>313.054640940315</v>
       </c>
       <c r="C30" t="n">
-        <v>315.0857860805166</v>
+        <v>314.5829271513063</v>
       </c>
       <c r="D30" t="n">
-        <v>309.8106862822301</v>
+        <v>310.8657222472937</v>
       </c>
       <c r="E30" t="n">
-        <v>312.4531860351562</v>
+        <v>311.2009582519531</v>
       </c>
       <c r="F30" t="n">
-        <v>5794100</v>
+        <v>5030200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B31" t="n">
-        <v>313.054640940315</v>
+        <v>311.8320301504691</v>
       </c>
       <c r="C31" t="n">
-        <v>314.5829271513063</v>
+        <v>317.7381540918137</v>
       </c>
       <c r="D31" t="n">
-        <v>310.8657222472937</v>
+        <v>311.7827121499603</v>
       </c>
       <c r="E31" t="n">
-        <v>311.2009582519531</v>
+        <v>315.9239196777344</v>
       </c>
       <c r="F31" t="n">
-        <v>5030200</v>
+        <v>10578300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B32" t="n">
-        <v>311.8320000281587</v>
+        <v>314.7604311532612</v>
       </c>
       <c r="C32" t="n">
-        <v>317.7381233989844</v>
+        <v>316.1408235578094</v>
       </c>
       <c r="D32" t="n">
-        <v>311.782682032414</v>
+        <v>304.7722577523736</v>
       </c>
       <c r="E32" t="n">
-        <v>315.9238891601562</v>
+        <v>305.1469421386719</v>
       </c>
       <c r="F32" t="n">
-        <v>10578300</v>
+        <v>8973300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B33" t="n">
-        <v>314.7604311532612</v>
+        <v>303.2045199796025</v>
       </c>
       <c r="C33" t="n">
-        <v>316.1408235578094</v>
+        <v>303.3327046462357</v>
       </c>
       <c r="D33" t="n">
-        <v>304.7722577523736</v>
+        <v>297.0124483237873</v>
       </c>
       <c r="E33" t="n">
-        <v>305.1469421386719</v>
+        <v>299.3591003417969</v>
       </c>
       <c r="F33" t="n">
-        <v>8973300</v>
+        <v>10327000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B34" t="n">
-        <v>303.2045199796025</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C34" t="n">
-        <v>303.3327046462357</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D34" t="n">
-        <v>297.0124483237873</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E34" t="n">
-        <v>299.3591003417969</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F34" t="n">
-        <v>10327000</v>
+        <v>8344000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B35" t="n">
-        <v>299.7436397411884</v>
+        <v>295.3066317863286</v>
       </c>
       <c r="C35" t="n">
-        <v>301.3113742461044</v>
+        <v>298.70833958092</v>
       </c>
       <c r="D35" t="n">
-        <v>293.5022804823602</v>
+        <v>292.8613440028039</v>
       </c>
       <c r="E35" t="n">
-        <v>296.1644592285156</v>
+        <v>295.2178955078125</v>
       </c>
       <c r="F35" t="n">
-        <v>8344000</v>
+        <v>8077300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B36" t="n">
-        <v>295.3066317863286</v>
+        <v>295.5432899586994</v>
       </c>
       <c r="C36" t="n">
-        <v>298.70833958092</v>
+        <v>300.1873662746028</v>
       </c>
       <c r="D36" t="n">
-        <v>292.8613440028039</v>
+        <v>295.0798692888629</v>
       </c>
       <c r="E36" t="n">
-        <v>295.2178955078125</v>
+        <v>299.0238647460938</v>
       </c>
       <c r="F36" t="n">
-        <v>8077300</v>
+        <v>5546600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B37" t="n">
-        <v>295.5432899586994</v>
+        <v>302.0508736933244</v>
       </c>
       <c r="C37" t="n">
-        <v>300.1873662746028</v>
+        <v>305.5807663052954</v>
       </c>
       <c r="D37" t="n">
-        <v>295.0798692888629</v>
+        <v>293.9854105998292</v>
       </c>
       <c r="E37" t="n">
-        <v>299.0238647460938</v>
+        <v>294.2023315429688</v>
       </c>
       <c r="F37" t="n">
-        <v>5546600</v>
+        <v>7501600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B38" t="n">
-        <v>302.0508736933244</v>
+        <v>297.0715864028587</v>
       </c>
       <c r="C38" t="n">
-        <v>305.5807663052954</v>
+        <v>297.456110287291</v>
       </c>
       <c r="D38" t="n">
-        <v>293.9854105998292</v>
+        <v>288.7103057597054</v>
       </c>
       <c r="E38" t="n">
-        <v>294.2023315429688</v>
+        <v>293.8473510742188</v>
       </c>
       <c r="F38" t="n">
-        <v>7501600</v>
+        <v>11766800</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B39" t="n">
-        <v>297.0715864028587</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C39" t="n">
-        <v>297.456110287291</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D39" t="n">
-        <v>288.7103057597054</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E39" t="n">
-        <v>293.8473510742188</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F39" t="n">
-        <v>11766800</v>
+        <v>10940200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B40" t="n">
-        <v>294.0642973394352</v>
+        <v>295.8489209666184</v>
       </c>
       <c r="C40" t="n">
-        <v>295.6221924256846</v>
+        <v>300.2366275598507</v>
       </c>
       <c r="D40" t="n">
-        <v>290.386540762355</v>
+        <v>291.4217960873232</v>
       </c>
       <c r="E40" t="n">
-        <v>293.8276672363281</v>
+        <v>298.7576293945312</v>
       </c>
       <c r="F40" t="n">
-        <v>10940200</v>
+        <v>8877200</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B41" t="n">
-        <v>295.848951187077</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C41" t="n">
-        <v>300.236658228506</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D41" t="n">
-        <v>291.4218258555586</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E41" t="n">
-        <v>298.7576599121094</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F41" t="n">
-        <v>8877200</v>
+        <v>7910900</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B42" t="n">
-        <v>300.7296512123902</v>
+        <v>304.7722767012305</v>
       </c>
       <c r="C42" t="n">
-        <v>304.2102259719906</v>
+        <v>309.3275869646093</v>
       </c>
       <c r="D42" t="n">
-        <v>298.9548653069277</v>
+        <v>303.9243019705234</v>
       </c>
       <c r="E42" t="n">
-        <v>303.3327026367188</v>
+        <v>308.696533203125</v>
       </c>
       <c r="F42" t="n">
-        <v>7910900</v>
+        <v>4322400</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B43" t="n">
-        <v>304.7722465716023</v>
+        <v>308.5683618849884</v>
       </c>
       <c r="C43" t="n">
-        <v>309.3275563846455</v>
+        <v>309.6430970545817</v>
       </c>
       <c r="D43" t="n">
-        <v>303.9242719247256</v>
+        <v>304.2201032083801</v>
       </c>
       <c r="E43" t="n">
-        <v>308.6965026855469</v>
+        <v>304.5947875976562</v>
       </c>
       <c r="F43" t="n">
-        <v>4322400</v>
+        <v>7727300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B44" t="n">
-        <v>308.5683618849884</v>
+        <v>304.4172805196406</v>
       </c>
       <c r="C44" t="n">
-        <v>309.6430970545817</v>
+        <v>306.1329390093465</v>
       </c>
       <c r="D44" t="n">
-        <v>304.2201032083801</v>
+        <v>302.7903884074122</v>
       </c>
       <c r="E44" t="n">
-        <v>304.5947875976562</v>
+        <v>303.5693359375</v>
       </c>
       <c r="F44" t="n">
-        <v>7727300</v>
+        <v>7249000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B45" t="n">
-        <v>304.4172805196406</v>
+        <v>302.8988595387675</v>
       </c>
       <c r="C45" t="n">
-        <v>306.1329390093465</v>
+        <v>307.9865871384521</v>
       </c>
       <c r="D45" t="n">
-        <v>302.7903884074122</v>
+        <v>302.5044359255107</v>
       </c>
       <c r="E45" t="n">
-        <v>303.5693359375</v>
+        <v>307.7598266601562</v>
       </c>
       <c r="F45" t="n">
-        <v>7249000</v>
+        <v>8535300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B46" t="n">
-        <v>302.8988895743303</v>
+        <v>308.8740221323167</v>
       </c>
       <c r="C46" t="n">
-        <v>307.9866176785159</v>
+        <v>314.0307770729326</v>
       </c>
       <c r="D46" t="n">
-        <v>302.5044659219624</v>
+        <v>308.617652791837</v>
       </c>
       <c r="E46" t="n">
-        <v>307.7598571777344</v>
+        <v>311.6742553710938</v>
       </c>
       <c r="F46" t="n">
-        <v>8535300</v>
+        <v>9627800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B47" t="n">
-        <v>308.8739918889233</v>
+        <v>311.2206946896725</v>
       </c>
       <c r="C47" t="n">
-        <v>314.0307463246157</v>
+        <v>314.0209278419201</v>
       </c>
       <c r="D47" t="n">
-        <v>308.6176225735461</v>
+        <v>310.2741141188276</v>
       </c>
       <c r="E47" t="n">
-        <v>311.6742248535156</v>
+        <v>310.6290893554688</v>
       </c>
       <c r="F47" t="n">
-        <v>9627800</v>
+        <v>6518900</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B48" t="n">
-        <v>311.2206641139725</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C48" t="n">
-        <v>314.0208969911127</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D48" t="n">
-        <v>310.2740836361238</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E48" t="n">
-        <v>310.6290588378906</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F48" t="n">
-        <v>6518900</v>
+        <v>7417200</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B49" t="n">
-        <v>310.6487980837529</v>
+        <v>310.5403463950657</v>
       </c>
       <c r="C49" t="n">
-        <v>312.0390600856641</v>
+        <v>314.3364178531727</v>
       </c>
       <c r="D49" t="n">
-        <v>308.9627484602848</v>
+        <v>295.8193608594167</v>
       </c>
       <c r="E49" t="n">
-        <v>310.7966918945312</v>
+        <v>296.3025207519531</v>
       </c>
       <c r="F49" t="n">
-        <v>7417200</v>
+        <v>18049200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B50" t="n">
-        <v>310.5403783790639</v>
+        <v>296.2926621709551</v>
       </c>
       <c r="C50" t="n">
-        <v>314.336450228146</v>
+        <v>306.8329925602339</v>
       </c>
       <c r="D50" t="n">
-        <v>295.8193913272319</v>
+        <v>294.2812160390869</v>
       </c>
       <c r="E50" t="n">
-        <v>296.3025512695312</v>
+        <v>305.7680969238281</v>
       </c>
       <c r="F50" t="n">
-        <v>18049200</v>
+        <v>18874100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B51" t="n">
-        <v>296.2926621709551</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C51" t="n">
-        <v>306.8329925602339</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D51" t="n">
-        <v>294.2812160390869</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E51" t="n">
-        <v>305.7680969238281</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F51" t="n">
-        <v>18874100</v>
+        <v>9721900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B52" t="n">
-        <v>304.9102649889192</v>
+        <v>315.2040954937631</v>
       </c>
       <c r="C52" t="n">
-        <v>313.5476242674454</v>
+        <v>315.7858311866128</v>
       </c>
       <c r="D52" t="n">
-        <v>304.9102649889192</v>
+        <v>312.1672323684923</v>
       </c>
       <c r="E52" t="n">
-        <v>312.9363098144531</v>
+        <v>314.0603332519531</v>
       </c>
       <c r="F52" t="n">
-        <v>9721900</v>
+        <v>8982900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B53" t="n">
-        <v>315.2040954937631</v>
+        <v>315.115395356304</v>
       </c>
       <c r="C53" t="n">
-        <v>315.7858311866128</v>
+        <v>318.3593402708456</v>
       </c>
       <c r="D53" t="n">
-        <v>312.1672323684923</v>
+        <v>313.9322146909975</v>
       </c>
       <c r="E53" t="n">
-        <v>314.0603332519531</v>
+        <v>315.5393676757812</v>
       </c>
       <c r="F53" t="n">
-        <v>8982900</v>
+        <v>10864100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B54" t="n">
-        <v>315.1153648797306</v>
+        <v>314.6223410116007</v>
       </c>
       <c r="C54" t="n">
-        <v>318.3593094805321</v>
+        <v>315.0463132571263</v>
       </c>
       <c r="D54" t="n">
-        <v>313.9321843288561</v>
+        <v>309.9980044156554</v>
       </c>
       <c r="E54" t="n">
-        <v>315.5393371582031</v>
+        <v>311.1318969726562</v>
       </c>
       <c r="F54" t="n">
-        <v>10864100</v>
+        <v>8331300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B55" t="n">
-        <v>314.6223718715413</v>
+        <v>313.9716244610726</v>
       </c>
       <c r="C55" t="n">
-        <v>315.0463441586525</v>
+        <v>314.8984658400699</v>
       </c>
       <c r="D55" t="n">
-        <v>309.9980348220149</v>
+        <v>310.2544194174254</v>
       </c>
       <c r="E55" t="n">
-        <v>311.1319274902344</v>
+        <v>310.5699462890625</v>
       </c>
       <c r="F55" t="n">
-        <v>8331300</v>
+        <v>8718700</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B56" t="n">
-        <v>313.971593609235</v>
+        <v>311.5756418636432</v>
       </c>
       <c r="C56" t="n">
-        <v>314.8984348971578</v>
+        <v>313.2518519730792</v>
       </c>
       <c r="D56" t="n">
-        <v>310.254388930852</v>
+        <v>307.8485673512913</v>
       </c>
       <c r="E56" t="n">
-        <v>310.5699157714844</v>
+        <v>308.6176452636719</v>
       </c>
       <c r="F56" t="n">
-        <v>8718700</v>
+        <v>11444900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B57" t="n">
-        <v>311.5756418636432</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C57" t="n">
-        <v>313.2518519730792</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D57" t="n">
-        <v>307.8485673512913</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E57" t="n">
-        <v>308.6176452636719</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F57" t="n">
-        <v>11444900</v>
+        <v>24494400</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B58" t="n">
-        <v>309.3965776494671</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="C58" t="n">
-        <v>314.099781180705</v>
+        <v>318.7043994886834</v>
       </c>
       <c r="D58" t="n">
-        <v>308.8049723403709</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="E58" t="n">
-        <v>312.7686767578125</v>
+        <v>318.5663452148438</v>
       </c>
       <c r="F58" t="n">
-        <v>24494400</v>
+        <v>8354600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B59" t="n">
-        <v>313.0644852104395</v>
+        <v>319.0790830432475</v>
       </c>
       <c r="C59" t="n">
-        <v>318.7043994886834</v>
+        <v>323.1907116116738</v>
       </c>
       <c r="D59" t="n">
-        <v>313.0644852104395</v>
+        <v>318.5663744582675</v>
       </c>
       <c r="E59" t="n">
-        <v>318.5663452148438</v>
+        <v>321.3666076660156</v>
       </c>
       <c r="F59" t="n">
-        <v>8354600</v>
+        <v>6668300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B60" t="n">
-        <v>319.079052742897</v>
+        <v>321.6722493328215</v>
       </c>
       <c r="C60" t="n">
-        <v>323.1906809208754</v>
+        <v>325.3697449529369</v>
       </c>
       <c r="D60" t="n">
-        <v>318.5663442066048</v>
+        <v>320.9426198260136</v>
       </c>
       <c r="E60" t="n">
-        <v>321.3665771484375</v>
+        <v>324.5612487792969</v>
       </c>
       <c r="F60" t="n">
-        <v>6668300</v>
+        <v>4289300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B61" t="n">
-        <v>321.6722493328215</v>
+        <v>324.502058709128</v>
       </c>
       <c r="C61" t="n">
-        <v>325.3697449529369</v>
+        <v>326.2275566521161</v>
       </c>
       <c r="D61" t="n">
-        <v>320.9426198260136</v>
+        <v>321.9680645986219</v>
       </c>
       <c r="E61" t="n">
-        <v>324.5612487792969</v>
+        <v>323.3188781738281</v>
       </c>
       <c r="F61" t="n">
-        <v>4289300</v>
+        <v>4158300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B62" t="n">
-        <v>324.5020893383847</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C62" t="n">
-        <v>326.22758744424</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D62" t="n">
-        <v>321.9680949886989</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E62" t="n">
-        <v>323.3189086914062</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F62" t="n">
-        <v>4158300</v>
+        <v>8635300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B63" t="n">
-        <v>322.4216288798564</v>
+        <v>320.2622768741799</v>
       </c>
       <c r="C63" t="n">
-        <v>323.1808371734579</v>
+        <v>320.3904615362508</v>
       </c>
       <c r="D63" t="n">
-        <v>319.0002116144308</v>
+        <v>317.9747523718436</v>
       </c>
       <c r="E63" t="n">
-        <v>319.2171325683594</v>
+        <v>318.8917541503906</v>
       </c>
       <c r="F63" t="n">
-        <v>8635300</v>
+        <v>7904300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B64" t="n">
-        <v>320.2622768741799</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C64" t="n">
-        <v>320.3904615362508</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D64" t="n">
-        <v>317.9747523718436</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E64" t="n">
-        <v>318.8917541503906</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F64" t="n">
-        <v>7904300</v>
+        <v>5048500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B65" t="n">
-        <v>319.7988699190817</v>
+        <v>317.9846554663246</v>
       </c>
       <c r="C65" t="n">
-        <v>320.3313177342217</v>
+        <v>321.169442848154</v>
       </c>
       <c r="D65" t="n">
-        <v>317.5310845539587</v>
+        <v>316.2492877176746</v>
       </c>
       <c r="E65" t="n">
-        <v>317.7085571289062</v>
+        <v>320.9229431152344</v>
       </c>
       <c r="F65" t="n">
-        <v>5048500</v>
+        <v>8054000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B66" t="n">
-        <v>317.9846252281575</v>
+        <v>320.942628937084</v>
       </c>
       <c r="C66" t="n">
-        <v>321.1694123071354</v>
+        <v>332.5281155423397</v>
       </c>
       <c r="D66" t="n">
-        <v>316.2492576445291</v>
+        <v>320.636971697701</v>
       </c>
       <c r="E66" t="n">
-        <v>320.9229125976562</v>
+        <v>329.3630676269531</v>
       </c>
       <c r="F66" t="n">
-        <v>8054000</v>
+        <v>10752600</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,25 +2159,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B67" t="n">
-        <v>320.942599199713</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C67" t="n">
-        <v>332.5280847314999</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D67" t="n">
-        <v>320.6369419886511</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E67" t="n">
-        <v>329.363037109375</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F67" t="n">
-        <v>10752600</v>
+        <v>7660800</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2185,25 +2185,25 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B68" t="n">
-        <v>329.4422902981328</v>
+        <v>327.9764659913386</v>
       </c>
       <c r="C68" t="n">
-        <v>332.6612412306879</v>
+        <v>328.9767963949314</v>
       </c>
       <c r="D68" t="n">
-        <v>327.491109600743</v>
+        <v>321.4989374679619</v>
       </c>
       <c r="E68" t="n">
-        <v>331.4132690429688</v>
+        <v>323.8660888671875</v>
       </c>
       <c r="F68" t="n">
-        <v>7660800</v>
+        <v>9815200</v>
       </c>
       <c r="G68" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B69" t="n">
-        <v>327.9764350864437</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C69" t="n">
-        <v>328.9767653957764</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D69" t="n">
-        <v>321.4989071734381</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E69" t="n">
-        <v>323.8660583496094</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F69" t="n">
-        <v>9815200</v>
+        <v>11737100</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B70" t="n">
-        <v>323.2718313763784</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C70" t="n">
-        <v>328.2339475379842</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D70" t="n">
-        <v>322.5388804495614</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E70" t="n">
-        <v>326.6393432617188</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F70" t="n">
-        <v>11737100</v>
+        <v>6738100</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B71" t="n">
-        <v>326.1936353875406</v>
+        <v>318.8049029297019</v>
       </c>
       <c r="C71" t="n">
-        <v>328.7291759216584</v>
+        <v>322.9053354478686</v>
       </c>
       <c r="D71" t="n">
-        <v>325.0348299492433</v>
+        <v>318.1611187929736</v>
       </c>
       <c r="E71" t="n">
-        <v>326.0450744628906</v>
+        <v>321.3899536132812</v>
       </c>
       <c r="F71" t="n">
-        <v>6738100</v>
+        <v>12805100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B72" t="n">
-        <v>318.8049332018166</v>
+        <v>321.2017547389941</v>
       </c>
       <c r="C72" t="n">
-        <v>322.9053661093398</v>
+        <v>323.7372950994605</v>
       </c>
       <c r="D72" t="n">
-        <v>318.1611490039577</v>
+        <v>307.6029450408882</v>
       </c>
       <c r="E72" t="n">
-        <v>321.3899841308594</v>
+        <v>307.9297790527344</v>
       </c>
       <c r="F72" t="n">
-        <v>12805100</v>
+        <v>19371200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B73" t="n">
-        <v>321.2017865718998</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C73" t="n">
-        <v>323.7373271836527</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D73" t="n">
-        <v>307.6029755260753</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E73" t="n">
-        <v>307.9298095703125</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F73" t="n">
-        <v>19371200</v>
+        <v>25951500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B74" t="n">
-        <v>305.2556057077196</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C74" t="n">
-        <v>308.7815926253858</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D74" t="n">
-        <v>303.1954601804828</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E74" t="n">
-        <v>304.9287414550781</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F74" t="n">
-        <v>25951500</v>
+        <v>14751400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B75" t="n">
-        <v>305.5230197927318</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C75" t="n">
-        <v>309.95031666446</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D75" t="n">
-        <v>304.8098971346673</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E75" t="n">
-        <v>306.3054809570312</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F75" t="n">
-        <v>14751400</v>
+        <v>14652500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B76" t="n">
-        <v>307.385060616362</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C76" t="n">
-        <v>314.1795087286461</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D76" t="n">
-        <v>307.0383983149945</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E76" t="n">
-        <v>309.4848022460938</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F76" t="n">
-        <v>14652500</v>
+        <v>12900600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B77" t="n">
-        <v>303.2845981841295</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C77" t="n">
-        <v>308.1774060521912</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D77" t="n">
-        <v>298.9761500928895</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E77" t="n">
-        <v>299.8477478027344</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F77" t="n">
-        <v>12900600</v>
+        <v>10270100</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B78" t="n">
-        <v>300.5311849469782</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C78" t="n">
-        <v>302.4823658305288</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D78" t="n">
-        <v>298.2729680555718</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E78" t="n">
-        <v>299.1544799804688</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F78" t="n">
-        <v>10270100</v>
+        <v>10535800</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B79" t="n">
-        <v>301.9474777854751</v>
+        <v>299.1148112655088</v>
       </c>
       <c r="C79" t="n">
-        <v>305.2555953909441</v>
+        <v>299.4812715954647</v>
       </c>
       <c r="D79" t="n">
-        <v>300.0062112868251</v>
+        <v>293.6772702297321</v>
       </c>
       <c r="E79" t="n">
-        <v>300.729248046875</v>
+        <v>294.8757019042969</v>
       </c>
       <c r="F79" t="n">
-        <v>10535800</v>
+        <v>11107900</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B80" t="n">
-        <v>299.1148422218051</v>
+        <v>294.9648486176391</v>
       </c>
       <c r="C80" t="n">
-        <v>299.4813025896872</v>
+        <v>298.8969221500132</v>
       </c>
       <c r="D80" t="n">
-        <v>293.6773006232809</v>
+        <v>294.6083024116733</v>
       </c>
       <c r="E80" t="n">
-        <v>294.875732421875</v>
+        <v>298.1640014648438</v>
       </c>
       <c r="F80" t="n">
-        <v>11107900</v>
+        <v>11752700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B81" t="n">
-        <v>294.9648788077786</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C81" t="n">
-        <v>298.8969527426069</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D81" t="n">
-        <v>294.6083325653198</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E81" t="n">
-        <v>298.1640319824219</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F81" t="n">
-        <v>11752700</v>
+        <v>11527400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B82" t="n">
-        <v>298.4512235287846</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C82" t="n">
-        <v>299.0851237823749</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D82" t="n">
-        <v>295.3016109870806</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E82" t="n">
-        <v>297.4409790039062</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F82" t="n">
-        <v>11527400</v>
+        <v>9556700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B83" t="n">
-        <v>297.4013222225187</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C83" t="n">
-        <v>299.0355829225425</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D83" t="n">
-        <v>295.2025300603667</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E83" t="n">
-        <v>297.8965454101562</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F83" t="n">
-        <v>9556700</v>
+        <v>11580000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B84" t="n">
-        <v>299.5110006693188</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C84" t="n">
-        <v>303.898671192008</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D84" t="n">
-        <v>299.3327275624257</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E84" t="n">
-        <v>303.4926147460938</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F84" t="n">
-        <v>11580000</v>
+        <v>11953200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B85" t="n">
-        <v>302.333781642444</v>
+        <v>301.5513314360023</v>
       </c>
       <c r="C85" t="n">
-        <v>304.9881708986046</v>
+        <v>306.3450888451811</v>
       </c>
       <c r="D85" t="n">
-        <v>299.6694782493637</v>
+        <v>298.4908553932551</v>
       </c>
       <c r="E85" t="n">
-        <v>302.9676818847656</v>
+        <v>305.1961975097656</v>
       </c>
       <c r="F85" t="n">
-        <v>11953200</v>
+        <v>9839400</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B86" t="n">
-        <v>301.5513012828864</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C86" t="n">
-        <v>306.3450582127215</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D86" t="n">
-        <v>298.4908255461663</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E86" t="n">
-        <v>305.1961669921875</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F86" t="n">
-        <v>9839400</v>
+        <v>12688000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B87" t="n">
-        <v>306.7709905338949</v>
+        <v>311.4062598905275</v>
       </c>
       <c r="C87" t="n">
-        <v>313.2286905211348</v>
+        <v>316.2594412620415</v>
       </c>
       <c r="D87" t="n">
-        <v>306.1470044328188</v>
+        <v>311.4062598905275</v>
       </c>
       <c r="E87" t="n">
-        <v>311.8420715332031</v>
+        <v>314.2389221191406</v>
       </c>
       <c r="F87" t="n">
-        <v>12688000</v>
+        <v>9848800</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B88" t="n">
-        <v>311.4062901330092</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C88" t="n">
-        <v>316.2594719758441</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D88" t="n">
-        <v>311.4062901330092</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E88" t="n">
-        <v>314.2389526367188</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F88" t="n">
-        <v>9848800</v>
+        <v>9388000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B89" t="n">
-        <v>311.9906259989966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C89" t="n">
-        <v>312.9909865673853</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D89" t="n">
-        <v>302.6210112179966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E89" t="n">
-        <v>307.1968688964844</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F89" t="n">
-        <v>9388000</v>
+        <v>17797400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B90" t="n">
-        <v>311.7034102684662</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C90" t="n">
-        <v>321.1522783634816</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D90" t="n">
-        <v>311.7034102684662</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E90" t="n">
-        <v>319.3199462890625</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F90" t="n">
-        <v>17797400</v>
+        <v>11477500</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B91" t="n">
-        <v>318.2700781279603</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C91" t="n">
-        <v>323.2817350541263</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D91" t="n">
-        <v>317.0518180384032</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E91" t="n">
-        <v>319.0228271484375</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F91" t="n">
-        <v>11477500</v>
+        <v>9902200</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B92" t="n">
-        <v>319.4684837021083</v>
+        <v>320.1519144431551</v>
       </c>
       <c r="C92" t="n">
-        <v>323.014298845819</v>
+        <v>322.1724337503843</v>
       </c>
       <c r="D92" t="n">
-        <v>312.1094739861534</v>
+        <v>305.7805563960757</v>
       </c>
       <c r="E92" t="n">
-        <v>315.2392883300781</v>
+        <v>307.8505859375</v>
       </c>
       <c r="F92" t="n">
-        <v>9902200</v>
+        <v>8703500</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B93" t="n">
-        <v>320.1518827061323</v>
+        <v>309.2966060076438</v>
       </c>
       <c r="C93" t="n">
-        <v>322.1724018130651</v>
+        <v>310.6238005797982</v>
       </c>
       <c r="D93" t="n">
-        <v>305.7805260837019</v>
+        <v>297.1537232583444</v>
       </c>
       <c r="E93" t="n">
-        <v>307.8505554199219</v>
+        <v>299.7487182617188</v>
       </c>
       <c r="F93" t="n">
-        <v>8703500</v>
+        <v>13443400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B94" t="n">
-        <v>309.2966374972976</v>
+        <v>295.6680481198895</v>
       </c>
       <c r="C94" t="n">
-        <v>310.6238322045743</v>
+        <v>301.3829431862302</v>
       </c>
       <c r="D94" t="n">
-        <v>297.1537535117247</v>
+        <v>293.6871553220786</v>
       </c>
       <c r="E94" t="n">
-        <v>299.7487487792969</v>
+        <v>299.6595458984375</v>
       </c>
       <c r="F94" t="n">
-        <v>13443400</v>
+        <v>9114500</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B95" t="n">
-        <v>295.6680782309701</v>
+        <v>299.8675549474044</v>
       </c>
       <c r="C95" t="n">
-        <v>301.3829738793206</v>
+        <v>305.2951817518681</v>
       </c>
       <c r="D95" t="n">
-        <v>293.6871852314235</v>
+        <v>299.6100292169066</v>
       </c>
       <c r="E95" t="n">
-        <v>299.6595764160156</v>
+        <v>304.19580078125</v>
       </c>
       <c r="F95" t="n">
-        <v>9114500</v>
+        <v>8896800</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B96" t="n">
-        <v>299.8675850307636</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C96" t="n">
-        <v>305.2952123797385</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D96" t="n">
-        <v>299.6100592744303</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E96" t="n">
-        <v>304.1958312988281</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F96" t="n">
-        <v>8896800</v>
+        <v>7209600</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B97" t="n">
-        <v>305.5130974954087</v>
+        <v>304.2354576365961</v>
       </c>
       <c r="C97" t="n">
-        <v>309.2966101142475</v>
+        <v>306.226234501648</v>
       </c>
       <c r="D97" t="n">
-        <v>304.2849535938903</v>
+        <v>302.2050242231491</v>
       </c>
       <c r="E97" t="n">
-        <v>305.8300476074219</v>
+        <v>305.1070251464844</v>
       </c>
       <c r="F97" t="n">
-        <v>7209600</v>
+        <v>6737700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B98" t="n">
-        <v>304.2354272061944</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C98" t="n">
-        <v>306.2262038721237</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D98" t="n">
-        <v>302.2049939958365</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E98" t="n">
-        <v>305.1069946289062</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F98" t="n">
-        <v>6737700</v>
+        <v>7792700</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B99" t="n">
-        <v>305.4536802835111</v>
+        <v>305.8498774375392</v>
       </c>
       <c r="C99" t="n">
-        <v>308.0288471084009</v>
+        <v>308.028871901531</v>
       </c>
       <c r="D99" t="n">
-        <v>302.7596647203387</v>
+        <v>292.2807780649544</v>
       </c>
       <c r="E99" t="n">
-        <v>307.8208618164062</v>
+        <v>294.8262329101562</v>
       </c>
       <c r="F99" t="n">
-        <v>7792700</v>
+        <v>12955400</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B100" t="n">
-        <v>305.8498457788994</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C100" t="n">
-        <v>308.0288400173425</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D100" t="n">
-        <v>292.2807478108573</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E100" t="n">
-        <v>294.8262023925781</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F100" t="n">
-        <v>12955400</v>
+        <v>13554100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B101" t="n">
-        <v>293.9843218466586</v>
+        <v>295.7869207463737</v>
       </c>
       <c r="C101" t="n">
-        <v>296.886322684036</v>
+        <v>300.7589506810849</v>
       </c>
       <c r="D101" t="n">
-        <v>288.5962907533433</v>
+        <v>294.1724883145502</v>
       </c>
       <c r="E101" t="n">
-        <v>294.459716796875</v>
+        <v>300.4023742675781</v>
       </c>
       <c r="F101" t="n">
-        <v>13554100</v>
+        <v>8095500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B102" t="n">
-        <v>295.7869507950724</v>
+        <v>301.670173133609</v>
       </c>
       <c r="C102" t="n">
-        <v>300.7589812348872</v>
+        <v>306.0578739762234</v>
       </c>
       <c r="D102" t="n">
-        <v>294.1725181992404</v>
+        <v>300.7391812579012</v>
       </c>
       <c r="E102" t="n">
-        <v>300.4024047851562</v>
+        <v>303.2053833007812</v>
       </c>
       <c r="F102" t="n">
-        <v>8095500</v>
+        <v>7007800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B103" t="n">
-        <v>301.670173133609</v>
+        <v>297.1339389424841</v>
       </c>
       <c r="C103" t="n">
-        <v>306.0578739762234</v>
+        <v>300.0557680991628</v>
       </c>
       <c r="D103" t="n">
-        <v>300.7391812579012</v>
+        <v>291.636973162459</v>
       </c>
       <c r="E103" t="n">
-        <v>303.2053833007812</v>
+        <v>297.4310607910156</v>
       </c>
       <c r="F103" t="n">
-        <v>7007800</v>
+        <v>18620800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B104" t="n">
-        <v>297.1339389424841</v>
+        <v>291.9935267958635</v>
       </c>
       <c r="C104" t="n">
-        <v>300.0557680991628</v>
+        <v>297.1141484397957</v>
       </c>
       <c r="D104" t="n">
-        <v>291.636973162459</v>
+        <v>290.4088063693875</v>
       </c>
       <c r="E104" t="n">
-        <v>297.4310607910156</v>
+        <v>294.7172546386719</v>
       </c>
       <c r="F104" t="n">
-        <v>18620800</v>
+        <v>8508900</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B105" t="n">
-        <v>291.9935267958635</v>
+        <v>289.4975898716125</v>
       </c>
       <c r="C105" t="n">
-        <v>297.1141484397957</v>
+        <v>299.5011046657454</v>
       </c>
       <c r="D105" t="n">
-        <v>290.4088063693875</v>
+        <v>286.7342359222354</v>
       </c>
       <c r="E105" t="n">
-        <v>294.7172546386719</v>
+        <v>297.3914489746094</v>
       </c>
       <c r="F105" t="n">
-        <v>8508900</v>
+        <v>10278200</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B106" t="n">
-        <v>289.4975898716125</v>
+        <v>297.1240288614248</v>
       </c>
       <c r="C106" t="n">
-        <v>299.5011046657454</v>
+        <v>298.1243894751821</v>
       </c>
       <c r="D106" t="n">
-        <v>286.7342359222354</v>
+        <v>292.993883980321</v>
       </c>
       <c r="E106" t="n">
-        <v>297.3914489746094</v>
+        <v>296.52978515625</v>
       </c>
       <c r="F106" t="n">
-        <v>10278200</v>
+        <v>8055700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B107" t="n">
-        <v>297.1240288614248</v>
+        <v>295.1332451958745</v>
       </c>
       <c r="C107" t="n">
-        <v>298.1243894751821</v>
+        <v>298.3620800816865</v>
       </c>
       <c r="D107" t="n">
-        <v>292.993883980321</v>
+        <v>289.6362492414601</v>
       </c>
       <c r="E107" t="n">
-        <v>296.52978515625</v>
+        <v>290.7455444335938</v>
       </c>
       <c r="F107" t="n">
-        <v>8055700</v>
+        <v>12732500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B108" t="n">
-        <v>295.1332451958745</v>
+        <v>283.6044306839189</v>
       </c>
       <c r="C108" t="n">
-        <v>298.3620800816865</v>
+        <v>287.2195541533999</v>
       </c>
       <c r="D108" t="n">
-        <v>289.6362492414601</v>
+        <v>280.9995517042956</v>
       </c>
       <c r="E108" t="n">
-        <v>290.7455444335938</v>
+        <v>286.7144470214844</v>
       </c>
       <c r="F108" t="n">
-        <v>12732500</v>
+        <v>13496500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B109" t="n">
-        <v>283.6044306839189</v>
+        <v>282.7724816341387</v>
       </c>
       <c r="C109" t="n">
-        <v>287.2195541533999</v>
+        <v>288.3189881947603</v>
       </c>
       <c r="D109" t="n">
-        <v>280.9995517042956</v>
+        <v>277.7707387954702</v>
       </c>
       <c r="E109" t="n">
-        <v>286.7144470214844</v>
+        <v>287.1502685546875</v>
       </c>
       <c r="F109" t="n">
-        <v>13496500</v>
+        <v>12241100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B110" t="n">
-        <v>282.7724816341387</v>
+        <v>286.5262662545288</v>
       </c>
       <c r="C110" t="n">
-        <v>288.3189881947603</v>
+        <v>289.9532025593205</v>
       </c>
       <c r="D110" t="n">
-        <v>277.7707387954702</v>
+        <v>284.4364084963449</v>
       </c>
       <c r="E110" t="n">
-        <v>287.1502685546875</v>
+        <v>285.9716186523438</v>
       </c>
       <c r="F110" t="n">
-        <v>12241100</v>
+        <v>8344900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B111" t="n">
-        <v>286.5262662545288</v>
+        <v>286.0508472723319</v>
       </c>
       <c r="C111" t="n">
-        <v>289.9532025593205</v>
+        <v>287.7049062038017</v>
       </c>
       <c r="D111" t="n">
-        <v>284.4364084963449</v>
+        <v>282.1385715612803</v>
       </c>
       <c r="E111" t="n">
-        <v>285.9716186523438</v>
+        <v>284.7731628417969</v>
       </c>
       <c r="F111" t="n">
-        <v>8344900</v>
+        <v>10205000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B112" t="n">
-        <v>286.0508166178312</v>
+        <v>280.1279843639117</v>
       </c>
       <c r="C112" t="n">
-        <v>287.7048753720447</v>
+        <v>281.1679713767581</v>
       </c>
       <c r="D112" t="n">
-        <v>282.1385413260368</v>
+        <v>276.4336380780354</v>
       </c>
       <c r="E112" t="n">
-        <v>284.7731323242188</v>
+        <v>280.1874389648438</v>
       </c>
       <c r="F112" t="n">
-        <v>10205000</v>
+        <v>13760500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B113" t="n">
-        <v>280.1279538528093</v>
+        <v>281.9504072447318</v>
       </c>
       <c r="C113" t="n">
-        <v>281.167940752382</v>
+        <v>284.4463214441296</v>
       </c>
       <c r="D113" t="n">
-        <v>276.4336079693154</v>
+        <v>280.2468381234208</v>
       </c>
       <c r="E113" t="n">
-        <v>280.1874084472656</v>
+        <v>280.7321472167969</v>
       </c>
       <c r="F113" t="n">
-        <v>13760500</v>
+        <v>9091200</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B114" t="n">
-        <v>281.9504072447318</v>
+        <v>283.6044205599556</v>
       </c>
       <c r="C114" t="n">
-        <v>284.4463214441296</v>
+        <v>286.506421278288</v>
       </c>
       <c r="D114" t="n">
-        <v>280.2468381234208</v>
+        <v>281.8909373944359</v>
       </c>
       <c r="E114" t="n">
-        <v>280.7321472167969</v>
+        <v>283.4261474609375</v>
       </c>
       <c r="F114" t="n">
-        <v>9091200</v>
+        <v>8149000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B115" t="n">
-        <v>283.6044205599556</v>
+        <v>286.2390279690733</v>
       </c>
       <c r="C115" t="n">
-        <v>286.506421278288</v>
+        <v>288.9726698808299</v>
       </c>
       <c r="D115" t="n">
-        <v>281.8909373944359</v>
+        <v>283.2181783456238</v>
       </c>
       <c r="E115" t="n">
-        <v>283.4261474609375</v>
+        <v>284.1492004394531</v>
       </c>
       <c r="F115" t="n">
-        <v>8149000</v>
+        <v>8961200</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B116" t="n">
-        <v>286.2390279690733</v>
+        <v>284.0897180113691</v>
       </c>
       <c r="C116" t="n">
-        <v>288.9726698808299</v>
+        <v>286.6450865635814</v>
       </c>
       <c r="D116" t="n">
-        <v>283.2181783456238</v>
+        <v>282.3960631878955</v>
       </c>
       <c r="E116" t="n">
-        <v>284.1492004394531</v>
+        <v>284.9910278320312</v>
       </c>
       <c r="F116" t="n">
-        <v>8961200</v>
+        <v>10057000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B117" t="n">
-        <v>284.0897484324327</v>
+        <v>284.1392890417467</v>
       </c>
       <c r="C117" t="n">
-        <v>286.6451172582804</v>
+        <v>286.7441681021885</v>
       </c>
       <c r="D117" t="n">
-        <v>282.3960934275981</v>
+        <v>281.900870340191</v>
       </c>
       <c r="E117" t="n">
-        <v>284.9910583496094</v>
+        <v>285.2188720703125</v>
       </c>
       <c r="F117" t="n">
-        <v>10057000</v>
+        <v>9846700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B118" t="n">
-        <v>284.1392586396808</v>
+        <v>285.3277943529036</v>
       </c>
       <c r="C118" t="n">
-        <v>286.7441374214082</v>
+        <v>287.9326733008621</v>
       </c>
       <c r="D118" t="n">
-        <v>281.9008401776293</v>
+        <v>282.5446423017302</v>
       </c>
       <c r="E118" t="n">
-        <v>285.2188415527344</v>
+        <v>283.8223266601562</v>
       </c>
       <c r="F118" t="n">
-        <v>9846700</v>
+        <v>22436500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B119" t="n">
-        <v>285.327825032355</v>
+        <v>291.4982779446762</v>
       </c>
       <c r="C119" t="n">
-        <v>287.9327042603992</v>
+        <v>292.9245231806114</v>
       </c>
       <c r="D119" t="n">
-        <v>282.5446726819272</v>
+        <v>285.2188513876401</v>
       </c>
       <c r="E119" t="n">
-        <v>283.8223571777344</v>
+        <v>287.1403198242188</v>
       </c>
       <c r="F119" t="n">
-        <v>22436500</v>
+        <v>11470800</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B120" t="n">
-        <v>291.4982779446762</v>
+        <v>283.4360748065673</v>
       </c>
       <c r="C120" t="n">
-        <v>292.9245231806114</v>
+        <v>292.6571288676103</v>
       </c>
       <c r="D120" t="n">
-        <v>285.2188513876401</v>
+        <v>282.6436995084055</v>
       </c>
       <c r="E120" t="n">
-        <v>287.1403198242188</v>
+        <v>289.6065368652344</v>
       </c>
       <c r="F120" t="n">
-        <v>11470800</v>
+        <v>11092300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B121" t="n">
-        <v>283.4360748065673</v>
+        <v>291.3398308899875</v>
       </c>
       <c r="C121" t="n">
-        <v>292.6571288676103</v>
+        <v>294.7965097163498</v>
       </c>
       <c r="D121" t="n">
-        <v>282.6436995084055</v>
+        <v>289.6461758443202</v>
       </c>
       <c r="E121" t="n">
-        <v>289.6065368652344</v>
+        <v>292.5977172851562</v>
       </c>
       <c r="F121" t="n">
-        <v>11092300</v>
+        <v>12188200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B122" t="n">
-        <v>291.3398308899875</v>
+        <v>289.7847899387647</v>
       </c>
       <c r="C122" t="n">
-        <v>294.7965097163498</v>
+        <v>292.1717693530369</v>
       </c>
       <c r="D122" t="n">
-        <v>289.6461758443202</v>
+        <v>287.9524883078727</v>
       </c>
       <c r="E122" t="n">
-        <v>292.5977172851562</v>
+        <v>288.8735961914062</v>
       </c>
       <c r="F122" t="n">
-        <v>12188200</v>
+        <v>8669200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B123" t="n">
-        <v>289.7848205526045</v>
+        <v>286.3777093696089</v>
       </c>
       <c r="C123" t="n">
-        <v>292.1718002190451</v>
+        <v>287.3384134369941</v>
       </c>
       <c r="D123" t="n">
-        <v>287.9525187281419</v>
+        <v>279.0582953832721</v>
       </c>
       <c r="E123" t="n">
-        <v>288.8736267089844</v>
+        <v>280.1378784179688</v>
       </c>
       <c r="F123" t="n">
-        <v>8669200</v>
+        <v>9873300</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B124" t="n">
-        <v>286.3777093696089</v>
+        <v>282.0197247859078</v>
       </c>
       <c r="C124" t="n">
-        <v>287.3384134369941</v>
+        <v>284.505755156032</v>
       </c>
       <c r="D124" t="n">
-        <v>279.0582953832721</v>
+        <v>279.6327451103039</v>
       </c>
       <c r="E124" t="n">
-        <v>280.1378784179688</v>
+        <v>281.0589904785156</v>
       </c>
       <c r="F124" t="n">
-        <v>9873300</v>
+        <v>11734400</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B125" t="n">
-        <v>282.0197247859078</v>
+        <v>285.7140887250632</v>
       </c>
       <c r="C125" t="n">
-        <v>284.505755156032</v>
+        <v>292.2510413422024</v>
       </c>
       <c r="D125" t="n">
-        <v>279.6327451103039</v>
+        <v>282.2277281014015</v>
       </c>
       <c r="E125" t="n">
-        <v>281.0589904785156</v>
+        <v>291.3497314453125</v>
       </c>
       <c r="F125" t="n">
-        <v>11734400</v>
+        <v>12956900</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B126" t="n">
-        <v>285.7140887250632</v>
+        <v>292.567989087923</v>
       </c>
       <c r="C126" t="n">
-        <v>292.2510413422024</v>
+        <v>295.8661624411999</v>
       </c>
       <c r="D126" t="n">
-        <v>282.2277281014015</v>
+        <v>290.1116710297465</v>
       </c>
       <c r="E126" t="n">
-        <v>291.3497314453125</v>
+        <v>292.5580749511719</v>
       </c>
       <c r="F126" t="n">
-        <v>12956900</v>
+        <v>11267200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B127" t="n">
-        <v>292.567989087923</v>
+        <v>289.1212191631598</v>
       </c>
       <c r="C127" t="n">
-        <v>295.8661624411999</v>
+        <v>292.7957669317203</v>
       </c>
       <c r="D127" t="n">
-        <v>290.1116710297465</v>
+        <v>285.9616926535428</v>
       </c>
       <c r="E127" t="n">
-        <v>292.5580749511719</v>
+        <v>291.7855224609375</v>
       </c>
       <c r="F127" t="n">
-        <v>11267200</v>
+        <v>6669300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,25 +3745,25 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B128" t="n">
-        <v>289.1212191631598</v>
+        <v>292.7412191857173</v>
       </c>
       <c r="C128" t="n">
-        <v>292.7957669317203</v>
+        <v>295.4987855589938</v>
       </c>
       <c r="D128" t="n">
-        <v>285.9616926535428</v>
+        <v>291.8850906324002</v>
       </c>
       <c r="E128" t="n">
-        <v>291.7855224609375</v>
+        <v>294.125</v>
       </c>
       <c r="F128" t="n">
-        <v>6669300</v>
+        <v>7142600</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -3771,25 +3771,25 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B129" t="n">
-        <v>292.7412191857173</v>
+        <v>291.8253790066561</v>
       </c>
       <c r="C129" t="n">
-        <v>295.4987855589938</v>
+        <v>296.8427544058445</v>
       </c>
       <c r="D129" t="n">
-        <v>291.8850906324002</v>
+        <v>291.3873498301165</v>
       </c>
       <c r="E129" t="n">
-        <v>294.125</v>
+        <v>296.0662536621094</v>
       </c>
       <c r="F129" t="n">
-        <v>7142600</v>
+        <v>7849100</v>
       </c>
       <c r="G129" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B130" t="n">
-        <v>291.8253790066561</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="C130" t="n">
-        <v>296.8427544058445</v>
+        <v>309.8640903908154</v>
       </c>
       <c r="D130" t="n">
-        <v>291.3873498301165</v>
+        <v>303.9606617936424</v>
       </c>
       <c r="E130" t="n">
-        <v>296.0662536621094</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="F130" t="n">
-        <v>7849100</v>
+        <v>10590200</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B131" t="n">
-        <v>306.5888366699219</v>
+        <v>305.5734164156603</v>
       </c>
       <c r="C131" t="n">
-        <v>309.8640903908154</v>
+        <v>309.8640846884941</v>
       </c>
       <c r="D131" t="n">
-        <v>303.9606617936424</v>
+        <v>304.73715687535</v>
       </c>
       <c r="E131" t="n">
-        <v>306.5888366699219</v>
+        <v>308.938232421875</v>
       </c>
       <c r="F131" t="n">
-        <v>10590200</v>
+        <v>6586600</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B132" t="n">
-        <v>305.5734164156603</v>
+        <v>308.6097380099313</v>
       </c>
       <c r="C132" t="n">
-        <v>309.8640846884941</v>
+        <v>308.9581744354404</v>
       </c>
       <c r="D132" t="n">
-        <v>304.73715687535</v>
+        <v>305.344449093958</v>
       </c>
       <c r="E132" t="n">
-        <v>308.938232421875</v>
+        <v>308.4803161621094</v>
       </c>
       <c r="F132" t="n">
-        <v>6586600</v>
+        <v>6069700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B133" t="n">
-        <v>308.6097380099313</v>
+        <v>306.0910825316173</v>
       </c>
       <c r="C133" t="n">
-        <v>308.9581744354404</v>
+        <v>312.3329523629397</v>
       </c>
       <c r="D133" t="n">
-        <v>305.344449093958</v>
+        <v>304.0900871089203</v>
       </c>
       <c r="E133" t="n">
-        <v>308.4803161621094</v>
+        <v>312.2732238769531</v>
       </c>
       <c r="F133" t="n">
-        <v>6069700</v>
+        <v>8318200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B134" t="n">
-        <v>306.0910825316173</v>
+        <v>308.4305432499699</v>
       </c>
       <c r="C134" t="n">
-        <v>312.3329523629397</v>
+        <v>312.9103618924516</v>
       </c>
       <c r="D134" t="n">
-        <v>304.0900871089203</v>
+        <v>307.4847916064935</v>
       </c>
       <c r="E134" t="n">
-        <v>312.2732238769531</v>
+        <v>309.7247009277344</v>
       </c>
       <c r="F134" t="n">
-        <v>8318200</v>
+        <v>11455500</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B135" t="n">
-        <v>308.4305432499699</v>
+        <v>312.5420354159922</v>
       </c>
       <c r="C135" t="n">
-        <v>312.9103618924516</v>
+        <v>312.8307129741003</v>
       </c>
       <c r="D135" t="n">
-        <v>307.4847916064935</v>
+        <v>302.8954898881459</v>
       </c>
       <c r="E135" t="n">
-        <v>309.7247009277344</v>
+        <v>304.5579833984375</v>
       </c>
       <c r="F135" t="n">
-        <v>11455500</v>
+        <v>9885800</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B136" t="n">
-        <v>312.5420354159922</v>
+        <v>303.9805907681049</v>
       </c>
       <c r="C136" t="n">
-        <v>312.8307129741003</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="D136" t="n">
-        <v>302.8954898881459</v>
+        <v>303.8312695552229</v>
       </c>
       <c r="E136" t="n">
-        <v>304.5579833984375</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="F136" t="n">
-        <v>9885800</v>
+        <v>8208600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B137" t="n">
-        <v>303.9805907681049</v>
+        <v>311.068653468178</v>
       </c>
       <c r="C137" t="n">
-        <v>308.5599670410156</v>
+        <v>313.4877482505245</v>
       </c>
       <c r="D137" t="n">
-        <v>303.8312695552229</v>
+        <v>308.6993222963794</v>
       </c>
       <c r="E137" t="n">
-        <v>308.5599670410156</v>
+        <v>308.8984375</v>
       </c>
       <c r="F137" t="n">
-        <v>8208600</v>
+        <v>11082400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B138" t="n">
-        <v>311.068653468178</v>
+        <v>309.4559416581444</v>
       </c>
       <c r="C138" t="n">
-        <v>313.4877482505245</v>
+        <v>315.7077766193834</v>
       </c>
       <c r="D138" t="n">
-        <v>308.6993222963794</v>
+        <v>308.9780833700189</v>
       </c>
       <c r="E138" t="n">
-        <v>308.8984375</v>
+        <v>315.5683898925781</v>
       </c>
       <c r="F138" t="n">
-        <v>11082400</v>
+        <v>10772000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B139" t="n">
-        <v>309.4559416581444</v>
+        <v>316.0661368489313</v>
       </c>
       <c r="C139" t="n">
-        <v>315.7077766193834</v>
+        <v>318.8038038717339</v>
       </c>
       <c r="D139" t="n">
-        <v>308.9780833700189</v>
+        <v>311.3474041387296</v>
       </c>
       <c r="E139" t="n">
-        <v>315.5683898925781</v>
+        <v>311.5962829589844</v>
       </c>
       <c r="F139" t="n">
-        <v>10772000</v>
+        <v>7084300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B140" t="n">
-        <v>316.0661368489313</v>
+        <v>313.4379903862348</v>
       </c>
       <c r="C140" t="n">
-        <v>318.8038038717339</v>
+        <v>313.7366328164263</v>
       </c>
       <c r="D140" t="n">
-        <v>311.3474041387296</v>
+        <v>310.5410372905177</v>
       </c>
       <c r="E140" t="n">
-        <v>311.5962829589844</v>
+        <v>311.6161804199219</v>
       </c>
       <c r="F140" t="n">
-        <v>7084300</v>
+        <v>5545900</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B141" t="n">
-        <v>313.4379903862348</v>
+        <v>312.1139549773267</v>
       </c>
       <c r="C141" t="n">
-        <v>313.7366328164263</v>
+        <v>313.5773637260273</v>
       </c>
       <c r="D141" t="n">
-        <v>310.5410372905177</v>
+        <v>307.5047445243564</v>
       </c>
       <c r="E141" t="n">
-        <v>311.6161804199219</v>
+        <v>310.2921752929688</v>
       </c>
       <c r="F141" t="n">
-        <v>5545900</v>
+        <v>6969700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B142" t="n">
-        <v>312.1139549773267</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="C142" t="n">
-        <v>313.5773637260273</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="D142" t="n">
-        <v>307.5047445243564</v>
+        <v>306.5092257615542</v>
       </c>
       <c r="E142" t="n">
-        <v>310.2921752929688</v>
+        <v>306.8974609375</v>
       </c>
       <c r="F142" t="n">
-        <v>6969700</v>
+        <v>5215300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B143" t="n">
-        <v>309.7545850384977</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="C143" t="n">
-        <v>309.7545850384977</v>
+        <v>311.1781431330245</v>
       </c>
       <c r="D143" t="n">
-        <v>306.5092257615542</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="E143" t="n">
-        <v>306.8974609375</v>
+        <v>310.232421875</v>
       </c>
       <c r="F143" t="n">
-        <v>5215300</v>
+        <v>7925300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B144" t="n">
-        <v>305.5037244427344</v>
+        <v>313.7864355589005</v>
       </c>
       <c r="C144" t="n">
-        <v>311.1781431330245</v>
+        <v>314.035314384572</v>
       </c>
       <c r="D144" t="n">
-        <v>305.5037244427344</v>
+        <v>309.7745101043047</v>
       </c>
       <c r="E144" t="n">
-        <v>310.232421875</v>
+        <v>310.0532531738281</v>
       </c>
       <c r="F144" t="n">
-        <v>7925300</v>
+        <v>7398600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B145" t="n">
-        <v>313.7864355589005</v>
+        <v>309.1771855961317</v>
       </c>
       <c r="C145" t="n">
-        <v>314.035314384572</v>
+        <v>310.6505287563671</v>
       </c>
       <c r="D145" t="n">
-        <v>309.7745101043047</v>
+        <v>305.9118967162461</v>
       </c>
       <c r="E145" t="n">
-        <v>310.0532531738281</v>
+        <v>307.8630981445312</v>
       </c>
       <c r="F145" t="n">
-        <v>7398600</v>
+        <v>8031800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B146" t="n">
-        <v>309.1771855961317</v>
+        <v>305.6928786901284</v>
       </c>
       <c r="C146" t="n">
-        <v>310.6505287563671</v>
+        <v>312.6913497643884</v>
       </c>
       <c r="D146" t="n">
-        <v>305.9118967162461</v>
+        <v>305.1951210592971</v>
       </c>
       <c r="E146" t="n">
-        <v>307.8630981445312</v>
+        <v>311.8252563476562</v>
       </c>
       <c r="F146" t="n">
-        <v>8031800</v>
+        <v>8865400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B147" t="n">
-        <v>305.6928786901284</v>
+        <v>312.5420381202088</v>
       </c>
       <c r="C147" t="n">
-        <v>312.6913497643884</v>
+        <v>314.6624601726697</v>
       </c>
       <c r="D147" t="n">
-        <v>305.1951210592971</v>
+        <v>310.431520181067</v>
       </c>
       <c r="E147" t="n">
-        <v>311.8252563476562</v>
+        <v>311.0686645507812</v>
       </c>
       <c r="F147" t="n">
-        <v>8865400</v>
+        <v>6135400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B148" t="n">
-        <v>312.5420381202088</v>
+        <v>309.2269452093906</v>
       </c>
       <c r="C148" t="n">
-        <v>314.6624601726697</v>
+        <v>309.2568094519629</v>
       </c>
       <c r="D148" t="n">
-        <v>310.431520181067</v>
+        <v>305.1353920734132</v>
       </c>
       <c r="E148" t="n">
-        <v>311.0686645507812</v>
+        <v>306.270263671875</v>
       </c>
       <c r="F148" t="n">
-        <v>6135400</v>
+        <v>7338200</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B149" t="n">
-        <v>309.2269452093906</v>
+        <v>306.3299974055641</v>
       </c>
       <c r="C149" t="n">
-        <v>309.2568094519629</v>
+        <v>309.5753869306937</v>
       </c>
       <c r="D149" t="n">
-        <v>305.1353920734132</v>
+        <v>305.42407485773</v>
       </c>
       <c r="E149" t="n">
-        <v>306.270263671875</v>
+        <v>308.0124206542969</v>
       </c>
       <c r="F149" t="n">
-        <v>7338200</v>
+        <v>6316800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B150" t="n">
-        <v>306.3299974055641</v>
+        <v>310.0532528884956</v>
       </c>
       <c r="C150" t="n">
-        <v>309.5753869306937</v>
+        <v>314.8416790595512</v>
       </c>
       <c r="D150" t="n">
-        <v>305.42407485773</v>
+        <v>309.9536952821754</v>
       </c>
       <c r="E150" t="n">
-        <v>308.0124206542969</v>
+        <v>313.4877624511719</v>
       </c>
       <c r="F150" t="n">
-        <v>6316800</v>
+        <v>8629500</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B151" t="n">
-        <v>310.0532528884956</v>
+        <v>313.2388767644321</v>
       </c>
       <c r="C151" t="n">
-        <v>314.8416790595512</v>
+        <v>314.8814709002291</v>
       </c>
       <c r="D151" t="n">
-        <v>309.9536952821754</v>
+        <v>304.7670623908274</v>
       </c>
       <c r="E151" t="n">
-        <v>313.4877624511719</v>
+        <v>304.8964538574219</v>
       </c>
       <c r="F151" t="n">
-        <v>8629500</v>
+        <v>8359600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B152" t="n">
-        <v>313.2388767644321</v>
+        <v>306.8675912418493</v>
       </c>
       <c r="C152" t="n">
-        <v>314.8814709002291</v>
+        <v>307.6042628420606</v>
       </c>
       <c r="D152" t="n">
-        <v>304.7670623908274</v>
+        <v>299.1523476664256</v>
       </c>
       <c r="E152" t="n">
-        <v>304.8964538574219</v>
+        <v>300.7451782226562</v>
       </c>
       <c r="F152" t="n">
-        <v>8359600</v>
+        <v>9464300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B153" t="n">
-        <v>306.8675912418493</v>
+        <v>300.7451596100784</v>
       </c>
       <c r="C153" t="n">
-        <v>307.6042628420606</v>
+        <v>301.8302675742967</v>
       </c>
       <c r="D153" t="n">
-        <v>299.1523476664256</v>
+        <v>297.5395993270601</v>
       </c>
       <c r="E153" t="n">
-        <v>300.7451782226562</v>
+        <v>298.6545715332031</v>
       </c>
       <c r="F153" t="n">
-        <v>9464300</v>
+        <v>9512000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B154" t="n">
-        <v>300.7451596100784</v>
+        <v>298.6744753830843</v>
       </c>
       <c r="C154" t="n">
-        <v>301.8302675742967</v>
+        <v>304.6873960201211</v>
       </c>
       <c r="D154" t="n">
-        <v>297.5395993270601</v>
+        <v>294.2245209852311</v>
       </c>
       <c r="E154" t="n">
-        <v>298.6545715332031</v>
+        <v>303.5126953125</v>
       </c>
       <c r="F154" t="n">
-        <v>9512000</v>
+        <v>9498200</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B155" t="n">
-        <v>298.6744753830843</v>
+        <v>300.9144028967509</v>
       </c>
       <c r="C155" t="n">
-        <v>304.6873960201211</v>
+        <v>301.6411400127173</v>
       </c>
       <c r="D155" t="n">
-        <v>294.2245209852311</v>
+        <v>298.7242874353194</v>
       </c>
       <c r="E155" t="n">
-        <v>303.5126953125</v>
+        <v>298.9034729003906</v>
       </c>
       <c r="F155" t="n">
-        <v>9498200</v>
+        <v>7709500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B156" t="n">
-        <v>300.9144028967509</v>
+        <v>300.8945046380796</v>
       </c>
       <c r="C156" t="n">
-        <v>301.6411400127173</v>
+        <v>302.387777613951</v>
       </c>
       <c r="D156" t="n">
-        <v>298.7242874353194</v>
+        <v>297.4699295162906</v>
       </c>
       <c r="E156" t="n">
-        <v>298.9034729003906</v>
+        <v>298.5650024414062</v>
       </c>
       <c r="F156" t="n">
-        <v>7709500</v>
+        <v>7364300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B157" t="n">
-        <v>300.8945046380796</v>
+        <v>298.8636262885424</v>
       </c>
       <c r="C157" t="n">
-        <v>302.387777613951</v>
+        <v>299.4410421498196</v>
       </c>
       <c r="D157" t="n">
-        <v>297.4699295162906</v>
+        <v>295.1205095874812</v>
       </c>
       <c r="E157" t="n">
-        <v>298.5650024414062</v>
+        <v>296.4743957519531</v>
       </c>
       <c r="F157" t="n">
-        <v>7364300</v>
+        <v>8699300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B158" t="n">
-        <v>298.8636262885424</v>
+        <v>296.6635495230975</v>
       </c>
       <c r="C158" t="n">
-        <v>299.4410421498196</v>
+        <v>299.908939014877</v>
       </c>
       <c r="D158" t="n">
-        <v>295.1205095874812</v>
+        <v>295.8870488301784</v>
       </c>
       <c r="E158" t="n">
-        <v>296.4743957519531</v>
+        <v>299.3813171386719</v>
       </c>
       <c r="F158" t="n">
-        <v>8699300</v>
+        <v>7546300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B159" t="n">
-        <v>296.6635495230975</v>
+        <v>299.7396822358739</v>
       </c>
       <c r="C159" t="n">
-        <v>299.908939014877</v>
+        <v>300.436555061437</v>
       </c>
       <c r="D159" t="n">
-        <v>295.8870488301784</v>
+        <v>293.935841710235</v>
       </c>
       <c r="E159" t="n">
-        <v>299.3813171386719</v>
+        <v>294.3738708496094</v>
       </c>
       <c r="F159" t="n">
-        <v>7546300</v>
+        <v>8066900</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B160" t="n">
-        <v>299.7396822358739</v>
+        <v>295.3694126574367</v>
       </c>
       <c r="C160" t="n">
-        <v>300.436555061437</v>
+        <v>301.57145376365</v>
       </c>
       <c r="D160" t="n">
-        <v>293.935841710235</v>
+        <v>292.3530024013792</v>
       </c>
       <c r="E160" t="n">
-        <v>294.3738708496094</v>
+        <v>300.625732421875</v>
       </c>
       <c r="F160" t="n">
-        <v>8066900</v>
+        <v>9327000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B161" t="n">
-        <v>295.3694126574367</v>
+        <v>299.8790926087445</v>
       </c>
       <c r="C161" t="n">
-        <v>301.57145376365</v>
+        <v>302.6167597554335</v>
       </c>
       <c r="D161" t="n">
-        <v>292.3530024013792</v>
+        <v>298.8636475324957</v>
       </c>
       <c r="E161" t="n">
-        <v>300.625732421875</v>
+        <v>301.6411437988281</v>
       </c>
       <c r="F161" t="n">
-        <v>9327000</v>
+        <v>7874400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B162" t="n">
-        <v>299.8790926087445</v>
+        <v>303.3135932887391</v>
       </c>
       <c r="C162" t="n">
-        <v>302.6167597554335</v>
+        <v>306.0711901040885</v>
       </c>
       <c r="D162" t="n">
-        <v>298.8636475324957</v>
+        <v>302.4773640852478</v>
       </c>
       <c r="E162" t="n">
-        <v>301.6411437988281</v>
+        <v>305.0059814453125</v>
       </c>
       <c r="F162" t="n">
-        <v>7874400</v>
+        <v>5973900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B163" t="n">
-        <v>303.3135932887391</v>
+        <v>307.1065011172144</v>
       </c>
       <c r="C163" t="n">
-        <v>306.0711901040885</v>
+        <v>308.5400455607295</v>
       </c>
       <c r="D163" t="n">
-        <v>302.4773640852478</v>
+        <v>304.0701916446211</v>
       </c>
       <c r="E163" t="n">
-        <v>305.0059814453125</v>
+        <v>305.3643493652344</v>
       </c>
       <c r="F163" t="n">
-        <v>5973900</v>
+        <v>7725400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B164" t="n">
-        <v>307.1065011172144</v>
+        <v>303.6321536663258</v>
       </c>
       <c r="C164" t="n">
-        <v>308.5400455607295</v>
+        <v>304.5281113223131</v>
       </c>
       <c r="D164" t="n">
-        <v>304.0701916446211</v>
+        <v>294.4236375305438</v>
       </c>
       <c r="E164" t="n">
-        <v>305.3643493652344</v>
+        <v>297.9378051757812</v>
       </c>
       <c r="F164" t="n">
-        <v>7725400</v>
+        <v>11779200</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B165" t="n">
-        <v>303.6321536663258</v>
+        <v>296.2354906683788</v>
       </c>
       <c r="C165" t="n">
-        <v>304.5281113223131</v>
+        <v>299.7197941661088</v>
       </c>
       <c r="D165" t="n">
-        <v>294.4236375305438</v>
+        <v>294.4236455581874</v>
       </c>
       <c r="E165" t="n">
-        <v>297.9378051757812</v>
+        <v>295.3992614746094</v>
       </c>
       <c r="F165" t="n">
-        <v>11779200</v>
+        <v>9757700</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B166" t="n">
-        <v>296.2354906683788</v>
+        <v>295.070728717322</v>
       </c>
       <c r="C166" t="n">
-        <v>299.7197941661088</v>
+        <v>298.5351328968941</v>
       </c>
       <c r="D166" t="n">
-        <v>294.4236455581874</v>
+        <v>293.8761285862639</v>
       </c>
       <c r="E166" t="n">
-        <v>295.3992614746094</v>
+        <v>297.9676818847656</v>
       </c>
       <c r="F166" t="n">
-        <v>9757700</v>
+        <v>13969000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B167" t="n">
-        <v>295.070728717322</v>
+        <v>296.3549462063085</v>
       </c>
       <c r="C167" t="n">
-        <v>298.5351328968941</v>
+        <v>298.2065900448191</v>
       </c>
       <c r="D167" t="n">
-        <v>293.8761285862639</v>
+        <v>293.9457858606032</v>
       </c>
       <c r="E167" t="n">
-        <v>297.9676818847656</v>
+        <v>295.2499084472656</v>
       </c>
       <c r="F167" t="n">
-        <v>13969000</v>
+        <v>7930000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B168" t="n">
-        <v>296.3549462063085</v>
+        <v>295.170270518017</v>
       </c>
       <c r="C168" t="n">
-        <v>298.2065900448191</v>
+        <v>300.7152977310929</v>
       </c>
       <c r="D168" t="n">
-        <v>293.9457858606032</v>
+        <v>293.9457758280521</v>
       </c>
       <c r="E168" t="n">
-        <v>295.2499084472656</v>
+        <v>299.6102600097656</v>
       </c>
       <c r="F168" t="n">
-        <v>7930000</v>
+        <v>8296200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B169" t="n">
-        <v>295.170270518017</v>
+        <v>298.5749714904202</v>
       </c>
       <c r="C169" t="n">
-        <v>300.7152977310929</v>
+        <v>300.6058008918799</v>
       </c>
       <c r="D169" t="n">
-        <v>293.9457758280521</v>
+        <v>295.2300241797341</v>
       </c>
       <c r="E169" t="n">
-        <v>299.6102600097656</v>
+        <v>299.5007934570312</v>
       </c>
       <c r="F169" t="n">
-        <v>8296200</v>
+        <v>7003900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B170" t="n">
-        <v>298.5749714904202</v>
+        <v>304.3688300919619</v>
       </c>
       <c r="C170" t="n">
-        <v>300.6058008918799</v>
+        <v>311.5066879726736</v>
       </c>
       <c r="D170" t="n">
-        <v>295.2300241797341</v>
+        <v>303.0746723882986</v>
       </c>
       <c r="E170" t="n">
-        <v>299.5007934570312</v>
+        <v>309.4957580566406</v>
       </c>
       <c r="F170" t="n">
-        <v>7003900</v>
+        <v>10345200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B171" t="n">
-        <v>304.3688300919619</v>
+        <v>312.8805189963161</v>
       </c>
       <c r="C171" t="n">
-        <v>311.5066879726736</v>
+        <v>313.5873263681962</v>
       </c>
       <c r="D171" t="n">
-        <v>303.0746723882986</v>
+        <v>308.211549706599</v>
       </c>
       <c r="E171" t="n">
-        <v>309.4957580566406</v>
+        <v>310.9691162109375</v>
       </c>
       <c r="F171" t="n">
-        <v>10345200</v>
+        <v>9118800</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B172" t="n">
-        <v>312.8805189963161</v>
+        <v>311.8451695343703</v>
       </c>
       <c r="C172" t="n">
-        <v>313.5873263681962</v>
+        <v>314.881479064701</v>
       </c>
       <c r="D172" t="n">
-        <v>308.211549706599</v>
+        <v>309.3862455138746</v>
       </c>
       <c r="E172" t="n">
-        <v>310.9691162109375</v>
+        <v>309.7147521972656</v>
       </c>
       <c r="F172" t="n">
-        <v>9118800</v>
+        <v>6827000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B173" t="n">
-        <v>311.8451695343703</v>
+        <v>312.1040028799189</v>
       </c>
       <c r="C173" t="n">
-        <v>314.881479064701</v>
+        <v>315.0009559692908</v>
       </c>
       <c r="D173" t="n">
-        <v>309.3862455138746</v>
+        <v>307.6241841525692</v>
       </c>
       <c r="E173" t="n">
-        <v>309.7147521972656</v>
+        <v>311.2976379394531</v>
       </c>
       <c r="F173" t="n">
-        <v>6827000</v>
+        <v>11594600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B174" t="n">
-        <v>312.1040028799189</v>
+        <v>311.1582462393224</v>
       </c>
       <c r="C174" t="n">
-        <v>315.0009559692908</v>
+        <v>313.3384270822022</v>
       </c>
       <c r="D174" t="n">
-        <v>307.6241841525692</v>
+        <v>307.6440785979976</v>
       </c>
       <c r="E174" t="n">
-        <v>311.2976379394531</v>
+        <v>307.7536010742188</v>
       </c>
       <c r="F174" t="n">
-        <v>11594600</v>
+        <v>7446200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B175" t="n">
-        <v>311.1582462393224</v>
+        <v>308.1717081621576</v>
       </c>
       <c r="C175" t="n">
-        <v>313.3384270822022</v>
+        <v>313.3085706612414</v>
       </c>
       <c r="D175" t="n">
-        <v>307.6440785979976</v>
+        <v>307.4947650619962</v>
       </c>
       <c r="E175" t="n">
-        <v>307.7536010742188</v>
+        <v>312.0840759277344</v>
       </c>
       <c r="F175" t="n">
-        <v>7446200</v>
+        <v>9116600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B176" t="n">
-        <v>308.1717081621576</v>
+        <v>314.5529794375797</v>
       </c>
       <c r="C176" t="n">
-        <v>313.3085706612414</v>
+        <v>319.8590627688811</v>
       </c>
       <c r="D176" t="n">
-        <v>307.4947650619962</v>
+        <v>314.1348496322589</v>
       </c>
       <c r="E176" t="n">
-        <v>312.0840759277344</v>
+        <v>319.2816772460938</v>
       </c>
       <c r="F176" t="n">
-        <v>9116600</v>
+        <v>7426200</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B177" t="n">
-        <v>314.5529794375797</v>
+        <v>322.4673390673774</v>
       </c>
       <c r="C177" t="n">
-        <v>319.8590627688811</v>
+        <v>324.4583697274161</v>
       </c>
       <c r="D177" t="n">
-        <v>314.1348496322589</v>
+        <v>317.4101041776777</v>
       </c>
       <c r="E177" t="n">
-        <v>319.2816772460938</v>
+        <v>317.9675903320312</v>
       </c>
       <c r="F177" t="n">
-        <v>7426200</v>
+        <v>7988900</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B178" t="n">
-        <v>322.4673390673774</v>
+        <v>322.8455866314347</v>
       </c>
       <c r="C178" t="n">
-        <v>324.4583697274161</v>
+        <v>330.2621874699331</v>
       </c>
       <c r="D178" t="n">
-        <v>317.4101041776777</v>
+        <v>322.5668435738929</v>
       </c>
       <c r="E178" t="n">
-        <v>317.9675903320312</v>
+        <v>329.6549377441406</v>
       </c>
       <c r="F178" t="n">
-        <v>7988900</v>
+        <v>11094900</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B179" t="n">
-        <v>322.8455866314347</v>
+        <v>330.6902497468859</v>
       </c>
       <c r="C179" t="n">
-        <v>330.2621874699331</v>
+        <v>336.2551763704633</v>
       </c>
       <c r="D179" t="n">
-        <v>322.5668435738929</v>
+        <v>330.0133066656099</v>
       </c>
       <c r="E179" t="n">
-        <v>329.6549377441406</v>
+        <v>331.9645080566406</v>
       </c>
       <c r="F179" t="n">
-        <v>11094900</v>
+        <v>12246400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B180" t="n">
-        <v>330.6902497468859</v>
+        <v>335.4388795655989</v>
       </c>
       <c r="C180" t="n">
-        <v>336.2551763704633</v>
+        <v>336.5737511659094</v>
       </c>
       <c r="D180" t="n">
-        <v>330.0133066656099</v>
+        <v>322.7062308624821</v>
       </c>
       <c r="E180" t="n">
-        <v>331.9645080566406</v>
+        <v>323.761474609375</v>
       </c>
       <c r="F180" t="n">
-        <v>12246400</v>
+        <v>20111000</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B181" t="n">
-        <v>335.4388795655989</v>
+        <v>328.221392261561</v>
       </c>
       <c r="C181" t="n">
-        <v>336.5737511659094</v>
+        <v>331.2776010100568</v>
       </c>
       <c r="D181" t="n">
-        <v>322.7062308624821</v>
+        <v>325.2846101022313</v>
       </c>
       <c r="E181" t="n">
-        <v>323.761474609375</v>
+        <v>329.993408203125</v>
       </c>
       <c r="F181" t="n">
-        <v>20111000</v>
+        <v>10182500</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B182" t="n">
-        <v>328.221392261561</v>
+        <v>327.9924099173137</v>
       </c>
       <c r="C182" t="n">
-        <v>331.2776010100568</v>
+        <v>333.8659438033595</v>
       </c>
       <c r="D182" t="n">
-        <v>325.2846101022313</v>
+        <v>325.7425357353925</v>
       </c>
       <c r="E182" t="n">
-        <v>329.993408203125</v>
+        <v>332.6414794921875</v>
       </c>
       <c r="F182" t="n">
-        <v>10182500</v>
+        <v>7582200</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B183" t="n">
-        <v>327.9924099173137</v>
+        <v>331.5762891678024</v>
       </c>
       <c r="C183" t="n">
-        <v>333.8659438033595</v>
+        <v>333.0297330031709</v>
       </c>
       <c r="D183" t="n">
-        <v>325.7425357353925</v>
+        <v>328.291070440402</v>
       </c>
       <c r="E183" t="n">
-        <v>332.6414794921875</v>
+        <v>331.95458984375</v>
       </c>
       <c r="F183" t="n">
-        <v>7582200</v>
+        <v>7907400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B184" t="n">
-        <v>331.5762891678024</v>
+        <v>333.4577793441399</v>
       </c>
       <c r="C184" t="n">
-        <v>333.0297330031709</v>
+        <v>341.909724468194</v>
       </c>
       <c r="D184" t="n">
-        <v>328.291070440402</v>
+        <v>333.2586945227413</v>
       </c>
       <c r="E184" t="n">
-        <v>331.95458984375</v>
+        <v>333.6170654296875</v>
       </c>
       <c r="F184" t="n">
-        <v>7907400</v>
+        <v>10043100</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B185" t="n">
-        <v>333.4577793441399</v>
+        <v>334.4931229022353</v>
       </c>
       <c r="C185" t="n">
-        <v>341.909724468194</v>
+        <v>334.8913229247855</v>
       </c>
       <c r="D185" t="n">
-        <v>333.2586945227413</v>
+        <v>326.0312433050061</v>
       </c>
       <c r="E185" t="n">
-        <v>333.6170654296875</v>
+        <v>327.5742797851562</v>
       </c>
       <c r="F185" t="n">
-        <v>10043100</v>
+        <v>17640900</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B186" t="n">
-        <v>334.4931229022353</v>
+        <v>326.8077430430495</v>
       </c>
       <c r="C186" t="n">
-        <v>334.8913229247855</v>
+        <v>330.8993264933345</v>
       </c>
       <c r="D186" t="n">
-        <v>326.0312433050061</v>
+        <v>325.7325999471821</v>
       </c>
       <c r="E186" t="n">
-        <v>327.5742797851562</v>
+        <v>327.9127807617188</v>
       </c>
       <c r="F186" t="n">
-        <v>17640900</v>
+        <v>7981800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B187" t="n">
-        <v>326.8077430430495</v>
+        <v>327.4150312810326</v>
       </c>
       <c r="C187" t="n">
-        <v>330.8993264933345</v>
+        <v>328.9580677951163</v>
       </c>
       <c r="D187" t="n">
-        <v>325.7325999471821</v>
+        <v>325.2149206632551</v>
       </c>
       <c r="E187" t="n">
-        <v>327.9127807617188</v>
+        <v>325.8619995117188</v>
       </c>
       <c r="F187" t="n">
-        <v>7981800</v>
+        <v>8080100</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B188" t="n">
-        <v>327.4150312810326</v>
+        <v>326.8973584256916</v>
       </c>
       <c r="C188" t="n">
-        <v>328.9580677951163</v>
+        <v>334.1347741939035</v>
       </c>
       <c r="D188" t="n">
-        <v>325.2149206632551</v>
+        <v>323.5524415571975</v>
       </c>
       <c r="E188" t="n">
-        <v>325.8619995117188</v>
+        <v>332.5718078613281</v>
       </c>
       <c r="F188" t="n">
-        <v>8080100</v>
+        <v>15210200</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B189" t="n">
-        <v>326.8973584256916</v>
+        <v>336.5040683580973</v>
       </c>
       <c r="C189" t="n">
-        <v>334.1347741939035</v>
+        <v>338.4751995750331</v>
       </c>
       <c r="D189" t="n">
-        <v>323.5524415571975</v>
+        <v>330.2820977776739</v>
       </c>
       <c r="E189" t="n">
-        <v>332.5718078613281</v>
+        <v>332.9700012207031</v>
       </c>
       <c r="F189" t="n">
-        <v>15210200</v>
+        <v>8413900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,25 +5357,25 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B190" t="n">
-        <v>336.5040683580973</v>
+        <v>335</v>
       </c>
       <c r="C190" t="n">
-        <v>338.4751995750331</v>
+        <v>339.7200012207031</v>
       </c>
       <c r="D190" t="n">
-        <v>330.2820977776739</v>
+        <v>334.1099853515625</v>
       </c>
       <c r="E190" t="n">
-        <v>332.9700012207031</v>
+        <v>337.7200012207031</v>
       </c>
       <c r="F190" t="n">
-        <v>8413900</v>
+        <v>8673500</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5383,25 +5383,25 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B191" t="n">
-        <v>335</v>
+        <v>340.9800109863281</v>
       </c>
       <c r="C191" t="n">
-        <v>339.7200012207031</v>
+        <v>341.3999938964844</v>
       </c>
       <c r="D191" t="n">
-        <v>334.1099853515625</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E191" t="n">
-        <v>337.7200012207031</v>
+        <v>339.2200012207031</v>
       </c>
       <c r="F191" t="n">
-        <v>8673500</v>
+        <v>7115800</v>
       </c>
       <c r="G191" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B192" t="n">
-        <v>340.9800109863281</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="C192" t="n">
-        <v>341.3999938964844</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="D192" t="n">
-        <v>337.0899963378906</v>
+        <v>330.1300048828125</v>
       </c>
       <c r="E192" t="n">
-        <v>339.2200012207031</v>
+        <v>330.6199951171875</v>
       </c>
       <c r="F192" t="n">
-        <v>7115800</v>
+        <v>18505200</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B193" t="n">
-        <v>336.5299987792969</v>
+        <v>331.4599914550781</v>
       </c>
       <c r="C193" t="n">
-        <v>336.5299987792969</v>
+        <v>337</v>
       </c>
       <c r="D193" t="n">
-        <v>330.1300048828125</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="E193" t="n">
-        <v>330.6199951171875</v>
+        <v>335.4700012207031</v>
       </c>
       <c r="F193" t="n">
-        <v>18505200</v>
+        <v>15570600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B194" t="n">
-        <v>331.4599914550781</v>
+        <v>337.4700012207031</v>
       </c>
       <c r="C194" t="n">
-        <v>337</v>
+        <v>338.5899963378906</v>
       </c>
       <c r="D194" t="n">
-        <v>330.8099975585938</v>
+        <v>335.7699890136719</v>
       </c>
       <c r="E194" t="n">
-        <v>335.4700012207031</v>
+        <v>336.4700012207031</v>
       </c>
       <c r="F194" t="n">
-        <v>15570600</v>
+        <v>6299000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B195" t="n">
-        <v>337.4700012207031</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="C195" t="n">
-        <v>338.5899963378906</v>
+        <v>338.3500061035156</v>
       </c>
       <c r="D195" t="n">
-        <v>335.7699890136719</v>
+        <v>332.5</v>
       </c>
       <c r="E195" t="n">
-        <v>336.4700012207031</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="F195" t="n">
-        <v>6299000</v>
+        <v>7120300</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B196" t="n">
-        <v>338.3399963378906</v>
+        <v>327</v>
       </c>
       <c r="C196" t="n">
-        <v>338.3500061035156</v>
+        <v>344.7300109863281</v>
       </c>
       <c r="D196" t="n">
-        <v>332.5</v>
+        <v>325.75</v>
       </c>
       <c r="E196" t="n">
-        <v>334.5299987792969</v>
+        <v>342.8900146484375</v>
       </c>
       <c r="F196" t="n">
-        <v>7120300</v>
+        <v>14537900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>327</v>
+        <v>345.8500061035156</v>
       </c>
       <c r="C197" t="n">
-        <v>344.7300109863281</v>
+        <v>351.239990234375</v>
       </c>
       <c r="D197" t="n">
-        <v>325.75</v>
+        <v>344.0499877929688</v>
       </c>
       <c r="E197" t="n">
-        <v>342.8900146484375</v>
+        <v>346.9100036621094</v>
       </c>
       <c r="F197" t="n">
-        <v>14537900</v>
+        <v>10750000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B198" t="n">
-        <v>345.8500061035156</v>
+        <v>349.2799987792969</v>
       </c>
       <c r="C198" t="n">
-        <v>351.239990234375</v>
+        <v>349.3399963378906</v>
       </c>
       <c r="D198" t="n">
-        <v>344.0499877929688</v>
+        <v>341.1099853515625</v>
       </c>
       <c r="E198" t="n">
-        <v>346.9100036621094</v>
+        <v>343.1499938964844</v>
       </c>
       <c r="F198" t="n">
-        <v>10750000</v>
+        <v>12432400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B199" t="n">
-        <v>349.2799987792969</v>
+        <v>339.0299987792969</v>
       </c>
       <c r="C199" t="n">
-        <v>349.3399963378906</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="D199" t="n">
-        <v>341.1099853515625</v>
+        <v>335.0499877929688</v>
       </c>
       <c r="E199" t="n">
-        <v>343.1499938964844</v>
+        <v>341.1000061035156</v>
       </c>
       <c r="F199" t="n">
-        <v>12432400</v>
+        <v>9250900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B200" t="n">
-        <v>339.0299987792969</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="C200" t="n">
-        <v>346.1300048828125</v>
+        <v>344.260009765625</v>
       </c>
       <c r="D200" t="n">
-        <v>335.0499877929688</v>
+        <v>337.3699951171875</v>
       </c>
       <c r="E200" t="n">
-        <v>341.1000061035156</v>
+        <v>338.8699951171875</v>
       </c>
       <c r="F200" t="n">
-        <v>9250900</v>
+        <v>7723300</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B201" t="n">
-        <v>341.7999877929688</v>
+        <v>340.1199951171875</v>
       </c>
       <c r="C201" t="n">
-        <v>344.260009765625</v>
+        <v>345.739990234375</v>
       </c>
       <c r="D201" t="n">
-        <v>337.3699951171875</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E201" t="n">
-        <v>338.8699951171875</v>
+        <v>345.2300109863281</v>
       </c>
       <c r="F201" t="n">
-        <v>7723300</v>
+        <v>6015300</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B202" t="n">
-        <v>340.1199951171875</v>
+        <v>345.0700073242188</v>
       </c>
       <c r="C202" t="n">
-        <v>345.739990234375</v>
+        <v>349.0700073242188</v>
       </c>
       <c r="D202" t="n">
-        <v>337.2999877929688</v>
+        <v>344.25</v>
       </c>
       <c r="E202" t="n">
-        <v>345.2300109863281</v>
+        <v>348.2099914550781</v>
       </c>
       <c r="F202" t="n">
-        <v>6015300</v>
+        <v>8040200</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B203" t="n">
-        <v>345.0700073242188</v>
+        <v>346.5799865722656</v>
       </c>
       <c r="C203" t="n">
-        <v>349.0700073242188</v>
+        <v>349.9200134277344</v>
       </c>
       <c r="D203" t="n">
-        <v>344.25</v>
+        <v>345.4200134277344</v>
       </c>
       <c r="E203" t="n">
-        <v>348.2099914550781</v>
+        <v>349.8999938964844</v>
       </c>
       <c r="F203" t="n">
-        <v>8040200</v>
+        <v>10913000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B204" t="n">
-        <v>346.5799865722656</v>
+        <v>350.6400146484375</v>
       </c>
       <c r="C204" t="n">
-        <v>349.9200134277344</v>
+        <v>353.3699951171875</v>
       </c>
       <c r="D204" t="n">
-        <v>345.4200134277344</v>
+        <v>347.5</v>
       </c>
       <c r="E204" t="n">
-        <v>349.8999938964844</v>
+        <v>353.2099914550781</v>
       </c>
       <c r="F204" t="n">
-        <v>10913000</v>
+        <v>7520800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B205" t="n">
-        <v>350.6400146484375</v>
+        <v>357.8900146484375</v>
       </c>
       <c r="C205" t="n">
-        <v>353.3699951171875</v>
+        <v>359.0499877929688</v>
       </c>
       <c r="D205" t="n">
-        <v>347.5</v>
+        <v>352.5799865722656</v>
       </c>
       <c r="E205" t="n">
-        <v>353.2099914550781</v>
+        <v>356.2000122070312</v>
       </c>
       <c r="F205" t="n">
-        <v>7520800</v>
+        <v>7884900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B206" t="n">
-        <v>357.8900146484375</v>
+        <v>357.2999877929688</v>
       </c>
       <c r="C206" t="n">
-        <v>359.0499877929688</v>
+        <v>359.2999877929688</v>
       </c>
       <c r="D206" t="n">
-        <v>352.5799865722656</v>
+        <v>354.1499938964844</v>
       </c>
       <c r="E206" t="n">
-        <v>356.2000122070312</v>
+        <v>357.3099975585938</v>
       </c>
       <c r="F206" t="n">
-        <v>7884900</v>
+        <v>6533800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B207" t="n">
-        <v>357.2999877929688</v>
+        <v>356.5</v>
       </c>
       <c r="C207" t="n">
-        <v>359.2999877929688</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D207" t="n">
-        <v>354.1499938964844</v>
+        <v>343.7799987792969</v>
       </c>
       <c r="E207" t="n">
-        <v>357.3099975585938</v>
+        <v>344.7099914550781</v>
       </c>
       <c r="F207" t="n">
-        <v>6533800</v>
+        <v>8265300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B208" t="n">
-        <v>356.5</v>
+        <v>347.5400085449219</v>
       </c>
       <c r="C208" t="n">
-        <v>357.3699951171875</v>
+        <v>352.2799987792969</v>
       </c>
       <c r="D208" t="n">
-        <v>343.7799987792969</v>
+        <v>345.3699951171875</v>
       </c>
       <c r="E208" t="n">
-        <v>344.7099914550781</v>
+        <v>350.8500061035156</v>
       </c>
       <c r="F208" t="n">
-        <v>8265300</v>
+        <v>7606500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B209" t="n">
-        <v>347.5400085449219</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C209" t="n">
-        <v>352.2799987792969</v>
+        <v>354.4700012207031</v>
       </c>
       <c r="D209" t="n">
-        <v>345.3699951171875</v>
+        <v>349.7000122070312</v>
       </c>
       <c r="E209" t="n">
-        <v>350.8500061035156</v>
+        <v>351.7900085449219</v>
       </c>
       <c r="F209" t="n">
-        <v>7606500</v>
+        <v>6603400</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B210" t="n">
-        <v>353.2999877929688</v>
+        <v>353.75</v>
       </c>
       <c r="C210" t="n">
-        <v>354.4700012207031</v>
+        <v>355.6199951171875</v>
       </c>
       <c r="D210" t="n">
-        <v>349.7000122070312</v>
+        <v>350.8399963378906</v>
       </c>
       <c r="E210" t="n">
-        <v>351.7900085449219</v>
+        <v>352.6400146484375</v>
       </c>
       <c r="F210" t="n">
-        <v>6603400</v>
+        <v>6436600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B211" t="n">
-        <v>353.75</v>
+        <v>355</v>
       </c>
       <c r="C211" t="n">
-        <v>355.6199951171875</v>
+        <v>363</v>
       </c>
       <c r="D211" t="n">
-        <v>350.8399963378906</v>
+        <v>353.8699951171875</v>
       </c>
       <c r="E211" t="n">
-        <v>352.6400146484375</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F211" t="n">
-        <v>6436600</v>
+        <v>8477200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B212" t="n">
-        <v>355</v>
+        <v>358.9700012207031</v>
       </c>
       <c r="C212" t="n">
-        <v>363</v>
+        <v>362.1700134277344</v>
       </c>
       <c r="D212" t="n">
-        <v>353.8699951171875</v>
+        <v>358.2000122070312</v>
       </c>
       <c r="E212" t="n">
-        <v>357.5199890136719</v>
+        <v>359.239990234375</v>
       </c>
       <c r="F212" t="n">
-        <v>8477200</v>
+        <v>5269500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B213" t="n">
-        <v>358.9700012207031</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="C213" t="n">
-        <v>362.1700134277344</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="D213" t="n">
-        <v>358.2000122070312</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="E213" t="n">
-        <v>359.239990234375</v>
+        <v>356.2999877929688</v>
       </c>
       <c r="F213" t="n">
-        <v>5269500</v>
+        <v>5820100</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B214" t="n">
-        <v>362.8099975585938</v>
+        <v>355.760009765625</v>
       </c>
       <c r="C214" t="n">
-        <v>362.8099975585938</v>
+        <v>358.8500061035156</v>
       </c>
       <c r="D214" t="n">
-        <v>354.9500122070312</v>
+        <v>353.3299865722656</v>
       </c>
       <c r="E214" t="n">
-        <v>356.2999877929688</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F214" t="n">
-        <v>5820100</v>
+        <v>4566200</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B215" t="n">
-        <v>355.760009765625</v>
+        <v>357.9599914550781</v>
       </c>
       <c r="C215" t="n">
-        <v>358.8500061035156</v>
+        <v>359.989990234375</v>
       </c>
       <c r="D215" t="n">
-        <v>353.3299865722656</v>
+        <v>356.5</v>
       </c>
       <c r="E215" t="n">
-        <v>357.5199890136719</v>
+        <v>359.7900085449219</v>
       </c>
       <c r="F215" t="n">
-        <v>4566200</v>
+        <v>5327500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B216" t="n">
-        <v>357.9599914550781</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="C216" t="n">
-        <v>359.989990234375</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="D216" t="n">
-        <v>356.5</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="E216" t="n">
-        <v>359.7900085449219</v>
+        <v>362.0400085449219</v>
       </c>
       <c r="F216" t="n">
-        <v>5327500</v>
+        <v>4576500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B217" t="n">
-        <v>360.0499877929688</v>
+        <v>362.9700012207031</v>
       </c>
       <c r="C217" t="n">
-        <v>363.1199951171875</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="D217" t="n">
-        <v>358.6000061035156</v>
+        <v>361.2999877929688</v>
       </c>
       <c r="E217" t="n">
-        <v>362.0400085449219</v>
+        <v>365.1799926757812</v>
       </c>
       <c r="F217" t="n">
-        <v>4576500</v>
+        <v>4366800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B218" t="n">
-        <v>362.9700012207031</v>
+        <v>366.5</v>
       </c>
       <c r="C218" t="n">
-        <v>366.0899963378906</v>
+        <v>366.5</v>
       </c>
       <c r="D218" t="n">
-        <v>361.2999877929688</v>
+        <v>361.5199890136719</v>
       </c>
       <c r="E218" t="n">
-        <v>365.1799926757812</v>
+        <v>363.1099853515625</v>
       </c>
       <c r="F218" t="n">
-        <v>4366800</v>
+        <v>5102700</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B219" t="n">
-        <v>366.5</v>
+        <v>363</v>
       </c>
       <c r="C219" t="n">
-        <v>366.5</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="D219" t="n">
-        <v>361.5199890136719</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="E219" t="n">
-        <v>363.1099853515625</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="F219" t="n">
-        <v>5102700</v>
+        <v>5058600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B220" t="n">
-        <v>363</v>
+        <v>361.9400024414062</v>
       </c>
       <c r="C220" t="n">
-        <v>365.8999938964844</v>
+        <v>365.75</v>
       </c>
       <c r="D220" t="n">
-        <v>361.4500122070312</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="E220" t="n">
-        <v>362.8399963378906</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="F220" t="n">
-        <v>5058600</v>
+        <v>5282600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B221" t="n">
-        <v>361.9400024414062</v>
+        <v>362.3399963378906</v>
       </c>
       <c r="C221" t="n">
-        <v>365.75</v>
+        <v>363.5700073242188</v>
       </c>
       <c r="D221" t="n">
-        <v>360.9599914550781</v>
+        <v>359.2699890136719</v>
       </c>
       <c r="E221" t="n">
-        <v>360.9599914550781</v>
+        <v>363.25</v>
       </c>
       <c r="F221" t="n">
-        <v>5282600</v>
+        <v>5525100</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B222" t="n">
-        <v>362.3399963378906</v>
+        <v>363.010009765625</v>
       </c>
       <c r="C222" t="n">
-        <v>363.5700073242188</v>
+        <v>363.0499877929688</v>
       </c>
       <c r="D222" t="n">
-        <v>359.2699890136719</v>
+        <v>355.6499938964844</v>
       </c>
       <c r="E222" t="n">
-        <v>363.25</v>
+        <v>357.260009765625</v>
       </c>
       <c r="F222" t="n">
-        <v>5525100</v>
+        <v>6696200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B223" t="n">
-        <v>363.010009765625</v>
+        <v>357.6000061035156</v>
       </c>
       <c r="C223" t="n">
-        <v>363.0499877929688</v>
+        <v>357.9500122070312</v>
       </c>
       <c r="D223" t="n">
-        <v>355.6499938964844</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E223" t="n">
-        <v>357.260009765625</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="F223" t="n">
-        <v>6696200</v>
+        <v>6799700</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B224" t="n">
-        <v>357.6000061035156</v>
+        <v>354.0700073242188</v>
       </c>
       <c r="C224" t="n">
-        <v>357.9500122070312</v>
+        <v>356.8599853515625</v>
       </c>
       <c r="D224" t="n">
-        <v>351.5499877929688</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="E224" t="n">
-        <v>351.5499877929688</v>
+        <v>351.5799865722656</v>
       </c>
       <c r="F224" t="n">
-        <v>6799700</v>
+        <v>8112100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B225" t="n">
-        <v>354.0700073242188</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C225" t="n">
-        <v>356.8599853515625</v>
+        <v>358.2799987792969</v>
       </c>
       <c r="D225" t="n">
-        <v>350.3699951171875</v>
+        <v>352.8200073242188</v>
       </c>
       <c r="E225" t="n">
-        <v>351.5799865722656</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="F225" t="n">
-        <v>8112100</v>
+        <v>4394400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B226" t="n">
-        <v>353.2999877929688</v>
+        <v>357</v>
       </c>
       <c r="C226" t="n">
-        <v>358.2799987792969</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D226" t="n">
-        <v>352.8200073242188</v>
+        <v>353.0700073242188</v>
       </c>
       <c r="E226" t="n">
-        <v>356.3900146484375</v>
+        <v>356.6900024414062</v>
       </c>
       <c r="F226" t="n">
-        <v>4394400</v>
+        <v>4298000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B227" t="n">
-        <v>357</v>
+        <v>356.5</v>
       </c>
       <c r="C227" t="n">
-        <v>357.3699951171875</v>
+        <v>358.3500061035156</v>
       </c>
       <c r="D227" t="n">
-        <v>353.0700073242188</v>
+        <v>354.6000061035156</v>
       </c>
       <c r="E227" t="n">
-        <v>356.6900024414062</v>
+        <v>356.5</v>
       </c>
       <c r="F227" t="n">
-        <v>4298000</v>
+        <v>5796500</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B228" t="n">
-        <v>356.5</v>
+        <v>354.6799926757812</v>
       </c>
       <c r="C228" t="n">
-        <v>358.3500061035156</v>
+        <v>357.5700073242188</v>
       </c>
       <c r="D228" t="n">
-        <v>354.6000061035156</v>
+        <v>352.2300109863281</v>
       </c>
       <c r="E228" t="n">
-        <v>356.5</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="F228" t="n">
-        <v>5796500</v>
+        <v>5209900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B229" t="n">
-        <v>354.6799926757812</v>
+        <v>355.6700134277344</v>
       </c>
       <c r="C229" t="n">
-        <v>357.5700073242188</v>
+        <v>358.7300109863281</v>
       </c>
       <c r="D229" t="n">
-        <v>352.2300109863281</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="E229" t="n">
-        <v>354.2200012207031</v>
+        <v>357.6199951171875</v>
       </c>
       <c r="F229" t="n">
-        <v>5209900</v>
+        <v>3914500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B230" t="n">
-        <v>355.6700134277344</v>
+        <v>355.8999938964844</v>
       </c>
       <c r="C230" t="n">
-        <v>358.7300109863281</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="D230" t="n">
-        <v>354.2200012207031</v>
+        <v>354.7699890136719</v>
       </c>
       <c r="E230" t="n">
-        <v>357.6199951171875</v>
+        <v>356.0199890136719</v>
       </c>
       <c r="F230" t="n">
-        <v>3914500</v>
+        <v>7962900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B231" t="n">
-        <v>355.8999938964844</v>
+        <v>355.7300109863281</v>
       </c>
       <c r="C231" t="n">
-        <v>357.7699890136719</v>
+        <v>359.9299926757812</v>
       </c>
       <c r="D231" t="n">
-        <v>354.7699890136719</v>
+        <v>354.1199951171875</v>
       </c>
       <c r="E231" t="n">
-        <v>356.0199890136719</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="F231" t="n">
-        <v>7962900</v>
+        <v>5079000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B232" t="n">
-        <v>355.7300109863281</v>
+        <v>357.5499877929688</v>
       </c>
       <c r="C232" t="n">
-        <v>359.9299926757812</v>
+        <v>361.4700012207031</v>
       </c>
       <c r="D232" t="n">
-        <v>354.1199951171875</v>
+        <v>353.7900085449219</v>
       </c>
       <c r="E232" t="n">
-        <v>354.9500122070312</v>
+        <v>356.2200012207031</v>
       </c>
       <c r="F232" t="n">
-        <v>5079000</v>
+        <v>5341400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B233" t="n">
-        <v>357.5499877929688</v>
+        <v>358.6799926757812</v>
       </c>
       <c r="C233" t="n">
-        <v>361.4700012207031</v>
+        <v>362.8500061035156</v>
       </c>
       <c r="D233" t="n">
-        <v>353.7900085449219</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="E233" t="n">
-        <v>356.2200012207031</v>
+        <v>362.0599975585938</v>
       </c>
       <c r="F233" t="n">
-        <v>5341400</v>
+        <v>5414200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B234" t="n">
-        <v>358.6799926757812</v>
+        <v>361</v>
       </c>
       <c r="C234" t="n">
-        <v>362.8500061035156</v>
+        <v>362.8599853515625</v>
       </c>
       <c r="D234" t="n">
-        <v>356.3900146484375</v>
+        <v>355.2000122070312</v>
       </c>
       <c r="E234" t="n">
-        <v>362.0599975585938</v>
+        <v>358.6400146484375</v>
       </c>
       <c r="F234" t="n">
-        <v>5414200</v>
+        <v>4873500</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B235" t="n">
-        <v>361</v>
+        <v>357.1000061035156</v>
       </c>
       <c r="C235" t="n">
-        <v>362.8599853515625</v>
+        <v>358.5499877929688</v>
       </c>
       <c r="D235" t="n">
-        <v>355.2000122070312</v>
+        <v>353.2300109863281</v>
       </c>
       <c r="E235" t="n">
-        <v>358.6400146484375</v>
+        <v>353.510009765625</v>
       </c>
       <c r="F235" t="n">
-        <v>4873500</v>
+        <v>5631400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B236" t="n">
-        <v>357.1000061035156</v>
+        <v>352</v>
       </c>
       <c r="C236" t="n">
-        <v>358.5499877929688</v>
+        <v>356.3299865722656</v>
       </c>
       <c r="D236" t="n">
-        <v>353.2300109863281</v>
+        <v>348.6900024414062</v>
       </c>
       <c r="E236" t="n">
-        <v>353.510009765625</v>
+        <v>354.7099914550781</v>
       </c>
       <c r="F236" t="n">
-        <v>5631400</v>
+        <v>6318200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B237" t="n">
-        <v>352</v>
+        <v>353.510009765625</v>
       </c>
       <c r="C237" t="n">
-        <v>356.3299865722656</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="D237" t="n">
-        <v>348.6900024414062</v>
+        <v>351.1199951171875</v>
       </c>
       <c r="E237" t="n">
-        <v>354.7099914550781</v>
+        <v>353.5599975585938</v>
       </c>
       <c r="F237" t="n">
-        <v>6318200</v>
+        <v>4184200</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B238" t="n">
-        <v>353.510009765625</v>
+        <v>358.3200073242188</v>
       </c>
       <c r="C238" t="n">
-        <v>354.2200012207031</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="D238" t="n">
-        <v>351.1199951171875</v>
+        <v>354.7900085449219</v>
       </c>
       <c r="E238" t="n">
-        <v>353.5599975585938</v>
+        <v>356.2300109863281</v>
       </c>
       <c r="F238" t="n">
-        <v>4184200</v>
+        <v>5354600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B239" t="n">
-        <v>358.3200073242188</v>
+        <v>354.2300109863281</v>
       </c>
       <c r="C239" t="n">
-        <v>360.0499877929688</v>
+        <v>355.2799987792969</v>
       </c>
       <c r="D239" t="n">
-        <v>354.7900085449219</v>
+        <v>347.5499877929688</v>
       </c>
       <c r="E239" t="n">
-        <v>356.2300109863281</v>
+        <v>350.1300048828125</v>
       </c>
       <c r="F239" t="n">
-        <v>5354600</v>
+        <v>9609900</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B240" t="n">
-        <v>354.2300109863281</v>
+        <v>351</v>
       </c>
       <c r="C240" t="n">
-        <v>355.2799987792969</v>
+        <v>354.7000122070312</v>
       </c>
       <c r="D240" t="n">
-        <v>347.5499877929688</v>
+        <v>343.0700073242188</v>
       </c>
       <c r="E240" t="n">
-        <v>350.1300048828125</v>
+        <v>352.489990234375</v>
       </c>
       <c r="F240" t="n">
-        <v>9609900</v>
+        <v>14026500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B241" t="n">
-        <v>351</v>
+        <v>353.3800048828125</v>
       </c>
       <c r="C241" t="n">
-        <v>354.7000122070312</v>
+        <v>355.6000061035156</v>
       </c>
       <c r="D241" t="n">
-        <v>343.0700073242188</v>
+        <v>344.6900024414062</v>
       </c>
       <c r="E241" t="n">
-        <v>352.489990234375</v>
+        <v>348.9200134277344</v>
       </c>
       <c r="F241" t="n">
-        <v>14026500</v>
+        <v>8303400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B242" t="n">
-        <v>353.3800048828125</v>
+        <v>352.25</v>
       </c>
       <c r="C242" t="n">
-        <v>355.6000061035156</v>
+        <v>353.489990234375</v>
       </c>
       <c r="D242" t="n">
-        <v>344.6900024414062</v>
+        <v>345.2699890136719</v>
       </c>
       <c r="E242" t="n">
-        <v>348.9200134277344</v>
+        <v>349.3099975585938</v>
       </c>
       <c r="F242" t="n">
-        <v>8303400</v>
+        <v>6480100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B243" t="n">
-        <v>352.25</v>
+        <v>347.8900146484375</v>
       </c>
       <c r="C243" t="n">
-        <v>353.489990234375</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="D243" t="n">
-        <v>345.2699890136719</v>
+        <v>345.010009765625</v>
       </c>
       <c r="E243" t="n">
-        <v>349.3099975585938</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="F243" t="n">
-        <v>6480100</v>
+        <v>18312400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B244" t="n">
-        <v>347.8900146484375</v>
+        <v>353.6700134277344</v>
       </c>
       <c r="C244" t="n">
-        <v>349.6700134277344</v>
+        <v>354.5</v>
       </c>
       <c r="D244" t="n">
-        <v>345.010009765625</v>
+        <v>350.0799865722656</v>
       </c>
       <c r="E244" t="n">
-        <v>349.6700134277344</v>
+        <v>352.0400085449219</v>
       </c>
       <c r="F244" t="n">
-        <v>18312400</v>
+        <v>6414700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B245" t="n">
-        <v>353.6700134277344</v>
+        <v>352</v>
       </c>
       <c r="C245" t="n">
-        <v>354.5</v>
+        <v>352.1000061035156</v>
       </c>
       <c r="D245" t="n">
-        <v>350.0799865722656</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E245" t="n">
-        <v>352.0400085449219</v>
+        <v>340</v>
       </c>
       <c r="F245" t="n">
-        <v>6414700</v>
+        <v>11485600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B246" t="n">
-        <v>352</v>
+        <v>337.6099853515625</v>
       </c>
       <c r="C246" t="n">
-        <v>352.1000061035156</v>
+        <v>341.4400024414062</v>
       </c>
       <c r="D246" t="n">
-        <v>337.2999877929688</v>
+        <v>336.9800109863281</v>
       </c>
       <c r="E246" t="n">
-        <v>340</v>
+        <v>337.5299987792969</v>
       </c>
       <c r="F246" t="n">
-        <v>11485600</v>
+        <v>7068500</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B247" t="n">
-        <v>337.6099853515625</v>
+        <v>338.1199951171875</v>
       </c>
       <c r="C247" t="n">
-        <v>341.4400024414062</v>
+        <v>339.3699951171875</v>
       </c>
       <c r="D247" t="n">
-        <v>336.9800109863281</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="E247" t="n">
-        <v>337.5299987792969</v>
+        <v>338.5599975585938</v>
       </c>
       <c r="F247" t="n">
-        <v>7068500</v>
+        <v>6934300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B248" t="n">
-        <v>338.1199951171875</v>
+        <v>340.7699890136719</v>
       </c>
       <c r="C248" t="n">
-        <v>339.3699951171875</v>
+        <v>343.3099975585938</v>
       </c>
       <c r="D248" t="n">
-        <v>335.2799987792969</v>
+        <v>338.6400146484375</v>
       </c>
       <c r="E248" t="n">
-        <v>338.5599975585938</v>
+        <v>343.0599975585938</v>
       </c>
       <c r="F248" t="n">
-        <v>6934300</v>
+        <v>11460300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B249" t="n">
-        <v>340.7699890136719</v>
+        <v>341.8299865722656</v>
       </c>
       <c r="C249" t="n">
-        <v>343.3099975585938</v>
+        <v>342</v>
       </c>
       <c r="D249" t="n">
-        <v>338.6400146484375</v>
+        <v>336.2999877929688</v>
       </c>
       <c r="E249" t="n">
-        <v>343.0599975585938</v>
+        <v>336.5899963378906</v>
       </c>
       <c r="F249" t="n">
-        <v>11460300</v>
+        <v>10483700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B250" t="n">
-        <v>341.8299865722656</v>
+        <v>337</v>
       </c>
       <c r="C250" t="n">
-        <v>342</v>
+        <v>338.75</v>
       </c>
       <c r="D250" t="n">
-        <v>336.2999877929688</v>
+        <v>333.3299865722656</v>
       </c>
       <c r="E250" t="n">
-        <v>336.5899963378906</v>
+        <v>334.9800109863281</v>
       </c>
       <c r="F250" t="n">
-        <v>10483700</v>
+        <v>7254900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B251" t="n">
-        <v>337</v>
+        <v>334.8900146484375</v>
       </c>
       <c r="C251" t="n">
-        <v>338.75</v>
+        <v>336.3399963378906</v>
       </c>
       <c r="D251" t="n">
-        <v>333.3299865722656</v>
+        <v>330.8299865722656</v>
       </c>
       <c r="E251" t="n">
-        <v>334.9800109863281</v>
+        <v>330.8299865722656</v>
       </c>
       <c r="F251" t="n">
-        <v>7254900</v>
+        <v>9113300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B252" t="n">
-        <v>334.8900146484375</v>
+        <v>328.75</v>
       </c>
       <c r="C252" t="n">
-        <v>336.3399963378906</v>
+        <v>333.5799865722656</v>
       </c>
       <c r="D252" t="n">
-        <v>330.8299865722656</v>
+        <v>325.8699951171875</v>
       </c>
       <c r="E252" t="n">
-        <v>330.8299865722656</v>
+        <v>333.1799926757812</v>
       </c>
       <c r="F252" t="n">
-        <v>9113300</v>
+        <v>8160000</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10017,37 +10017,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>333.18</v>
+      </c>
+      <c r="D2" t="n">
         <v>330.83</v>
       </c>
-      <c r="D2" t="n">
-        <v>334.98</v>
-      </c>
       <c r="E2" t="n">
-        <v>334.89</v>
+        <v>328.75</v>
       </c>
       <c r="F2" t="n">
-        <v>336.34</v>
+        <v>333.58</v>
       </c>
       <c r="G2" t="n">
-        <v>330.83</v>
+        <v>325.87</v>
       </c>
       <c r="H2" t="n">
-        <v>9109409</v>
+        <v>8061036</v>
       </c>
       <c r="I2" t="n">
-        <v>7658070</v>
+        <v>7677139</v>
       </c>
       <c r="J2" t="n">
-        <v>879407726592</v>
+        <v>885654487040</v>
       </c>
       <c r="K2" t="n">
-        <v>14.346487</v>
+        <v>14.262842</v>
       </c>
       <c r="L2" t="n">
-        <v>13.207034</v>
+        <v>13.318027</v>
       </c>
       <c r="M2" t="n">
-        <v>23.06</v>
+        <v>23.36</v>
       </c>
       <c r="N2" t="n">
         <v>366.5</v>
@@ -10059,7 +10059,7 @@
         <v>0.975</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R2" t="n">
         <v>0.34921002</v>
@@ -10087,7 +10087,7 @@
         <v>133.007</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4873126</v>
+        <v>2.5049808</v>
       </c>
       <c r="Z2" t="n">
         <v>0.469</v>
@@ -10099,7 +10099,7 @@
         <v>186328006656</v>
       </c>
       <c r="AC2" t="n">
-        <v>717335756800</v>
+        <v>723582451712</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:02:45</t>
+          <t>2026-10-02 19:38:27</t>
         </is>
       </c>
     </row>

--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B2" t="n">
-        <v>304.1807853263183</v>
+        <v>302.7188095956571</v>
       </c>
       <c r="C2" t="n">
-        <v>304.7302708010082</v>
+        <v>305.809673335546</v>
       </c>
       <c r="D2" t="n">
-        <v>300.3932583082978</v>
+        <v>302.4244230832239</v>
       </c>
       <c r="E2" t="n">
-        <v>301.7767639160156</v>
+        <v>304.2102661132812</v>
       </c>
       <c r="F2" t="n">
-        <v>7600000</v>
+        <v>6029900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,25 +495,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B3" t="n">
-        <v>302.7187488597389</v>
+        <v>305.8371035459471</v>
       </c>
       <c r="C3" t="n">
-        <v>305.8096119794931</v>
+        <v>307.3851288987199</v>
       </c>
       <c r="D3" t="n">
-        <v>302.4243624063698</v>
+        <v>300.8578215934895</v>
       </c>
       <c r="E3" t="n">
-        <v>304.210205078125</v>
+        <v>304.8511047363281</v>
       </c>
       <c r="F3" t="n">
-        <v>6029900</v>
+        <v>7214500</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -521,25 +521,25 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B4" t="n">
-        <v>305.8371035459471</v>
+        <v>305.0187502270194</v>
       </c>
       <c r="C4" t="n">
-        <v>307.3851288987199</v>
+        <v>305.6695130787729</v>
       </c>
       <c r="D4" t="n">
-        <v>300.8578215934895</v>
+        <v>300.4338615931582</v>
       </c>
       <c r="E4" t="n">
-        <v>304.8511047363281</v>
+        <v>303.3819885253906</v>
       </c>
       <c r="F4" t="n">
-        <v>7214500</v>
+        <v>8454200</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B5" t="n">
-        <v>305.0187809092415</v>
+        <v>303.894722712774</v>
       </c>
       <c r="C5" t="n">
-        <v>305.6695438264559</v>
+        <v>304.4567493262524</v>
       </c>
       <c r="D5" t="n">
-        <v>300.4338918141804</v>
+        <v>299.2999640741864</v>
       </c>
       <c r="E5" t="n">
-        <v>303.3820190429688</v>
+        <v>299.7732543945312</v>
       </c>
       <c r="F5" t="n">
-        <v>8454200</v>
+        <v>6489900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B6" t="n">
-        <v>303.8946917756213</v>
+        <v>300.7789375021521</v>
       </c>
       <c r="C6" t="n">
-        <v>304.4567183318842</v>
+        <v>303.7270945284432</v>
       </c>
       <c r="D6" t="n">
-        <v>299.2999336047902</v>
+        <v>299.1422058887319</v>
       </c>
       <c r="E6" t="n">
-        <v>299.7732238769531</v>
+        <v>301.2522277832031</v>
       </c>
       <c r="F6" t="n">
-        <v>6489900</v>
+        <v>7060300</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B7" t="n">
-        <v>300.7789070325195</v>
+        <v>301.3804193716138</v>
       </c>
       <c r="C7" t="n">
-        <v>303.7270637601551</v>
+        <v>306.1230715472904</v>
       </c>
       <c r="D7" t="n">
-        <v>299.1421755849041</v>
+        <v>296.5983188157025</v>
       </c>
       <c r="E7" t="n">
-        <v>301.252197265625</v>
+        <v>296.6772155761719</v>
       </c>
       <c r="F7" t="n">
-        <v>7060300</v>
+        <v>8597400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B8" t="n">
-        <v>301.3804193716138</v>
+        <v>301.321238204041</v>
       </c>
       <c r="C8" t="n">
-        <v>306.1230715472904</v>
+        <v>305.1271791148808</v>
       </c>
       <c r="D8" t="n">
-        <v>296.5983188157025</v>
+        <v>301.173344402637</v>
       </c>
       <c r="E8" t="n">
-        <v>296.6772155761719</v>
+        <v>303.6580505371094</v>
       </c>
       <c r="F8" t="n">
-        <v>8597400</v>
+        <v>10788700</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B9" t="n">
-        <v>301.3212684867699</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C9" t="n">
-        <v>305.1272097801061</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D9" t="n">
-        <v>301.1733746705027</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E9" t="n">
-        <v>303.6580810546875</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F9" t="n">
-        <v>10788700</v>
+        <v>16178800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B10" t="n">
-        <v>301.5578902761218</v>
+        <v>302.1001843350741</v>
       </c>
       <c r="C10" t="n">
-        <v>302.7016525742085</v>
+        <v>307.7499381556482</v>
       </c>
       <c r="D10" t="n">
-        <v>290.0907186231138</v>
+        <v>301.1634734465224</v>
       </c>
       <c r="E10" t="n">
-        <v>297.8505249023438</v>
+        <v>301.4099731445312</v>
       </c>
       <c r="F10" t="n">
-        <v>16178800</v>
+        <v>11354800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B11" t="n">
-        <v>302.1002149225357</v>
+        <v>301.0747572360179</v>
       </c>
       <c r="C11" t="n">
-        <v>307.7499693151439</v>
+        <v>304.3581201926382</v>
       </c>
       <c r="D11" t="n">
-        <v>301.1635039391426</v>
+        <v>292.9106878973514</v>
       </c>
       <c r="E11" t="n">
-        <v>301.4100036621094</v>
+        <v>294.360107421875</v>
       </c>
       <c r="F11" t="n">
-        <v>11354800</v>
+        <v>10549400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B12" t="n">
-        <v>301.0747260223031</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C12" t="n">
-        <v>304.358088638523</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D12" t="n">
-        <v>292.9106575300408</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E12" t="n">
-        <v>294.3600769042969</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F12" t="n">
-        <v>10549400</v>
+        <v>10153500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B13" t="n">
-        <v>294.9714335987563</v>
+        <v>294.3206459359216</v>
       </c>
       <c r="C13" t="n">
-        <v>295.3559575215809</v>
+        <v>299.4379821870563</v>
       </c>
       <c r="D13" t="n">
-        <v>290.0808874955599</v>
+        <v>293.9854099500461</v>
       </c>
       <c r="E13" t="n">
-        <v>293.3938293457031</v>
+        <v>298.1265869140625</v>
       </c>
       <c r="F13" t="n">
-        <v>10153500</v>
+        <v>6894900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B14" t="n">
-        <v>294.3206459359216</v>
+        <v>297.436411288458</v>
       </c>
       <c r="C14" t="n">
-        <v>299.4379821870563</v>
+        <v>299.7929328501146</v>
       </c>
       <c r="D14" t="n">
-        <v>293.9854099500461</v>
+        <v>292.8416531202475</v>
       </c>
       <c r="E14" t="n">
-        <v>298.1265869140625</v>
+        <v>292.9303894042969</v>
       </c>
       <c r="F14" t="n">
-        <v>6894900</v>
+        <v>7372700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B15" t="n">
-        <v>297.4363803014411</v>
+        <v>293.6008552074487</v>
       </c>
       <c r="C15" t="n">
-        <v>299.7929016175946</v>
+        <v>293.8868032880077</v>
       </c>
       <c r="D15" t="n">
-        <v>292.841622611914</v>
+        <v>286.4721030595595</v>
       </c>
       <c r="E15" t="n">
-        <v>292.9303588867188</v>
+        <v>289.9920959472656</v>
       </c>
       <c r="F15" t="n">
-        <v>7372700</v>
+        <v>8054100</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B16" t="n">
-        <v>293.6008861047978</v>
+        <v>290.2583437522712</v>
       </c>
       <c r="C16" t="n">
-        <v>293.8868342154489</v>
+        <v>292.2204718178062</v>
       </c>
       <c r="D16" t="n">
-        <v>286.4721332067081</v>
+        <v>288.4145307332595</v>
       </c>
       <c r="E16" t="n">
-        <v>289.9921264648438</v>
+        <v>290.4161071777344</v>
       </c>
       <c r="F16" t="n">
-        <v>8054100</v>
+        <v>5438800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B17" t="n">
-        <v>290.2583437522712</v>
+        <v>291.9345194575729</v>
       </c>
       <c r="C17" t="n">
-        <v>292.2204718178062</v>
+        <v>298.3632510673837</v>
       </c>
       <c r="D17" t="n">
-        <v>288.4145307332595</v>
+        <v>291.3133654724136</v>
       </c>
       <c r="E17" t="n">
-        <v>290.4161071777344</v>
+        <v>296.2334899902344</v>
       </c>
       <c r="F17" t="n">
-        <v>5438800</v>
+        <v>7228300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B18" t="n">
-        <v>291.9345194575729</v>
+        <v>297.92941246883</v>
       </c>
       <c r="C18" t="n">
-        <v>298.3632510673837</v>
+        <v>300.2662249001909</v>
       </c>
       <c r="D18" t="n">
-        <v>291.3133654724136</v>
+        <v>296.7955198233114</v>
       </c>
       <c r="E18" t="n">
-        <v>296.2334899902344</v>
+        <v>299.8915405273438</v>
       </c>
       <c r="F18" t="n">
-        <v>7228300</v>
+        <v>5642200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B19" t="n">
-        <v>297.92941246883</v>
+        <v>300.5915953010157</v>
       </c>
       <c r="C19" t="n">
-        <v>300.2662249001909</v>
+        <v>303.6580673748709</v>
       </c>
       <c r="D19" t="n">
-        <v>296.7955198233114</v>
+        <v>298.915415308335</v>
       </c>
       <c r="E19" t="n">
-        <v>299.8915405273438</v>
+        <v>301.0845947265625</v>
       </c>
       <c r="F19" t="n">
-        <v>5642200</v>
+        <v>6336000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B20" t="n">
-        <v>300.5915953010157</v>
+        <v>299.2605157595805</v>
       </c>
       <c r="C20" t="n">
-        <v>303.6580673748709</v>
+        <v>303.9341406042103</v>
       </c>
       <c r="D20" t="n">
-        <v>298.915415308335</v>
+        <v>298.7675163425421</v>
       </c>
       <c r="E20" t="n">
-        <v>301.0845947265625</v>
+        <v>301.2325134277344</v>
       </c>
       <c r="F20" t="n">
-        <v>6336000</v>
+        <v>7520300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B21" t="n">
-        <v>299.2605157595805</v>
+        <v>301.5085931686638</v>
       </c>
       <c r="C21" t="n">
-        <v>303.9341406042103</v>
+        <v>308.2330823767899</v>
       </c>
       <c r="D21" t="n">
-        <v>298.7675163425421</v>
+        <v>300.828251563059</v>
       </c>
       <c r="E21" t="n">
-        <v>301.2325134277344</v>
+        <v>305.1074829101562</v>
       </c>
       <c r="F21" t="n">
-        <v>7520300</v>
+        <v>7514600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B22" t="n">
-        <v>301.5086233262724</v>
+        <v>304.2200828300273</v>
       </c>
       <c r="C22" t="n">
-        <v>308.233113206998</v>
+        <v>308.4894444595929</v>
       </c>
       <c r="D22" t="n">
-        <v>300.8282816526182</v>
+        <v>302.9481359332913</v>
       </c>
       <c r="E22" t="n">
-        <v>305.1075134277344</v>
+        <v>306.7639465332031</v>
       </c>
       <c r="F22" t="n">
-        <v>7514600</v>
+        <v>7721300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B23" t="n">
-        <v>304.220113094536</v>
+        <v>306.6456604912348</v>
       </c>
       <c r="C23" t="n">
-        <v>308.4894751488275</v>
+        <v>307.9471862719047</v>
       </c>
       <c r="D23" t="n">
-        <v>302.9481660712639</v>
+        <v>301.9227172950412</v>
       </c>
       <c r="E23" t="n">
-        <v>306.7639770507812</v>
+        <v>305.0187683105469</v>
       </c>
       <c r="F23" t="n">
-        <v>7721300</v>
+        <v>7770000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B24" t="n">
-        <v>306.6456604912348</v>
+        <v>302.415720333495</v>
       </c>
       <c r="C24" t="n">
-        <v>307.9471862719047</v>
+        <v>307.8485840116909</v>
       </c>
       <c r="D24" t="n">
-        <v>301.9227172950412</v>
+        <v>300.8282765156093</v>
       </c>
       <c r="E24" t="n">
-        <v>305.0187683105469</v>
+        <v>304.920166015625</v>
       </c>
       <c r="F24" t="n">
-        <v>7770000</v>
+        <v>7085200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B25" t="n">
-        <v>302.415720333495</v>
+        <v>305.2751066360906</v>
       </c>
       <c r="C25" t="n">
-        <v>307.8485840116909</v>
+        <v>308.7162632770978</v>
       </c>
       <c r="D25" t="n">
-        <v>300.8282765156093</v>
+        <v>301.3508502506656</v>
       </c>
       <c r="E25" t="n">
-        <v>304.920166015625</v>
+        <v>307.3161315917969</v>
       </c>
       <c r="F25" t="n">
-        <v>7085200</v>
+        <v>6865200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B26" t="n">
-        <v>305.2750763211935</v>
+        <v>306.6357687557767</v>
       </c>
       <c r="C26" t="n">
-        <v>308.7162326204817</v>
+        <v>310.4318702971036</v>
       </c>
       <c r="D26" t="n">
-        <v>301.350820325461</v>
+        <v>305.9160088624015</v>
       </c>
       <c r="E26" t="n">
-        <v>307.3161010742188</v>
+        <v>309.0317687988281</v>
       </c>
       <c r="F26" t="n">
-        <v>6865200</v>
+        <v>7206100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B27" t="n">
-        <v>306.6357990367445</v>
+        <v>307.5232049313688</v>
       </c>
       <c r="C27" t="n">
-        <v>310.4319009529449</v>
+        <v>310.0276204199649</v>
       </c>
       <c r="D27" t="n">
-        <v>305.9160390722913</v>
+        <v>303.3327096940284</v>
       </c>
       <c r="E27" t="n">
-        <v>309.0317993164062</v>
+        <v>309.8106994628906</v>
       </c>
       <c r="F27" t="n">
-        <v>7206100</v>
+        <v>7302300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B28" t="n">
-        <v>307.5231746391179</v>
+        <v>310.5896337890794</v>
       </c>
       <c r="C28" t="n">
-        <v>310.0275898810191</v>
+        <v>315.0857860805166</v>
       </c>
       <c r="D28" t="n">
-        <v>303.3326798145578</v>
+        <v>309.8106862822301</v>
       </c>
       <c r="E28" t="n">
-        <v>309.8106689453125</v>
+        <v>312.4531860351562</v>
       </c>
       <c r="F28" t="n">
-        <v>7302300</v>
+        <v>5794100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B29" t="n">
-        <v>310.5896641246428</v>
+        <v>313.0546102409576</v>
       </c>
       <c r="C29" t="n">
-        <v>315.0858168552232</v>
+        <v>314.5828963020791</v>
       </c>
       <c r="D29" t="n">
-        <v>309.810716541713</v>
+        <v>310.8656917625901</v>
       </c>
       <c r="E29" t="n">
-        <v>312.4532165527344</v>
+        <v>311.200927734375</v>
       </c>
       <c r="F29" t="n">
-        <v>5794100</v>
+        <v>5030200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B30" t="n">
-        <v>313.054640940315</v>
+        <v>311.8320000281587</v>
       </c>
       <c r="C30" t="n">
-        <v>314.5829271513063</v>
+        <v>317.7381233989844</v>
       </c>
       <c r="D30" t="n">
-        <v>310.8657222472937</v>
+        <v>311.782682032414</v>
       </c>
       <c r="E30" t="n">
-        <v>311.2009582519531</v>
+        <v>315.9238891601562</v>
       </c>
       <c r="F30" t="n">
-        <v>5030200</v>
+        <v>10578300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B31" t="n">
-        <v>311.8320301504691</v>
+        <v>314.7604626322791</v>
       </c>
       <c r="C31" t="n">
-        <v>317.7381540918137</v>
+        <v>316.1408551748796</v>
       </c>
       <c r="D31" t="n">
-        <v>311.7827121499603</v>
+        <v>304.7722882324798</v>
       </c>
       <c r="E31" t="n">
-        <v>315.9239196777344</v>
+        <v>305.14697265625</v>
       </c>
       <c r="F31" t="n">
-        <v>10578300</v>
+        <v>8973300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B32" t="n">
-        <v>314.7604311532612</v>
+        <v>303.2044890700107</v>
       </c>
       <c r="C32" t="n">
-        <v>316.1408235578094</v>
+        <v>303.3326737235763</v>
       </c>
       <c r="D32" t="n">
-        <v>304.7722577523736</v>
+        <v>297.012418045434</v>
       </c>
       <c r="E32" t="n">
-        <v>305.1469421386719</v>
+        <v>299.3590698242188</v>
       </c>
       <c r="F32" t="n">
-        <v>8973300</v>
+        <v>10327000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B33" t="n">
-        <v>303.2045199796025</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C33" t="n">
-        <v>303.3327046462357</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D33" t="n">
-        <v>297.0124483237873</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E33" t="n">
-        <v>299.3591003417969</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F33" t="n">
-        <v>10327000</v>
+        <v>8344000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B34" t="n">
-        <v>299.7436397411884</v>
+        <v>295.3066623130797</v>
       </c>
       <c r="C34" t="n">
-        <v>301.3113742461044</v>
+        <v>298.708370459316</v>
       </c>
       <c r="D34" t="n">
-        <v>293.5022804823602</v>
+        <v>292.8613742767781</v>
       </c>
       <c r="E34" t="n">
-        <v>296.1644592285156</v>
+        <v>295.2179260253906</v>
       </c>
       <c r="F34" t="n">
-        <v>8344000</v>
+        <v>8077300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B35" t="n">
-        <v>295.3066317863286</v>
+        <v>295.5432597963394</v>
       </c>
       <c r="C35" t="n">
-        <v>298.70833958092</v>
+        <v>300.1873356382808</v>
       </c>
       <c r="D35" t="n">
-        <v>292.8613440028039</v>
+        <v>295.0798391737984</v>
       </c>
       <c r="E35" t="n">
-        <v>295.2178955078125</v>
+        <v>299.0238342285156</v>
       </c>
       <c r="F35" t="n">
-        <v>8077300</v>
+        <v>5546600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B36" t="n">
-        <v>295.5432899586994</v>
+        <v>302.0508736933244</v>
       </c>
       <c r="C36" t="n">
-        <v>300.1873662746028</v>
+        <v>305.5807663052954</v>
       </c>
       <c r="D36" t="n">
-        <v>295.0798692888629</v>
+        <v>293.9854105998292</v>
       </c>
       <c r="E36" t="n">
-        <v>299.0238647460938</v>
+        <v>294.2023315429688</v>
       </c>
       <c r="F36" t="n">
-        <v>5546600</v>
+        <v>7501600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B37" t="n">
-        <v>302.0508736933244</v>
+        <v>297.0715864028587</v>
       </c>
       <c r="C37" t="n">
-        <v>305.5807663052954</v>
+        <v>297.456110287291</v>
       </c>
       <c r="D37" t="n">
-        <v>293.9854105998292</v>
+        <v>288.7103057597054</v>
       </c>
       <c r="E37" t="n">
-        <v>294.2023315429688</v>
+        <v>293.8473510742188</v>
       </c>
       <c r="F37" t="n">
-        <v>7501600</v>
+        <v>11766800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B38" t="n">
-        <v>297.0715864028587</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C38" t="n">
-        <v>297.456110287291</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D38" t="n">
-        <v>288.7103057597054</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E38" t="n">
-        <v>293.8473510742188</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F38" t="n">
-        <v>11766800</v>
+        <v>10940200</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B39" t="n">
-        <v>294.0642973394352</v>
+        <v>295.848951187077</v>
       </c>
       <c r="C39" t="n">
-        <v>295.6221924256846</v>
+        <v>300.236658228506</v>
       </c>
       <c r="D39" t="n">
-        <v>290.386540762355</v>
+        <v>291.4218258555586</v>
       </c>
       <c r="E39" t="n">
-        <v>293.8276672363281</v>
+        <v>298.7576599121094</v>
       </c>
       <c r="F39" t="n">
-        <v>10940200</v>
+        <v>8877200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B40" t="n">
-        <v>295.8489209666184</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C40" t="n">
-        <v>300.2366275598507</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D40" t="n">
-        <v>291.4217960873232</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E40" t="n">
-        <v>298.7576293945312</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F40" t="n">
-        <v>8877200</v>
+        <v>7910900</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B41" t="n">
-        <v>300.7296512123902</v>
+        <v>304.7722465716023</v>
       </c>
       <c r="C41" t="n">
-        <v>304.2102259719906</v>
+        <v>309.3275563846455</v>
       </c>
       <c r="D41" t="n">
-        <v>298.9548653069277</v>
+        <v>303.9242719247256</v>
       </c>
       <c r="E41" t="n">
-        <v>303.3327026367188</v>
+        <v>308.6965026855469</v>
       </c>
       <c r="F41" t="n">
-        <v>7910900</v>
+        <v>4322400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B42" t="n">
-        <v>304.7722767012305</v>
+        <v>308.5683309692949</v>
       </c>
       <c r="C42" t="n">
-        <v>309.3275869646093</v>
+        <v>309.6430660312097</v>
       </c>
       <c r="D42" t="n">
-        <v>303.9243019705234</v>
+        <v>304.2200727283419</v>
       </c>
       <c r="E42" t="n">
-        <v>308.696533203125</v>
+        <v>304.5947570800781</v>
       </c>
       <c r="F42" t="n">
-        <v>4322400</v>
+        <v>7727300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B43" t="n">
-        <v>308.5683618849884</v>
+        <v>304.4172805196406</v>
       </c>
       <c r="C43" t="n">
-        <v>309.6430970545817</v>
+        <v>306.1329390093465</v>
       </c>
       <c r="D43" t="n">
-        <v>304.2201032083801</v>
+        <v>302.7903884074122</v>
       </c>
       <c r="E43" t="n">
-        <v>304.5947875976562</v>
+        <v>303.5693359375</v>
       </c>
       <c r="F43" t="n">
-        <v>7727300</v>
+        <v>7249000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B44" t="n">
-        <v>304.4172805196406</v>
+        <v>302.8988595387675</v>
       </c>
       <c r="C44" t="n">
-        <v>306.1329390093465</v>
+        <v>307.9865871384521</v>
       </c>
       <c r="D44" t="n">
-        <v>302.7903884074122</v>
+        <v>302.5044359255107</v>
       </c>
       <c r="E44" t="n">
-        <v>303.5693359375</v>
+        <v>307.7598266601562</v>
       </c>
       <c r="F44" t="n">
-        <v>7249000</v>
+        <v>8535300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B45" t="n">
-        <v>302.8988595387675</v>
+        <v>308.8740221323167</v>
       </c>
       <c r="C45" t="n">
-        <v>307.9865871384521</v>
+        <v>314.0307770729326</v>
       </c>
       <c r="D45" t="n">
-        <v>302.5044359255107</v>
+        <v>308.617652791837</v>
       </c>
       <c r="E45" t="n">
-        <v>307.7598266601562</v>
+        <v>311.6742553710938</v>
       </c>
       <c r="F45" t="n">
-        <v>8535300</v>
+        <v>9627800</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B46" t="n">
-        <v>308.8740221323167</v>
+        <v>311.2206946896725</v>
       </c>
       <c r="C46" t="n">
-        <v>314.0307770729326</v>
+        <v>314.0209278419201</v>
       </c>
       <c r="D46" t="n">
-        <v>308.617652791837</v>
+        <v>310.2741141188276</v>
       </c>
       <c r="E46" t="n">
-        <v>311.6742553710938</v>
+        <v>310.6290893554688</v>
       </c>
       <c r="F46" t="n">
-        <v>9627800</v>
+        <v>6518900</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B47" t="n">
-        <v>311.2206946896725</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C47" t="n">
-        <v>314.0209278419201</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D47" t="n">
-        <v>310.2741141188276</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E47" t="n">
-        <v>310.6290893554688</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F47" t="n">
-        <v>6518900</v>
+        <v>7417200</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B48" t="n">
-        <v>310.6487980837529</v>
+        <v>310.5403783790639</v>
       </c>
       <c r="C48" t="n">
-        <v>312.0390600856641</v>
+        <v>314.336450228146</v>
       </c>
       <c r="D48" t="n">
-        <v>308.9627484602848</v>
+        <v>295.8193913272319</v>
       </c>
       <c r="E48" t="n">
-        <v>310.7966918945312</v>
+        <v>296.3025512695312</v>
       </c>
       <c r="F48" t="n">
-        <v>7417200</v>
+        <v>18049200</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B49" t="n">
-        <v>310.5403463950657</v>
+        <v>296.292632599085</v>
       </c>
       <c r="C49" t="n">
-        <v>314.3364178531727</v>
+        <v>306.8329619363725</v>
       </c>
       <c r="D49" t="n">
-        <v>295.8193608594167</v>
+        <v>294.2811866679717</v>
       </c>
       <c r="E49" t="n">
-        <v>296.3025207519531</v>
+        <v>305.76806640625</v>
       </c>
       <c r="F49" t="n">
-        <v>18049200</v>
+        <v>18874100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B50" t="n">
-        <v>296.2926621709551</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C50" t="n">
-        <v>306.8329925602339</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D50" t="n">
-        <v>294.2812160390869</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E50" t="n">
-        <v>305.7680969238281</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F50" t="n">
-        <v>18874100</v>
+        <v>9721900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B51" t="n">
-        <v>304.9102649889192</v>
+        <v>315.2041261224818</v>
       </c>
       <c r="C51" t="n">
-        <v>313.5476242674454</v>
+        <v>315.7858618718594</v>
       </c>
       <c r="D51" t="n">
-        <v>304.9102649889192</v>
+        <v>312.1672627021157</v>
       </c>
       <c r="E51" t="n">
-        <v>312.9363098144531</v>
+        <v>314.0603637695312</v>
       </c>
       <c r="F51" t="n">
-        <v>9721900</v>
+        <v>8982900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B52" t="n">
-        <v>315.2040954937631</v>
+        <v>315.115395356304</v>
       </c>
       <c r="C52" t="n">
-        <v>315.7858311866128</v>
+        <v>318.3593402708456</v>
       </c>
       <c r="D52" t="n">
-        <v>312.1672323684923</v>
+        <v>313.9322146909975</v>
       </c>
       <c r="E52" t="n">
-        <v>314.0603332519531</v>
+        <v>315.5393676757812</v>
       </c>
       <c r="F52" t="n">
-        <v>8982900</v>
+        <v>10864100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B53" t="n">
-        <v>315.115395356304</v>
+        <v>314.6224027314819</v>
       </c>
       <c r="C53" t="n">
-        <v>318.3593402708456</v>
+        <v>315.0463750601788</v>
       </c>
       <c r="D53" t="n">
-        <v>313.9322146909975</v>
+        <v>309.9980652283745</v>
       </c>
       <c r="E53" t="n">
-        <v>315.5393676757812</v>
+        <v>311.1319580078125</v>
       </c>
       <c r="F53" t="n">
-        <v>10864100</v>
+        <v>8331300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B54" t="n">
-        <v>314.6223410116007</v>
+        <v>313.971593609235</v>
       </c>
       <c r="C54" t="n">
-        <v>315.0463132571263</v>
+        <v>314.8984348971578</v>
       </c>
       <c r="D54" t="n">
-        <v>309.9980044156554</v>
+        <v>310.254388930852</v>
       </c>
       <c r="E54" t="n">
-        <v>311.1318969726562</v>
+        <v>310.5699157714844</v>
       </c>
       <c r="F54" t="n">
-        <v>8331300</v>
+        <v>8718700</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B55" t="n">
-        <v>313.9716244610726</v>
+        <v>311.575672673722</v>
       </c>
       <c r="C55" t="n">
-        <v>314.8984658400699</v>
+        <v>313.2518829489097</v>
       </c>
       <c r="D55" t="n">
-        <v>310.2544194174254</v>
+        <v>307.8485977928193</v>
       </c>
       <c r="E55" t="n">
-        <v>310.5699462890625</v>
+        <v>308.61767578125</v>
       </c>
       <c r="F55" t="n">
-        <v>8718700</v>
+        <v>11444900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B56" t="n">
-        <v>311.5756418636432</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C56" t="n">
-        <v>313.2518519730792</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D56" t="n">
-        <v>307.8485673512913</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E56" t="n">
-        <v>308.6176452636719</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F56" t="n">
-        <v>11444900</v>
+        <v>24494400</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B57" t="n">
-        <v>309.3965776494671</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="C57" t="n">
-        <v>314.099781180705</v>
+        <v>318.7043994886834</v>
       </c>
       <c r="D57" t="n">
-        <v>308.8049723403709</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="E57" t="n">
-        <v>312.7686767578125</v>
+        <v>318.5663452148438</v>
       </c>
       <c r="F57" t="n">
-        <v>24494400</v>
+        <v>8354600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B58" t="n">
-        <v>313.0644852104395</v>
+        <v>319.0790830432475</v>
       </c>
       <c r="C58" t="n">
-        <v>318.7043994886834</v>
+        <v>323.1907116116738</v>
       </c>
       <c r="D58" t="n">
-        <v>313.0644852104395</v>
+        <v>318.5663744582675</v>
       </c>
       <c r="E58" t="n">
-        <v>318.5663452148438</v>
+        <v>321.3666076660156</v>
       </c>
       <c r="F58" t="n">
-        <v>8354600</v>
+        <v>6668300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B59" t="n">
-        <v>319.0790830432475</v>
+        <v>321.6722493328215</v>
       </c>
       <c r="C59" t="n">
-        <v>323.1907116116738</v>
+        <v>325.3697449529369</v>
       </c>
       <c r="D59" t="n">
-        <v>318.5663744582675</v>
+        <v>320.9426198260136</v>
       </c>
       <c r="E59" t="n">
-        <v>321.3666076660156</v>
+        <v>324.5612487792969</v>
       </c>
       <c r="F59" t="n">
-        <v>6668300</v>
+        <v>4289300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B60" t="n">
-        <v>321.6722493328215</v>
+        <v>324.502058709128</v>
       </c>
       <c r="C60" t="n">
-        <v>325.3697449529369</v>
+        <v>326.2275566521161</v>
       </c>
       <c r="D60" t="n">
-        <v>320.9426198260136</v>
+        <v>321.9680645986219</v>
       </c>
       <c r="E60" t="n">
-        <v>324.5612487792969</v>
+        <v>323.3188781738281</v>
       </c>
       <c r="F60" t="n">
-        <v>4289300</v>
+        <v>4158300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B61" t="n">
-        <v>324.502058709128</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C61" t="n">
-        <v>326.2275566521161</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D61" t="n">
-        <v>321.9680645986219</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E61" t="n">
-        <v>323.3188781738281</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F61" t="n">
-        <v>4158300</v>
+        <v>8635300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B62" t="n">
-        <v>322.4216288798564</v>
+        <v>320.2623075229155</v>
       </c>
       <c r="C62" t="n">
-        <v>323.1808371734579</v>
+        <v>320.3904921972535</v>
       </c>
       <c r="D62" t="n">
-        <v>319.0002116144308</v>
+        <v>317.9747828016658</v>
       </c>
       <c r="E62" t="n">
-        <v>319.2171325683594</v>
+        <v>318.8917846679688</v>
       </c>
       <c r="F62" t="n">
-        <v>8635300</v>
+        <v>7904300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B63" t="n">
-        <v>320.2622768741799</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C63" t="n">
-        <v>320.3904615362508</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D63" t="n">
-        <v>317.9747523718436</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E63" t="n">
-        <v>318.8917541503906</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F63" t="n">
-        <v>7904300</v>
+        <v>5048500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B64" t="n">
-        <v>319.7988699190817</v>
+        <v>317.9846252281575</v>
       </c>
       <c r="C64" t="n">
-        <v>320.3313177342217</v>
+        <v>321.1694123071354</v>
       </c>
       <c r="D64" t="n">
-        <v>317.5310845539587</v>
+        <v>316.2492576445291</v>
       </c>
       <c r="E64" t="n">
-        <v>317.7085571289062</v>
+        <v>320.9229125976562</v>
       </c>
       <c r="F64" t="n">
-        <v>5048500</v>
+        <v>8054000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B65" t="n">
-        <v>317.9846554663246</v>
+        <v>320.9426586744551</v>
       </c>
       <c r="C65" t="n">
-        <v>321.169442848154</v>
+        <v>332.5281463531796</v>
       </c>
       <c r="D65" t="n">
-        <v>316.2492877176746</v>
+        <v>320.637001406751</v>
       </c>
       <c r="E65" t="n">
-        <v>320.9229431152344</v>
+        <v>329.3630981445312</v>
       </c>
       <c r="F65" t="n">
-        <v>8054000</v>
+        <v>10752600</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,25 +2133,25 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B66" t="n">
-        <v>320.942628937084</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C66" t="n">
-        <v>332.5281155423397</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D66" t="n">
-        <v>320.636971697701</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E66" t="n">
-        <v>329.3630676269531</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F66" t="n">
-        <v>10752600</v>
+        <v>7660800</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2159,25 +2159,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B67" t="n">
-        <v>329.4422902981328</v>
+        <v>327.9764350864437</v>
       </c>
       <c r="C67" t="n">
-        <v>332.6612412306879</v>
+        <v>328.9767653957764</v>
       </c>
       <c r="D67" t="n">
-        <v>327.491109600743</v>
+        <v>321.4989071734381</v>
       </c>
       <c r="E67" t="n">
-        <v>331.4132690429688</v>
+        <v>323.8660583496094</v>
       </c>
       <c r="F67" t="n">
-        <v>7660800</v>
+        <v>9815200</v>
       </c>
       <c r="G67" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B68" t="n">
-        <v>327.9764659913386</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C68" t="n">
-        <v>328.9767963949314</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D68" t="n">
-        <v>321.4989374679619</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E68" t="n">
-        <v>323.8660888671875</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F68" t="n">
-        <v>9815200</v>
+        <v>11737100</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B69" t="n">
-        <v>323.2718313763784</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C69" t="n">
-        <v>328.2339475379842</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D69" t="n">
-        <v>322.5388804495614</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E69" t="n">
-        <v>326.6393432617188</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F69" t="n">
-        <v>11737100</v>
+        <v>6738100</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B70" t="n">
-        <v>326.1936353875406</v>
+        <v>318.8049332018166</v>
       </c>
       <c r="C70" t="n">
-        <v>328.7291759216584</v>
+        <v>322.9053661093398</v>
       </c>
       <c r="D70" t="n">
-        <v>325.0348299492433</v>
+        <v>318.1611490039577</v>
       </c>
       <c r="E70" t="n">
-        <v>326.0450744628906</v>
+        <v>321.3899841308594</v>
       </c>
       <c r="F70" t="n">
-        <v>6738100</v>
+        <v>12805100</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B71" t="n">
-        <v>318.8049029297019</v>
+        <v>321.2017865718998</v>
       </c>
       <c r="C71" t="n">
-        <v>322.9053354478686</v>
+        <v>323.7373271836527</v>
       </c>
       <c r="D71" t="n">
-        <v>318.1611187929736</v>
+        <v>307.6029755260753</v>
       </c>
       <c r="E71" t="n">
-        <v>321.3899536132812</v>
+        <v>307.9298095703125</v>
       </c>
       <c r="F71" t="n">
-        <v>12805100</v>
+        <v>19371200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B72" t="n">
-        <v>321.2017547389941</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C72" t="n">
-        <v>323.7372950994605</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D72" t="n">
-        <v>307.6029450408882</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E72" t="n">
-        <v>307.9297790527344</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F72" t="n">
-        <v>19371200</v>
+        <v>25951500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B73" t="n">
-        <v>305.2556057077196</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C73" t="n">
-        <v>308.7815926253858</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D73" t="n">
-        <v>303.1954601804828</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E73" t="n">
-        <v>304.9287414550781</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F73" t="n">
-        <v>25951500</v>
+        <v>14751400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B74" t="n">
-        <v>305.5230197927318</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C74" t="n">
-        <v>309.95031666446</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D74" t="n">
-        <v>304.8098971346673</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E74" t="n">
-        <v>306.3054809570312</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F74" t="n">
-        <v>14751400</v>
+        <v>14652500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B75" t="n">
-        <v>307.385060616362</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C75" t="n">
-        <v>314.1795087286461</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D75" t="n">
-        <v>307.0383983149945</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E75" t="n">
-        <v>309.4848022460938</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F75" t="n">
-        <v>14652500</v>
+        <v>12900600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B76" t="n">
-        <v>303.2845981841295</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C76" t="n">
-        <v>308.1774060521912</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D76" t="n">
-        <v>298.9761500928895</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E76" t="n">
-        <v>299.8477478027344</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F76" t="n">
-        <v>12900600</v>
+        <v>10270100</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B77" t="n">
-        <v>300.5311849469782</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C77" t="n">
-        <v>302.4823658305288</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D77" t="n">
-        <v>298.2729680555718</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E77" t="n">
-        <v>299.1544799804688</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F77" t="n">
-        <v>10270100</v>
+        <v>10535800</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B78" t="n">
-        <v>301.9474777854751</v>
+        <v>299.1148422218051</v>
       </c>
       <c r="C78" t="n">
-        <v>305.2555953909441</v>
+        <v>299.4813025896872</v>
       </c>
       <c r="D78" t="n">
-        <v>300.0062112868251</v>
+        <v>293.6773006232809</v>
       </c>
       <c r="E78" t="n">
-        <v>300.729248046875</v>
+        <v>294.875732421875</v>
       </c>
       <c r="F78" t="n">
-        <v>10535800</v>
+        <v>11107900</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B79" t="n">
-        <v>299.1148112655088</v>
+        <v>294.9648788077786</v>
       </c>
       <c r="C79" t="n">
-        <v>299.4812715954647</v>
+        <v>298.8969527426069</v>
       </c>
       <c r="D79" t="n">
-        <v>293.6772702297321</v>
+        <v>294.6083325653198</v>
       </c>
       <c r="E79" t="n">
-        <v>294.8757019042969</v>
+        <v>298.1640319824219</v>
       </c>
       <c r="F79" t="n">
-        <v>11107900</v>
+        <v>11752700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B80" t="n">
-        <v>294.9648486176391</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C80" t="n">
-        <v>298.8969221500132</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D80" t="n">
-        <v>294.6083024116733</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E80" t="n">
-        <v>298.1640014648438</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F80" t="n">
-        <v>11752700</v>
+        <v>11527400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B81" t="n">
-        <v>298.4512235287846</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C81" t="n">
-        <v>299.0851237823749</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D81" t="n">
-        <v>295.3016109870806</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E81" t="n">
-        <v>297.4409790039062</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F81" t="n">
-        <v>11527400</v>
+        <v>9556700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B82" t="n">
-        <v>297.4013222225187</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C82" t="n">
-        <v>299.0355829225425</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D82" t="n">
-        <v>295.2025300603667</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E82" t="n">
-        <v>297.8965454101562</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F82" t="n">
-        <v>9556700</v>
+        <v>11580000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B83" t="n">
-        <v>299.5110006693188</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C83" t="n">
-        <v>303.898671192008</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D83" t="n">
-        <v>299.3327275624257</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E83" t="n">
-        <v>303.4926147460938</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F83" t="n">
-        <v>11580000</v>
+        <v>11953200</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B84" t="n">
-        <v>302.333781642444</v>
+        <v>301.5513012828864</v>
       </c>
       <c r="C84" t="n">
-        <v>304.9881708986046</v>
+        <v>306.3450582127215</v>
       </c>
       <c r="D84" t="n">
-        <v>299.6694782493637</v>
+        <v>298.4908255461663</v>
       </c>
       <c r="E84" t="n">
-        <v>302.9676818847656</v>
+        <v>305.1961669921875</v>
       </c>
       <c r="F84" t="n">
-        <v>11953200</v>
+        <v>9839400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B85" t="n">
-        <v>301.5513314360023</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C85" t="n">
-        <v>306.3450888451811</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D85" t="n">
-        <v>298.4908553932551</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E85" t="n">
-        <v>305.1961975097656</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F85" t="n">
-        <v>9839400</v>
+        <v>12688000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B86" t="n">
-        <v>306.7709905338949</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="C86" t="n">
-        <v>313.2286905211348</v>
+        <v>316.2594719758441</v>
       </c>
       <c r="D86" t="n">
-        <v>306.1470044328188</v>
+        <v>311.4062901330092</v>
       </c>
       <c r="E86" t="n">
-        <v>311.8420715332031</v>
+        <v>314.2389526367188</v>
       </c>
       <c r="F86" t="n">
-        <v>12688000</v>
+        <v>9848800</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B87" t="n">
-        <v>311.4062598905275</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C87" t="n">
-        <v>316.2594412620415</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D87" t="n">
-        <v>311.4062598905275</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E87" t="n">
-        <v>314.2389221191406</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F87" t="n">
-        <v>9848800</v>
+        <v>9388000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B88" t="n">
-        <v>311.9906259989966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C88" t="n">
-        <v>312.9909865673853</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D88" t="n">
-        <v>302.6210112179966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E88" t="n">
-        <v>307.1968688964844</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F88" t="n">
-        <v>9388000</v>
+        <v>17797400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B89" t="n">
-        <v>311.7034102684662</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C89" t="n">
-        <v>321.1522783634816</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D89" t="n">
-        <v>311.7034102684662</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E89" t="n">
-        <v>319.3199462890625</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F89" t="n">
-        <v>17797400</v>
+        <v>11477500</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B90" t="n">
-        <v>318.2700781279603</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C90" t="n">
-        <v>323.2817350541263</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D90" t="n">
-        <v>317.0518180384032</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E90" t="n">
-        <v>319.0228271484375</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F90" t="n">
-        <v>11477500</v>
+        <v>9902200</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B91" t="n">
-        <v>319.4684837021083</v>
+        <v>320.1518827061323</v>
       </c>
       <c r="C91" t="n">
-        <v>323.014298845819</v>
+        <v>322.1724018130651</v>
       </c>
       <c r="D91" t="n">
-        <v>312.1094739861534</v>
+        <v>305.7805260837019</v>
       </c>
       <c r="E91" t="n">
-        <v>315.2392883300781</v>
+        <v>307.8505554199219</v>
       </c>
       <c r="F91" t="n">
-        <v>9902200</v>
+        <v>8703500</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B92" t="n">
-        <v>320.1519144431551</v>
+        <v>309.2966374972976</v>
       </c>
       <c r="C92" t="n">
-        <v>322.1724337503843</v>
+        <v>310.6238322045743</v>
       </c>
       <c r="D92" t="n">
-        <v>305.7805563960757</v>
+        <v>297.1537535117247</v>
       </c>
       <c r="E92" t="n">
-        <v>307.8505859375</v>
+        <v>299.7487487792969</v>
       </c>
       <c r="F92" t="n">
-        <v>8703500</v>
+        <v>13443400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B93" t="n">
-        <v>309.2966060076438</v>
+        <v>295.6680782309701</v>
       </c>
       <c r="C93" t="n">
-        <v>310.6238005797982</v>
+        <v>301.3829738793206</v>
       </c>
       <c r="D93" t="n">
-        <v>297.1537232583444</v>
+        <v>293.6871852314235</v>
       </c>
       <c r="E93" t="n">
-        <v>299.7487182617188</v>
+        <v>299.6595764160156</v>
       </c>
       <c r="F93" t="n">
-        <v>13443400</v>
+        <v>9114500</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B94" t="n">
-        <v>295.6680481198895</v>
+        <v>299.8675850307636</v>
       </c>
       <c r="C94" t="n">
-        <v>301.3829431862302</v>
+        <v>305.2952123797385</v>
       </c>
       <c r="D94" t="n">
-        <v>293.6871553220786</v>
+        <v>299.6100592744303</v>
       </c>
       <c r="E94" t="n">
-        <v>299.6595458984375</v>
+        <v>304.1958312988281</v>
       </c>
       <c r="F94" t="n">
-        <v>9114500</v>
+        <v>8896800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B95" t="n">
-        <v>299.8675549474044</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C95" t="n">
-        <v>305.2951817518681</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D95" t="n">
-        <v>299.6100292169066</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E95" t="n">
-        <v>304.19580078125</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F95" t="n">
-        <v>8896800</v>
+        <v>7209600</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B96" t="n">
-        <v>305.5130974954087</v>
+        <v>304.2354272061944</v>
       </c>
       <c r="C96" t="n">
-        <v>309.2966101142475</v>
+        <v>306.2262038721237</v>
       </c>
       <c r="D96" t="n">
-        <v>304.2849535938903</v>
+        <v>302.2049939958365</v>
       </c>
       <c r="E96" t="n">
-        <v>305.8300476074219</v>
+        <v>305.1069946289062</v>
       </c>
       <c r="F96" t="n">
-        <v>7209600</v>
+        <v>6737700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B97" t="n">
-        <v>304.2354576365961</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C97" t="n">
-        <v>306.226234501648</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D97" t="n">
-        <v>302.2050242231491</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E97" t="n">
-        <v>305.1070251464844</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F97" t="n">
-        <v>6737700</v>
+        <v>7792700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B98" t="n">
-        <v>305.4536802835111</v>
+        <v>305.8498457788994</v>
       </c>
       <c r="C98" t="n">
-        <v>308.0288471084009</v>
+        <v>308.0288400173425</v>
       </c>
       <c r="D98" t="n">
-        <v>302.7596647203387</v>
+        <v>292.2807478108573</v>
       </c>
       <c r="E98" t="n">
-        <v>307.8208618164062</v>
+        <v>294.8262023925781</v>
       </c>
       <c r="F98" t="n">
-        <v>7792700</v>
+        <v>12955400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B99" t="n">
-        <v>305.8498774375392</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C99" t="n">
-        <v>308.028871901531</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D99" t="n">
-        <v>292.2807780649544</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E99" t="n">
-        <v>294.8262329101562</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F99" t="n">
-        <v>12955400</v>
+        <v>13554100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B100" t="n">
-        <v>293.9843218466586</v>
+        <v>295.7869507950724</v>
       </c>
       <c r="C100" t="n">
-        <v>296.886322684036</v>
+        <v>300.7589812348872</v>
       </c>
       <c r="D100" t="n">
-        <v>288.5962907533433</v>
+        <v>294.1725181992404</v>
       </c>
       <c r="E100" t="n">
-        <v>294.459716796875</v>
+        <v>300.4024047851562</v>
       </c>
       <c r="F100" t="n">
-        <v>13554100</v>
+        <v>8095500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B101" t="n">
-        <v>295.7869207463737</v>
+        <v>301.670173133609</v>
       </c>
       <c r="C101" t="n">
-        <v>300.7589506810849</v>
+        <v>306.0578739762234</v>
       </c>
       <c r="D101" t="n">
-        <v>294.1724883145502</v>
+        <v>300.7391812579012</v>
       </c>
       <c r="E101" t="n">
-        <v>300.4023742675781</v>
+        <v>303.2053833007812</v>
       </c>
       <c r="F101" t="n">
-        <v>8095500</v>
+        <v>7007800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B102" t="n">
-        <v>301.670173133609</v>
+        <v>297.1339389424841</v>
       </c>
       <c r="C102" t="n">
-        <v>306.0578739762234</v>
+        <v>300.0557680991628</v>
       </c>
       <c r="D102" t="n">
-        <v>300.7391812579012</v>
+        <v>291.636973162459</v>
       </c>
       <c r="E102" t="n">
-        <v>303.2053833007812</v>
+        <v>297.4310607910156</v>
       </c>
       <c r="F102" t="n">
-        <v>7007800</v>
+        <v>18620800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B103" t="n">
-        <v>297.1339389424841</v>
+        <v>291.9935267958635</v>
       </c>
       <c r="C103" t="n">
-        <v>300.0557680991628</v>
+        <v>297.1141484397957</v>
       </c>
       <c r="D103" t="n">
-        <v>291.636973162459</v>
+        <v>290.4088063693875</v>
       </c>
       <c r="E103" t="n">
-        <v>297.4310607910156</v>
+        <v>294.7172546386719</v>
       </c>
       <c r="F103" t="n">
-        <v>18620800</v>
+        <v>8508900</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B104" t="n">
-        <v>291.9935267958635</v>
+        <v>289.4975898716125</v>
       </c>
       <c r="C104" t="n">
-        <v>297.1141484397957</v>
+        <v>299.5011046657454</v>
       </c>
       <c r="D104" t="n">
-        <v>290.4088063693875</v>
+        <v>286.7342359222354</v>
       </c>
       <c r="E104" t="n">
-        <v>294.7172546386719</v>
+        <v>297.3914489746094</v>
       </c>
       <c r="F104" t="n">
-        <v>8508900</v>
+        <v>10278200</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B105" t="n">
-        <v>289.4975898716125</v>
+        <v>297.1240288614248</v>
       </c>
       <c r="C105" t="n">
-        <v>299.5011046657454</v>
+        <v>298.1243894751821</v>
       </c>
       <c r="D105" t="n">
-        <v>286.7342359222354</v>
+        <v>292.993883980321</v>
       </c>
       <c r="E105" t="n">
-        <v>297.3914489746094</v>
+        <v>296.52978515625</v>
       </c>
       <c r="F105" t="n">
-        <v>10278200</v>
+        <v>8055700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B106" t="n">
-        <v>297.1240288614248</v>
+        <v>295.1332451958745</v>
       </c>
       <c r="C106" t="n">
-        <v>298.1243894751821</v>
+        <v>298.3620800816865</v>
       </c>
       <c r="D106" t="n">
-        <v>292.993883980321</v>
+        <v>289.6362492414601</v>
       </c>
       <c r="E106" t="n">
-        <v>296.52978515625</v>
+        <v>290.7455444335938</v>
       </c>
       <c r="F106" t="n">
-        <v>8055700</v>
+        <v>12732500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B107" t="n">
-        <v>295.1332451958745</v>
+        <v>283.6044306839189</v>
       </c>
       <c r="C107" t="n">
-        <v>298.3620800816865</v>
+        <v>287.2195541533999</v>
       </c>
       <c r="D107" t="n">
-        <v>289.6362492414601</v>
+        <v>280.9995517042956</v>
       </c>
       <c r="E107" t="n">
-        <v>290.7455444335938</v>
+        <v>286.7144470214844</v>
       </c>
       <c r="F107" t="n">
-        <v>12732500</v>
+        <v>13496500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B108" t="n">
-        <v>283.6044306839189</v>
+        <v>282.7724816341387</v>
       </c>
       <c r="C108" t="n">
-        <v>287.2195541533999</v>
+        <v>288.3189881947603</v>
       </c>
       <c r="D108" t="n">
-        <v>280.9995517042956</v>
+        <v>277.7707387954702</v>
       </c>
       <c r="E108" t="n">
-        <v>286.7144470214844</v>
+        <v>287.1502685546875</v>
       </c>
       <c r="F108" t="n">
-        <v>13496500</v>
+        <v>12241100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B109" t="n">
-        <v>282.7724816341387</v>
+        <v>286.5262662545288</v>
       </c>
       <c r="C109" t="n">
-        <v>288.3189881947603</v>
+        <v>289.9532025593205</v>
       </c>
       <c r="D109" t="n">
-        <v>277.7707387954702</v>
+        <v>284.4364084963449</v>
       </c>
       <c r="E109" t="n">
-        <v>287.1502685546875</v>
+        <v>285.9716186523438</v>
       </c>
       <c r="F109" t="n">
-        <v>12241100</v>
+        <v>8344900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B110" t="n">
-        <v>286.5262662545288</v>
+        <v>286.0508166178312</v>
       </c>
       <c r="C110" t="n">
-        <v>289.9532025593205</v>
+        <v>287.7048753720447</v>
       </c>
       <c r="D110" t="n">
-        <v>284.4364084963449</v>
+        <v>282.1385413260368</v>
       </c>
       <c r="E110" t="n">
-        <v>285.9716186523438</v>
+        <v>284.7731323242188</v>
       </c>
       <c r="F110" t="n">
-        <v>8344900</v>
+        <v>10205000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B111" t="n">
-        <v>286.0508472723319</v>
+        <v>280.1279538528093</v>
       </c>
       <c r="C111" t="n">
-        <v>287.7049062038017</v>
+        <v>281.167940752382</v>
       </c>
       <c r="D111" t="n">
-        <v>282.1385715612803</v>
+        <v>276.4336079693154</v>
       </c>
       <c r="E111" t="n">
-        <v>284.7731628417969</v>
+        <v>280.1874084472656</v>
       </c>
       <c r="F111" t="n">
-        <v>10205000</v>
+        <v>13760500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B112" t="n">
-        <v>280.1279843639117</v>
+        <v>281.9504072447318</v>
       </c>
       <c r="C112" t="n">
-        <v>281.1679713767581</v>
+        <v>284.4463214441296</v>
       </c>
       <c r="D112" t="n">
-        <v>276.4336380780354</v>
+        <v>280.2468381234208</v>
       </c>
       <c r="E112" t="n">
-        <v>280.1874389648438</v>
+        <v>280.7321472167969</v>
       </c>
       <c r="F112" t="n">
-        <v>13760500</v>
+        <v>9091200</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B113" t="n">
-        <v>281.9504072447318</v>
+        <v>283.6044205599556</v>
       </c>
       <c r="C113" t="n">
-        <v>284.4463214441296</v>
+        <v>286.506421278288</v>
       </c>
       <c r="D113" t="n">
-        <v>280.2468381234208</v>
+        <v>281.8909373944359</v>
       </c>
       <c r="E113" t="n">
-        <v>280.7321472167969</v>
+        <v>283.4261474609375</v>
       </c>
       <c r="F113" t="n">
-        <v>9091200</v>
+        <v>8149000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B114" t="n">
-        <v>283.6044205599556</v>
+        <v>286.2390279690733</v>
       </c>
       <c r="C114" t="n">
-        <v>286.506421278288</v>
+        <v>288.9726698808299</v>
       </c>
       <c r="D114" t="n">
-        <v>281.8909373944359</v>
+        <v>283.2181783456238</v>
       </c>
       <c r="E114" t="n">
-        <v>283.4261474609375</v>
+        <v>284.1492004394531</v>
       </c>
       <c r="F114" t="n">
-        <v>8149000</v>
+        <v>8961200</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B115" t="n">
-        <v>286.2390279690733</v>
+        <v>284.0897484324327</v>
       </c>
       <c r="C115" t="n">
-        <v>288.9726698808299</v>
+        <v>286.6451172582804</v>
       </c>
       <c r="D115" t="n">
-        <v>283.2181783456238</v>
+        <v>282.3960934275981</v>
       </c>
       <c r="E115" t="n">
-        <v>284.1492004394531</v>
+        <v>284.9910583496094</v>
       </c>
       <c r="F115" t="n">
-        <v>8961200</v>
+        <v>10057000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B116" t="n">
-        <v>284.0897180113691</v>
+        <v>284.1392586396808</v>
       </c>
       <c r="C116" t="n">
-        <v>286.6450865635814</v>
+        <v>286.7441374214082</v>
       </c>
       <c r="D116" t="n">
-        <v>282.3960631878955</v>
+        <v>281.9008401776293</v>
       </c>
       <c r="E116" t="n">
-        <v>284.9910278320312</v>
+        <v>285.2188415527344</v>
       </c>
       <c r="F116" t="n">
-        <v>10057000</v>
+        <v>9846700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B117" t="n">
-        <v>284.1392890417467</v>
+        <v>285.327825032355</v>
       </c>
       <c r="C117" t="n">
-        <v>286.7441681021885</v>
+        <v>287.9327042603992</v>
       </c>
       <c r="D117" t="n">
-        <v>281.900870340191</v>
+        <v>282.5446726819272</v>
       </c>
       <c r="E117" t="n">
-        <v>285.2188720703125</v>
+        <v>283.8223571777344</v>
       </c>
       <c r="F117" t="n">
-        <v>9846700</v>
+        <v>22436500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B118" t="n">
-        <v>285.3277943529036</v>
+        <v>291.4982779446762</v>
       </c>
       <c r="C118" t="n">
-        <v>287.9326733008621</v>
+        <v>292.9245231806114</v>
       </c>
       <c r="D118" t="n">
-        <v>282.5446423017302</v>
+        <v>285.2188513876401</v>
       </c>
       <c r="E118" t="n">
-        <v>283.8223266601562</v>
+        <v>287.1403198242188</v>
       </c>
       <c r="F118" t="n">
-        <v>22436500</v>
+        <v>11470800</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B119" t="n">
-        <v>291.4982779446762</v>
+        <v>283.4360748065673</v>
       </c>
       <c r="C119" t="n">
-        <v>292.9245231806114</v>
+        <v>292.6571288676103</v>
       </c>
       <c r="D119" t="n">
-        <v>285.2188513876401</v>
+        <v>282.6436995084055</v>
       </c>
       <c r="E119" t="n">
-        <v>287.1403198242188</v>
+        <v>289.6065368652344</v>
       </c>
       <c r="F119" t="n">
-        <v>11470800</v>
+        <v>11092300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B120" t="n">
-        <v>283.4360748065673</v>
+        <v>291.3398308899875</v>
       </c>
       <c r="C120" t="n">
-        <v>292.6571288676103</v>
+        <v>294.7965097163498</v>
       </c>
       <c r="D120" t="n">
-        <v>282.6436995084055</v>
+        <v>289.6461758443202</v>
       </c>
       <c r="E120" t="n">
-        <v>289.6065368652344</v>
+        <v>292.5977172851562</v>
       </c>
       <c r="F120" t="n">
-        <v>11092300</v>
+        <v>12188200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B121" t="n">
-        <v>291.3398308899875</v>
+        <v>289.7848205526045</v>
       </c>
       <c r="C121" t="n">
-        <v>294.7965097163498</v>
+        <v>292.1718002190451</v>
       </c>
       <c r="D121" t="n">
-        <v>289.6461758443202</v>
+        <v>287.9525187281419</v>
       </c>
       <c r="E121" t="n">
-        <v>292.5977172851562</v>
+        <v>288.8736267089844</v>
       </c>
       <c r="F121" t="n">
-        <v>12188200</v>
+        <v>8669200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B122" t="n">
-        <v>289.7847899387647</v>
+        <v>286.3777093696089</v>
       </c>
       <c r="C122" t="n">
-        <v>292.1717693530369</v>
+        <v>287.3384134369941</v>
       </c>
       <c r="D122" t="n">
-        <v>287.9524883078727</v>
+        <v>279.0582953832721</v>
       </c>
       <c r="E122" t="n">
-        <v>288.8735961914062</v>
+        <v>280.1378784179688</v>
       </c>
       <c r="F122" t="n">
-        <v>8669200</v>
+        <v>9873300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B123" t="n">
-        <v>286.3777093696089</v>
+        <v>282.0197247859078</v>
       </c>
       <c r="C123" t="n">
-        <v>287.3384134369941</v>
+        <v>284.505755156032</v>
       </c>
       <c r="D123" t="n">
-        <v>279.0582953832721</v>
+        <v>279.6327451103039</v>
       </c>
       <c r="E123" t="n">
-        <v>280.1378784179688</v>
+        <v>281.0589904785156</v>
       </c>
       <c r="F123" t="n">
-        <v>9873300</v>
+        <v>11734400</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>282.0197247859078</v>
+        <v>285.7140887250632</v>
       </c>
       <c r="C124" t="n">
-        <v>284.505755156032</v>
+        <v>292.2510413422024</v>
       </c>
       <c r="D124" t="n">
-        <v>279.6327451103039</v>
+        <v>282.2277281014015</v>
       </c>
       <c r="E124" t="n">
-        <v>281.0589904785156</v>
+        <v>291.3497314453125</v>
       </c>
       <c r="F124" t="n">
-        <v>11734400</v>
+        <v>12956900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B125" t="n">
-        <v>285.7140887250632</v>
+        <v>292.567989087923</v>
       </c>
       <c r="C125" t="n">
-        <v>292.2510413422024</v>
+        <v>295.8661624411999</v>
       </c>
       <c r="D125" t="n">
-        <v>282.2277281014015</v>
+        <v>290.1116710297465</v>
       </c>
       <c r="E125" t="n">
-        <v>291.3497314453125</v>
+        <v>292.5580749511719</v>
       </c>
       <c r="F125" t="n">
-        <v>12956900</v>
+        <v>11267200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B126" t="n">
-        <v>292.567989087923</v>
+        <v>289.1212191631598</v>
       </c>
       <c r="C126" t="n">
-        <v>295.8661624411999</v>
+        <v>292.7957669317203</v>
       </c>
       <c r="D126" t="n">
-        <v>290.1116710297465</v>
+        <v>285.9616926535428</v>
       </c>
       <c r="E126" t="n">
-        <v>292.5580749511719</v>
+        <v>291.7855224609375</v>
       </c>
       <c r="F126" t="n">
-        <v>11267200</v>
+        <v>6669300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,25 +3719,25 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B127" t="n">
-        <v>289.1212191631598</v>
+        <v>292.7412191857173</v>
       </c>
       <c r="C127" t="n">
-        <v>292.7957669317203</v>
+        <v>295.4987855589938</v>
       </c>
       <c r="D127" t="n">
-        <v>285.9616926535428</v>
+        <v>291.8850906324002</v>
       </c>
       <c r="E127" t="n">
-        <v>291.7855224609375</v>
+        <v>294.125</v>
       </c>
       <c r="F127" t="n">
-        <v>6669300</v>
+        <v>7142600</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -3745,25 +3745,25 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B128" t="n">
-        <v>292.7412191857173</v>
+        <v>291.8253790066561</v>
       </c>
       <c r="C128" t="n">
-        <v>295.4987855589938</v>
+        <v>296.8427544058445</v>
       </c>
       <c r="D128" t="n">
-        <v>291.8850906324002</v>
+        <v>291.3873498301165</v>
       </c>
       <c r="E128" t="n">
-        <v>294.125</v>
+        <v>296.0662536621094</v>
       </c>
       <c r="F128" t="n">
-        <v>7142600</v>
+        <v>7849100</v>
       </c>
       <c r="G128" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B129" t="n">
-        <v>291.8253790066561</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="C129" t="n">
-        <v>296.8427544058445</v>
+        <v>309.8640903908154</v>
       </c>
       <c r="D129" t="n">
-        <v>291.3873498301165</v>
+        <v>303.9606617936424</v>
       </c>
       <c r="E129" t="n">
-        <v>296.0662536621094</v>
+        <v>306.5888366699219</v>
       </c>
       <c r="F129" t="n">
-        <v>7849100</v>
+        <v>10590200</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B130" t="n">
-        <v>306.5888366699219</v>
+        <v>305.5734164156603</v>
       </c>
       <c r="C130" t="n">
-        <v>309.8640903908154</v>
+        <v>309.8640846884941</v>
       </c>
       <c r="D130" t="n">
-        <v>303.9606617936424</v>
+        <v>304.73715687535</v>
       </c>
       <c r="E130" t="n">
-        <v>306.5888366699219</v>
+        <v>308.938232421875</v>
       </c>
       <c r="F130" t="n">
-        <v>10590200</v>
+        <v>6586600</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B131" t="n">
-        <v>305.5734164156603</v>
+        <v>308.6097380099313</v>
       </c>
       <c r="C131" t="n">
-        <v>309.8640846884941</v>
+        <v>308.9581744354404</v>
       </c>
       <c r="D131" t="n">
-        <v>304.73715687535</v>
+        <v>305.344449093958</v>
       </c>
       <c r="E131" t="n">
-        <v>308.938232421875</v>
+        <v>308.4803161621094</v>
       </c>
       <c r="F131" t="n">
-        <v>6586600</v>
+        <v>6069700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B132" t="n">
-        <v>308.6097380099313</v>
+        <v>306.0910825316173</v>
       </c>
       <c r="C132" t="n">
-        <v>308.9581744354404</v>
+        <v>312.3329523629397</v>
       </c>
       <c r="D132" t="n">
-        <v>305.344449093958</v>
+        <v>304.0900871089203</v>
       </c>
       <c r="E132" t="n">
-        <v>308.4803161621094</v>
+        <v>312.2732238769531</v>
       </c>
       <c r="F132" t="n">
-        <v>6069700</v>
+        <v>8318200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B133" t="n">
-        <v>306.0910825316173</v>
+        <v>308.4305432499699</v>
       </c>
       <c r="C133" t="n">
-        <v>312.3329523629397</v>
+        <v>312.9103618924516</v>
       </c>
       <c r="D133" t="n">
-        <v>304.0900871089203</v>
+        <v>307.4847916064935</v>
       </c>
       <c r="E133" t="n">
-        <v>312.2732238769531</v>
+        <v>309.7247009277344</v>
       </c>
       <c r="F133" t="n">
-        <v>8318200</v>
+        <v>11455500</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B134" t="n">
-        <v>308.4305432499699</v>
+        <v>312.5420354159922</v>
       </c>
       <c r="C134" t="n">
-        <v>312.9103618924516</v>
+        <v>312.8307129741003</v>
       </c>
       <c r="D134" t="n">
-        <v>307.4847916064935</v>
+        <v>302.8954898881459</v>
       </c>
       <c r="E134" t="n">
-        <v>309.7247009277344</v>
+        <v>304.5579833984375</v>
       </c>
       <c r="F134" t="n">
-        <v>11455500</v>
+        <v>9885800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B135" t="n">
-        <v>312.5420354159922</v>
+        <v>303.9805907681049</v>
       </c>
       <c r="C135" t="n">
-        <v>312.8307129741003</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="D135" t="n">
-        <v>302.8954898881459</v>
+        <v>303.8312695552229</v>
       </c>
       <c r="E135" t="n">
-        <v>304.5579833984375</v>
+        <v>308.5599670410156</v>
       </c>
       <c r="F135" t="n">
-        <v>9885800</v>
+        <v>8208600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B136" t="n">
-        <v>303.9805907681049</v>
+        <v>311.068653468178</v>
       </c>
       <c r="C136" t="n">
-        <v>308.5599670410156</v>
+        <v>313.4877482505245</v>
       </c>
       <c r="D136" t="n">
-        <v>303.8312695552229</v>
+        <v>308.6993222963794</v>
       </c>
       <c r="E136" t="n">
-        <v>308.5599670410156</v>
+        <v>308.8984375</v>
       </c>
       <c r="F136" t="n">
-        <v>8208600</v>
+        <v>11082400</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B137" t="n">
-        <v>311.068653468178</v>
+        <v>309.4559416581444</v>
       </c>
       <c r="C137" t="n">
-        <v>313.4877482505245</v>
+        <v>315.7077766193834</v>
       </c>
       <c r="D137" t="n">
-        <v>308.6993222963794</v>
+        <v>308.9780833700189</v>
       </c>
       <c r="E137" t="n">
-        <v>308.8984375</v>
+        <v>315.5683898925781</v>
       </c>
       <c r="F137" t="n">
-        <v>11082400</v>
+        <v>10772000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B138" t="n">
-        <v>309.4559416581444</v>
+        <v>316.0661368489313</v>
       </c>
       <c r="C138" t="n">
-        <v>315.7077766193834</v>
+        <v>318.8038038717339</v>
       </c>
       <c r="D138" t="n">
-        <v>308.9780833700189</v>
+        <v>311.3474041387296</v>
       </c>
       <c r="E138" t="n">
-        <v>315.5683898925781</v>
+        <v>311.5962829589844</v>
       </c>
       <c r="F138" t="n">
-        <v>10772000</v>
+        <v>7084300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B139" t="n">
-        <v>316.0661368489313</v>
+        <v>313.4379903862348</v>
       </c>
       <c r="C139" t="n">
-        <v>318.8038038717339</v>
+        <v>313.7366328164263</v>
       </c>
       <c r="D139" t="n">
-        <v>311.3474041387296</v>
+        <v>310.5410372905177</v>
       </c>
       <c r="E139" t="n">
-        <v>311.5962829589844</v>
+        <v>311.6161804199219</v>
       </c>
       <c r="F139" t="n">
-        <v>7084300</v>
+        <v>5545900</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B140" t="n">
-        <v>313.4379903862348</v>
+        <v>312.1139549773267</v>
       </c>
       <c r="C140" t="n">
-        <v>313.7366328164263</v>
+        <v>313.5773637260273</v>
       </c>
       <c r="D140" t="n">
-        <v>310.5410372905177</v>
+        <v>307.5047445243564</v>
       </c>
       <c r="E140" t="n">
-        <v>311.6161804199219</v>
+        <v>310.2921752929688</v>
       </c>
       <c r="F140" t="n">
-        <v>5545900</v>
+        <v>6969700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B141" t="n">
-        <v>312.1139549773267</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="C141" t="n">
-        <v>313.5773637260273</v>
+        <v>309.7545850384977</v>
       </c>
       <c r="D141" t="n">
-        <v>307.5047445243564</v>
+        <v>306.5092257615542</v>
       </c>
       <c r="E141" t="n">
-        <v>310.2921752929688</v>
+        <v>306.8974609375</v>
       </c>
       <c r="F141" t="n">
-        <v>6969700</v>
+        <v>5215300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B142" t="n">
-        <v>309.7545850384977</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="C142" t="n">
-        <v>309.7545850384977</v>
+        <v>311.1781431330245</v>
       </c>
       <c r="D142" t="n">
-        <v>306.5092257615542</v>
+        <v>305.5037244427344</v>
       </c>
       <c r="E142" t="n">
-        <v>306.8974609375</v>
+        <v>310.232421875</v>
       </c>
       <c r="F142" t="n">
-        <v>5215300</v>
+        <v>7925300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B143" t="n">
-        <v>305.5037244427344</v>
+        <v>313.7864355589005</v>
       </c>
       <c r="C143" t="n">
-        <v>311.1781431330245</v>
+        <v>314.035314384572</v>
       </c>
       <c r="D143" t="n">
-        <v>305.5037244427344</v>
+        <v>309.7745101043047</v>
       </c>
       <c r="E143" t="n">
-        <v>310.232421875</v>
+        <v>310.0532531738281</v>
       </c>
       <c r="F143" t="n">
-        <v>7925300</v>
+        <v>7398600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B144" t="n">
-        <v>313.7864355589005</v>
+        <v>309.1771855961317</v>
       </c>
       <c r="C144" t="n">
-        <v>314.035314384572</v>
+        <v>310.6505287563671</v>
       </c>
       <c r="D144" t="n">
-        <v>309.7745101043047</v>
+        <v>305.9118967162461</v>
       </c>
       <c r="E144" t="n">
-        <v>310.0532531738281</v>
+        <v>307.8630981445312</v>
       </c>
       <c r="F144" t="n">
-        <v>7398600</v>
+        <v>8031800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B145" t="n">
-        <v>309.1771855961317</v>
+        <v>305.6928786901284</v>
       </c>
       <c r="C145" t="n">
-        <v>310.6505287563671</v>
+        <v>312.6913497643884</v>
       </c>
       <c r="D145" t="n">
-        <v>305.9118967162461</v>
+        <v>305.1951210592971</v>
       </c>
       <c r="E145" t="n">
-        <v>307.8630981445312</v>
+        <v>311.8252563476562</v>
       </c>
       <c r="F145" t="n">
-        <v>8031800</v>
+        <v>8865400</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B146" t="n">
-        <v>305.6928786901284</v>
+        <v>312.5420381202088</v>
       </c>
       <c r="C146" t="n">
-        <v>312.6913497643884</v>
+        <v>314.6624601726697</v>
       </c>
       <c r="D146" t="n">
-        <v>305.1951210592971</v>
+        <v>310.431520181067</v>
       </c>
       <c r="E146" t="n">
-        <v>311.8252563476562</v>
+        <v>311.0686645507812</v>
       </c>
       <c r="F146" t="n">
-        <v>8865400</v>
+        <v>6135400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B147" t="n">
-        <v>312.5420381202088</v>
+        <v>309.2269452093906</v>
       </c>
       <c r="C147" t="n">
-        <v>314.6624601726697</v>
+        <v>309.2568094519629</v>
       </c>
       <c r="D147" t="n">
-        <v>310.431520181067</v>
+        <v>305.1353920734132</v>
       </c>
       <c r="E147" t="n">
-        <v>311.0686645507812</v>
+        <v>306.270263671875</v>
       </c>
       <c r="F147" t="n">
-        <v>6135400</v>
+        <v>7338200</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B148" t="n">
-        <v>309.2269452093906</v>
+        <v>306.3299974055641</v>
       </c>
       <c r="C148" t="n">
-        <v>309.2568094519629</v>
+        <v>309.5753869306937</v>
       </c>
       <c r="D148" t="n">
-        <v>305.1353920734132</v>
+        <v>305.42407485773</v>
       </c>
       <c r="E148" t="n">
-        <v>306.270263671875</v>
+        <v>308.0124206542969</v>
       </c>
       <c r="F148" t="n">
-        <v>7338200</v>
+        <v>6316800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B149" t="n">
-        <v>306.3299974055641</v>
+        <v>310.0532528884956</v>
       </c>
       <c r="C149" t="n">
-        <v>309.5753869306937</v>
+        <v>314.8416790595512</v>
       </c>
       <c r="D149" t="n">
-        <v>305.42407485773</v>
+        <v>309.9536952821754</v>
       </c>
       <c r="E149" t="n">
-        <v>308.0124206542969</v>
+        <v>313.4877624511719</v>
       </c>
       <c r="F149" t="n">
-        <v>6316800</v>
+        <v>8629500</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B150" t="n">
-        <v>310.0532528884956</v>
+        <v>313.2388767644321</v>
       </c>
       <c r="C150" t="n">
-        <v>314.8416790595512</v>
+        <v>314.8814709002291</v>
       </c>
       <c r="D150" t="n">
-        <v>309.9536952821754</v>
+        <v>304.7670623908274</v>
       </c>
       <c r="E150" t="n">
-        <v>313.4877624511719</v>
+        <v>304.8964538574219</v>
       </c>
       <c r="F150" t="n">
-        <v>8629500</v>
+        <v>8359600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B151" t="n">
-        <v>313.2388767644321</v>
+        <v>306.8675912418493</v>
       </c>
       <c r="C151" t="n">
-        <v>314.8814709002291</v>
+        <v>307.6042628420606</v>
       </c>
       <c r="D151" t="n">
-        <v>304.7670623908274</v>
+        <v>299.1523476664256</v>
       </c>
       <c r="E151" t="n">
-        <v>304.8964538574219</v>
+        <v>300.7451782226562</v>
       </c>
       <c r="F151" t="n">
-        <v>8359600</v>
+        <v>9464300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B152" t="n">
-        <v>306.8675912418493</v>
+        <v>300.7451596100784</v>
       </c>
       <c r="C152" t="n">
-        <v>307.6042628420606</v>
+        <v>301.8302675742967</v>
       </c>
       <c r="D152" t="n">
-        <v>299.1523476664256</v>
+        <v>297.5395993270601</v>
       </c>
       <c r="E152" t="n">
-        <v>300.7451782226562</v>
+        <v>298.6545715332031</v>
       </c>
       <c r="F152" t="n">
-        <v>9464300</v>
+        <v>9512000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B153" t="n">
-        <v>300.7451596100784</v>
+        <v>298.6744753830843</v>
       </c>
       <c r="C153" t="n">
-        <v>301.8302675742967</v>
+        <v>304.6873960201211</v>
       </c>
       <c r="D153" t="n">
-        <v>297.5395993270601</v>
+        <v>294.2245209852311</v>
       </c>
       <c r="E153" t="n">
-        <v>298.6545715332031</v>
+        <v>303.5126953125</v>
       </c>
       <c r="F153" t="n">
-        <v>9512000</v>
+        <v>9498200</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B154" t="n">
-        <v>298.6744753830843</v>
+        <v>300.9144028967509</v>
       </c>
       <c r="C154" t="n">
-        <v>304.6873960201211</v>
+        <v>301.6411400127173</v>
       </c>
       <c r="D154" t="n">
-        <v>294.2245209852311</v>
+        <v>298.7242874353194</v>
       </c>
       <c r="E154" t="n">
-        <v>303.5126953125</v>
+        <v>298.9034729003906</v>
       </c>
       <c r="F154" t="n">
-        <v>9498200</v>
+        <v>7709500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B155" t="n">
-        <v>300.9144028967509</v>
+        <v>300.8945046380796</v>
       </c>
       <c r="C155" t="n">
-        <v>301.6411400127173</v>
+        <v>302.387777613951</v>
       </c>
       <c r="D155" t="n">
-        <v>298.7242874353194</v>
+        <v>297.4699295162906</v>
       </c>
       <c r="E155" t="n">
-        <v>298.9034729003906</v>
+        <v>298.5650024414062</v>
       </c>
       <c r="F155" t="n">
-        <v>7709500</v>
+        <v>7364300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B156" t="n">
-        <v>300.8945046380796</v>
+        <v>298.8636262885424</v>
       </c>
       <c r="C156" t="n">
-        <v>302.387777613951</v>
+        <v>299.4410421498196</v>
       </c>
       <c r="D156" t="n">
-        <v>297.4699295162906</v>
+        <v>295.1205095874812</v>
       </c>
       <c r="E156" t="n">
-        <v>298.5650024414062</v>
+        <v>296.4743957519531</v>
       </c>
       <c r="F156" t="n">
-        <v>7364300</v>
+        <v>8699300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B157" t="n">
-        <v>298.8636262885424</v>
+        <v>296.6635495230975</v>
       </c>
       <c r="C157" t="n">
-        <v>299.4410421498196</v>
+        <v>299.908939014877</v>
       </c>
       <c r="D157" t="n">
-        <v>295.1205095874812</v>
+        <v>295.8870488301784</v>
       </c>
       <c r="E157" t="n">
-        <v>296.4743957519531</v>
+        <v>299.3813171386719</v>
       </c>
       <c r="F157" t="n">
-        <v>8699300</v>
+        <v>7546300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B158" t="n">
-        <v>296.6635495230975</v>
+        <v>299.7396822358739</v>
       </c>
       <c r="C158" t="n">
-        <v>299.908939014877</v>
+        <v>300.436555061437</v>
       </c>
       <c r="D158" t="n">
-        <v>295.8870488301784</v>
+        <v>293.935841710235</v>
       </c>
       <c r="E158" t="n">
-        <v>299.3813171386719</v>
+        <v>294.3738708496094</v>
       </c>
       <c r="F158" t="n">
-        <v>7546300</v>
+        <v>8066900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B159" t="n">
-        <v>299.7396822358739</v>
+        <v>295.3694126574367</v>
       </c>
       <c r="C159" t="n">
-        <v>300.436555061437</v>
+        <v>301.57145376365</v>
       </c>
       <c r="D159" t="n">
-        <v>293.935841710235</v>
+        <v>292.3530024013792</v>
       </c>
       <c r="E159" t="n">
-        <v>294.3738708496094</v>
+        <v>300.625732421875</v>
       </c>
       <c r="F159" t="n">
-        <v>8066900</v>
+        <v>9327000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B160" t="n">
-        <v>295.3694126574367</v>
+        <v>299.8790926087445</v>
       </c>
       <c r="C160" t="n">
-        <v>301.57145376365</v>
+        <v>302.6167597554335</v>
       </c>
       <c r="D160" t="n">
-        <v>292.3530024013792</v>
+        <v>298.8636475324957</v>
       </c>
       <c r="E160" t="n">
-        <v>300.625732421875</v>
+        <v>301.6411437988281</v>
       </c>
       <c r="F160" t="n">
-        <v>9327000</v>
+        <v>7874400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B161" t="n">
-        <v>299.8790926087445</v>
+        <v>303.3135932887391</v>
       </c>
       <c r="C161" t="n">
-        <v>302.6167597554335</v>
+        <v>306.0711901040885</v>
       </c>
       <c r="D161" t="n">
-        <v>298.8636475324957</v>
+        <v>302.4773640852478</v>
       </c>
       <c r="E161" t="n">
-        <v>301.6411437988281</v>
+        <v>305.0059814453125</v>
       </c>
       <c r="F161" t="n">
-        <v>7874400</v>
+        <v>5973900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B162" t="n">
-        <v>303.3135932887391</v>
+        <v>307.1065011172144</v>
       </c>
       <c r="C162" t="n">
-        <v>306.0711901040885</v>
+        <v>308.5400455607295</v>
       </c>
       <c r="D162" t="n">
-        <v>302.4773640852478</v>
+        <v>304.0701916446211</v>
       </c>
       <c r="E162" t="n">
-        <v>305.0059814453125</v>
+        <v>305.3643493652344</v>
       </c>
       <c r="F162" t="n">
-        <v>5973900</v>
+        <v>7725400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B163" t="n">
-        <v>307.1065011172144</v>
+        <v>303.6321536663258</v>
       </c>
       <c r="C163" t="n">
-        <v>308.5400455607295</v>
+        <v>304.5281113223131</v>
       </c>
       <c r="D163" t="n">
-        <v>304.0701916446211</v>
+        <v>294.4236375305438</v>
       </c>
       <c r="E163" t="n">
-        <v>305.3643493652344</v>
+        <v>297.9378051757812</v>
       </c>
       <c r="F163" t="n">
-        <v>7725400</v>
+        <v>11779200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B164" t="n">
-        <v>303.6321536663258</v>
+        <v>296.2354906683788</v>
       </c>
       <c r="C164" t="n">
-        <v>304.5281113223131</v>
+        <v>299.7197941661088</v>
       </c>
       <c r="D164" t="n">
-        <v>294.4236375305438</v>
+        <v>294.4236455581874</v>
       </c>
       <c r="E164" t="n">
-        <v>297.9378051757812</v>
+        <v>295.3992614746094</v>
       </c>
       <c r="F164" t="n">
-        <v>11779200</v>
+        <v>9757700</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B165" t="n">
-        <v>296.2354906683788</v>
+        <v>295.070728717322</v>
       </c>
       <c r="C165" t="n">
-        <v>299.7197941661088</v>
+        <v>298.5351328968941</v>
       </c>
       <c r="D165" t="n">
-        <v>294.4236455581874</v>
+        <v>293.8761285862639</v>
       </c>
       <c r="E165" t="n">
-        <v>295.3992614746094</v>
+        <v>297.9676818847656</v>
       </c>
       <c r="F165" t="n">
-        <v>9757700</v>
+        <v>13969000</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B166" t="n">
-        <v>295.070728717322</v>
+        <v>296.3549462063085</v>
       </c>
       <c r="C166" t="n">
-        <v>298.5351328968941</v>
+        <v>298.2065900448191</v>
       </c>
       <c r="D166" t="n">
-        <v>293.8761285862639</v>
+        <v>293.9457858606032</v>
       </c>
       <c r="E166" t="n">
-        <v>297.9676818847656</v>
+        <v>295.2499084472656</v>
       </c>
       <c r="F166" t="n">
-        <v>13969000</v>
+        <v>7930000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B167" t="n">
-        <v>296.3549462063085</v>
+        <v>295.170270518017</v>
       </c>
       <c r="C167" t="n">
-        <v>298.2065900448191</v>
+        <v>300.7152977310929</v>
       </c>
       <c r="D167" t="n">
-        <v>293.9457858606032</v>
+        <v>293.9457758280521</v>
       </c>
       <c r="E167" t="n">
-        <v>295.2499084472656</v>
+        <v>299.6102600097656</v>
       </c>
       <c r="F167" t="n">
-        <v>7930000</v>
+        <v>8296200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B168" t="n">
-        <v>295.170270518017</v>
+        <v>298.5749714904202</v>
       </c>
       <c r="C168" t="n">
-        <v>300.7152977310929</v>
+        <v>300.6058008918799</v>
       </c>
       <c r="D168" t="n">
-        <v>293.9457758280521</v>
+        <v>295.2300241797341</v>
       </c>
       <c r="E168" t="n">
-        <v>299.6102600097656</v>
+        <v>299.5007934570312</v>
       </c>
       <c r="F168" t="n">
-        <v>8296200</v>
+        <v>7003900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B169" t="n">
-        <v>298.5749714904202</v>
+        <v>304.3688300919619</v>
       </c>
       <c r="C169" t="n">
-        <v>300.6058008918799</v>
+        <v>311.5066879726736</v>
       </c>
       <c r="D169" t="n">
-        <v>295.2300241797341</v>
+        <v>303.0746723882986</v>
       </c>
       <c r="E169" t="n">
-        <v>299.5007934570312</v>
+        <v>309.4957580566406</v>
       </c>
       <c r="F169" t="n">
-        <v>7003900</v>
+        <v>10345200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B170" t="n">
-        <v>304.3688300919619</v>
+        <v>312.8805189963161</v>
       </c>
       <c r="C170" t="n">
-        <v>311.5066879726736</v>
+        <v>313.5873263681962</v>
       </c>
       <c r="D170" t="n">
-        <v>303.0746723882986</v>
+        <v>308.211549706599</v>
       </c>
       <c r="E170" t="n">
-        <v>309.4957580566406</v>
+        <v>310.9691162109375</v>
       </c>
       <c r="F170" t="n">
-        <v>10345200</v>
+        <v>9118800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B171" t="n">
-        <v>312.8805189963161</v>
+        <v>311.8451695343703</v>
       </c>
       <c r="C171" t="n">
-        <v>313.5873263681962</v>
+        <v>314.881479064701</v>
       </c>
       <c r="D171" t="n">
-        <v>308.211549706599</v>
+        <v>309.3862455138746</v>
       </c>
       <c r="E171" t="n">
-        <v>310.9691162109375</v>
+        <v>309.7147521972656</v>
       </c>
       <c r="F171" t="n">
-        <v>9118800</v>
+        <v>6827000</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B172" t="n">
-        <v>311.8451695343703</v>
+        <v>312.1040028799189</v>
       </c>
       <c r="C172" t="n">
-        <v>314.881479064701</v>
+        <v>315.0009559692908</v>
       </c>
       <c r="D172" t="n">
-        <v>309.3862455138746</v>
+        <v>307.6241841525692</v>
       </c>
       <c r="E172" t="n">
-        <v>309.7147521972656</v>
+        <v>311.2976379394531</v>
       </c>
       <c r="F172" t="n">
-        <v>6827000</v>
+        <v>11594600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B173" t="n">
-        <v>312.1040028799189</v>
+        <v>311.1582462393224</v>
       </c>
       <c r="C173" t="n">
-        <v>315.0009559692908</v>
+        <v>313.3384270822022</v>
       </c>
       <c r="D173" t="n">
-        <v>307.6241841525692</v>
+        <v>307.6440785979976</v>
       </c>
       <c r="E173" t="n">
-        <v>311.2976379394531</v>
+        <v>307.7536010742188</v>
       </c>
       <c r="F173" t="n">
-        <v>11594600</v>
+        <v>7446200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B174" t="n">
-        <v>311.1582462393224</v>
+        <v>308.1717081621576</v>
       </c>
       <c r="C174" t="n">
-        <v>313.3384270822022</v>
+        <v>313.3085706612414</v>
       </c>
       <c r="D174" t="n">
-        <v>307.6440785979976</v>
+        <v>307.4947650619962</v>
       </c>
       <c r="E174" t="n">
-        <v>307.7536010742188</v>
+        <v>312.0840759277344</v>
       </c>
       <c r="F174" t="n">
-        <v>7446200</v>
+        <v>9116600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B175" t="n">
-        <v>308.1717081621576</v>
+        <v>314.5529794375797</v>
       </c>
       <c r="C175" t="n">
-        <v>313.3085706612414</v>
+        <v>319.8590627688811</v>
       </c>
       <c r="D175" t="n">
-        <v>307.4947650619962</v>
+        <v>314.1348496322589</v>
       </c>
       <c r="E175" t="n">
-        <v>312.0840759277344</v>
+        <v>319.2816772460938</v>
       </c>
       <c r="F175" t="n">
-        <v>9116600</v>
+        <v>7426200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B176" t="n">
-        <v>314.5529794375797</v>
+        <v>322.4673390673774</v>
       </c>
       <c r="C176" t="n">
-        <v>319.8590627688811</v>
+        <v>324.4583697274161</v>
       </c>
       <c r="D176" t="n">
-        <v>314.1348496322589</v>
+        <v>317.4101041776777</v>
       </c>
       <c r="E176" t="n">
-        <v>319.2816772460938</v>
+        <v>317.9675903320312</v>
       </c>
       <c r="F176" t="n">
-        <v>7426200</v>
+        <v>7988900</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B177" t="n">
-        <v>322.4673390673774</v>
+        <v>322.8455866314347</v>
       </c>
       <c r="C177" t="n">
-        <v>324.4583697274161</v>
+        <v>330.2621874699331</v>
       </c>
       <c r="D177" t="n">
-        <v>317.4101041776777</v>
+        <v>322.5668435738929</v>
       </c>
       <c r="E177" t="n">
-        <v>317.9675903320312</v>
+        <v>329.6549377441406</v>
       </c>
       <c r="F177" t="n">
-        <v>7988900</v>
+        <v>11094900</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B178" t="n">
-        <v>322.8455866314347</v>
+        <v>330.6902497468859</v>
       </c>
       <c r="C178" t="n">
-        <v>330.2621874699331</v>
+        <v>336.2551763704633</v>
       </c>
       <c r="D178" t="n">
-        <v>322.5668435738929</v>
+        <v>330.0133066656099</v>
       </c>
       <c r="E178" t="n">
-        <v>329.6549377441406</v>
+        <v>331.9645080566406</v>
       </c>
       <c r="F178" t="n">
-        <v>11094900</v>
+        <v>12246400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B179" t="n">
-        <v>330.6902497468859</v>
+        <v>335.4388795655989</v>
       </c>
       <c r="C179" t="n">
-        <v>336.2551763704633</v>
+        <v>336.5737511659094</v>
       </c>
       <c r="D179" t="n">
-        <v>330.0133066656099</v>
+        <v>322.7062308624821</v>
       </c>
       <c r="E179" t="n">
-        <v>331.9645080566406</v>
+        <v>323.761474609375</v>
       </c>
       <c r="F179" t="n">
-        <v>12246400</v>
+        <v>20111000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B180" t="n">
-        <v>335.4388795655989</v>
+        <v>328.221392261561</v>
       </c>
       <c r="C180" t="n">
-        <v>336.5737511659094</v>
+        <v>331.2776010100568</v>
       </c>
       <c r="D180" t="n">
-        <v>322.7062308624821</v>
+        <v>325.2846101022313</v>
       </c>
       <c r="E180" t="n">
-        <v>323.761474609375</v>
+        <v>329.993408203125</v>
       </c>
       <c r="F180" t="n">
-        <v>20111000</v>
+        <v>10182500</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B181" t="n">
-        <v>328.221392261561</v>
+        <v>327.9924099173137</v>
       </c>
       <c r="C181" t="n">
-        <v>331.2776010100568</v>
+        <v>333.8659438033595</v>
       </c>
       <c r="D181" t="n">
-        <v>325.2846101022313</v>
+        <v>325.7425357353925</v>
       </c>
       <c r="E181" t="n">
-        <v>329.993408203125</v>
+        <v>332.6414794921875</v>
       </c>
       <c r="F181" t="n">
-        <v>10182500</v>
+        <v>7582200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B182" t="n">
-        <v>327.9924099173137</v>
+        <v>331.5762891678024</v>
       </c>
       <c r="C182" t="n">
-        <v>333.8659438033595</v>
+        <v>333.0297330031709</v>
       </c>
       <c r="D182" t="n">
-        <v>325.7425357353925</v>
+        <v>328.291070440402</v>
       </c>
       <c r="E182" t="n">
-        <v>332.6414794921875</v>
+        <v>331.95458984375</v>
       </c>
       <c r="F182" t="n">
-        <v>7582200</v>
+        <v>7907400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B183" t="n">
-        <v>331.5762891678024</v>
+        <v>333.4577793441399</v>
       </c>
       <c r="C183" t="n">
-        <v>333.0297330031709</v>
+        <v>341.909724468194</v>
       </c>
       <c r="D183" t="n">
-        <v>328.291070440402</v>
+        <v>333.2586945227413</v>
       </c>
       <c r="E183" t="n">
-        <v>331.95458984375</v>
+        <v>333.6170654296875</v>
       </c>
       <c r="F183" t="n">
-        <v>7907400</v>
+        <v>10043100</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B184" t="n">
-        <v>333.4577793441399</v>
+        <v>334.4931229022353</v>
       </c>
       <c r="C184" t="n">
-        <v>341.909724468194</v>
+        <v>334.8913229247855</v>
       </c>
       <c r="D184" t="n">
-        <v>333.2586945227413</v>
+        <v>326.0312433050061</v>
       </c>
       <c r="E184" t="n">
-        <v>333.6170654296875</v>
+        <v>327.5742797851562</v>
       </c>
       <c r="F184" t="n">
-        <v>10043100</v>
+        <v>17640900</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B185" t="n">
-        <v>334.4931229022353</v>
+        <v>326.8077430430495</v>
       </c>
       <c r="C185" t="n">
-        <v>334.8913229247855</v>
+        <v>330.8993264933345</v>
       </c>
       <c r="D185" t="n">
-        <v>326.0312433050061</v>
+        <v>325.7325999471821</v>
       </c>
       <c r="E185" t="n">
-        <v>327.5742797851562</v>
+        <v>327.9127807617188</v>
       </c>
       <c r="F185" t="n">
-        <v>17640900</v>
+        <v>7981800</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B186" t="n">
-        <v>326.8077430430495</v>
+        <v>327.4150312810326</v>
       </c>
       <c r="C186" t="n">
-        <v>330.8993264933345</v>
+        <v>328.9580677951163</v>
       </c>
       <c r="D186" t="n">
-        <v>325.7325999471821</v>
+        <v>325.2149206632551</v>
       </c>
       <c r="E186" t="n">
-        <v>327.9127807617188</v>
+        <v>325.8619995117188</v>
       </c>
       <c r="F186" t="n">
-        <v>7981800</v>
+        <v>8080100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B187" t="n">
-        <v>327.4150312810326</v>
+        <v>326.8973584256916</v>
       </c>
       <c r="C187" t="n">
-        <v>328.9580677951163</v>
+        <v>334.1347741939035</v>
       </c>
       <c r="D187" t="n">
-        <v>325.2149206632551</v>
+        <v>323.5524415571975</v>
       </c>
       <c r="E187" t="n">
-        <v>325.8619995117188</v>
+        <v>332.5718078613281</v>
       </c>
       <c r="F187" t="n">
-        <v>8080100</v>
+        <v>15210200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B188" t="n">
-        <v>326.8973584256916</v>
+        <v>336.5040683580973</v>
       </c>
       <c r="C188" t="n">
-        <v>334.1347741939035</v>
+        <v>338.4751995750331</v>
       </c>
       <c r="D188" t="n">
-        <v>323.5524415571975</v>
+        <v>330.2820977776739</v>
       </c>
       <c r="E188" t="n">
-        <v>332.5718078613281</v>
+        <v>332.9700012207031</v>
       </c>
       <c r="F188" t="n">
-        <v>15210200</v>
+        <v>8413900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,25 +5331,25 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B189" t="n">
-        <v>336.5040683580973</v>
+        <v>335</v>
       </c>
       <c r="C189" t="n">
-        <v>338.4751995750331</v>
+        <v>339.7200012207031</v>
       </c>
       <c r="D189" t="n">
-        <v>330.2820977776739</v>
+        <v>334.1099853515625</v>
       </c>
       <c r="E189" t="n">
-        <v>332.9700012207031</v>
+        <v>337.7200012207031</v>
       </c>
       <c r="F189" t="n">
-        <v>8413900</v>
+        <v>8673500</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5357,25 +5357,25 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B190" t="n">
-        <v>335</v>
+        <v>340.9800109863281</v>
       </c>
       <c r="C190" t="n">
-        <v>339.7200012207031</v>
+        <v>341.3999938964844</v>
       </c>
       <c r="D190" t="n">
-        <v>334.1099853515625</v>
+        <v>337.0899963378906</v>
       </c>
       <c r="E190" t="n">
-        <v>337.7200012207031</v>
+        <v>339.2200012207031</v>
       </c>
       <c r="F190" t="n">
-        <v>8673500</v>
+        <v>7115800</v>
       </c>
       <c r="G190" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B191" t="n">
-        <v>340.9800109863281</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="C191" t="n">
-        <v>341.3999938964844</v>
+        <v>336.5299987792969</v>
       </c>
       <c r="D191" t="n">
-        <v>337.0899963378906</v>
+        <v>330.1300048828125</v>
       </c>
       <c r="E191" t="n">
-        <v>339.2200012207031</v>
+        <v>330.6199951171875</v>
       </c>
       <c r="F191" t="n">
-        <v>7115800</v>
+        <v>18505200</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B192" t="n">
-        <v>336.5299987792969</v>
+        <v>331.4599914550781</v>
       </c>
       <c r="C192" t="n">
-        <v>336.5299987792969</v>
+        <v>337</v>
       </c>
       <c r="D192" t="n">
-        <v>330.1300048828125</v>
+        <v>330.8099975585938</v>
       </c>
       <c r="E192" t="n">
-        <v>330.6199951171875</v>
+        <v>335.4700012207031</v>
       </c>
       <c r="F192" t="n">
-        <v>18505200</v>
+        <v>15570600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B193" t="n">
-        <v>331.4599914550781</v>
+        <v>337.4700012207031</v>
       </c>
       <c r="C193" t="n">
-        <v>337</v>
+        <v>338.5899963378906</v>
       </c>
       <c r="D193" t="n">
-        <v>330.8099975585938</v>
+        <v>335.7699890136719</v>
       </c>
       <c r="E193" t="n">
-        <v>335.4700012207031</v>
+        <v>336.4700012207031</v>
       </c>
       <c r="F193" t="n">
-        <v>15570600</v>
+        <v>6299000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B194" t="n">
-        <v>337.4700012207031</v>
+        <v>338.3399963378906</v>
       </c>
       <c r="C194" t="n">
-        <v>338.5899963378906</v>
+        <v>338.3500061035156</v>
       </c>
       <c r="D194" t="n">
-        <v>335.7699890136719</v>
+        <v>332.5</v>
       </c>
       <c r="E194" t="n">
-        <v>336.4700012207031</v>
+        <v>334.5299987792969</v>
       </c>
       <c r="F194" t="n">
-        <v>6299000</v>
+        <v>7120300</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B195" t="n">
-        <v>338.3399963378906</v>
+        <v>327</v>
       </c>
       <c r="C195" t="n">
-        <v>338.3500061035156</v>
+        <v>344.7300109863281</v>
       </c>
       <c r="D195" t="n">
-        <v>332.5</v>
+        <v>325.75</v>
       </c>
       <c r="E195" t="n">
-        <v>334.5299987792969</v>
+        <v>342.8900146484375</v>
       </c>
       <c r="F195" t="n">
-        <v>7120300</v>
+        <v>14537900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>327</v>
+        <v>345.8500061035156</v>
       </c>
       <c r="C196" t="n">
-        <v>344.7300109863281</v>
+        <v>351.239990234375</v>
       </c>
       <c r="D196" t="n">
-        <v>325.75</v>
+        <v>344.0499877929688</v>
       </c>
       <c r="E196" t="n">
-        <v>342.8900146484375</v>
+        <v>346.9100036621094</v>
       </c>
       <c r="F196" t="n">
-        <v>14537900</v>
+        <v>10750000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B197" t="n">
-        <v>345.8500061035156</v>
+        <v>349.2799987792969</v>
       </c>
       <c r="C197" t="n">
-        <v>351.239990234375</v>
+        <v>349.3399963378906</v>
       </c>
       <c r="D197" t="n">
-        <v>344.0499877929688</v>
+        <v>341.1099853515625</v>
       </c>
       <c r="E197" t="n">
-        <v>346.9100036621094</v>
+        <v>343.1499938964844</v>
       </c>
       <c r="F197" t="n">
-        <v>10750000</v>
+        <v>12432400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B198" t="n">
-        <v>349.2799987792969</v>
+        <v>339.0299987792969</v>
       </c>
       <c r="C198" t="n">
-        <v>349.3399963378906</v>
+        <v>346.1300048828125</v>
       </c>
       <c r="D198" t="n">
-        <v>341.1099853515625</v>
+        <v>335.0499877929688</v>
       </c>
       <c r="E198" t="n">
-        <v>343.1499938964844</v>
+        <v>341.1000061035156</v>
       </c>
       <c r="F198" t="n">
-        <v>12432400</v>
+        <v>9250900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B199" t="n">
-        <v>339.0299987792969</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="C199" t="n">
-        <v>346.1300048828125</v>
+        <v>344.260009765625</v>
       </c>
       <c r="D199" t="n">
-        <v>335.0499877929688</v>
+        <v>337.3699951171875</v>
       </c>
       <c r="E199" t="n">
-        <v>341.1000061035156</v>
+        <v>338.8699951171875</v>
       </c>
       <c r="F199" t="n">
-        <v>9250900</v>
+        <v>7723300</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B200" t="n">
-        <v>341.7999877929688</v>
+        <v>340.1199951171875</v>
       </c>
       <c r="C200" t="n">
-        <v>344.260009765625</v>
+        <v>345.739990234375</v>
       </c>
       <c r="D200" t="n">
-        <v>337.3699951171875</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E200" t="n">
-        <v>338.8699951171875</v>
+        <v>345.2300109863281</v>
       </c>
       <c r="F200" t="n">
-        <v>7723300</v>
+        <v>6015300</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B201" t="n">
-        <v>340.1199951171875</v>
+        <v>345.0700073242188</v>
       </c>
       <c r="C201" t="n">
-        <v>345.739990234375</v>
+        <v>349.0700073242188</v>
       </c>
       <c r="D201" t="n">
-        <v>337.2999877929688</v>
+        <v>344.25</v>
       </c>
       <c r="E201" t="n">
-        <v>345.2300109863281</v>
+        <v>348.2099914550781</v>
       </c>
       <c r="F201" t="n">
-        <v>6015300</v>
+        <v>8040200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B202" t="n">
-        <v>345.0700073242188</v>
+        <v>346.5799865722656</v>
       </c>
       <c r="C202" t="n">
-        <v>349.0700073242188</v>
+        <v>349.9200134277344</v>
       </c>
       <c r="D202" t="n">
-        <v>344.25</v>
+        <v>345.4200134277344</v>
       </c>
       <c r="E202" t="n">
-        <v>348.2099914550781</v>
+        <v>349.8999938964844</v>
       </c>
       <c r="F202" t="n">
-        <v>8040200</v>
+        <v>10913000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B203" t="n">
-        <v>346.5799865722656</v>
+        <v>350.6400146484375</v>
       </c>
       <c r="C203" t="n">
-        <v>349.9200134277344</v>
+        <v>353.3699951171875</v>
       </c>
       <c r="D203" t="n">
-        <v>345.4200134277344</v>
+        <v>347.5</v>
       </c>
       <c r="E203" t="n">
-        <v>349.8999938964844</v>
+        <v>353.2099914550781</v>
       </c>
       <c r="F203" t="n">
-        <v>10913000</v>
+        <v>7520800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B204" t="n">
-        <v>350.6400146484375</v>
+        <v>357.8900146484375</v>
       </c>
       <c r="C204" t="n">
-        <v>353.3699951171875</v>
+        <v>359.0499877929688</v>
       </c>
       <c r="D204" t="n">
-        <v>347.5</v>
+        <v>352.5799865722656</v>
       </c>
       <c r="E204" t="n">
-        <v>353.2099914550781</v>
+        <v>356.2000122070312</v>
       </c>
       <c r="F204" t="n">
-        <v>7520800</v>
+        <v>7884900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B205" t="n">
-        <v>357.8900146484375</v>
+        <v>357.2999877929688</v>
       </c>
       <c r="C205" t="n">
-        <v>359.0499877929688</v>
+        <v>359.2999877929688</v>
       </c>
       <c r="D205" t="n">
-        <v>352.5799865722656</v>
+        <v>354.1499938964844</v>
       </c>
       <c r="E205" t="n">
-        <v>356.2000122070312</v>
+        <v>357.3099975585938</v>
       </c>
       <c r="F205" t="n">
-        <v>7884900</v>
+        <v>6533800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B206" t="n">
-        <v>357.2999877929688</v>
+        <v>356.5</v>
       </c>
       <c r="C206" t="n">
-        <v>359.2999877929688</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D206" t="n">
-        <v>354.1499938964844</v>
+        <v>343.7799987792969</v>
       </c>
       <c r="E206" t="n">
-        <v>357.3099975585938</v>
+        <v>344.7099914550781</v>
       </c>
       <c r="F206" t="n">
-        <v>6533800</v>
+        <v>8265300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B207" t="n">
-        <v>356.5</v>
+        <v>347.5400085449219</v>
       </c>
       <c r="C207" t="n">
-        <v>357.3699951171875</v>
+        <v>352.2799987792969</v>
       </c>
       <c r="D207" t="n">
-        <v>343.7799987792969</v>
+        <v>345.3699951171875</v>
       </c>
       <c r="E207" t="n">
-        <v>344.7099914550781</v>
+        <v>350.8500061035156</v>
       </c>
       <c r="F207" t="n">
-        <v>8265300</v>
+        <v>7606500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B208" t="n">
-        <v>347.5400085449219</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C208" t="n">
-        <v>352.2799987792969</v>
+        <v>354.4700012207031</v>
       </c>
       <c r="D208" t="n">
-        <v>345.3699951171875</v>
+        <v>349.7000122070312</v>
       </c>
       <c r="E208" t="n">
-        <v>350.8500061035156</v>
+        <v>351.7900085449219</v>
       </c>
       <c r="F208" t="n">
-        <v>7606500</v>
+        <v>6603400</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B209" t="n">
-        <v>353.2999877929688</v>
+        <v>353.75</v>
       </c>
       <c r="C209" t="n">
-        <v>354.4700012207031</v>
+        <v>355.6199951171875</v>
       </c>
       <c r="D209" t="n">
-        <v>349.7000122070312</v>
+        <v>350.8399963378906</v>
       </c>
       <c r="E209" t="n">
-        <v>351.7900085449219</v>
+        <v>352.6400146484375</v>
       </c>
       <c r="F209" t="n">
-        <v>6603400</v>
+        <v>6436600</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B210" t="n">
-        <v>353.75</v>
+        <v>355</v>
       </c>
       <c r="C210" t="n">
-        <v>355.6199951171875</v>
+        <v>363</v>
       </c>
       <c r="D210" t="n">
-        <v>350.8399963378906</v>
+        <v>353.8699951171875</v>
       </c>
       <c r="E210" t="n">
-        <v>352.6400146484375</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F210" t="n">
-        <v>6436600</v>
+        <v>8477200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B211" t="n">
-        <v>355</v>
+        <v>358.9700012207031</v>
       </c>
       <c r="C211" t="n">
-        <v>363</v>
+        <v>362.1700134277344</v>
       </c>
       <c r="D211" t="n">
-        <v>353.8699951171875</v>
+        <v>358.2000122070312</v>
       </c>
       <c r="E211" t="n">
-        <v>357.5199890136719</v>
+        <v>359.239990234375</v>
       </c>
       <c r="F211" t="n">
-        <v>8477200</v>
+        <v>5269500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B212" t="n">
-        <v>358.9700012207031</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="C212" t="n">
-        <v>362.1700134277344</v>
+        <v>362.8099975585938</v>
       </c>
       <c r="D212" t="n">
-        <v>358.2000122070312</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="E212" t="n">
-        <v>359.239990234375</v>
+        <v>356.2999877929688</v>
       </c>
       <c r="F212" t="n">
-        <v>5269500</v>
+        <v>5820100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B213" t="n">
-        <v>362.8099975585938</v>
+        <v>355.760009765625</v>
       </c>
       <c r="C213" t="n">
-        <v>362.8099975585938</v>
+        <v>358.8500061035156</v>
       </c>
       <c r="D213" t="n">
-        <v>354.9500122070312</v>
+        <v>353.3299865722656</v>
       </c>
       <c r="E213" t="n">
-        <v>356.2999877929688</v>
+        <v>357.5199890136719</v>
       </c>
       <c r="F213" t="n">
-        <v>5820100</v>
+        <v>4566200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B214" t="n">
-        <v>355.760009765625</v>
+        <v>357.9599914550781</v>
       </c>
       <c r="C214" t="n">
-        <v>358.8500061035156</v>
+        <v>359.989990234375</v>
       </c>
       <c r="D214" t="n">
-        <v>353.3299865722656</v>
+        <v>356.5</v>
       </c>
       <c r="E214" t="n">
-        <v>357.5199890136719</v>
+        <v>359.7900085449219</v>
       </c>
       <c r="F214" t="n">
-        <v>4566200</v>
+        <v>5327500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B215" t="n">
-        <v>357.9599914550781</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="C215" t="n">
-        <v>359.989990234375</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="D215" t="n">
-        <v>356.5</v>
+        <v>358.6000061035156</v>
       </c>
       <c r="E215" t="n">
-        <v>359.7900085449219</v>
+        <v>362.0400085449219</v>
       </c>
       <c r="F215" t="n">
-        <v>5327500</v>
+        <v>4576500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B216" t="n">
-        <v>360.0499877929688</v>
+        <v>362.9700012207031</v>
       </c>
       <c r="C216" t="n">
-        <v>363.1199951171875</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="D216" t="n">
-        <v>358.6000061035156</v>
+        <v>361.2999877929688</v>
       </c>
       <c r="E216" t="n">
-        <v>362.0400085449219</v>
+        <v>365.1799926757812</v>
       </c>
       <c r="F216" t="n">
-        <v>4576500</v>
+        <v>4366800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B217" t="n">
-        <v>362.9700012207031</v>
+        <v>366.5</v>
       </c>
       <c r="C217" t="n">
-        <v>366.0899963378906</v>
+        <v>366.5</v>
       </c>
       <c r="D217" t="n">
-        <v>361.2999877929688</v>
+        <v>361.5199890136719</v>
       </c>
       <c r="E217" t="n">
-        <v>365.1799926757812</v>
+        <v>363.1099853515625</v>
       </c>
       <c r="F217" t="n">
-        <v>4366800</v>
+        <v>5102700</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B218" t="n">
-        <v>366.5</v>
+        <v>363</v>
       </c>
       <c r="C218" t="n">
-        <v>366.5</v>
+        <v>365.8999938964844</v>
       </c>
       <c r="D218" t="n">
-        <v>361.5199890136719</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="E218" t="n">
-        <v>363.1099853515625</v>
+        <v>362.8399963378906</v>
       </c>
       <c r="F218" t="n">
-        <v>5102700</v>
+        <v>5058600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B219" t="n">
-        <v>363</v>
+        <v>361.9400024414062</v>
       </c>
       <c r="C219" t="n">
-        <v>365.8999938964844</v>
+        <v>365.75</v>
       </c>
       <c r="D219" t="n">
-        <v>361.4500122070312</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="E219" t="n">
-        <v>362.8399963378906</v>
+        <v>360.9599914550781</v>
       </c>
       <c r="F219" t="n">
-        <v>5058600</v>
+        <v>5282600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B220" t="n">
-        <v>361.9400024414062</v>
+        <v>362.3399963378906</v>
       </c>
       <c r="C220" t="n">
-        <v>365.75</v>
+        <v>363.5700073242188</v>
       </c>
       <c r="D220" t="n">
-        <v>360.9599914550781</v>
+        <v>359.2699890136719</v>
       </c>
       <c r="E220" t="n">
-        <v>360.9599914550781</v>
+        <v>363.25</v>
       </c>
       <c r="F220" t="n">
-        <v>5282600</v>
+        <v>5525100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B221" t="n">
-        <v>362.3399963378906</v>
+        <v>363.010009765625</v>
       </c>
       <c r="C221" t="n">
-        <v>363.5700073242188</v>
+        <v>363.0499877929688</v>
       </c>
       <c r="D221" t="n">
-        <v>359.2699890136719</v>
+        <v>355.6499938964844</v>
       </c>
       <c r="E221" t="n">
-        <v>363.25</v>
+        <v>357.260009765625</v>
       </c>
       <c r="F221" t="n">
-        <v>5525100</v>
+        <v>6696200</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B222" t="n">
-        <v>363.010009765625</v>
+        <v>357.6000061035156</v>
       </c>
       <c r="C222" t="n">
-        <v>363.0499877929688</v>
+        <v>357.9500122070312</v>
       </c>
       <c r="D222" t="n">
-        <v>355.6499938964844</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E222" t="n">
-        <v>357.260009765625</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="F222" t="n">
-        <v>6696200</v>
+        <v>6799700</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B223" t="n">
-        <v>357.6000061035156</v>
+        <v>354.0700073242188</v>
       </c>
       <c r="C223" t="n">
-        <v>357.9500122070312</v>
+        <v>356.8599853515625</v>
       </c>
       <c r="D223" t="n">
-        <v>351.5499877929688</v>
+        <v>350.3699951171875</v>
       </c>
       <c r="E223" t="n">
-        <v>351.5499877929688</v>
+        <v>351.5799865722656</v>
       </c>
       <c r="F223" t="n">
-        <v>6799700</v>
+        <v>8112100</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B224" t="n">
-        <v>354.0700073242188</v>
+        <v>353.2999877929688</v>
       </c>
       <c r="C224" t="n">
-        <v>356.8599853515625</v>
+        <v>358.2799987792969</v>
       </c>
       <c r="D224" t="n">
-        <v>350.3699951171875</v>
+        <v>352.8200073242188</v>
       </c>
       <c r="E224" t="n">
-        <v>351.5799865722656</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="F224" t="n">
-        <v>8112100</v>
+        <v>4394400</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B225" t="n">
-        <v>353.2999877929688</v>
+        <v>357</v>
       </c>
       <c r="C225" t="n">
-        <v>358.2799987792969</v>
+        <v>357.3699951171875</v>
       </c>
       <c r="D225" t="n">
-        <v>352.8200073242188</v>
+        <v>353.0700073242188</v>
       </c>
       <c r="E225" t="n">
-        <v>356.3900146484375</v>
+        <v>356.6900024414062</v>
       </c>
       <c r="F225" t="n">
-        <v>4394400</v>
+        <v>4298000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B226" t="n">
-        <v>357</v>
+        <v>356.5</v>
       </c>
       <c r="C226" t="n">
-        <v>357.3699951171875</v>
+        <v>358.3500061035156</v>
       </c>
       <c r="D226" t="n">
-        <v>353.0700073242188</v>
+        <v>354.6000061035156</v>
       </c>
       <c r="E226" t="n">
-        <v>356.6900024414062</v>
+        <v>356.5</v>
       </c>
       <c r="F226" t="n">
-        <v>4298000</v>
+        <v>5796500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B227" t="n">
-        <v>356.5</v>
+        <v>354.6799926757812</v>
       </c>
       <c r="C227" t="n">
-        <v>358.3500061035156</v>
+        <v>357.5700073242188</v>
       </c>
       <c r="D227" t="n">
-        <v>354.6000061035156</v>
+        <v>352.2300109863281</v>
       </c>
       <c r="E227" t="n">
-        <v>356.5</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="F227" t="n">
-        <v>5796500</v>
+        <v>5209900</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B228" t="n">
-        <v>354.6799926757812</v>
+        <v>355.6700134277344</v>
       </c>
       <c r="C228" t="n">
-        <v>357.5700073242188</v>
+        <v>358.7300109863281</v>
       </c>
       <c r="D228" t="n">
-        <v>352.2300109863281</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="E228" t="n">
-        <v>354.2200012207031</v>
+        <v>357.6199951171875</v>
       </c>
       <c r="F228" t="n">
-        <v>5209900</v>
+        <v>3914500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B229" t="n">
-        <v>355.6700134277344</v>
+        <v>355.8999938964844</v>
       </c>
       <c r="C229" t="n">
-        <v>358.7300109863281</v>
+        <v>357.7699890136719</v>
       </c>
       <c r="D229" t="n">
-        <v>354.2200012207031</v>
+        <v>354.7699890136719</v>
       </c>
       <c r="E229" t="n">
-        <v>357.6199951171875</v>
+        <v>356.0199890136719</v>
       </c>
       <c r="F229" t="n">
-        <v>3914500</v>
+        <v>7962900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B230" t="n">
-        <v>355.8999938964844</v>
+        <v>355.7300109863281</v>
       </c>
       <c r="C230" t="n">
-        <v>357.7699890136719</v>
+        <v>359.9299926757812</v>
       </c>
       <c r="D230" t="n">
-        <v>354.7699890136719</v>
+        <v>354.1199951171875</v>
       </c>
       <c r="E230" t="n">
-        <v>356.0199890136719</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="F230" t="n">
-        <v>7962900</v>
+        <v>5079000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B231" t="n">
-        <v>355.7300109863281</v>
+        <v>357.5499877929688</v>
       </c>
       <c r="C231" t="n">
-        <v>359.9299926757812</v>
+        <v>361.4700012207031</v>
       </c>
       <c r="D231" t="n">
-        <v>354.1199951171875</v>
+        <v>353.7900085449219</v>
       </c>
       <c r="E231" t="n">
-        <v>354.9500122070312</v>
+        <v>356.2200012207031</v>
       </c>
       <c r="F231" t="n">
-        <v>5079000</v>
+        <v>5341400</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B232" t="n">
-        <v>357.5499877929688</v>
+        <v>358.6799926757812</v>
       </c>
       <c r="C232" t="n">
-        <v>361.4700012207031</v>
+        <v>362.8500061035156</v>
       </c>
       <c r="D232" t="n">
-        <v>353.7900085449219</v>
+        <v>356.3900146484375</v>
       </c>
       <c r="E232" t="n">
-        <v>356.2200012207031</v>
+        <v>362.0599975585938</v>
       </c>
       <c r="F232" t="n">
-        <v>5341400</v>
+        <v>5414200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B233" t="n">
-        <v>358.6799926757812</v>
+        <v>361</v>
       </c>
       <c r="C233" t="n">
-        <v>362.8500061035156</v>
+        <v>362.8599853515625</v>
       </c>
       <c r="D233" t="n">
-        <v>356.3900146484375</v>
+        <v>355.2000122070312</v>
       </c>
       <c r="E233" t="n">
-        <v>362.0599975585938</v>
+        <v>358.6400146484375</v>
       </c>
       <c r="F233" t="n">
-        <v>5414200</v>
+        <v>4873500</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B234" t="n">
-        <v>361</v>
+        <v>357.1000061035156</v>
       </c>
       <c r="C234" t="n">
-        <v>362.8599853515625</v>
+        <v>358.5499877929688</v>
       </c>
       <c r="D234" t="n">
-        <v>355.2000122070312</v>
+        <v>353.2300109863281</v>
       </c>
       <c r="E234" t="n">
-        <v>358.6400146484375</v>
+        <v>353.510009765625</v>
       </c>
       <c r="F234" t="n">
-        <v>4873500</v>
+        <v>5631400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B235" t="n">
-        <v>357.1000061035156</v>
+        <v>352</v>
       </c>
       <c r="C235" t="n">
-        <v>358.5499877929688</v>
+        <v>356.3299865722656</v>
       </c>
       <c r="D235" t="n">
-        <v>353.2300109863281</v>
+        <v>348.6900024414062</v>
       </c>
       <c r="E235" t="n">
-        <v>353.510009765625</v>
+        <v>354.7099914550781</v>
       </c>
       <c r="F235" t="n">
-        <v>5631400</v>
+        <v>6318200</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B236" t="n">
-        <v>352</v>
+        <v>353.510009765625</v>
       </c>
       <c r="C236" t="n">
-        <v>356.3299865722656</v>
+        <v>354.2200012207031</v>
       </c>
       <c r="D236" t="n">
-        <v>348.6900024414062</v>
+        <v>351.1199951171875</v>
       </c>
       <c r="E236" t="n">
-        <v>354.7099914550781</v>
+        <v>353.5599975585938</v>
       </c>
       <c r="F236" t="n">
-        <v>6318200</v>
+        <v>4184200</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B237" t="n">
-        <v>353.510009765625</v>
+        <v>358.3200073242188</v>
       </c>
       <c r="C237" t="n">
-        <v>354.2200012207031</v>
+        <v>360.0499877929688</v>
       </c>
       <c r="D237" t="n">
-        <v>351.1199951171875</v>
+        <v>354.7900085449219</v>
       </c>
       <c r="E237" t="n">
-        <v>353.5599975585938</v>
+        <v>356.2300109863281</v>
       </c>
       <c r="F237" t="n">
-        <v>4184200</v>
+        <v>5354600</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B238" t="n">
-        <v>358.3200073242188</v>
+        <v>354.2300109863281</v>
       </c>
       <c r="C238" t="n">
-        <v>360.0499877929688</v>
+        <v>355.2799987792969</v>
       </c>
       <c r="D238" t="n">
-        <v>354.7900085449219</v>
+        <v>347.5499877929688</v>
       </c>
       <c r="E238" t="n">
-        <v>356.2300109863281</v>
+        <v>350.1300048828125</v>
       </c>
       <c r="F238" t="n">
-        <v>5354600</v>
+        <v>9609900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B239" t="n">
-        <v>354.2300109863281</v>
+        <v>351</v>
       </c>
       <c r="C239" t="n">
-        <v>355.2799987792969</v>
+        <v>354.7000122070312</v>
       </c>
       <c r="D239" t="n">
-        <v>347.5499877929688</v>
+        <v>343.0700073242188</v>
       </c>
       <c r="E239" t="n">
-        <v>350.1300048828125</v>
+        <v>352.489990234375</v>
       </c>
       <c r="F239" t="n">
-        <v>9609900</v>
+        <v>14026500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B240" t="n">
-        <v>351</v>
+        <v>353.3800048828125</v>
       </c>
       <c r="C240" t="n">
-        <v>354.7000122070312</v>
+        <v>355.6000061035156</v>
       </c>
       <c r="D240" t="n">
-        <v>343.0700073242188</v>
+        <v>344.6900024414062</v>
       </c>
       <c r="E240" t="n">
-        <v>352.489990234375</v>
+        <v>348.9200134277344</v>
       </c>
       <c r="F240" t="n">
-        <v>14026500</v>
+        <v>8303400</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B241" t="n">
-        <v>353.3800048828125</v>
+        <v>352.25</v>
       </c>
       <c r="C241" t="n">
-        <v>355.6000061035156</v>
+        <v>353.489990234375</v>
       </c>
       <c r="D241" t="n">
-        <v>344.6900024414062</v>
+        <v>345.2699890136719</v>
       </c>
       <c r="E241" t="n">
-        <v>348.9200134277344</v>
+        <v>349.3099975585938</v>
       </c>
       <c r="F241" t="n">
-        <v>8303400</v>
+        <v>6480100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B242" t="n">
-        <v>352.25</v>
+        <v>347.8900146484375</v>
       </c>
       <c r="C242" t="n">
-        <v>353.489990234375</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="D242" t="n">
-        <v>345.2699890136719</v>
+        <v>345.010009765625</v>
       </c>
       <c r="E242" t="n">
-        <v>349.3099975585938</v>
+        <v>349.6700134277344</v>
       </c>
       <c r="F242" t="n">
-        <v>6480100</v>
+        <v>18312400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B243" t="n">
-        <v>347.8900146484375</v>
+        <v>353.6700134277344</v>
       </c>
       <c r="C243" t="n">
-        <v>349.6700134277344</v>
+        <v>354.5</v>
       </c>
       <c r="D243" t="n">
-        <v>345.010009765625</v>
+        <v>350.0799865722656</v>
       </c>
       <c r="E243" t="n">
-        <v>349.6700134277344</v>
+        <v>352.0400085449219</v>
       </c>
       <c r="F243" t="n">
-        <v>18312400</v>
+        <v>6414700</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B244" t="n">
-        <v>353.6700134277344</v>
+        <v>352</v>
       </c>
       <c r="C244" t="n">
-        <v>354.5</v>
+        <v>352.1000061035156</v>
       </c>
       <c r="D244" t="n">
-        <v>350.0799865722656</v>
+        <v>337.2999877929688</v>
       </c>
       <c r="E244" t="n">
-        <v>352.0400085449219</v>
+        <v>340</v>
       </c>
       <c r="F244" t="n">
-        <v>6414700</v>
+        <v>11485600</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B245" t="n">
-        <v>352</v>
+        <v>337.6099853515625</v>
       </c>
       <c r="C245" t="n">
-        <v>352.1000061035156</v>
+        <v>341.4400024414062</v>
       </c>
       <c r="D245" t="n">
-        <v>337.2999877929688</v>
+        <v>336.9800109863281</v>
       </c>
       <c r="E245" t="n">
-        <v>340</v>
+        <v>337.5299987792969</v>
       </c>
       <c r="F245" t="n">
-        <v>11485600</v>
+        <v>7068500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B246" t="n">
-        <v>337.6099853515625</v>
+        <v>338.1199951171875</v>
       </c>
       <c r="C246" t="n">
-        <v>341.4400024414062</v>
+        <v>339.3699951171875</v>
       </c>
       <c r="D246" t="n">
-        <v>336.9800109863281</v>
+        <v>335.2799987792969</v>
       </c>
       <c r="E246" t="n">
-        <v>337.5299987792969</v>
+        <v>338.5599975585938</v>
       </c>
       <c r="F246" t="n">
-        <v>7068500</v>
+        <v>6934300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B247" t="n">
-        <v>338.1199951171875</v>
+        <v>340.7699890136719</v>
       </c>
       <c r="C247" t="n">
-        <v>339.3699951171875</v>
+        <v>343.3099975585938</v>
       </c>
       <c r="D247" t="n">
-        <v>335.2799987792969</v>
+        <v>338.6400146484375</v>
       </c>
       <c r="E247" t="n">
-        <v>338.5599975585938</v>
+        <v>343.0599975585938</v>
       </c>
       <c r="F247" t="n">
-        <v>6934300</v>
+        <v>11460300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B248" t="n">
-        <v>340.7699890136719</v>
+        <v>341.8299865722656</v>
       </c>
       <c r="C248" t="n">
-        <v>343.3099975585938</v>
+        <v>342</v>
       </c>
       <c r="D248" t="n">
-        <v>338.6400146484375</v>
+        <v>336.2999877929688</v>
       </c>
       <c r="E248" t="n">
-        <v>343.0599975585938</v>
+        <v>336.5899963378906</v>
       </c>
       <c r="F248" t="n">
-        <v>11460300</v>
+        <v>10483700</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B249" t="n">
-        <v>341.8299865722656</v>
+        <v>337</v>
       </c>
       <c r="C249" t="n">
-        <v>342</v>
+        <v>338.75</v>
       </c>
       <c r="D249" t="n">
-        <v>336.2999877929688</v>
+        <v>333.3299865722656</v>
       </c>
       <c r="E249" t="n">
-        <v>336.5899963378906</v>
+        <v>334.9800109863281</v>
       </c>
       <c r="F249" t="n">
-        <v>10483700</v>
+        <v>7254900</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>337</v>
+        <v>334.8900146484375</v>
       </c>
       <c r="C250" t="n">
-        <v>338.75</v>
+        <v>336.3399963378906</v>
       </c>
       <c r="D250" t="n">
-        <v>333.3299865722656</v>
+        <v>330.8299865722656</v>
       </c>
       <c r="E250" t="n">
-        <v>334.9800109863281</v>
+        <v>330.8299865722656</v>
       </c>
       <c r="F250" t="n">
-        <v>7254900</v>
+        <v>9113300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B251" t="n">
-        <v>334.8900146484375</v>
+        <v>328.75</v>
       </c>
       <c r="C251" t="n">
-        <v>336.3399963378906</v>
+        <v>333.5799865722656</v>
       </c>
       <c r="D251" t="n">
-        <v>330.8299865722656</v>
+        <v>325.8699951171875</v>
       </c>
       <c r="E251" t="n">
-        <v>330.8299865722656</v>
+        <v>333.1799926757812</v>
       </c>
       <c r="F251" t="n">
-        <v>9113300</v>
+        <v>8160000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B252" t="n">
-        <v>328.75</v>
+        <v>334</v>
       </c>
       <c r="C252" t="n">
-        <v>333.5799865722656</v>
+        <v>334.8450012207031</v>
       </c>
       <c r="D252" t="n">
-        <v>325.8699951171875</v>
+        <v>330</v>
       </c>
       <c r="E252" t="n">
-        <v>333.1799926757812</v>
+        <v>332.3800048828125</v>
       </c>
       <c r="F252" t="n">
-        <v>8160000</v>
+        <v>6539384</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10017,34 +10017,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>332.38</v>
+      </c>
+      <c r="D2" t="n">
         <v>333.18</v>
       </c>
-      <c r="D2" t="n">
-        <v>330.83</v>
-      </c>
       <c r="E2" t="n">
-        <v>328.75</v>
+        <v>334</v>
       </c>
       <c r="F2" t="n">
-        <v>333.58</v>
+        <v>334.845</v>
       </c>
       <c r="G2" t="n">
-        <v>325.87</v>
+        <v>330</v>
       </c>
       <c r="H2" t="n">
-        <v>8061036</v>
+        <v>6539384</v>
       </c>
       <c r="I2" t="n">
         <v>7677139</v>
       </c>
       <c r="J2" t="n">
-        <v>885654487040</v>
+        <v>883527974912</v>
       </c>
       <c r="K2" t="n">
-        <v>14.262842</v>
+        <v>14.228596</v>
       </c>
       <c r="L2" t="n">
-        <v>13.318027</v>
+        <v>13.286049</v>
       </c>
       <c r="M2" t="n">
         <v>23.36</v>
@@ -10087,7 +10087,7 @@
         <v>133.007</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.5049808</v>
+        <v>2.4989662</v>
       </c>
       <c r="Z2" t="n">
         <v>0.469</v>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:38:27</t>
+          <t>2026-10-03 05:34:30</t>
         </is>
       </c>
     </row>

--- a/data/JPM_data.xlsx
+++ b/data/JPM_data.xlsx
@@ -469,25 +469,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B2" t="n">
-        <v>302.7188095956571</v>
+        <v>305.8371035459471</v>
       </c>
       <c r="C2" t="n">
-        <v>305.809673335546</v>
+        <v>307.3851288987199</v>
       </c>
       <c r="D2" t="n">
-        <v>302.4244230832239</v>
+        <v>300.8578215934895</v>
       </c>
       <c r="E2" t="n">
-        <v>304.2102661132812</v>
+        <v>304.8511047363281</v>
       </c>
       <c r="F2" t="n">
-        <v>6029900</v>
+        <v>7214500</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -495,25 +495,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B3" t="n">
-        <v>305.8371035459471</v>
+        <v>305.0187809092415</v>
       </c>
       <c r="C3" t="n">
-        <v>307.3851288987199</v>
+        <v>305.6695438264559</v>
       </c>
       <c r="D3" t="n">
-        <v>300.8578215934895</v>
+        <v>300.4338918141804</v>
       </c>
       <c r="E3" t="n">
-        <v>304.8511047363281</v>
+        <v>303.3820190429688</v>
       </c>
       <c r="F3" t="n">
-        <v>7214500</v>
+        <v>8454200</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B4" t="n">
-        <v>305.0187502270194</v>
+        <v>303.8946917756213</v>
       </c>
       <c r="C4" t="n">
-        <v>305.6695130787729</v>
+        <v>304.4567183318842</v>
       </c>
       <c r="D4" t="n">
-        <v>300.4338615931582</v>
+        <v>299.2999336047902</v>
       </c>
       <c r="E4" t="n">
-        <v>303.3819885253906</v>
+        <v>299.7732238769531</v>
       </c>
       <c r="F4" t="n">
-        <v>8454200</v>
+        <v>6489900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B5" t="n">
-        <v>303.894722712774</v>
+        <v>300.7789070325195</v>
       </c>
       <c r="C5" t="n">
-        <v>304.4567493262524</v>
+        <v>303.7270637601551</v>
       </c>
       <c r="D5" t="n">
-        <v>299.2999640741864</v>
+        <v>299.1421755849041</v>
       </c>
       <c r="E5" t="n">
-        <v>299.7732543945312</v>
+        <v>301.252197265625</v>
       </c>
       <c r="F5" t="n">
-        <v>6489900</v>
+        <v>7060300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B6" t="n">
-        <v>300.7789375021521</v>
+        <v>301.3804193716138</v>
       </c>
       <c r="C6" t="n">
-        <v>303.7270945284432</v>
+        <v>306.1230715472904</v>
       </c>
       <c r="D6" t="n">
-        <v>299.1422058887319</v>
+        <v>296.5983188157025</v>
       </c>
       <c r="E6" t="n">
-        <v>301.2522277832031</v>
+        <v>296.6772155761719</v>
       </c>
       <c r="F6" t="n">
-        <v>7060300</v>
+        <v>8597400</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B7" t="n">
-        <v>301.3804193716138</v>
+        <v>301.3212684867699</v>
       </c>
       <c r="C7" t="n">
-        <v>306.1230715472904</v>
+        <v>305.1272097801061</v>
       </c>
       <c r="D7" t="n">
-        <v>296.5983188157025</v>
+        <v>301.1733746705027</v>
       </c>
       <c r="E7" t="n">
-        <v>296.6772155761719</v>
+        <v>303.6580810546875</v>
       </c>
       <c r="F7" t="n">
-        <v>8597400</v>
+        <v>10788700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B8" t="n">
-        <v>301.321238204041</v>
+        <v>301.5578902761218</v>
       </c>
       <c r="C8" t="n">
-        <v>305.1271791148808</v>
+        <v>302.7016525742085</v>
       </c>
       <c r="D8" t="n">
-        <v>301.173344402637</v>
+        <v>290.0907186231138</v>
       </c>
       <c r="E8" t="n">
-        <v>303.6580505371094</v>
+        <v>297.8505249023438</v>
       </c>
       <c r="F8" t="n">
-        <v>10788700</v>
+        <v>16178800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B9" t="n">
-        <v>301.5578902761218</v>
+        <v>302.1002149225357</v>
       </c>
       <c r="C9" t="n">
-        <v>302.7016525742085</v>
+        <v>307.7499693151439</v>
       </c>
       <c r="D9" t="n">
-        <v>290.0907186231138</v>
+        <v>301.1635039391426</v>
       </c>
       <c r="E9" t="n">
-        <v>297.8505249023438</v>
+        <v>301.4100036621094</v>
       </c>
       <c r="F9" t="n">
-        <v>16178800</v>
+        <v>11354800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B10" t="n">
-        <v>302.1001843350741</v>
+        <v>301.0747260223031</v>
       </c>
       <c r="C10" t="n">
-        <v>307.7499381556482</v>
+        <v>304.358088638523</v>
       </c>
       <c r="D10" t="n">
-        <v>301.1634734465224</v>
+        <v>292.9106575300408</v>
       </c>
       <c r="E10" t="n">
-        <v>301.4099731445312</v>
+        <v>294.3600769042969</v>
       </c>
       <c r="F10" t="n">
-        <v>11354800</v>
+        <v>10549400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B11" t="n">
-        <v>301.0747572360179</v>
+        <v>294.9714335987563</v>
       </c>
       <c r="C11" t="n">
-        <v>304.3581201926382</v>
+        <v>295.3559575215809</v>
       </c>
       <c r="D11" t="n">
-        <v>292.9106878973514</v>
+        <v>290.0808874955599</v>
       </c>
       <c r="E11" t="n">
-        <v>294.360107421875</v>
+        <v>293.3938293457031</v>
       </c>
       <c r="F11" t="n">
-        <v>10549400</v>
+        <v>10153500</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B12" t="n">
-        <v>294.9714335987563</v>
+        <v>294.3206459359216</v>
       </c>
       <c r="C12" t="n">
-        <v>295.3559575215809</v>
+        <v>299.4379821870563</v>
       </c>
       <c r="D12" t="n">
-        <v>290.0808874955599</v>
+        <v>293.9854099500461</v>
       </c>
       <c r="E12" t="n">
-        <v>293.3938293457031</v>
+        <v>298.1265869140625</v>
       </c>
       <c r="F12" t="n">
-        <v>10153500</v>
+        <v>6894900</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B13" t="n">
-        <v>294.3206459359216</v>
+        <v>297.4363803014411</v>
       </c>
       <c r="C13" t="n">
-        <v>299.4379821870563</v>
+        <v>299.7929016175946</v>
       </c>
       <c r="D13" t="n">
-        <v>293.9854099500461</v>
+        <v>292.841622611914</v>
       </c>
       <c r="E13" t="n">
-        <v>298.1265869140625</v>
+        <v>292.9303588867188</v>
       </c>
       <c r="F13" t="n">
-        <v>6894900</v>
+        <v>7372700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B14" t="n">
-        <v>297.436411288458</v>
+        <v>293.6008861047978</v>
       </c>
       <c r="C14" t="n">
-        <v>299.7929328501146</v>
+        <v>293.8868342154489</v>
       </c>
       <c r="D14" t="n">
-        <v>292.8416531202475</v>
+        <v>286.4721332067081</v>
       </c>
       <c r="E14" t="n">
-        <v>292.9303894042969</v>
+        <v>289.9921264648438</v>
       </c>
       <c r="F14" t="n">
-        <v>7372700</v>
+        <v>8054100</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B15" t="n">
-        <v>293.6008552074487</v>
+        <v>290.2583437522712</v>
       </c>
       <c r="C15" t="n">
-        <v>293.8868032880077</v>
+        <v>292.2204718178062</v>
       </c>
       <c r="D15" t="n">
-        <v>286.4721030595595</v>
+        <v>288.4145307332595</v>
       </c>
       <c r="E15" t="n">
-        <v>289.9920959472656</v>
+        <v>290.4161071777344</v>
       </c>
       <c r="F15" t="n">
-        <v>8054100</v>
+        <v>5438800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B16" t="n">
-        <v>290.2583437522712</v>
+        <v>291.9345194575729</v>
       </c>
       <c r="C16" t="n">
-        <v>292.2204718178062</v>
+        <v>298.3632510673837</v>
       </c>
       <c r="D16" t="n">
-        <v>288.4145307332595</v>
+        <v>291.3133654724136</v>
       </c>
       <c r="E16" t="n">
-        <v>290.4161071777344</v>
+        <v>296.2334899902344</v>
       </c>
       <c r="F16" t="n">
-        <v>5438800</v>
+        <v>7228300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B17" t="n">
-        <v>291.9345194575729</v>
+        <v>297.92941246883</v>
       </c>
       <c r="C17" t="n">
-        <v>298.3632510673837</v>
+        <v>300.2662249001909</v>
       </c>
       <c r="D17" t="n">
-        <v>291.3133654724136</v>
+        <v>296.7955198233114</v>
       </c>
       <c r="E17" t="n">
-        <v>296.2334899902344</v>
+        <v>299.8915405273438</v>
       </c>
       <c r="F17" t="n">
-        <v>7228300</v>
+        <v>5642200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B18" t="n">
-        <v>297.92941246883</v>
+        <v>300.5915953010157</v>
       </c>
       <c r="C18" t="n">
-        <v>300.2662249001909</v>
+        <v>303.6580673748709</v>
       </c>
       <c r="D18" t="n">
-        <v>296.7955198233114</v>
+        <v>298.915415308335</v>
       </c>
       <c r="E18" t="n">
-        <v>299.8915405273438</v>
+        <v>301.0845947265625</v>
       </c>
       <c r="F18" t="n">
-        <v>5642200</v>
+        <v>6336000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B19" t="n">
-        <v>300.5915953010157</v>
+        <v>299.2605157595805</v>
       </c>
       <c r="C19" t="n">
-        <v>303.6580673748709</v>
+        <v>303.9341406042103</v>
       </c>
       <c r="D19" t="n">
-        <v>298.915415308335</v>
+        <v>298.7675163425421</v>
       </c>
       <c r="E19" t="n">
-        <v>301.0845947265625</v>
+        <v>301.2325134277344</v>
       </c>
       <c r="F19" t="n">
-        <v>6336000</v>
+        <v>7520300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B20" t="n">
-        <v>299.2605157595805</v>
+        <v>301.5086233262724</v>
       </c>
       <c r="C20" t="n">
-        <v>303.9341406042103</v>
+        <v>308.233113206998</v>
       </c>
       <c r="D20" t="n">
-        <v>298.7675163425421</v>
+        <v>300.8282816526182</v>
       </c>
       <c r="E20" t="n">
-        <v>301.2325134277344</v>
+        <v>305.1075134277344</v>
       </c>
       <c r="F20" t="n">
-        <v>7520300</v>
+        <v>7514600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B21" t="n">
-        <v>301.5085931686638</v>
+        <v>304.220113094536</v>
       </c>
       <c r="C21" t="n">
-        <v>308.2330823767899</v>
+        <v>308.4894751488275</v>
       </c>
       <c r="D21" t="n">
-        <v>300.828251563059</v>
+        <v>302.9481660712639</v>
       </c>
       <c r="E21" t="n">
-        <v>305.1074829101562</v>
+        <v>306.7639770507812</v>
       </c>
       <c r="F21" t="n">
-        <v>7514600</v>
+        <v>7721300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B22" t="n">
-        <v>304.2200828300273</v>
+        <v>306.6456604912348</v>
       </c>
       <c r="C22" t="n">
-        <v>308.4894444595929</v>
+        <v>307.9471862719047</v>
       </c>
       <c r="D22" t="n">
-        <v>302.9481359332913</v>
+        <v>301.9227172950412</v>
       </c>
       <c r="E22" t="n">
-        <v>306.7639465332031</v>
+        <v>305.0187683105469</v>
       </c>
       <c r="F22" t="n">
-        <v>7721300</v>
+        <v>7770000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B23" t="n">
-        <v>306.6456604912348</v>
+        <v>302.415720333495</v>
       </c>
       <c r="C23" t="n">
-        <v>307.9471862719047</v>
+        <v>307.8485840116909</v>
       </c>
       <c r="D23" t="n">
-        <v>301.9227172950412</v>
+        <v>300.8282765156093</v>
       </c>
       <c r="E23" t="n">
-        <v>305.0187683105469</v>
+        <v>304.920166015625</v>
       </c>
       <c r="F23" t="n">
-        <v>7770000</v>
+        <v>7085200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B24" t="n">
-        <v>302.415720333495</v>
+        <v>305.2750763211935</v>
       </c>
       <c r="C24" t="n">
-        <v>307.8485840116909</v>
+        <v>308.7162326204817</v>
       </c>
       <c r="D24" t="n">
-        <v>300.8282765156093</v>
+        <v>301.350820325461</v>
       </c>
       <c r="E24" t="n">
-        <v>304.920166015625</v>
+        <v>307.3161010742188</v>
       </c>
       <c r="F24" t="n">
-        <v>7085200</v>
+        <v>6865200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B25" t="n">
-        <v>305.2751066360906</v>
+        <v>306.6357990367445</v>
       </c>
       <c r="C25" t="n">
-        <v>308.7162632770978</v>
+        <v>310.4319009529449</v>
       </c>
       <c r="D25" t="n">
-        <v>301.3508502506656</v>
+        <v>305.9160390722913</v>
       </c>
       <c r="E25" t="n">
-        <v>307.3161315917969</v>
+        <v>309.0317993164062</v>
       </c>
       <c r="F25" t="n">
-        <v>6865200</v>
+        <v>7206100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B26" t="n">
-        <v>306.6357687557767</v>
+        <v>307.5231746391179</v>
       </c>
       <c r="C26" t="n">
-        <v>310.4318702971036</v>
+        <v>310.0275898810191</v>
       </c>
       <c r="D26" t="n">
-        <v>305.9160088624015</v>
+        <v>303.3326798145578</v>
       </c>
       <c r="E26" t="n">
-        <v>309.0317687988281</v>
+        <v>309.8106689453125</v>
       </c>
       <c r="F26" t="n">
-        <v>7206100</v>
+        <v>7302300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B27" t="n">
-        <v>307.5232049313688</v>
+        <v>310.5896641246428</v>
       </c>
       <c r="C27" t="n">
-        <v>310.0276204199649</v>
+        <v>315.0858168552232</v>
       </c>
       <c r="D27" t="n">
-        <v>303.3327096940284</v>
+        <v>309.810716541713</v>
       </c>
       <c r="E27" t="n">
-        <v>309.8106994628906</v>
+        <v>312.4532165527344</v>
       </c>
       <c r="F27" t="n">
-        <v>7302300</v>
+        <v>5794100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B28" t="n">
-        <v>310.5896337890794</v>
+        <v>313.054640940315</v>
       </c>
       <c r="C28" t="n">
-        <v>315.0857860805166</v>
+        <v>314.5829271513063</v>
       </c>
       <c r="D28" t="n">
-        <v>309.8106862822301</v>
+        <v>310.8657222472937</v>
       </c>
       <c r="E28" t="n">
-        <v>312.4531860351562</v>
+        <v>311.2009582519531</v>
       </c>
       <c r="F28" t="n">
-        <v>5794100</v>
+        <v>5030200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B29" t="n">
-        <v>313.0546102409576</v>
+        <v>311.8320301504691</v>
       </c>
       <c r="C29" t="n">
-        <v>314.5828963020791</v>
+        <v>317.7381540918137</v>
       </c>
       <c r="D29" t="n">
-        <v>310.8656917625901</v>
+        <v>311.7827121499603</v>
       </c>
       <c r="E29" t="n">
-        <v>311.200927734375</v>
+        <v>315.9239196777344</v>
       </c>
       <c r="F29" t="n">
-        <v>5030200</v>
+        <v>10578300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B30" t="n">
-        <v>311.8320000281587</v>
+        <v>314.7604311532612</v>
       </c>
       <c r="C30" t="n">
-        <v>317.7381233989844</v>
+        <v>316.1408235578094</v>
       </c>
       <c r="D30" t="n">
-        <v>311.782682032414</v>
+        <v>304.7722577523736</v>
       </c>
       <c r="E30" t="n">
-        <v>315.9238891601562</v>
+        <v>305.1469421386719</v>
       </c>
       <c r="F30" t="n">
-        <v>10578300</v>
+        <v>8973300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B31" t="n">
-        <v>314.7604626322791</v>
+        <v>303.2045199796025</v>
       </c>
       <c r="C31" t="n">
-        <v>316.1408551748796</v>
+        <v>303.3327046462357</v>
       </c>
       <c r="D31" t="n">
-        <v>304.7722882324798</v>
+        <v>297.0124483237873</v>
       </c>
       <c r="E31" t="n">
-        <v>305.14697265625</v>
+        <v>299.3591003417969</v>
       </c>
       <c r="F31" t="n">
-        <v>8973300</v>
+        <v>10327000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B32" t="n">
-        <v>303.2044890700107</v>
+        <v>299.7436397411884</v>
       </c>
       <c r="C32" t="n">
-        <v>303.3326737235763</v>
+        <v>301.3113742461044</v>
       </c>
       <c r="D32" t="n">
-        <v>297.012418045434</v>
+        <v>293.5022804823602</v>
       </c>
       <c r="E32" t="n">
-        <v>299.3590698242188</v>
+        <v>296.1644592285156</v>
       </c>
       <c r="F32" t="n">
-        <v>10327000</v>
+        <v>8344000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B33" t="n">
-        <v>299.7436397411884</v>
+        <v>295.3066317863286</v>
       </c>
       <c r="C33" t="n">
-        <v>301.3113742461044</v>
+        <v>298.70833958092</v>
       </c>
       <c r="D33" t="n">
-        <v>293.5022804823602</v>
+        <v>292.8613440028039</v>
       </c>
       <c r="E33" t="n">
-        <v>296.1644592285156</v>
+        <v>295.2178955078125</v>
       </c>
       <c r="F33" t="n">
-        <v>8344000</v>
+        <v>8077300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B34" t="n">
-        <v>295.3066623130797</v>
+        <v>295.5432899586994</v>
       </c>
       <c r="C34" t="n">
-        <v>298.708370459316</v>
+        <v>300.1873662746028</v>
       </c>
       <c r="D34" t="n">
-        <v>292.8613742767781</v>
+        <v>295.0798692888629</v>
       </c>
       <c r="E34" t="n">
-        <v>295.2179260253906</v>
+        <v>299.0238647460938</v>
       </c>
       <c r="F34" t="n">
-        <v>8077300</v>
+        <v>5546600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B35" t="n">
-        <v>295.5432597963394</v>
+        <v>302.0508736933244</v>
       </c>
       <c r="C35" t="n">
-        <v>300.1873356382808</v>
+        <v>305.5807663052954</v>
       </c>
       <c r="D35" t="n">
-        <v>295.0798391737984</v>
+        <v>293.9854105998292</v>
       </c>
       <c r="E35" t="n">
-        <v>299.0238342285156</v>
+        <v>294.2023315429688</v>
       </c>
       <c r="F35" t="n">
-        <v>5546600</v>
+        <v>7501600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B36" t="n">
-        <v>302.0508736933244</v>
+        <v>297.0715864028587</v>
       </c>
       <c r="C36" t="n">
-        <v>305.5807663052954</v>
+        <v>297.456110287291</v>
       </c>
       <c r="D36" t="n">
-        <v>293.9854105998292</v>
+        <v>288.7103057597054</v>
       </c>
       <c r="E36" t="n">
-        <v>294.2023315429688</v>
+        <v>293.8473510742188</v>
       </c>
       <c r="F36" t="n">
-        <v>7501600</v>
+        <v>11766800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B37" t="n">
-        <v>297.0715864028587</v>
+        <v>294.0642973394352</v>
       </c>
       <c r="C37" t="n">
-        <v>297.456110287291</v>
+        <v>295.6221924256846</v>
       </c>
       <c r="D37" t="n">
-        <v>288.7103057597054</v>
+        <v>290.386540762355</v>
       </c>
       <c r="E37" t="n">
-        <v>293.8473510742188</v>
+        <v>293.8276672363281</v>
       </c>
       <c r="F37" t="n">
-        <v>11766800</v>
+        <v>10940200</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B38" t="n">
-        <v>294.0642973394352</v>
+        <v>295.8489209666184</v>
       </c>
       <c r="C38" t="n">
-        <v>295.6221924256846</v>
+        <v>300.2366275598507</v>
       </c>
       <c r="D38" t="n">
-        <v>290.386540762355</v>
+        <v>291.4217960873232</v>
       </c>
       <c r="E38" t="n">
-        <v>293.8276672363281</v>
+        <v>298.7576293945312</v>
       </c>
       <c r="F38" t="n">
-        <v>10940200</v>
+        <v>8877200</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B39" t="n">
-        <v>295.848951187077</v>
+        <v>300.7296512123902</v>
       </c>
       <c r="C39" t="n">
-        <v>300.236658228506</v>
+        <v>304.2102259719906</v>
       </c>
       <c r="D39" t="n">
-        <v>291.4218258555586</v>
+        <v>298.9548653069277</v>
       </c>
       <c r="E39" t="n">
-        <v>298.7576599121094</v>
+        <v>303.3327026367188</v>
       </c>
       <c r="F39" t="n">
-        <v>8877200</v>
+        <v>7910900</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B40" t="n">
-        <v>300.7296512123902</v>
+        <v>304.7722767012305</v>
       </c>
       <c r="C40" t="n">
-        <v>304.2102259719906</v>
+        <v>309.3275869646093</v>
       </c>
       <c r="D40" t="n">
-        <v>298.9548653069277</v>
+        <v>303.9243019705234</v>
       </c>
       <c r="E40" t="n">
-        <v>303.3327026367188</v>
+        <v>308.696533203125</v>
       </c>
       <c r="F40" t="n">
-        <v>7910900</v>
+        <v>4322400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B41" t="n">
-        <v>304.7722465716023</v>
+        <v>308.5683618849884</v>
       </c>
       <c r="C41" t="n">
-        <v>309.3275563846455</v>
+        <v>309.6430970545817</v>
       </c>
       <c r="D41" t="n">
-        <v>303.9242719247256</v>
+        <v>304.2201032083801</v>
       </c>
       <c r="E41" t="n">
-        <v>308.6965026855469</v>
+        <v>304.5947875976562</v>
       </c>
       <c r="F41" t="n">
-        <v>4322400</v>
+        <v>7727300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B42" t="n">
-        <v>308.5683309692949</v>
+        <v>304.4172805196406</v>
       </c>
       <c r="C42" t="n">
-        <v>309.6430660312097</v>
+        <v>306.1329390093465</v>
       </c>
       <c r="D42" t="n">
-        <v>304.2200727283419</v>
+        <v>302.7903884074122</v>
       </c>
       <c r="E42" t="n">
-        <v>304.5947570800781</v>
+        <v>303.5693359375</v>
       </c>
       <c r="F42" t="n">
-        <v>7727300</v>
+        <v>7249000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B43" t="n">
-        <v>304.4172805196406</v>
+        <v>302.8988595387675</v>
       </c>
       <c r="C43" t="n">
-        <v>306.1329390093465</v>
+        <v>307.9865871384521</v>
       </c>
       <c r="D43" t="n">
-        <v>302.7903884074122</v>
+        <v>302.5044359255107</v>
       </c>
       <c r="E43" t="n">
-        <v>303.5693359375</v>
+        <v>307.7598266601562</v>
       </c>
       <c r="F43" t="n">
-        <v>7249000</v>
+        <v>8535300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B44" t="n">
-        <v>302.8988595387675</v>
+        <v>308.8740221323167</v>
       </c>
       <c r="C44" t="n">
-        <v>307.9865871384521</v>
+        <v>314.0307770729326</v>
       </c>
       <c r="D44" t="n">
-        <v>302.5044359255107</v>
+        <v>308.617652791837</v>
       </c>
       <c r="E44" t="n">
-        <v>307.7598266601562</v>
+        <v>311.6742553710938</v>
       </c>
       <c r="F44" t="n">
-        <v>8535300</v>
+        <v>9627800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B45" t="n">
-        <v>308.8740221323167</v>
+        <v>311.2206946896725</v>
       </c>
       <c r="C45" t="n">
-        <v>314.0307770729326</v>
+        <v>314.0209278419201</v>
       </c>
       <c r="D45" t="n">
-        <v>308.617652791837</v>
+        <v>310.2741141188276</v>
       </c>
       <c r="E45" t="n">
-        <v>311.6742553710938</v>
+        <v>310.6290893554688</v>
       </c>
       <c r="F45" t="n">
-        <v>9627800</v>
+        <v>6518900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B46" t="n">
-        <v>311.2206946896725</v>
+        <v>310.6487980837529</v>
       </c>
       <c r="C46" t="n">
-        <v>314.0209278419201</v>
+        <v>312.0390600856641</v>
       </c>
       <c r="D46" t="n">
-        <v>310.2741141188276</v>
+        <v>308.9627484602848</v>
       </c>
       <c r="E46" t="n">
-        <v>310.6290893554688</v>
+        <v>310.7966918945312</v>
       </c>
       <c r="F46" t="n">
-        <v>6518900</v>
+        <v>7417200</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B47" t="n">
-        <v>310.6487980837529</v>
+        <v>310.5403463950657</v>
       </c>
       <c r="C47" t="n">
-        <v>312.0390600856641</v>
+        <v>314.3364178531727</v>
       </c>
       <c r="D47" t="n">
-        <v>308.9627484602848</v>
+        <v>295.8193608594167</v>
       </c>
       <c r="E47" t="n">
-        <v>310.7966918945312</v>
+        <v>296.3025207519531</v>
       </c>
       <c r="F47" t="n">
-        <v>7417200</v>
+        <v>18049200</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B48" t="n">
-        <v>310.5403783790639</v>
+        <v>296.2926621709551</v>
       </c>
       <c r="C48" t="n">
-        <v>314.336450228146</v>
+        <v>306.8329925602339</v>
       </c>
       <c r="D48" t="n">
-        <v>295.8193913272319</v>
+        <v>294.2812160390869</v>
       </c>
       <c r="E48" t="n">
-        <v>296.3025512695312</v>
+        <v>305.7680969238281</v>
       </c>
       <c r="F48" t="n">
-        <v>18049200</v>
+        <v>18874100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B49" t="n">
-        <v>296.292632599085</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="C49" t="n">
-        <v>306.8329619363725</v>
+        <v>313.5476242674454</v>
       </c>
       <c r="D49" t="n">
-        <v>294.2811866679717</v>
+        <v>304.9102649889192</v>
       </c>
       <c r="E49" t="n">
-        <v>305.76806640625</v>
+        <v>312.9363098144531</v>
       </c>
       <c r="F49" t="n">
-        <v>18874100</v>
+        <v>9721900</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B50" t="n">
-        <v>304.9102649889192</v>
+        <v>315.2040954937631</v>
       </c>
       <c r="C50" t="n">
-        <v>313.5476242674454</v>
+        <v>315.7858311866128</v>
       </c>
       <c r="D50" t="n">
-        <v>304.9102649889192</v>
+        <v>312.1672323684923</v>
       </c>
       <c r="E50" t="n">
-        <v>312.9363098144531</v>
+        <v>314.0603332519531</v>
       </c>
       <c r="F50" t="n">
-        <v>9721900</v>
+        <v>8982900</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B51" t="n">
-        <v>315.2041261224818</v>
+        <v>315.115395356304</v>
       </c>
       <c r="C51" t="n">
-        <v>315.7858618718594</v>
+        <v>318.3593402708456</v>
       </c>
       <c r="D51" t="n">
-        <v>312.1672627021157</v>
+        <v>313.9322146909975</v>
       </c>
       <c r="E51" t="n">
-        <v>314.0603637695312</v>
+        <v>315.5393676757812</v>
       </c>
       <c r="F51" t="n">
-        <v>8982900</v>
+        <v>10864100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B52" t="n">
-        <v>315.115395356304</v>
+        <v>314.6223410116007</v>
       </c>
       <c r="C52" t="n">
-        <v>318.3593402708456</v>
+        <v>315.0463132571263</v>
       </c>
       <c r="D52" t="n">
-        <v>313.9322146909975</v>
+        <v>309.9980044156554</v>
       </c>
       <c r="E52" t="n">
-        <v>315.5393676757812</v>
+        <v>311.1318969726562</v>
       </c>
       <c r="F52" t="n">
-        <v>10864100</v>
+        <v>8331300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B53" t="n">
-        <v>314.6224027314819</v>
+        <v>313.9716244610726</v>
       </c>
       <c r="C53" t="n">
-        <v>315.0463750601788</v>
+        <v>314.8984658400699</v>
       </c>
       <c r="D53" t="n">
-        <v>309.9980652283745</v>
+        <v>310.2544194174254</v>
       </c>
       <c r="E53" t="n">
-        <v>311.1319580078125</v>
+        <v>310.5699462890625</v>
       </c>
       <c r="F53" t="n">
-        <v>8331300</v>
+        <v>8718700</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B54" t="n">
-        <v>313.971593609235</v>
+        <v>311.5756418636432</v>
       </c>
       <c r="C54" t="n">
-        <v>314.8984348971578</v>
+        <v>313.2518519730792</v>
       </c>
       <c r="D54" t="n">
-        <v>310.254388930852</v>
+        <v>307.8485673512913</v>
       </c>
       <c r="E54" t="n">
-        <v>310.5699157714844</v>
+        <v>308.6176452636719</v>
       </c>
       <c r="F54" t="n">
-        <v>8718700</v>
+        <v>11444900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B55" t="n">
-        <v>311.575672673722</v>
+        <v>309.3965776494671</v>
       </c>
       <c r="C55" t="n">
-        <v>313.2518829489097</v>
+        <v>314.099781180705</v>
       </c>
       <c r="D55" t="n">
-        <v>307.8485977928193</v>
+        <v>308.8049723403709</v>
       </c>
       <c r="E55" t="n">
-        <v>308.61767578125</v>
+        <v>312.7686767578125</v>
       </c>
       <c r="F55" t="n">
-        <v>11444900</v>
+        <v>24494400</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B56" t="n">
-        <v>309.3965776494671</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="C56" t="n">
-        <v>314.099781180705</v>
+        <v>318.7043994886834</v>
       </c>
       <c r="D56" t="n">
-        <v>308.8049723403709</v>
+        <v>313.0644852104395</v>
       </c>
       <c r="E56" t="n">
-        <v>312.7686767578125</v>
+        <v>318.5663452148438</v>
       </c>
       <c r="F56" t="n">
-        <v>24494400</v>
+        <v>8354600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B57" t="n">
-        <v>313.0644852104395</v>
+        <v>319.0790830432475</v>
       </c>
       <c r="C57" t="n">
-        <v>318.7043994886834</v>
+        <v>323.1907116116738</v>
       </c>
       <c r="D57" t="n">
-        <v>313.0644852104395</v>
+        <v>318.5663744582675</v>
       </c>
       <c r="E57" t="n">
-        <v>318.5663452148438</v>
+        <v>321.3666076660156</v>
       </c>
       <c r="F57" t="n">
-        <v>8354600</v>
+        <v>6668300</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B58" t="n">
-        <v>319.0790830432475</v>
+        <v>321.6722493328215</v>
       </c>
       <c r="C58" t="n">
-        <v>323.1907116116738</v>
+        <v>325.3697449529369</v>
       </c>
       <c r="D58" t="n">
-        <v>318.5663744582675</v>
+        <v>320.9426198260136</v>
       </c>
       <c r="E58" t="n">
-        <v>321.3666076660156</v>
+        <v>324.5612487792969</v>
       </c>
       <c r="F58" t="n">
-        <v>6668300</v>
+        <v>4289300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B59" t="n">
-        <v>321.6722493328215</v>
+        <v>324.502058709128</v>
       </c>
       <c r="C59" t="n">
-        <v>325.3697449529369</v>
+        <v>326.2275566521161</v>
       </c>
       <c r="D59" t="n">
-        <v>320.9426198260136</v>
+        <v>321.9680645986219</v>
       </c>
       <c r="E59" t="n">
-        <v>324.5612487792969</v>
+        <v>323.3188781738281</v>
       </c>
       <c r="F59" t="n">
-        <v>4289300</v>
+        <v>4158300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B60" t="n">
-        <v>324.502058709128</v>
+        <v>322.4216288798564</v>
       </c>
       <c r="C60" t="n">
-        <v>326.2275566521161</v>
+        <v>323.1808371734579</v>
       </c>
       <c r="D60" t="n">
-        <v>321.9680645986219</v>
+        <v>319.0002116144308</v>
       </c>
       <c r="E60" t="n">
-        <v>323.3188781738281</v>
+        <v>319.2171325683594</v>
       </c>
       <c r="F60" t="n">
-        <v>4158300</v>
+        <v>8635300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B61" t="n">
-        <v>322.4216288798564</v>
+        <v>320.2622768741799</v>
       </c>
       <c r="C61" t="n">
-        <v>323.1808371734579</v>
+        <v>320.3904615362508</v>
       </c>
       <c r="D61" t="n">
-        <v>319.0002116144308</v>
+        <v>317.9747523718436</v>
       </c>
       <c r="E61" t="n">
-        <v>319.2171325683594</v>
+        <v>318.8917541503906</v>
       </c>
       <c r="F61" t="n">
-        <v>8635300</v>
+        <v>7904300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B62" t="n">
-        <v>320.2623075229155</v>
+        <v>319.7988699190817</v>
       </c>
       <c r="C62" t="n">
-        <v>320.3904921972535</v>
+        <v>320.3313177342217</v>
       </c>
       <c r="D62" t="n">
-        <v>317.9747828016658</v>
+        <v>317.5310845539587</v>
       </c>
       <c r="E62" t="n">
-        <v>318.8917846679688</v>
+        <v>317.7085571289062</v>
       </c>
       <c r="F62" t="n">
-        <v>7904300</v>
+        <v>5048500</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B63" t="n">
-        <v>319.7988699190817</v>
+        <v>317.9846554663246</v>
       </c>
       <c r="C63" t="n">
-        <v>320.3313177342217</v>
+        <v>321.169442848154</v>
       </c>
       <c r="D63" t="n">
-        <v>317.5310845539587</v>
+        <v>316.2492877176746</v>
       </c>
       <c r="E63" t="n">
-        <v>317.7085571289062</v>
+        <v>320.9229431152344</v>
       </c>
       <c r="F63" t="n">
-        <v>5048500</v>
+        <v>8054000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B64" t="n">
-        <v>317.9846252281575</v>
+        <v>320.942628937084</v>
       </c>
       <c r="C64" t="n">
-        <v>321.1694123071354</v>
+        <v>332.5281155423397</v>
       </c>
       <c r="D64" t="n">
-        <v>316.2492576445291</v>
+        <v>320.636971697701</v>
       </c>
       <c r="E64" t="n">
-        <v>320.9229125976562</v>
+        <v>329.3630676269531</v>
       </c>
       <c r="F64" t="n">
-        <v>8054000</v>
+        <v>10752600</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,25 +2107,25 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B65" t="n">
-        <v>320.9426586744551</v>
+        <v>329.4422902981328</v>
       </c>
       <c r="C65" t="n">
-        <v>332.5281463531796</v>
+        <v>332.6612412306879</v>
       </c>
       <c r="D65" t="n">
-        <v>320.637001406751</v>
+        <v>327.491109600743</v>
       </c>
       <c r="E65" t="n">
-        <v>329.3630981445312</v>
+        <v>331.4132690429688</v>
       </c>
       <c r="F65" t="n">
-        <v>10752600</v>
+        <v>7660800</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2133,25 +2133,25 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B66" t="n">
-        <v>329.4422902981328</v>
+        <v>327.9764659913386</v>
       </c>
       <c r="C66" t="n">
-        <v>332.6612412306879</v>
+        <v>328.9767963949314</v>
       </c>
       <c r="D66" t="n">
-        <v>327.491109600743</v>
+        <v>321.4989374679619</v>
       </c>
       <c r="E66" t="n">
-        <v>331.4132690429688</v>
+        <v>323.8660888671875</v>
       </c>
       <c r="F66" t="n">
-        <v>7660800</v>
+        <v>9815200</v>
       </c>
       <c r="G66" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B67" t="n">
-        <v>327.9764350864437</v>
+        <v>323.2718313763784</v>
       </c>
       <c r="C67" t="n">
-        <v>328.9767653957764</v>
+        <v>328.2339475379842</v>
       </c>
       <c r="D67" t="n">
-        <v>321.4989071734381</v>
+        <v>322.5388804495614</v>
       </c>
       <c r="E67" t="n">
-        <v>323.8660583496094</v>
+        <v>326.6393432617188</v>
       </c>
       <c r="F67" t="n">
-        <v>9815200</v>
+        <v>11737100</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B68" t="n">
-        <v>323.2718313763784</v>
+        <v>326.1936353875406</v>
       </c>
       <c r="C68" t="n">
-        <v>328.2339475379842</v>
+        <v>328.7291759216584</v>
       </c>
       <c r="D68" t="n">
-        <v>322.5388804495614</v>
+        <v>325.0348299492433</v>
       </c>
       <c r="E68" t="n">
-        <v>326.6393432617188</v>
+        <v>326.0450744628906</v>
       </c>
       <c r="F68" t="n">
-        <v>11737100</v>
+        <v>6738100</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B69" t="n">
-        <v>326.1936353875406</v>
+        <v>318.8049029297019</v>
       </c>
       <c r="C69" t="n">
-        <v>328.7291759216584</v>
+        <v>322.9053354478686</v>
       </c>
       <c r="D69" t="n">
-        <v>325.0348299492433</v>
+        <v>318.1611187929736</v>
       </c>
       <c r="E69" t="n">
-        <v>326.0450744628906</v>
+        <v>321.3899536132812</v>
       </c>
       <c r="F69" t="n">
-        <v>6738100</v>
+        <v>12805100</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B70" t="n">
-        <v>318.8049332018166</v>
+        <v>321.2017547389941</v>
       </c>
       <c r="C70" t="n">
-        <v>322.9053661093398</v>
+        <v>323.7372950994605</v>
       </c>
       <c r="D70" t="n">
-        <v>318.1611490039577</v>
+        <v>307.6029450408882</v>
       </c>
       <c r="E70" t="n">
-        <v>321.3899841308594</v>
+        <v>307.9297790527344</v>
       </c>
       <c r="F70" t="n">
-        <v>12805100</v>
+        <v>19371200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B71" t="n">
-        <v>321.2017865718998</v>
+        <v>305.2556057077196</v>
       </c>
       <c r="C71" t="n">
-        <v>323.7373271836527</v>
+        <v>308.7815926253858</v>
       </c>
       <c r="D71" t="n">
-        <v>307.6029755260753</v>
+        <v>303.1954601804828</v>
       </c>
       <c r="E71" t="n">
-        <v>307.9298095703125</v>
+        <v>304.9287414550781</v>
       </c>
       <c r="F71" t="n">
-        <v>19371200</v>
+        <v>25951500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B72" t="n">
-        <v>305.2556057077196</v>
+        <v>305.5230197927318</v>
       </c>
       <c r="C72" t="n">
-        <v>308.7815926253858</v>
+        <v>309.95031666446</v>
       </c>
       <c r="D72" t="n">
-        <v>303.1954601804828</v>
+        <v>304.8098971346673</v>
       </c>
       <c r="E72" t="n">
-        <v>304.9287414550781</v>
+        <v>306.3054809570312</v>
       </c>
       <c r="F72" t="n">
-        <v>25951500</v>
+        <v>14751400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B73" t="n">
-        <v>305.5230197927318</v>
+        <v>307.385060616362</v>
       </c>
       <c r="C73" t="n">
-        <v>309.95031666446</v>
+        <v>314.1795087286461</v>
       </c>
       <c r="D73" t="n">
-        <v>304.8098971346673</v>
+        <v>307.0383983149945</v>
       </c>
       <c r="E73" t="n">
-        <v>306.3054809570312</v>
+        <v>309.4848022460938</v>
       </c>
       <c r="F73" t="n">
-        <v>14751400</v>
+        <v>14652500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B74" t="n">
-        <v>307.385060616362</v>
+        <v>303.2845981841295</v>
       </c>
       <c r="C74" t="n">
-        <v>314.1795087286461</v>
+        <v>308.1774060521912</v>
       </c>
       <c r="D74" t="n">
-        <v>307.0383983149945</v>
+        <v>298.9761500928895</v>
       </c>
       <c r="E74" t="n">
-        <v>309.4848022460938</v>
+        <v>299.8477478027344</v>
       </c>
       <c r="F74" t="n">
-        <v>14652500</v>
+        <v>12900600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B75" t="n">
-        <v>303.2845981841295</v>
+        <v>300.5311849469782</v>
       </c>
       <c r="C75" t="n">
-        <v>308.1774060521912</v>
+        <v>302.4823658305288</v>
       </c>
       <c r="D75" t="n">
-        <v>298.9761500928895</v>
+        <v>298.2729680555718</v>
       </c>
       <c r="E75" t="n">
-        <v>299.8477478027344</v>
+        <v>299.1544799804688</v>
       </c>
       <c r="F75" t="n">
-        <v>12900600</v>
+        <v>10270100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B76" t="n">
-        <v>300.5311849469782</v>
+        <v>301.9474777854751</v>
       </c>
       <c r="C76" t="n">
-        <v>302.4823658305288</v>
+        <v>305.2555953909441</v>
       </c>
       <c r="D76" t="n">
-        <v>298.2729680555718</v>
+        <v>300.0062112868251</v>
       </c>
       <c r="E76" t="n">
-        <v>299.1544799804688</v>
+        <v>300.729248046875</v>
       </c>
       <c r="F76" t="n">
-        <v>10270100</v>
+        <v>10535800</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B77" t="n">
-        <v>301.9474777854751</v>
+        <v>299.1148112655088</v>
       </c>
       <c r="C77" t="n">
-        <v>305.2555953909441</v>
+        <v>299.4812715954647</v>
       </c>
       <c r="D77" t="n">
-        <v>300.0062112868251</v>
+        <v>293.6772702297321</v>
       </c>
       <c r="E77" t="n">
-        <v>300.729248046875</v>
+        <v>294.8757019042969</v>
       </c>
       <c r="F77" t="n">
-        <v>10535800</v>
+        <v>11107900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B78" t="n">
-        <v>299.1148422218051</v>
+        <v>294.9648486176391</v>
       </c>
       <c r="C78" t="n">
-        <v>299.4813025896872</v>
+        <v>298.8969221500132</v>
       </c>
       <c r="D78" t="n">
-        <v>293.6773006232809</v>
+        <v>294.6083024116733</v>
       </c>
       <c r="E78" t="n">
-        <v>294.875732421875</v>
+        <v>298.1640014648438</v>
       </c>
       <c r="F78" t="n">
-        <v>11107900</v>
+        <v>11752700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B79" t="n">
-        <v>294.9648788077786</v>
+        <v>298.4512235287846</v>
       </c>
       <c r="C79" t="n">
-        <v>298.8969527426069</v>
+        <v>299.0851237823749</v>
       </c>
       <c r="D79" t="n">
-        <v>294.6083325653198</v>
+        <v>295.3016109870806</v>
       </c>
       <c r="E79" t="n">
-        <v>298.1640319824219</v>
+        <v>297.4409790039062</v>
       </c>
       <c r="F79" t="n">
-        <v>11752700</v>
+        <v>11527400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B80" t="n">
-        <v>298.4512235287846</v>
+        <v>297.4013222225187</v>
       </c>
       <c r="C80" t="n">
-        <v>299.0851237823749</v>
+        <v>299.0355829225425</v>
       </c>
       <c r="D80" t="n">
-        <v>295.3016109870806</v>
+        <v>295.2025300603667</v>
       </c>
       <c r="E80" t="n">
-        <v>297.4409790039062</v>
+        <v>297.8965454101562</v>
       </c>
       <c r="F80" t="n">
-        <v>11527400</v>
+        <v>9556700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B81" t="n">
-        <v>297.4013222225187</v>
+        <v>299.5110006693188</v>
       </c>
       <c r="C81" t="n">
-        <v>299.0355829225425</v>
+        <v>303.898671192008</v>
       </c>
       <c r="D81" t="n">
-        <v>295.2025300603667</v>
+        <v>299.3327275624257</v>
       </c>
       <c r="E81" t="n">
-        <v>297.8965454101562</v>
+        <v>303.4926147460938</v>
       </c>
       <c r="F81" t="n">
-        <v>9556700</v>
+        <v>11580000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B82" t="n">
-        <v>299.5110006693188</v>
+        <v>302.333781642444</v>
       </c>
       <c r="C82" t="n">
-        <v>303.898671192008</v>
+        <v>304.9881708986046</v>
       </c>
       <c r="D82" t="n">
-        <v>299.3327275624257</v>
+        <v>299.6694782493637</v>
       </c>
       <c r="E82" t="n">
-        <v>303.4926147460938</v>
+        <v>302.9676818847656</v>
       </c>
       <c r="F82" t="n">
-        <v>11580000</v>
+        <v>11953200</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B83" t="n">
-        <v>302.333781642444</v>
+        <v>301.5513314360023</v>
       </c>
       <c r="C83" t="n">
-        <v>304.9881708986046</v>
+        <v>306.3450888451811</v>
       </c>
       <c r="D83" t="n">
-        <v>299.6694782493637</v>
+        <v>298.4908553932551</v>
       </c>
       <c r="E83" t="n">
-        <v>302.9676818847656</v>
+        <v>305.1961975097656</v>
       </c>
       <c r="F83" t="n">
-        <v>11953200</v>
+        <v>9839400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B84" t="n">
-        <v>301.5513012828864</v>
+        <v>306.7709905338949</v>
       </c>
       <c r="C84" t="n">
-        <v>306.3450582127215</v>
+        <v>313.2286905211348</v>
       </c>
       <c r="D84" t="n">
-        <v>298.4908255461663</v>
+        <v>306.1470044328188</v>
       </c>
       <c r="E84" t="n">
-        <v>305.1961669921875</v>
+        <v>311.8420715332031</v>
       </c>
       <c r="F84" t="n">
-        <v>9839400</v>
+        <v>12688000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B85" t="n">
-        <v>306.7709905338949</v>
+        <v>311.4062598905275</v>
       </c>
       <c r="C85" t="n">
-        <v>313.2286905211348</v>
+        <v>316.2594412620415</v>
       </c>
       <c r="D85" t="n">
-        <v>306.1470044328188</v>
+        <v>311.4062598905275</v>
       </c>
       <c r="E85" t="n">
-        <v>311.8420715332031</v>
+        <v>314.2389221191406</v>
       </c>
       <c r="F85" t="n">
-        <v>12688000</v>
+        <v>9848800</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B86" t="n">
-        <v>311.4062901330092</v>
+        <v>311.9906259989966</v>
       </c>
       <c r="C86" t="n">
-        <v>316.2594719758441</v>
+        <v>312.9909865673853</v>
       </c>
       <c r="D86" t="n">
-        <v>311.4062901330092</v>
+        <v>302.6210112179966</v>
       </c>
       <c r="E86" t="n">
-        <v>314.2389526367188</v>
+        <v>307.1968688964844</v>
       </c>
       <c r="F86" t="n">
-        <v>9848800</v>
+        <v>9388000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B87" t="n">
-        <v>311.9906259989966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="C87" t="n">
-        <v>312.9909865673853</v>
+        <v>321.1522783634816</v>
       </c>
       <c r="D87" t="n">
-        <v>302.6210112179966</v>
+        <v>311.7034102684662</v>
       </c>
       <c r="E87" t="n">
-        <v>307.1968688964844</v>
+        <v>319.3199462890625</v>
       </c>
       <c r="F87" t="n">
-        <v>9388000</v>
+        <v>17797400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B88" t="n">
-        <v>311.7034102684662</v>
+        <v>318.2700781279603</v>
       </c>
       <c r="C88" t="n">
-        <v>321.1522783634816</v>
+        <v>323.2817350541263</v>
       </c>
       <c r="D88" t="n">
-        <v>311.7034102684662</v>
+        <v>317.0518180384032</v>
       </c>
       <c r="E88" t="n">
-        <v>319.3199462890625</v>
+        <v>319.0228271484375</v>
       </c>
       <c r="F88" t="n">
-        <v>17797400</v>
+        <v>11477500</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B89" t="n">
-        <v>318.2700781279603</v>
+        <v>319.4684837021083</v>
       </c>
       <c r="C89" t="n">
-        <v>323.2817350541263</v>
+        <v>323.014298845819</v>
       </c>
       <c r="D89" t="n">
-        <v>317.0518180384032</v>
+        <v>312.1094739861534</v>
       </c>
       <c r="E89" t="n">
-        <v>319.0228271484375</v>
+        <v>315.2392883300781</v>
       </c>
       <c r="F89" t="n">
-        <v>11477500</v>
+        <v>9902200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B90" t="n">
-        <v>319.4684837021083</v>
+        <v>320.1519144431551</v>
       </c>
       <c r="C90" t="n">
-        <v>323.014298845819</v>
+        <v>322.1724337503843</v>
       </c>
       <c r="D90" t="n">
-        <v>312.1094739861534</v>
+        <v>305.7805563960757</v>
       </c>
       <c r="E90" t="n">
-        <v>315.2392883300781</v>
+        <v>307.8505859375</v>
       </c>
       <c r="F90" t="n">
-        <v>9902200</v>
+        <v>8703500</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B91" t="n">
-        <v>320.1518827061323</v>
+        <v>309.2966060076438</v>
       </c>
       <c r="C91" t="n">
-        <v>322.1724018130651</v>
+        <v>310.6238005797982</v>
       </c>
       <c r="D91" t="n">
-        <v>305.7805260837019</v>
+        <v>297.1537232583444</v>
       </c>
       <c r="E91" t="n">
-        <v>307.8505554199219</v>
+        <v>299.7487182617188</v>
       </c>
       <c r="F91" t="n">
-        <v>8703500</v>
+        <v>13443400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B92" t="n">
-        <v>309.2966374972976</v>
+        <v>295.6680481198895</v>
       </c>
       <c r="C92" t="n">
-        <v>310.6238322045743</v>
+        <v>301.3829431862302</v>
       </c>
       <c r="D92" t="n">
-        <v>297.1537535117247</v>
+        <v>293.6871553220786</v>
       </c>
       <c r="E92" t="n">
-        <v>299.7487487792969</v>
+        <v>299.6595458984375</v>
       </c>
       <c r="F92" t="n">
-        <v>13443400</v>
+        <v>9114500</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B93" t="n">
-        <v>295.6680782309701</v>
+        <v>299.8675549474044</v>
       </c>
       <c r="C93" t="n">
-        <v>301.3829738793206</v>
+        <v>305.2951817518681</v>
       </c>
       <c r="D93" t="n">
-        <v>293.6871852314235</v>
+        <v>299.6100292169066</v>
       </c>
       <c r="E93" t="n">
-        <v>299.6595764160156</v>
+        <v>304.19580078125</v>
       </c>
       <c r="F93" t="n">
-        <v>9114500</v>
+        <v>8896800</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B94" t="n">
-        <v>299.8675850307636</v>
+        <v>305.5130974954087</v>
       </c>
       <c r="C94" t="n">
-        <v>305.2952123797385</v>
+        <v>309.2966101142475</v>
       </c>
       <c r="D94" t="n">
-        <v>299.6100592744303</v>
+        <v>304.2849535938903</v>
       </c>
       <c r="E94" t="n">
-        <v>304.1958312988281</v>
+        <v>305.8300476074219</v>
       </c>
       <c r="F94" t="n">
-        <v>8896800</v>
+        <v>7209600</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B95" t="n">
-        <v>305.5130974954087</v>
+        <v>304.2354576365961</v>
       </c>
       <c r="C95" t="n">
-        <v>309.2966101142475</v>
+        <v>306.226234501648</v>
       </c>
       <c r="D95" t="n">
-        <v>304.2849535938903</v>
+        <v>302.2050242231491</v>
       </c>
       <c r="E95" t="n">
-        <v>305.8300476074219</v>
+        <v>305.1070251464844</v>
       </c>
       <c r="F95" t="n">
-        <v>7209600</v>
+        <v>6737700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B96" t="n">
-        <v>304.2354272061944</v>
+        <v>305.4536802835111</v>
       </c>
       <c r="C96" t="n">
-        <v>306.2262038721237</v>
+        <v>308.0288471084009</v>
       </c>
       <c r="D96" t="n">
-        <v>302.2049939958365</v>
+        <v>302.7596647203387</v>
       </c>
       <c r="E96" t="n">
-        <v>305.1069946289062</v>
+        <v>307.8208618164062</v>
       </c>
       <c r="F96" t="n">
-        <v>6737700</v>
+        <v>7792700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B97" t="n">
-        <v>305.4536802835111</v>
+        <v>305.8498774375392</v>
       </c>
       <c r="C97" t="n">
-        <v>308.0288471084009</v>
+        <v>308.028871901531</v>
       </c>
       <c r="D97" t="n">
-        <v>302.7596647203387</v>
+        <v>292.2807780649544</v>
       </c>
       <c r="E97" t="n">
-        <v>307.8208618164062</v>
+        <v>294.8262329101562</v>
       </c>
       <c r="F97" t="n">
-        <v>7792700</v>
+        <v>12955400</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B98" t="n">
-        <v>305.8498457788994</v>
+        <v>293.9843218466586</v>
       </c>
       <c r="C98" t="n">
-        <v>308.0288400173425</v>
+        <v>296.886322684036</v>
       </c>
       <c r="D98" t="n">
-        <v>292.2807478108573</v>
+        <v>288.5962907533433</v>
       </c>
       <c r="E98" t="n">
-        <v>294.8262023925781</v>
+        <v>294.459716796875</v>
       </c>
       <c r="F98" t="n">
-        <v>12955400</v>
+        <v>13554100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B99" t="n">
-        <v>293.9843218466586</v>
+        <v>295.7869207463737</v>
       </c>
       <c r="C99" t="n">
-        <v>296.886322684036</v>
+        <v>300.7589506810849</v>
       </c>
       <c r="D99" t="n">
-        <v>288.5962907533433</v>
+        <v>294.1724883145502</v>
       </c>
       <c r="E99" t="n">
-        <v>294.459716796875</v>
+        <v>300.4023742675781</